--- a/Ведомость ТКИ-441 2026-2027.xlsx
+++ b/Ведомость ТКИ-441 2026-2027.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\StegMethods\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82CC1D3E-004E-4BBE-BE68-9BEC98AD73E6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F973D5DE-4589-4428-9638-3FA56A88DF65}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="139">
   <si>
     <t>Ведомость посещаемости занятий студентами группы ТКИ РУТ МИИТ</t>
   </si>
@@ -232,12 +232,6 @@
     <t>НОВЫЙ МЕТОД СТЕГОАНАЛИЗА ТЕКСТОВЫХ ДАННЫХ, ПОЛУЧЕННЫХ КОДИРОВАНИЕМ ДЛИН СЕРИЙ СИНОНИМОВ / Нечта И.В. // Безопасность информационных технологий. 2018. Т. 25. № 2. С. 114-120.</t>
   </si>
   <si>
-    <t>Вводная лекция. ДПФ</t>
-  </si>
-  <si>
-    <t>Преобразование Фурье</t>
-  </si>
-  <si>
     <t>Автоношкин</t>
   </si>
   <si>
@@ -259,9 +253,6 @@
     <t>Отдельное задание про граф, соц сети и меню</t>
   </si>
   <si>
-    <t>ГПСЧ. Преобразование Фурье</t>
-  </si>
-  <si>
     <t>БПФ</t>
   </si>
   <si>
@@ -431,6 +422,27 @@
   </si>
   <si>
     <t>2 задание Конахович. Скрытие в изображениях и звуковых файлах. К.р. Форензика</t>
+  </si>
+  <si>
+    <t>б</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>л</t>
+  </si>
+  <si>
+    <t>п</t>
+  </si>
+  <si>
+    <t>ГПСЧ.</t>
+  </si>
+  <si>
+    <t>Вводная лекция. Множества ортогональных функций.</t>
+  </si>
+  <si>
+    <t>Множества ортогональных функций на основе перямоугольных импульсов.</t>
   </si>
 </sst>
 </file>
@@ -690,7 +702,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -759,18 +771,22 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -789,22 +805,185 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -821,13 +1000,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>37</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
+      <xdr:col>42</xdr:col>
       <xdr:colOff>485775</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -1129,237 +1308,318 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BB65"/>
+  <dimension ref="A1:BQ65"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="35.5703125" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="19" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" customWidth="1"/>
-    <col min="21" max="21" width="11.5703125" customWidth="1"/>
-    <col min="24" max="24" width="12.28515625" customWidth="1"/>
-    <col min="25" max="25" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.7109375" customWidth="1"/>
-    <col min="27" max="27" width="11.85546875" customWidth="1"/>
-    <col min="28" max="28" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="9.140625" style="12"/>
-    <col min="34" max="34" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="11.5703125" customWidth="1"/>
-    <col min="51" max="51" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="35" width="10.85546875" customWidth="1"/>
+    <col min="36" max="36" width="11.5703125" customWidth="1"/>
+    <col min="39" max="39" width="12.28515625" customWidth="1"/>
+    <col min="40" max="40" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="15.7109375" customWidth="1"/>
+    <col min="42" max="42" width="11.85546875" customWidth="1"/>
+    <col min="43" max="43" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="9.140625" style="12"/>
+    <col min="49" max="49" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="11.5703125" customWidth="1"/>
+    <col min="66" max="66" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
-    </row>
-    <row r="2" spans="1:53" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="40"/>
+      <c r="U1" s="40"/>
+      <c r="V1" s="40"/>
+      <c r="W1" s="40"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="40"/>
+      <c r="Z1" s="40"/>
+      <c r="AA1" s="40"/>
+      <c r="AB1" s="40"/>
+      <c r="AC1" s="40"/>
+      <c r="AD1" s="40"/>
+      <c r="AE1" s="40"/>
+      <c r="AF1" s="40"/>
+      <c r="AG1" s="40"/>
+      <c r="AH1" s="40"/>
+      <c r="AI1" s="40"/>
+      <c r="AJ1" s="40"/>
+      <c r="AK1" s="40"/>
+      <c r="AL1" s="40"/>
+      <c r="AM1" s="40"/>
+      <c r="AN1" s="40"/>
+    </row>
+    <row r="2" spans="1:68" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="34" t="s">
+      <c r="B2" s="41"/>
+      <c r="C2" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="34">
-        <v>46269</v>
-      </c>
-      <c r="E2" s="34">
-        <v>46276</v>
-      </c>
-      <c r="F2" s="48">
-        <v>46283</v>
-      </c>
-      <c r="G2" s="34">
-        <v>46290</v>
-      </c>
-      <c r="H2" s="48">
-        <v>46297</v>
-      </c>
-      <c r="I2" s="34">
-        <v>46304</v>
-      </c>
-      <c r="J2" s="48">
-        <v>46311</v>
-      </c>
-      <c r="K2" s="34">
-        <v>46318</v>
-      </c>
-      <c r="L2" s="48">
-        <v>46325</v>
-      </c>
-      <c r="M2" s="34">
-        <v>46332</v>
-      </c>
-      <c r="N2" s="48">
-        <v>46339</v>
-      </c>
-      <c r="O2" s="34">
-        <v>46346</v>
-      </c>
-      <c r="P2" s="48">
-        <v>46353</v>
-      </c>
-      <c r="Q2" s="34">
-        <v>46360</v>
-      </c>
-      <c r="R2" s="48">
-        <v>46367</v>
-      </c>
-      <c r="S2" s="34">
-        <v>46374</v>
-      </c>
-      <c r="T2" s="34">
-        <v>46381</v>
-      </c>
-      <c r="U2" s="35" t="s">
+      <c r="D2" s="50">
+        <v>46268</v>
+      </c>
+      <c r="E2" s="50">
+        <v>46272</v>
+      </c>
+      <c r="F2" s="50">
+        <v>46275</v>
+      </c>
+      <c r="G2" s="50">
+        <v>46279</v>
+      </c>
+      <c r="H2" s="51">
+        <v>46282</v>
+      </c>
+      <c r="I2" s="50">
+        <v>46286</v>
+      </c>
+      <c r="J2" s="51">
+        <v>46289</v>
+      </c>
+      <c r="K2" s="50">
+        <v>46293</v>
+      </c>
+      <c r="L2" s="51">
+        <v>46296</v>
+      </c>
+      <c r="M2" s="50">
+        <v>46300</v>
+      </c>
+      <c r="N2" s="51">
+        <v>46303</v>
+      </c>
+      <c r="O2" s="50">
+        <v>46307</v>
+      </c>
+      <c r="P2" s="51">
+        <v>46310</v>
+      </c>
+      <c r="Q2" s="50">
+        <v>46314</v>
+      </c>
+      <c r="R2" s="51">
+        <v>46317</v>
+      </c>
+      <c r="S2" s="50">
+        <v>46321</v>
+      </c>
+      <c r="T2" s="50">
+        <v>46324</v>
+      </c>
+      <c r="U2" s="50">
+        <v>46328</v>
+      </c>
+      <c r="V2" s="50">
+        <v>46331</v>
+      </c>
+      <c r="W2" s="50">
+        <v>46335</v>
+      </c>
+      <c r="X2" s="50">
+        <v>46338</v>
+      </c>
+      <c r="Y2" s="50">
+        <v>46342</v>
+      </c>
+      <c r="Z2" s="50">
+        <v>46345</v>
+      </c>
+      <c r="AA2" s="50">
+        <v>46349</v>
+      </c>
+      <c r="AB2" s="50">
+        <v>46352</v>
+      </c>
+      <c r="AC2" s="50">
+        <v>46356</v>
+      </c>
+      <c r="AD2" s="51">
+        <v>46359</v>
+      </c>
+      <c r="AE2" s="51">
+        <v>46363</v>
+      </c>
+      <c r="AF2" s="51">
+        <v>46366</v>
+      </c>
+      <c r="AG2" s="51">
+        <v>46370</v>
+      </c>
+      <c r="AH2" s="51">
+        <v>46373</v>
+      </c>
+      <c r="AI2" s="51">
+        <v>46377</v>
+      </c>
+      <c r="AJ2" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="V2" s="35"/>
-      <c r="W2" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="X2" s="37"/>
-      <c r="Y2" s="38"/>
-      <c r="Z2" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="AA2" s="37"/>
-      <c r="AB2" s="38"/>
-      <c r="AC2" s="36" t="s">
+      <c r="AK2" s="41"/>
+      <c r="AL2" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM2" s="35"/>
+      <c r="AN2" s="36"/>
+      <c r="AO2" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="AP2" s="35"/>
+      <c r="AQ2" s="36"/>
+      <c r="AR2" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="AD2" s="37"/>
-      <c r="AE2" s="38"/>
-      <c r="AF2" s="36" t="s">
+      <c r="AS2" s="35"/>
+      <c r="AT2" s="36"/>
+      <c r="AU2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="AG2" s="37"/>
-      <c r="AH2" s="38"/>
-      <c r="AI2" s="36" t="s">
+      <c r="AV2" s="35"/>
+      <c r="AW2" s="36"/>
+      <c r="AX2" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="AJ2" s="37"/>
-      <c r="AK2" s="37"/>
-      <c r="AL2" s="38"/>
-      <c r="AM2" s="36" t="s">
+      <c r="AY2" s="35"/>
+      <c r="AZ2" s="35"/>
+      <c r="BA2" s="36"/>
+      <c r="BB2" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="AN2" s="37"/>
-      <c r="AO2" s="37"/>
-      <c r="AP2" s="38" t="s">
+      <c r="BC2" s="35"/>
+      <c r="BD2" s="35"/>
+      <c r="BE2" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="AQ2" s="36" t="s">
+      <c r="BF2" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="AR2" s="37"/>
-      <c r="AS2" s="38"/>
-      <c r="AT2" s="36" t="s">
+      <c r="BG2" s="35"/>
+      <c r="BH2" s="36"/>
+      <c r="BI2" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="AU2" s="37"/>
-      <c r="AV2" s="38"/>
-    </row>
-    <row r="3" spans="1:53" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BJ2" s="35"/>
+      <c r="BK2" s="36"/>
+    </row>
+    <row r="3" spans="1:68" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="49"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="49"/>
-      <c r="Q3" s="35"/>
-      <c r="R3" s="49"/>
-      <c r="S3" s="35"/>
-      <c r="T3" s="35"/>
-      <c r="U3" s="35"/>
-      <c r="V3" s="35"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="51"/>
-      <c r="Y3" s="41"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="40"/>
-      <c r="AB3" s="41"/>
-      <c r="AC3" s="39"/>
-      <c r="AD3" s="40"/>
-      <c r="AE3" s="41"/>
-      <c r="AF3" s="39"/>
-      <c r="AG3" s="40"/>
-      <c r="AH3" s="41"/>
-      <c r="AI3" s="39"/>
-      <c r="AJ3" s="40"/>
-      <c r="AK3" s="40"/>
-      <c r="AL3" s="41"/>
-      <c r="AM3" s="39"/>
-      <c r="AN3" s="40"/>
-      <c r="AO3" s="40"/>
-      <c r="AP3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="52"/>
+      <c r="P3" s="53"/>
+      <c r="Q3" s="52"/>
+      <c r="R3" s="53"/>
+      <c r="S3" s="52"/>
+      <c r="T3" s="52"/>
+      <c r="U3" s="52"/>
+      <c r="V3" s="52"/>
+      <c r="W3" s="52"/>
+      <c r="X3" s="52"/>
+      <c r="Y3" s="52"/>
+      <c r="Z3" s="52"/>
+      <c r="AA3" s="52"/>
+      <c r="AB3" s="52"/>
+      <c r="AC3" s="52"/>
+      <c r="AD3" s="53"/>
+      <c r="AE3" s="53"/>
+      <c r="AF3" s="53"/>
+      <c r="AG3" s="53"/>
+      <c r="AH3" s="53"/>
+      <c r="AI3" s="53"/>
+      <c r="AJ3" s="41"/>
+      <c r="AK3" s="41"/>
+      <c r="AL3" s="37"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="39"/>
+      <c r="AO3" s="37"/>
+      <c r="AP3" s="38"/>
       <c r="AQ3" s="39"/>
-      <c r="AR3" s="40"/>
-      <c r="AS3" s="41"/>
+      <c r="AR3" s="37"/>
+      <c r="AS3" s="38"/>
       <c r="AT3" s="39"/>
-      <c r="AU3" s="40"/>
-      <c r="AV3" s="41"/>
-    </row>
-    <row r="4" spans="1:53" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="AU3" s="37"/>
+      <c r="AV3" s="38"/>
+      <c r="AW3" s="39"/>
+      <c r="AX3" s="37"/>
+      <c r="AY3" s="38"/>
+      <c r="AZ3" s="38"/>
+      <c r="BA3" s="39"/>
+      <c r="BB3" s="37"/>
+      <c r="BC3" s="38"/>
+      <c r="BD3" s="38"/>
+      <c r="BE3" s="39"/>
+      <c r="BF3" s="37"/>
+      <c r="BG3" s="38"/>
+      <c r="BH3" s="39"/>
+      <c r="BI3" s="37"/>
+      <c r="BJ3" s="38"/>
+      <c r="BK3" s="39"/>
+    </row>
+    <row r="4" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C4" s="4">
         <v>1</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
+        <v>128</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H4" s="17"/>
       <c r="I4" s="17"/>
       <c r="J4" s="17"/>
@@ -1373,51 +1633,72 @@
       <c r="R4" s="17"/>
       <c r="S4" s="17"/>
       <c r="T4" s="17"/>
-      <c r="U4" s="18"/>
+      <c r="U4" s="17"/>
       <c r="V4" s="17"/>
-      <c r="W4" s="19"/>
-      <c r="X4" s="19"/>
-      <c r="Y4" s="18"/>
-      <c r="Z4" s="20"/>
-      <c r="AA4" s="19"/>
-      <c r="AB4" s="21"/>
+      <c r="W4" s="17"/>
+      <c r="X4" s="17"/>
+      <c r="Y4" s="17"/>
+      <c r="Z4" s="17"/>
+      <c r="AA4" s="17"/>
+      <c r="AB4" s="17"/>
       <c r="AC4" s="17"/>
-      <c r="AD4" s="22"/>
-      <c r="AE4" s="18"/>
+      <c r="AD4" s="17"/>
+      <c r="AE4" s="17"/>
       <c r="AF4" s="17"/>
-      <c r="AG4" s="22"/>
-      <c r="AH4" s="21"/>
+      <c r="AG4" s="17"/>
+      <c r="AH4" s="17"/>
       <c r="AI4" s="17"/>
-      <c r="AJ4" s="17"/>
+      <c r="AJ4" s="18"/>
       <c r="AK4" s="17"/>
-      <c r="AL4" s="18"/>
-      <c r="AM4" s="17"/>
-      <c r="AN4" s="17"/>
-      <c r="AO4" s="17"/>
-      <c r="AP4" s="18"/>
-      <c r="AQ4" s="18"/>
+      <c r="AL4" s="19"/>
+      <c r="AM4" s="19"/>
+      <c r="AN4" s="18"/>
+      <c r="AO4" s="20"/>
+      <c r="AP4" s="19"/>
+      <c r="AQ4" s="21"/>
       <c r="AR4" s="17"/>
-      <c r="AS4" s="17"/>
-      <c r="AT4" s="17"/>
+      <c r="AS4" s="22"/>
+      <c r="AT4" s="18"/>
       <c r="AU4" s="17"/>
-      <c r="AV4" s="17"/>
-    </row>
-    <row r="5" spans="1:53" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="AV4" s="22"/>
+      <c r="AW4" s="21"/>
+      <c r="AX4" s="17"/>
+      <c r="AY4" s="17"/>
+      <c r="AZ4" s="17"/>
+      <c r="BA4" s="18"/>
+      <c r="BB4" s="17"/>
+      <c r="BC4" s="17"/>
+      <c r="BD4" s="17"/>
+      <c r="BE4" s="18"/>
+      <c r="BF4" s="18"/>
+      <c r="BG4" s="17"/>
+      <c r="BH4" s="17"/>
+      <c r="BI4" s="17"/>
+      <c r="BJ4" s="17"/>
+      <c r="BK4" s="17"/>
+    </row>
+    <row r="5" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C5" s="4">
         <v>2</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
+        <v>128</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H5" s="17"/>
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
@@ -1431,66 +1712,87 @@
       <c r="R5" s="17"/>
       <c r="S5" s="17"/>
       <c r="T5" s="17"/>
-      <c r="U5" s="18"/>
+      <c r="U5" s="17"/>
       <c r="V5" s="17"/>
-      <c r="W5" s="19"/>
-      <c r="X5" s="19"/>
-      <c r="Y5" s="21"/>
-      <c r="Z5" s="20"/>
-      <c r="AA5" s="19"/>
-      <c r="AB5" s="21"/>
+      <c r="W5" s="17"/>
+      <c r="X5" s="17"/>
+      <c r="Y5" s="17"/>
+      <c r="Z5" s="17"/>
+      <c r="AA5" s="17"/>
+      <c r="AB5" s="17"/>
       <c r="AC5" s="17"/>
       <c r="AD5" s="17"/>
-      <c r="AE5" s="18"/>
+      <c r="AE5" s="17"/>
       <c r="AF5" s="17"/>
       <c r="AG5" s="17"/>
-      <c r="AH5" s="18"/>
+      <c r="AH5" s="17"/>
       <c r="AI5" s="17"/>
-      <c r="AJ5" s="17"/>
+      <c r="AJ5" s="18"/>
       <c r="AK5" s="17"/>
-      <c r="AL5" s="18"/>
-      <c r="AM5" s="17"/>
-      <c r="AN5" s="17"/>
-      <c r="AO5" s="17"/>
-      <c r="AP5" s="18"/>
-      <c r="AQ5" s="18"/>
+      <c r="AL5" s="19"/>
+      <c r="AM5" s="19"/>
+      <c r="AN5" s="21"/>
+      <c r="AO5" s="20"/>
+      <c r="AP5" s="19"/>
+      <c r="AQ5" s="21"/>
       <c r="AR5" s="17"/>
       <c r="AS5" s="17"/>
-      <c r="AT5" s="17"/>
+      <c r="AT5" s="18"/>
       <c r="AU5" s="17"/>
       <c r="AV5" s="17"/>
-      <c r="AW5">
+      <c r="AW5" s="18"/>
+      <c r="AX5" s="17"/>
+      <c r="AY5" s="17"/>
+      <c r="AZ5" s="17"/>
+      <c r="BA5" s="18"/>
+      <c r="BB5" s="17"/>
+      <c r="BC5" s="17"/>
+      <c r="BD5" s="17"/>
+      <c r="BE5" s="18"/>
+      <c r="BF5" s="18"/>
+      <c r="BG5" s="17"/>
+      <c r="BH5" s="17"/>
+      <c r="BI5" s="17"/>
+      <c r="BJ5" s="17"/>
+      <c r="BK5" s="17"/>
+      <c r="BL5">
         <v>1</v>
       </c>
-      <c r="AX5" t="s">
+      <c r="BM5" t="s">
         <v>18</v>
       </c>
-      <c r="AY5" s="7" t="s">
+      <c r="BN5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="AZ5" t="s">
+      <c r="BO5" t="s">
         <v>20</v>
       </c>
-      <c r="BA5" t="s">
+      <c r="BP5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:53" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:68" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C6" s="4">
         <v>3</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
+        <v>128</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H6" s="17"/>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
@@ -1504,57 +1806,78 @@
       <c r="R6" s="17"/>
       <c r="S6" s="17"/>
       <c r="T6" s="17"/>
-      <c r="U6" s="18"/>
+      <c r="U6" s="17"/>
       <c r="V6" s="17"/>
-      <c r="W6" s="19"/>
-      <c r="X6" s="19"/>
-      <c r="Y6" s="21"/>
-      <c r="Z6" s="20"/>
-      <c r="AA6" s="19"/>
-      <c r="AB6" s="21"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="17"/>
+      <c r="Z6" s="17"/>
+      <c r="AA6" s="17"/>
+      <c r="AB6" s="17"/>
       <c r="AC6" s="17"/>
-      <c r="AD6" s="19"/>
-      <c r="AE6" s="18"/>
+      <c r="AD6" s="17"/>
+      <c r="AE6" s="17"/>
       <c r="AF6" s="17"/>
-      <c r="AG6" s="22"/>
-      <c r="AH6" s="18"/>
+      <c r="AG6" s="17"/>
+      <c r="AH6" s="17"/>
       <c r="AI6" s="17"/>
-      <c r="AJ6" s="22"/>
+      <c r="AJ6" s="18"/>
       <c r="AK6" s="17"/>
-      <c r="AL6" s="18"/>
-      <c r="AM6" s="17"/>
-      <c r="AN6" s="17"/>
-      <c r="AO6" s="17"/>
-      <c r="AP6" s="18"/>
-      <c r="AQ6" s="18"/>
+      <c r="AL6" s="19"/>
+      <c r="AM6" s="19"/>
+      <c r="AN6" s="21"/>
+      <c r="AO6" s="20"/>
+      <c r="AP6" s="19"/>
+      <c r="AQ6" s="21"/>
       <c r="AR6" s="17"/>
-      <c r="AS6" s="17"/>
-      <c r="AT6" s="17"/>
+      <c r="AS6" s="19"/>
+      <c r="AT6" s="18"/>
       <c r="AU6" s="17"/>
-      <c r="AV6" s="17"/>
-      <c r="AW6">
+      <c r="AV6" s="22"/>
+      <c r="AW6" s="18"/>
+      <c r="AX6" s="17"/>
+      <c r="AY6" s="22"/>
+      <c r="AZ6" s="17"/>
+      <c r="BA6" s="18"/>
+      <c r="BB6" s="17"/>
+      <c r="BC6" s="17"/>
+      <c r="BD6" s="17"/>
+      <c r="BE6" s="18"/>
+      <c r="BF6" s="18"/>
+      <c r="BG6" s="17"/>
+      <c r="BH6" s="17"/>
+      <c r="BI6" s="17"/>
+      <c r="BJ6" s="17"/>
+      <c r="BK6" s="17"/>
+      <c r="BL6">
         <v>2</v>
       </c>
-      <c r="AY6" s="7" t="s">
+      <c r="BN6" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:53" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:68" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C7" s="4">
         <v>4</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
+        <v>128</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H7" s="17"/>
       <c r="I7" s="17"/>
       <c r="J7" s="23"/>
@@ -1570,55 +1893,76 @@
       <c r="T7" s="17"/>
       <c r="U7" s="17"/>
       <c r="V7" s="17"/>
-      <c r="W7" s="19"/>
-      <c r="X7" s="19"/>
-      <c r="Y7" s="25"/>
-      <c r="Z7" s="20"/>
-      <c r="AA7" s="19"/>
+      <c r="W7" s="17"/>
+      <c r="X7" s="17"/>
+      <c r="Y7" s="17"/>
+      <c r="Z7" s="17"/>
+      <c r="AA7" s="17"/>
       <c r="AB7" s="17"/>
       <c r="AC7" s="17"/>
-      <c r="AD7" s="19"/>
+      <c r="AD7" s="17"/>
       <c r="AE7" s="17"/>
       <c r="AF7" s="17"/>
       <c r="AG7" s="17"/>
       <c r="AH7" s="17"/>
       <c r="AI7" s="17"/>
-      <c r="AJ7" s="22"/>
+      <c r="AJ7" s="17"/>
       <c r="AK7" s="17"/>
-      <c r="AL7" s="17"/>
-      <c r="AM7" s="17"/>
-      <c r="AN7" s="17"/>
-      <c r="AO7" s="17"/>
-      <c r="AP7" s="17"/>
+      <c r="AL7" s="19"/>
+      <c r="AM7" s="19"/>
+      <c r="AN7" s="25"/>
+      <c r="AO7" s="20"/>
+      <c r="AP7" s="19"/>
       <c r="AQ7" s="17"/>
       <c r="AR7" s="17"/>
-      <c r="AS7" s="17"/>
+      <c r="AS7" s="19"/>
       <c r="AT7" s="17"/>
       <c r="AU7" s="17"/>
       <c r="AV7" s="17"/>
-      <c r="AW7" s="16">
+      <c r="AW7" s="17"/>
+      <c r="AX7" s="17"/>
+      <c r="AY7" s="22"/>
+      <c r="AZ7" s="17"/>
+      <c r="BA7" s="17"/>
+      <c r="BB7" s="17"/>
+      <c r="BC7" s="17"/>
+      <c r="BD7" s="17"/>
+      <c r="BE7" s="17"/>
+      <c r="BF7" s="17"/>
+      <c r="BG7" s="17"/>
+      <c r="BH7" s="17"/>
+      <c r="BI7" s="17"/>
+      <c r="BJ7" s="17"/>
+      <c r="BK7" s="17"/>
+      <c r="BL7" s="16">
         <v>3</v>
       </c>
-      <c r="AY7" s="7" t="s">
+      <c r="BN7" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:53" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C8" s="4">
         <v>17</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
+        <v>129</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>129</v>
+      </c>
       <c r="H8" s="17"/>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
@@ -1634,11 +1978,11 @@
       <c r="T8" s="17"/>
       <c r="U8" s="17"/>
       <c r="V8" s="17"/>
-      <c r="W8" s="19"/>
-      <c r="X8" s="19"/>
-      <c r="Y8" s="25"/>
-      <c r="Z8" s="20"/>
-      <c r="AA8" s="19"/>
+      <c r="W8" s="17"/>
+      <c r="X8" s="17"/>
+      <c r="Y8" s="17"/>
+      <c r="Z8" s="17"/>
+      <c r="AA8" s="17"/>
       <c r="AB8" s="17"/>
       <c r="AC8" s="17"/>
       <c r="AD8" s="17"/>
@@ -1649,40 +1993,61 @@
       <c r="AI8" s="17"/>
       <c r="AJ8" s="17"/>
       <c r="AK8" s="17"/>
-      <c r="AL8" s="17"/>
-      <c r="AM8" s="17"/>
-      <c r="AN8" s="17"/>
-      <c r="AO8" s="17"/>
-      <c r="AP8" s="17"/>
+      <c r="AL8" s="19"/>
+      <c r="AM8" s="19"/>
+      <c r="AN8" s="25"/>
+      <c r="AO8" s="20"/>
+      <c r="AP8" s="19"/>
       <c r="AQ8" s="17"/>
       <c r="AR8" s="17"/>
       <c r="AS8" s="17"/>
       <c r="AT8" s="17"/>
       <c r="AU8" s="17"/>
       <c r="AV8" s="17"/>
-      <c r="AW8">
+      <c r="AW8" s="17"/>
+      <c r="AX8" s="17"/>
+      <c r="AY8" s="17"/>
+      <c r="AZ8" s="17"/>
+      <c r="BA8" s="17"/>
+      <c r="BB8" s="17"/>
+      <c r="BC8" s="17"/>
+      <c r="BD8" s="17"/>
+      <c r="BE8" s="17"/>
+      <c r="BF8" s="17"/>
+      <c r="BG8" s="17"/>
+      <c r="BH8" s="17"/>
+      <c r="BI8" s="17"/>
+      <c r="BJ8" s="17"/>
+      <c r="BK8" s="17"/>
+      <c r="BL8">
         <v>4</v>
       </c>
-      <c r="AY8" t="s">
+      <c r="BN8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:53" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C9" s="4">
         <v>5</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
+        <v>128</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
@@ -1696,42 +2061,57 @@
       <c r="R9" s="17"/>
       <c r="S9" s="17"/>
       <c r="T9" s="17"/>
-      <c r="U9" s="18"/>
+      <c r="U9" s="17"/>
       <c r="V9" s="17"/>
-      <c r="W9" s="19"/>
-      <c r="X9" s="19"/>
-      <c r="Y9" s="21"/>
-      <c r="Z9" s="20"/>
-      <c r="AA9" s="19"/>
-      <c r="AB9" s="21"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="17"/>
+      <c r="Y9" s="17"/>
+      <c r="Z9" s="17"/>
+      <c r="AA9" s="17"/>
+      <c r="AB9" s="17"/>
       <c r="AC9" s="17"/>
       <c r="AD9" s="17"/>
-      <c r="AE9" s="18"/>
+      <c r="AE9" s="17"/>
       <c r="AF9" s="17"/>
       <c r="AG9" s="17"/>
-      <c r="AH9" s="18"/>
+      <c r="AH9" s="17"/>
       <c r="AI9" s="17"/>
-      <c r="AJ9" s="17"/>
+      <c r="AJ9" s="18"/>
       <c r="AK9" s="17"/>
-      <c r="AL9" s="18"/>
-      <c r="AM9" s="17"/>
-      <c r="AN9" s="17"/>
-      <c r="AO9" s="17"/>
-      <c r="AP9" s="18"/>
-      <c r="AQ9" s="18"/>
+      <c r="AL9" s="19"/>
+      <c r="AM9" s="19"/>
+      <c r="AN9" s="21"/>
+      <c r="AO9" s="20"/>
+      <c r="AP9" s="19"/>
+      <c r="AQ9" s="21"/>
       <c r="AR9" s="17"/>
       <c r="AS9" s="17"/>
-      <c r="AT9" s="17"/>
+      <c r="AT9" s="18"/>
       <c r="AU9" s="17"/>
       <c r="AV9" s="17"/>
-      <c r="AW9">
+      <c r="AW9" s="18"/>
+      <c r="AX9" s="17"/>
+      <c r="AY9" s="17"/>
+      <c r="AZ9" s="17"/>
+      <c r="BA9" s="18"/>
+      <c r="BB9" s="17"/>
+      <c r="BC9" s="17"/>
+      <c r="BD9" s="17"/>
+      <c r="BE9" s="18"/>
+      <c r="BF9" s="18"/>
+      <c r="BG9" s="17"/>
+      <c r="BH9" s="17"/>
+      <c r="BI9" s="17"/>
+      <c r="BJ9" s="17"/>
+      <c r="BK9" s="17"/>
+      <c r="BL9">
         <v>5</v>
       </c>
-      <c r="AY9" t="s">
+      <c r="BN9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:53" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -1742,11 +2122,17 @@
         <v>6</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
+        <v>128</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H10" s="17"/>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
@@ -1760,57 +2146,78 @@
       <c r="R10" s="17"/>
       <c r="S10" s="17"/>
       <c r="T10" s="17"/>
-      <c r="U10" s="18"/>
+      <c r="U10" s="17"/>
       <c r="V10" s="17"/>
-      <c r="W10" s="19"/>
-      <c r="X10" s="19"/>
-      <c r="Y10" s="21"/>
-      <c r="Z10" s="20"/>
-      <c r="AA10" s="19"/>
-      <c r="AB10" s="18"/>
+      <c r="W10" s="17"/>
+      <c r="X10" s="17"/>
+      <c r="Y10" s="17"/>
+      <c r="Z10" s="17"/>
+      <c r="AA10" s="17"/>
+      <c r="AB10" s="17"/>
       <c r="AC10" s="17"/>
-      <c r="AD10" s="22"/>
-      <c r="AE10" s="18"/>
+      <c r="AD10" s="17"/>
+      <c r="AE10" s="17"/>
       <c r="AF10" s="17"/>
       <c r="AG10" s="17"/>
       <c r="AH10" s="17"/>
       <c r="AI10" s="17"/>
-      <c r="AJ10" s="17"/>
+      <c r="AJ10" s="18"/>
       <c r="AK10" s="17"/>
-      <c r="AL10" s="18"/>
-      <c r="AM10" s="17"/>
-      <c r="AN10" s="17"/>
-      <c r="AO10" s="17"/>
-      <c r="AP10" s="18"/>
+      <c r="AL10" s="19"/>
+      <c r="AM10" s="19"/>
+      <c r="AN10" s="21"/>
+      <c r="AO10" s="20"/>
+      <c r="AP10" s="19"/>
       <c r="AQ10" s="18"/>
       <c r="AR10" s="17"/>
-      <c r="AS10" s="17"/>
-      <c r="AT10" s="17"/>
+      <c r="AS10" s="22"/>
+      <c r="AT10" s="18"/>
       <c r="AU10" s="17"/>
       <c r="AV10" s="17"/>
-      <c r="AW10">
+      <c r="AW10" s="17"/>
+      <c r="AX10" s="17"/>
+      <c r="AY10" s="17"/>
+      <c r="AZ10" s="17"/>
+      <c r="BA10" s="18"/>
+      <c r="BB10" s="17"/>
+      <c r="BC10" s="17"/>
+      <c r="BD10" s="17"/>
+      <c r="BE10" s="18"/>
+      <c r="BF10" s="18"/>
+      <c r="BG10" s="17"/>
+      <c r="BH10" s="17"/>
+      <c r="BI10" s="17"/>
+      <c r="BJ10" s="17"/>
+      <c r="BK10" s="17"/>
+      <c r="BL10">
         <v>6</v>
       </c>
-      <c r="AY10" t="s">
+      <c r="BN10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:53" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C11" s="4">
         <v>7</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
+        <v>128</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H11" s="17"/>
       <c r="I11" s="17"/>
       <c r="J11" s="17"/>
@@ -1824,57 +2231,78 @@
       <c r="R11" s="17"/>
       <c r="S11" s="17"/>
       <c r="T11" s="17"/>
-      <c r="U11" s="18"/>
+      <c r="U11" s="17"/>
       <c r="V11" s="17"/>
-      <c r="W11" s="19"/>
-      <c r="X11" s="19"/>
-      <c r="Y11" s="21"/>
-      <c r="Z11" s="20"/>
-      <c r="AA11" s="19"/>
-      <c r="AB11" s="18"/>
+      <c r="W11" s="17"/>
+      <c r="X11" s="17"/>
+      <c r="Y11" s="17"/>
+      <c r="Z11" s="17"/>
+      <c r="AA11" s="17"/>
+      <c r="AB11" s="17"/>
       <c r="AC11" s="17"/>
-      <c r="AD11" s="22"/>
-      <c r="AE11" s="18"/>
+      <c r="AD11" s="17"/>
+      <c r="AE11" s="17"/>
       <c r="AF11" s="17"/>
       <c r="AG11" s="17"/>
-      <c r="AH11" s="18"/>
+      <c r="AH11" s="17"/>
       <c r="AI11" s="17"/>
-      <c r="AJ11" s="17"/>
+      <c r="AJ11" s="18"/>
       <c r="AK11" s="17"/>
-      <c r="AL11" s="18"/>
-      <c r="AM11" s="17"/>
-      <c r="AN11" s="17"/>
-      <c r="AO11" s="17"/>
-      <c r="AP11" s="18"/>
+      <c r="AL11" s="19"/>
+      <c r="AM11" s="19"/>
+      <c r="AN11" s="21"/>
+      <c r="AO11" s="20"/>
+      <c r="AP11" s="19"/>
       <c r="AQ11" s="18"/>
       <c r="AR11" s="17"/>
-      <c r="AS11" s="17"/>
-      <c r="AT11" s="17"/>
+      <c r="AS11" s="22"/>
+      <c r="AT11" s="18"/>
       <c r="AU11" s="17"/>
       <c r="AV11" s="17"/>
-      <c r="AW11">
+      <c r="AW11" s="18"/>
+      <c r="AX11" s="17"/>
+      <c r="AY11" s="17"/>
+      <c r="AZ11" s="17"/>
+      <c r="BA11" s="18"/>
+      <c r="BB11" s="17"/>
+      <c r="BC11" s="17"/>
+      <c r="BD11" s="17"/>
+      <c r="BE11" s="18"/>
+      <c r="BF11" s="18"/>
+      <c r="BG11" s="17"/>
+      <c r="BH11" s="17"/>
+      <c r="BI11" s="17"/>
+      <c r="BJ11" s="17"/>
+      <c r="BK11" s="17"/>
+      <c r="BL11">
         <v>7</v>
       </c>
-      <c r="AY11" t="s">
+      <c r="BN11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:53" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>9</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C12" s="4">
         <v>8</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
+        <v>128</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>129</v>
+      </c>
       <c r="H12" s="17"/>
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
@@ -1888,57 +2316,78 @@
       <c r="R12" s="17"/>
       <c r="S12" s="17"/>
       <c r="T12" s="17"/>
-      <c r="U12" s="18"/>
+      <c r="U12" s="17"/>
       <c r="V12" s="17"/>
-      <c r="W12" s="19"/>
-      <c r="X12" s="19"/>
-      <c r="Y12" s="21"/>
-      <c r="Z12" s="26"/>
-      <c r="AA12" s="19"/>
-      <c r="AB12" s="21"/>
+      <c r="W12" s="17"/>
+      <c r="X12" s="17"/>
+      <c r="Y12" s="17"/>
+      <c r="Z12" s="17"/>
+      <c r="AA12" s="17"/>
+      <c r="AB12" s="17"/>
       <c r="AC12" s="17"/>
-      <c r="AD12" s="22"/>
-      <c r="AE12" s="21"/>
+      <c r="AD12" s="17"/>
+      <c r="AE12" s="17"/>
       <c r="AF12" s="17"/>
       <c r="AG12" s="17"/>
-      <c r="AH12" s="18"/>
+      <c r="AH12" s="17"/>
       <c r="AI12" s="17"/>
-      <c r="AJ12" s="17"/>
+      <c r="AJ12" s="18"/>
       <c r="AK12" s="17"/>
-      <c r="AL12" s="18"/>
-      <c r="AM12" s="17"/>
-      <c r="AN12" s="17"/>
-      <c r="AO12" s="17"/>
-      <c r="AP12" s="18"/>
-      <c r="AQ12" s="18"/>
+      <c r="AL12" s="19"/>
+      <c r="AM12" s="19"/>
+      <c r="AN12" s="21"/>
+      <c r="AO12" s="26"/>
+      <c r="AP12" s="19"/>
+      <c r="AQ12" s="21"/>
       <c r="AR12" s="17"/>
-      <c r="AS12" s="17"/>
-      <c r="AT12" s="17"/>
+      <c r="AS12" s="22"/>
+      <c r="AT12" s="21"/>
       <c r="AU12" s="17"/>
       <c r="AV12" s="17"/>
-      <c r="AW12">
+      <c r="AW12" s="18"/>
+      <c r="AX12" s="17"/>
+      <c r="AY12" s="17"/>
+      <c r="AZ12" s="17"/>
+      <c r="BA12" s="18"/>
+      <c r="BB12" s="17"/>
+      <c r="BC12" s="17"/>
+      <c r="BD12" s="17"/>
+      <c r="BE12" s="18"/>
+      <c r="BF12" s="18"/>
+      <c r="BG12" s="17"/>
+      <c r="BH12" s="17"/>
+      <c r="BI12" s="17"/>
+      <c r="BJ12" s="17"/>
+      <c r="BK12" s="17"/>
+      <c r="BL12">
         <v>8</v>
       </c>
-      <c r="AY12" t="s">
+      <c r="BN12" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:53" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C13" s="4">
         <v>9</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
+        <v>128</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
       <c r="J13" s="17"/>
@@ -1952,57 +2401,78 @@
       <c r="R13" s="17"/>
       <c r="S13" s="17"/>
       <c r="T13" s="17"/>
-      <c r="U13" s="18"/>
+      <c r="U13" s="17"/>
       <c r="V13" s="17"/>
-      <c r="W13" s="19"/>
-      <c r="X13" s="19"/>
-      <c r="Y13" s="21"/>
-      <c r="Z13" s="22"/>
-      <c r="AA13" s="19"/>
-      <c r="AB13" s="18"/>
+      <c r="W13" s="17"/>
+      <c r="X13" s="17"/>
+      <c r="Y13" s="17"/>
+      <c r="Z13" s="17"/>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="17"/>
       <c r="AC13" s="17"/>
-      <c r="AD13" s="22"/>
-      <c r="AE13" s="18"/>
+      <c r="AD13" s="17"/>
+      <c r="AE13" s="17"/>
       <c r="AF13" s="17"/>
       <c r="AG13" s="17"/>
-      <c r="AH13" s="18"/>
+      <c r="AH13" s="17"/>
       <c r="AI13" s="17"/>
-      <c r="AJ13" s="17"/>
+      <c r="AJ13" s="18"/>
       <c r="AK13" s="17"/>
-      <c r="AL13" s="18"/>
-      <c r="AM13" s="17"/>
-      <c r="AN13" s="17"/>
-      <c r="AO13" s="17"/>
-      <c r="AP13" s="18"/>
+      <c r="AL13" s="19"/>
+      <c r="AM13" s="19"/>
+      <c r="AN13" s="21"/>
+      <c r="AO13" s="22"/>
+      <c r="AP13" s="19"/>
       <c r="AQ13" s="18"/>
       <c r="AR13" s="17"/>
-      <c r="AS13" s="17"/>
-      <c r="AT13" s="17"/>
+      <c r="AS13" s="22"/>
+      <c r="AT13" s="18"/>
       <c r="AU13" s="17"/>
       <c r="AV13" s="17"/>
-      <c r="AW13">
+      <c r="AW13" s="18"/>
+      <c r="AX13" s="17"/>
+      <c r="AY13" s="17"/>
+      <c r="AZ13" s="17"/>
+      <c r="BA13" s="18"/>
+      <c r="BB13" s="17"/>
+      <c r="BC13" s="17"/>
+      <c r="BD13" s="17"/>
+      <c r="BE13" s="18"/>
+      <c r="BF13" s="18"/>
+      <c r="BG13" s="17"/>
+      <c r="BH13" s="17"/>
+      <c r="BI13" s="17"/>
+      <c r="BJ13" s="17"/>
+      <c r="BK13" s="17"/>
+      <c r="BL13">
         <v>9</v>
       </c>
-      <c r="AY13" t="s">
+      <c r="BN13" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:53" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C14" s="4">
         <v>10</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
+        <v>128</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
       <c r="J14" s="17"/>
@@ -2018,11 +2488,11 @@
       <c r="T14" s="17"/>
       <c r="U14" s="17"/>
       <c r="V14" s="17"/>
-      <c r="W14" s="19"/>
-      <c r="X14" s="19"/>
-      <c r="Y14" s="25"/>
-      <c r="Z14" s="20"/>
-      <c r="AA14" s="19"/>
+      <c r="W14" s="17"/>
+      <c r="X14" s="17"/>
+      <c r="Y14" s="17"/>
+      <c r="Z14" s="17"/>
+      <c r="AA14" s="17"/>
       <c r="AB14" s="17"/>
       <c r="AC14" s="17"/>
       <c r="AD14" s="17"/>
@@ -2033,40 +2503,61 @@
       <c r="AI14" s="17"/>
       <c r="AJ14" s="17"/>
       <c r="AK14" s="17"/>
-      <c r="AL14" s="17"/>
-      <c r="AM14" s="17"/>
-      <c r="AN14" s="17"/>
-      <c r="AO14" s="17"/>
-      <c r="AP14" s="17"/>
+      <c r="AL14" s="19"/>
+      <c r="AM14" s="19"/>
+      <c r="AN14" s="25"/>
+      <c r="AO14" s="20"/>
+      <c r="AP14" s="19"/>
       <c r="AQ14" s="17"/>
       <c r="AR14" s="17"/>
       <c r="AS14" s="17"/>
       <c r="AT14" s="17"/>
       <c r="AU14" s="17"/>
       <c r="AV14" s="17"/>
-      <c r="AW14">
+      <c r="AW14" s="17"/>
+      <c r="AX14" s="17"/>
+      <c r="AY14" s="17"/>
+      <c r="AZ14" s="17"/>
+      <c r="BA14" s="17"/>
+      <c r="BB14" s="17"/>
+      <c r="BC14" s="17"/>
+      <c r="BD14" s="17"/>
+      <c r="BE14" s="17"/>
+      <c r="BF14" s="17"/>
+      <c r="BG14" s="17"/>
+      <c r="BH14" s="17"/>
+      <c r="BI14" s="17"/>
+      <c r="BJ14" s="17"/>
+      <c r="BK14" s="17"/>
+      <c r="BL14">
         <v>10</v>
       </c>
-      <c r="AY14" t="s">
+      <c r="BN14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:53" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C15" s="4">
         <v>7</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
+        <v>128</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
@@ -2080,57 +2571,78 @@
       <c r="R15" s="17"/>
       <c r="S15" s="17"/>
       <c r="T15" s="17"/>
-      <c r="U15" s="18"/>
+      <c r="U15" s="17"/>
       <c r="V15" s="17"/>
-      <c r="W15" s="19"/>
-      <c r="X15" s="19"/>
-      <c r="Y15" s="18"/>
-      <c r="Z15" s="20"/>
-      <c r="AA15" s="19"/>
-      <c r="AB15" s="21"/>
+      <c r="W15" s="17"/>
+      <c r="X15" s="17"/>
+      <c r="Y15" s="17"/>
+      <c r="Z15" s="17"/>
+      <c r="AA15" s="17"/>
+      <c r="AB15" s="17"/>
       <c r="AC15" s="17"/>
-      <c r="AD15" s="22"/>
-      <c r="AE15" s="18"/>
+      <c r="AD15" s="17"/>
+      <c r="AE15" s="17"/>
       <c r="AF15" s="17"/>
-      <c r="AG15" s="22"/>
-      <c r="AH15" s="21"/>
+      <c r="AG15" s="17"/>
+      <c r="AH15" s="17"/>
       <c r="AI15" s="17"/>
-      <c r="AJ15" s="17"/>
+      <c r="AJ15" s="18"/>
       <c r="AK15" s="17"/>
-      <c r="AL15" s="18"/>
-      <c r="AM15" s="17"/>
-      <c r="AN15" s="17"/>
-      <c r="AO15" s="17"/>
-      <c r="AP15" s="17"/>
-      <c r="AQ15" s="18"/>
+      <c r="AL15" s="19"/>
+      <c r="AM15" s="19"/>
+      <c r="AN15" s="18"/>
+      <c r="AO15" s="20"/>
+      <c r="AP15" s="19"/>
+      <c r="AQ15" s="21"/>
       <c r="AR15" s="17"/>
-      <c r="AS15" s="17"/>
-      <c r="AT15" s="17"/>
+      <c r="AS15" s="22"/>
+      <c r="AT15" s="18"/>
       <c r="AU15" s="17"/>
-      <c r="AV15" s="17"/>
-      <c r="AW15">
+      <c r="AV15" s="22"/>
+      <c r="AW15" s="21"/>
+      <c r="AX15" s="17"/>
+      <c r="AY15" s="17"/>
+      <c r="AZ15" s="17"/>
+      <c r="BA15" s="18"/>
+      <c r="BB15" s="17"/>
+      <c r="BC15" s="17"/>
+      <c r="BD15" s="17"/>
+      <c r="BE15" s="17"/>
+      <c r="BF15" s="18"/>
+      <c r="BG15" s="17"/>
+      <c r="BH15" s="17"/>
+      <c r="BI15" s="17"/>
+      <c r="BJ15" s="17"/>
+      <c r="BK15" s="17"/>
+      <c r="BL15">
         <v>11</v>
       </c>
-      <c r="AY15" t="s">
+      <c r="BN15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:53" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C16" s="4">
         <v>1</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
+        <v>128</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
@@ -2144,57 +2656,78 @@
       <c r="R16" s="17"/>
       <c r="S16" s="17"/>
       <c r="T16" s="17"/>
-      <c r="U16" s="18"/>
+      <c r="U16" s="17"/>
       <c r="V16" s="17"/>
-      <c r="W16" s="18"/>
-      <c r="X16" s="19"/>
-      <c r="Y16" s="25"/>
-      <c r="Z16" s="26"/>
-      <c r="AA16" s="19"/>
-      <c r="AB16" s="18"/>
+      <c r="W16" s="17"/>
+      <c r="X16" s="17"/>
+      <c r="Y16" s="17"/>
+      <c r="Z16" s="17"/>
+      <c r="AA16" s="17"/>
+      <c r="AB16" s="17"/>
       <c r="AC16" s="17"/>
-      <c r="AD16" s="22"/>
-      <c r="AE16" s="18"/>
+      <c r="AD16" s="17"/>
+      <c r="AE16" s="17"/>
       <c r="AF16" s="17"/>
-      <c r="AG16" s="22"/>
-      <c r="AH16" s="18"/>
+      <c r="AG16" s="17"/>
+      <c r="AH16" s="17"/>
       <c r="AI16" s="17"/>
-      <c r="AJ16" s="27"/>
+      <c r="AJ16" s="18"/>
       <c r="AK16" s="17"/>
       <c r="AL16" s="18"/>
-      <c r="AM16" s="17"/>
-      <c r="AN16" s="17"/>
-      <c r="AO16" s="17"/>
-      <c r="AP16" s="18"/>
+      <c r="AM16" s="19"/>
+      <c r="AN16" s="25"/>
+      <c r="AO16" s="26"/>
+      <c r="AP16" s="19"/>
       <c r="AQ16" s="18"/>
       <c r="AR16" s="17"/>
-      <c r="AS16" s="17"/>
-      <c r="AT16" s="17"/>
+      <c r="AS16" s="22"/>
+      <c r="AT16" s="18"/>
       <c r="AU16" s="17"/>
-      <c r="AV16" s="17"/>
-      <c r="AW16">
+      <c r="AV16" s="22"/>
+      <c r="AW16" s="18"/>
+      <c r="AX16" s="17"/>
+      <c r="AY16" s="27"/>
+      <c r="AZ16" s="17"/>
+      <c r="BA16" s="18"/>
+      <c r="BB16" s="17"/>
+      <c r="BC16" s="17"/>
+      <c r="BD16" s="17"/>
+      <c r="BE16" s="18"/>
+      <c r="BF16" s="18"/>
+      <c r="BG16" s="17"/>
+      <c r="BH16" s="17"/>
+      <c r="BI16" s="17"/>
+      <c r="BJ16" s="17"/>
+      <c r="BK16" s="17"/>
+      <c r="BL16">
         <v>12</v>
       </c>
-      <c r="AY16" t="s">
+      <c r="BN16" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:51" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>14</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C17" s="4">
         <v>11</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
+        <v>128</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
       <c r="J17" s="17"/>
@@ -2208,57 +2741,78 @@
       <c r="R17" s="17"/>
       <c r="S17" s="17"/>
       <c r="T17" s="17"/>
-      <c r="U17" s="18"/>
+      <c r="U17" s="17"/>
       <c r="V17" s="17"/>
-      <c r="W17" s="19"/>
-      <c r="X17" s="19"/>
-      <c r="Y17" s="21"/>
-      <c r="Z17" s="20"/>
-      <c r="AA17" s="19"/>
-      <c r="AB17" s="18"/>
+      <c r="W17" s="17"/>
+      <c r="X17" s="17"/>
+      <c r="Y17" s="17"/>
+      <c r="Z17" s="17"/>
+      <c r="AA17" s="17"/>
+      <c r="AB17" s="17"/>
       <c r="AC17" s="17"/>
       <c r="AD17" s="17"/>
-      <c r="AE17" s="18"/>
+      <c r="AE17" s="17"/>
       <c r="AF17" s="17"/>
       <c r="AG17" s="17"/>
-      <c r="AH17" s="18"/>
+      <c r="AH17" s="17"/>
       <c r="AI17" s="17"/>
-      <c r="AJ17" s="17"/>
+      <c r="AJ17" s="18"/>
       <c r="AK17" s="17"/>
-      <c r="AL17" s="18"/>
-      <c r="AM17" s="17"/>
-      <c r="AN17" s="17"/>
-      <c r="AO17" s="17"/>
-      <c r="AP17" s="18"/>
+      <c r="AL17" s="19"/>
+      <c r="AM17" s="19"/>
+      <c r="AN17" s="21"/>
+      <c r="AO17" s="20"/>
+      <c r="AP17" s="19"/>
       <c r="AQ17" s="18"/>
       <c r="AR17" s="17"/>
       <c r="AS17" s="17"/>
-      <c r="AT17" s="17"/>
+      <c r="AT17" s="18"/>
       <c r="AU17" s="17"/>
       <c r="AV17" s="17"/>
-      <c r="AW17">
+      <c r="AW17" s="18"/>
+      <c r="AX17" s="17"/>
+      <c r="AY17" s="17"/>
+      <c r="AZ17" s="17"/>
+      <c r="BA17" s="18"/>
+      <c r="BB17" s="17"/>
+      <c r="BC17" s="17"/>
+      <c r="BD17" s="17"/>
+      <c r="BE17" s="18"/>
+      <c r="BF17" s="18"/>
+      <c r="BG17" s="17"/>
+      <c r="BH17" s="17"/>
+      <c r="BI17" s="17"/>
+      <c r="BJ17" s="17"/>
+      <c r="BK17" s="17"/>
+      <c r="BL17">
         <v>13</v>
       </c>
-      <c r="AY17" t="s">
+      <c r="BN17" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:51" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C18" s="4">
         <v>12</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
+        <v>128</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>132</v>
+      </c>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
       <c r="J18" s="17"/>
@@ -2272,57 +2826,78 @@
       <c r="R18" s="17"/>
       <c r="S18" s="17"/>
       <c r="T18" s="17"/>
-      <c r="U18" s="18"/>
+      <c r="U18" s="17"/>
       <c r="V18" s="17"/>
-      <c r="W18" s="19"/>
-      <c r="X18" s="19"/>
-      <c r="Y18" s="21"/>
-      <c r="Z18" s="28"/>
-      <c r="AA18" s="19"/>
-      <c r="AB18" s="21"/>
+      <c r="W18" s="17"/>
+      <c r="X18" s="17"/>
+      <c r="Y18" s="17"/>
+      <c r="Z18" s="17"/>
+      <c r="AA18" s="17"/>
+      <c r="AB18" s="17"/>
       <c r="AC18" s="17"/>
-      <c r="AD18" s="22"/>
-      <c r="AE18" s="18"/>
+      <c r="AD18" s="17"/>
+      <c r="AE18" s="17"/>
       <c r="AF18" s="17"/>
       <c r="AG18" s="17"/>
-      <c r="AH18" s="18"/>
+      <c r="AH18" s="17"/>
       <c r="AI18" s="17"/>
-      <c r="AJ18" s="17"/>
+      <c r="AJ18" s="18"/>
       <c r="AK18" s="17"/>
-      <c r="AL18" s="18"/>
-      <c r="AM18" s="17"/>
-      <c r="AN18" s="17"/>
-      <c r="AO18" s="17"/>
-      <c r="AP18" s="18"/>
-      <c r="AQ18" s="18"/>
+      <c r="AL18" s="19"/>
+      <c r="AM18" s="19"/>
+      <c r="AN18" s="21"/>
+      <c r="AO18" s="28"/>
+      <c r="AP18" s="19"/>
+      <c r="AQ18" s="21"/>
       <c r="AR18" s="17"/>
-      <c r="AS18" s="17"/>
-      <c r="AT18" s="17"/>
+      <c r="AS18" s="22"/>
+      <c r="AT18" s="18"/>
       <c r="AU18" s="17"/>
       <c r="AV18" s="17"/>
-      <c r="AW18">
+      <c r="AW18" s="18"/>
+      <c r="AX18" s="17"/>
+      <c r="AY18" s="17"/>
+      <c r="AZ18" s="17"/>
+      <c r="BA18" s="18"/>
+      <c r="BB18" s="17"/>
+      <c r="BC18" s="17"/>
+      <c r="BD18" s="17"/>
+      <c r="BE18" s="18"/>
+      <c r="BF18" s="18"/>
+      <c r="BG18" s="17"/>
+      <c r="BH18" s="17"/>
+      <c r="BI18" s="17"/>
+      <c r="BJ18" s="17"/>
+      <c r="BK18" s="17"/>
+      <c r="BL18">
         <v>14</v>
       </c>
-      <c r="AY18" t="s">
+      <c r="BN18" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:51" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>16</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C19" s="4">
         <v>11</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
+        <v>128</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
       <c r="J19" s="17"/>
@@ -2336,57 +2911,78 @@
       <c r="R19" s="17"/>
       <c r="S19" s="17"/>
       <c r="T19" s="17"/>
-      <c r="U19" s="18"/>
+      <c r="U19" s="17"/>
       <c r="V19" s="17"/>
-      <c r="W19" s="19"/>
-      <c r="X19" s="19"/>
-      <c r="Y19" s="21"/>
-      <c r="Z19" s="26"/>
-      <c r="AA19" s="19"/>
-      <c r="AB19" s="21"/>
+      <c r="W19" s="17"/>
+      <c r="X19" s="17"/>
+      <c r="Y19" s="17"/>
+      <c r="Z19" s="17"/>
+      <c r="AA19" s="17"/>
+      <c r="AB19" s="17"/>
       <c r="AC19" s="17"/>
-      <c r="AD19" s="22"/>
-      <c r="AE19" s="21"/>
+      <c r="AD19" s="17"/>
+      <c r="AE19" s="17"/>
       <c r="AF19" s="17"/>
       <c r="AG19" s="17"/>
-      <c r="AH19" s="21"/>
+      <c r="AH19" s="17"/>
       <c r="AI19" s="17"/>
-      <c r="AJ19" s="17"/>
+      <c r="AJ19" s="18"/>
       <c r="AK19" s="17"/>
-      <c r="AL19" s="18"/>
-      <c r="AM19" s="17"/>
-      <c r="AN19" s="17"/>
-      <c r="AO19" s="17"/>
-      <c r="AP19" s="18"/>
-      <c r="AQ19" s="18"/>
+      <c r="AL19" s="19"/>
+      <c r="AM19" s="19"/>
+      <c r="AN19" s="21"/>
+      <c r="AO19" s="26"/>
+      <c r="AP19" s="19"/>
+      <c r="AQ19" s="21"/>
       <c r="AR19" s="17"/>
-      <c r="AS19" s="17"/>
-      <c r="AT19" s="17"/>
+      <c r="AS19" s="22"/>
+      <c r="AT19" s="21"/>
       <c r="AU19" s="17"/>
       <c r="AV19" s="17"/>
-      <c r="AW19">
+      <c r="AW19" s="21"/>
+      <c r="AX19" s="17"/>
+      <c r="AY19" s="17"/>
+      <c r="AZ19" s="17"/>
+      <c r="BA19" s="18"/>
+      <c r="BB19" s="17"/>
+      <c r="BC19" s="17"/>
+      <c r="BD19" s="17"/>
+      <c r="BE19" s="18"/>
+      <c r="BF19" s="18"/>
+      <c r="BG19" s="17"/>
+      <c r="BH19" s="17"/>
+      <c r="BI19" s="17"/>
+      <c r="BJ19" s="17"/>
+      <c r="BK19" s="17"/>
+      <c r="BL19">
         <v>15</v>
       </c>
-      <c r="AY19" t="s">
+      <c r="BN19" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:51" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C20" s="4">
         <v>5</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
+        <v>128</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
@@ -2400,57 +2996,78 @@
       <c r="R20" s="17"/>
       <c r="S20" s="17"/>
       <c r="T20" s="17"/>
-      <c r="U20" s="18"/>
+      <c r="U20" s="17"/>
       <c r="V20" s="17"/>
-      <c r="W20" s="19"/>
-      <c r="X20" s="19"/>
-      <c r="Y20" s="21"/>
-      <c r="Z20" s="28"/>
-      <c r="AA20" s="19"/>
-      <c r="AB20" s="18"/>
+      <c r="W20" s="17"/>
+      <c r="X20" s="17"/>
+      <c r="Y20" s="17"/>
+      <c r="Z20" s="17"/>
+      <c r="AA20" s="17"/>
+      <c r="AB20" s="17"/>
       <c r="AC20" s="17"/>
-      <c r="AD20" s="29"/>
+      <c r="AD20" s="17"/>
       <c r="AE20" s="17"/>
       <c r="AF20" s="17"/>
       <c r="AG20" s="17"/>
-      <c r="AH20" s="18"/>
+      <c r="AH20" s="17"/>
       <c r="AI20" s="17"/>
-      <c r="AJ20" s="17"/>
+      <c r="AJ20" s="18"/>
       <c r="AK20" s="17"/>
-      <c r="AL20" s="18"/>
-      <c r="AM20" s="17"/>
-      <c r="AN20" s="17"/>
-      <c r="AO20" s="17"/>
-      <c r="AP20" s="18"/>
+      <c r="AL20" s="19"/>
+      <c r="AM20" s="19"/>
+      <c r="AN20" s="21"/>
+      <c r="AO20" s="28"/>
+      <c r="AP20" s="19"/>
       <c r="AQ20" s="18"/>
       <c r="AR20" s="17"/>
-      <c r="AS20" s="17"/>
+      <c r="AS20" s="29"/>
       <c r="AT20" s="17"/>
       <c r="AU20" s="17"/>
       <c r="AV20" s="17"/>
-      <c r="AW20">
+      <c r="AW20" s="18"/>
+      <c r="AX20" s="17"/>
+      <c r="AY20" s="17"/>
+      <c r="AZ20" s="17"/>
+      <c r="BA20" s="18"/>
+      <c r="BB20" s="17"/>
+      <c r="BC20" s="17"/>
+      <c r="BD20" s="17"/>
+      <c r="BE20" s="18"/>
+      <c r="BF20" s="18"/>
+      <c r="BG20" s="17"/>
+      <c r="BH20" s="17"/>
+      <c r="BI20" s="17"/>
+      <c r="BJ20" s="17"/>
+      <c r="BK20" s="17"/>
+      <c r="BL20">
         <v>16</v>
       </c>
-      <c r="AY20" t="s">
+      <c r="BN20" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:51" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C21" s="4">
         <v>17</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
+        <v>129</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H21" s="17"/>
       <c r="I21" s="17"/>
       <c r="J21" s="17"/>
@@ -2464,57 +3081,78 @@
       <c r="R21" s="17"/>
       <c r="S21" s="17"/>
       <c r="T21" s="17"/>
-      <c r="U21" s="18"/>
+      <c r="U21" s="17"/>
       <c r="V21" s="17"/>
-      <c r="W21" s="19"/>
-      <c r="X21" s="19"/>
-      <c r="Y21" s="21"/>
-      <c r="Z21" s="20"/>
-      <c r="AA21" s="19"/>
-      <c r="AB21" s="21"/>
+      <c r="W21" s="17"/>
+      <c r="X21" s="17"/>
+      <c r="Y21" s="17"/>
+      <c r="Z21" s="17"/>
+      <c r="AA21" s="17"/>
+      <c r="AB21" s="17"/>
       <c r="AC21" s="17"/>
       <c r="AD21" s="17"/>
-      <c r="AE21" s="18"/>
+      <c r="AE21" s="17"/>
       <c r="AF21" s="17"/>
       <c r="AG21" s="17"/>
-      <c r="AH21" s="18"/>
+      <c r="AH21" s="17"/>
       <c r="AI21" s="17"/>
-      <c r="AJ21" s="17"/>
+      <c r="AJ21" s="18"/>
       <c r="AK21" s="17"/>
-      <c r="AL21" s="18"/>
-      <c r="AM21" s="17"/>
-      <c r="AN21" s="17"/>
-      <c r="AO21" s="17"/>
-      <c r="AP21" s="18"/>
-      <c r="AQ21" s="18"/>
+      <c r="AL21" s="19"/>
+      <c r="AM21" s="19"/>
+      <c r="AN21" s="21"/>
+      <c r="AO21" s="20"/>
+      <c r="AP21" s="19"/>
+      <c r="AQ21" s="21"/>
       <c r="AR21" s="17"/>
       <c r="AS21" s="17"/>
-      <c r="AT21" s="17"/>
+      <c r="AT21" s="18"/>
       <c r="AU21" s="17"/>
       <c r="AV21" s="17"/>
-      <c r="AW21" s="16">
+      <c r="AW21" s="18"/>
+      <c r="AX21" s="17"/>
+      <c r="AY21" s="17"/>
+      <c r="AZ21" s="17"/>
+      <c r="BA21" s="18"/>
+      <c r="BB21" s="17"/>
+      <c r="BC21" s="17"/>
+      <c r="BD21" s="17"/>
+      <c r="BE21" s="18"/>
+      <c r="BF21" s="18"/>
+      <c r="BG21" s="17"/>
+      <c r="BH21" s="17"/>
+      <c r="BI21" s="17"/>
+      <c r="BJ21" s="17"/>
+      <c r="BK21" s="17"/>
+      <c r="BL21" s="16">
         <v>17</v>
       </c>
-      <c r="AY21" t="s">
+      <c r="BN21" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:51" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C22" s="4">
         <v>13</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
+        <v>128</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H22" s="17"/>
       <c r="I22" s="17"/>
       <c r="J22" s="17"/>
@@ -2528,57 +3166,78 @@
       <c r="R22" s="17"/>
       <c r="S22" s="17"/>
       <c r="T22" s="17"/>
-      <c r="U22" s="18"/>
+      <c r="U22" s="17"/>
       <c r="V22" s="17"/>
-      <c r="W22" s="19"/>
-      <c r="X22" s="19"/>
-      <c r="Y22" s="21"/>
-      <c r="Z22" s="28"/>
-      <c r="AA22" s="19"/>
-      <c r="AB22" s="21"/>
+      <c r="W22" s="17"/>
+      <c r="X22" s="17"/>
+      <c r="Y22" s="17"/>
+      <c r="Z22" s="17"/>
+      <c r="AA22" s="17"/>
+      <c r="AB22" s="17"/>
       <c r="AC22" s="17"/>
-      <c r="AD22" s="22"/>
-      <c r="AE22" s="18"/>
+      <c r="AD22" s="17"/>
+      <c r="AE22" s="17"/>
       <c r="AF22" s="17"/>
-      <c r="AG22" s="22"/>
-      <c r="AH22" s="18"/>
+      <c r="AG22" s="17"/>
+      <c r="AH22" s="17"/>
       <c r="AI22" s="17"/>
-      <c r="AJ22" s="17"/>
+      <c r="AJ22" s="18"/>
       <c r="AK22" s="17"/>
-      <c r="AL22" s="18"/>
-      <c r="AM22" s="17"/>
-      <c r="AN22" s="17"/>
-      <c r="AO22" s="17"/>
-      <c r="AP22" s="18"/>
-      <c r="AQ22" s="18"/>
+      <c r="AL22" s="19"/>
+      <c r="AM22" s="19"/>
+      <c r="AN22" s="21"/>
+      <c r="AO22" s="28"/>
+      <c r="AP22" s="19"/>
+      <c r="AQ22" s="21"/>
       <c r="AR22" s="17"/>
-      <c r="AS22" s="17"/>
-      <c r="AT22" s="17"/>
+      <c r="AS22" s="22"/>
+      <c r="AT22" s="18"/>
       <c r="AU22" s="17"/>
-      <c r="AV22" s="17"/>
-      <c r="AW22">
+      <c r="AV22" s="22"/>
+      <c r="AW22" s="18"/>
+      <c r="AX22" s="17"/>
+      <c r="AY22" s="17"/>
+      <c r="AZ22" s="17"/>
+      <c r="BA22" s="18"/>
+      <c r="BB22" s="17"/>
+      <c r="BC22" s="17"/>
+      <c r="BD22" s="17"/>
+      <c r="BE22" s="18"/>
+      <c r="BF22" s="18"/>
+      <c r="BG22" s="17"/>
+      <c r="BH22" s="17"/>
+      <c r="BI22" s="17"/>
+      <c r="BJ22" s="17"/>
+      <c r="BK22" s="17"/>
+      <c r="BL22">
         <v>18</v>
       </c>
-      <c r="AY22" t="s">
+      <c r="BN22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:51" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C23" s="4">
         <v>14</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
+        <v>128</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>132</v>
+      </c>
       <c r="H23" s="17"/>
       <c r="I23" s="17"/>
       <c r="J23" s="17"/>
@@ -2592,57 +3251,78 @@
       <c r="R23" s="17"/>
       <c r="S23" s="17"/>
       <c r="T23" s="17"/>
-      <c r="U23" s="18"/>
+      <c r="U23" s="17"/>
       <c r="V23" s="17"/>
-      <c r="W23" s="18"/>
-      <c r="X23" s="19"/>
-      <c r="Y23" s="21"/>
+      <c r="W23" s="17"/>
+      <c r="X23" s="17"/>
+      <c r="Y23" s="17"/>
       <c r="Z23" s="17"/>
-      <c r="AA23" s="19"/>
-      <c r="AB23" s="18"/>
+      <c r="AA23" s="17"/>
+      <c r="AB23" s="17"/>
       <c r="AC23" s="17"/>
-      <c r="AD23" s="22"/>
+      <c r="AD23" s="17"/>
       <c r="AE23" s="17"/>
       <c r="AF23" s="17"/>
-      <c r="AG23" s="22"/>
-      <c r="AH23" s="18"/>
+      <c r="AG23" s="17"/>
+      <c r="AH23" s="17"/>
       <c r="AI23" s="17"/>
-      <c r="AJ23" s="27"/>
+      <c r="AJ23" s="18"/>
       <c r="AK23" s="17"/>
       <c r="AL23" s="18"/>
-      <c r="AM23" s="17"/>
-      <c r="AN23" s="17"/>
+      <c r="AM23" s="19"/>
+      <c r="AN23" s="21"/>
       <c r="AO23" s="17"/>
-      <c r="AP23" s="18"/>
+      <c r="AP23" s="19"/>
       <c r="AQ23" s="18"/>
       <c r="AR23" s="17"/>
-      <c r="AS23" s="17"/>
+      <c r="AS23" s="22"/>
       <c r="AT23" s="17"/>
       <c r="AU23" s="17"/>
-      <c r="AV23" s="17"/>
-      <c r="AW23">
+      <c r="AV23" s="22"/>
+      <c r="AW23" s="18"/>
+      <c r="AX23" s="17"/>
+      <c r="AY23" s="27"/>
+      <c r="AZ23" s="17"/>
+      <c r="BA23" s="18"/>
+      <c r="BB23" s="17"/>
+      <c r="BC23" s="17"/>
+      <c r="BD23" s="17"/>
+      <c r="BE23" s="18"/>
+      <c r="BF23" s="18"/>
+      <c r="BG23" s="17"/>
+      <c r="BH23" s="17"/>
+      <c r="BI23" s="17"/>
+      <c r="BJ23" s="17"/>
+      <c r="BK23" s="17"/>
+      <c r="BL23">
         <v>19</v>
       </c>
-      <c r="AY23" t="s">
+      <c r="BN23" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:51" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C24" s="4">
         <v>15</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
+        <v>128</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H24" s="17"/>
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
@@ -2658,9 +3338,9 @@
       <c r="T24" s="17"/>
       <c r="U24" s="17"/>
       <c r="V24" s="17"/>
-      <c r="W24" s="19"/>
-      <c r="X24" s="19"/>
-      <c r="Y24" s="25"/>
+      <c r="W24" s="17"/>
+      <c r="X24" s="17"/>
+      <c r="Y24" s="17"/>
       <c r="Z24" s="17"/>
       <c r="AA24" s="17"/>
       <c r="AB24" s="17"/>
@@ -2673,9 +3353,9 @@
       <c r="AI24" s="17"/>
       <c r="AJ24" s="17"/>
       <c r="AK24" s="17"/>
-      <c r="AL24" s="17"/>
-      <c r="AM24" s="17"/>
-      <c r="AN24" s="17"/>
+      <c r="AL24" s="19"/>
+      <c r="AM24" s="19"/>
+      <c r="AN24" s="25"/>
       <c r="AO24" s="17"/>
       <c r="AP24" s="17"/>
       <c r="AQ24" s="17"/>
@@ -2684,29 +3364,50 @@
       <c r="AT24" s="17"/>
       <c r="AU24" s="17"/>
       <c r="AV24" s="17"/>
-      <c r="AW24">
+      <c r="AW24" s="17"/>
+      <c r="AX24" s="17"/>
+      <c r="AY24" s="17"/>
+      <c r="AZ24" s="17"/>
+      <c r="BA24" s="17"/>
+      <c r="BB24" s="17"/>
+      <c r="BC24" s="17"/>
+      <c r="BD24" s="17"/>
+      <c r="BE24" s="17"/>
+      <c r="BF24" s="17"/>
+      <c r="BG24" s="17"/>
+      <c r="BH24" s="17"/>
+      <c r="BI24" s="17"/>
+      <c r="BJ24" s="17"/>
+      <c r="BK24" s="17"/>
+      <c r="BL24">
         <v>20</v>
       </c>
-      <c r="AY24" t="s">
+      <c r="BN24" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:51" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>22</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C25" s="4">
         <v>16</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
+        <v>128</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G25" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H25" s="17"/>
       <c r="I25" s="17"/>
       <c r="J25" s="17"/>
@@ -2720,57 +3421,78 @@
       <c r="R25" s="17"/>
       <c r="S25" s="17"/>
       <c r="T25" s="17"/>
-      <c r="U25" s="18"/>
+      <c r="U25" s="17"/>
       <c r="V25" s="17"/>
-      <c r="W25" s="19"/>
-      <c r="X25" s="19"/>
-      <c r="Y25" s="21"/>
-      <c r="Z25" s="20"/>
-      <c r="AA25" s="19"/>
-      <c r="AB25" s="21"/>
+      <c r="W25" s="17"/>
+      <c r="X25" s="17"/>
+      <c r="Y25" s="17"/>
+      <c r="Z25" s="17"/>
+      <c r="AA25" s="17"/>
+      <c r="AB25" s="17"/>
       <c r="AC25" s="17"/>
-      <c r="AD25" s="19"/>
-      <c r="AE25" s="18"/>
+      <c r="AD25" s="17"/>
+      <c r="AE25" s="17"/>
       <c r="AF25" s="17"/>
-      <c r="AG25" s="22"/>
-      <c r="AH25" s="18"/>
+      <c r="AG25" s="17"/>
+      <c r="AH25" s="17"/>
       <c r="AI25" s="17"/>
-      <c r="AJ25" s="22"/>
+      <c r="AJ25" s="18"/>
       <c r="AK25" s="17"/>
-      <c r="AL25" s="18"/>
-      <c r="AM25" s="17"/>
-      <c r="AN25" s="17"/>
-      <c r="AO25" s="17"/>
-      <c r="AP25" s="18"/>
-      <c r="AQ25" s="18"/>
+      <c r="AL25" s="19"/>
+      <c r="AM25" s="19"/>
+      <c r="AN25" s="21"/>
+      <c r="AO25" s="20"/>
+      <c r="AP25" s="19"/>
+      <c r="AQ25" s="21"/>
       <c r="AR25" s="17"/>
-      <c r="AS25" s="17"/>
-      <c r="AT25" s="17"/>
+      <c r="AS25" s="19"/>
+      <c r="AT25" s="18"/>
       <c r="AU25" s="17"/>
-      <c r="AV25" s="17"/>
-      <c r="AW25">
+      <c r="AV25" s="22"/>
+      <c r="AW25" s="18"/>
+      <c r="AX25" s="17"/>
+      <c r="AY25" s="22"/>
+      <c r="AZ25" s="17"/>
+      <c r="BA25" s="18"/>
+      <c r="BB25" s="17"/>
+      <c r="BC25" s="17"/>
+      <c r="BD25" s="17"/>
+      <c r="BE25" s="18"/>
+      <c r="BF25" s="18"/>
+      <c r="BG25" s="17"/>
+      <c r="BH25" s="17"/>
+      <c r="BI25" s="17"/>
+      <c r="BJ25" s="17"/>
+      <c r="BK25" s="17"/>
+      <c r="BL25">
         <v>21</v>
       </c>
-      <c r="AY25" t="s">
+      <c r="BN25" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="1:51" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C26" s="4">
         <v>9</v>
       </c>
-      <c r="D26" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
+      <c r="D26" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>132</v>
+      </c>
       <c r="H26" s="30"/>
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
@@ -2784,60 +3506,81 @@
       <c r="R26" s="30"/>
       <c r="S26" s="30"/>
       <c r="T26" s="30"/>
-      <c r="U26" s="18"/>
+      <c r="U26" s="30"/>
       <c r="V26" s="30"/>
-      <c r="W26" s="19"/>
-      <c r="X26" s="19"/>
-      <c r="Y26" s="21"/>
-      <c r="Z26" s="20"/>
-      <c r="AA26" s="19"/>
-      <c r="AB26" s="18"/>
-      <c r="AC26" s="17"/>
-      <c r="AD26" s="22"/>
-      <c r="AE26" s="18"/>
-      <c r="AF26" s="17"/>
-      <c r="AG26" s="17"/>
+      <c r="W26" s="30"/>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30"/>
+      <c r="AA26" s="30"/>
+      <c r="AB26" s="30"/>
+      <c r="AC26" s="30"/>
+      <c r="AD26" s="30"/>
+      <c r="AE26" s="30"/>
+      <c r="AF26" s="30"/>
+      <c r="AG26" s="30"/>
       <c r="AH26" s="30"/>
-      <c r="AI26" s="17"/>
-      <c r="AJ26" s="17"/>
-      <c r="AK26" s="17"/>
-      <c r="AL26" s="18"/>
-      <c r="AM26" s="17"/>
-      <c r="AN26" s="17"/>
-      <c r="AO26" s="17"/>
-      <c r="AP26" s="18"/>
+      <c r="AI26" s="30"/>
+      <c r="AJ26" s="18"/>
+      <c r="AK26" s="30"/>
+      <c r="AL26" s="19"/>
+      <c r="AM26" s="19"/>
+      <c r="AN26" s="21"/>
+      <c r="AO26" s="20"/>
+      <c r="AP26" s="19"/>
       <c r="AQ26" s="18"/>
-      <c r="AR26" s="30"/>
-      <c r="AS26" s="30"/>
-      <c r="AT26" s="30"/>
-      <c r="AU26" s="30"/>
-      <c r="AV26" s="30"/>
-      <c r="AW26" s="14">
+      <c r="AR26" s="17"/>
+      <c r="AS26" s="22"/>
+      <c r="AT26" s="18"/>
+      <c r="AU26" s="17"/>
+      <c r="AV26" s="17"/>
+      <c r="AW26" s="30"/>
+      <c r="AX26" s="17"/>
+      <c r="AY26" s="17"/>
+      <c r="AZ26" s="17"/>
+      <c r="BA26" s="18"/>
+      <c r="BB26" s="17"/>
+      <c r="BC26" s="17"/>
+      <c r="BD26" s="17"/>
+      <c r="BE26" s="18"/>
+      <c r="BF26" s="18"/>
+      <c r="BG26" s="30"/>
+      <c r="BH26" s="30"/>
+      <c r="BI26" s="30"/>
+      <c r="BJ26" s="30"/>
+      <c r="BK26" s="30"/>
+      <c r="BL26" s="14">
         <v>22</v>
       </c>
-      <c r="AX26" s="15" t="s">
+      <c r="BM26" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="AY26" s="14" t="s">
+      <c r="BN26" s="14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:51" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>24</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C27" s="4">
         <v>2</v>
       </c>
-      <c r="D27" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="E27" s="31"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
+      <c r="D27" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G27" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H27" s="30"/>
       <c r="I27" s="31"/>
       <c r="J27" s="31"/>
@@ -2851,57 +3594,78 @@
       <c r="R27" s="31"/>
       <c r="S27" s="31"/>
       <c r="T27" s="31"/>
-      <c r="U27" s="18"/>
+      <c r="U27" s="31"/>
       <c r="V27" s="31"/>
-      <c r="W27" s="19"/>
-      <c r="X27" s="19"/>
-      <c r="Y27" s="18"/>
-      <c r="Z27" s="28"/>
-      <c r="AA27" s="19"/>
-      <c r="AB27" s="18"/>
-      <c r="AC27" s="17"/>
-      <c r="AD27" s="29"/>
-      <c r="AE27" s="17"/>
-      <c r="AF27" s="17"/>
-      <c r="AG27" s="17"/>
-      <c r="AH27" s="18"/>
-      <c r="AI27" s="17"/>
-      <c r="AJ27" s="17"/>
-      <c r="AK27" s="17"/>
-      <c r="AL27" s="18"/>
-      <c r="AM27" s="17"/>
-      <c r="AN27" s="17"/>
-      <c r="AO27" s="17"/>
-      <c r="AP27" s="18"/>
+      <c r="W27" s="31"/>
+      <c r="X27" s="31"/>
+      <c r="Y27" s="31"/>
+      <c r="Z27" s="31"/>
+      <c r="AA27" s="31"/>
+      <c r="AB27" s="31"/>
+      <c r="AC27" s="31"/>
+      <c r="AD27" s="31"/>
+      <c r="AE27" s="31"/>
+      <c r="AF27" s="31"/>
+      <c r="AG27" s="31"/>
+      <c r="AH27" s="31"/>
+      <c r="AI27" s="31"/>
+      <c r="AJ27" s="18"/>
+      <c r="AK27" s="31"/>
+      <c r="AL27" s="19"/>
+      <c r="AM27" s="19"/>
+      <c r="AN27" s="18"/>
+      <c r="AO27" s="28"/>
+      <c r="AP27" s="19"/>
       <c r="AQ27" s="18"/>
-      <c r="AR27" s="31"/>
-      <c r="AS27" s="31"/>
-      <c r="AT27" s="31"/>
-      <c r="AU27" s="31"/>
-      <c r="AV27" s="31"/>
-      <c r="AW27">
+      <c r="AR27" s="17"/>
+      <c r="AS27" s="29"/>
+      <c r="AT27" s="17"/>
+      <c r="AU27" s="17"/>
+      <c r="AV27" s="17"/>
+      <c r="AW27" s="18"/>
+      <c r="AX27" s="17"/>
+      <c r="AY27" s="17"/>
+      <c r="AZ27" s="17"/>
+      <c r="BA27" s="18"/>
+      <c r="BB27" s="17"/>
+      <c r="BC27" s="17"/>
+      <c r="BD27" s="17"/>
+      <c r="BE27" s="18"/>
+      <c r="BF27" s="18"/>
+      <c r="BG27" s="31"/>
+      <c r="BH27" s="31"/>
+      <c r="BI27" s="31"/>
+      <c r="BJ27" s="31"/>
+      <c r="BK27" s="31"/>
+      <c r="BL27">
         <v>23</v>
       </c>
-      <c r="AY27" t="s">
+      <c r="BN27" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C28" s="4">
         <v>13</v>
       </c>
-      <c r="D28" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="E28" s="31"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
+      <c r="D28" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>129</v>
+      </c>
       <c r="H28" s="30"/>
       <c r="I28" s="31"/>
       <c r="J28" s="31"/>
@@ -2915,51 +3679,72 @@
       <c r="R28" s="31"/>
       <c r="S28" s="31"/>
       <c r="T28" s="31"/>
-      <c r="U28" s="18"/>
+      <c r="U28" s="31"/>
       <c r="V28" s="31"/>
-      <c r="W28" s="19"/>
-      <c r="X28" s="19"/>
-      <c r="Y28" s="33"/>
-      <c r="Z28" s="28"/>
-      <c r="AA28" s="19"/>
-      <c r="AB28" s="18"/>
-      <c r="AC28" s="17"/>
-      <c r="AD28" s="29"/>
-      <c r="AE28" s="17"/>
-      <c r="AF28" s="17"/>
-      <c r="AG28" s="17"/>
-      <c r="AH28" s="18"/>
-      <c r="AI28" s="17"/>
-      <c r="AJ28" s="17"/>
-      <c r="AK28" s="17"/>
-      <c r="AL28" s="18"/>
-      <c r="AM28" s="17"/>
-      <c r="AN28" s="17"/>
-      <c r="AO28" s="17"/>
-      <c r="AP28" s="18"/>
+      <c r="W28" s="31"/>
+      <c r="X28" s="31"/>
+      <c r="Y28" s="31"/>
+      <c r="Z28" s="31"/>
+      <c r="AA28" s="31"/>
+      <c r="AB28" s="31"/>
+      <c r="AC28" s="31"/>
+      <c r="AD28" s="31"/>
+      <c r="AE28" s="31"/>
+      <c r="AF28" s="31"/>
+      <c r="AG28" s="31"/>
+      <c r="AH28" s="31"/>
+      <c r="AI28" s="31"/>
+      <c r="AJ28" s="18"/>
+      <c r="AK28" s="31"/>
+      <c r="AL28" s="19"/>
+      <c r="AM28" s="19"/>
+      <c r="AN28" s="33"/>
+      <c r="AO28" s="28"/>
+      <c r="AP28" s="19"/>
       <c r="AQ28" s="18"/>
-      <c r="AR28" s="31"/>
-      <c r="AS28" s="31"/>
-      <c r="AT28" s="31"/>
-      <c r="AU28" s="31"/>
-      <c r="AV28" s="31"/>
-    </row>
-    <row r="29" spans="1:51" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="AR28" s="17"/>
+      <c r="AS28" s="29"/>
+      <c r="AT28" s="17"/>
+      <c r="AU28" s="17"/>
+      <c r="AV28" s="17"/>
+      <c r="AW28" s="18"/>
+      <c r="AX28" s="17"/>
+      <c r="AY28" s="17"/>
+      <c r="AZ28" s="17"/>
+      <c r="BA28" s="18"/>
+      <c r="BB28" s="17"/>
+      <c r="BC28" s="17"/>
+      <c r="BD28" s="17"/>
+      <c r="BE28" s="18"/>
+      <c r="BF28" s="18"/>
+      <c r="BG28" s="31"/>
+      <c r="BH28" s="31"/>
+      <c r="BI28" s="31"/>
+      <c r="BJ28" s="31"/>
+      <c r="BK28" s="31"/>
+    </row>
+    <row r="29" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C29" s="4">
         <v>15</v>
       </c>
-      <c r="D29" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="E29" s="31"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
+      <c r="D29" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H29" s="30"/>
       <c r="I29" s="31"/>
       <c r="J29" s="31"/>
@@ -2973,51 +3758,72 @@
       <c r="R29" s="31"/>
       <c r="S29" s="31"/>
       <c r="T29" s="31"/>
-      <c r="U29" s="18"/>
+      <c r="U29" s="31"/>
       <c r="V29" s="31"/>
-      <c r="W29" s="19"/>
-      <c r="X29" s="19"/>
-      <c r="Y29" s="33"/>
-      <c r="Z29" s="28"/>
-      <c r="AA29" s="19"/>
-      <c r="AB29" s="18"/>
-      <c r="AC29" s="17"/>
-      <c r="AD29" s="29"/>
-      <c r="AE29" s="17"/>
-      <c r="AF29" s="17"/>
-      <c r="AG29" s="17"/>
-      <c r="AH29" s="18"/>
-      <c r="AI29" s="17"/>
-      <c r="AJ29" s="17"/>
-      <c r="AK29" s="17"/>
-      <c r="AL29" s="18"/>
-      <c r="AM29" s="17"/>
-      <c r="AN29" s="17"/>
-      <c r="AO29" s="17"/>
-      <c r="AP29" s="18"/>
+      <c r="W29" s="31"/>
+      <c r="X29" s="31"/>
+      <c r="Y29" s="31"/>
+      <c r="Z29" s="31"/>
+      <c r="AA29" s="31"/>
+      <c r="AB29" s="31"/>
+      <c r="AC29" s="31"/>
+      <c r="AD29" s="31"/>
+      <c r="AE29" s="31"/>
+      <c r="AF29" s="31"/>
+      <c r="AG29" s="31"/>
+      <c r="AH29" s="31"/>
+      <c r="AI29" s="31"/>
+      <c r="AJ29" s="18"/>
+      <c r="AK29" s="31"/>
+      <c r="AL29" s="19"/>
+      <c r="AM29" s="19"/>
+      <c r="AN29" s="33"/>
+      <c r="AO29" s="28"/>
+      <c r="AP29" s="19"/>
       <c r="AQ29" s="18"/>
-      <c r="AR29" s="31"/>
-      <c r="AS29" s="31"/>
-      <c r="AT29" s="31"/>
-      <c r="AU29" s="31"/>
-      <c r="AV29" s="31"/>
-    </row>
-    <row r="30" spans="1:51" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="AR29" s="17"/>
+      <c r="AS29" s="29"/>
+      <c r="AT29" s="17"/>
+      <c r="AU29" s="17"/>
+      <c r="AV29" s="17"/>
+      <c r="AW29" s="18"/>
+      <c r="AX29" s="17"/>
+      <c r="AY29" s="17"/>
+      <c r="AZ29" s="17"/>
+      <c r="BA29" s="18"/>
+      <c r="BB29" s="17"/>
+      <c r="BC29" s="17"/>
+      <c r="BD29" s="17"/>
+      <c r="BE29" s="18"/>
+      <c r="BF29" s="18"/>
+      <c r="BG29" s="31"/>
+      <c r="BH29" s="31"/>
+      <c r="BI29" s="31"/>
+      <c r="BJ29" s="31"/>
+      <c r="BK29" s="31"/>
+    </row>
+    <row r="30" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C30" s="4">
         <v>12</v>
       </c>
-      <c r="D30" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="E30" s="31"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
+      <c r="D30" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G30" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H30" s="30"/>
       <c r="I30" s="31"/>
       <c r="J30" s="31"/>
@@ -3031,51 +3837,72 @@
       <c r="R30" s="31"/>
       <c r="S30" s="31"/>
       <c r="T30" s="31"/>
-      <c r="U30" s="18"/>
+      <c r="U30" s="31"/>
       <c r="V30" s="31"/>
-      <c r="W30" s="19"/>
-      <c r="X30" s="19"/>
-      <c r="Y30" s="33"/>
-      <c r="Z30" s="28"/>
-      <c r="AA30" s="19"/>
-      <c r="AB30" s="18"/>
-      <c r="AC30" s="17"/>
-      <c r="AD30" s="29"/>
-      <c r="AE30" s="17"/>
-      <c r="AF30" s="17"/>
-      <c r="AG30" s="17"/>
-      <c r="AH30" s="18"/>
-      <c r="AI30" s="17"/>
-      <c r="AJ30" s="17"/>
-      <c r="AK30" s="17"/>
-      <c r="AL30" s="18"/>
-      <c r="AM30" s="17"/>
-      <c r="AN30" s="17"/>
-      <c r="AO30" s="17"/>
-      <c r="AP30" s="18"/>
+      <c r="W30" s="31"/>
+      <c r="X30" s="31"/>
+      <c r="Y30" s="31"/>
+      <c r="Z30" s="31"/>
+      <c r="AA30" s="31"/>
+      <c r="AB30" s="31"/>
+      <c r="AC30" s="31"/>
+      <c r="AD30" s="31"/>
+      <c r="AE30" s="31"/>
+      <c r="AF30" s="31"/>
+      <c r="AG30" s="31"/>
+      <c r="AH30" s="31"/>
+      <c r="AI30" s="31"/>
+      <c r="AJ30" s="18"/>
+      <c r="AK30" s="31"/>
+      <c r="AL30" s="19"/>
+      <c r="AM30" s="19"/>
+      <c r="AN30" s="33"/>
+      <c r="AO30" s="28"/>
+      <c r="AP30" s="19"/>
       <c r="AQ30" s="18"/>
-      <c r="AR30" s="31"/>
-      <c r="AS30" s="31"/>
-      <c r="AT30" s="31"/>
-      <c r="AU30" s="31"/>
-      <c r="AV30" s="31"/>
-    </row>
-    <row r="31" spans="1:51" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="AR30" s="17"/>
+      <c r="AS30" s="29"/>
+      <c r="AT30" s="17"/>
+      <c r="AU30" s="17"/>
+      <c r="AV30" s="17"/>
+      <c r="AW30" s="18"/>
+      <c r="AX30" s="17"/>
+      <c r="AY30" s="17"/>
+      <c r="AZ30" s="17"/>
+      <c r="BA30" s="18"/>
+      <c r="BB30" s="17"/>
+      <c r="BC30" s="17"/>
+      <c r="BD30" s="17"/>
+      <c r="BE30" s="18"/>
+      <c r="BF30" s="18"/>
+      <c r="BG30" s="31"/>
+      <c r="BH30" s="31"/>
+      <c r="BI30" s="31"/>
+      <c r="BJ30" s="31"/>
+      <c r="BK30" s="31"/>
+    </row>
+    <row r="31" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>28</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C31" s="4">
         <v>4</v>
       </c>
-      <c r="D31" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="E31" s="31"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
+      <c r="D31" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G31" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H31" s="30"/>
       <c r="I31" s="31"/>
       <c r="J31" s="31"/>
@@ -3089,51 +3916,72 @@
       <c r="R31" s="31"/>
       <c r="S31" s="31"/>
       <c r="T31" s="31"/>
-      <c r="U31" s="18"/>
+      <c r="U31" s="31"/>
       <c r="V31" s="31"/>
-      <c r="W31" s="19"/>
-      <c r="X31" s="19"/>
-      <c r="Y31" s="33"/>
-      <c r="Z31" s="28"/>
-      <c r="AA31" s="19"/>
-      <c r="AB31" s="18"/>
-      <c r="AC31" s="17"/>
-      <c r="AD31" s="29"/>
-      <c r="AE31" s="17"/>
-      <c r="AF31" s="17"/>
-      <c r="AG31" s="17"/>
-      <c r="AH31" s="18"/>
-      <c r="AI31" s="17"/>
-      <c r="AJ31" s="17"/>
-      <c r="AK31" s="17"/>
-      <c r="AL31" s="18"/>
-      <c r="AM31" s="17"/>
-      <c r="AN31" s="17"/>
-      <c r="AO31" s="17"/>
-      <c r="AP31" s="18"/>
+      <c r="W31" s="31"/>
+      <c r="X31" s="31"/>
+      <c r="Y31" s="31"/>
+      <c r="Z31" s="31"/>
+      <c r="AA31" s="31"/>
+      <c r="AB31" s="31"/>
+      <c r="AC31" s="31"/>
+      <c r="AD31" s="31"/>
+      <c r="AE31" s="31"/>
+      <c r="AF31" s="31"/>
+      <c r="AG31" s="31"/>
+      <c r="AH31" s="31"/>
+      <c r="AI31" s="31"/>
+      <c r="AJ31" s="18"/>
+      <c r="AK31" s="31"/>
+      <c r="AL31" s="19"/>
+      <c r="AM31" s="19"/>
+      <c r="AN31" s="33"/>
+      <c r="AO31" s="28"/>
+      <c r="AP31" s="19"/>
       <c r="AQ31" s="18"/>
-      <c r="AR31" s="31"/>
-      <c r="AS31" s="31"/>
-      <c r="AT31" s="31"/>
-      <c r="AU31" s="31"/>
-      <c r="AV31" s="31"/>
-    </row>
-    <row r="32" spans="1:51" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="AR31" s="17"/>
+      <c r="AS31" s="29"/>
+      <c r="AT31" s="17"/>
+      <c r="AU31" s="17"/>
+      <c r="AV31" s="17"/>
+      <c r="AW31" s="18"/>
+      <c r="AX31" s="17"/>
+      <c r="AY31" s="17"/>
+      <c r="AZ31" s="17"/>
+      <c r="BA31" s="18"/>
+      <c r="BB31" s="17"/>
+      <c r="BC31" s="17"/>
+      <c r="BD31" s="17"/>
+      <c r="BE31" s="18"/>
+      <c r="BF31" s="18"/>
+      <c r="BG31" s="31"/>
+      <c r="BH31" s="31"/>
+      <c r="BI31" s="31"/>
+      <c r="BJ31" s="31"/>
+      <c r="BK31" s="31"/>
+    </row>
+    <row r="32" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>29</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C32" s="4">
         <v>3</v>
       </c>
-      <c r="D32" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="E32" s="31"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
+      <c r="D32" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H32" s="30"/>
       <c r="I32" s="31"/>
       <c r="J32" s="31"/>
@@ -3147,51 +3995,72 @@
       <c r="R32" s="31"/>
       <c r="S32" s="31"/>
       <c r="T32" s="31"/>
-      <c r="U32" s="18"/>
+      <c r="U32" s="31"/>
       <c r="V32" s="31"/>
-      <c r="W32" s="19"/>
-      <c r="X32" s="19"/>
-      <c r="Y32" s="33"/>
-      <c r="Z32" s="28"/>
-      <c r="AA32" s="19"/>
-      <c r="AB32" s="18"/>
-      <c r="AC32" s="17"/>
-      <c r="AD32" s="29"/>
-      <c r="AE32" s="17"/>
-      <c r="AF32" s="17"/>
-      <c r="AG32" s="17"/>
-      <c r="AH32" s="18"/>
-      <c r="AI32" s="17"/>
-      <c r="AJ32" s="17"/>
-      <c r="AK32" s="17"/>
-      <c r="AL32" s="18"/>
-      <c r="AM32" s="17"/>
-      <c r="AN32" s="17"/>
-      <c r="AO32" s="17"/>
-      <c r="AP32" s="18"/>
+      <c r="W32" s="31"/>
+      <c r="X32" s="31"/>
+      <c r="Y32" s="31"/>
+      <c r="Z32" s="31"/>
+      <c r="AA32" s="31"/>
+      <c r="AB32" s="31"/>
+      <c r="AC32" s="31"/>
+      <c r="AD32" s="31"/>
+      <c r="AE32" s="31"/>
+      <c r="AF32" s="31"/>
+      <c r="AG32" s="31"/>
+      <c r="AH32" s="31"/>
+      <c r="AI32" s="31"/>
+      <c r="AJ32" s="18"/>
+      <c r="AK32" s="31"/>
+      <c r="AL32" s="19"/>
+      <c r="AM32" s="19"/>
+      <c r="AN32" s="33"/>
+      <c r="AO32" s="28"/>
+      <c r="AP32" s="19"/>
       <c r="AQ32" s="18"/>
-      <c r="AR32" s="31"/>
-      <c r="AS32" s="31"/>
-      <c r="AT32" s="31"/>
-      <c r="AU32" s="31"/>
-      <c r="AV32" s="31"/>
-    </row>
-    <row r="33" spans="1:51" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="AR32" s="17"/>
+      <c r="AS32" s="29"/>
+      <c r="AT32" s="17"/>
+      <c r="AU32" s="17"/>
+      <c r="AV32" s="17"/>
+      <c r="AW32" s="18"/>
+      <c r="AX32" s="17"/>
+      <c r="AY32" s="17"/>
+      <c r="AZ32" s="17"/>
+      <c r="BA32" s="18"/>
+      <c r="BB32" s="17"/>
+      <c r="BC32" s="17"/>
+      <c r="BD32" s="17"/>
+      <c r="BE32" s="18"/>
+      <c r="BF32" s="18"/>
+      <c r="BG32" s="31"/>
+      <c r="BH32" s="31"/>
+      <c r="BI32" s="31"/>
+      <c r="BJ32" s="31"/>
+      <c r="BK32" s="31"/>
+    </row>
+    <row r="33" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>30</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C33" s="4">
         <v>16</v>
       </c>
-      <c r="D33" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="E33" s="31"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
+      <c r="D33" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>129</v>
+      </c>
       <c r="H33" s="30"/>
       <c r="I33" s="31"/>
       <c r="J33" s="31"/>
@@ -3205,51 +4074,72 @@
       <c r="R33" s="31"/>
       <c r="S33" s="31"/>
       <c r="T33" s="31"/>
-      <c r="U33" s="18"/>
+      <c r="U33" s="31"/>
       <c r="V33" s="31"/>
-      <c r="W33" s="19"/>
-      <c r="X33" s="19"/>
-      <c r="Y33" s="33"/>
-      <c r="Z33" s="28"/>
-      <c r="AA33" s="19"/>
-      <c r="AB33" s="18"/>
-      <c r="AC33" s="17"/>
-      <c r="AD33" s="29"/>
-      <c r="AE33" s="17"/>
-      <c r="AF33" s="17"/>
-      <c r="AG33" s="17"/>
-      <c r="AH33" s="18"/>
-      <c r="AI33" s="17"/>
-      <c r="AJ33" s="17"/>
-      <c r="AK33" s="17"/>
-      <c r="AL33" s="18"/>
-      <c r="AM33" s="17"/>
-      <c r="AN33" s="17"/>
-      <c r="AO33" s="17"/>
-      <c r="AP33" s="18"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+      <c r="Z33" s="31"/>
+      <c r="AA33" s="31"/>
+      <c r="AB33" s="31"/>
+      <c r="AC33" s="31"/>
+      <c r="AD33" s="31"/>
+      <c r="AE33" s="31"/>
+      <c r="AF33" s="31"/>
+      <c r="AG33" s="31"/>
+      <c r="AH33" s="31"/>
+      <c r="AI33" s="31"/>
+      <c r="AJ33" s="18"/>
+      <c r="AK33" s="31"/>
+      <c r="AL33" s="19"/>
+      <c r="AM33" s="19"/>
+      <c r="AN33" s="33"/>
+      <c r="AO33" s="28"/>
+      <c r="AP33" s="19"/>
       <c r="AQ33" s="18"/>
-      <c r="AR33" s="31"/>
-      <c r="AS33" s="31"/>
-      <c r="AT33" s="31"/>
-      <c r="AU33" s="31"/>
-      <c r="AV33" s="31"/>
-    </row>
-    <row r="34" spans="1:51" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="AR33" s="17"/>
+      <c r="AS33" s="29"/>
+      <c r="AT33" s="17"/>
+      <c r="AU33" s="17"/>
+      <c r="AV33" s="17"/>
+      <c r="AW33" s="18"/>
+      <c r="AX33" s="17"/>
+      <c r="AY33" s="17"/>
+      <c r="AZ33" s="17"/>
+      <c r="BA33" s="18"/>
+      <c r="BB33" s="17"/>
+      <c r="BC33" s="17"/>
+      <c r="BD33" s="17"/>
+      <c r="BE33" s="18"/>
+      <c r="BF33" s="18"/>
+      <c r="BG33" s="31"/>
+      <c r="BH33" s="31"/>
+      <c r="BI33" s="31"/>
+      <c r="BJ33" s="31"/>
+      <c r="BK33" s="31"/>
+    </row>
+    <row r="34" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>31</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C34" s="4">
         <v>8</v>
       </c>
-      <c r="D34" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="E34" s="31"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
+      <c r="D34" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F34" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G34" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H34" s="30"/>
       <c r="I34" s="31"/>
       <c r="J34" s="31"/>
@@ -3263,51 +4153,72 @@
       <c r="R34" s="31"/>
       <c r="S34" s="31"/>
       <c r="T34" s="31"/>
-      <c r="U34" s="18"/>
+      <c r="U34" s="31"/>
       <c r="V34" s="31"/>
-      <c r="W34" s="19"/>
-      <c r="X34" s="19"/>
-      <c r="Y34" s="33"/>
-      <c r="Z34" s="28"/>
-      <c r="AA34" s="19"/>
-      <c r="AB34" s="18"/>
-      <c r="AC34" s="17"/>
-      <c r="AD34" s="29"/>
-      <c r="AE34" s="17"/>
-      <c r="AF34" s="17"/>
-      <c r="AG34" s="17"/>
-      <c r="AH34" s="18"/>
-      <c r="AI34" s="17"/>
-      <c r="AJ34" s="17"/>
-      <c r="AK34" s="17"/>
-      <c r="AL34" s="18"/>
-      <c r="AM34" s="17"/>
-      <c r="AN34" s="17"/>
-      <c r="AO34" s="17"/>
-      <c r="AP34" s="18"/>
+      <c r="W34" s="31"/>
+      <c r="X34" s="31"/>
+      <c r="Y34" s="31"/>
+      <c r="Z34" s="31"/>
+      <c r="AA34" s="31"/>
+      <c r="AB34" s="31"/>
+      <c r="AC34" s="31"/>
+      <c r="AD34" s="31"/>
+      <c r="AE34" s="31"/>
+      <c r="AF34" s="31"/>
+      <c r="AG34" s="31"/>
+      <c r="AH34" s="31"/>
+      <c r="AI34" s="31"/>
+      <c r="AJ34" s="18"/>
+      <c r="AK34" s="31"/>
+      <c r="AL34" s="19"/>
+      <c r="AM34" s="19"/>
+      <c r="AN34" s="33"/>
+      <c r="AO34" s="28"/>
+      <c r="AP34" s="19"/>
       <c r="AQ34" s="18"/>
-      <c r="AR34" s="31"/>
-      <c r="AS34" s="31"/>
-      <c r="AT34" s="31"/>
-      <c r="AU34" s="31"/>
-      <c r="AV34" s="31"/>
-    </row>
-    <row r="35" spans="1:51" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="AR34" s="17"/>
+      <c r="AS34" s="29"/>
+      <c r="AT34" s="17"/>
+      <c r="AU34" s="17"/>
+      <c r="AV34" s="17"/>
+      <c r="AW34" s="18"/>
+      <c r="AX34" s="17"/>
+      <c r="AY34" s="17"/>
+      <c r="AZ34" s="17"/>
+      <c r="BA34" s="18"/>
+      <c r="BB34" s="17"/>
+      <c r="BC34" s="17"/>
+      <c r="BD34" s="17"/>
+      <c r="BE34" s="18"/>
+      <c r="BF34" s="18"/>
+      <c r="BG34" s="31"/>
+      <c r="BH34" s="31"/>
+      <c r="BI34" s="31"/>
+      <c r="BJ34" s="31"/>
+      <c r="BK34" s="31"/>
+    </row>
+    <row r="35" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>32</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C35" s="4">
         <v>10</v>
       </c>
-      <c r="D35" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="E35" s="31"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
+      <c r="D35" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G35" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H35" s="30"/>
       <c r="I35" s="31"/>
       <c r="J35" s="31"/>
@@ -3321,51 +4232,72 @@
       <c r="R35" s="31"/>
       <c r="S35" s="31"/>
       <c r="T35" s="31"/>
-      <c r="U35" s="18"/>
+      <c r="U35" s="31"/>
       <c r="V35" s="31"/>
-      <c r="W35" s="19"/>
-      <c r="X35" s="19"/>
-      <c r="Y35" s="33"/>
-      <c r="Z35" s="28"/>
-      <c r="AA35" s="19"/>
-      <c r="AB35" s="18"/>
-      <c r="AC35" s="17"/>
-      <c r="AD35" s="29"/>
-      <c r="AE35" s="17"/>
-      <c r="AF35" s="17"/>
-      <c r="AG35" s="17"/>
-      <c r="AH35" s="18"/>
-      <c r="AI35" s="17"/>
-      <c r="AJ35" s="17"/>
-      <c r="AK35" s="17"/>
-      <c r="AL35" s="18"/>
-      <c r="AM35" s="17"/>
-      <c r="AN35" s="17"/>
-      <c r="AO35" s="17"/>
-      <c r="AP35" s="18"/>
+      <c r="W35" s="31"/>
+      <c r="X35" s="31"/>
+      <c r="Y35" s="31"/>
+      <c r="Z35" s="31"/>
+      <c r="AA35" s="31"/>
+      <c r="AB35" s="31"/>
+      <c r="AC35" s="31"/>
+      <c r="AD35" s="31"/>
+      <c r="AE35" s="31"/>
+      <c r="AF35" s="31"/>
+      <c r="AG35" s="31"/>
+      <c r="AH35" s="31"/>
+      <c r="AI35" s="31"/>
+      <c r="AJ35" s="18"/>
+      <c r="AK35" s="31"/>
+      <c r="AL35" s="19"/>
+      <c r="AM35" s="19"/>
+      <c r="AN35" s="33"/>
+      <c r="AO35" s="28"/>
+      <c r="AP35" s="19"/>
       <c r="AQ35" s="18"/>
-      <c r="AR35" s="31"/>
-      <c r="AS35" s="31"/>
-      <c r="AT35" s="31"/>
-      <c r="AU35" s="31"/>
-      <c r="AV35" s="31"/>
-    </row>
-    <row r="36" spans="1:51" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="AR35" s="17"/>
+      <c r="AS35" s="29"/>
+      <c r="AT35" s="17"/>
+      <c r="AU35" s="17"/>
+      <c r="AV35" s="17"/>
+      <c r="AW35" s="18"/>
+      <c r="AX35" s="17"/>
+      <c r="AY35" s="17"/>
+      <c r="AZ35" s="17"/>
+      <c r="BA35" s="18"/>
+      <c r="BB35" s="17"/>
+      <c r="BC35" s="17"/>
+      <c r="BD35" s="17"/>
+      <c r="BE35" s="18"/>
+      <c r="BF35" s="18"/>
+      <c r="BG35" s="31"/>
+      <c r="BH35" s="31"/>
+      <c r="BI35" s="31"/>
+      <c r="BJ35" s="31"/>
+      <c r="BK35" s="31"/>
+    </row>
+    <row r="36" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>33</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C36" s="4">
         <v>14</v>
       </c>
-      <c r="D36" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="E36" s="31"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
+      <c r="D36" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G36" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="H36" s="30"/>
       <c r="I36" s="31"/>
       <c r="J36" s="31"/>
@@ -3381,76 +4313,91 @@
       <c r="T36" s="31"/>
       <c r="U36" s="31"/>
       <c r="V36" s="31"/>
-      <c r="W36" s="19"/>
-      <c r="X36" s="19"/>
-      <c r="Y36" s="25"/>
-      <c r="Z36" s="20"/>
-      <c r="AA36" s="19"/>
-      <c r="AB36" s="17"/>
-      <c r="AC36" s="17"/>
-      <c r="AD36" s="17"/>
-      <c r="AE36" s="17"/>
-      <c r="AF36" s="17"/>
-      <c r="AG36" s="17"/>
-      <c r="AH36" s="17"/>
-      <c r="AI36" s="17"/>
+      <c r="W36" s="31"/>
+      <c r="X36" s="31"/>
+      <c r="Y36" s="31"/>
+      <c r="Z36" s="31"/>
+      <c r="AA36" s="31"/>
+      <c r="AB36" s="31"/>
+      <c r="AC36" s="31"/>
+      <c r="AD36" s="31"/>
+      <c r="AE36" s="31"/>
+      <c r="AF36" s="31"/>
+      <c r="AG36" s="31"/>
+      <c r="AH36" s="31"/>
+      <c r="AI36" s="31"/>
       <c r="AJ36" s="31"/>
       <c r="AK36" s="31"/>
-      <c r="AL36" s="31"/>
-      <c r="AM36" s="17"/>
-      <c r="AN36" s="17"/>
-      <c r="AO36" s="17"/>
-      <c r="AP36" s="31"/>
-      <c r="AQ36" s="31"/>
-      <c r="AR36" s="31"/>
-      <c r="AS36" s="31"/>
-      <c r="AT36" s="31"/>
-      <c r="AU36" s="31"/>
-      <c r="AV36" s="31"/>
-    </row>
-    <row r="37" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A37" s="42" t="s">
+      <c r="AL36" s="19"/>
+      <c r="AM36" s="19"/>
+      <c r="AN36" s="25"/>
+      <c r="AO36" s="20"/>
+      <c r="AP36" s="19"/>
+      <c r="AQ36" s="17"/>
+      <c r="AR36" s="17"/>
+      <c r="AS36" s="17"/>
+      <c r="AT36" s="17"/>
+      <c r="AU36" s="17"/>
+      <c r="AV36" s="17"/>
+      <c r="AW36" s="17"/>
+      <c r="AX36" s="17"/>
+      <c r="AY36" s="31"/>
+      <c r="AZ36" s="31"/>
+      <c r="BA36" s="31"/>
+      <c r="BB36" s="17"/>
+      <c r="BC36" s="17"/>
+      <c r="BD36" s="17"/>
+      <c r="BE36" s="31"/>
+      <c r="BF36" s="31"/>
+      <c r="BG36" s="31"/>
+      <c r="BH36" s="31"/>
+      <c r="BI36" s="31"/>
+      <c r="BJ36" s="31"/>
+      <c r="BK36" s="31"/>
+    </row>
+    <row r="37" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A37" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="B37" s="43"/>
-      <c r="C37" s="43"/>
-      <c r="D37" s="43"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="43"/>
-      <c r="I37" s="43"/>
-      <c r="J37" s="43"/>
-      <c r="K37" s="43"/>
-      <c r="L37" s="43"/>
-      <c r="M37" s="43"/>
-      <c r="N37" s="43"/>
-      <c r="O37" s="43"/>
-      <c r="P37" s="43"/>
-      <c r="Q37" s="43"/>
-      <c r="R37" s="43"/>
-      <c r="S37" s="43"/>
-      <c r="T37" s="43"/>
-      <c r="U37" s="43"/>
-      <c r="V37" s="43"/>
-      <c r="W37" s="43"/>
-      <c r="X37" s="43"/>
-      <c r="Y37" s="44"/>
-      <c r="Z37" s="2"/>
-      <c r="AA37" s="2"/>
-      <c r="AB37" s="2"/>
-      <c r="AC37" s="2"/>
-      <c r="AD37" s="2"/>
-      <c r="AE37" s="2"/>
-      <c r="AF37" s="2"/>
-      <c r="AG37" s="2"/>
-      <c r="AH37" s="2"/>
-      <c r="AI37" s="2"/>
-      <c r="AJ37" s="2"/>
-      <c r="AK37" s="2"/>
-      <c r="AL37" s="2"/>
-      <c r="AM37" s="2"/>
-      <c r="AN37" s="2"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="45"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="45"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="45"/>
+      <c r="K37" s="45"/>
+      <c r="L37" s="45"/>
+      <c r="M37" s="45"/>
+      <c r="N37" s="45"/>
+      <c r="O37" s="45"/>
+      <c r="P37" s="45"/>
+      <c r="Q37" s="45"/>
+      <c r="R37" s="45"/>
+      <c r="S37" s="45"/>
+      <c r="T37" s="45"/>
+      <c r="U37" s="45"/>
+      <c r="V37" s="45"/>
+      <c r="W37" s="45"/>
+      <c r="X37" s="45"/>
+      <c r="Y37" s="45"/>
+      <c r="Z37" s="45"/>
+      <c r="AA37" s="45"/>
+      <c r="AB37" s="45"/>
+      <c r="AC37" s="45"/>
+      <c r="AD37" s="45"/>
+      <c r="AE37" s="45"/>
+      <c r="AF37" s="45"/>
+      <c r="AG37" s="45"/>
+      <c r="AH37" s="45"/>
+      <c r="AI37" s="45"/>
+      <c r="AJ37" s="45"/>
+      <c r="AK37" s="45"/>
+      <c r="AL37" s="45"/>
+      <c r="AM37" s="45"/>
+      <c r="AN37" s="46"/>
       <c r="AO37" s="2"/>
       <c r="AP37" s="2"/>
       <c r="AQ37" s="2"/>
@@ -3459,56 +4406,71 @@
       <c r="AT37" s="2"/>
       <c r="AU37" s="2"/>
       <c r="AV37" s="2"/>
-      <c r="AW37">
+      <c r="AW37" s="2"/>
+      <c r="AX37" s="2"/>
+      <c r="AY37" s="2"/>
+      <c r="AZ37" s="2"/>
+      <c r="BA37" s="2"/>
+      <c r="BB37" s="2"/>
+      <c r="BC37" s="2"/>
+      <c r="BD37" s="2"/>
+      <c r="BE37" s="2"/>
+      <c r="BF37" s="2"/>
+      <c r="BG37" s="2"/>
+      <c r="BH37" s="2"/>
+      <c r="BI37" s="2"/>
+      <c r="BJ37" s="2"/>
+      <c r="BK37" s="2"/>
+      <c r="BL37">
         <v>24</v>
       </c>
-      <c r="AY37" t="s">
+      <c r="BN37" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A38" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="B38" s="46"/>
-      <c r="C38" s="46"/>
-      <c r="D38" s="46"/>
-      <c r="E38" s="46"/>
-      <c r="F38" s="46"/>
-      <c r="G38" s="46"/>
-      <c r="H38" s="46"/>
-      <c r="I38" s="46"/>
-      <c r="J38" s="46"/>
-      <c r="K38" s="46"/>
-      <c r="L38" s="46"/>
-      <c r="M38" s="46"/>
-      <c r="N38" s="46"/>
-      <c r="O38" s="46"/>
-      <c r="P38" s="46"/>
-      <c r="Q38" s="46"/>
-      <c r="R38" s="46"/>
-      <c r="S38" s="46"/>
-      <c r="T38" s="46"/>
-      <c r="U38" s="46"/>
-      <c r="V38" s="46"/>
-      <c r="W38" s="46"/>
-      <c r="X38" s="46"/>
-      <c r="Y38" s="47"/>
-      <c r="Z38" s="2"/>
-      <c r="AA38" s="2"/>
-      <c r="AB38" s="2"/>
-      <c r="AC38" s="2"/>
-      <c r="AD38" s="2"/>
-      <c r="AE38" s="2"/>
-      <c r="AF38" s="2"/>
-      <c r="AG38" s="2"/>
-      <c r="AH38" s="2"/>
-      <c r="AI38" s="2"/>
-      <c r="AJ38" s="2"/>
-      <c r="AK38" s="2"/>
-      <c r="AL38" s="2"/>
-      <c r="AM38" s="2"/>
-      <c r="AN38" s="2"/>
+    <row r="38" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A38" s="47" t="s">
+        <v>95</v>
+      </c>
+      <c r="B38" s="48"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="48"/>
+      <c r="E38" s="48"/>
+      <c r="F38" s="48"/>
+      <c r="G38" s="48"/>
+      <c r="H38" s="48"/>
+      <c r="I38" s="48"/>
+      <c r="J38" s="48"/>
+      <c r="K38" s="48"/>
+      <c r="L38" s="48"/>
+      <c r="M38" s="48"/>
+      <c r="N38" s="48"/>
+      <c r="O38" s="48"/>
+      <c r="P38" s="48"/>
+      <c r="Q38" s="48"/>
+      <c r="R38" s="48"/>
+      <c r="S38" s="48"/>
+      <c r="T38" s="48"/>
+      <c r="U38" s="48"/>
+      <c r="V38" s="48"/>
+      <c r="W38" s="48"/>
+      <c r="X38" s="48"/>
+      <c r="Y38" s="48"/>
+      <c r="Z38" s="48"/>
+      <c r="AA38" s="48"/>
+      <c r="AB38" s="48"/>
+      <c r="AC38" s="48"/>
+      <c r="AD38" s="48"/>
+      <c r="AE38" s="48"/>
+      <c r="AF38" s="48"/>
+      <c r="AG38" s="48"/>
+      <c r="AH38" s="48"/>
+      <c r="AI38" s="48"/>
+      <c r="AJ38" s="48"/>
+      <c r="AK38" s="48"/>
+      <c r="AL38" s="48"/>
+      <c r="AM38" s="48"/>
+      <c r="AN38" s="49"/>
       <c r="AO38" s="2"/>
       <c r="AP38" s="2"/>
       <c r="AQ38" s="2"/>
@@ -3517,14 +4479,29 @@
       <c r="AT38" s="2"/>
       <c r="AU38" s="2"/>
       <c r="AV38" s="2"/>
-      <c r="AW38">
+      <c r="AW38" s="2"/>
+      <c r="AX38" s="2"/>
+      <c r="AY38" s="2"/>
+      <c r="AZ38" s="2"/>
+      <c r="BA38" s="2"/>
+      <c r="BB38" s="2"/>
+      <c r="BC38" s="2"/>
+      <c r="BD38" s="2"/>
+      <c r="BE38" s="2"/>
+      <c r="BF38" s="2"/>
+      <c r="BG38" s="2"/>
+      <c r="BH38" s="2"/>
+      <c r="BI38" s="2"/>
+      <c r="BJ38" s="2"/>
+      <c r="BK38" s="2"/>
+      <c r="BL38">
         <v>25</v>
       </c>
-      <c r="AY38" t="s">
+      <c r="BN38" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:66" x14ac:dyDescent="0.25">
       <c r="D39">
         <v>1</v>
       </c>
@@ -3573,379 +4550,462 @@
       <c r="S39">
         <v>16</v>
       </c>
-      <c r="W39" t="s">
+      <c r="T39">
+        <v>17</v>
+      </c>
+      <c r="U39">
+        <v>18</v>
+      </c>
+      <c r="V39">
+        <v>19</v>
+      </c>
+      <c r="W39">
+        <v>20</v>
+      </c>
+      <c r="X39">
+        <v>21</v>
+      </c>
+      <c r="Y39">
+        <v>22</v>
+      </c>
+      <c r="Z39">
+        <v>23</v>
+      </c>
+      <c r="AA39">
+        <v>24</v>
+      </c>
+      <c r="AB39">
+        <v>25</v>
+      </c>
+      <c r="AC39">
+        <v>26</v>
+      </c>
+      <c r="AD39">
+        <v>27</v>
+      </c>
+      <c r="AE39">
+        <v>28</v>
+      </c>
+      <c r="AF39">
+        <v>29</v>
+      </c>
+      <c r="AG39">
+        <v>30</v>
+      </c>
+      <c r="AH39">
+        <v>31</v>
+      </c>
+      <c r="AI39">
+        <v>32</v>
+      </c>
+      <c r="BL39">
+        <v>26</v>
+      </c>
+      <c r="BN39" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E40" t="s">
+        <v>135</v>
+      </c>
+      <c r="F40" t="s">
+        <v>134</v>
+      </c>
+      <c r="G40" t="s">
+        <v>135</v>
+      </c>
+      <c r="H40" t="s">
+        <v>134</v>
+      </c>
+      <c r="I40" t="s">
+        <v>135</v>
+      </c>
+      <c r="J40" t="s">
+        <v>134</v>
+      </c>
+      <c r="K40" t="s">
+        <v>135</v>
+      </c>
+      <c r="L40" t="s">
+        <v>134</v>
+      </c>
+      <c r="M40" t="s">
+        <v>135</v>
+      </c>
+      <c r="N40" t="s">
+        <v>134</v>
+      </c>
+      <c r="O40" t="s">
+        <v>135</v>
+      </c>
+      <c r="P40" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>135</v>
+      </c>
+      <c r="R40" t="s">
+        <v>134</v>
+      </c>
+      <c r="S40" t="s">
+        <v>135</v>
+      </c>
+      <c r="AV40"/>
+      <c r="BL40">
+        <v>27</v>
+      </c>
+      <c r="BN40" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D41" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="I41" t="s">
+        <v>68</v>
+      </c>
+      <c r="K41" t="s">
+        <v>69</v>
+      </c>
+      <c r="M41" t="s">
+        <v>70</v>
+      </c>
+      <c r="N41" t="s">
+        <v>70</v>
+      </c>
+      <c r="O41" t="s">
+        <v>71</v>
+      </c>
+      <c r="AX41" t="s">
+        <v>74</v>
+      </c>
+      <c r="BL41">
+        <v>28</v>
+      </c>
+      <c r="BN41" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E42" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="H42" t="s">
+        <v>75</v>
+      </c>
+      <c r="J42" t="s">
+        <v>75</v>
+      </c>
+      <c r="L42" t="s">
+        <v>76</v>
+      </c>
+      <c r="P42" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX42" t="s">
+        <v>78</v>
+      </c>
+      <c r="BL42" s="14">
+        <v>29</v>
+      </c>
+      <c r="BM42" s="14"/>
+      <c r="BN42" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>79</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="L43" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL43" t="s">
         <v>63</v>
       </c>
-      <c r="X39" s="5" t="s">
+      <c r="AM43" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="AW39">
-        <v>26</v>
-      </c>
-      <c r="AY39" t="s">
+      <c r="BL43">
+        <v>30</v>
+      </c>
+      <c r="BN43" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="44" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
+        <v>82</v>
+      </c>
+      <c r="R44" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL44" t="s">
+        <v>65</v>
+      </c>
+      <c r="AM44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BL44">
+        <v>31</v>
+      </c>
+      <c r="BN44" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
+        <v>85</v>
+      </c>
+      <c r="AL45" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM45" t="s">
+        <v>73</v>
+      </c>
+      <c r="BL45" s="14">
+        <v>32</v>
+      </c>
+      <c r="BM45" s="14"/>
+      <c r="BN45" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BL46">
+        <v>33</v>
+      </c>
+      <c r="BN46" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BL47">
+        <v>34</v>
+      </c>
+      <c r="BN47" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="48" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BL48">
+        <v>35</v>
+      </c>
+      <c r="BN48" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BL49">
+        <v>36</v>
+      </c>
+      <c r="BN49" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN50" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="52" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BN52" s="8"/>
+      <c r="BO52" s="9"/>
+      <c r="BP52" s="8"/>
+    </row>
+    <row r="53" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BL53">
+        <v>37</v>
+      </c>
+      <c r="BN53" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="BO53" s="10"/>
+      <c r="BP53" s="10"/>
+    </row>
+    <row r="54" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BL54">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40">
-        <v>3</v>
-      </c>
-      <c r="E40">
-        <v>2</v>
-      </c>
-      <c r="F40">
-        <v>1</v>
-      </c>
-      <c r="G40">
-        <v>3</v>
-      </c>
-      <c r="H40">
-        <v>3</v>
-      </c>
-      <c r="I40">
-        <v>3</v>
-      </c>
-      <c r="J40">
-        <v>3</v>
-      </c>
-      <c r="K40">
-        <v>2</v>
-      </c>
-      <c r="L40">
-        <v>3</v>
-      </c>
-      <c r="M40">
-        <v>2</v>
-      </c>
-      <c r="N40">
-        <v>3</v>
-      </c>
-      <c r="O40">
-        <v>2</v>
-      </c>
-      <c r="P40">
-        <v>3</v>
-      </c>
-      <c r="Q40">
-        <v>2</v>
-      </c>
-      <c r="R40">
-        <v>3</v>
-      </c>
-      <c r="S40">
-        <v>2</v>
-      </c>
-      <c r="W40" t="s">
-        <v>65</v>
-      </c>
-      <c r="X40" t="s">
-        <v>66</v>
-      </c>
-      <c r="AW40">
-        <v>27</v>
-      </c>
-      <c r="AY40" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="41" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" t="s">
-        <v>68</v>
-      </c>
-      <c r="G41" t="s">
-        <v>69</v>
-      </c>
-      <c r="I41" t="s">
-        <v>70</v>
-      </c>
-      <c r="K41" t="s">
-        <v>71</v>
-      </c>
-      <c r="M41" t="s">
-        <v>72</v>
-      </c>
-      <c r="N41" t="s">
-        <v>72</v>
-      </c>
-      <c r="O41" t="s">
-        <v>73</v>
-      </c>
-      <c r="W41" t="s">
-        <v>74</v>
-      </c>
-      <c r="X41" t="s">
-        <v>75</v>
-      </c>
-      <c r="AI41" t="s">
-        <v>76</v>
-      </c>
-      <c r="AW41">
-        <v>28</v>
-      </c>
-      <c r="AY41" t="s">
+      <c r="BN54" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="BO54" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="BP54" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="BQ54">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E42" t="s">
-        <v>77</v>
-      </c>
-      <c r="H42" t="s">
-        <v>78</v>
-      </c>
-      <c r="J42" t="s">
-        <v>78</v>
-      </c>
-      <c r="L42" t="s">
-        <v>79</v>
-      </c>
-      <c r="P42" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI42" t="s">
-        <v>81</v>
-      </c>
-      <c r="AW42" s="14">
-        <v>29</v>
-      </c>
-      <c r="AX42" s="14"/>
-      <c r="AY42" s="14" t="s">
+    <row r="55" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BN55" s="10"/>
+      <c r="BO55" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="BP55" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="BQ55">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BL56">
+        <v>39</v>
+      </c>
+      <c r="BN56" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="BO56" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="BP56" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="BQ56">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BL57">
         <v>40</v>
       </c>
-    </row>
-    <row r="43" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D43" t="s">
-        <v>82</v>
-      </c>
-      <c r="L43" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW43">
-        <v>30</v>
-      </c>
-      <c r="AY43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D44" t="s">
-        <v>85</v>
-      </c>
-      <c r="R44" t="s">
-        <v>86</v>
-      </c>
-      <c r="AW44">
-        <v>31</v>
-      </c>
-      <c r="AY44" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="45" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D45" t="s">
-        <v>88</v>
-      </c>
-      <c r="AW45" s="14">
-        <v>32</v>
-      </c>
-      <c r="AX45" s="14"/>
-      <c r="AY45" s="14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="46" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AW46">
+      <c r="BN57" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="BO57" s="10"/>
+      <c r="BP57" s="10"/>
+    </row>
+    <row r="58" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BL58" s="16">
+        <v>41</v>
+      </c>
+      <c r="BN58" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="BO58" s="10"/>
+      <c r="BP58" s="10"/>
+    </row>
+    <row r="59" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BL59">
+        <v>42</v>
+      </c>
+      <c r="BN59" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="BO59" s="10"/>
+      <c r="BP59" s="10"/>
+    </row>
+    <row r="60" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BL60">
+        <v>43</v>
+      </c>
+      <c r="BN60" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="AY46" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="47" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AW47">
-        <v>34</v>
-      </c>
-      <c r="AY47" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AW48">
-        <v>35</v>
-      </c>
-      <c r="AY48" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="49" spans="49:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AW49">
-        <v>36</v>
-      </c>
-      <c r="AY49" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="50" spans="49:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AY50" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="52" spans="49:54" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AY52" s="8"/>
-      <c r="AZ52" s="9"/>
-      <c r="BA52" s="8"/>
-    </row>
-    <row r="53" spans="49:54" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AW53">
-        <v>37</v>
-      </c>
-      <c r="AY53" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="AZ53" s="10"/>
-      <c r="BA53" s="10"/>
-    </row>
-    <row r="54" spans="49:54" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AW54">
-        <v>38</v>
-      </c>
-      <c r="AY54" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AZ54" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="BA54" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="BB54">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="55" spans="49:54" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AY55" s="10"/>
-      <c r="AZ55" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="BA55" s="8" t="s">
+      <c r="BO60" s="10"/>
+      <c r="BP60" s="10"/>
+    </row>
+    <row r="61" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BL61">
+        <v>44</v>
+      </c>
+      <c r="BN61" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="BO61" s="10"/>
+      <c r="BP61" s="10"/>
+    </row>
+    <row r="62" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BL62">
+        <v>45</v>
+      </c>
+      <c r="BN62" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="BO62" s="10"/>
+      <c r="BP62" s="10"/>
+    </row>
+    <row r="63" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BL63" s="16">
+        <v>46</v>
+      </c>
+      <c r="BN63" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="BO63" s="10"/>
+      <c r="BP63" s="10"/>
+    </row>
+    <row r="64" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BL64">
+        <v>47</v>
+      </c>
+      <c r="BN64" t="s">
         <v>93</v>
       </c>
-      <c r="BB55">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="56" spans="49:54" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AW56">
-        <v>39</v>
-      </c>
-      <c r="AY56" s="8" t="s">
+    </row>
+    <row r="65" spans="64:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BL65">
+        <v>48</v>
+      </c>
+      <c r="BN65" t="s">
         <v>94</v>
       </c>
-      <c r="AZ56" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="BA56" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="BB56">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="57" spans="49:54" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AW57">
-        <v>40</v>
-      </c>
-      <c r="AY57" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="AZ57" s="10"/>
-      <c r="BA57" s="10"/>
-    </row>
-    <row r="58" spans="49:54" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AW58" s="16">
-        <v>41</v>
-      </c>
-      <c r="AY58" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="AZ58" s="10"/>
-      <c r="BA58" s="10"/>
-    </row>
-    <row r="59" spans="49:54" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AW59">
-        <v>42</v>
-      </c>
-      <c r="AY59" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="AZ59" s="10"/>
-      <c r="BA59" s="10"/>
-    </row>
-    <row r="60" spans="49:54" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AW60">
-        <v>43</v>
-      </c>
-      <c r="AY60" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="AZ60" s="10"/>
-      <c r="BA60" s="10"/>
-    </row>
-    <row r="61" spans="49:54" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AW61">
-        <v>44</v>
-      </c>
-      <c r="AY61" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="AZ61" s="10"/>
-      <c r="BA61" s="10"/>
-    </row>
-    <row r="62" spans="49:54" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AW62">
-        <v>45</v>
-      </c>
-      <c r="AY62" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="AZ62" s="10"/>
-      <c r="BA62" s="10"/>
-    </row>
-    <row r="63" spans="49:54" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AW63" s="16">
-        <v>46</v>
-      </c>
-      <c r="AY63" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="AZ63" s="10"/>
-      <c r="BA63" s="10"/>
-    </row>
-    <row r="64" spans="49:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AW64">
-        <v>47</v>
-      </c>
-      <c r="AY64" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="65" spans="49:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AW65">
-        <v>48</v>
-      </c>
-      <c r="AY65" t="s">
-        <v>97</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="AF2:AH3"/>
-    <mergeCell ref="Z2:AB3"/>
-    <mergeCell ref="AC2:AE3"/>
-    <mergeCell ref="A1:Y1"/>
+  <mergeCells count="47">
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="AH2:AH3"/>
+    <mergeCell ref="AI2:AI3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="BI2:BK3"/>
+    <mergeCell ref="A37:AN37"/>
+    <mergeCell ref="A38:AN38"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="AJ2:AJ3"/>
+    <mergeCell ref="AK2:AK3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="AX2:BA3"/>
+    <mergeCell ref="BB2:BE3"/>
+    <mergeCell ref="BF2:BH3"/>
+    <mergeCell ref="AU2:AW3"/>
+    <mergeCell ref="AO2:AQ3"/>
+    <mergeCell ref="AR2:AT3"/>
+    <mergeCell ref="A1:AN1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
@@ -3957,28 +5017,12 @@
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="L2:L3"/>
     <mergeCell ref="M2:M3"/>
-    <mergeCell ref="W2:Y3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="AT2:AV3"/>
-    <mergeCell ref="A37:Y37"/>
-    <mergeCell ref="A38:Y38"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="AI2:AL3"/>
-    <mergeCell ref="AM2:AP3"/>
-    <mergeCell ref="AQ2:AS3"/>
+    <mergeCell ref="AL2:AN3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="AY6" r:id="rId1" display="Прикладная дискретная математика. Приложение. 2016. № 9. С. 68-70." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="AX26" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="AY47" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="BN6" r:id="rId1" display="Прикладная дискретная математика. Приложение. 2016. № 9. С. 68-70." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="BM26" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="BN47" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId4"/>
@@ -3987,12 +5031,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b78dbef7-f85b-47b5-8738-6377d50f4027" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bffb7b91-0466-4de0-9379-f5c53c3acedf">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4197,20 +5243,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b78dbef7-f85b-47b5-8738-6377d50f4027" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bffb7b91-0466-4de0-9379-f5c53c3acedf">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00280879-8A9A-4335-93BC-405126DC8F0C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12ECB55F-B88E-4FE2-9AD5-5CA5D433F306}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b78dbef7-f85b-47b5-8738-6377d50f4027"/>
+    <ds:schemaRef ds:uri="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4235,12 +5282,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12ECB55F-B88E-4FE2-9AD5-5CA5D433F306}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00280879-8A9A-4335-93BC-405126DC8F0C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b78dbef7-f85b-47b5-8738-6377d50f4027"/>
-    <ds:schemaRef ds:uri="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Ведомость ТКИ-441 2026-2027.xlsx
+++ b/Ведомость ТКИ-441 2026-2027.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\StegMethods\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chxrnvkha\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F973D5DE-4589-4428-9638-3FA56A88DF65}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE660568-346F-4A74-9467-CE41F317214B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="183">
   <si>
     <t>Ведомость посещаемости занятий студентами группы ТКИ РУТ МИИТ</t>
   </si>
@@ -37,9 +37,6 @@
   </si>
   <si>
     <t>зачет</t>
-  </si>
-  <si>
-    <t>3 задание Конахович</t>
   </si>
   <si>
     <t>Творческое задание</t>
@@ -232,9 +229,6 @@
     <t>НОВЫЙ МЕТОД СТЕГОАНАЛИЗА ТЕКСТОВЫХ ДАННЫХ, ПОЛУЧЕННЫХ КОДИРОВАНИЕМ ДЛИН СЕРИЙ СИНОНИМОВ / Нечта И.В. // Безопасность информационных технологий. 2018. Т. 25. № 2. С. 114-120.</t>
   </si>
   <si>
-    <t>Автоношкин</t>
-  </si>
-  <si>
     <t>ортогональные функции</t>
   </si>
   <si>
@@ -421,9 +415,6 @@
     <t>1 задание ГПСЧ</t>
   </si>
   <si>
-    <t>2 задание Конахович. Скрытие в изображениях и звуковых файлах. К.р. Форензика</t>
-  </si>
-  <si>
     <t>б</t>
   </si>
   <si>
@@ -443,6 +434,147 @@
   </si>
   <si>
     <t>Множества ортогональных функций на основе перямоугольных импульсов.</t>
+  </si>
+  <si>
+    <t>Зотьев Егор Евгеньевич</t>
+  </si>
+  <si>
+    <t>5.3.3.1</t>
+  </si>
+  <si>
+    <t>Метод относительной замены величин коэффициентов ДКП (метод Коха и Жао)</t>
+  </si>
+  <si>
+    <t>5.3.3.2</t>
+  </si>
+  <si>
+    <t>Метод Бенгама-Мемона-Эо-Юнг</t>
+  </si>
+  <si>
+    <t>5.3.3.3</t>
+  </si>
+  <si>
+    <t>Метод Хсу и Ву</t>
+  </si>
+  <si>
+    <t>Метод Фридриха</t>
+  </si>
+  <si>
+    <t>5.3.3.4</t>
+  </si>
+  <si>
+    <t>5.3.2.2</t>
+  </si>
+  <si>
+    <t>Метод псевдослучайного интервала</t>
+  </si>
+  <si>
+    <t>5.4.3</t>
+  </si>
+  <si>
+    <t>Метод расширения спектра (временная область)</t>
+  </si>
+  <si>
+    <t>5.4.4</t>
+  </si>
+  <si>
+    <t>Скрытие данных с использованием эхо-сигналов</t>
+  </si>
+  <si>
+    <t>Применение множества ортогональных функций на основе перямоугольных импульсов.</t>
+  </si>
+  <si>
+    <t>ГПСЧ. Лр2</t>
+  </si>
+  <si>
+    <t>5.3.2.8</t>
+  </si>
+  <si>
+    <t>Метод Дармстедтера-Делейгла-Квисквотера-Макка</t>
+  </si>
+  <si>
+    <t>5.3.2.7</t>
+  </si>
+  <si>
+    <t>Метод Куттера-Джордана-Боссена</t>
+  </si>
+  <si>
+    <t>5.3.2.6</t>
+  </si>
+  <si>
+    <t>Метод квантования изображения</t>
+  </si>
+  <si>
+    <t>5.3.2.5</t>
+  </si>
+  <si>
+    <t>Метод замены палитры</t>
+  </si>
+  <si>
+    <t>5.3.2.4</t>
+  </si>
+  <si>
+    <t>Метод блочного скрытия</t>
+  </si>
+  <si>
+    <t>5.4.2</t>
+  </si>
+  <si>
+    <t>Метод фазового кодирования</t>
+  </si>
+  <si>
+    <t>5.3.2.3</t>
+  </si>
+  <si>
+    <t>Метод псевдослучайной перестановки</t>
+  </si>
+  <si>
+    <t>Алгоритм F3</t>
+  </si>
+  <si>
+    <t>Алгоритм F4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 задание Конахович. Скрытие в изображениях и звуковых файлах. </t>
+  </si>
+  <si>
+    <t>3 задание. Форензика. Скрытие в текстовых файлах</t>
+  </si>
+  <si>
+    <t>Chromatic Aberration (CA)</t>
+  </si>
+  <si>
+    <t>Sensor Noise</t>
+  </si>
+  <si>
+    <t>JPEG Ghost</t>
+  </si>
+  <si>
+    <t>Rectification</t>
+  </si>
+  <si>
+    <t>Lens Distortion</t>
+  </si>
+  <si>
+    <t>Enhancement</t>
+  </si>
+  <si>
+    <t>9.7</t>
+  </si>
+  <si>
+    <t>9.6</t>
+  </si>
+  <si>
+    <t>9.8</t>
+  </si>
+  <si>
+    <t>Clustering</t>
+  </si>
+  <si>
+    <t>9.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Стеганография с использованием исполняемых файлов</t>
   </si>
 </sst>
 </file>
@@ -496,7 +628,7 @@
       <name val="Times New Roman"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -530,6 +662,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -702,7 +840,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -753,9 +891,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -771,6 +906,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -783,7 +925,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -805,16 +956,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -822,168 +964,7 @@
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1001,15 +982,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>37</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>166255</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>78427</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1032,8 +1013,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17421225" y="790575"/>
-          <a:ext cx="4648200" cy="5153025"/>
+          <a:off x="29307559" y="8714510"/>
+          <a:ext cx="4761634" cy="4913662"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1308,320 +1289,322 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BQ65"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BQ66"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.5703125" customWidth="1"/>
+    <col min="2" max="2" width="35.5546875" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="19" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="35" width="10.85546875" customWidth="1"/>
-    <col min="36" max="36" width="11.5703125" customWidth="1"/>
-    <col min="39" max="39" width="12.28515625" customWidth="1"/>
-    <col min="40" max="40" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="15.7109375" customWidth="1"/>
-    <col min="42" max="42" width="11.85546875" customWidth="1"/>
-    <col min="43" max="43" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="9.140625" style="12"/>
-    <col min="49" max="49" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="11.5703125" customWidth="1"/>
-    <col min="66" max="66" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="19" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="20" max="35" width="10.88671875" customWidth="1"/>
+    <col min="36" max="36" width="11.5546875" customWidth="1"/>
+    <col min="39" max="39" width="12.33203125" customWidth="1"/>
+    <col min="40" max="40" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="15.6640625" customWidth="1"/>
+    <col min="42" max="42" width="11.88671875" customWidth="1"/>
+    <col min="43" max="43" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="9.109375" style="12"/>
+    <col min="49" max="49" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="11.5546875" customWidth="1"/>
+    <col min="66" max="66" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="34.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:68" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="40"/>
-      <c r="Q1" s="40"/>
-      <c r="R1" s="40"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="40"/>
-      <c r="U1" s="40"/>
-      <c r="V1" s="40"/>
-      <c r="W1" s="40"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="40"/>
-      <c r="Z1" s="40"/>
-      <c r="AA1" s="40"/>
-      <c r="AB1" s="40"/>
-      <c r="AC1" s="40"/>
-      <c r="AD1" s="40"/>
-      <c r="AE1" s="40"/>
-      <c r="AF1" s="40"/>
-      <c r="AG1" s="40"/>
-      <c r="AH1" s="40"/>
-      <c r="AI1" s="40"/>
-      <c r="AJ1" s="40"/>
-      <c r="AK1" s="40"/>
-      <c r="AL1" s="40"/>
-      <c r="AM1" s="40"/>
-      <c r="AN1" s="40"/>
-    </row>
-    <row r="2" spans="1:68" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="44"/>
+      <c r="W1" s="44"/>
+      <c r="X1" s="44"/>
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="44"/>
+      <c r="AA1" s="44"/>
+      <c r="AB1" s="44"/>
+      <c r="AC1" s="44"/>
+      <c r="AD1" s="44"/>
+      <c r="AE1" s="44"/>
+      <c r="AF1" s="44"/>
+      <c r="AG1" s="44"/>
+      <c r="AH1" s="44"/>
+      <c r="AI1" s="44"/>
+      <c r="AJ1" s="44"/>
+      <c r="AK1" s="44"/>
+      <c r="AL1" s="44"/>
+      <c r="AM1" s="44"/>
+      <c r="AN1" s="44"/>
+    </row>
+    <row r="2" spans="1:68" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="42" t="s">
+      <c r="B2" s="45"/>
+      <c r="C2" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="50">
+      <c r="D2" s="46">
         <v>46268</v>
       </c>
-      <c r="E2" s="50">
+      <c r="E2" s="46">
         <v>46272</v>
       </c>
-      <c r="F2" s="50">
+      <c r="F2" s="46">
         <v>46275</v>
       </c>
-      <c r="G2" s="50">
+      <c r="G2" s="46">
         <v>46279</v>
       </c>
-      <c r="H2" s="51">
+      <c r="H2" s="48">
         <v>46282</v>
       </c>
-      <c r="I2" s="50">
+      <c r="I2" s="46">
         <v>46286</v>
       </c>
-      <c r="J2" s="51">
+      <c r="J2" s="48">
         <v>46289</v>
       </c>
-      <c r="K2" s="50">
+      <c r="K2" s="46">
         <v>46293</v>
       </c>
-      <c r="L2" s="51">
+      <c r="L2" s="48">
         <v>46296</v>
       </c>
-      <c r="M2" s="50">
+      <c r="M2" s="46">
         <v>46300</v>
       </c>
-      <c r="N2" s="51">
+      <c r="N2" s="48">
         <v>46303</v>
       </c>
-      <c r="O2" s="50">
+      <c r="O2" s="46">
         <v>46307</v>
       </c>
-      <c r="P2" s="51">
+      <c r="P2" s="48">
         <v>46310</v>
       </c>
-      <c r="Q2" s="50">
+      <c r="Q2" s="46">
         <v>46314</v>
       </c>
-      <c r="R2" s="51">
+      <c r="R2" s="48">
         <v>46317</v>
       </c>
-      <c r="S2" s="50">
+      <c r="S2" s="46">
         <v>46321</v>
       </c>
-      <c r="T2" s="50">
+      <c r="T2" s="46">
         <v>46324</v>
       </c>
-      <c r="U2" s="50">
+      <c r="U2" s="46">
         <v>46328</v>
       </c>
-      <c r="V2" s="50">
+      <c r="V2" s="46">
         <v>46331</v>
       </c>
-      <c r="W2" s="50">
+      <c r="W2" s="46">
         <v>46335</v>
       </c>
-      <c r="X2" s="50">
+      <c r="X2" s="46">
         <v>46338</v>
       </c>
-      <c r="Y2" s="50">
+      <c r="Y2" s="46">
         <v>46342</v>
       </c>
-      <c r="Z2" s="50">
+      <c r="Z2" s="46">
         <v>46345</v>
       </c>
-      <c r="AA2" s="50">
+      <c r="AA2" s="46">
         <v>46349</v>
       </c>
-      <c r="AB2" s="50">
+      <c r="AB2" s="46">
         <v>46352</v>
       </c>
-      <c r="AC2" s="50">
+      <c r="AC2" s="46">
         <v>46356</v>
       </c>
-      <c r="AD2" s="51">
+      <c r="AD2" s="48">
         <v>46359</v>
       </c>
-      <c r="AE2" s="51">
+      <c r="AE2" s="48">
         <v>46363</v>
       </c>
-      <c r="AF2" s="51">
+      <c r="AF2" s="48">
         <v>46366</v>
       </c>
-      <c r="AG2" s="51">
+      <c r="AG2" s="48">
         <v>46370</v>
       </c>
-      <c r="AH2" s="51">
+      <c r="AH2" s="48">
         <v>46373</v>
       </c>
-      <c r="AI2" s="51">
+      <c r="AI2" s="48">
         <v>46377</v>
       </c>
-      <c r="AJ2" s="41" t="s">
+      <c r="AJ2" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="AK2" s="41"/>
-      <c r="AL2" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="AM2" s="35"/>
-      <c r="AN2" s="36"/>
-      <c r="AO2" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="AP2" s="35"/>
-      <c r="AQ2" s="36"/>
-      <c r="AR2" s="34" t="s">
+      <c r="AK2" s="45"/>
+      <c r="AL2" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="AM2" s="39"/>
+      <c r="AN2" s="40"/>
+      <c r="AO2" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="AP2" s="39"/>
+      <c r="AQ2" s="40"/>
+      <c r="AR2" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="AS2" s="39"/>
+      <c r="AT2" s="40"/>
+      <c r="AU2" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="AS2" s="35"/>
-      <c r="AT2" s="36"/>
-      <c r="AU2" s="34" t="s">
+      <c r="AV2" s="39"/>
+      <c r="AW2" s="40"/>
+      <c r="AX2" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="AV2" s="35"/>
-      <c r="AW2" s="36"/>
-      <c r="AX2" s="34" t="s">
+      <c r="AY2" s="39"/>
+      <c r="AZ2" s="39"/>
+      <c r="BA2" s="40"/>
+      <c r="BB2" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="AY2" s="35"/>
-      <c r="AZ2" s="35"/>
-      <c r="BA2" s="36"/>
-      <c r="BB2" s="34" t="s">
+      <c r="BC2" s="39"/>
+      <c r="BD2" s="39"/>
+      <c r="BE2" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="BC2" s="35"/>
-      <c r="BD2" s="35"/>
-      <c r="BE2" s="36" t="s">
+      <c r="BF2" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="BF2" s="34" t="s">
+      <c r="BG2" s="39"/>
+      <c r="BH2" s="40"/>
+      <c r="BI2" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="BG2" s="35"/>
-      <c r="BH2" s="36"/>
-      <c r="BI2" s="34" t="s">
+      <c r="BJ2" s="39"/>
+      <c r="BK2" s="40"/>
+    </row>
+    <row r="3" spans="1:68" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="BJ2" s="35"/>
-      <c r="BK2" s="36"/>
-    </row>
-    <row r="3" spans="1:68" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="52"/>
-      <c r="P3" s="53"/>
-      <c r="Q3" s="52"/>
-      <c r="R3" s="53"/>
-      <c r="S3" s="52"/>
-      <c r="T3" s="52"/>
-      <c r="U3" s="52"/>
-      <c r="V3" s="52"/>
-      <c r="W3" s="52"/>
-      <c r="X3" s="52"/>
-      <c r="Y3" s="52"/>
-      <c r="Z3" s="52"/>
-      <c r="AA3" s="52"/>
-      <c r="AB3" s="52"/>
-      <c r="AC3" s="52"/>
-      <c r="AD3" s="53"/>
-      <c r="AE3" s="53"/>
-      <c r="AF3" s="53"/>
-      <c r="AG3" s="53"/>
-      <c r="AH3" s="53"/>
-      <c r="AI3" s="53"/>
-      <c r="AJ3" s="41"/>
-      <c r="AK3" s="41"/>
-      <c r="AL3" s="37"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="39"/>
-      <c r="AO3" s="37"/>
-      <c r="AP3" s="38"/>
-      <c r="AQ3" s="39"/>
-      <c r="AR3" s="37"/>
-      <c r="AS3" s="38"/>
-      <c r="AT3" s="39"/>
-      <c r="AU3" s="37"/>
-      <c r="AV3" s="38"/>
-      <c r="AW3" s="39"/>
-      <c r="AX3" s="37"/>
-      <c r="AY3" s="38"/>
-      <c r="AZ3" s="38"/>
-      <c r="BA3" s="39"/>
-      <c r="BB3" s="37"/>
-      <c r="BC3" s="38"/>
-      <c r="BD3" s="38"/>
-      <c r="BE3" s="39"/>
-      <c r="BF3" s="37"/>
-      <c r="BG3" s="38"/>
-      <c r="BH3" s="39"/>
-      <c r="BI3" s="37"/>
-      <c r="BJ3" s="38"/>
-      <c r="BK3" s="39"/>
-    </row>
-    <row r="4" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C3" s="45"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="47"/>
+      <c r="T3" s="47"/>
+      <c r="U3" s="47"/>
+      <c r="V3" s="47"/>
+      <c r="W3" s="47"/>
+      <c r="X3" s="47"/>
+      <c r="Y3" s="47"/>
+      <c r="Z3" s="47"/>
+      <c r="AA3" s="47"/>
+      <c r="AB3" s="47"/>
+      <c r="AC3" s="47"/>
+      <c r="AD3" s="49"/>
+      <c r="AE3" s="49"/>
+      <c r="AF3" s="49"/>
+      <c r="AG3" s="49"/>
+      <c r="AH3" s="49"/>
+      <c r="AI3" s="49"/>
+      <c r="AJ3" s="45"/>
+      <c r="AK3" s="45"/>
+      <c r="AL3" s="41"/>
+      <c r="AM3" s="50"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="41"/>
+      <c r="AP3" s="42"/>
+      <c r="AQ3" s="43"/>
+      <c r="AR3" s="41"/>
+      <c r="AS3" s="42"/>
+      <c r="AT3" s="43"/>
+      <c r="AU3" s="41"/>
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="43"/>
+      <c r="AX3" s="41"/>
+      <c r="AY3" s="42"/>
+      <c r="AZ3" s="42"/>
+      <c r="BA3" s="43"/>
+      <c r="BB3" s="41"/>
+      <c r="BC3" s="42"/>
+      <c r="BD3" s="42"/>
+      <c r="BE3" s="43"/>
+      <c r="BF3" s="41"/>
+      <c r="BG3" s="42"/>
+      <c r="BH3" s="43"/>
+      <c r="BI3" s="41"/>
+      <c r="BJ3" s="42"/>
+      <c r="BK3" s="43"/>
+    </row>
+    <row r="4" spans="1:68" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C4" s="4">
         <v>1</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
+      <c r="I4" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="J4" s="17"/>
       <c r="K4" s="17"/>
       <c r="L4" s="17"/>
@@ -1653,15 +1636,27 @@
       <c r="AL4" s="19"/>
       <c r="AM4" s="19"/>
       <c r="AN4" s="18"/>
-      <c r="AO4" s="20"/>
-      <c r="AP4" s="19"/>
+      <c r="AO4" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="AP4" s="34" t="s">
+        <v>138</v>
+      </c>
       <c r="AQ4" s="21"/>
-      <c r="AR4" s="17"/>
-      <c r="AS4" s="22"/>
+      <c r="AR4" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="AS4" s="21" t="s">
+        <v>36</v>
+      </c>
       <c r="AT4" s="18"/>
-      <c r="AU4" s="17"/>
-      <c r="AV4" s="22"/>
-      <c r="AW4" s="21"/>
+      <c r="AU4" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="AV4" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="AW4" s="34"/>
       <c r="AX4" s="17"/>
       <c r="AY4" s="17"/>
       <c r="AZ4" s="17"/>
@@ -1677,30 +1672,32 @@
       <c r="BJ4" s="17"/>
       <c r="BK4" s="17"/>
     </row>
-    <row r="5" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:68" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C5" s="4">
         <v>2</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
+      <c r="I5" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="J5" s="17"/>
       <c r="K5" s="17"/>
       <c r="L5" s="17"/>
@@ -1732,15 +1729,27 @@
       <c r="AL5" s="19"/>
       <c r="AM5" s="19"/>
       <c r="AN5" s="21"/>
-      <c r="AO5" s="20"/>
-      <c r="AP5" s="19"/>
+      <c r="AO5" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="AP5" s="34" t="s">
+        <v>140</v>
+      </c>
       <c r="AQ5" s="21"/>
-      <c r="AR5" s="17"/>
-      <c r="AS5" s="17"/>
+      <c r="AR5" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS5" s="21" t="s">
+        <v>88</v>
+      </c>
       <c r="AT5" s="18"/>
-      <c r="AU5" s="17"/>
-      <c r="AV5" s="17"/>
-      <c r="AW5" s="18"/>
+      <c r="AU5" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="AV5" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="AW5" s="34"/>
       <c r="AX5" s="17"/>
       <c r="AY5" s="17"/>
       <c r="AZ5" s="17"/>
@@ -1759,42 +1768,44 @@
         <v>1</v>
       </c>
       <c r="BM5" t="s">
+        <v>17</v>
+      </c>
+      <c r="BN5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="BN5" s="7" t="s">
+      <c r="BO5" t="s">
         <v>19</v>
       </c>
-      <c r="BO5" t="s">
+      <c r="BP5" t="s">
         <v>20</v>
       </c>
-      <c r="BP5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:68" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:68" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C6" s="4">
         <v>3</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
+      <c r="I6" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
       <c r="L6" s="17"/>
@@ -1826,15 +1837,25 @@
       <c r="AL6" s="19"/>
       <c r="AM6" s="19"/>
       <c r="AN6" s="21"/>
-      <c r="AO6" s="20"/>
-      <c r="AP6" s="19"/>
+      <c r="AO6" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="AP6" s="34" t="s">
+        <v>142</v>
+      </c>
       <c r="AQ6" s="21"/>
-      <c r="AR6" s="17"/>
-      <c r="AS6" s="19"/>
+      <c r="AR6" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AS6" s="8" t="s">
+        <v>47</v>
+      </c>
       <c r="AT6" s="18"/>
-      <c r="AU6" s="17"/>
-      <c r="AV6" s="22"/>
-      <c r="AW6" s="18"/>
+      <c r="AU6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="AV6" s="34"/>
+      <c r="AW6" s="34"/>
       <c r="AX6" s="17"/>
       <c r="AY6" s="22"/>
       <c r="AZ6" s="17"/>
@@ -1853,33 +1874,35 @@
         <v>2</v>
       </c>
       <c r="BN6" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:68" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:68" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C7" s="4">
         <v>4</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
+      <c r="I7" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="J7" s="23"/>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
@@ -1911,15 +1934,25 @@
       <c r="AL7" s="19"/>
       <c r="AM7" s="19"/>
       <c r="AN7" s="25"/>
-      <c r="AO7" s="20"/>
-      <c r="AP7" s="19"/>
+      <c r="AO7" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="AP7" s="19" t="s">
+        <v>143</v>
+      </c>
       <c r="AQ7" s="17"/>
-      <c r="AR7" s="17"/>
-      <c r="AS7" s="19"/>
+      <c r="AR7" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="AS7" s="7" t="s">
+        <v>171</v>
+      </c>
       <c r="AT7" s="17"/>
-      <c r="AU7" s="17"/>
-      <c r="AV7" s="17"/>
-      <c r="AW7" s="17"/>
+      <c r="AU7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="AV7" s="34"/>
+      <c r="AW7" s="34"/>
       <c r="AX7" s="17"/>
       <c r="AY7" s="22"/>
       <c r="AZ7" s="17"/>
@@ -1938,33 +1971,35 @@
         <v>3</v>
       </c>
       <c r="BN7" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:68" ht="18" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C8" s="4">
         <v>17</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
+      <c r="I8" s="17" t="s">
+        <v>127</v>
+      </c>
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
       <c r="L8" s="17"/>
@@ -1996,13 +2031,23 @@
       <c r="AL8" s="19"/>
       <c r="AM8" s="19"/>
       <c r="AN8" s="25"/>
-      <c r="AO8" s="20"/>
-      <c r="AP8" s="19"/>
+      <c r="AO8" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="AP8" s="34" t="s">
+        <v>166</v>
+      </c>
       <c r="AQ8" s="17"/>
-      <c r="AR8" s="17"/>
-      <c r="AS8" s="17"/>
+      <c r="AR8" s="34">
+        <v>9.4</v>
+      </c>
+      <c r="AS8" s="7" t="s">
+        <v>172</v>
+      </c>
       <c r="AT8" s="17"/>
-      <c r="AU8" s="17"/>
+      <c r="AU8" s="37" t="s">
+        <v>22</v>
+      </c>
       <c r="AV8" s="17"/>
       <c r="AW8" s="17"/>
       <c r="AX8" s="17"/>
@@ -2023,33 +2068,35 @@
         <v>4</v>
       </c>
       <c r="BN8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:68" ht="18" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C9" s="4">
         <v>5</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
+      <c r="I9" s="17" t="s">
+        <v>127</v>
+      </c>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
@@ -2081,11 +2128,19 @@
       <c r="AL9" s="19"/>
       <c r="AM9" s="19"/>
       <c r="AN9" s="21"/>
-      <c r="AO9" s="20"/>
-      <c r="AP9" s="19"/>
+      <c r="AO9" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="AP9" s="19" t="s">
+        <v>148</v>
+      </c>
       <c r="AQ9" s="21"/>
-      <c r="AR9" s="17"/>
-      <c r="AS9" s="17"/>
+      <c r="AR9" s="34">
+        <v>9.1</v>
+      </c>
+      <c r="AS9" s="7" t="s">
+        <v>173</v>
+      </c>
       <c r="AT9" s="18"/>
       <c r="AU9" s="17"/>
       <c r="AV9" s="17"/>
@@ -2108,33 +2163,35 @@
         <v>5</v>
       </c>
       <c r="BN9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:68" ht="18" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" s="4">
         <v>6</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
+      <c r="I10" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="J10" s="17"/>
       <c r="K10" s="17"/>
       <c r="L10" s="17"/>
@@ -2166,12 +2223,20 @@
       <c r="AL10" s="19"/>
       <c r="AM10" s="19"/>
       <c r="AN10" s="21"/>
-      <c r="AO10" s="20"/>
-      <c r="AP10" s="19"/>
+      <c r="AO10" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="AP10" s="34" t="s">
+        <v>146</v>
+      </c>
       <c r="AQ10" s="18"/>
-      <c r="AR10" s="17"/>
-      <c r="AS10" s="22"/>
-      <c r="AT10" s="18"/>
+      <c r="AR10" s="34" t="s">
+        <v>177</v>
+      </c>
+      <c r="AS10" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="AT10" s="34"/>
       <c r="AU10" s="17"/>
       <c r="AV10" s="17"/>
       <c r="AW10" s="17"/>
@@ -2193,33 +2258,35 @@
         <v>6</v>
       </c>
       <c r="BN10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:68" ht="18" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C11" s="4">
         <v>7</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
+      <c r="I11" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="J11" s="17"/>
       <c r="K11" s="17"/>
       <c r="L11" s="17"/>
@@ -2251,12 +2318,20 @@
       <c r="AL11" s="19"/>
       <c r="AM11" s="19"/>
       <c r="AN11" s="21"/>
-      <c r="AO11" s="20"/>
-      <c r="AP11" s="19"/>
+      <c r="AO11" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="AP11" s="34" t="s">
+        <v>154</v>
+      </c>
       <c r="AQ11" s="18"/>
-      <c r="AR11" s="17"/>
-      <c r="AS11" s="22"/>
-      <c r="AT11" s="18"/>
+      <c r="AR11" s="34" t="s">
+        <v>181</v>
+      </c>
+      <c r="AS11" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="AT11" s="34"/>
       <c r="AU11" s="17"/>
       <c r="AV11" s="17"/>
       <c r="AW11" s="18"/>
@@ -2278,33 +2353,37 @@
         <v>7</v>
       </c>
       <c r="BN11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:68" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>9</v>
       </c>
-      <c r="B12" s="32" t="s">
-        <v>103</v>
+      <c r="B12" s="31" t="s">
+        <v>101</v>
       </c>
       <c r="C12" s="4">
         <v>8</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
+        <v>127</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="I12" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
       <c r="L12" s="17"/>
@@ -2336,12 +2415,18 @@
       <c r="AL12" s="19"/>
       <c r="AM12" s="19"/>
       <c r="AN12" s="21"/>
-      <c r="AO12" s="26"/>
-      <c r="AP12" s="19"/>
+      <c r="AO12" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="AP12" s="19" t="s">
+        <v>156</v>
+      </c>
       <c r="AQ12" s="21"/>
-      <c r="AR12" s="17"/>
-      <c r="AS12" s="22"/>
-      <c r="AT12" s="21"/>
+      <c r="AR12" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="AS12" s="34"/>
+      <c r="AT12" s="34"/>
       <c r="AU12" s="17"/>
       <c r="AV12" s="17"/>
       <c r="AW12" s="18"/>
@@ -2363,33 +2448,35 @@
         <v>8</v>
       </c>
       <c r="BN12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:68" ht="18" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C13" s="4">
         <v>9</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
+      <c r="I13" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="J13" s="17"/>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
@@ -2421,8 +2508,12 @@
       <c r="AL13" s="19"/>
       <c r="AM13" s="19"/>
       <c r="AN13" s="21"/>
-      <c r="AO13" s="22"/>
-      <c r="AP13" s="19"/>
+      <c r="AO13" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="AP13" s="34" t="s">
+        <v>158</v>
+      </c>
       <c r="AQ13" s="18"/>
       <c r="AR13" s="17"/>
       <c r="AS13" s="22"/>
@@ -2448,33 +2539,35 @@
         <v>9</v>
       </c>
       <c r="BN13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:68" ht="18" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C14" s="4">
         <v>10</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
+      <c r="I14" s="17" t="s">
+        <v>127</v>
+      </c>
       <c r="J14" s="17"/>
       <c r="K14" s="17"/>
       <c r="L14" s="17"/>
@@ -2506,8 +2599,12 @@
       <c r="AL14" s="19"/>
       <c r="AM14" s="19"/>
       <c r="AN14" s="25"/>
-      <c r="AO14" s="20"/>
-      <c r="AP14" s="19"/>
+      <c r="AO14" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="AP14" s="34" t="s">
+        <v>160</v>
+      </c>
       <c r="AQ14" s="17"/>
       <c r="AR14" s="17"/>
       <c r="AS14" s="17"/>
@@ -2533,33 +2630,35 @@
         <v>10</v>
       </c>
       <c r="BN14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:68" ht="18" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C15" s="4">
         <v>7</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
+      <c r="I15" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="J15" s="17"/>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
@@ -2591,8 +2690,12 @@
       <c r="AL15" s="19"/>
       <c r="AM15" s="19"/>
       <c r="AN15" s="18"/>
-      <c r="AO15" s="20"/>
-      <c r="AP15" s="19"/>
+      <c r="AO15" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="AP15" s="34" t="s">
+        <v>154</v>
+      </c>
       <c r="AQ15" s="21"/>
       <c r="AR15" s="17"/>
       <c r="AS15" s="22"/>
@@ -2618,33 +2721,35 @@
         <v>11</v>
       </c>
       <c r="BN15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:68" ht="18" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C16" s="4">
         <v>1</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
+      <c r="I16" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="J16" s="17"/>
       <c r="K16" s="17"/>
       <c r="L16" s="17"/>
@@ -2676,17 +2781,25 @@
       <c r="AL16" s="18"/>
       <c r="AM16" s="19"/>
       <c r="AN16" s="25"/>
-      <c r="AO16" s="26"/>
-      <c r="AP16" s="19"/>
+      <c r="AO16" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="AP16" s="34" t="s">
+        <v>138</v>
+      </c>
       <c r="AQ16" s="18"/>
-      <c r="AR16" s="17"/>
-      <c r="AS16" s="22"/>
+      <c r="AR16" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="AS16" s="21" t="s">
+        <v>36</v>
+      </c>
       <c r="AT16" s="18"/>
       <c r="AU16" s="17"/>
       <c r="AV16" s="22"/>
       <c r="AW16" s="18"/>
       <c r="AX16" s="17"/>
-      <c r="AY16" s="27"/>
+      <c r="AY16" s="26"/>
       <c r="AZ16" s="17"/>
       <c r="BA16" s="18"/>
       <c r="BB16" s="17"/>
@@ -2703,33 +2816,35 @@
         <v>12</v>
       </c>
       <c r="BN16" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:66" ht="18" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>14</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C17" s="4">
         <v>11</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
+      <c r="I17" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="J17" s="17"/>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
@@ -2761,8 +2876,12 @@
       <c r="AL17" s="19"/>
       <c r="AM17" s="19"/>
       <c r="AN17" s="21"/>
-      <c r="AO17" s="20"/>
-      <c r="AP17" s="19"/>
+      <c r="AO17" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="AP17" s="34" t="s">
+        <v>162</v>
+      </c>
       <c r="AQ17" s="18"/>
       <c r="AR17" s="17"/>
       <c r="AS17" s="17"/>
@@ -2788,33 +2907,37 @@
         <v>13</v>
       </c>
       <c r="BN17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:66" ht="18" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C18" s="4">
         <v>12</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
+        <v>129</v>
+      </c>
+      <c r="H18" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="J18" s="17"/>
       <c r="K18" s="17"/>
       <c r="L18" s="17"/>
@@ -2846,8 +2969,12 @@
       <c r="AL18" s="19"/>
       <c r="AM18" s="19"/>
       <c r="AN18" s="21"/>
-      <c r="AO18" s="28"/>
-      <c r="AP18" s="19"/>
+      <c r="AO18" s="35" t="s">
+        <v>163</v>
+      </c>
+      <c r="AP18" s="34" t="s">
+        <v>164</v>
+      </c>
       <c r="AQ18" s="21"/>
       <c r="AR18" s="17"/>
       <c r="AS18" s="22"/>
@@ -2873,33 +3000,35 @@
         <v>14</v>
       </c>
       <c r="BN18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:66" ht="18" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>16</v>
       </c>
-      <c r="B19" s="32" t="s">
-        <v>110</v>
+      <c r="B19" s="31" t="s">
+        <v>108</v>
       </c>
       <c r="C19" s="4">
         <v>11</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
+      <c r="I19" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="J19" s="17"/>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
@@ -2931,9 +3060,13 @@
       <c r="AL19" s="19"/>
       <c r="AM19" s="19"/>
       <c r="AN19" s="21"/>
-      <c r="AO19" s="26"/>
-      <c r="AP19" s="19"/>
-      <c r="AQ19" s="21"/>
+      <c r="AO19" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="AP19" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="AQ19" s="18"/>
       <c r="AR19" s="17"/>
       <c r="AS19" s="22"/>
       <c r="AT19" s="21"/>
@@ -2958,33 +3091,35 @@
         <v>15</v>
       </c>
       <c r="BN19" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:66" ht="18" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C20" s="4">
         <v>5</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
+      <c r="I20" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="J20" s="17"/>
       <c r="K20" s="17"/>
       <c r="L20" s="17"/>
@@ -3016,11 +3151,15 @@
       <c r="AL20" s="19"/>
       <c r="AM20" s="19"/>
       <c r="AN20" s="21"/>
-      <c r="AO20" s="28"/>
-      <c r="AP20" s="19"/>
+      <c r="AO20" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="AP20" s="19" t="s">
+        <v>148</v>
+      </c>
       <c r="AQ20" s="18"/>
       <c r="AR20" s="17"/>
-      <c r="AS20" s="29"/>
+      <c r="AS20" s="28"/>
       <c r="AT20" s="17"/>
       <c r="AU20" s="17"/>
       <c r="AV20" s="17"/>
@@ -3043,33 +3182,35 @@
         <v>16</v>
       </c>
       <c r="BN20" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:66" ht="18" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C21" s="4">
         <v>17</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
+      <c r="I21" s="17" t="s">
+        <v>127</v>
+      </c>
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
       <c r="L21" s="17"/>
@@ -3101,8 +3242,12 @@
       <c r="AL21" s="19"/>
       <c r="AM21" s="19"/>
       <c r="AN21" s="21"/>
-      <c r="AO21" s="20"/>
-      <c r="AP21" s="19"/>
+      <c r="AO21" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="AP21" s="34" t="s">
+        <v>166</v>
+      </c>
       <c r="AQ21" s="21"/>
       <c r="AR21" s="17"/>
       <c r="AS21" s="17"/>
@@ -3128,33 +3273,35 @@
         <v>17</v>
       </c>
       <c r="BN21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:66" ht="18" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C22" s="4">
         <v>13</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
+      <c r="I22" s="17" t="s">
+        <v>127</v>
+      </c>
       <c r="J22" s="17"/>
       <c r="K22" s="17"/>
       <c r="L22" s="17"/>
@@ -3186,8 +3333,12 @@
       <c r="AL22" s="19"/>
       <c r="AM22" s="19"/>
       <c r="AN22" s="21"/>
-      <c r="AO22" s="28"/>
-      <c r="AP22" s="19"/>
+      <c r="AO22" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="AP22" s="7" t="s">
+        <v>150</v>
+      </c>
       <c r="AQ22" s="21"/>
       <c r="AR22" s="17"/>
       <c r="AS22" s="22"/>
@@ -3213,33 +3364,35 @@
         <v>18</v>
       </c>
       <c r="BN22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:66" ht="18" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C23" s="4">
         <v>14</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
+      <c r="I23" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="J23" s="17"/>
       <c r="K23" s="17"/>
       <c r="L23" s="17"/>
@@ -3271,7 +3424,9 @@
       <c r="AL23" s="18"/>
       <c r="AM23" s="19"/>
       <c r="AN23" s="21"/>
-      <c r="AO23" s="17"/>
+      <c r="AO23" s="26" t="s">
+        <v>167</v>
+      </c>
       <c r="AP23" s="19"/>
       <c r="AQ23" s="18"/>
       <c r="AR23" s="17"/>
@@ -3281,7 +3436,7 @@
       <c r="AV23" s="22"/>
       <c r="AW23" s="18"/>
       <c r="AX23" s="17"/>
-      <c r="AY23" s="27"/>
+      <c r="AY23" s="26"/>
       <c r="AZ23" s="17"/>
       <c r="BA23" s="18"/>
       <c r="BB23" s="17"/>
@@ -3298,33 +3453,35 @@
         <v>19</v>
       </c>
       <c r="BN23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:66" ht="18" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C24" s="4">
         <v>15</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
+      <c r="I24" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="J24" s="17"/>
       <c r="K24" s="17"/>
       <c r="L24" s="17"/>
@@ -3356,7 +3513,9 @@
       <c r="AL24" s="19"/>
       <c r="AM24" s="19"/>
       <c r="AN24" s="25"/>
-      <c r="AO24" s="17"/>
+      <c r="AO24" s="26" t="s">
+        <v>168</v>
+      </c>
       <c r="AP24" s="17"/>
       <c r="AQ24" s="17"/>
       <c r="AR24" s="17"/>
@@ -3383,33 +3542,37 @@
         <v>20</v>
       </c>
       <c r="BN24" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:66" ht="18" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>22</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C25" s="4">
         <v>16</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
+        <v>126</v>
+      </c>
+      <c r="H25" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="I25" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="J25" s="17"/>
       <c r="K25" s="17"/>
       <c r="L25" s="17"/>
@@ -3441,7 +3604,9 @@
       <c r="AL25" s="19"/>
       <c r="AM25" s="19"/>
       <c r="AN25" s="21"/>
-      <c r="AO25" s="20"/>
+      <c r="AO25" s="26" t="s">
+        <v>51</v>
+      </c>
       <c r="AP25" s="19"/>
       <c r="AQ25" s="21"/>
       <c r="AR25" s="17"/>
@@ -3468,73 +3633,79 @@
         <v>21</v>
       </c>
       <c r="BN25" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="26" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:66" ht="18" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C26" s="4">
         <v>9</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="30"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="30"/>
+        <v>129</v>
+      </c>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
       <c r="O26" s="23"/>
-      <c r="P26" s="30"/>
-      <c r="Q26" s="30"/>
-      <c r="R26" s="30"/>
-      <c r="S26" s="30"/>
-      <c r="T26" s="30"/>
-      <c r="U26" s="30"/>
-      <c r="V26" s="30"/>
-      <c r="W26" s="30"/>
-      <c r="X26" s="30"/>
-      <c r="Y26" s="30"/>
-      <c r="Z26" s="30"/>
-      <c r="AA26" s="30"/>
-      <c r="AB26" s="30"/>
-      <c r="AC26" s="30"/>
-      <c r="AD26" s="30"/>
-      <c r="AE26" s="30"/>
-      <c r="AF26" s="30"/>
-      <c r="AG26" s="30"/>
-      <c r="AH26" s="30"/>
-      <c r="AI26" s="30"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="29"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="29"/>
+      <c r="T26" s="29"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="29"/>
+      <c r="W26" s="29"/>
+      <c r="X26" s="29"/>
+      <c r="Y26" s="29"/>
+      <c r="Z26" s="29"/>
+      <c r="AA26" s="29"/>
+      <c r="AB26" s="29"/>
+      <c r="AC26" s="29"/>
+      <c r="AD26" s="29"/>
+      <c r="AE26" s="29"/>
+      <c r="AF26" s="29"/>
+      <c r="AG26" s="29"/>
+      <c r="AH26" s="29"/>
+      <c r="AI26" s="29"/>
       <c r="AJ26" s="18"/>
-      <c r="AK26" s="30"/>
+      <c r="AK26" s="29"/>
       <c r="AL26" s="19"/>
       <c r="AM26" s="19"/>
       <c r="AN26" s="21"/>
-      <c r="AO26" s="20"/>
-      <c r="AP26" s="19"/>
+      <c r="AO26" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="AP26" s="34" t="s">
+        <v>158</v>
+      </c>
       <c r="AQ26" s="18"/>
       <c r="AR26" s="17"/>
       <c r="AS26" s="22"/>
       <c r="AT26" s="18"/>
       <c r="AU26" s="17"/>
       <c r="AV26" s="17"/>
-      <c r="AW26" s="30"/>
+      <c r="AW26" s="29"/>
       <c r="AX26" s="17"/>
       <c r="AY26" s="17"/>
       <c r="AZ26" s="17"/>
@@ -3544,81 +3715,91 @@
       <c r="BD26" s="17"/>
       <c r="BE26" s="18"/>
       <c r="BF26" s="18"/>
-      <c r="BG26" s="30"/>
-      <c r="BH26" s="30"/>
-      <c r="BI26" s="30"/>
-      <c r="BJ26" s="30"/>
-      <c r="BK26" s="30"/>
+      <c r="BG26" s="29"/>
+      <c r="BH26" s="29"/>
+      <c r="BI26" s="29"/>
+      <c r="BJ26" s="29"/>
+      <c r="BK26" s="29"/>
       <c r="BL26" s="14">
         <v>22</v>
       </c>
       <c r="BM26" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BN26" s="14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:66" ht="18" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>24</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C27" s="4">
         <v>2</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="H27" s="30"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="31"/>
-      <c r="K27" s="31"/>
-      <c r="L27" s="31"/>
-      <c r="M27" s="31"/>
-      <c r="N27" s="31"/>
-      <c r="O27" s="31"/>
-      <c r="P27" s="31"/>
-      <c r="Q27" s="31"/>
-      <c r="R27" s="31"/>
-      <c r="S27" s="31"/>
-      <c r="T27" s="31"/>
-      <c r="U27" s="31"/>
-      <c r="V27" s="31"/>
-      <c r="W27" s="31"/>
-      <c r="X27" s="31"/>
-      <c r="Y27" s="31"/>
-      <c r="Z27" s="31"/>
-      <c r="AA27" s="31"/>
-      <c r="AB27" s="31"/>
-      <c r="AC27" s="31"/>
-      <c r="AD27" s="31"/>
-      <c r="AE27" s="31"/>
-      <c r="AF27" s="31"/>
-      <c r="AG27" s="31"/>
-      <c r="AH27" s="31"/>
-      <c r="AI27" s="31"/>
+        <v>126</v>
+      </c>
+      <c r="H27" s="29"/>
+      <c r="I27" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="30"/>
+      <c r="P27" s="30"/>
+      <c r="Q27" s="30"/>
+      <c r="R27" s="30"/>
+      <c r="S27" s="30"/>
+      <c r="T27" s="30"/>
+      <c r="U27" s="30"/>
+      <c r="V27" s="30"/>
+      <c r="W27" s="30"/>
+      <c r="X27" s="30"/>
+      <c r="Y27" s="30"/>
+      <c r="Z27" s="30"/>
+      <c r="AA27" s="30"/>
+      <c r="AB27" s="30"/>
+      <c r="AC27" s="30"/>
+      <c r="AD27" s="30"/>
+      <c r="AE27" s="30"/>
+      <c r="AF27" s="30"/>
+      <c r="AG27" s="30"/>
+      <c r="AH27" s="30"/>
+      <c r="AI27" s="30"/>
       <c r="AJ27" s="18"/>
-      <c r="AK27" s="31"/>
+      <c r="AK27" s="30"/>
       <c r="AL27" s="19"/>
       <c r="AM27" s="19"/>
       <c r="AN27" s="18"/>
-      <c r="AO27" s="28"/>
-      <c r="AP27" s="19"/>
+      <c r="AO27" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="AP27" s="34" t="s">
+        <v>140</v>
+      </c>
       <c r="AQ27" s="18"/>
-      <c r="AR27" s="17"/>
-      <c r="AS27" s="29"/>
+      <c r="AR27" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS27" s="21" t="s">
+        <v>88</v>
+      </c>
       <c r="AT27" s="17"/>
       <c r="AU27" s="17"/>
       <c r="AV27" s="17"/>
@@ -3632,78 +3813,86 @@
       <c r="BD27" s="17"/>
       <c r="BE27" s="18"/>
       <c r="BF27" s="18"/>
-      <c r="BG27" s="31"/>
-      <c r="BH27" s="31"/>
-      <c r="BI27" s="31"/>
-      <c r="BJ27" s="31"/>
-      <c r="BK27" s="31"/>
+      <c r="BG27" s="30"/>
+      <c r="BH27" s="30"/>
+      <c r="BI27" s="30"/>
+      <c r="BJ27" s="30"/>
+      <c r="BK27" s="30"/>
       <c r="BL27">
         <v>23</v>
       </c>
       <c r="BN27" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:66" ht="18" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C28" s="4">
         <v>13</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="H28" s="30"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
-      <c r="T28" s="31"/>
-      <c r="U28" s="31"/>
-      <c r="V28" s="31"/>
-      <c r="W28" s="31"/>
-      <c r="X28" s="31"/>
-      <c r="Y28" s="31"/>
-      <c r="Z28" s="31"/>
-      <c r="AA28" s="31"/>
-      <c r="AB28" s="31"/>
-      <c r="AC28" s="31"/>
-      <c r="AD28" s="31"/>
-      <c r="AE28" s="31"/>
-      <c r="AF28" s="31"/>
-      <c r="AG28" s="31"/>
-      <c r="AH28" s="31"/>
-      <c r="AI28" s="31"/>
+        <v>127</v>
+      </c>
+      <c r="H28" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="I28" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="30"/>
+      <c r="P28" s="30"/>
+      <c r="Q28" s="30"/>
+      <c r="R28" s="30"/>
+      <c r="S28" s="30"/>
+      <c r="T28" s="30"/>
+      <c r="U28" s="30"/>
+      <c r="V28" s="30"/>
+      <c r="W28" s="30"/>
+      <c r="X28" s="30"/>
+      <c r="Y28" s="30"/>
+      <c r="Z28" s="30"/>
+      <c r="AA28" s="30"/>
+      <c r="AB28" s="30"/>
+      <c r="AC28" s="30"/>
+      <c r="AD28" s="30"/>
+      <c r="AE28" s="30"/>
+      <c r="AF28" s="30"/>
+      <c r="AG28" s="30"/>
+      <c r="AH28" s="30"/>
+      <c r="AI28" s="30"/>
       <c r="AJ28" s="18"/>
-      <c r="AK28" s="31"/>
+      <c r="AK28" s="30"/>
       <c r="AL28" s="19"/>
       <c r="AM28" s="19"/>
-      <c r="AN28" s="33"/>
-      <c r="AO28" s="28"/>
-      <c r="AP28" s="19"/>
+      <c r="AN28" s="32"/>
+      <c r="AO28" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="AP28" s="7" t="s">
+        <v>150</v>
+      </c>
       <c r="AQ28" s="18"/>
       <c r="AR28" s="17"/>
-      <c r="AS28" s="29"/>
+      <c r="AS28" s="28"/>
       <c r="AT28" s="17"/>
       <c r="AU28" s="17"/>
       <c r="AV28" s="17"/>
@@ -3717,72 +3906,76 @@
       <c r="BD28" s="17"/>
       <c r="BE28" s="18"/>
       <c r="BF28" s="18"/>
-      <c r="BG28" s="31"/>
-      <c r="BH28" s="31"/>
-      <c r="BI28" s="31"/>
-      <c r="BJ28" s="31"/>
-      <c r="BK28" s="31"/>
-    </row>
-    <row r="29" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="BG28" s="30"/>
+      <c r="BH28" s="30"/>
+      <c r="BI28" s="30"/>
+      <c r="BJ28" s="30"/>
+      <c r="BK28" s="30"/>
+    </row>
+    <row r="29" spans="1:66" ht="18" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C29" s="4">
         <v>15</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="H29" s="30"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="31"/>
-      <c r="N29" s="31"/>
-      <c r="O29" s="31"/>
-      <c r="P29" s="31"/>
-      <c r="Q29" s="31"/>
-      <c r="R29" s="31"/>
-      <c r="S29" s="31"/>
-      <c r="T29" s="31"/>
-      <c r="U29" s="31"/>
-      <c r="V29" s="31"/>
-      <c r="W29" s="31"/>
-      <c r="X29" s="31"/>
-      <c r="Y29" s="31"/>
-      <c r="Z29" s="31"/>
-      <c r="AA29" s="31"/>
-      <c r="AB29" s="31"/>
-      <c r="AC29" s="31"/>
-      <c r="AD29" s="31"/>
-      <c r="AE29" s="31"/>
-      <c r="AF29" s="31"/>
-      <c r="AG29" s="31"/>
-      <c r="AH29" s="31"/>
-      <c r="AI29" s="31"/>
+        <v>126</v>
+      </c>
+      <c r="H29" s="29"/>
+      <c r="I29" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="30"/>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="30"/>
+      <c r="AA29" s="30"/>
+      <c r="AB29" s="30"/>
+      <c r="AC29" s="30"/>
+      <c r="AD29" s="30"/>
+      <c r="AE29" s="30"/>
+      <c r="AF29" s="30"/>
+      <c r="AG29" s="30"/>
+      <c r="AH29" s="30"/>
+      <c r="AI29" s="30"/>
       <c r="AJ29" s="18"/>
-      <c r="AK29" s="31"/>
+      <c r="AK29" s="30"/>
       <c r="AL29" s="19"/>
       <c r="AM29" s="19"/>
-      <c r="AN29" s="33"/>
-      <c r="AO29" s="28"/>
+      <c r="AN29" s="32"/>
+      <c r="AO29" s="26" t="s">
+        <v>168</v>
+      </c>
       <c r="AP29" s="19"/>
       <c r="AQ29" s="18"/>
       <c r="AR29" s="17"/>
-      <c r="AS29" s="29"/>
+      <c r="AS29" s="28"/>
       <c r="AT29" s="17"/>
       <c r="AU29" s="17"/>
       <c r="AV29" s="17"/>
@@ -3796,72 +3989,78 @@
       <c r="BD29" s="17"/>
       <c r="BE29" s="18"/>
       <c r="BF29" s="18"/>
-      <c r="BG29" s="31"/>
-      <c r="BH29" s="31"/>
-      <c r="BI29" s="31"/>
-      <c r="BJ29" s="31"/>
-      <c r="BK29" s="31"/>
-    </row>
-    <row r="30" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="BG29" s="30"/>
+      <c r="BH29" s="30"/>
+      <c r="BI29" s="30"/>
+      <c r="BJ29" s="30"/>
+      <c r="BK29" s="30"/>
+    </row>
+    <row r="30" spans="1:66" ht="18" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C30" s="4">
         <v>12</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="H30" s="30"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="31"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="31"/>
-      <c r="M30" s="31"/>
-      <c r="N30" s="31"/>
-      <c r="O30" s="31"/>
-      <c r="P30" s="31"/>
-      <c r="Q30" s="31"/>
-      <c r="R30" s="31"/>
-      <c r="S30" s="31"/>
-      <c r="T30" s="31"/>
-      <c r="U30" s="31"/>
-      <c r="V30" s="31"/>
-      <c r="W30" s="31"/>
-      <c r="X30" s="31"/>
-      <c r="Y30" s="31"/>
-      <c r="Z30" s="31"/>
-      <c r="AA30" s="31"/>
-      <c r="AB30" s="31"/>
-      <c r="AC30" s="31"/>
-      <c r="AD30" s="31"/>
-      <c r="AE30" s="31"/>
-      <c r="AF30" s="31"/>
-      <c r="AG30" s="31"/>
-      <c r="AH30" s="31"/>
-      <c r="AI30" s="31"/>
+        <v>126</v>
+      </c>
+      <c r="H30" s="29"/>
+      <c r="I30" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="30"/>
+      <c r="P30" s="30"/>
+      <c r="Q30" s="30"/>
+      <c r="R30" s="30"/>
+      <c r="S30" s="30"/>
+      <c r="T30" s="30"/>
+      <c r="U30" s="30"/>
+      <c r="V30" s="30"/>
+      <c r="W30" s="30"/>
+      <c r="X30" s="30"/>
+      <c r="Y30" s="30"/>
+      <c r="Z30" s="30"/>
+      <c r="AA30" s="30"/>
+      <c r="AB30" s="30"/>
+      <c r="AC30" s="30"/>
+      <c r="AD30" s="30"/>
+      <c r="AE30" s="30"/>
+      <c r="AF30" s="30"/>
+      <c r="AG30" s="30"/>
+      <c r="AH30" s="30"/>
+      <c r="AI30" s="30"/>
       <c r="AJ30" s="18"/>
-      <c r="AK30" s="31"/>
+      <c r="AK30" s="30"/>
       <c r="AL30" s="19"/>
       <c r="AM30" s="19"/>
-      <c r="AN30" s="33"/>
-      <c r="AO30" s="28"/>
-      <c r="AP30" s="19"/>
+      <c r="AN30" s="32"/>
+      <c r="AO30" s="35" t="s">
+        <v>163</v>
+      </c>
+      <c r="AP30" s="34" t="s">
+        <v>164</v>
+      </c>
       <c r="AQ30" s="18"/>
       <c r="AR30" s="17"/>
-      <c r="AS30" s="29"/>
+      <c r="AS30" s="28"/>
       <c r="AT30" s="17"/>
       <c r="AU30" s="17"/>
       <c r="AV30" s="17"/>
@@ -3875,72 +4074,78 @@
       <c r="BD30" s="17"/>
       <c r="BE30" s="18"/>
       <c r="BF30" s="18"/>
-      <c r="BG30" s="31"/>
-      <c r="BH30" s="31"/>
-      <c r="BI30" s="31"/>
-      <c r="BJ30" s="31"/>
-      <c r="BK30" s="31"/>
-    </row>
-    <row r="31" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="BG30" s="30"/>
+      <c r="BH30" s="30"/>
+      <c r="BI30" s="30"/>
+      <c r="BJ30" s="30"/>
+      <c r="BK30" s="30"/>
+    </row>
+    <row r="31" spans="1:66" ht="18" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>28</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C31" s="4">
         <v>4</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="H31" s="30"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="31"/>
-      <c r="K31" s="31"/>
-      <c r="L31" s="31"/>
-      <c r="M31" s="31"/>
-      <c r="N31" s="31"/>
-      <c r="O31" s="31"/>
-      <c r="P31" s="31"/>
-      <c r="Q31" s="31"/>
-      <c r="R31" s="31"/>
-      <c r="S31" s="31"/>
-      <c r="T31" s="31"/>
-      <c r="U31" s="31"/>
-      <c r="V31" s="31"/>
-      <c r="W31" s="31"/>
-      <c r="X31" s="31"/>
-      <c r="Y31" s="31"/>
-      <c r="Z31" s="31"/>
-      <c r="AA31" s="31"/>
-      <c r="AB31" s="31"/>
-      <c r="AC31" s="31"/>
-      <c r="AD31" s="31"/>
-      <c r="AE31" s="31"/>
-      <c r="AF31" s="31"/>
-      <c r="AG31" s="31"/>
-      <c r="AH31" s="31"/>
-      <c r="AI31" s="31"/>
+        <v>126</v>
+      </c>
+      <c r="H31" s="29"/>
+      <c r="I31" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="30"/>
+      <c r="P31" s="30"/>
+      <c r="Q31" s="30"/>
+      <c r="R31" s="30"/>
+      <c r="S31" s="30"/>
+      <c r="T31" s="30"/>
+      <c r="U31" s="30"/>
+      <c r="V31" s="30"/>
+      <c r="W31" s="30"/>
+      <c r="X31" s="30"/>
+      <c r="Y31" s="30"/>
+      <c r="Z31" s="30"/>
+      <c r="AA31" s="30"/>
+      <c r="AB31" s="30"/>
+      <c r="AC31" s="30"/>
+      <c r="AD31" s="30"/>
+      <c r="AE31" s="30"/>
+      <c r="AF31" s="30"/>
+      <c r="AG31" s="30"/>
+      <c r="AH31" s="30"/>
+      <c r="AI31" s="30"/>
       <c r="AJ31" s="18"/>
-      <c r="AK31" s="31"/>
+      <c r="AK31" s="30"/>
       <c r="AL31" s="19"/>
       <c r="AM31" s="19"/>
-      <c r="AN31" s="33"/>
-      <c r="AO31" s="28"/>
-      <c r="AP31" s="19"/>
+      <c r="AN31" s="32"/>
+      <c r="AO31" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="AP31" s="19" t="s">
+        <v>143</v>
+      </c>
       <c r="AQ31" s="18"/>
       <c r="AR31" s="17"/>
-      <c r="AS31" s="29"/>
+      <c r="AS31" s="28"/>
       <c r="AT31" s="17"/>
       <c r="AU31" s="17"/>
       <c r="AV31" s="17"/>
@@ -3954,72 +4159,82 @@
       <c r="BD31" s="17"/>
       <c r="BE31" s="18"/>
       <c r="BF31" s="18"/>
-      <c r="BG31" s="31"/>
-      <c r="BH31" s="31"/>
-      <c r="BI31" s="31"/>
-      <c r="BJ31" s="31"/>
-      <c r="BK31" s="31"/>
-    </row>
-    <row r="32" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="BG31" s="30"/>
+      <c r="BH31" s="30"/>
+      <c r="BI31" s="30"/>
+      <c r="BJ31" s="30"/>
+      <c r="BK31" s="30"/>
+    </row>
+    <row r="32" spans="1:66" ht="18" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>29</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C32" s="4">
         <v>3</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="H32" s="30"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="31"/>
-      <c r="L32" s="31"/>
-      <c r="M32" s="31"/>
-      <c r="N32" s="31"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="31"/>
-      <c r="Q32" s="31"/>
-      <c r="R32" s="31"/>
-      <c r="S32" s="31"/>
-      <c r="T32" s="31"/>
-      <c r="U32" s="31"/>
-      <c r="V32" s="31"/>
-      <c r="W32" s="31"/>
-      <c r="X32" s="31"/>
-      <c r="Y32" s="31"/>
-      <c r="Z32" s="31"/>
-      <c r="AA32" s="31"/>
-      <c r="AB32" s="31"/>
-      <c r="AC32" s="31"/>
-      <c r="AD32" s="31"/>
-      <c r="AE32" s="31"/>
-      <c r="AF32" s="31"/>
-      <c r="AG32" s="31"/>
-      <c r="AH32" s="31"/>
-      <c r="AI32" s="31"/>
+        <v>126</v>
+      </c>
+      <c r="H32" s="29"/>
+      <c r="I32" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="30"/>
+      <c r="X32" s="30"/>
+      <c r="Y32" s="30"/>
+      <c r="Z32" s="30"/>
+      <c r="AA32" s="30"/>
+      <c r="AB32" s="30"/>
+      <c r="AC32" s="30"/>
+      <c r="AD32" s="30"/>
+      <c r="AE32" s="30"/>
+      <c r="AF32" s="30"/>
+      <c r="AG32" s="30"/>
+      <c r="AH32" s="30"/>
+      <c r="AI32" s="30"/>
       <c r="AJ32" s="18"/>
-      <c r="AK32" s="31"/>
+      <c r="AK32" s="30"/>
       <c r="AL32" s="19"/>
       <c r="AM32" s="19"/>
-      <c r="AN32" s="33"/>
-      <c r="AO32" s="28"/>
-      <c r="AP32" s="19"/>
+      <c r="AN32" s="32"/>
+      <c r="AO32" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="AP32" s="34" t="s">
+        <v>142</v>
+      </c>
       <c r="AQ32" s="18"/>
-      <c r="AR32" s="17"/>
-      <c r="AS32" s="29"/>
+      <c r="AR32" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="AS32" s="28" t="s">
+        <v>47</v>
+      </c>
       <c r="AT32" s="17"/>
       <c r="AU32" s="17"/>
       <c r="AV32" s="17"/>
@@ -4033,72 +4248,76 @@
       <c r="BD32" s="17"/>
       <c r="BE32" s="18"/>
       <c r="BF32" s="18"/>
-      <c r="BG32" s="31"/>
-      <c r="BH32" s="31"/>
-      <c r="BI32" s="31"/>
-      <c r="BJ32" s="31"/>
-      <c r="BK32" s="31"/>
-    </row>
-    <row r="33" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="BG32" s="30"/>
+      <c r="BH32" s="30"/>
+      <c r="BI32" s="30"/>
+      <c r="BJ32" s="30"/>
+      <c r="BK32" s="30"/>
+    </row>
+    <row r="33" spans="1:66" ht="18" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>30</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C33" s="4">
         <v>16</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="H33" s="30"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="31"/>
-      <c r="L33" s="31"/>
-      <c r="M33" s="31"/>
-      <c r="N33" s="31"/>
-      <c r="O33" s="31"/>
-      <c r="P33" s="31"/>
-      <c r="Q33" s="31"/>
-      <c r="R33" s="31"/>
-      <c r="S33" s="31"/>
-      <c r="T33" s="31"/>
-      <c r="U33" s="31"/>
-      <c r="V33" s="31"/>
-      <c r="W33" s="31"/>
-      <c r="X33" s="31"/>
-      <c r="Y33" s="31"/>
-      <c r="Z33" s="31"/>
-      <c r="AA33" s="31"/>
-      <c r="AB33" s="31"/>
-      <c r="AC33" s="31"/>
-      <c r="AD33" s="31"/>
-      <c r="AE33" s="31"/>
-      <c r="AF33" s="31"/>
-      <c r="AG33" s="31"/>
-      <c r="AH33" s="31"/>
-      <c r="AI33" s="31"/>
+        <v>127</v>
+      </c>
+      <c r="H33" s="29"/>
+      <c r="I33" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="30"/>
+      <c r="N33" s="30"/>
+      <c r="O33" s="30"/>
+      <c r="P33" s="30"/>
+      <c r="Q33" s="30"/>
+      <c r="R33" s="30"/>
+      <c r="S33" s="30"/>
+      <c r="T33" s="30"/>
+      <c r="U33" s="30"/>
+      <c r="V33" s="30"/>
+      <c r="W33" s="30"/>
+      <c r="X33" s="30"/>
+      <c r="Y33" s="30"/>
+      <c r="Z33" s="30"/>
+      <c r="AA33" s="30"/>
+      <c r="AB33" s="30"/>
+      <c r="AC33" s="30"/>
+      <c r="AD33" s="30"/>
+      <c r="AE33" s="30"/>
+      <c r="AF33" s="30"/>
+      <c r="AG33" s="30"/>
+      <c r="AH33" s="30"/>
+      <c r="AI33" s="30"/>
       <c r="AJ33" s="18"/>
-      <c r="AK33" s="31"/>
+      <c r="AK33" s="30"/>
       <c r="AL33" s="19"/>
       <c r="AM33" s="19"/>
-      <c r="AN33" s="33"/>
-      <c r="AO33" s="28"/>
+      <c r="AN33" s="32"/>
+      <c r="AO33" s="26" t="s">
+        <v>51</v>
+      </c>
       <c r="AP33" s="19"/>
       <c r="AQ33" s="18"/>
       <c r="AR33" s="17"/>
-      <c r="AS33" s="29"/>
+      <c r="AS33" s="28"/>
       <c r="AT33" s="17"/>
       <c r="AU33" s="17"/>
       <c r="AV33" s="17"/>
@@ -4112,72 +4331,78 @@
       <c r="BD33" s="17"/>
       <c r="BE33" s="18"/>
       <c r="BF33" s="18"/>
-      <c r="BG33" s="31"/>
-      <c r="BH33" s="31"/>
-      <c r="BI33" s="31"/>
-      <c r="BJ33" s="31"/>
-      <c r="BK33" s="31"/>
-    </row>
-    <row r="34" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="BG33" s="30"/>
+      <c r="BH33" s="30"/>
+      <c r="BI33" s="30"/>
+      <c r="BJ33" s="30"/>
+      <c r="BK33" s="30"/>
+    </row>
+    <row r="34" spans="1:66" ht="18" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>31</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C34" s="4">
         <v>8</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="H34" s="30"/>
-      <c r="I34" s="31"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="31"/>
-      <c r="L34" s="31"/>
-      <c r="M34" s="31"/>
-      <c r="N34" s="31"/>
-      <c r="O34" s="31"/>
-      <c r="P34" s="31"/>
-      <c r="Q34" s="31"/>
-      <c r="R34" s="31"/>
-      <c r="S34" s="31"/>
-      <c r="T34" s="31"/>
-      <c r="U34" s="31"/>
-      <c r="V34" s="31"/>
-      <c r="W34" s="31"/>
-      <c r="X34" s="31"/>
-      <c r="Y34" s="31"/>
-      <c r="Z34" s="31"/>
-      <c r="AA34" s="31"/>
-      <c r="AB34" s="31"/>
-      <c r="AC34" s="31"/>
-      <c r="AD34" s="31"/>
-      <c r="AE34" s="31"/>
-      <c r="AF34" s="31"/>
-      <c r="AG34" s="31"/>
-      <c r="AH34" s="31"/>
-      <c r="AI34" s="31"/>
+        <v>126</v>
+      </c>
+      <c r="H34" s="29"/>
+      <c r="I34" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="30"/>
+      <c r="N34" s="30"/>
+      <c r="O34" s="30"/>
+      <c r="P34" s="30"/>
+      <c r="Q34" s="30"/>
+      <c r="R34" s="30"/>
+      <c r="S34" s="30"/>
+      <c r="T34" s="30"/>
+      <c r="U34" s="30"/>
+      <c r="V34" s="30"/>
+      <c r="W34" s="30"/>
+      <c r="X34" s="30"/>
+      <c r="Y34" s="30"/>
+      <c r="Z34" s="30"/>
+      <c r="AA34" s="30"/>
+      <c r="AB34" s="30"/>
+      <c r="AC34" s="30"/>
+      <c r="AD34" s="30"/>
+      <c r="AE34" s="30"/>
+      <c r="AF34" s="30"/>
+      <c r="AG34" s="30"/>
+      <c r="AH34" s="30"/>
+      <c r="AI34" s="30"/>
       <c r="AJ34" s="18"/>
-      <c r="AK34" s="31"/>
+      <c r="AK34" s="30"/>
       <c r="AL34" s="19"/>
       <c r="AM34" s="19"/>
-      <c r="AN34" s="33"/>
-      <c r="AO34" s="28"/>
-      <c r="AP34" s="19"/>
+      <c r="AN34" s="32"/>
+      <c r="AO34" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="AP34" s="19" t="s">
+        <v>156</v>
+      </c>
       <c r="AQ34" s="18"/>
       <c r="AR34" s="17"/>
-      <c r="AS34" s="29"/>
+      <c r="AS34" s="28"/>
       <c r="AT34" s="17"/>
       <c r="AU34" s="17"/>
       <c r="AV34" s="17"/>
@@ -4191,72 +4416,78 @@
       <c r="BD34" s="17"/>
       <c r="BE34" s="18"/>
       <c r="BF34" s="18"/>
-      <c r="BG34" s="31"/>
-      <c r="BH34" s="31"/>
-      <c r="BI34" s="31"/>
-      <c r="BJ34" s="31"/>
-      <c r="BK34" s="31"/>
-    </row>
-    <row r="35" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="BG34" s="30"/>
+      <c r="BH34" s="30"/>
+      <c r="BI34" s="30"/>
+      <c r="BJ34" s="30"/>
+      <c r="BK34" s="30"/>
+    </row>
+    <row r="35" spans="1:66" ht="18" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>32</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C35" s="4">
         <v>10</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="H35" s="30"/>
-      <c r="I35" s="31"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="31"/>
-      <c r="L35" s="31"/>
-      <c r="M35" s="31"/>
-      <c r="N35" s="31"/>
-      <c r="O35" s="31"/>
-      <c r="P35" s="31"/>
-      <c r="Q35" s="31"/>
-      <c r="R35" s="31"/>
-      <c r="S35" s="31"/>
-      <c r="T35" s="31"/>
-      <c r="U35" s="31"/>
-      <c r="V35" s="31"/>
-      <c r="W35" s="31"/>
-      <c r="X35" s="31"/>
-      <c r="Y35" s="31"/>
-      <c r="Z35" s="31"/>
-      <c r="AA35" s="31"/>
-      <c r="AB35" s="31"/>
-      <c r="AC35" s="31"/>
-      <c r="AD35" s="31"/>
-      <c r="AE35" s="31"/>
-      <c r="AF35" s="31"/>
-      <c r="AG35" s="31"/>
-      <c r="AH35" s="31"/>
-      <c r="AI35" s="31"/>
+        <v>126</v>
+      </c>
+      <c r="H35" s="29"/>
+      <c r="I35" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
+      <c r="O35" s="30"/>
+      <c r="P35" s="30"/>
+      <c r="Q35" s="30"/>
+      <c r="R35" s="30"/>
+      <c r="S35" s="30"/>
+      <c r="T35" s="30"/>
+      <c r="U35" s="30"/>
+      <c r="V35" s="30"/>
+      <c r="W35" s="30"/>
+      <c r="X35" s="30"/>
+      <c r="Y35" s="30"/>
+      <c r="Z35" s="30"/>
+      <c r="AA35" s="30"/>
+      <c r="AB35" s="30"/>
+      <c r="AC35" s="30"/>
+      <c r="AD35" s="30"/>
+      <c r="AE35" s="30"/>
+      <c r="AF35" s="30"/>
+      <c r="AG35" s="30"/>
+      <c r="AH35" s="30"/>
+      <c r="AI35" s="30"/>
       <c r="AJ35" s="18"/>
-      <c r="AK35" s="31"/>
+      <c r="AK35" s="30"/>
       <c r="AL35" s="19"/>
       <c r="AM35" s="19"/>
-      <c r="AN35" s="33"/>
-      <c r="AO35" s="28"/>
-      <c r="AP35" s="19"/>
+      <c r="AN35" s="32"/>
+      <c r="AO35" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="AP35" s="34" t="s">
+        <v>160</v>
+      </c>
       <c r="AQ35" s="18"/>
       <c r="AR35" s="17"/>
-      <c r="AS35" s="29"/>
+      <c r="AS35" s="28"/>
       <c r="AT35" s="17"/>
       <c r="AU35" s="17"/>
       <c r="AV35" s="17"/>
@@ -4270,68 +4501,72 @@
       <c r="BD35" s="17"/>
       <c r="BE35" s="18"/>
       <c r="BF35" s="18"/>
-      <c r="BG35" s="31"/>
-      <c r="BH35" s="31"/>
-      <c r="BI35" s="31"/>
-      <c r="BJ35" s="31"/>
-      <c r="BK35" s="31"/>
-    </row>
-    <row r="36" spans="1:66" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="BG35" s="30"/>
+      <c r="BH35" s="30"/>
+      <c r="BI35" s="30"/>
+      <c r="BJ35" s="30"/>
+      <c r="BK35" s="30"/>
+    </row>
+    <row r="36" spans="1:66" ht="18" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>33</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C36" s="4">
         <v>14</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F36" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="H36" s="30"/>
-      <c r="I36" s="31"/>
-      <c r="J36" s="31"/>
-      <c r="K36" s="31"/>
-      <c r="L36" s="31"/>
-      <c r="M36" s="31"/>
-      <c r="N36" s="31"/>
-      <c r="O36" s="31"/>
+        <v>126</v>
+      </c>
+      <c r="H36" s="29"/>
+      <c r="I36" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="J36" s="30"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="30"/>
+      <c r="M36" s="30"/>
+      <c r="N36" s="30"/>
+      <c r="O36" s="30"/>
       <c r="P36" s="17"/>
-      <c r="Q36" s="31"/>
-      <c r="R36" s="31"/>
-      <c r="S36" s="31"/>
-      <c r="T36" s="31"/>
-      <c r="U36" s="31"/>
-      <c r="V36" s="31"/>
-      <c r="W36" s="31"/>
-      <c r="X36" s="31"/>
-      <c r="Y36" s="31"/>
-      <c r="Z36" s="31"/>
-      <c r="AA36" s="31"/>
-      <c r="AB36" s="31"/>
-      <c r="AC36" s="31"/>
-      <c r="AD36" s="31"/>
-      <c r="AE36" s="31"/>
-      <c r="AF36" s="31"/>
-      <c r="AG36" s="31"/>
-      <c r="AH36" s="31"/>
-      <c r="AI36" s="31"/>
-      <c r="AJ36" s="31"/>
-      <c r="AK36" s="31"/>
+      <c r="Q36" s="30"/>
+      <c r="R36" s="30"/>
+      <c r="S36" s="30"/>
+      <c r="T36" s="30"/>
+      <c r="U36" s="30"/>
+      <c r="V36" s="30"/>
+      <c r="W36" s="30"/>
+      <c r="X36" s="30"/>
+      <c r="Y36" s="30"/>
+      <c r="Z36" s="30"/>
+      <c r="AA36" s="30"/>
+      <c r="AB36" s="30"/>
+      <c r="AC36" s="30"/>
+      <c r="AD36" s="30"/>
+      <c r="AE36" s="30"/>
+      <c r="AF36" s="30"/>
+      <c r="AG36" s="30"/>
+      <c r="AH36" s="30"/>
+      <c r="AI36" s="30"/>
+      <c r="AJ36" s="30"/>
+      <c r="AK36" s="30"/>
       <c r="AL36" s="19"/>
       <c r="AM36" s="19"/>
       <c r="AN36" s="25"/>
-      <c r="AO36" s="20"/>
+      <c r="AO36" s="26" t="s">
+        <v>167</v>
+      </c>
       <c r="AP36" s="19"/>
       <c r="AQ36" s="17"/>
       <c r="AR36" s="17"/>
@@ -4341,136 +4576,150 @@
       <c r="AV36" s="17"/>
       <c r="AW36" s="17"/>
       <c r="AX36" s="17"/>
-      <c r="AY36" s="31"/>
-      <c r="AZ36" s="31"/>
-      <c r="BA36" s="31"/>
+      <c r="AY36" s="30"/>
+      <c r="AZ36" s="30"/>
+      <c r="BA36" s="30"/>
       <c r="BB36" s="17"/>
       <c r="BC36" s="17"/>
       <c r="BD36" s="17"/>
-      <c r="BE36" s="31"/>
-      <c r="BF36" s="31"/>
-      <c r="BG36" s="31"/>
-      <c r="BH36" s="31"/>
-      <c r="BI36" s="31"/>
-      <c r="BJ36" s="31"/>
-      <c r="BK36" s="31"/>
-    </row>
-    <row r="37" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A37" s="44" t="s">
-        <v>61</v>
-      </c>
-      <c r="B37" s="45"/>
-      <c r="C37" s="45"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="45"/>
-      <c r="H37" s="45"/>
-      <c r="I37" s="45"/>
-      <c r="J37" s="45"/>
-      <c r="K37" s="45"/>
-      <c r="L37" s="45"/>
-      <c r="M37" s="45"/>
-      <c r="N37" s="45"/>
-      <c r="O37" s="45"/>
-      <c r="P37" s="45"/>
-      <c r="Q37" s="45"/>
-      <c r="R37" s="45"/>
-      <c r="S37" s="45"/>
-      <c r="T37" s="45"/>
-      <c r="U37" s="45"/>
-      <c r="V37" s="45"/>
-      <c r="W37" s="45"/>
-      <c r="X37" s="45"/>
-      <c r="Y37" s="45"/>
-      <c r="Z37" s="45"/>
-      <c r="AA37" s="45"/>
-      <c r="AB37" s="45"/>
-      <c r="AC37" s="45"/>
-      <c r="AD37" s="45"/>
-      <c r="AE37" s="45"/>
-      <c r="AF37" s="45"/>
-      <c r="AG37" s="45"/>
-      <c r="AH37" s="45"/>
-      <c r="AI37" s="45"/>
-      <c r="AJ37" s="45"/>
-      <c r="AK37" s="45"/>
-      <c r="AL37" s="45"/>
-      <c r="AM37" s="45"/>
-      <c r="AN37" s="46"/>
-      <c r="AO37" s="2"/>
-      <c r="AP37" s="2"/>
-      <c r="AQ37" s="2"/>
-      <c r="AR37" s="2"/>
-      <c r="AS37" s="2"/>
-      <c r="AT37" s="2"/>
-      <c r="AU37" s="2"/>
-      <c r="AV37" s="2"/>
-      <c r="AW37" s="2"/>
-      <c r="AX37" s="2"/>
-      <c r="AY37" s="2"/>
-      <c r="AZ37" s="2"/>
-      <c r="BA37" s="2"/>
-      <c r="BB37" s="2"/>
-      <c r="BC37" s="2"/>
-      <c r="BD37" s="2"/>
-      <c r="BE37" s="2"/>
-      <c r="BF37" s="2"/>
-      <c r="BG37" s="2"/>
-      <c r="BH37" s="2"/>
-      <c r="BI37" s="2"/>
-      <c r="BJ37" s="2"/>
-      <c r="BK37" s="2"/>
-      <c r="BL37">
-        <v>24</v>
-      </c>
-      <c r="BN37" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A38" s="47" t="s">
-        <v>95</v>
-      </c>
-      <c r="B38" s="48"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="48"/>
-      <c r="H38" s="48"/>
-      <c r="I38" s="48"/>
-      <c r="J38" s="48"/>
-      <c r="K38" s="48"/>
-      <c r="L38" s="48"/>
-      <c r="M38" s="48"/>
-      <c r="N38" s="48"/>
-      <c r="O38" s="48"/>
-      <c r="P38" s="48"/>
-      <c r="Q38" s="48"/>
-      <c r="R38" s="48"/>
-      <c r="S38" s="48"/>
-      <c r="T38" s="48"/>
-      <c r="U38" s="48"/>
-      <c r="V38" s="48"/>
-      <c r="W38" s="48"/>
-      <c r="X38" s="48"/>
-      <c r="Y38" s="48"/>
-      <c r="Z38" s="48"/>
-      <c r="AA38" s="48"/>
-      <c r="AB38" s="48"/>
-      <c r="AC38" s="48"/>
-      <c r="AD38" s="48"/>
-      <c r="AE38" s="48"/>
-      <c r="AF38" s="48"/>
-      <c r="AG38" s="48"/>
-      <c r="AH38" s="48"/>
-      <c r="AI38" s="48"/>
-      <c r="AJ38" s="48"/>
-      <c r="AK38" s="48"/>
-      <c r="AL38" s="48"/>
-      <c r="AM38" s="48"/>
-      <c r="AN38" s="49"/>
+      <c r="BE36" s="30"/>
+      <c r="BF36" s="30"/>
+      <c r="BG36" s="30"/>
+      <c r="BH36" s="30"/>
+      <c r="BI36" s="30"/>
+      <c r="BJ36" s="30"/>
+      <c r="BK36" s="30"/>
+    </row>
+    <row r="37" spans="1:66" ht="18" x14ac:dyDescent="0.35">
+      <c r="A37" s="3">
+        <v>34</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C37" s="4">
+        <v>18</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="H37" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="I37" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="S37" s="30"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="30"/>
+      <c r="X37" s="30"/>
+      <c r="Y37" s="30"/>
+      <c r="Z37" s="30"/>
+      <c r="AA37" s="30"/>
+      <c r="AB37" s="30"/>
+      <c r="AC37" s="30"/>
+      <c r="AD37" s="30"/>
+      <c r="AE37" s="30"/>
+      <c r="AF37" s="30"/>
+      <c r="AG37" s="30"/>
+      <c r="AH37" s="30"/>
+      <c r="AI37" s="30"/>
+      <c r="AJ37" s="30"/>
+      <c r="AK37" s="30"/>
+      <c r="AL37" s="19"/>
+      <c r="AM37" s="19"/>
+      <c r="AN37" s="25"/>
+      <c r="AO37" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="AP37" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="AQ37" s="17"/>
+      <c r="AR37" s="17"/>
+      <c r="AS37" s="17"/>
+      <c r="AT37" s="17"/>
+      <c r="AU37" s="17"/>
+      <c r="AV37" s="17"/>
+      <c r="AW37" s="17"/>
+      <c r="AX37" s="17"/>
+      <c r="AY37" s="30"/>
+      <c r="AZ37" s="30"/>
+      <c r="BA37" s="30"/>
+      <c r="BB37" s="17"/>
+      <c r="BC37" s="17"/>
+      <c r="BD37" s="17"/>
+      <c r="BE37" s="30"/>
+      <c r="BF37" s="30"/>
+      <c r="BG37" s="30"/>
+      <c r="BH37" s="30"/>
+      <c r="BI37" s="30"/>
+      <c r="BJ37" s="30"/>
+      <c r="BK37" s="30"/>
+    </row>
+    <row r="38" spans="1:66" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A38" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" s="52"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="52"/>
+      <c r="L38" s="52"/>
+      <c r="M38" s="52"/>
+      <c r="N38" s="52"/>
+      <c r="O38" s="52"/>
+      <c r="P38" s="52"/>
+      <c r="Q38" s="52"/>
+      <c r="R38" s="52"/>
+      <c r="S38" s="52"/>
+      <c r="T38" s="52"/>
+      <c r="U38" s="52"/>
+      <c r="V38" s="52"/>
+      <c r="W38" s="52"/>
+      <c r="X38" s="52"/>
+      <c r="Y38" s="52"/>
+      <c r="Z38" s="52"/>
+      <c r="AA38" s="52"/>
+      <c r="AB38" s="52"/>
+      <c r="AC38" s="52"/>
+      <c r="AD38" s="52"/>
+      <c r="AE38" s="52"/>
+      <c r="AF38" s="52"/>
+      <c r="AG38" s="52"/>
+      <c r="AH38" s="52"/>
+      <c r="AI38" s="52"/>
+      <c r="AJ38" s="52"/>
+      <c r="AK38" s="52"/>
+      <c r="AL38" s="52"/>
+      <c r="AM38" s="52"/>
+      <c r="AN38" s="53"/>
       <c r="AO38" s="2"/>
       <c r="AP38" s="2"/>
       <c r="AQ38" s="2"/>
@@ -4495,478 +4744,552 @@
       <c r="BJ38" s="2"/>
       <c r="BK38" s="2"/>
       <c r="BL38">
+        <v>24</v>
+      </c>
+      <c r="BN38" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:66" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A39" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39" s="55"/>
+      <c r="C39" s="55"/>
+      <c r="D39" s="55"/>
+      <c r="E39" s="55"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="55"/>
+      <c r="J39" s="55"/>
+      <c r="K39" s="55"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="55"/>
+      <c r="N39" s="55"/>
+      <c r="O39" s="55"/>
+      <c r="P39" s="55"/>
+      <c r="Q39" s="55"/>
+      <c r="R39" s="55"/>
+      <c r="S39" s="55"/>
+      <c r="T39" s="55"/>
+      <c r="U39" s="55"/>
+      <c r="V39" s="55"/>
+      <c r="W39" s="55"/>
+      <c r="X39" s="55"/>
+      <c r="Y39" s="55"/>
+      <c r="Z39" s="55"/>
+      <c r="AA39" s="55"/>
+      <c r="AB39" s="55"/>
+      <c r="AC39" s="55"/>
+      <c r="AD39" s="55"/>
+      <c r="AE39" s="55"/>
+      <c r="AF39" s="55"/>
+      <c r="AG39" s="55"/>
+      <c r="AH39" s="55"/>
+      <c r="AI39" s="55"/>
+      <c r="AJ39" s="55"/>
+      <c r="AK39" s="55"/>
+      <c r="AL39" s="55"/>
+      <c r="AM39" s="55"/>
+      <c r="AN39" s="56"/>
+      <c r="AO39" s="2"/>
+      <c r="AP39" s="2"/>
+      <c r="AQ39" s="2"/>
+      <c r="AR39" s="2"/>
+      <c r="AS39" s="2"/>
+      <c r="AT39" s="2"/>
+      <c r="AU39" s="2"/>
+      <c r="AV39" s="2"/>
+      <c r="AW39" s="2"/>
+      <c r="AX39" s="2"/>
+      <c r="AY39" s="2"/>
+      <c r="AZ39" s="2"/>
+      <c r="BA39" s="2"/>
+      <c r="BB39" s="2"/>
+      <c r="BC39" s="2"/>
+      <c r="BD39" s="2"/>
+      <c r="BE39" s="2"/>
+      <c r="BF39" s="2"/>
+      <c r="BG39" s="2"/>
+      <c r="BH39" s="2"/>
+      <c r="BI39" s="2"/>
+      <c r="BJ39" s="2"/>
+      <c r="BK39" s="2"/>
+      <c r="BL39">
         <v>25</v>
       </c>
-      <c r="BN38" t="s">
+      <c r="BN39" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:66" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
+      </c>
+      <c r="F40">
+        <v>3</v>
+      </c>
+      <c r="G40">
+        <v>4</v>
+      </c>
+      <c r="H40">
+        <v>5</v>
+      </c>
+      <c r="I40">
+        <v>6</v>
+      </c>
+      <c r="J40">
+        <v>7</v>
+      </c>
+      <c r="K40">
+        <v>8</v>
+      </c>
+      <c r="L40">
+        <v>9</v>
+      </c>
+      <c r="M40">
+        <v>10</v>
+      </c>
+      <c r="N40">
+        <v>11</v>
+      </c>
+      <c r="O40">
+        <v>12</v>
+      </c>
+      <c r="P40">
+        <v>13</v>
+      </c>
+      <c r="Q40">
+        <v>14</v>
+      </c>
+      <c r="R40">
+        <v>15</v>
+      </c>
+      <c r="S40">
+        <v>16</v>
+      </c>
+      <c r="T40">
+        <v>17</v>
+      </c>
+      <c r="U40">
+        <v>18</v>
+      </c>
+      <c r="V40">
+        <v>19</v>
+      </c>
+      <c r="W40">
+        <v>20</v>
+      </c>
+      <c r="X40">
+        <v>21</v>
+      </c>
+      <c r="Y40">
+        <v>22</v>
+      </c>
+      <c r="Z40">
+        <v>23</v>
+      </c>
+      <c r="AA40">
+        <v>24</v>
+      </c>
+      <c r="AB40">
+        <v>25</v>
+      </c>
+      <c r="AC40">
+        <v>26</v>
+      </c>
+      <c r="AD40">
+        <v>27</v>
+      </c>
+      <c r="AE40">
+        <v>28</v>
+      </c>
+      <c r="AF40">
+        <v>29</v>
+      </c>
+      <c r="AG40">
         <v>30</v>
       </c>
-    </row>
-    <row r="39" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="E39">
-        <v>2</v>
-      </c>
-      <c r="F39">
-        <v>3</v>
-      </c>
-      <c r="G39">
-        <v>4</v>
-      </c>
-      <c r="H39">
-        <v>5</v>
-      </c>
-      <c r="I39">
-        <v>6</v>
-      </c>
-      <c r="J39">
-        <v>7</v>
-      </c>
-      <c r="K39">
-        <v>8</v>
-      </c>
-      <c r="L39">
-        <v>9</v>
-      </c>
-      <c r="M39">
-        <v>10</v>
-      </c>
-      <c r="N39">
-        <v>11</v>
-      </c>
-      <c r="O39">
-        <v>12</v>
-      </c>
-      <c r="P39">
-        <v>13</v>
-      </c>
-      <c r="Q39">
-        <v>14</v>
-      </c>
-      <c r="R39">
-        <v>15</v>
-      </c>
-      <c r="S39">
-        <v>16</v>
-      </c>
-      <c r="T39">
-        <v>17</v>
-      </c>
-      <c r="U39">
-        <v>18</v>
-      </c>
-      <c r="V39">
-        <v>19</v>
-      </c>
-      <c r="W39">
-        <v>20</v>
-      </c>
-      <c r="X39">
-        <v>21</v>
-      </c>
-      <c r="Y39">
+      <c r="AH40">
+        <v>31</v>
+      </c>
+      <c r="AI40">
+        <v>32</v>
+      </c>
+      <c r="BL40">
+        <v>26</v>
+      </c>
+      <c r="BN40" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D41" t="s">
+        <v>131</v>
+      </c>
+      <c r="E41" t="s">
+        <v>132</v>
+      </c>
+      <c r="F41" t="s">
+        <v>131</v>
+      </c>
+      <c r="G41" t="s">
+        <v>132</v>
+      </c>
+      <c r="H41" t="s">
+        <v>131</v>
+      </c>
+      <c r="I41" t="s">
+        <v>132</v>
+      </c>
+      <c r="J41" t="s">
+        <v>131</v>
+      </c>
+      <c r="K41" t="s">
+        <v>132</v>
+      </c>
+      <c r="L41" t="s">
+        <v>131</v>
+      </c>
+      <c r="M41" t="s">
+        <v>132</v>
+      </c>
+      <c r="N41" t="s">
+        <v>131</v>
+      </c>
+      <c r="O41" t="s">
+        <v>132</v>
+      </c>
+      <c r="P41" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>132</v>
+      </c>
+      <c r="R41" t="s">
+        <v>131</v>
+      </c>
+      <c r="S41" t="s">
+        <v>132</v>
+      </c>
+      <c r="AV41"/>
+      <c r="BL41">
+        <v>27</v>
+      </c>
+      <c r="BN41" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="42" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D42" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="I42" t="s">
+        <v>152</v>
+      </c>
+      <c r="K42" t="s">
+        <v>67</v>
+      </c>
+      <c r="M42" t="s">
+        <v>68</v>
+      </c>
+      <c r="N42" t="s">
+        <v>68</v>
+      </c>
+      <c r="O42" t="s">
+        <v>69</v>
+      </c>
+      <c r="AX42" t="s">
+        <v>72</v>
+      </c>
+      <c r="BL42">
+        <v>28</v>
+      </c>
+      <c r="BN42" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E43" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="H43" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="J43" t="s">
+        <v>73</v>
+      </c>
+      <c r="L43" t="s">
+        <v>74</v>
+      </c>
+      <c r="P43" t="s">
+        <v>75</v>
+      </c>
+      <c r="AX43" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL43" s="14">
+        <v>29</v>
+      </c>
+      <c r="BM43" s="14"/>
+      <c r="BN43" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D44" t="s">
+        <v>77</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="L44" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL44" t="s">
+        <v>62</v>
+      </c>
+      <c r="AM44" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="BL44">
+        <v>30</v>
+      </c>
+      <c r="BN44" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D45" t="s">
+        <v>80</v>
+      </c>
+      <c r="R45" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL45" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM45" t="s">
+        <v>65</v>
+      </c>
+      <c r="BL45">
+        <v>31</v>
+      </c>
+      <c r="BN45" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="46" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D46" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL46" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM46" t="s">
+        <v>71</v>
+      </c>
+      <c r="BL46" s="14">
+        <v>32</v>
+      </c>
+      <c r="BM46" s="14"/>
+      <c r="BN46" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="47" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BL47">
+        <v>33</v>
+      </c>
+      <c r="BN47" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BL48">
+        <v>34</v>
+      </c>
+      <c r="BN48" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="49" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BL49">
+        <v>35</v>
+      </c>
+      <c r="BN49" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BL50" s="37">
+        <v>36</v>
+      </c>
+      <c r="BM50" s="37"/>
+      <c r="BN50" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="Z39">
-        <v>23</v>
-      </c>
-      <c r="AA39">
-        <v>24</v>
-      </c>
-      <c r="AB39">
-        <v>25</v>
-      </c>
-      <c r="AC39">
-        <v>26</v>
-      </c>
-      <c r="AD39">
-        <v>27</v>
-      </c>
-      <c r="AE39">
-        <v>28</v>
-      </c>
-      <c r="AF39">
-        <v>29</v>
-      </c>
-      <c r="AG39">
-        <v>30</v>
-      </c>
-      <c r="AH39">
-        <v>31</v>
-      </c>
-      <c r="AI39">
-        <v>32</v>
-      </c>
-      <c r="BL39">
-        <v>26</v>
-      </c>
-      <c r="BN39" t="s">
+    </row>
+    <row r="51" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BN51" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="53" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="BN53" s="8"/>
+      <c r="BO53" s="9"/>
+      <c r="BP53" s="8"/>
+    </row>
+    <row r="54" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="BL54">
+        <v>37</v>
+      </c>
+      <c r="BN54" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="BO54" s="10"/>
+      <c r="BP54" s="10"/>
+    </row>
+    <row r="55" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="BL55">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" t="s">
-        <v>134</v>
-      </c>
-      <c r="E40" t="s">
-        <v>135</v>
-      </c>
-      <c r="F40" t="s">
-        <v>134</v>
-      </c>
-      <c r="G40" t="s">
-        <v>135</v>
-      </c>
-      <c r="H40" t="s">
-        <v>134</v>
-      </c>
-      <c r="I40" t="s">
-        <v>135</v>
-      </c>
-      <c r="J40" t="s">
-        <v>134</v>
-      </c>
-      <c r="K40" t="s">
-        <v>135</v>
-      </c>
-      <c r="L40" t="s">
-        <v>134</v>
-      </c>
-      <c r="M40" t="s">
-        <v>135</v>
-      </c>
-      <c r="N40" t="s">
-        <v>134</v>
-      </c>
-      <c r="O40" t="s">
-        <v>135</v>
-      </c>
-      <c r="P40" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>135</v>
-      </c>
-      <c r="R40" t="s">
-        <v>134</v>
-      </c>
-      <c r="S40" t="s">
-        <v>135</v>
-      </c>
-      <c r="AV40"/>
-      <c r="BL40">
-        <v>27</v>
-      </c>
-      <c r="BN40" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="41" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="I41" t="s">
-        <v>68</v>
-      </c>
-      <c r="K41" t="s">
-        <v>69</v>
-      </c>
-      <c r="M41" t="s">
-        <v>70</v>
-      </c>
-      <c r="N41" t="s">
-        <v>70</v>
-      </c>
-      <c r="O41" t="s">
-        <v>71</v>
-      </c>
-      <c r="AX41" t="s">
-        <v>74</v>
-      </c>
-      <c r="BL41">
-        <v>28</v>
-      </c>
-      <c r="BN41" t="s">
+      <c r="BN55" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="BO55" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="BP55" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="BQ55">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E42" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="G42" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="H42" t="s">
-        <v>75</v>
-      </c>
-      <c r="J42" t="s">
-        <v>75</v>
-      </c>
-      <c r="L42" t="s">
-        <v>76</v>
-      </c>
-      <c r="P42" t="s">
-        <v>77</v>
-      </c>
-      <c r="AX42" t="s">
-        <v>78</v>
-      </c>
-      <c r="BL42" s="14">
-        <v>29</v>
-      </c>
-      <c r="BM42" s="14"/>
-      <c r="BN42" s="14" t="s">
+    <row r="56" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="BN56" s="10"/>
+      <c r="BO56" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="BP56" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="BQ56">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="BL57">
+        <v>39</v>
+      </c>
+      <c r="BN57" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="BO57" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="BP57" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="BQ57">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="58" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="BL58">
         <v>40</v>
       </c>
-    </row>
-    <row r="43" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D43" t="s">
-        <v>79</v>
-      </c>
-      <c r="F43" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="L43" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL43" t="s">
-        <v>63</v>
-      </c>
-      <c r="AM43" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="BL43">
-        <v>30</v>
-      </c>
-      <c r="BN43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D44" t="s">
-        <v>82</v>
-      </c>
-      <c r="R44" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL44" t="s">
-        <v>65</v>
-      </c>
-      <c r="AM44" t="s">
-        <v>66</v>
-      </c>
-      <c r="BL44">
-        <v>31</v>
-      </c>
-      <c r="BN44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="45" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D45" t="s">
-        <v>85</v>
-      </c>
-      <c r="AL45" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM45" t="s">
-        <v>73</v>
-      </c>
-      <c r="BL45" s="14">
-        <v>32</v>
-      </c>
-      <c r="BM45" s="14"/>
-      <c r="BN45" s="14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="46" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BL46">
-        <v>33</v>
-      </c>
-      <c r="BN46" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="47" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BL47">
-        <v>34</v>
-      </c>
-      <c r="BN47" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BL48">
-        <v>35</v>
-      </c>
-      <c r="BN48" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="49" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BL49">
-        <v>36</v>
-      </c>
-      <c r="BN49" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="50" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN50" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="52" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BN52" s="8"/>
-      <c r="BO52" s="9"/>
-      <c r="BP52" s="8"/>
-    </row>
-    <row r="53" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BL53">
-        <v>37</v>
-      </c>
-      <c r="BN53" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="BO53" s="10"/>
-      <c r="BP53" s="10"/>
-    </row>
-    <row r="54" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BL54">
-        <v>38</v>
-      </c>
-      <c r="BN54" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="BO54" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="BP54" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="BQ54">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="55" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BN55" s="10"/>
-      <c r="BO55" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="BP55" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="BQ55">
+      <c r="BN58" s="11" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="56" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BL56">
-        <v>39</v>
-      </c>
-      <c r="BN56" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="BO56" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="BP56" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="BQ56">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="57" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BL57">
-        <v>40</v>
-      </c>
-      <c r="BN57" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="BO57" s="10"/>
-      <c r="BP57" s="10"/>
-    </row>
-    <row r="58" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BL58" s="16">
-        <v>41</v>
-      </c>
-      <c r="BN58" s="8" t="s">
-        <v>25</v>
       </c>
       <c r="BO58" s="10"/>
       <c r="BP58" s="10"/>
     </row>
-    <row r="59" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BL59">
-        <v>42</v>
+    <row r="59" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="BL59" s="16">
+        <v>41</v>
       </c>
       <c r="BN59" s="8" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="BO59" s="10"/>
       <c r="BP59" s="10"/>
     </row>
-    <row r="60" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="BL60">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="BN60" s="8" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="BO60" s="10"/>
       <c r="BP60" s="10"/>
     </row>
-    <row r="61" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="BL61">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="BN61" s="8" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="BO61" s="10"/>
       <c r="BP61" s="10"/>
     </row>
-    <row r="62" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="BL62">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="BN62" s="8" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="BO62" s="10"/>
       <c r="BP62" s="10"/>
     </row>
-    <row r="63" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BL63" s="16">
-        <v>46</v>
+    <row r="63" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="BL63">
+        <v>45</v>
       </c>
       <c r="BN63" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BO63" s="10"/>
       <c r="BP63" s="10"/>
     </row>
-    <row r="64" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BL64">
+    <row r="64" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="BL64" s="16">
+        <v>46</v>
+      </c>
+      <c r="BN64" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="BO64" s="10"/>
+      <c r="BP64" s="10"/>
+    </row>
+    <row r="65" spans="64:66" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BL65">
         <v>47</v>
       </c>
-      <c r="BN64" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="65" spans="64:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BL65">
+      <c r="BN65" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="66" spans="64:66" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BL66">
         <v>48</v>
       </c>
-      <c r="BN65" t="s">
-        <v>94</v>
+      <c r="BN66" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -4988,8 +5311,8 @@
     <mergeCell ref="Y2:Y3"/>
     <mergeCell ref="T2:T3"/>
     <mergeCell ref="BI2:BK3"/>
-    <mergeCell ref="A37:AN37"/>
     <mergeCell ref="A38:AN38"/>
+    <mergeCell ref="A39:AN39"/>
     <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="S2:S3"/>
     <mergeCell ref="AJ2:AJ3"/>
@@ -5022,7 +5345,7 @@
   <hyperlinks>
     <hyperlink ref="BN6" r:id="rId1" display="Прикладная дискретная математика. Приложение. 2016. № 9. С. 68-70." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="BM26" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="BN47" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="BN48" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId4"/>

--- a/Ведомость ТКИ-441 2026-2027.xlsx
+++ b/Ведомость ТКИ-441 2026-2027.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chxrnvkha\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\StegMethods\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE660568-346F-4A74-9467-CE41F317214B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8C3F93-103A-4ED0-A172-42296236476F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1515" yWindow="1155" windowWidth="14310" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="185">
   <si>
     <t>Ведомость посещаемости занятий студентами группы ТКИ РУТ МИИТ</t>
   </si>
@@ -575,6 +575,12 @@
   </si>
   <si>
     <t xml:space="preserve"> Стеганография с использованием исполняемых файлов</t>
+  </si>
+  <si>
+    <t>ДПФ и БПФ</t>
+  </si>
+  <si>
+    <t>ДПФ</t>
   </si>
 </sst>
 </file>
@@ -913,16 +919,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -931,13 +931,12 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -956,15 +955,103 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -981,13 +1068,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>37</xdr:col>
+      <xdr:col>39</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>166255</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>42</xdr:col>
+      <xdr:col>44</xdr:col>
       <xdr:colOff>638175</xdr:colOff>
       <xdr:row>63</xdr:row>
       <xdr:rowOff>78427</xdr:rowOff>
@@ -1289,297 +1376,311 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BQ66"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:BS66"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="35.5546875" customWidth="1"/>
+    <col min="2" max="2" width="35.5703125" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="19" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="20" max="35" width="10.88671875" customWidth="1"/>
-    <col min="36" max="36" width="11.5546875" customWidth="1"/>
-    <col min="39" max="39" width="12.33203125" customWidth="1"/>
-    <col min="40" max="40" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="15.6640625" customWidth="1"/>
-    <col min="42" max="42" width="11.88671875" customWidth="1"/>
-    <col min="43" max="43" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="9.109375" style="12"/>
-    <col min="49" max="49" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="11.5546875" customWidth="1"/>
-    <col min="66" max="66" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" customWidth="1"/>
+    <col min="7" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="21" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="37" width="10.85546875" customWidth="1"/>
+    <col min="38" max="38" width="11.5703125" customWidth="1"/>
+    <col min="41" max="41" width="12.28515625" customWidth="1"/>
+    <col min="42" max="42" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="15.7109375" customWidth="1"/>
+    <col min="44" max="44" width="11.85546875" customWidth="1"/>
+    <col min="45" max="45" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="9.140625" style="12"/>
+    <col min="51" max="51" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="11.5703125" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="34.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
-      <c r="W1" s="44"/>
-      <c r="X1" s="44"/>
-      <c r="Y1" s="44"/>
-      <c r="Z1" s="44"/>
-      <c r="AA1" s="44"/>
-      <c r="AB1" s="44"/>
-      <c r="AC1" s="44"/>
-      <c r="AD1" s="44"/>
-      <c r="AE1" s="44"/>
-      <c r="AF1" s="44"/>
-      <c r="AG1" s="44"/>
-      <c r="AH1" s="44"/>
-      <c r="AI1" s="44"/>
-      <c r="AJ1" s="44"/>
-      <c r="AK1" s="44"/>
-      <c r="AL1" s="44"/>
-      <c r="AM1" s="44"/>
-      <c r="AN1" s="44"/>
-    </row>
-    <row r="2" spans="1:68" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="56"/>
+      <c r="Z1" s="56"/>
+      <c r="AA1" s="56"/>
+      <c r="AB1" s="56"/>
+      <c r="AC1" s="56"/>
+      <c r="AD1" s="56"/>
+      <c r="AE1" s="56"/>
+      <c r="AF1" s="56"/>
+      <c r="AG1" s="56"/>
+      <c r="AH1" s="56"/>
+      <c r="AI1" s="56"/>
+      <c r="AJ1" s="56"/>
+      <c r="AK1" s="56"/>
+      <c r="AL1" s="56"/>
+      <c r="AM1" s="56"/>
+      <c r="AN1" s="56"/>
+      <c r="AO1" s="56"/>
+      <c r="AP1" s="56"/>
+    </row>
+    <row r="2" spans="1:70" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="57" t="s">
+      <c r="B2" s="54"/>
+      <c r="C2" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="46">
+      <c r="D2" s="40">
         <v>46268</v>
       </c>
-      <c r="E2" s="46">
+      <c r="E2" s="40">
         <v>46272</v>
       </c>
-      <c r="F2" s="46">
+      <c r="F2" s="40">
+        <v>46273</v>
+      </c>
+      <c r="G2" s="40">
         <v>46275</v>
       </c>
-      <c r="G2" s="46">
+      <c r="H2" s="40">
         <v>46279</v>
       </c>
-      <c r="H2" s="48">
+      <c r="I2" s="38">
         <v>46282</v>
       </c>
-      <c r="I2" s="46">
+      <c r="J2" s="40">
         <v>46286</v>
       </c>
-      <c r="J2" s="48">
+      <c r="K2" s="40">
+        <v>46287</v>
+      </c>
+      <c r="L2" s="38">
         <v>46289</v>
       </c>
-      <c r="K2" s="46">
+      <c r="M2" s="40">
         <v>46293</v>
       </c>
-      <c r="L2" s="48">
+      <c r="N2" s="38">
         <v>46296</v>
       </c>
-      <c r="M2" s="46">
+      <c r="O2" s="40">
         <v>46300</v>
       </c>
-      <c r="N2" s="48">
+      <c r="P2" s="38">
         <v>46303</v>
       </c>
-      <c r="O2" s="46">
+      <c r="Q2" s="40">
         <v>46307</v>
       </c>
-      <c r="P2" s="48">
+      <c r="R2" s="38">
         <v>46310</v>
       </c>
-      <c r="Q2" s="46">
+      <c r="S2" s="40">
         <v>46314</v>
       </c>
-      <c r="R2" s="48">
+      <c r="T2" s="38">
         <v>46317</v>
       </c>
-      <c r="S2" s="46">
+      <c r="U2" s="40">
         <v>46321</v>
       </c>
-      <c r="T2" s="46">
+      <c r="V2" s="40">
         <v>46324</v>
       </c>
-      <c r="U2" s="46">
+      <c r="W2" s="40">
         <v>46328</v>
       </c>
-      <c r="V2" s="46">
+      <c r="X2" s="40">
         <v>46331</v>
       </c>
-      <c r="W2" s="46">
+      <c r="Y2" s="40">
         <v>46335</v>
       </c>
-      <c r="X2" s="46">
+      <c r="Z2" s="40">
         <v>46338</v>
       </c>
-      <c r="Y2" s="46">
+      <c r="AA2" s="40">
         <v>46342</v>
       </c>
-      <c r="Z2" s="46">
+      <c r="AB2" s="40">
         <v>46345</v>
       </c>
-      <c r="AA2" s="46">
+      <c r="AC2" s="40">
         <v>46349</v>
       </c>
-      <c r="AB2" s="46">
+      <c r="AD2" s="40">
         <v>46352</v>
       </c>
-      <c r="AC2" s="46">
+      <c r="AE2" s="40">
         <v>46356</v>
       </c>
-      <c r="AD2" s="48">
+      <c r="AF2" s="38">
         <v>46359</v>
       </c>
-      <c r="AE2" s="48">
+      <c r="AG2" s="38">
         <v>46363</v>
       </c>
-      <c r="AF2" s="48">
+      <c r="AH2" s="38">
         <v>46366</v>
       </c>
-      <c r="AG2" s="48">
+      <c r="AI2" s="38">
         <v>46370</v>
       </c>
-      <c r="AH2" s="48">
+      <c r="AJ2" s="38">
         <v>46373</v>
       </c>
-      <c r="AI2" s="48">
+      <c r="AK2" s="38">
         <v>46377</v>
       </c>
-      <c r="AJ2" s="45" t="s">
+      <c r="AL2" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="AK2" s="45"/>
-      <c r="AL2" s="38" t="s">
+      <c r="AM2" s="54"/>
+      <c r="AN2" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="AM2" s="39"/>
-      <c r="AN2" s="40"/>
-      <c r="AO2" s="38" t="s">
+      <c r="AO2" s="43"/>
+      <c r="AP2" s="44"/>
+      <c r="AQ2" s="42" t="s">
         <v>169</v>
       </c>
-      <c r="AP2" s="39"/>
-      <c r="AQ2" s="40"/>
-      <c r="AR2" s="38" t="s">
+      <c r="AR2" s="43"/>
+      <c r="AS2" s="44"/>
+      <c r="AT2" s="42" t="s">
         <v>170</v>
       </c>
-      <c r="AS2" s="39"/>
-      <c r="AT2" s="40"/>
-      <c r="AU2" s="38" t="s">
+      <c r="AU2" s="43"/>
+      <c r="AV2" s="44"/>
+      <c r="AW2" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="AV2" s="39"/>
-      <c r="AW2" s="40"/>
-      <c r="AX2" s="38" t="s">
+      <c r="AX2" s="43"/>
+      <c r="AY2" s="44"/>
+      <c r="AZ2" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="AY2" s="39"/>
-      <c r="AZ2" s="39"/>
-      <c r="BA2" s="40"/>
-      <c r="BB2" s="38" t="s">
+      <c r="BA2" s="43"/>
+      <c r="BB2" s="43"/>
+      <c r="BC2" s="44"/>
+      <c r="BD2" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="BC2" s="39"/>
-      <c r="BD2" s="39"/>
-      <c r="BE2" s="40" t="s">
+      <c r="BE2" s="43"/>
+      <c r="BF2" s="43"/>
+      <c r="BG2" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="BF2" s="38" t="s">
+      <c r="BH2" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="BG2" s="39"/>
-      <c r="BH2" s="40"/>
-      <c r="BI2" s="38" t="s">
+      <c r="BI2" s="43"/>
+      <c r="BJ2" s="44"/>
+      <c r="BK2" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="BJ2" s="39"/>
-      <c r="BK2" s="40"/>
-    </row>
-    <row r="3" spans="1:68" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BL2" s="43"/>
+      <c r="BM2" s="44"/>
+    </row>
+    <row r="3" spans="1:70" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="47"/>
-      <c r="N3" s="49"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="49"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="49"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="W3" s="47"/>
-      <c r="X3" s="47"/>
-      <c r="Y3" s="47"/>
-      <c r="Z3" s="47"/>
-      <c r="AA3" s="47"/>
-      <c r="AB3" s="47"/>
-      <c r="AC3" s="47"/>
-      <c r="AD3" s="49"/>
-      <c r="AE3" s="49"/>
-      <c r="AF3" s="49"/>
-      <c r="AG3" s="49"/>
-      <c r="AH3" s="49"/>
-      <c r="AI3" s="49"/>
-      <c r="AJ3" s="45"/>
-      <c r="AK3" s="45"/>
-      <c r="AL3" s="41"/>
-      <c r="AM3" s="50"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="41"/>
-      <c r="AP3" s="42"/>
-      <c r="AQ3" s="43"/>
-      <c r="AR3" s="41"/>
-      <c r="AS3" s="42"/>
-      <c r="AT3" s="43"/>
-      <c r="AU3" s="41"/>
-      <c r="AV3" s="42"/>
-      <c r="AW3" s="43"/>
-      <c r="AX3" s="41"/>
-      <c r="AY3" s="42"/>
-      <c r="AZ3" s="42"/>
-      <c r="BA3" s="43"/>
-      <c r="BB3" s="41"/>
-      <c r="BC3" s="42"/>
-      <c r="BD3" s="42"/>
-      <c r="BE3" s="43"/>
-      <c r="BF3" s="41"/>
-      <c r="BG3" s="42"/>
-      <c r="BH3" s="43"/>
-      <c r="BI3" s="41"/>
-      <c r="BJ3" s="42"/>
-      <c r="BK3" s="43"/>
-    </row>
-    <row r="4" spans="1:68" ht="18" x14ac:dyDescent="0.35">
+      <c r="C3" s="54"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="41"/>
+      <c r="V3" s="41"/>
+      <c r="W3" s="41"/>
+      <c r="X3" s="41"/>
+      <c r="Y3" s="41"/>
+      <c r="Z3" s="41"/>
+      <c r="AA3" s="41"/>
+      <c r="AB3" s="41"/>
+      <c r="AC3" s="41"/>
+      <c r="AD3" s="41"/>
+      <c r="AE3" s="41"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="39"/>
+      <c r="AH3" s="39"/>
+      <c r="AI3" s="39"/>
+      <c r="AJ3" s="39"/>
+      <c r="AK3" s="39"/>
+      <c r="AL3" s="54"/>
+      <c r="AM3" s="54"/>
+      <c r="AN3" s="45"/>
+      <c r="AO3" s="57"/>
+      <c r="AP3" s="47"/>
+      <c r="AQ3" s="45"/>
+      <c r="AR3" s="46"/>
+      <c r="AS3" s="47"/>
+      <c r="AT3" s="45"/>
+      <c r="AU3" s="46"/>
+      <c r="AV3" s="47"/>
+      <c r="AW3" s="45"/>
+      <c r="AX3" s="46"/>
+      <c r="AY3" s="47"/>
+      <c r="AZ3" s="45"/>
+      <c r="BA3" s="46"/>
+      <c r="BB3" s="46"/>
+      <c r="BC3" s="47"/>
+      <c r="BD3" s="45"/>
+      <c r="BE3" s="46"/>
+      <c r="BF3" s="46"/>
+      <c r="BG3" s="47"/>
+      <c r="BH3" s="45"/>
+      <c r="BI3" s="46"/>
+      <c r="BJ3" s="47"/>
+      <c r="BK3" s="45"/>
+      <c r="BL3" s="46"/>
+      <c r="BM3" s="47"/>
+    </row>
+    <row r="4" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -1595,19 +1696,21 @@
       <c r="E4" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F4" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F4" s="17"/>
       <c r="G4" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="J4" s="17"/>
+      <c r="H4" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
+      <c r="L4" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M4" s="17"/>
       <c r="N4" s="17"/>
       <c r="O4" s="17"/>
@@ -1631,48 +1734,50 @@
       <c r="AG4" s="17"/>
       <c r="AH4" s="17"/>
       <c r="AI4" s="17"/>
-      <c r="AJ4" s="18"/>
+      <c r="AJ4" s="17"/>
       <c r="AK4" s="17"/>
-      <c r="AL4" s="19"/>
-      <c r="AM4" s="19"/>
-      <c r="AN4" s="18"/>
-      <c r="AO4" s="33" t="s">
+      <c r="AL4" s="18"/>
+      <c r="AM4" s="17"/>
+      <c r="AN4" s="19"/>
+      <c r="AO4" s="19"/>
+      <c r="AP4" s="18"/>
+      <c r="AQ4" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="AP4" s="34" t="s">
+      <c r="AR4" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="AQ4" s="21"/>
-      <c r="AR4" s="21" t="s">
+      <c r="AS4" s="21"/>
+      <c r="AT4" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="AS4" s="21" t="s">
+      <c r="AU4" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="AT4" s="18"/>
-      <c r="AU4" s="34" t="s">
+      <c r="AV4" s="18"/>
+      <c r="AW4" s="34" t="s">
         <v>178</v>
       </c>
-      <c r="AV4" s="34" t="s">
+      <c r="AX4" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="AW4" s="34"/>
-      <c r="AX4" s="17"/>
-      <c r="AY4" s="17"/>
+      <c r="AY4" s="34"/>
       <c r="AZ4" s="17"/>
-      <c r="BA4" s="18"/>
+      <c r="BA4" s="17"/>
       <c r="BB4" s="17"/>
-      <c r="BC4" s="17"/>
+      <c r="BC4" s="18"/>
       <c r="BD4" s="17"/>
-      <c r="BE4" s="18"/>
-      <c r="BF4" s="18"/>
-      <c r="BG4" s="17"/>
-      <c r="BH4" s="17"/>
+      <c r="BE4" s="17"/>
+      <c r="BF4" s="17"/>
+      <c r="BG4" s="18"/>
+      <c r="BH4" s="18"/>
       <c r="BI4" s="17"/>
       <c r="BJ4" s="17"/>
       <c r="BK4" s="17"/>
-    </row>
-    <row r="5" spans="1:68" ht="18" x14ac:dyDescent="0.35">
+      <c r="BL4" s="17"/>
+      <c r="BM4" s="17"/>
+    </row>
+    <row r="5" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -1688,19 +1793,21 @@
       <c r="E5" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F5" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F5" s="17"/>
       <c r="G5" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="J5" s="17"/>
+      <c r="H5" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
+      <c r="L5" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="M5" s="17"/>
       <c r="N5" s="17"/>
       <c r="O5" s="17"/>
@@ -1724,63 +1831,65 @@
       <c r="AG5" s="17"/>
       <c r="AH5" s="17"/>
       <c r="AI5" s="17"/>
-      <c r="AJ5" s="18"/>
+      <c r="AJ5" s="17"/>
       <c r="AK5" s="17"/>
-      <c r="AL5" s="19"/>
-      <c r="AM5" s="19"/>
-      <c r="AN5" s="21"/>
-      <c r="AO5" s="33" t="s">
+      <c r="AL5" s="18"/>
+      <c r="AM5" s="17"/>
+      <c r="AN5" s="19"/>
+      <c r="AO5" s="19"/>
+      <c r="AP5" s="21"/>
+      <c r="AQ5" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="AP5" s="34" t="s">
+      <c r="AR5" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="AQ5" s="21"/>
-      <c r="AR5" s="21" t="s">
+      <c r="AS5" s="21"/>
+      <c r="AT5" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="AS5" s="21" t="s">
+      <c r="AU5" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="AT5" s="18"/>
-      <c r="AU5" s="34" t="s">
+      <c r="AV5" s="18"/>
+      <c r="AW5" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="AV5" s="34" t="s">
+      <c r="AX5" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="AW5" s="34"/>
-      <c r="AX5" s="17"/>
-      <c r="AY5" s="17"/>
+      <c r="AY5" s="34"/>
       <c r="AZ5" s="17"/>
-      <c r="BA5" s="18"/>
+      <c r="BA5" s="17"/>
       <c r="BB5" s="17"/>
-      <c r="BC5" s="17"/>
+      <c r="BC5" s="18"/>
       <c r="BD5" s="17"/>
-      <c r="BE5" s="18"/>
-      <c r="BF5" s="18"/>
-      <c r="BG5" s="17"/>
-      <c r="BH5" s="17"/>
+      <c r="BE5" s="17"/>
+      <c r="BF5" s="17"/>
+      <c r="BG5" s="18"/>
+      <c r="BH5" s="18"/>
       <c r="BI5" s="17"/>
       <c r="BJ5" s="17"/>
       <c r="BK5" s="17"/>
-      <c r="BL5">
+      <c r="BL5" s="17"/>
+      <c r="BM5" s="17"/>
+      <c r="BN5">
         <v>1</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BO5" t="s">
         <v>17</v>
       </c>
-      <c r="BN5" s="7" t="s">
+      <c r="BP5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="BO5" t="s">
+      <c r="BQ5" t="s">
         <v>19</v>
       </c>
-      <c r="BP5" t="s">
+      <c r="BR5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:68" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:70" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -1796,19 +1905,21 @@
       <c r="E6" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F6" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F6" s="17"/>
       <c r="G6" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="J6" s="17"/>
+      <c r="H6" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
+      <c r="L6" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M6" s="17"/>
       <c r="N6" s="17"/>
       <c r="O6" s="17"/>
@@ -1832,52 +1943,54 @@
       <c r="AG6" s="17"/>
       <c r="AH6" s="17"/>
       <c r="AI6" s="17"/>
-      <c r="AJ6" s="18"/>
+      <c r="AJ6" s="17"/>
       <c r="AK6" s="17"/>
-      <c r="AL6" s="19"/>
-      <c r="AM6" s="19"/>
-      <c r="AN6" s="21"/>
-      <c r="AO6" s="33" t="s">
+      <c r="AL6" s="18"/>
+      <c r="AM6" s="17"/>
+      <c r="AN6" s="19"/>
+      <c r="AO6" s="19"/>
+      <c r="AP6" s="21"/>
+      <c r="AQ6" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="AP6" s="34" t="s">
+      <c r="AR6" s="34" t="s">
         <v>142</v>
       </c>
-      <c r="AQ6" s="21"/>
-      <c r="AR6" s="11" t="s">
+      <c r="AS6" s="21"/>
+      <c r="AT6" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="AS6" s="8" t="s">
+      <c r="AU6" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AT6" s="18"/>
-      <c r="AU6" s="8" t="s">
+      <c r="AV6" s="18"/>
+      <c r="AW6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="AV6" s="34"/>
-      <c r="AW6" s="34"/>
-      <c r="AX6" s="17"/>
-      <c r="AY6" s="22"/>
+      <c r="AX6" s="34"/>
+      <c r="AY6" s="34"/>
       <c r="AZ6" s="17"/>
-      <c r="BA6" s="18"/>
+      <c r="BA6" s="22"/>
       <c r="BB6" s="17"/>
-      <c r="BC6" s="17"/>
+      <c r="BC6" s="18"/>
       <c r="BD6" s="17"/>
-      <c r="BE6" s="18"/>
-      <c r="BF6" s="18"/>
-      <c r="BG6" s="17"/>
-      <c r="BH6" s="17"/>
+      <c r="BE6" s="17"/>
+      <c r="BF6" s="17"/>
+      <c r="BG6" s="18"/>
+      <c r="BH6" s="18"/>
       <c r="BI6" s="17"/>
       <c r="BJ6" s="17"/>
       <c r="BK6" s="17"/>
-      <c r="BL6">
+      <c r="BL6" s="17"/>
+      <c r="BM6" s="17"/>
+      <c r="BN6">
         <v>2</v>
       </c>
-      <c r="BN6" s="7" t="s">
+      <c r="BP6" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:68" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:70" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -1893,22 +2006,24 @@
       <c r="E7" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F7" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F7" s="17"/>
       <c r="G7" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="J7" s="23"/>
+      <c r="H7" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="24"/>
+      <c r="L7" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="M7" s="17"/>
       <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
+      <c r="O7" s="24"/>
       <c r="P7" s="17"/>
       <c r="Q7" s="17"/>
       <c r="R7" s="17"/>
@@ -1931,32 +2046,32 @@
       <c r="AI7" s="17"/>
       <c r="AJ7" s="17"/>
       <c r="AK7" s="17"/>
-      <c r="AL7" s="19"/>
-      <c r="AM7" s="19"/>
-      <c r="AN7" s="25"/>
-      <c r="AO7" s="20" t="s">
+      <c r="AL7" s="17"/>
+      <c r="AM7" s="17"/>
+      <c r="AN7" s="19"/>
+      <c r="AO7" s="19"/>
+      <c r="AP7" s="25"/>
+      <c r="AQ7" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="AP7" s="19" t="s">
+      <c r="AR7" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="AQ7" s="17"/>
-      <c r="AR7" s="34">
+      <c r="AS7" s="17"/>
+      <c r="AT7" s="34">
         <v>9.3000000000000007</v>
       </c>
-      <c r="AS7" s="7" t="s">
+      <c r="AU7" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="AT7" s="17"/>
-      <c r="AU7" s="11" t="s">
+      <c r="AV7" s="17"/>
+      <c r="AW7" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="AV7" s="34"/>
-      <c r="AW7" s="34"/>
-      <c r="AX7" s="17"/>
-      <c r="AY7" s="22"/>
+      <c r="AX7" s="34"/>
+      <c r="AY7" s="34"/>
       <c r="AZ7" s="17"/>
-      <c r="BA7" s="17"/>
+      <c r="BA7" s="22"/>
       <c r="BB7" s="17"/>
       <c r="BC7" s="17"/>
       <c r="BD7" s="17"/>
@@ -1967,14 +2082,16 @@
       <c r="BI7" s="17"/>
       <c r="BJ7" s="17"/>
       <c r="BK7" s="17"/>
-      <c r="BL7" s="16">
+      <c r="BL7" s="17"/>
+      <c r="BM7" s="17"/>
+      <c r="BN7" s="16">
         <v>3</v>
       </c>
-      <c r="BN7" s="7" t="s">
+      <c r="BP7" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:68" ht="18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -1990,19 +2107,21 @@
       <c r="E8" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="F8" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F8" s="17"/>
       <c r="G8" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H8" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17" t="s">
+      <c r="I8" s="17"/>
+      <c r="J8" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="J8" s="17"/>
       <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
+      <c r="L8" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M8" s="17"/>
       <c r="N8" s="17"/>
       <c r="O8" s="17"/>
@@ -2028,28 +2147,28 @@
       <c r="AI8" s="17"/>
       <c r="AJ8" s="17"/>
       <c r="AK8" s="17"/>
-      <c r="AL8" s="19"/>
-      <c r="AM8" s="19"/>
-      <c r="AN8" s="25"/>
-      <c r="AO8" s="36" t="s">
+      <c r="AL8" s="17"/>
+      <c r="AM8" s="17"/>
+      <c r="AN8" s="19"/>
+      <c r="AO8" s="19"/>
+      <c r="AP8" s="25"/>
+      <c r="AQ8" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="AP8" s="34" t="s">
+      <c r="AR8" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="AQ8" s="17"/>
-      <c r="AR8" s="34">
+      <c r="AS8" s="17"/>
+      <c r="AT8" s="34">
         <v>9.4</v>
       </c>
-      <c r="AS8" s="7" t="s">
+      <c r="AU8" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="AT8" s="17"/>
-      <c r="AU8" s="37" t="s">
+      <c r="AV8" s="17"/>
+      <c r="AW8" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="AV8" s="17"/>
-      <c r="AW8" s="17"/>
       <c r="AX8" s="17"/>
       <c r="AY8" s="17"/>
       <c r="AZ8" s="17"/>
@@ -2064,14 +2183,16 @@
       <c r="BI8" s="17"/>
       <c r="BJ8" s="17"/>
       <c r="BK8" s="17"/>
-      <c r="BL8">
+      <c r="BL8" s="17"/>
+      <c r="BM8" s="17"/>
+      <c r="BN8">
         <v>4</v>
       </c>
-      <c r="BN8" t="s">
+      <c r="BP8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:68" ht="18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -2087,19 +2208,21 @@
       <c r="E9" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F9" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F9" s="17"/>
       <c r="G9" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17" t="s">
+      <c r="H9" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="J9" s="17"/>
       <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
+      <c r="L9" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M9" s="17"/>
       <c r="N9" s="17"/>
       <c r="O9" s="17"/>
@@ -2123,50 +2246,52 @@
       <c r="AG9" s="17"/>
       <c r="AH9" s="17"/>
       <c r="AI9" s="17"/>
-      <c r="AJ9" s="18"/>
+      <c r="AJ9" s="17"/>
       <c r="AK9" s="17"/>
-      <c r="AL9" s="19"/>
-      <c r="AM9" s="19"/>
-      <c r="AN9" s="21"/>
-      <c r="AO9" s="27" t="s">
+      <c r="AL9" s="18"/>
+      <c r="AM9" s="17"/>
+      <c r="AN9" s="19"/>
+      <c r="AO9" s="19"/>
+      <c r="AP9" s="21"/>
+      <c r="AQ9" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="AP9" s="19" t="s">
+      <c r="AR9" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="AQ9" s="21"/>
-      <c r="AR9" s="34">
+      <c r="AS9" s="21"/>
+      <c r="AT9" s="34">
         <v>9.1</v>
       </c>
-      <c r="AS9" s="7" t="s">
+      <c r="AU9" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="AT9" s="18"/>
-      <c r="AU9" s="17"/>
-      <c r="AV9" s="17"/>
-      <c r="AW9" s="18"/>
+      <c r="AV9" s="18"/>
+      <c r="AW9" s="17"/>
       <c r="AX9" s="17"/>
-      <c r="AY9" s="17"/>
+      <c r="AY9" s="18"/>
       <c r="AZ9" s="17"/>
-      <c r="BA9" s="18"/>
+      <c r="BA9" s="17"/>
       <c r="BB9" s="17"/>
-      <c r="BC9" s="17"/>
+      <c r="BC9" s="18"/>
       <c r="BD9" s="17"/>
-      <c r="BE9" s="18"/>
-      <c r="BF9" s="18"/>
-      <c r="BG9" s="17"/>
-      <c r="BH9" s="17"/>
+      <c r="BE9" s="17"/>
+      <c r="BF9" s="17"/>
+      <c r="BG9" s="18"/>
+      <c r="BH9" s="18"/>
       <c r="BI9" s="17"/>
       <c r="BJ9" s="17"/>
       <c r="BK9" s="17"/>
-      <c r="BL9">
+      <c r="BL9" s="17"/>
+      <c r="BM9" s="17"/>
+      <c r="BN9">
         <v>5</v>
       </c>
-      <c r="BN9" t="s">
+      <c r="BP9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:68" ht="18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -2182,19 +2307,21 @@
       <c r="E10" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F10" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F10" s="17"/>
       <c r="G10" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="J10" s="17"/>
+      <c r="H10" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
+      <c r="L10" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M10" s="17"/>
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
@@ -2218,50 +2345,52 @@
       <c r="AG10" s="17"/>
       <c r="AH10" s="17"/>
       <c r="AI10" s="17"/>
-      <c r="AJ10" s="18"/>
+      <c r="AJ10" s="17"/>
       <c r="AK10" s="17"/>
-      <c r="AL10" s="19"/>
-      <c r="AM10" s="19"/>
-      <c r="AN10" s="21"/>
-      <c r="AO10" s="33" t="s">
+      <c r="AL10" s="18"/>
+      <c r="AM10" s="17"/>
+      <c r="AN10" s="19"/>
+      <c r="AO10" s="19"/>
+      <c r="AP10" s="21"/>
+      <c r="AQ10" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="AP10" s="34" t="s">
+      <c r="AR10" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="AQ10" s="18"/>
-      <c r="AR10" s="34" t="s">
+      <c r="AS10" s="18"/>
+      <c r="AT10" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="AS10" s="34" t="s">
+      <c r="AU10" s="34" t="s">
         <v>174</v>
       </c>
-      <c r="AT10" s="34"/>
-      <c r="AU10" s="17"/>
-      <c r="AV10" s="17"/>
+      <c r="AV10" s="34"/>
       <c r="AW10" s="17"/>
       <c r="AX10" s="17"/>
       <c r="AY10" s="17"/>
       <c r="AZ10" s="17"/>
-      <c r="BA10" s="18"/>
+      <c r="BA10" s="17"/>
       <c r="BB10" s="17"/>
-      <c r="BC10" s="17"/>
+      <c r="BC10" s="18"/>
       <c r="BD10" s="17"/>
-      <c r="BE10" s="18"/>
-      <c r="BF10" s="18"/>
-      <c r="BG10" s="17"/>
-      <c r="BH10" s="17"/>
+      <c r="BE10" s="17"/>
+      <c r="BF10" s="17"/>
+      <c r="BG10" s="18"/>
+      <c r="BH10" s="18"/>
       <c r="BI10" s="17"/>
       <c r="BJ10" s="17"/>
       <c r="BK10" s="17"/>
-      <c r="BL10">
+      <c r="BL10" s="17"/>
+      <c r="BM10" s="17"/>
+      <c r="BN10">
         <v>6</v>
       </c>
-      <c r="BN10" t="s">
+      <c r="BP10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:68" ht="18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -2277,19 +2406,21 @@
       <c r="E11" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F11" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F11" s="17"/>
       <c r="G11" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="J11" s="17"/>
+      <c r="H11" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
+      <c r="L11" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M11" s="17"/>
       <c r="N11" s="17"/>
       <c r="O11" s="17"/>
@@ -2313,50 +2444,52 @@
       <c r="AG11" s="17"/>
       <c r="AH11" s="17"/>
       <c r="AI11" s="17"/>
-      <c r="AJ11" s="18"/>
+      <c r="AJ11" s="17"/>
       <c r="AK11" s="17"/>
-      <c r="AL11" s="19"/>
-      <c r="AM11" s="19"/>
-      <c r="AN11" s="21"/>
-      <c r="AO11" s="33" t="s">
+      <c r="AL11" s="18"/>
+      <c r="AM11" s="17"/>
+      <c r="AN11" s="19"/>
+      <c r="AO11" s="19"/>
+      <c r="AP11" s="21"/>
+      <c r="AQ11" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="AP11" s="34" t="s">
+      <c r="AR11" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="AQ11" s="18"/>
-      <c r="AR11" s="34" t="s">
+      <c r="AS11" s="18"/>
+      <c r="AT11" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="AS11" s="34" t="s">
+      <c r="AU11" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="AT11" s="34"/>
-      <c r="AU11" s="17"/>
-      <c r="AV11" s="17"/>
-      <c r="AW11" s="18"/>
+      <c r="AV11" s="34"/>
+      <c r="AW11" s="17"/>
       <c r="AX11" s="17"/>
-      <c r="AY11" s="17"/>
+      <c r="AY11" s="18"/>
       <c r="AZ11" s="17"/>
-      <c r="BA11" s="18"/>
+      <c r="BA11" s="17"/>
       <c r="BB11" s="17"/>
-      <c r="BC11" s="17"/>
+      <c r="BC11" s="18"/>
       <c r="BD11" s="17"/>
-      <c r="BE11" s="18"/>
-      <c r="BF11" s="18"/>
-      <c r="BG11" s="17"/>
-      <c r="BH11" s="17"/>
+      <c r="BE11" s="17"/>
+      <c r="BF11" s="17"/>
+      <c r="BG11" s="18"/>
+      <c r="BH11" s="18"/>
       <c r="BI11" s="17"/>
       <c r="BJ11" s="17"/>
       <c r="BK11" s="17"/>
-      <c r="BL11">
+      <c r="BL11" s="17"/>
+      <c r="BM11" s="17"/>
+      <c r="BN11">
         <v>7</v>
       </c>
-      <c r="BN11" t="s">
+      <c r="BP11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:68" ht="18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -2372,21 +2505,23 @@
       <c r="E12" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F12" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F12" s="17"/>
       <c r="G12" s="17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>127</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="J12" s="17"/>
+        <v>127</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
+      <c r="L12" s="2" t="s">
+        <v>129</v>
+      </c>
       <c r="M12" s="17"/>
       <c r="N12" s="17"/>
       <c r="O12" s="17"/>
@@ -2410,48 +2545,50 @@
       <c r="AG12" s="17"/>
       <c r="AH12" s="17"/>
       <c r="AI12" s="17"/>
-      <c r="AJ12" s="18"/>
+      <c r="AJ12" s="17"/>
       <c r="AK12" s="17"/>
-      <c r="AL12" s="19"/>
-      <c r="AM12" s="19"/>
-      <c r="AN12" s="21"/>
-      <c r="AO12" s="20" t="s">
+      <c r="AL12" s="18"/>
+      <c r="AM12" s="17"/>
+      <c r="AN12" s="19"/>
+      <c r="AO12" s="19"/>
+      <c r="AP12" s="21"/>
+      <c r="AQ12" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="AP12" s="19" t="s">
+      <c r="AR12" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="AQ12" s="21"/>
-      <c r="AR12" s="34" t="s">
+      <c r="AS12" s="21"/>
+      <c r="AT12" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="AS12" s="34"/>
-      <c r="AT12" s="34"/>
-      <c r="AU12" s="17"/>
-      <c r="AV12" s="17"/>
-      <c r="AW12" s="18"/>
+      <c r="AU12" s="34"/>
+      <c r="AV12" s="34"/>
+      <c r="AW12" s="17"/>
       <c r="AX12" s="17"/>
-      <c r="AY12" s="17"/>
+      <c r="AY12" s="18"/>
       <c r="AZ12" s="17"/>
-      <c r="BA12" s="18"/>
+      <c r="BA12" s="17"/>
       <c r="BB12" s="17"/>
-      <c r="BC12" s="17"/>
+      <c r="BC12" s="18"/>
       <c r="BD12" s="17"/>
-      <c r="BE12" s="18"/>
-      <c r="BF12" s="18"/>
-      <c r="BG12" s="17"/>
-      <c r="BH12" s="17"/>
+      <c r="BE12" s="17"/>
+      <c r="BF12" s="17"/>
+      <c r="BG12" s="18"/>
+      <c r="BH12" s="18"/>
       <c r="BI12" s="17"/>
       <c r="BJ12" s="17"/>
       <c r="BK12" s="17"/>
-      <c r="BL12">
+      <c r="BL12" s="17"/>
+      <c r="BM12" s="17"/>
+      <c r="BN12">
         <v>8</v>
       </c>
-      <c r="BN12" t="s">
+      <c r="BP12" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:68" ht="18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -2467,19 +2604,21 @@
       <c r="E13" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F13" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F13" s="17"/>
       <c r="G13" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="J13" s="17"/>
+      <c r="H13" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
+      <c r="L13" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M13" s="17"/>
       <c r="N13" s="17"/>
       <c r="O13" s="17"/>
@@ -2503,46 +2642,48 @@
       <c r="AG13" s="17"/>
       <c r="AH13" s="17"/>
       <c r="AI13" s="17"/>
-      <c r="AJ13" s="18"/>
+      <c r="AJ13" s="17"/>
       <c r="AK13" s="17"/>
-      <c r="AL13" s="19"/>
-      <c r="AM13" s="19"/>
-      <c r="AN13" s="21"/>
-      <c r="AO13" s="33" t="s">
+      <c r="AL13" s="18"/>
+      <c r="AM13" s="17"/>
+      <c r="AN13" s="19"/>
+      <c r="AO13" s="19"/>
+      <c r="AP13" s="21"/>
+      <c r="AQ13" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="AP13" s="34" t="s">
+      <c r="AR13" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="AQ13" s="18"/>
-      <c r="AR13" s="17"/>
-      <c r="AS13" s="22"/>
-      <c r="AT13" s="18"/>
-      <c r="AU13" s="17"/>
-      <c r="AV13" s="17"/>
-      <c r="AW13" s="18"/>
+      <c r="AS13" s="18"/>
+      <c r="AT13" s="17"/>
+      <c r="AU13" s="22"/>
+      <c r="AV13" s="18"/>
+      <c r="AW13" s="17"/>
       <c r="AX13" s="17"/>
-      <c r="AY13" s="17"/>
+      <c r="AY13" s="18"/>
       <c r="AZ13" s="17"/>
-      <c r="BA13" s="18"/>
+      <c r="BA13" s="17"/>
       <c r="BB13" s="17"/>
-      <c r="BC13" s="17"/>
+      <c r="BC13" s="18"/>
       <c r="BD13" s="17"/>
-      <c r="BE13" s="18"/>
-      <c r="BF13" s="18"/>
-      <c r="BG13" s="17"/>
-      <c r="BH13" s="17"/>
+      <c r="BE13" s="17"/>
+      <c r="BF13" s="17"/>
+      <c r="BG13" s="18"/>
+      <c r="BH13" s="18"/>
       <c r="BI13" s="17"/>
       <c r="BJ13" s="17"/>
       <c r="BK13" s="17"/>
-      <c r="BL13">
+      <c r="BL13" s="17"/>
+      <c r="BM13" s="17"/>
+      <c r="BN13">
         <v>9</v>
       </c>
-      <c r="BN13" t="s">
+      <c r="BP13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:68" ht="18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -2558,23 +2699,25 @@
       <c r="E14" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F14" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F14" s="17"/>
       <c r="G14" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17" t="s">
+      <c r="H14" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="J14" s="17"/>
       <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
+      <c r="L14" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M14" s="17"/>
-      <c r="N14" s="23"/>
+      <c r="N14" s="17"/>
       <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
+      <c r="P14" s="23"/>
       <c r="Q14" s="17"/>
       <c r="R14" s="17"/>
       <c r="S14" s="17"/>
@@ -2596,17 +2739,17 @@
       <c r="AI14" s="17"/>
       <c r="AJ14" s="17"/>
       <c r="AK14" s="17"/>
-      <c r="AL14" s="19"/>
-      <c r="AM14" s="19"/>
-      <c r="AN14" s="25"/>
-      <c r="AO14" s="36" t="s">
+      <c r="AL14" s="17"/>
+      <c r="AM14" s="17"/>
+      <c r="AN14" s="19"/>
+      <c r="AO14" s="19"/>
+      <c r="AP14" s="25"/>
+      <c r="AQ14" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="AP14" s="34" t="s">
+      <c r="AR14" s="34" t="s">
         <v>160</v>
       </c>
-      <c r="AQ14" s="17"/>
-      <c r="AR14" s="17"/>
       <c r="AS14" s="17"/>
       <c r="AT14" s="17"/>
       <c r="AU14" s="17"/>
@@ -2626,14 +2769,16 @@
       <c r="BI14" s="17"/>
       <c r="BJ14" s="17"/>
       <c r="BK14" s="17"/>
-      <c r="BL14">
+      <c r="BL14" s="17"/>
+      <c r="BM14" s="17"/>
+      <c r="BN14">
         <v>10</v>
       </c>
-      <c r="BN14" t="s">
+      <c r="BP14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:68" ht="18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -2649,19 +2794,21 @@
       <c r="E15" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F15" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F15" s="17"/>
       <c r="G15" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="J15" s="17"/>
+      <c r="H15" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
+      <c r="L15" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M15" s="17"/>
       <c r="N15" s="17"/>
       <c r="O15" s="17"/>
@@ -2685,46 +2832,48 @@
       <c r="AG15" s="17"/>
       <c r="AH15" s="17"/>
       <c r="AI15" s="17"/>
-      <c r="AJ15" s="18"/>
+      <c r="AJ15" s="17"/>
       <c r="AK15" s="17"/>
-      <c r="AL15" s="19"/>
-      <c r="AM15" s="19"/>
-      <c r="AN15" s="18"/>
-      <c r="AO15" s="33" t="s">
+      <c r="AL15" s="18"/>
+      <c r="AM15" s="17"/>
+      <c r="AN15" s="19"/>
+      <c r="AO15" s="19"/>
+      <c r="AP15" s="18"/>
+      <c r="AQ15" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="AP15" s="34" t="s">
+      <c r="AR15" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="AQ15" s="21"/>
-      <c r="AR15" s="17"/>
-      <c r="AS15" s="22"/>
-      <c r="AT15" s="18"/>
-      <c r="AU15" s="17"/>
-      <c r="AV15" s="22"/>
-      <c r="AW15" s="21"/>
-      <c r="AX15" s="17"/>
-      <c r="AY15" s="17"/>
+      <c r="AS15" s="21"/>
+      <c r="AT15" s="17"/>
+      <c r="AU15" s="22"/>
+      <c r="AV15" s="18"/>
+      <c r="AW15" s="17"/>
+      <c r="AX15" s="22"/>
+      <c r="AY15" s="21"/>
       <c r="AZ15" s="17"/>
-      <c r="BA15" s="18"/>
+      <c r="BA15" s="17"/>
       <c r="BB15" s="17"/>
-      <c r="BC15" s="17"/>
+      <c r="BC15" s="18"/>
       <c r="BD15" s="17"/>
       <c r="BE15" s="17"/>
-      <c r="BF15" s="18"/>
+      <c r="BF15" s="17"/>
       <c r="BG15" s="17"/>
-      <c r="BH15" s="17"/>
+      <c r="BH15" s="18"/>
       <c r="BI15" s="17"/>
       <c r="BJ15" s="17"/>
       <c r="BK15" s="17"/>
-      <c r="BL15">
+      <c r="BL15" s="17"/>
+      <c r="BM15" s="17"/>
+      <c r="BN15">
         <v>11</v>
       </c>
-      <c r="BN15" t="s">
+      <c r="BP15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:68" ht="18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -2740,19 +2889,21 @@
       <c r="E16" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F16" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F16" s="17"/>
       <c r="G16" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="J16" s="17"/>
+      <c r="H16" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
+      <c r="L16" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M16" s="17"/>
       <c r="N16" s="17"/>
       <c r="O16" s="17"/>
@@ -2776,50 +2927,52 @@
       <c r="AG16" s="17"/>
       <c r="AH16" s="17"/>
       <c r="AI16" s="17"/>
-      <c r="AJ16" s="18"/>
+      <c r="AJ16" s="17"/>
       <c r="AK16" s="17"/>
       <c r="AL16" s="18"/>
-      <c r="AM16" s="19"/>
-      <c r="AN16" s="25"/>
-      <c r="AO16" s="33" t="s">
+      <c r="AM16" s="17"/>
+      <c r="AN16" s="18"/>
+      <c r="AO16" s="19"/>
+      <c r="AP16" s="25"/>
+      <c r="AQ16" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="AP16" s="34" t="s">
+      <c r="AR16" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="AQ16" s="18"/>
-      <c r="AR16" s="21" t="s">
+      <c r="AS16" s="18"/>
+      <c r="AT16" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="AS16" s="21" t="s">
+      <c r="AU16" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="AT16" s="18"/>
-      <c r="AU16" s="17"/>
-      <c r="AV16" s="22"/>
-      <c r="AW16" s="18"/>
-      <c r="AX16" s="17"/>
-      <c r="AY16" s="26"/>
+      <c r="AV16" s="18"/>
+      <c r="AW16" s="17"/>
+      <c r="AX16" s="22"/>
+      <c r="AY16" s="18"/>
       <c r="AZ16" s="17"/>
-      <c r="BA16" s="18"/>
+      <c r="BA16" s="26"/>
       <c r="BB16" s="17"/>
-      <c r="BC16" s="17"/>
+      <c r="BC16" s="18"/>
       <c r="BD16" s="17"/>
-      <c r="BE16" s="18"/>
-      <c r="BF16" s="18"/>
-      <c r="BG16" s="17"/>
-      <c r="BH16" s="17"/>
+      <c r="BE16" s="17"/>
+      <c r="BF16" s="17"/>
+      <c r="BG16" s="18"/>
+      <c r="BH16" s="18"/>
       <c r="BI16" s="17"/>
       <c r="BJ16" s="17"/>
       <c r="BK16" s="17"/>
-      <c r="BL16">
+      <c r="BL16" s="17"/>
+      <c r="BM16" s="17"/>
+      <c r="BN16">
         <v>12</v>
       </c>
-      <c r="BN16" t="s">
+      <c r="BP16" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:66" ht="18" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -2835,19 +2988,21 @@
       <c r="E17" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F17" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F17" s="17"/>
       <c r="G17" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="J17" s="17"/>
+      <c r="H17" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
+      <c r="L17" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M17" s="17"/>
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
@@ -2871,46 +3026,48 @@
       <c r="AG17" s="17"/>
       <c r="AH17" s="17"/>
       <c r="AI17" s="17"/>
-      <c r="AJ17" s="18"/>
+      <c r="AJ17" s="17"/>
       <c r="AK17" s="17"/>
-      <c r="AL17" s="19"/>
-      <c r="AM17" s="19"/>
-      <c r="AN17" s="21"/>
-      <c r="AO17" s="33" t="s">
+      <c r="AL17" s="18"/>
+      <c r="AM17" s="17"/>
+      <c r="AN17" s="19"/>
+      <c r="AO17" s="19"/>
+      <c r="AP17" s="21"/>
+      <c r="AQ17" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="AP17" s="34" t="s">
+      <c r="AR17" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="AQ17" s="18"/>
-      <c r="AR17" s="17"/>
-      <c r="AS17" s="17"/>
-      <c r="AT17" s="18"/>
+      <c r="AS17" s="18"/>
+      <c r="AT17" s="17"/>
       <c r="AU17" s="17"/>
-      <c r="AV17" s="17"/>
-      <c r="AW17" s="18"/>
+      <c r="AV17" s="18"/>
+      <c r="AW17" s="17"/>
       <c r="AX17" s="17"/>
-      <c r="AY17" s="17"/>
+      <c r="AY17" s="18"/>
       <c r="AZ17" s="17"/>
-      <c r="BA17" s="18"/>
+      <c r="BA17" s="17"/>
       <c r="BB17" s="17"/>
-      <c r="BC17" s="17"/>
+      <c r="BC17" s="18"/>
       <c r="BD17" s="17"/>
-      <c r="BE17" s="18"/>
-      <c r="BF17" s="18"/>
-      <c r="BG17" s="17"/>
-      <c r="BH17" s="17"/>
+      <c r="BE17" s="17"/>
+      <c r="BF17" s="17"/>
+      <c r="BG17" s="18"/>
+      <c r="BH17" s="18"/>
       <c r="BI17" s="17"/>
       <c r="BJ17" s="17"/>
       <c r="BK17" s="17"/>
-      <c r="BL17">
+      <c r="BL17" s="17"/>
+      <c r="BM17" s="17"/>
+      <c r="BN17">
         <v>13</v>
       </c>
-      <c r="BN17" t="s">
+      <c r="BP17" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:66" ht="18" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -2926,21 +3083,23 @@
       <c r="E18" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F18" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F18" s="17"/>
       <c r="G18" s="17" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>129</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="J18" s="17"/>
+        <v>129</v>
+      </c>
+      <c r="J18" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
+      <c r="L18" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M18" s="17"/>
       <c r="N18" s="17"/>
       <c r="O18" s="17"/>
@@ -2964,46 +3123,48 @@
       <c r="AG18" s="17"/>
       <c r="AH18" s="17"/>
       <c r="AI18" s="17"/>
-      <c r="AJ18" s="18"/>
+      <c r="AJ18" s="17"/>
       <c r="AK18" s="17"/>
-      <c r="AL18" s="19"/>
-      <c r="AM18" s="19"/>
-      <c r="AN18" s="21"/>
-      <c r="AO18" s="35" t="s">
+      <c r="AL18" s="18"/>
+      <c r="AM18" s="17"/>
+      <c r="AN18" s="19"/>
+      <c r="AO18" s="19"/>
+      <c r="AP18" s="21"/>
+      <c r="AQ18" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="AP18" s="34" t="s">
+      <c r="AR18" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="AQ18" s="21"/>
-      <c r="AR18" s="17"/>
-      <c r="AS18" s="22"/>
-      <c r="AT18" s="18"/>
-      <c r="AU18" s="17"/>
-      <c r="AV18" s="17"/>
-      <c r="AW18" s="18"/>
+      <c r="AS18" s="21"/>
+      <c r="AT18" s="17"/>
+      <c r="AU18" s="22"/>
+      <c r="AV18" s="18"/>
+      <c r="AW18" s="17"/>
       <c r="AX18" s="17"/>
-      <c r="AY18" s="17"/>
+      <c r="AY18" s="18"/>
       <c r="AZ18" s="17"/>
-      <c r="BA18" s="18"/>
+      <c r="BA18" s="17"/>
       <c r="BB18" s="17"/>
-      <c r="BC18" s="17"/>
+      <c r="BC18" s="18"/>
       <c r="BD18" s="17"/>
-      <c r="BE18" s="18"/>
-      <c r="BF18" s="18"/>
-      <c r="BG18" s="17"/>
-      <c r="BH18" s="17"/>
+      <c r="BE18" s="17"/>
+      <c r="BF18" s="17"/>
+      <c r="BG18" s="18"/>
+      <c r="BH18" s="18"/>
       <c r="BI18" s="17"/>
       <c r="BJ18" s="17"/>
       <c r="BK18" s="17"/>
-      <c r="BL18">
+      <c r="BL18" s="17"/>
+      <c r="BM18" s="17"/>
+      <c r="BN18">
         <v>14</v>
       </c>
-      <c r="BN18" t="s">
+      <c r="BP18" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:66" ht="18" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -3019,19 +3180,21 @@
       <c r="E19" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F19" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F19" s="17"/>
       <c r="G19" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="J19" s="17"/>
+      <c r="H19" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
+      <c r="L19" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M19" s="17"/>
       <c r="N19" s="17"/>
       <c r="O19" s="17"/>
@@ -3055,46 +3218,48 @@
       <c r="AG19" s="17"/>
       <c r="AH19" s="17"/>
       <c r="AI19" s="17"/>
-      <c r="AJ19" s="18"/>
+      <c r="AJ19" s="17"/>
       <c r="AK19" s="17"/>
-      <c r="AL19" s="19"/>
-      <c r="AM19" s="19"/>
-      <c r="AN19" s="21"/>
-      <c r="AO19" s="33" t="s">
+      <c r="AL19" s="18"/>
+      <c r="AM19" s="17"/>
+      <c r="AN19" s="19"/>
+      <c r="AO19" s="19"/>
+      <c r="AP19" s="21"/>
+      <c r="AQ19" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="AP19" s="34" t="s">
+      <c r="AR19" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="AQ19" s="18"/>
-      <c r="AR19" s="17"/>
-      <c r="AS19" s="22"/>
-      <c r="AT19" s="21"/>
-      <c r="AU19" s="17"/>
-      <c r="AV19" s="17"/>
-      <c r="AW19" s="21"/>
+      <c r="AS19" s="18"/>
+      <c r="AT19" s="17"/>
+      <c r="AU19" s="22"/>
+      <c r="AV19" s="21"/>
+      <c r="AW19" s="17"/>
       <c r="AX19" s="17"/>
-      <c r="AY19" s="17"/>
+      <c r="AY19" s="21"/>
       <c r="AZ19" s="17"/>
-      <c r="BA19" s="18"/>
+      <c r="BA19" s="17"/>
       <c r="BB19" s="17"/>
-      <c r="BC19" s="17"/>
+      <c r="BC19" s="18"/>
       <c r="BD19" s="17"/>
-      <c r="BE19" s="18"/>
-      <c r="BF19" s="18"/>
-      <c r="BG19" s="17"/>
-      <c r="BH19" s="17"/>
+      <c r="BE19" s="17"/>
+      <c r="BF19" s="17"/>
+      <c r="BG19" s="18"/>
+      <c r="BH19" s="18"/>
       <c r="BI19" s="17"/>
       <c r="BJ19" s="17"/>
       <c r="BK19" s="17"/>
-      <c r="BL19">
+      <c r="BL19" s="17"/>
+      <c r="BM19" s="17"/>
+      <c r="BN19">
         <v>15</v>
       </c>
-      <c r="BN19" t="s">
+      <c r="BP19" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:66" ht="18" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -3110,19 +3275,21 @@
       <c r="E20" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F20" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F20" s="17"/>
       <c r="G20" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="J20" s="17"/>
+      <c r="H20" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
+      <c r="L20" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="M20" s="17"/>
       <c r="N20" s="17"/>
       <c r="O20" s="17"/>
@@ -3146,46 +3313,48 @@
       <c r="AG20" s="17"/>
       <c r="AH20" s="17"/>
       <c r="AI20" s="17"/>
-      <c r="AJ20" s="18"/>
+      <c r="AJ20" s="17"/>
       <c r="AK20" s="17"/>
-      <c r="AL20" s="19"/>
-      <c r="AM20" s="19"/>
-      <c r="AN20" s="21"/>
-      <c r="AO20" s="27" t="s">
+      <c r="AL20" s="18"/>
+      <c r="AM20" s="17"/>
+      <c r="AN20" s="19"/>
+      <c r="AO20" s="19"/>
+      <c r="AP20" s="21"/>
+      <c r="AQ20" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="AP20" s="19" t="s">
+      <c r="AR20" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="AQ20" s="18"/>
-      <c r="AR20" s="17"/>
-      <c r="AS20" s="28"/>
+      <c r="AS20" s="18"/>
       <c r="AT20" s="17"/>
-      <c r="AU20" s="17"/>
+      <c r="AU20" s="28"/>
       <c r="AV20" s="17"/>
-      <c r="AW20" s="18"/>
+      <c r="AW20" s="17"/>
       <c r="AX20" s="17"/>
-      <c r="AY20" s="17"/>
+      <c r="AY20" s="18"/>
       <c r="AZ20" s="17"/>
-      <c r="BA20" s="18"/>
+      <c r="BA20" s="17"/>
       <c r="BB20" s="17"/>
-      <c r="BC20" s="17"/>
+      <c r="BC20" s="18"/>
       <c r="BD20" s="17"/>
-      <c r="BE20" s="18"/>
-      <c r="BF20" s="18"/>
-      <c r="BG20" s="17"/>
-      <c r="BH20" s="17"/>
+      <c r="BE20" s="17"/>
+      <c r="BF20" s="17"/>
+      <c r="BG20" s="18"/>
+      <c r="BH20" s="18"/>
       <c r="BI20" s="17"/>
       <c r="BJ20" s="17"/>
       <c r="BK20" s="17"/>
-      <c r="BL20">
+      <c r="BL20" s="17"/>
+      <c r="BM20" s="17"/>
+      <c r="BN20">
         <v>16</v>
       </c>
-      <c r="BN20" t="s">
+      <c r="BP20" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:66" ht="18" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -3201,19 +3370,21 @@
       <c r="E21" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="F21" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F21" s="17"/>
       <c r="G21" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17" t="s">
+      <c r="H21" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="J21" s="17"/>
       <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
+      <c r="L21" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M21" s="17"/>
       <c r="N21" s="17"/>
       <c r="O21" s="17"/>
@@ -3237,46 +3408,48 @@
       <c r="AG21" s="17"/>
       <c r="AH21" s="17"/>
       <c r="AI21" s="17"/>
-      <c r="AJ21" s="18"/>
+      <c r="AJ21" s="17"/>
       <c r="AK21" s="17"/>
-      <c r="AL21" s="19"/>
-      <c r="AM21" s="19"/>
-      <c r="AN21" s="21"/>
-      <c r="AO21" s="36" t="s">
+      <c r="AL21" s="18"/>
+      <c r="AM21" s="17"/>
+      <c r="AN21" s="19"/>
+      <c r="AO21" s="19"/>
+      <c r="AP21" s="21"/>
+      <c r="AQ21" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="AP21" s="34" t="s">
+      <c r="AR21" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="AQ21" s="21"/>
-      <c r="AR21" s="17"/>
-      <c r="AS21" s="17"/>
-      <c r="AT21" s="18"/>
+      <c r="AS21" s="21"/>
+      <c r="AT21" s="17"/>
       <c r="AU21" s="17"/>
-      <c r="AV21" s="17"/>
-      <c r="AW21" s="18"/>
+      <c r="AV21" s="18"/>
+      <c r="AW21" s="17"/>
       <c r="AX21" s="17"/>
-      <c r="AY21" s="17"/>
+      <c r="AY21" s="18"/>
       <c r="AZ21" s="17"/>
-      <c r="BA21" s="18"/>
+      <c r="BA21" s="17"/>
       <c r="BB21" s="17"/>
-      <c r="BC21" s="17"/>
+      <c r="BC21" s="18"/>
       <c r="BD21" s="17"/>
-      <c r="BE21" s="18"/>
-      <c r="BF21" s="18"/>
-      <c r="BG21" s="17"/>
-      <c r="BH21" s="17"/>
+      <c r="BE21" s="17"/>
+      <c r="BF21" s="17"/>
+      <c r="BG21" s="18"/>
+      <c r="BH21" s="18"/>
       <c r="BI21" s="17"/>
       <c r="BJ21" s="17"/>
       <c r="BK21" s="17"/>
-      <c r="BL21" s="16">
+      <c r="BL21" s="17"/>
+      <c r="BM21" s="17"/>
+      <c r="BN21" s="16">
         <v>17</v>
       </c>
-      <c r="BN21" t="s">
+      <c r="BP21" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:66" ht="18" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -3292,19 +3465,21 @@
       <c r="E22" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F22" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F22" s="17"/>
       <c r="G22" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17" t="s">
+      <c r="H22" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="J22" s="17"/>
       <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
+      <c r="L22" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M22" s="17"/>
       <c r="N22" s="17"/>
       <c r="O22" s="17"/>
@@ -3328,46 +3503,48 @@
       <c r="AG22" s="17"/>
       <c r="AH22" s="17"/>
       <c r="AI22" s="17"/>
-      <c r="AJ22" s="18"/>
+      <c r="AJ22" s="17"/>
       <c r="AK22" s="17"/>
-      <c r="AL22" s="19"/>
-      <c r="AM22" s="19"/>
-      <c r="AN22" s="21"/>
-      <c r="AO22" s="27" t="s">
+      <c r="AL22" s="18"/>
+      <c r="AM22" s="17"/>
+      <c r="AN22" s="19"/>
+      <c r="AO22" s="19"/>
+      <c r="AP22" s="21"/>
+      <c r="AQ22" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="AP22" s="7" t="s">
+      <c r="AR22" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="AQ22" s="21"/>
-      <c r="AR22" s="17"/>
-      <c r="AS22" s="22"/>
-      <c r="AT22" s="18"/>
-      <c r="AU22" s="17"/>
-      <c r="AV22" s="22"/>
-      <c r="AW22" s="18"/>
-      <c r="AX22" s="17"/>
-      <c r="AY22" s="17"/>
+      <c r="AS22" s="21"/>
+      <c r="AT22" s="17"/>
+      <c r="AU22" s="22"/>
+      <c r="AV22" s="18"/>
+      <c r="AW22" s="17"/>
+      <c r="AX22" s="22"/>
+      <c r="AY22" s="18"/>
       <c r="AZ22" s="17"/>
-      <c r="BA22" s="18"/>
+      <c r="BA22" s="17"/>
       <c r="BB22" s="17"/>
-      <c r="BC22" s="17"/>
+      <c r="BC22" s="18"/>
       <c r="BD22" s="17"/>
-      <c r="BE22" s="18"/>
-      <c r="BF22" s="18"/>
-      <c r="BG22" s="17"/>
-      <c r="BH22" s="17"/>
+      <c r="BE22" s="17"/>
+      <c r="BF22" s="17"/>
+      <c r="BG22" s="18"/>
+      <c r="BH22" s="18"/>
       <c r="BI22" s="17"/>
       <c r="BJ22" s="17"/>
       <c r="BK22" s="17"/>
-      <c r="BL22">
+      <c r="BL22" s="17"/>
+      <c r="BM22" s="17"/>
+      <c r="BN22">
         <v>18</v>
       </c>
-      <c r="BN22" t="s">
+      <c r="BP22" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:66" ht="18" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:68" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -3383,24 +3560,26 @@
       <c r="E23" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F23" s="17" t="s">
+      <c r="F23" s="17"/>
+      <c r="G23" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="G23" s="17" t="s">
+      <c r="H23" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="J23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
+      <c r="L23" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M23" s="17"/>
       <c r="N23" s="17"/>
-      <c r="O23" s="23"/>
+      <c r="O23" s="17"/>
       <c r="P23" s="17"/>
-      <c r="Q23" s="17"/>
+      <c r="Q23" s="23"/>
       <c r="R23" s="17"/>
       <c r="S23" s="17"/>
       <c r="T23" s="17"/>
@@ -3419,44 +3598,46 @@
       <c r="AG23" s="17"/>
       <c r="AH23" s="17"/>
       <c r="AI23" s="17"/>
-      <c r="AJ23" s="18"/>
+      <c r="AJ23" s="17"/>
       <c r="AK23" s="17"/>
       <c r="AL23" s="18"/>
-      <c r="AM23" s="19"/>
-      <c r="AN23" s="21"/>
-      <c r="AO23" s="26" t="s">
+      <c r="AM23" s="17"/>
+      <c r="AN23" s="18"/>
+      <c r="AO23" s="19"/>
+      <c r="AP23" s="21"/>
+      <c r="AQ23" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="AP23" s="19"/>
-      <c r="AQ23" s="18"/>
-      <c r="AR23" s="17"/>
-      <c r="AS23" s="22"/>
+      <c r="AR23" s="19"/>
+      <c r="AS23" s="18"/>
       <c r="AT23" s="17"/>
-      <c r="AU23" s="17"/>
-      <c r="AV23" s="22"/>
-      <c r="AW23" s="18"/>
-      <c r="AX23" s="17"/>
-      <c r="AY23" s="26"/>
+      <c r="AU23" s="22"/>
+      <c r="AV23" s="17"/>
+      <c r="AW23" s="17"/>
+      <c r="AX23" s="22"/>
+      <c r="AY23" s="18"/>
       <c r="AZ23" s="17"/>
-      <c r="BA23" s="18"/>
+      <c r="BA23" s="26"/>
       <c r="BB23" s="17"/>
-      <c r="BC23" s="17"/>
+      <c r="BC23" s="18"/>
       <c r="BD23" s="17"/>
-      <c r="BE23" s="18"/>
-      <c r="BF23" s="18"/>
-      <c r="BG23" s="17"/>
-      <c r="BH23" s="17"/>
+      <c r="BE23" s="17"/>
+      <c r="BF23" s="17"/>
+      <c r="BG23" s="18"/>
+      <c r="BH23" s="18"/>
       <c r="BI23" s="17"/>
       <c r="BJ23" s="17"/>
       <c r="BK23" s="17"/>
-      <c r="BL23">
+      <c r="BL23" s="17"/>
+      <c r="BM23" s="17"/>
+      <c r="BN23">
         <v>19</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BP23" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:66" ht="18" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:68" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -3472,19 +3653,21 @@
       <c r="E24" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F24" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F24" s="17"/>
       <c r="G24" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="J24" s="17"/>
+      <c r="H24" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
+      <c r="L24" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M24" s="17"/>
       <c r="N24" s="17"/>
       <c r="O24" s="17"/>
@@ -3510,14 +3693,14 @@
       <c r="AI24" s="17"/>
       <c r="AJ24" s="17"/>
       <c r="AK24" s="17"/>
-      <c r="AL24" s="19"/>
-      <c r="AM24" s="19"/>
-      <c r="AN24" s="25"/>
-      <c r="AO24" s="26" t="s">
+      <c r="AL24" s="17"/>
+      <c r="AM24" s="17"/>
+      <c r="AN24" s="19"/>
+      <c r="AO24" s="19"/>
+      <c r="AP24" s="25"/>
+      <c r="AQ24" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="AP24" s="17"/>
-      <c r="AQ24" s="17"/>
       <c r="AR24" s="17"/>
       <c r="AS24" s="17"/>
       <c r="AT24" s="17"/>
@@ -3538,14 +3721,16 @@
       <c r="BI24" s="17"/>
       <c r="BJ24" s="17"/>
       <c r="BK24" s="17"/>
-      <c r="BL24">
+      <c r="BL24" s="17"/>
+      <c r="BM24" s="17"/>
+      <c r="BN24">
         <v>20</v>
       </c>
-      <c r="BN24" t="s">
+      <c r="BP24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:66" ht="18" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:68" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -3561,21 +3746,23 @@
       <c r="E25" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F25" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F25" s="17"/>
       <c r="G25" s="17" t="s">
         <v>126</v>
       </c>
       <c r="H25" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I25" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="I25" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="J25" s="17"/>
+      <c r="J25" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
+      <c r="L25" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M25" s="17"/>
       <c r="N25" s="17"/>
       <c r="O25" s="17"/>
@@ -3599,44 +3786,46 @@
       <c r="AG25" s="17"/>
       <c r="AH25" s="17"/>
       <c r="AI25" s="17"/>
-      <c r="AJ25" s="18"/>
+      <c r="AJ25" s="17"/>
       <c r="AK25" s="17"/>
-      <c r="AL25" s="19"/>
-      <c r="AM25" s="19"/>
-      <c r="AN25" s="21"/>
-      <c r="AO25" s="26" t="s">
+      <c r="AL25" s="18"/>
+      <c r="AM25" s="17"/>
+      <c r="AN25" s="19"/>
+      <c r="AO25" s="19"/>
+      <c r="AP25" s="21"/>
+      <c r="AQ25" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="AP25" s="19"/>
-      <c r="AQ25" s="21"/>
-      <c r="AR25" s="17"/>
-      <c r="AS25" s="19"/>
-      <c r="AT25" s="18"/>
-      <c r="AU25" s="17"/>
-      <c r="AV25" s="22"/>
-      <c r="AW25" s="18"/>
-      <c r="AX25" s="17"/>
-      <c r="AY25" s="22"/>
+      <c r="AR25" s="19"/>
+      <c r="AS25" s="21"/>
+      <c r="AT25" s="17"/>
+      <c r="AU25" s="19"/>
+      <c r="AV25" s="18"/>
+      <c r="AW25" s="17"/>
+      <c r="AX25" s="22"/>
+      <c r="AY25" s="18"/>
       <c r="AZ25" s="17"/>
-      <c r="BA25" s="18"/>
+      <c r="BA25" s="22"/>
       <c r="BB25" s="17"/>
-      <c r="BC25" s="17"/>
+      <c r="BC25" s="18"/>
       <c r="BD25" s="17"/>
-      <c r="BE25" s="18"/>
-      <c r="BF25" s="18"/>
-      <c r="BG25" s="17"/>
-      <c r="BH25" s="17"/>
+      <c r="BE25" s="17"/>
+      <c r="BF25" s="17"/>
+      <c r="BG25" s="18"/>
+      <c r="BH25" s="18"/>
       <c r="BI25" s="17"/>
       <c r="BJ25" s="17"/>
       <c r="BK25" s="17"/>
-      <c r="BL25">
+      <c r="BL25" s="17"/>
+      <c r="BM25" s="17"/>
+      <c r="BN25">
         <v>21</v>
       </c>
-      <c r="BN25" t="s">
+      <c r="BP25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:66" ht="18" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -3652,24 +3841,26 @@
       <c r="E26" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F26" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F26" s="17"/>
       <c r="G26" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H26" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="J26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29" t="s">
+        <v>126</v>
+      </c>
       <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
+      <c r="L26" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M26" s="29"/>
       <c r="N26" s="29"/>
-      <c r="O26" s="23"/>
+      <c r="O26" s="29"/>
       <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
+      <c r="Q26" s="23"/>
       <c r="R26" s="29"/>
       <c r="S26" s="29"/>
       <c r="T26" s="29"/>
@@ -3688,49 +3879,51 @@
       <c r="AG26" s="29"/>
       <c r="AH26" s="29"/>
       <c r="AI26" s="29"/>
-      <c r="AJ26" s="18"/>
+      <c r="AJ26" s="29"/>
       <c r="AK26" s="29"/>
-      <c r="AL26" s="19"/>
-      <c r="AM26" s="19"/>
-      <c r="AN26" s="21"/>
-      <c r="AO26" s="20" t="s">
+      <c r="AL26" s="18"/>
+      <c r="AM26" s="29"/>
+      <c r="AN26" s="19"/>
+      <c r="AO26" s="19"/>
+      <c r="AP26" s="21"/>
+      <c r="AQ26" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="AP26" s="34" t="s">
+      <c r="AR26" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="AQ26" s="18"/>
-      <c r="AR26" s="17"/>
-      <c r="AS26" s="22"/>
-      <c r="AT26" s="18"/>
-      <c r="AU26" s="17"/>
-      <c r="AV26" s="17"/>
-      <c r="AW26" s="29"/>
+      <c r="AS26" s="18"/>
+      <c r="AT26" s="17"/>
+      <c r="AU26" s="22"/>
+      <c r="AV26" s="18"/>
+      <c r="AW26" s="17"/>
       <c r="AX26" s="17"/>
-      <c r="AY26" s="17"/>
+      <c r="AY26" s="29"/>
       <c r="AZ26" s="17"/>
-      <c r="BA26" s="18"/>
+      <c r="BA26" s="17"/>
       <c r="BB26" s="17"/>
-      <c r="BC26" s="17"/>
+      <c r="BC26" s="18"/>
       <c r="BD26" s="17"/>
-      <c r="BE26" s="18"/>
-      <c r="BF26" s="18"/>
-      <c r="BG26" s="29"/>
-      <c r="BH26" s="29"/>
+      <c r="BE26" s="17"/>
+      <c r="BF26" s="17"/>
+      <c r="BG26" s="18"/>
+      <c r="BH26" s="18"/>
       <c r="BI26" s="29"/>
       <c r="BJ26" s="29"/>
       <c r="BK26" s="29"/>
-      <c r="BL26" s="14">
+      <c r="BL26" s="29"/>
+      <c r="BM26" s="29"/>
+      <c r="BN26" s="14">
         <v>22</v>
       </c>
-      <c r="BM26" s="15" t="s">
+      <c r="BO26" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="BN26" s="14" t="s">
+      <c r="BP26" s="14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:66" ht="18" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -3746,19 +3939,21 @@
       <c r="E27" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F27" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F27" s="17"/>
       <c r="G27" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H27" s="29"/>
-      <c r="I27" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="J27" s="30"/>
+      <c r="H27" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I27" s="29"/>
+      <c r="J27" s="30" t="s">
+        <v>126</v>
+      </c>
       <c r="K27" s="30"/>
-      <c r="L27" s="30"/>
+      <c r="L27" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M27" s="30"/>
       <c r="N27" s="30"/>
       <c r="O27" s="30"/>
@@ -3782,50 +3977,52 @@
       <c r="AG27" s="30"/>
       <c r="AH27" s="30"/>
       <c r="AI27" s="30"/>
-      <c r="AJ27" s="18"/>
+      <c r="AJ27" s="30"/>
       <c r="AK27" s="30"/>
-      <c r="AL27" s="19"/>
-      <c r="AM27" s="19"/>
-      <c r="AN27" s="18"/>
-      <c r="AO27" s="20" t="s">
+      <c r="AL27" s="18"/>
+      <c r="AM27" s="30"/>
+      <c r="AN27" s="19"/>
+      <c r="AO27" s="19"/>
+      <c r="AP27" s="18"/>
+      <c r="AQ27" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="AP27" s="34" t="s">
+      <c r="AR27" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="AQ27" s="18"/>
-      <c r="AR27" s="21" t="s">
+      <c r="AS27" s="18"/>
+      <c r="AT27" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="AS27" s="21" t="s">
+      <c r="AU27" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="AT27" s="17"/>
-      <c r="AU27" s="17"/>
       <c r="AV27" s="17"/>
-      <c r="AW27" s="18"/>
+      <c r="AW27" s="17"/>
       <c r="AX27" s="17"/>
-      <c r="AY27" s="17"/>
+      <c r="AY27" s="18"/>
       <c r="AZ27" s="17"/>
-      <c r="BA27" s="18"/>
+      <c r="BA27" s="17"/>
       <c r="BB27" s="17"/>
-      <c r="BC27" s="17"/>
+      <c r="BC27" s="18"/>
       <c r="BD27" s="17"/>
-      <c r="BE27" s="18"/>
-      <c r="BF27" s="18"/>
-      <c r="BG27" s="30"/>
-      <c r="BH27" s="30"/>
+      <c r="BE27" s="17"/>
+      <c r="BF27" s="17"/>
+      <c r="BG27" s="18"/>
+      <c r="BH27" s="18"/>
       <c r="BI27" s="30"/>
       <c r="BJ27" s="30"/>
       <c r="BK27" s="30"/>
-      <c r="BL27">
+      <c r="BL27" s="30"/>
+      <c r="BM27" s="30"/>
+      <c r="BN27">
         <v>23</v>
       </c>
-      <c r="BN27" t="s">
+      <c r="BP27" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:66" ht="18" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -3841,21 +4038,23 @@
       <c r="E28" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F28" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F28" s="17"/>
       <c r="G28" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H28" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="H28" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="I28" s="30" t="s">
+      <c r="I28" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="J28" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="J28" s="30"/>
       <c r="K28" s="30"/>
-      <c r="L28" s="30"/>
+      <c r="L28" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M28" s="30"/>
       <c r="N28" s="30"/>
       <c r="O28" s="30"/>
@@ -3879,40 +4078,42 @@
       <c r="AG28" s="30"/>
       <c r="AH28" s="30"/>
       <c r="AI28" s="30"/>
-      <c r="AJ28" s="18"/>
+      <c r="AJ28" s="30"/>
       <c r="AK28" s="30"/>
-      <c r="AL28" s="19"/>
-      <c r="AM28" s="19"/>
-      <c r="AN28" s="32"/>
-      <c r="AO28" s="27" t="s">
+      <c r="AL28" s="18"/>
+      <c r="AM28" s="30"/>
+      <c r="AN28" s="19"/>
+      <c r="AO28" s="19"/>
+      <c r="AP28" s="32"/>
+      <c r="AQ28" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="AP28" s="7" t="s">
+      <c r="AR28" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="AQ28" s="18"/>
-      <c r="AR28" s="17"/>
-      <c r="AS28" s="28"/>
+      <c r="AS28" s="18"/>
       <c r="AT28" s="17"/>
-      <c r="AU28" s="17"/>
+      <c r="AU28" s="28"/>
       <c r="AV28" s="17"/>
-      <c r="AW28" s="18"/>
+      <c r="AW28" s="17"/>
       <c r="AX28" s="17"/>
-      <c r="AY28" s="17"/>
+      <c r="AY28" s="18"/>
       <c r="AZ28" s="17"/>
-      <c r="BA28" s="18"/>
+      <c r="BA28" s="17"/>
       <c r="BB28" s="17"/>
-      <c r="BC28" s="17"/>
+      <c r="BC28" s="18"/>
       <c r="BD28" s="17"/>
-      <c r="BE28" s="18"/>
-      <c r="BF28" s="18"/>
-      <c r="BG28" s="30"/>
-      <c r="BH28" s="30"/>
+      <c r="BE28" s="17"/>
+      <c r="BF28" s="17"/>
+      <c r="BG28" s="18"/>
+      <c r="BH28" s="18"/>
       <c r="BI28" s="30"/>
       <c r="BJ28" s="30"/>
       <c r="BK28" s="30"/>
-    </row>
-    <row r="29" spans="1:66" ht="18" x14ac:dyDescent="0.35">
+      <c r="BL28" s="30"/>
+      <c r="BM28" s="30"/>
+    </row>
+    <row r="29" spans="1:68" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -3928,19 +4129,21 @@
       <c r="E29" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F29" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F29" s="17"/>
       <c r="G29" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H29" s="29"/>
-      <c r="I29" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="J29" s="30"/>
+      <c r="H29" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I29" s="29"/>
+      <c r="J29" s="30" t="s">
+        <v>126</v>
+      </c>
       <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
+      <c r="L29" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M29" s="30"/>
       <c r="N29" s="30"/>
       <c r="O29" s="30"/>
@@ -3964,38 +4167,40 @@
       <c r="AG29" s="30"/>
       <c r="AH29" s="30"/>
       <c r="AI29" s="30"/>
-      <c r="AJ29" s="18"/>
+      <c r="AJ29" s="30"/>
       <c r="AK29" s="30"/>
-      <c r="AL29" s="19"/>
-      <c r="AM29" s="19"/>
-      <c r="AN29" s="32"/>
-      <c r="AO29" s="26" t="s">
+      <c r="AL29" s="18"/>
+      <c r="AM29" s="30"/>
+      <c r="AN29" s="19"/>
+      <c r="AO29" s="19"/>
+      <c r="AP29" s="32"/>
+      <c r="AQ29" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="AP29" s="19"/>
-      <c r="AQ29" s="18"/>
-      <c r="AR29" s="17"/>
-      <c r="AS29" s="28"/>
+      <c r="AR29" s="19"/>
+      <c r="AS29" s="18"/>
       <c r="AT29" s="17"/>
-      <c r="AU29" s="17"/>
+      <c r="AU29" s="28"/>
       <c r="AV29" s="17"/>
-      <c r="AW29" s="18"/>
+      <c r="AW29" s="17"/>
       <c r="AX29" s="17"/>
-      <c r="AY29" s="17"/>
+      <c r="AY29" s="18"/>
       <c r="AZ29" s="17"/>
-      <c r="BA29" s="18"/>
+      <c r="BA29" s="17"/>
       <c r="BB29" s="17"/>
-      <c r="BC29" s="17"/>
+      <c r="BC29" s="18"/>
       <c r="BD29" s="17"/>
-      <c r="BE29" s="18"/>
-      <c r="BF29" s="18"/>
-      <c r="BG29" s="30"/>
-      <c r="BH29" s="30"/>
+      <c r="BE29" s="17"/>
+      <c r="BF29" s="17"/>
+      <c r="BG29" s="18"/>
+      <c r="BH29" s="18"/>
       <c r="BI29" s="30"/>
       <c r="BJ29" s="30"/>
       <c r="BK29" s="30"/>
-    </row>
-    <row r="30" spans="1:66" ht="18" x14ac:dyDescent="0.35">
+      <c r="BL29" s="30"/>
+      <c r="BM29" s="30"/>
+    </row>
+    <row r="30" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -4011,19 +4216,21 @@
       <c r="E30" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F30" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F30" s="17"/>
       <c r="G30" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H30" s="29"/>
-      <c r="I30" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="J30" s="30"/>
+      <c r="H30" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I30" s="29"/>
+      <c r="J30" s="30" t="s">
+        <v>126</v>
+      </c>
       <c r="K30" s="30"/>
-      <c r="L30" s="30"/>
+      <c r="L30" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M30" s="30"/>
       <c r="N30" s="30"/>
       <c r="O30" s="30"/>
@@ -4047,40 +4254,42 @@
       <c r="AG30" s="30"/>
       <c r="AH30" s="30"/>
       <c r="AI30" s="30"/>
-      <c r="AJ30" s="18"/>
+      <c r="AJ30" s="30"/>
       <c r="AK30" s="30"/>
-      <c r="AL30" s="19"/>
-      <c r="AM30" s="19"/>
-      <c r="AN30" s="32"/>
-      <c r="AO30" s="35" t="s">
+      <c r="AL30" s="18"/>
+      <c r="AM30" s="30"/>
+      <c r="AN30" s="19"/>
+      <c r="AO30" s="19"/>
+      <c r="AP30" s="32"/>
+      <c r="AQ30" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="AP30" s="34" t="s">
+      <c r="AR30" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="AQ30" s="18"/>
-      <c r="AR30" s="17"/>
-      <c r="AS30" s="28"/>
+      <c r="AS30" s="18"/>
       <c r="AT30" s="17"/>
-      <c r="AU30" s="17"/>
+      <c r="AU30" s="28"/>
       <c r="AV30" s="17"/>
-      <c r="AW30" s="18"/>
+      <c r="AW30" s="17"/>
       <c r="AX30" s="17"/>
-      <c r="AY30" s="17"/>
+      <c r="AY30" s="18"/>
       <c r="AZ30" s="17"/>
-      <c r="BA30" s="18"/>
+      <c r="BA30" s="17"/>
       <c r="BB30" s="17"/>
-      <c r="BC30" s="17"/>
+      <c r="BC30" s="18"/>
       <c r="BD30" s="17"/>
-      <c r="BE30" s="18"/>
-      <c r="BF30" s="18"/>
-      <c r="BG30" s="30"/>
-      <c r="BH30" s="30"/>
+      <c r="BE30" s="17"/>
+      <c r="BF30" s="17"/>
+      <c r="BG30" s="18"/>
+      <c r="BH30" s="18"/>
       <c r="BI30" s="30"/>
       <c r="BJ30" s="30"/>
       <c r="BK30" s="30"/>
-    </row>
-    <row r="31" spans="1:66" ht="18" x14ac:dyDescent="0.35">
+      <c r="BL30" s="30"/>
+      <c r="BM30" s="30"/>
+    </row>
+    <row r="31" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -4096,19 +4305,21 @@
       <c r="E31" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F31" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F31" s="17"/>
       <c r="G31" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H31" s="29"/>
-      <c r="I31" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="J31" s="30"/>
+      <c r="H31" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I31" s="29"/>
+      <c r="J31" s="30" t="s">
+        <v>126</v>
+      </c>
       <c r="K31" s="30"/>
-      <c r="L31" s="30"/>
+      <c r="L31" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M31" s="30"/>
       <c r="N31" s="30"/>
       <c r="O31" s="30"/>
@@ -4132,40 +4343,42 @@
       <c r="AG31" s="30"/>
       <c r="AH31" s="30"/>
       <c r="AI31" s="30"/>
-      <c r="AJ31" s="18"/>
+      <c r="AJ31" s="30"/>
       <c r="AK31" s="30"/>
-      <c r="AL31" s="19"/>
-      <c r="AM31" s="19"/>
-      <c r="AN31" s="32"/>
-      <c r="AO31" s="20" t="s">
+      <c r="AL31" s="18"/>
+      <c r="AM31" s="30"/>
+      <c r="AN31" s="19"/>
+      <c r="AO31" s="19"/>
+      <c r="AP31" s="32"/>
+      <c r="AQ31" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="AP31" s="19" t="s">
+      <c r="AR31" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="AQ31" s="18"/>
-      <c r="AR31" s="17"/>
-      <c r="AS31" s="28"/>
+      <c r="AS31" s="18"/>
       <c r="AT31" s="17"/>
-      <c r="AU31" s="17"/>
+      <c r="AU31" s="28"/>
       <c r="AV31" s="17"/>
-      <c r="AW31" s="18"/>
+      <c r="AW31" s="17"/>
       <c r="AX31" s="17"/>
-      <c r="AY31" s="17"/>
+      <c r="AY31" s="18"/>
       <c r="AZ31" s="17"/>
-      <c r="BA31" s="18"/>
+      <c r="BA31" s="17"/>
       <c r="BB31" s="17"/>
-      <c r="BC31" s="17"/>
+      <c r="BC31" s="18"/>
       <c r="BD31" s="17"/>
-      <c r="BE31" s="18"/>
-      <c r="BF31" s="18"/>
-      <c r="BG31" s="30"/>
-      <c r="BH31" s="30"/>
+      <c r="BE31" s="17"/>
+      <c r="BF31" s="17"/>
+      <c r="BG31" s="18"/>
+      <c r="BH31" s="18"/>
       <c r="BI31" s="30"/>
       <c r="BJ31" s="30"/>
       <c r="BK31" s="30"/>
-    </row>
-    <row r="32" spans="1:66" ht="18" x14ac:dyDescent="0.35">
+      <c r="BL31" s="30"/>
+      <c r="BM31" s="30"/>
+    </row>
+    <row r="32" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -4181,19 +4394,21 @@
       <c r="E32" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F32" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F32" s="17"/>
       <c r="G32" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H32" s="29"/>
-      <c r="I32" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="J32" s="30"/>
+      <c r="H32" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I32" s="29"/>
+      <c r="J32" s="30" t="s">
+        <v>126</v>
+      </c>
       <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
+      <c r="L32" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M32" s="30"/>
       <c r="N32" s="30"/>
       <c r="O32" s="30"/>
@@ -4217,44 +4432,46 @@
       <c r="AG32" s="30"/>
       <c r="AH32" s="30"/>
       <c r="AI32" s="30"/>
-      <c r="AJ32" s="18"/>
+      <c r="AJ32" s="30"/>
       <c r="AK32" s="30"/>
-      <c r="AL32" s="19"/>
-      <c r="AM32" s="19"/>
-      <c r="AN32" s="32"/>
-      <c r="AO32" s="33" t="s">
+      <c r="AL32" s="18"/>
+      <c r="AM32" s="30"/>
+      <c r="AN32" s="19"/>
+      <c r="AO32" s="19"/>
+      <c r="AP32" s="32"/>
+      <c r="AQ32" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="AP32" s="34" t="s">
+      <c r="AR32" s="34" t="s">
         <v>142</v>
       </c>
-      <c r="AQ32" s="18"/>
-      <c r="AR32" s="17" t="s">
+      <c r="AS32" s="18"/>
+      <c r="AT32" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="AS32" s="28" t="s">
+      <c r="AU32" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="AT32" s="17"/>
-      <c r="AU32" s="17"/>
       <c r="AV32" s="17"/>
-      <c r="AW32" s="18"/>
+      <c r="AW32" s="17"/>
       <c r="AX32" s="17"/>
-      <c r="AY32" s="17"/>
+      <c r="AY32" s="18"/>
       <c r="AZ32" s="17"/>
-      <c r="BA32" s="18"/>
+      <c r="BA32" s="17"/>
       <c r="BB32" s="17"/>
-      <c r="BC32" s="17"/>
+      <c r="BC32" s="18"/>
       <c r="BD32" s="17"/>
-      <c r="BE32" s="18"/>
-      <c r="BF32" s="18"/>
-      <c r="BG32" s="30"/>
-      <c r="BH32" s="30"/>
+      <c r="BE32" s="17"/>
+      <c r="BF32" s="17"/>
+      <c r="BG32" s="18"/>
+      <c r="BH32" s="18"/>
       <c r="BI32" s="30"/>
       <c r="BJ32" s="30"/>
       <c r="BK32" s="30"/>
-    </row>
-    <row r="33" spans="1:66" ht="18" x14ac:dyDescent="0.35">
+      <c r="BL32" s="30"/>
+      <c r="BM32" s="30"/>
+    </row>
+    <row r="33" spans="1:68" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -4270,19 +4487,21 @@
       <c r="E33" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="F33" s="17" t="s">
+      <c r="F33" s="17"/>
+      <c r="G33" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="G33" s="17" t="s">
+      <c r="H33" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="H33" s="29"/>
-      <c r="I33" s="30" t="s">
+      <c r="I33" s="29"/>
+      <c r="J33" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="J33" s="30"/>
       <c r="K33" s="30"/>
-      <c r="L33" s="30"/>
+      <c r="L33" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M33" s="30"/>
       <c r="N33" s="30"/>
       <c r="O33" s="30"/>
@@ -4306,38 +4525,40 @@
       <c r="AG33" s="30"/>
       <c r="AH33" s="30"/>
       <c r="AI33" s="30"/>
-      <c r="AJ33" s="18"/>
+      <c r="AJ33" s="30"/>
       <c r="AK33" s="30"/>
-      <c r="AL33" s="19"/>
-      <c r="AM33" s="19"/>
-      <c r="AN33" s="32"/>
-      <c r="AO33" s="26" t="s">
+      <c r="AL33" s="18"/>
+      <c r="AM33" s="30"/>
+      <c r="AN33" s="19"/>
+      <c r="AO33" s="19"/>
+      <c r="AP33" s="32"/>
+      <c r="AQ33" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="AP33" s="19"/>
-      <c r="AQ33" s="18"/>
-      <c r="AR33" s="17"/>
-      <c r="AS33" s="28"/>
+      <c r="AR33" s="19"/>
+      <c r="AS33" s="18"/>
       <c r="AT33" s="17"/>
-      <c r="AU33" s="17"/>
+      <c r="AU33" s="28"/>
       <c r="AV33" s="17"/>
-      <c r="AW33" s="18"/>
+      <c r="AW33" s="17"/>
       <c r="AX33" s="17"/>
-      <c r="AY33" s="17"/>
+      <c r="AY33" s="18"/>
       <c r="AZ33" s="17"/>
-      <c r="BA33" s="18"/>
+      <c r="BA33" s="17"/>
       <c r="BB33" s="17"/>
-      <c r="BC33" s="17"/>
+      <c r="BC33" s="18"/>
       <c r="BD33" s="17"/>
-      <c r="BE33" s="18"/>
-      <c r="BF33" s="18"/>
-      <c r="BG33" s="30"/>
-      <c r="BH33" s="30"/>
+      <c r="BE33" s="17"/>
+      <c r="BF33" s="17"/>
+      <c r="BG33" s="18"/>
+      <c r="BH33" s="18"/>
       <c r="BI33" s="30"/>
       <c r="BJ33" s="30"/>
       <c r="BK33" s="30"/>
-    </row>
-    <row r="34" spans="1:66" ht="18" x14ac:dyDescent="0.35">
+      <c r="BL33" s="30"/>
+      <c r="BM33" s="30"/>
+    </row>
+    <row r="34" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -4353,19 +4574,21 @@
       <c r="E34" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F34" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F34" s="17"/>
       <c r="G34" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H34" s="29"/>
-      <c r="I34" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="J34" s="30"/>
+      <c r="H34" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I34" s="29"/>
+      <c r="J34" s="30" t="s">
+        <v>126</v>
+      </c>
       <c r="K34" s="30"/>
-      <c r="L34" s="30"/>
+      <c r="L34" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M34" s="30"/>
       <c r="N34" s="30"/>
       <c r="O34" s="30"/>
@@ -4389,40 +4612,42 @@
       <c r="AG34" s="30"/>
       <c r="AH34" s="30"/>
       <c r="AI34" s="30"/>
-      <c r="AJ34" s="18"/>
+      <c r="AJ34" s="30"/>
       <c r="AK34" s="30"/>
-      <c r="AL34" s="19"/>
-      <c r="AM34" s="19"/>
-      <c r="AN34" s="32"/>
-      <c r="AO34" s="20" t="s">
+      <c r="AL34" s="18"/>
+      <c r="AM34" s="30"/>
+      <c r="AN34" s="19"/>
+      <c r="AO34" s="19"/>
+      <c r="AP34" s="32"/>
+      <c r="AQ34" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="AP34" s="19" t="s">
+      <c r="AR34" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="AQ34" s="18"/>
-      <c r="AR34" s="17"/>
-      <c r="AS34" s="28"/>
+      <c r="AS34" s="18"/>
       <c r="AT34" s="17"/>
-      <c r="AU34" s="17"/>
+      <c r="AU34" s="28"/>
       <c r="AV34" s="17"/>
-      <c r="AW34" s="18"/>
+      <c r="AW34" s="17"/>
       <c r="AX34" s="17"/>
-      <c r="AY34" s="17"/>
+      <c r="AY34" s="18"/>
       <c r="AZ34" s="17"/>
-      <c r="BA34" s="18"/>
+      <c r="BA34" s="17"/>
       <c r="BB34" s="17"/>
-      <c r="BC34" s="17"/>
+      <c r="BC34" s="18"/>
       <c r="BD34" s="17"/>
-      <c r="BE34" s="18"/>
-      <c r="BF34" s="18"/>
-      <c r="BG34" s="30"/>
-      <c r="BH34" s="30"/>
+      <c r="BE34" s="17"/>
+      <c r="BF34" s="17"/>
+      <c r="BG34" s="18"/>
+      <c r="BH34" s="18"/>
       <c r="BI34" s="30"/>
       <c r="BJ34" s="30"/>
       <c r="BK34" s="30"/>
-    </row>
-    <row r="35" spans="1:66" ht="18" x14ac:dyDescent="0.35">
+      <c r="BL34" s="30"/>
+      <c r="BM34" s="30"/>
+    </row>
+    <row r="35" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -4438,19 +4663,21 @@
       <c r="E35" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F35" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F35" s="17"/>
       <c r="G35" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H35" s="29"/>
-      <c r="I35" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="J35" s="30"/>
+      <c r="H35" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I35" s="29"/>
+      <c r="J35" s="30" t="s">
+        <v>126</v>
+      </c>
       <c r="K35" s="30"/>
-      <c r="L35" s="30"/>
+      <c r="L35" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="M35" s="30"/>
       <c r="N35" s="30"/>
       <c r="O35" s="30"/>
@@ -4474,40 +4701,42 @@
       <c r="AG35" s="30"/>
       <c r="AH35" s="30"/>
       <c r="AI35" s="30"/>
-      <c r="AJ35" s="18"/>
+      <c r="AJ35" s="30"/>
       <c r="AK35" s="30"/>
-      <c r="AL35" s="19"/>
-      <c r="AM35" s="19"/>
-      <c r="AN35" s="32"/>
-      <c r="AO35" s="36" t="s">
+      <c r="AL35" s="18"/>
+      <c r="AM35" s="30"/>
+      <c r="AN35" s="19"/>
+      <c r="AO35" s="19"/>
+      <c r="AP35" s="32"/>
+      <c r="AQ35" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="AP35" s="34" t="s">
+      <c r="AR35" s="34" t="s">
         <v>160</v>
       </c>
-      <c r="AQ35" s="18"/>
-      <c r="AR35" s="17"/>
-      <c r="AS35" s="28"/>
+      <c r="AS35" s="18"/>
       <c r="AT35" s="17"/>
-      <c r="AU35" s="17"/>
+      <c r="AU35" s="28"/>
       <c r="AV35" s="17"/>
-      <c r="AW35" s="18"/>
+      <c r="AW35" s="17"/>
       <c r="AX35" s="17"/>
-      <c r="AY35" s="17"/>
+      <c r="AY35" s="18"/>
       <c r="AZ35" s="17"/>
-      <c r="BA35" s="18"/>
+      <c r="BA35" s="17"/>
       <c r="BB35" s="17"/>
-      <c r="BC35" s="17"/>
+      <c r="BC35" s="18"/>
       <c r="BD35" s="17"/>
-      <c r="BE35" s="18"/>
-      <c r="BF35" s="18"/>
-      <c r="BG35" s="30"/>
-      <c r="BH35" s="30"/>
+      <c r="BE35" s="17"/>
+      <c r="BF35" s="17"/>
+      <c r="BG35" s="18"/>
+      <c r="BH35" s="18"/>
       <c r="BI35" s="30"/>
       <c r="BJ35" s="30"/>
       <c r="BK35" s="30"/>
-    </row>
-    <row r="36" spans="1:66" ht="18" x14ac:dyDescent="0.35">
+      <c r="BL35" s="30"/>
+      <c r="BM35" s="30"/>
+    </row>
+    <row r="36" spans="1:68" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -4523,25 +4752,27 @@
       <c r="E36" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F36" s="17" t="s">
-        <v>126</v>
-      </c>
+      <c r="F36" s="17"/>
       <c r="G36" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="H36" s="29"/>
-      <c r="I36" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="J36" s="30"/>
+      <c r="H36" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="I36" s="29"/>
+      <c r="J36" s="30" t="s">
+        <v>126</v>
+      </c>
       <c r="K36" s="30"/>
-      <c r="L36" s="30"/>
+      <c r="L36" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M36" s="30"/>
       <c r="N36" s="30"/>
       <c r="O36" s="30"/>
-      <c r="P36" s="17"/>
+      <c r="P36" s="30"/>
       <c r="Q36" s="30"/>
-      <c r="R36" s="30"/>
+      <c r="R36" s="17"/>
       <c r="S36" s="30"/>
       <c r="T36" s="30"/>
       <c r="U36" s="30"/>
@@ -4561,36 +4792,38 @@
       <c r="AI36" s="30"/>
       <c r="AJ36" s="30"/>
       <c r="AK36" s="30"/>
-      <c r="AL36" s="19"/>
-      <c r="AM36" s="19"/>
-      <c r="AN36" s="25"/>
-      <c r="AO36" s="26" t="s">
+      <c r="AL36" s="30"/>
+      <c r="AM36" s="30"/>
+      <c r="AN36" s="19"/>
+      <c r="AO36" s="19"/>
+      <c r="AP36" s="25"/>
+      <c r="AQ36" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="AP36" s="19"/>
-      <c r="AQ36" s="17"/>
-      <c r="AR36" s="17"/>
+      <c r="AR36" s="19"/>
       <c r="AS36" s="17"/>
       <c r="AT36" s="17"/>
       <c r="AU36" s="17"/>
       <c r="AV36" s="17"/>
       <c r="AW36" s="17"/>
       <c r="AX36" s="17"/>
-      <c r="AY36" s="30"/>
-      <c r="AZ36" s="30"/>
+      <c r="AY36" s="17"/>
+      <c r="AZ36" s="17"/>
       <c r="BA36" s="30"/>
-      <c r="BB36" s="17"/>
-      <c r="BC36" s="17"/>
+      <c r="BB36" s="30"/>
+      <c r="BC36" s="30"/>
       <c r="BD36" s="17"/>
-      <c r="BE36" s="30"/>
-      <c r="BF36" s="30"/>
+      <c r="BE36" s="17"/>
+      <c r="BF36" s="17"/>
       <c r="BG36" s="30"/>
       <c r="BH36" s="30"/>
       <c r="BI36" s="30"/>
       <c r="BJ36" s="30"/>
       <c r="BK36" s="30"/>
-    </row>
-    <row r="37" spans="1:66" ht="18" x14ac:dyDescent="0.35">
+      <c r="BL36" s="30"/>
+      <c r="BM36" s="30"/>
+    </row>
+    <row r="37" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -4606,27 +4839,29 @@
       <c r="E37" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="F37" s="17" t="s">
-        <v>127</v>
-      </c>
+      <c r="F37" s="17"/>
       <c r="G37" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="H37" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="I37" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="J37" s="30"/>
+      <c r="H37" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="I37" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="J37" s="30" t="s">
+        <v>126</v>
+      </c>
       <c r="K37" s="30"/>
-      <c r="L37" s="30"/>
+      <c r="L37" s="30" t="s">
+        <v>127</v>
+      </c>
       <c r="M37" s="30"/>
       <c r="N37" s="30"/>
       <c r="O37" s="30"/>
-      <c r="P37" s="17"/>
+      <c r="P37" s="30"/>
       <c r="Q37" s="30"/>
-      <c r="R37" s="30"/>
+      <c r="R37" s="17"/>
       <c r="S37" s="30"/>
       <c r="T37" s="30"/>
       <c r="U37" s="30"/>
@@ -4646,82 +4881,84 @@
       <c r="AI37" s="30"/>
       <c r="AJ37" s="30"/>
       <c r="AK37" s="30"/>
-      <c r="AL37" s="19"/>
-      <c r="AM37" s="19"/>
-      <c r="AN37" s="25"/>
-      <c r="AO37" s="33" t="s">
+      <c r="AL37" s="30"/>
+      <c r="AM37" s="30"/>
+      <c r="AN37" s="19"/>
+      <c r="AO37" s="19"/>
+      <c r="AP37" s="25"/>
+      <c r="AQ37" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="AP37" s="34" t="s">
+      <c r="AR37" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="AQ37" s="17"/>
-      <c r="AR37" s="17"/>
       <c r="AS37" s="17"/>
       <c r="AT37" s="17"/>
       <c r="AU37" s="17"/>
       <c r="AV37" s="17"/>
       <c r="AW37" s="17"/>
       <c r="AX37" s="17"/>
-      <c r="AY37" s="30"/>
-      <c r="AZ37" s="30"/>
+      <c r="AY37" s="17"/>
+      <c r="AZ37" s="17"/>
       <c r="BA37" s="30"/>
-      <c r="BB37" s="17"/>
-      <c r="BC37" s="17"/>
+      <c r="BB37" s="30"/>
+      <c r="BC37" s="30"/>
       <c r="BD37" s="17"/>
-      <c r="BE37" s="30"/>
-      <c r="BF37" s="30"/>
+      <c r="BE37" s="17"/>
+      <c r="BF37" s="17"/>
       <c r="BG37" s="30"/>
       <c r="BH37" s="30"/>
       <c r="BI37" s="30"/>
       <c r="BJ37" s="30"/>
       <c r="BK37" s="30"/>
-    </row>
-    <row r="38" spans="1:66" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A38" s="51" t="s">
+      <c r="BL37" s="30"/>
+      <c r="BM37" s="30"/>
+    </row>
+    <row r="38" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A38" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="B38" s="52"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="52"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="52"/>
-      <c r="K38" s="52"/>
-      <c r="L38" s="52"/>
-      <c r="M38" s="52"/>
-      <c r="N38" s="52"/>
-      <c r="O38" s="52"/>
-      <c r="P38" s="52"/>
-      <c r="Q38" s="52"/>
-      <c r="R38" s="52"/>
-      <c r="S38" s="52"/>
-      <c r="T38" s="52"/>
-      <c r="U38" s="52"/>
-      <c r="V38" s="52"/>
-      <c r="W38" s="52"/>
-      <c r="X38" s="52"/>
-      <c r="Y38" s="52"/>
-      <c r="Z38" s="52"/>
-      <c r="AA38" s="52"/>
-      <c r="AB38" s="52"/>
-      <c r="AC38" s="52"/>
-      <c r="AD38" s="52"/>
-      <c r="AE38" s="52"/>
-      <c r="AF38" s="52"/>
-      <c r="AG38" s="52"/>
-      <c r="AH38" s="52"/>
-      <c r="AI38" s="52"/>
-      <c r="AJ38" s="52"/>
-      <c r="AK38" s="52"/>
-      <c r="AL38" s="52"/>
-      <c r="AM38" s="52"/>
-      <c r="AN38" s="53"/>
-      <c r="AO38" s="2"/>
-      <c r="AP38" s="2"/>
+      <c r="B38" s="49"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="49"/>
+      <c r="E38" s="49"/>
+      <c r="F38" s="49"/>
+      <c r="G38" s="49"/>
+      <c r="H38" s="49"/>
+      <c r="I38" s="49"/>
+      <c r="J38" s="49"/>
+      <c r="K38" s="49"/>
+      <c r="L38" s="49"/>
+      <c r="M38" s="49"/>
+      <c r="N38" s="49"/>
+      <c r="O38" s="49"/>
+      <c r="P38" s="49"/>
+      <c r="Q38" s="49"/>
+      <c r="R38" s="49"/>
+      <c r="S38" s="49"/>
+      <c r="T38" s="49"/>
+      <c r="U38" s="49"/>
+      <c r="V38" s="49"/>
+      <c r="W38" s="49"/>
+      <c r="X38" s="49"/>
+      <c r="Y38" s="49"/>
+      <c r="Z38" s="49"/>
+      <c r="AA38" s="49"/>
+      <c r="AB38" s="49"/>
+      <c r="AC38" s="49"/>
+      <c r="AD38" s="49"/>
+      <c r="AE38" s="49"/>
+      <c r="AF38" s="49"/>
+      <c r="AG38" s="49"/>
+      <c r="AH38" s="49"/>
+      <c r="AI38" s="49"/>
+      <c r="AJ38" s="49"/>
+      <c r="AK38" s="49"/>
+      <c r="AL38" s="49"/>
+      <c r="AM38" s="49"/>
+      <c r="AN38" s="49"/>
+      <c r="AO38" s="49"/>
+      <c r="AP38" s="50"/>
       <c r="AQ38" s="2"/>
       <c r="AR38" s="2"/>
       <c r="AS38" s="2"/>
@@ -4743,58 +4980,60 @@
       <c r="BI38" s="2"/>
       <c r="BJ38" s="2"/>
       <c r="BK38" s="2"/>
-      <c r="BL38">
+      <c r="BL38" s="2"/>
+      <c r="BM38" s="2"/>
+      <c r="BN38">
         <v>24</v>
       </c>
-      <c r="BN38" t="s">
+      <c r="BP38" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:66" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A39" s="54" t="s">
+    <row r="39" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A39" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="B39" s="55"/>
-      <c r="C39" s="55"/>
-      <c r="D39" s="55"/>
-      <c r="E39" s="55"/>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55"/>
-      <c r="H39" s="55"/>
-      <c r="I39" s="55"/>
-      <c r="J39" s="55"/>
-      <c r="K39" s="55"/>
-      <c r="L39" s="55"/>
-      <c r="M39" s="55"/>
-      <c r="N39" s="55"/>
-      <c r="O39" s="55"/>
-      <c r="P39" s="55"/>
-      <c r="Q39" s="55"/>
-      <c r="R39" s="55"/>
-      <c r="S39" s="55"/>
-      <c r="T39" s="55"/>
-      <c r="U39" s="55"/>
-      <c r="V39" s="55"/>
-      <c r="W39" s="55"/>
-      <c r="X39" s="55"/>
-      <c r="Y39" s="55"/>
-      <c r="Z39" s="55"/>
-      <c r="AA39" s="55"/>
-      <c r="AB39" s="55"/>
-      <c r="AC39" s="55"/>
-      <c r="AD39" s="55"/>
-      <c r="AE39" s="55"/>
-      <c r="AF39" s="55"/>
-      <c r="AG39" s="55"/>
-      <c r="AH39" s="55"/>
-      <c r="AI39" s="55"/>
-      <c r="AJ39" s="55"/>
-      <c r="AK39" s="55"/>
-      <c r="AL39" s="55"/>
-      <c r="AM39" s="55"/>
-      <c r="AN39" s="56"/>
-      <c r="AO39" s="2"/>
-      <c r="AP39" s="2"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
+      <c r="G39" s="52"/>
+      <c r="H39" s="52"/>
+      <c r="I39" s="52"/>
+      <c r="J39" s="52"/>
+      <c r="K39" s="52"/>
+      <c r="L39" s="52"/>
+      <c r="M39" s="52"/>
+      <c r="N39" s="52"/>
+      <c r="O39" s="52"/>
+      <c r="P39" s="52"/>
+      <c r="Q39" s="52"/>
+      <c r="R39" s="52"/>
+      <c r="S39" s="52"/>
+      <c r="T39" s="52"/>
+      <c r="U39" s="52"/>
+      <c r="V39" s="52"/>
+      <c r="W39" s="52"/>
+      <c r="X39" s="52"/>
+      <c r="Y39" s="52"/>
+      <c r="Z39" s="52"/>
+      <c r="AA39" s="52"/>
+      <c r="AB39" s="52"/>
+      <c r="AC39" s="52"/>
+      <c r="AD39" s="52"/>
+      <c r="AE39" s="52"/>
+      <c r="AF39" s="52"/>
+      <c r="AG39" s="52"/>
+      <c r="AH39" s="52"/>
+      <c r="AI39" s="52"/>
+      <c r="AJ39" s="52"/>
+      <c r="AK39" s="52"/>
+      <c r="AL39" s="52"/>
+      <c r="AM39" s="52"/>
+      <c r="AN39" s="52"/>
+      <c r="AO39" s="52"/>
+      <c r="AP39" s="53"/>
       <c r="AQ39" s="2"/>
       <c r="AR39" s="2"/>
       <c r="AS39" s="2"/>
@@ -4816,14 +5055,16 @@
       <c r="BI39" s="2"/>
       <c r="BJ39" s="2"/>
       <c r="BK39" s="2"/>
-      <c r="BL39">
+      <c r="BL39" s="2"/>
+      <c r="BM39" s="2"/>
+      <c r="BN39">
         <v>25</v>
       </c>
-      <c r="BN39" t="s">
+      <c r="BP39" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:66" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:68" x14ac:dyDescent="0.25">
       <c r="D40">
         <v>1</v>
       </c>
@@ -4920,14 +5161,20 @@
       <c r="AI40">
         <v>32</v>
       </c>
-      <c r="BL40">
+      <c r="AJ40">
+        <v>33</v>
+      </c>
+      <c r="AK40">
+        <v>34</v>
+      </c>
+      <c r="BN40">
         <v>26</v>
       </c>
-      <c r="BN40" t="s">
+      <c r="BP40" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" t="s">
         <v>131</v>
       </c>
@@ -4938,19 +5185,19 @@
         <v>131</v>
       </c>
       <c r="G41" t="s">
+        <v>131</v>
+      </c>
+      <c r="H41" t="s">
         <v>132</v>
       </c>
-      <c r="H41" t="s">
+      <c r="I41" t="s">
         <v>131</v>
       </c>
-      <c r="I41" t="s">
+      <c r="J41" t="s">
         <v>132</v>
       </c>
-      <c r="J41" t="s">
+      <c r="K41" t="s">
         <v>131</v>
-      </c>
-      <c r="K41" t="s">
-        <v>132</v>
       </c>
       <c r="L41" t="s">
         <v>131</v>
@@ -4976,376 +5223,391 @@
       <c r="S41" t="s">
         <v>132</v>
       </c>
-      <c r="AV41"/>
-      <c r="BL41">
+      <c r="T41" t="s">
+        <v>131</v>
+      </c>
+      <c r="U41" t="s">
+        <v>132</v>
+      </c>
+      <c r="AX41"/>
+      <c r="BN41">
         <v>27</v>
       </c>
-      <c r="BN41" t="s">
+      <c r="BP41" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="I42" t="s">
+      <c r="J42" t="s">
         <v>152</v>
       </c>
       <c r="K42" t="s">
+        <v>184</v>
+      </c>
+      <c r="L42" t="s">
+        <v>183</v>
+      </c>
+      <c r="M42" t="s">
         <v>67</v>
       </c>
-      <c r="M42" t="s">
+      <c r="O42" t="s">
         <v>68</v>
       </c>
-      <c r="N42" t="s">
+      <c r="P42" t="s">
         <v>68</v>
       </c>
-      <c r="O42" t="s">
+      <c r="Q42" t="s">
         <v>69</v>
       </c>
-      <c r="AX42" t="s">
+      <c r="AZ42" t="s">
         <v>72</v>
       </c>
-      <c r="BL42">
+      <c r="BN42">
         <v>28</v>
       </c>
-      <c r="BN42" t="s">
+      <c r="BP42" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E43" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="G43" s="16" t="s">
+      <c r="F43" s="16"/>
+      <c r="H43" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="H43" s="16" t="s">
+      <c r="I43" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="J43" t="s">
+      <c r="L43" t="s">
         <v>73</v>
       </c>
-      <c r="L43" t="s">
+      <c r="N43" t="s">
         <v>74</v>
       </c>
-      <c r="P43" t="s">
+      <c r="R43" t="s">
         <v>75</v>
       </c>
-      <c r="AX43" t="s">
+      <c r="AZ43" t="s">
         <v>76</v>
       </c>
-      <c r="BL43" s="14">
+      <c r="BN43" s="14">
         <v>29</v>
       </c>
-      <c r="BM43" s="14"/>
-      <c r="BN43" s="14" t="s">
+      <c r="BO43" s="14"/>
+      <c r="BP43" s="14" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" t="s">
         <v>77</v>
       </c>
-      <c r="F44" s="16" t="s">
+      <c r="G44" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="L44" t="s">
+      <c r="N44" t="s">
         <v>78</v>
       </c>
-      <c r="Q44" t="s">
+      <c r="S44" t="s">
         <v>79</v>
       </c>
-      <c r="AL44" t="s">
+      <c r="AN44" t="s">
         <v>62</v>
       </c>
-      <c r="AM44" s="5" t="s">
+      <c r="AO44" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="BL44">
+      <c r="BN44">
         <v>30</v>
       </c>
-      <c r="BN44" t="s">
+      <c r="BP44" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" t="s">
         <v>80</v>
       </c>
-      <c r="R45" t="s">
+      <c r="T45" t="s">
         <v>81</v>
       </c>
-      <c r="AL45" t="s">
+      <c r="AN45" t="s">
         <v>64</v>
       </c>
-      <c r="AM45" t="s">
+      <c r="AO45" t="s">
         <v>65</v>
       </c>
-      <c r="BL45">
+      <c r="BN45">
         <v>31</v>
       </c>
-      <c r="BN45" t="s">
+      <c r="BP45" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="46" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" t="s">
         <v>83</v>
       </c>
-      <c r="AL46" t="s">
+      <c r="AN46" t="s">
         <v>70</v>
       </c>
-      <c r="AM46" t="s">
+      <c r="AO46" t="s">
         <v>71</v>
       </c>
-      <c r="BL46" s="14">
+      <c r="BN46" s="14">
         <v>32</v>
       </c>
-      <c r="BM46" s="14"/>
-      <c r="BN46" s="14" t="s">
+      <c r="BO46" s="14"/>
+      <c r="BP46" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BL47">
+    <row r="47" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN47">
         <v>33</v>
       </c>
-      <c r="BN47" t="s">
+      <c r="BP47" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BL48">
+    <row r="48" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN48">
         <v>34</v>
       </c>
-      <c r="BN48" s="6" t="s">
+      <c r="BP48" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="49" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BL49">
+    <row r="49" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN49">
         <v>35</v>
       </c>
-      <c r="BN49" t="s">
+      <c r="BP49" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BL50" s="37">
+    <row r="50" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN50" s="37">
         <v>36</v>
       </c>
-      <c r="BM50" s="37"/>
-      <c r="BN50" s="37" t="s">
+      <c r="BO50" s="37"/>
+      <c r="BP50" s="37" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BN51" t="s">
+    <row r="51" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BP51" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="53" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="BN53" s="8"/>
-      <c r="BO53" s="9"/>
+    <row r="53" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BP53" s="8"/>
-    </row>
-    <row r="54" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="BL54">
+      <c r="BQ53" s="9"/>
+      <c r="BR53" s="8"/>
+    </row>
+    <row r="54" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BN54">
         <v>37</v>
       </c>
-      <c r="BN54" s="13" t="s">
+      <c r="BP54" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="BO54" s="10"/>
-      <c r="BP54" s="10"/>
-    </row>
-    <row r="55" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="BL55">
+      <c r="BQ54" s="10"/>
+      <c r="BR54" s="10"/>
+    </row>
+    <row r="55" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BN55">
         <v>38</v>
       </c>
-      <c r="BN55" s="13" t="s">
+      <c r="BP55" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="BO55" s="11" t="s">
+      <c r="BQ55" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="BP55" s="8" t="s">
+      <c r="BR55" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="BQ55">
+      <c r="BS55">
         <v>49</v>
       </c>
     </row>
-    <row r="56" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="BN56" s="10"/>
-      <c r="BO56" s="11" t="s">
+    <row r="56" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BP56" s="10"/>
+      <c r="BQ56" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="BP56" s="8" t="s">
+      <c r="BR56" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="BQ56">
+      <c r="BS56">
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="BL57">
+    <row r="57" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BN57">
         <v>39</v>
       </c>
-      <c r="BN57" s="8" t="s">
+      <c r="BP57" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="BO57" s="11" t="s">
+      <c r="BQ57" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="BP57" s="8" t="s">
+      <c r="BR57" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="BQ57">
+      <c r="BS57">
         <v>51</v>
       </c>
     </row>
-    <row r="58" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="BL58">
+    <row r="58" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BN58">
         <v>40</v>
       </c>
-      <c r="BN58" s="11" t="s">
+      <c r="BP58" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="BO58" s="10"/>
-      <c r="BP58" s="10"/>
-    </row>
-    <row r="59" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="BL59" s="16">
+      <c r="BQ58" s="10"/>
+      <c r="BR58" s="10"/>
+    </row>
+    <row r="59" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BN59" s="16">
         <v>41</v>
       </c>
-      <c r="BN59" s="8" t="s">
+      <c r="BP59" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="BO59" s="10"/>
-      <c r="BP59" s="10"/>
-    </row>
-    <row r="60" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="BL60">
+      <c r="BQ59" s="10"/>
+      <c r="BR59" s="10"/>
+    </row>
+    <row r="60" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BN60">
         <v>42</v>
       </c>
-      <c r="BN60" s="8" t="s">
+      <c r="BP60" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="BO60" s="10"/>
-      <c r="BP60" s="10"/>
-    </row>
-    <row r="61" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="BL61">
+      <c r="BQ60" s="10"/>
+      <c r="BR60" s="10"/>
+    </row>
+    <row r="61" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BN61">
         <v>43</v>
       </c>
-      <c r="BN61" s="8" t="s">
+      <c r="BP61" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="BO61" s="10"/>
-      <c r="BP61" s="10"/>
-    </row>
-    <row r="62" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="BL62">
+      <c r="BQ61" s="10"/>
+      <c r="BR61" s="10"/>
+    </row>
+    <row r="62" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BN62">
         <v>44</v>
       </c>
-      <c r="BN62" s="8" t="s">
+      <c r="BP62" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="BO62" s="10"/>
-      <c r="BP62" s="10"/>
-    </row>
-    <row r="63" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="BL63">
+      <c r="BQ62" s="10"/>
+      <c r="BR62" s="10"/>
+    </row>
+    <row r="63" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BN63">
         <v>45</v>
       </c>
-      <c r="BN63" s="8" t="s">
+      <c r="BP63" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="BO63" s="10"/>
-      <c r="BP63" s="10"/>
-    </row>
-    <row r="64" spans="64:69" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="BL64" s="16">
+      <c r="BQ63" s="10"/>
+      <c r="BR63" s="10"/>
+    </row>
+    <row r="64" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BN64" s="16">
         <v>46</v>
       </c>
-      <c r="BN64" s="8" t="s">
+      <c r="BP64" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="BO64" s="10"/>
-      <c r="BP64" s="10"/>
-    </row>
-    <row r="65" spans="64:66" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BL65">
+      <c r="BQ64" s="10"/>
+      <c r="BR64" s="10"/>
+    </row>
+    <row r="65" spans="66:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN65">
         <v>47</v>
       </c>
-      <c r="BN65" t="s">
+      <c r="BP65" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="66" spans="64:66" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BL66">
+    <row r="66" spans="66:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN66">
         <v>48</v>
       </c>
-      <c r="BN66" t="s">
+      <c r="BP66" t="s">
         <v>92</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="49">
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="AW2:AY3"/>
+    <mergeCell ref="AQ2:AS3"/>
+    <mergeCell ref="AT2:AV3"/>
+    <mergeCell ref="A1:AP1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="AN2:AP3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="BK2:BM3"/>
+    <mergeCell ref="A38:AP38"/>
+    <mergeCell ref="A39:AP39"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="AL2:AL3"/>
+    <mergeCell ref="AM2:AM3"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="AZ2:BC3"/>
+    <mergeCell ref="BD2:BG3"/>
+    <mergeCell ref="BH2:BJ3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AD2:AD3"/>
     <mergeCell ref="AE2:AE3"/>
     <mergeCell ref="AF2:AF3"/>
     <mergeCell ref="AG2:AG3"/>
     <mergeCell ref="AH2:AH3"/>
     <mergeCell ref="AI2:AI3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="BI2:BK3"/>
-    <mergeCell ref="A38:AN38"/>
-    <mergeCell ref="A39:AN39"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="S2:S3"/>
     <mergeCell ref="AJ2:AJ3"/>
     <mergeCell ref="AK2:AK3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="AX2:BA3"/>
-    <mergeCell ref="BB2:BE3"/>
-    <mergeCell ref="BF2:BH3"/>
-    <mergeCell ref="AU2:AW3"/>
-    <mergeCell ref="AO2:AQ3"/>
-    <mergeCell ref="AR2:AT3"/>
-    <mergeCell ref="A1:AN1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="AL2:AN3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="BN6" r:id="rId1" display="Прикладная дискретная математика. Приложение. 2016. № 9. С. 68-70." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="BM26" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="BN48" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="BP6" r:id="rId1" display="Прикладная дискретная математика. Приложение. 2016. № 9. С. 68-70." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="BO26" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="BP48" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId4"/>
@@ -5354,14 +5616,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b78dbef7-f85b-47b5-8738-6377d50f4027" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bffb7b91-0466-4de0-9379-f5c53c3acedf">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5566,21 +5826,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b78dbef7-f85b-47b5-8738-6377d50f4027" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bffb7b91-0466-4de0-9379-f5c53c3acedf">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12ECB55F-B88E-4FE2-9AD5-5CA5D433F306}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00280879-8A9A-4335-93BC-405126DC8F0C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b78dbef7-f85b-47b5-8738-6377d50f4027"/>
-    <ds:schemaRef ds:uri="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5605,9 +5864,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00280879-8A9A-4335-93BC-405126DC8F0C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12ECB55F-B88E-4FE2-9AD5-5CA5D433F306}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b78dbef7-f85b-47b5-8738-6377d50f4027"/>
+    <ds:schemaRef ds:uri="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Ведомость ТКИ-441 2026-2027.xlsx
+++ b/Ведомость ТКИ-441 2026-2027.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\StegMethods\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\4527\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8C3F93-103A-4ED0-A172-42296236476F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1155" windowWidth="14310" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="185">
   <si>
     <t>Ведомость посещаемости занятий студентами группы ТКИ РУТ МИИТ</t>
   </si>
@@ -586,7 +585,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -846,7 +845,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -919,12 +918,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -937,6 +930,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -955,103 +961,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Hyperlink" xfId="1"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1375,7 +1297,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BS66"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1405,209 +1327,209 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
-      <c r="Y1" s="56"/>
-      <c r="Z1" s="56"/>
-      <c r="AA1" s="56"/>
-      <c r="AB1" s="56"/>
-      <c r="AC1" s="56"/>
-      <c r="AD1" s="56"/>
-      <c r="AE1" s="56"/>
-      <c r="AF1" s="56"/>
-      <c r="AG1" s="56"/>
-      <c r="AH1" s="56"/>
-      <c r="AI1" s="56"/>
-      <c r="AJ1" s="56"/>
-      <c r="AK1" s="56"/>
-      <c r="AL1" s="56"/>
-      <c r="AM1" s="56"/>
-      <c r="AN1" s="56"/>
-      <c r="AO1" s="56"/>
-      <c r="AP1" s="56"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="46"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="Z1" s="46"/>
+      <c r="AA1" s="46"/>
+      <c r="AB1" s="46"/>
+      <c r="AC1" s="46"/>
+      <c r="AD1" s="46"/>
+      <c r="AE1" s="46"/>
+      <c r="AF1" s="46"/>
+      <c r="AG1" s="46"/>
+      <c r="AH1" s="46"/>
+      <c r="AI1" s="46"/>
+      <c r="AJ1" s="46"/>
+      <c r="AK1" s="46"/>
+      <c r="AL1" s="46"/>
+      <c r="AM1" s="46"/>
+      <c r="AN1" s="46"/>
+      <c r="AO1" s="46"/>
+      <c r="AP1" s="46"/>
     </row>
     <row r="2" spans="1:70" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="40">
+      <c r="D2" s="38">
         <v>46268</v>
       </c>
-      <c r="E2" s="40">
+      <c r="E2" s="38">
         <v>46272</v>
       </c>
-      <c r="F2" s="40">
+      <c r="F2" s="38">
         <v>46273</v>
       </c>
-      <c r="G2" s="40">
+      <c r="G2" s="38">
         <v>46275</v>
       </c>
-      <c r="H2" s="40">
+      <c r="H2" s="38">
         <v>46279</v>
       </c>
-      <c r="I2" s="38">
+      <c r="I2" s="48">
         <v>46282</v>
       </c>
-      <c r="J2" s="40">
+      <c r="J2" s="38">
         <v>46286</v>
       </c>
-      <c r="K2" s="40">
+      <c r="K2" s="38">
         <v>46287</v>
       </c>
-      <c r="L2" s="38">
+      <c r="L2" s="48">
         <v>46289</v>
       </c>
-      <c r="M2" s="40">
+      <c r="M2" s="38">
         <v>46293</v>
       </c>
-      <c r="N2" s="38">
+      <c r="N2" s="48">
         <v>46296</v>
       </c>
-      <c r="O2" s="40">
+      <c r="O2" s="38">
         <v>46300</v>
       </c>
-      <c r="P2" s="38">
+      <c r="P2" s="48">
         <v>46303</v>
       </c>
-      <c r="Q2" s="40">
+      <c r="Q2" s="38">
         <v>46307</v>
       </c>
-      <c r="R2" s="38">
+      <c r="R2" s="48">
         <v>46310</v>
       </c>
-      <c r="S2" s="40">
+      <c r="S2" s="38">
         <v>46314</v>
       </c>
-      <c r="T2" s="38">
+      <c r="T2" s="48">
         <v>46317</v>
       </c>
-      <c r="U2" s="40">
+      <c r="U2" s="38">
         <v>46321</v>
       </c>
-      <c r="V2" s="40">
+      <c r="V2" s="38">
         <v>46324</v>
       </c>
-      <c r="W2" s="40">
+      <c r="W2" s="38">
         <v>46328</v>
       </c>
-      <c r="X2" s="40">
+      <c r="X2" s="38">
         <v>46331</v>
       </c>
-      <c r="Y2" s="40">
+      <c r="Y2" s="38">
         <v>46335</v>
       </c>
-      <c r="Z2" s="40">
+      <c r="Z2" s="38">
         <v>46338</v>
       </c>
-      <c r="AA2" s="40">
+      <c r="AA2" s="38">
         <v>46342</v>
       </c>
-      <c r="AB2" s="40">
+      <c r="AB2" s="38">
         <v>46345</v>
       </c>
-      <c r="AC2" s="40">
+      <c r="AC2" s="38">
         <v>46349</v>
       </c>
-      <c r="AD2" s="40">
+      <c r="AD2" s="38">
         <v>46352</v>
       </c>
-      <c r="AE2" s="40">
+      <c r="AE2" s="38">
         <v>46356</v>
       </c>
-      <c r="AF2" s="38">
+      <c r="AF2" s="48">
         <v>46359</v>
       </c>
-      <c r="AG2" s="38">
+      <c r="AG2" s="48">
         <v>46363</v>
       </c>
-      <c r="AH2" s="38">
+      <c r="AH2" s="48">
         <v>46366</v>
       </c>
-      <c r="AI2" s="38">
+      <c r="AI2" s="48">
         <v>46370</v>
       </c>
-      <c r="AJ2" s="38">
+      <c r="AJ2" s="48">
         <v>46373</v>
       </c>
-      <c r="AK2" s="38">
+      <c r="AK2" s="48">
         <v>46377</v>
       </c>
-      <c r="AL2" s="54" t="s">
+      <c r="AL2" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="AM2" s="54"/>
-      <c r="AN2" s="42" t="s">
+      <c r="AM2" s="47"/>
+      <c r="AN2" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="AO2" s="43"/>
-      <c r="AP2" s="44"/>
-      <c r="AQ2" s="42" t="s">
+      <c r="AO2" s="41"/>
+      <c r="AP2" s="42"/>
+      <c r="AQ2" s="40" t="s">
         <v>169</v>
       </c>
-      <c r="AR2" s="43"/>
-      <c r="AS2" s="44"/>
-      <c r="AT2" s="42" t="s">
+      <c r="AR2" s="41"/>
+      <c r="AS2" s="42"/>
+      <c r="AT2" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="AU2" s="43"/>
-      <c r="AV2" s="44"/>
-      <c r="AW2" s="42" t="s">
+      <c r="AU2" s="41"/>
+      <c r="AV2" s="42"/>
+      <c r="AW2" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="AX2" s="43"/>
-      <c r="AY2" s="44"/>
-      <c r="AZ2" s="42" t="s">
+      <c r="AX2" s="41"/>
+      <c r="AY2" s="42"/>
+      <c r="AZ2" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="BA2" s="43"/>
-      <c r="BB2" s="43"/>
-      <c r="BC2" s="44"/>
-      <c r="BD2" s="42" t="s">
+      <c r="BA2" s="41"/>
+      <c r="BB2" s="41"/>
+      <c r="BC2" s="42"/>
+      <c r="BD2" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="BE2" s="43"/>
-      <c r="BF2" s="43"/>
-      <c r="BG2" s="44" t="s">
+      <c r="BE2" s="41"/>
+      <c r="BF2" s="41"/>
+      <c r="BG2" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="BH2" s="42" t="s">
+      <c r="BH2" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="BI2" s="43"/>
-      <c r="BJ2" s="44"/>
-      <c r="BK2" s="42" t="s">
+      <c r="BI2" s="41"/>
+      <c r="BJ2" s="42"/>
+      <c r="BK2" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="BL2" s="43"/>
-      <c r="BM2" s="44"/>
+      <c r="BL2" s="41"/>
+      <c r="BM2" s="42"/>
     </row>
     <row r="3" spans="1:70" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1616,69 +1538,69 @@
       <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="41"/>
-      <c r="T3" s="39"/>
-      <c r="U3" s="41"/>
-      <c r="V3" s="41"/>
-      <c r="W3" s="41"/>
-      <c r="X3" s="41"/>
-      <c r="Y3" s="41"/>
-      <c r="Z3" s="41"/>
-      <c r="AA3" s="41"/>
-      <c r="AB3" s="41"/>
-      <c r="AC3" s="41"/>
-      <c r="AD3" s="41"/>
-      <c r="AE3" s="41"/>
-      <c r="AF3" s="39"/>
-      <c r="AG3" s="39"/>
-      <c r="AH3" s="39"/>
-      <c r="AI3" s="39"/>
-      <c r="AJ3" s="39"/>
-      <c r="AK3" s="39"/>
-      <c r="AL3" s="54"/>
-      <c r="AM3" s="54"/>
-      <c r="AN3" s="45"/>
-      <c r="AO3" s="57"/>
-      <c r="AP3" s="47"/>
-      <c r="AQ3" s="45"/>
-      <c r="AR3" s="46"/>
-      <c r="AS3" s="47"/>
-      <c r="AT3" s="45"/>
-      <c r="AU3" s="46"/>
-      <c r="AV3" s="47"/>
-      <c r="AW3" s="45"/>
-      <c r="AX3" s="46"/>
-      <c r="AY3" s="47"/>
-      <c r="AZ3" s="45"/>
-      <c r="BA3" s="46"/>
-      <c r="BB3" s="46"/>
-      <c r="BC3" s="47"/>
-      <c r="BD3" s="45"/>
-      <c r="BE3" s="46"/>
-      <c r="BF3" s="46"/>
-      <c r="BG3" s="47"/>
-      <c r="BH3" s="45"/>
-      <c r="BI3" s="46"/>
-      <c r="BJ3" s="47"/>
-      <c r="BK3" s="45"/>
-      <c r="BL3" s="46"/>
-      <c r="BM3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="39"/>
+      <c r="T3" s="49"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="39"/>
+      <c r="AA3" s="39"/>
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="39"/>
+      <c r="AD3" s="39"/>
+      <c r="AE3" s="39"/>
+      <c r="AF3" s="49"/>
+      <c r="AG3" s="49"/>
+      <c r="AH3" s="49"/>
+      <c r="AI3" s="49"/>
+      <c r="AJ3" s="49"/>
+      <c r="AK3" s="49"/>
+      <c r="AL3" s="47"/>
+      <c r="AM3" s="47"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="50"/>
+      <c r="AP3" s="45"/>
+      <c r="AQ3" s="43"/>
+      <c r="AR3" s="44"/>
+      <c r="AS3" s="45"/>
+      <c r="AT3" s="43"/>
+      <c r="AU3" s="44"/>
+      <c r="AV3" s="45"/>
+      <c r="AW3" s="43"/>
+      <c r="AX3" s="44"/>
+      <c r="AY3" s="45"/>
+      <c r="AZ3" s="43"/>
+      <c r="BA3" s="44"/>
+      <c r="BB3" s="44"/>
+      <c r="BC3" s="45"/>
+      <c r="BD3" s="43"/>
+      <c r="BE3" s="44"/>
+      <c r="BF3" s="44"/>
+      <c r="BG3" s="45"/>
+      <c r="BH3" s="43"/>
+      <c r="BI3" s="44"/>
+      <c r="BJ3" s="45"/>
+      <c r="BK3" s="43"/>
+      <c r="BL3" s="44"/>
+      <c r="BM3" s="45"/>
     </row>
     <row r="4" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
@@ -1711,7 +1633,9 @@
       <c r="L4" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="M4" s="17"/>
+      <c r="M4" s="59" t="s">
+        <v>126</v>
+      </c>
       <c r="N4" s="17"/>
       <c r="O4" s="17"/>
       <c r="P4" s="17"/>
@@ -1805,10 +1729,12 @@
         <v>126</v>
       </c>
       <c r="K5" s="17"/>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="M5" s="17"/>
+      <c r="M5" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="N5" s="17"/>
       <c r="O5" s="17"/>
       <c r="P5" s="17"/>
@@ -1917,10 +1843,12 @@
         <v>126</v>
       </c>
       <c r="K6" s="17"/>
-      <c r="L6" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M6" s="17"/>
+      <c r="L6" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M6" s="60" t="s">
+        <v>126</v>
+      </c>
       <c r="N6" s="17"/>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
@@ -2018,10 +1946,12 @@
         <v>126</v>
       </c>
       <c r="K7" s="17"/>
-      <c r="L7" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M7" s="17"/>
+      <c r="L7" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M7" s="58" t="s">
+        <v>126</v>
+      </c>
       <c r="N7" s="17"/>
       <c r="O7" s="24"/>
       <c r="P7" s="17"/>
@@ -2049,7 +1979,7 @@
       <c r="AL7" s="17"/>
       <c r="AM7" s="17"/>
       <c r="AN7" s="19"/>
-      <c r="AO7" s="19"/>
+      <c r="AO7" s="61"/>
       <c r="AP7" s="25"/>
       <c r="AQ7" s="20" t="s">
         <v>144</v>
@@ -2119,10 +2049,12 @@
         <v>127</v>
       </c>
       <c r="K8" s="17"/>
-      <c r="L8" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M8" s="17"/>
+      <c r="L8" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M8" s="17" t="s">
+        <v>127</v>
+      </c>
       <c r="N8" s="17"/>
       <c r="O8" s="17"/>
       <c r="P8" s="17"/>
@@ -2220,10 +2152,12 @@
         <v>127</v>
       </c>
       <c r="K9" s="17"/>
-      <c r="L9" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M9" s="17"/>
+      <c r="L9" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M9" s="59" t="s">
+        <v>126</v>
+      </c>
       <c r="N9" s="17"/>
       <c r="O9" s="17"/>
       <c r="P9" s="17"/>
@@ -2319,10 +2253,12 @@
         <v>126</v>
       </c>
       <c r="K10" s="17"/>
-      <c r="L10" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M10" s="17"/>
+      <c r="L10" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M10" s="17" t="s">
+        <v>127</v>
+      </c>
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
       <c r="P10" s="17"/>
@@ -2418,10 +2354,12 @@
         <v>126</v>
       </c>
       <c r="K11" s="17"/>
-      <c r="L11" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M11" s="17"/>
+      <c r="L11" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M11" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="N11" s="17"/>
       <c r="O11" s="17"/>
       <c r="P11" s="17"/>
@@ -2449,7 +2387,7 @@
       <c r="AL11" s="18"/>
       <c r="AM11" s="17"/>
       <c r="AN11" s="19"/>
-      <c r="AO11" s="19"/>
+      <c r="AO11" s="61"/>
       <c r="AP11" s="21"/>
       <c r="AQ11" s="33" t="s">
         <v>153</v>
@@ -2519,10 +2457,12 @@
         <v>126</v>
       </c>
       <c r="K12" s="17"/>
-      <c r="L12" s="2" t="s">
+      <c r="L12" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="M12" s="17"/>
+      <c r="M12" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="N12" s="17"/>
       <c r="O12" s="17"/>
       <c r="P12" s="17"/>
@@ -2550,7 +2490,7 @@
       <c r="AL12" s="18"/>
       <c r="AM12" s="17"/>
       <c r="AN12" s="19"/>
-      <c r="AO12" s="19"/>
+      <c r="AO12" s="61"/>
       <c r="AP12" s="21"/>
       <c r="AQ12" s="20" t="s">
         <v>155</v>
@@ -2616,10 +2556,12 @@
         <v>126</v>
       </c>
       <c r="K13" s="17"/>
-      <c r="L13" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M13" s="17"/>
+      <c r="L13" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M13" s="17" t="s">
+        <v>127</v>
+      </c>
       <c r="N13" s="17"/>
       <c r="O13" s="17"/>
       <c r="P13" s="17"/>
@@ -2711,10 +2653,12 @@
         <v>127</v>
       </c>
       <c r="K14" s="17"/>
-      <c r="L14" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M14" s="17"/>
+      <c r="L14" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M14" s="58" t="s">
+        <v>126</v>
+      </c>
       <c r="N14" s="17"/>
       <c r="O14" s="17"/>
       <c r="P14" s="23"/>
@@ -2806,10 +2750,12 @@
         <v>126</v>
       </c>
       <c r="K15" s="17"/>
-      <c r="L15" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M15" s="17"/>
+      <c r="L15" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M15" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="N15" s="17"/>
       <c r="O15" s="17"/>
       <c r="P15" s="17"/>
@@ -2901,10 +2847,12 @@
         <v>126</v>
       </c>
       <c r="K16" s="17"/>
-      <c r="L16" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M16" s="17"/>
+      <c r="L16" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M16" s="59" t="s">
+        <v>126</v>
+      </c>
       <c r="N16" s="17"/>
       <c r="O16" s="17"/>
       <c r="P16" s="17"/>
@@ -3000,10 +2948,12 @@
         <v>126</v>
       </c>
       <c r="K17" s="17"/>
-      <c r="L17" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M17" s="17"/>
+      <c r="L17" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M17" s="17" t="s">
+        <v>127</v>
+      </c>
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
       <c r="P17" s="17"/>
@@ -3097,10 +3047,12 @@
         <v>126</v>
       </c>
       <c r="K18" s="17"/>
-      <c r="L18" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M18" s="17"/>
+      <c r="L18" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M18" s="59" t="s">
+        <v>126</v>
+      </c>
       <c r="N18" s="17"/>
       <c r="O18" s="17"/>
       <c r="P18" s="17"/>
@@ -3192,10 +3144,12 @@
         <v>126</v>
       </c>
       <c r="K19" s="17"/>
-      <c r="L19" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M19" s="17"/>
+      <c r="L19" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="60" t="s">
+        <v>126</v>
+      </c>
       <c r="N19" s="17"/>
       <c r="O19" s="17"/>
       <c r="P19" s="17"/>
@@ -3223,7 +3177,7 @@
       <c r="AL19" s="18"/>
       <c r="AM19" s="17"/>
       <c r="AN19" s="19"/>
-      <c r="AO19" s="19"/>
+      <c r="AO19" s="61"/>
       <c r="AP19" s="21"/>
       <c r="AQ19" s="33" t="s">
         <v>161</v>
@@ -3287,10 +3241,12 @@
         <v>126</v>
       </c>
       <c r="K20" s="17"/>
-      <c r="L20" s="2" t="s">
+      <c r="L20" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="M20" s="17"/>
+      <c r="M20" s="59" t="s">
+        <v>126</v>
+      </c>
       <c r="N20" s="17"/>
       <c r="O20" s="17"/>
       <c r="P20" s="17"/>
@@ -3382,10 +3338,12 @@
         <v>127</v>
       </c>
       <c r="K21" s="17"/>
-      <c r="L21" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M21" s="17"/>
+      <c r="L21" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M21" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="N21" s="17"/>
       <c r="O21" s="17"/>
       <c r="P21" s="17"/>
@@ -3477,10 +3435,12 @@
         <v>127</v>
       </c>
       <c r="K22" s="17"/>
-      <c r="L22" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M22" s="17"/>
+      <c r="L22" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M22" s="17" t="s">
+        <v>127</v>
+      </c>
       <c r="N22" s="17"/>
       <c r="O22" s="17"/>
       <c r="P22" s="17"/>
@@ -3572,10 +3532,12 @@
         <v>126</v>
       </c>
       <c r="K23" s="17"/>
-      <c r="L23" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M23" s="17"/>
+      <c r="L23" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M23" s="17" t="s">
+        <v>127</v>
+      </c>
       <c r="N23" s="17"/>
       <c r="O23" s="17"/>
       <c r="P23" s="17"/>
@@ -3665,10 +3627,12 @@
         <v>126</v>
       </c>
       <c r="K24" s="17"/>
-      <c r="L24" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M24" s="17"/>
+      <c r="L24" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M24" s="17" t="s">
+        <v>127</v>
+      </c>
       <c r="N24" s="17"/>
       <c r="O24" s="17"/>
       <c r="P24" s="17"/>
@@ -3760,10 +3724,12 @@
         <v>126</v>
       </c>
       <c r="K25" s="17"/>
-      <c r="L25" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M25" s="17"/>
+      <c r="L25" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M25" s="17" t="s">
+        <v>127</v>
+      </c>
       <c r="N25" s="17"/>
       <c r="O25" s="17"/>
       <c r="P25" s="17"/>
@@ -3848,15 +3814,17 @@
       <c r="H26" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="K26" s="29"/>
-      <c r="L26" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M26" s="29"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M26" s="29" t="s">
+        <v>127</v>
+      </c>
       <c r="N26" s="29"/>
       <c r="O26" s="29"/>
       <c r="P26" s="29"/>
@@ -3946,15 +3914,17 @@
       <c r="H27" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="I27" s="29"/>
-      <c r="J27" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="K27" s="30"/>
-      <c r="L27" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M27" s="30"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>127</v>
+      </c>
       <c r="N27" s="30"/>
       <c r="O27" s="30"/>
       <c r="P27" s="30"/>
@@ -4045,17 +4015,19 @@
       <c r="H28" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="I28" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="J28" s="30" t="s">
+      <c r="I28" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J28" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="K28" s="30"/>
-      <c r="L28" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M28" s="30"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>127</v>
+      </c>
       <c r="N28" s="30"/>
       <c r="O28" s="30"/>
       <c r="P28" s="30"/>
@@ -4136,15 +4108,17 @@
       <c r="H29" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="I29" s="29"/>
-      <c r="J29" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="K29" s="30"/>
-      <c r="L29" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M29" s="30"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>127</v>
+      </c>
       <c r="N29" s="30"/>
       <c r="O29" s="30"/>
       <c r="P29" s="30"/>
@@ -4223,15 +4197,17 @@
       <c r="H30" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="I30" s="29"/>
-      <c r="J30" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="K30" s="30"/>
-      <c r="L30" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M30" s="30"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M30" s="59" t="s">
+        <v>126</v>
+      </c>
       <c r="N30" s="30"/>
       <c r="O30" s="30"/>
       <c r="P30" s="30"/>
@@ -4312,15 +4288,17 @@
       <c r="H31" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="I31" s="29"/>
-      <c r="J31" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="K31" s="30"/>
-      <c r="L31" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M31" s="30"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M31" s="58" t="s">
+        <v>126</v>
+      </c>
       <c r="N31" s="30"/>
       <c r="O31" s="30"/>
       <c r="P31" s="30"/>
@@ -4401,15 +4379,17 @@
       <c r="H32" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="I32" s="29"/>
-      <c r="J32" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="K32" s="30"/>
-      <c r="L32" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M32" s="30"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M32" s="60" t="s">
+        <v>126</v>
+      </c>
       <c r="N32" s="30"/>
       <c r="O32" s="30"/>
       <c r="P32" s="30"/>
@@ -4494,15 +4474,17 @@
       <c r="H33" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="I33" s="29"/>
-      <c r="J33" s="30" t="s">
+      <c r="I33" s="17"/>
+      <c r="J33" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="K33" s="30"/>
-      <c r="L33" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M33" s="30"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>127</v>
+      </c>
       <c r="N33" s="30"/>
       <c r="O33" s="30"/>
       <c r="P33" s="30"/>
@@ -4581,15 +4563,17 @@
       <c r="H34" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="I34" s="29"/>
-      <c r="J34" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="K34" s="30"/>
-      <c r="L34" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M34" s="30"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>127</v>
+      </c>
       <c r="N34" s="30"/>
       <c r="O34" s="30"/>
       <c r="P34" s="30"/>
@@ -4670,15 +4654,17 @@
       <c r="H35" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="I35" s="29"/>
-      <c r="J35" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="K35" s="30"/>
-      <c r="L35" s="2" t="s">
+      <c r="I35" s="17"/>
+      <c r="J35" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="M35" s="30"/>
+      <c r="M35" s="58" t="s">
+        <v>126</v>
+      </c>
       <c r="N35" s="30"/>
       <c r="O35" s="30"/>
       <c r="P35" s="30"/>
@@ -4759,15 +4745,17 @@
       <c r="H36" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="I36" s="29"/>
-      <c r="J36" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="K36" s="30"/>
-      <c r="L36" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M36" s="30"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>127</v>
+      </c>
       <c r="N36" s="30"/>
       <c r="O36" s="30"/>
       <c r="P36" s="30"/>
@@ -4846,17 +4834,19 @@
       <c r="H37" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="I37" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="J37" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="K37" s="30"/>
-      <c r="L37" s="30" t="s">
+      <c r="I37" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J37" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="M37" s="30"/>
+      <c r="M37" s="2" t="s">
+        <v>127</v>
+      </c>
       <c r="N37" s="30"/>
       <c r="O37" s="30"/>
       <c r="P37" s="30"/>
@@ -4915,50 +4905,50 @@
       <c r="BM37" s="30"/>
     </row>
     <row r="38" spans="1:68" x14ac:dyDescent="0.25">
-      <c r="A38" s="48" t="s">
+      <c r="A38" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="B38" s="49"/>
-      <c r="C38" s="49"/>
-      <c r="D38" s="49"/>
-      <c r="E38" s="49"/>
-      <c r="F38" s="49"/>
-      <c r="G38" s="49"/>
-      <c r="H38" s="49"/>
-      <c r="I38" s="49"/>
-      <c r="J38" s="49"/>
-      <c r="K38" s="49"/>
-      <c r="L38" s="49"/>
-      <c r="M38" s="49"/>
-      <c r="N38" s="49"/>
-      <c r="O38" s="49"/>
-      <c r="P38" s="49"/>
-      <c r="Q38" s="49"/>
-      <c r="R38" s="49"/>
-      <c r="S38" s="49"/>
-      <c r="T38" s="49"/>
-      <c r="U38" s="49"/>
-      <c r="V38" s="49"/>
-      <c r="W38" s="49"/>
-      <c r="X38" s="49"/>
-      <c r="Y38" s="49"/>
-      <c r="Z38" s="49"/>
-      <c r="AA38" s="49"/>
-      <c r="AB38" s="49"/>
-      <c r="AC38" s="49"/>
-      <c r="AD38" s="49"/>
-      <c r="AE38" s="49"/>
-      <c r="AF38" s="49"/>
-      <c r="AG38" s="49"/>
-      <c r="AH38" s="49"/>
-      <c r="AI38" s="49"/>
-      <c r="AJ38" s="49"/>
-      <c r="AK38" s="49"/>
-      <c r="AL38" s="49"/>
-      <c r="AM38" s="49"/>
-      <c r="AN38" s="49"/>
-      <c r="AO38" s="49"/>
-      <c r="AP38" s="50"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="52"/>
+      <c r="L38" s="52"/>
+      <c r="M38" s="52"/>
+      <c r="N38" s="52"/>
+      <c r="O38" s="52"/>
+      <c r="P38" s="52"/>
+      <c r="Q38" s="52"/>
+      <c r="R38" s="52"/>
+      <c r="S38" s="52"/>
+      <c r="T38" s="52"/>
+      <c r="U38" s="52"/>
+      <c r="V38" s="52"/>
+      <c r="W38" s="52"/>
+      <c r="X38" s="52"/>
+      <c r="Y38" s="52"/>
+      <c r="Z38" s="52"/>
+      <c r="AA38" s="52"/>
+      <c r="AB38" s="52"/>
+      <c r="AC38" s="52"/>
+      <c r="AD38" s="52"/>
+      <c r="AE38" s="52"/>
+      <c r="AF38" s="52"/>
+      <c r="AG38" s="52"/>
+      <c r="AH38" s="52"/>
+      <c r="AI38" s="52"/>
+      <c r="AJ38" s="52"/>
+      <c r="AK38" s="52"/>
+      <c r="AL38" s="52"/>
+      <c r="AM38" s="52"/>
+      <c r="AN38" s="52"/>
+      <c r="AO38" s="52"/>
+      <c r="AP38" s="53"/>
       <c r="AQ38" s="2"/>
       <c r="AR38" s="2"/>
       <c r="AS38" s="2"/>
@@ -4990,50 +4980,50 @@
       </c>
     </row>
     <row r="39" spans="1:68" x14ac:dyDescent="0.25">
-      <c r="A39" s="51" t="s">
+      <c r="A39" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="B39" s="52"/>
-      <c r="C39" s="52"/>
-      <c r="D39" s="52"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="52"/>
-      <c r="G39" s="52"/>
-      <c r="H39" s="52"/>
-      <c r="I39" s="52"/>
-      <c r="J39" s="52"/>
-      <c r="K39" s="52"/>
-      <c r="L39" s="52"/>
-      <c r="M39" s="52"/>
-      <c r="N39" s="52"/>
-      <c r="O39" s="52"/>
-      <c r="P39" s="52"/>
-      <c r="Q39" s="52"/>
-      <c r="R39" s="52"/>
-      <c r="S39" s="52"/>
-      <c r="T39" s="52"/>
-      <c r="U39" s="52"/>
-      <c r="V39" s="52"/>
-      <c r="W39" s="52"/>
-      <c r="X39" s="52"/>
-      <c r="Y39" s="52"/>
-      <c r="Z39" s="52"/>
-      <c r="AA39" s="52"/>
-      <c r="AB39" s="52"/>
-      <c r="AC39" s="52"/>
-      <c r="AD39" s="52"/>
-      <c r="AE39" s="52"/>
-      <c r="AF39" s="52"/>
-      <c r="AG39" s="52"/>
-      <c r="AH39" s="52"/>
-      <c r="AI39" s="52"/>
-      <c r="AJ39" s="52"/>
-      <c r="AK39" s="52"/>
-      <c r="AL39" s="52"/>
-      <c r="AM39" s="52"/>
-      <c r="AN39" s="52"/>
-      <c r="AO39" s="52"/>
-      <c r="AP39" s="53"/>
+      <c r="B39" s="55"/>
+      <c r="C39" s="55"/>
+      <c r="D39" s="55"/>
+      <c r="E39" s="55"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="55"/>
+      <c r="J39" s="55"/>
+      <c r="K39" s="55"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="55"/>
+      <c r="N39" s="55"/>
+      <c r="O39" s="55"/>
+      <c r="P39" s="55"/>
+      <c r="Q39" s="55"/>
+      <c r="R39" s="55"/>
+      <c r="S39" s="55"/>
+      <c r="T39" s="55"/>
+      <c r="U39" s="55"/>
+      <c r="V39" s="55"/>
+      <c r="W39" s="55"/>
+      <c r="X39" s="55"/>
+      <c r="Y39" s="55"/>
+      <c r="Z39" s="55"/>
+      <c r="AA39" s="55"/>
+      <c r="AB39" s="55"/>
+      <c r="AC39" s="55"/>
+      <c r="AD39" s="55"/>
+      <c r="AE39" s="55"/>
+      <c r="AF39" s="55"/>
+      <c r="AG39" s="55"/>
+      <c r="AH39" s="55"/>
+      <c r="AI39" s="55"/>
+      <c r="AJ39" s="55"/>
+      <c r="AK39" s="55"/>
+      <c r="AL39" s="55"/>
+      <c r="AM39" s="55"/>
+      <c r="AN39" s="55"/>
+      <c r="AO39" s="55"/>
+      <c r="AP39" s="56"/>
       <c r="AQ39" s="2"/>
       <c r="AR39" s="2"/>
       <c r="AS39" s="2"/>
@@ -5554,25 +5544,7 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="AW2:AY3"/>
-    <mergeCell ref="AQ2:AS3"/>
-    <mergeCell ref="AT2:AV3"/>
-    <mergeCell ref="A1:AP1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="AN2:AP3"/>
-    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="AK2:AK3"/>
     <mergeCell ref="BK2:BM3"/>
     <mergeCell ref="A38:AP38"/>
     <mergeCell ref="A39:AP39"/>
@@ -5589,8 +5561,27 @@
     <mergeCell ref="BD2:BG3"/>
     <mergeCell ref="BH2:BJ3"/>
     <mergeCell ref="W2:W3"/>
+    <mergeCell ref="A1:AP1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="AN2:AP3"/>
+    <mergeCell ref="V2:V3"/>
     <mergeCell ref="X2:X3"/>
     <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="AW2:AY3"/>
+    <mergeCell ref="AQ2:AS3"/>
+    <mergeCell ref="AT2:AV3"/>
     <mergeCell ref="Z2:Z3"/>
     <mergeCell ref="AA2:AA3"/>
     <mergeCell ref="AB2:AB3"/>
@@ -5602,12 +5593,11 @@
     <mergeCell ref="AH2:AH3"/>
     <mergeCell ref="AI2:AI3"/>
     <mergeCell ref="AJ2:AJ3"/>
-    <mergeCell ref="AK2:AK3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="BP6" r:id="rId1" display="Прикладная дискретная математика. Приложение. 2016. № 9. С. 68-70." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="BO26" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="BP48" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="BP6" r:id="rId1" display="Прикладная дискретная математика. Приложение. 2016. № 9. С. 68-70."/>
+    <hyperlink ref="BO26" r:id="rId2"/>
+    <hyperlink ref="BP48" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId4"/>
@@ -5616,12 +5606,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b78dbef7-f85b-47b5-8738-6377d50f4027" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bffb7b91-0466-4de0-9379-f5c53c3acedf">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5826,20 +5818,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b78dbef7-f85b-47b5-8738-6377d50f4027" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bffb7b91-0466-4de0-9379-f5c53c3acedf">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00280879-8A9A-4335-93BC-405126DC8F0C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12ECB55F-B88E-4FE2-9AD5-5CA5D433F306}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b78dbef7-f85b-47b5-8738-6377d50f4027"/>
+    <ds:schemaRef ds:uri="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5864,12 +5857,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12ECB55F-B88E-4FE2-9AD5-5CA5D433F306}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00280879-8A9A-4335-93BC-405126DC8F0C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b78dbef7-f85b-47b5-8738-6377d50f4027"/>
-    <ds:schemaRef ds:uri="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Ведомость ТКИ-441 2026-2027.xlsx
+++ b/Ведомость ТКИ-441 2026-2027.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\4527\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\StegMethods\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7294C5F-390D-4784-84A7-EE088D54566A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="185">
   <si>
     <t>Ведомость посещаемости занятий студентами группы ТКИ РУТ МИИТ</t>
   </si>
@@ -585,7 +586,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -918,10 +919,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -930,19 +935,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -961,16 +953,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1"/>
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -990,13 +991,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>39</xdr:col>
+      <xdr:col>42</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>166255</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>44</xdr:col>
+      <xdr:col>47</xdr:col>
       <xdr:colOff>638175</xdr:colOff>
       <xdr:row>63</xdr:row>
       <xdr:rowOff>78427</xdr:rowOff>
@@ -1297,8 +1298,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BS66"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BV66"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="35.5703125" customWidth="1"/>
@@ -1307,302 +1308,321 @@
     <col min="6" max="6" width="10.85546875" customWidth="1"/>
     <col min="7" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.85546875" customWidth="1"/>
-    <col min="12" max="21" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="37" width="10.85546875" customWidth="1"/>
-    <col min="38" max="38" width="11.5703125" customWidth="1"/>
-    <col min="41" max="41" width="12.28515625" customWidth="1"/>
-    <col min="42" max="42" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="15.7109375" customWidth="1"/>
-    <col min="44" max="44" width="11.85546875" customWidth="1"/>
-    <col min="45" max="45" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="9.140625" style="12"/>
-    <col min="51" max="51" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="11.5703125" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" customWidth="1"/>
+    <col min="17" max="20" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.85546875" customWidth="1"/>
+    <col min="22" max="23" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="40" width="10.85546875" customWidth="1"/>
+    <col min="41" max="41" width="11.5703125" customWidth="1"/>
+    <col min="44" max="44" width="12.28515625" customWidth="1"/>
+    <col min="45" max="45" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="15.7109375" customWidth="1"/>
+    <col min="47" max="47" width="11.85546875" customWidth="1"/>
+    <col min="48" max="48" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="9.140625" style="12"/>
+    <col min="54" max="54" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="11.5703125" customWidth="1"/>
+    <col min="71" max="71" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="34.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A1" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
-      <c r="S1" s="46"/>
-      <c r="T1" s="46"/>
-      <c r="U1" s="46"/>
-      <c r="V1" s="46"/>
-      <c r="W1" s="46"/>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="46"/>
-      <c r="Z1" s="46"/>
-      <c r="AA1" s="46"/>
-      <c r="AB1" s="46"/>
-      <c r="AC1" s="46"/>
-      <c r="AD1" s="46"/>
-      <c r="AE1" s="46"/>
-      <c r="AF1" s="46"/>
-      <c r="AG1" s="46"/>
-      <c r="AH1" s="46"/>
-      <c r="AI1" s="46"/>
-      <c r="AJ1" s="46"/>
-      <c r="AK1" s="46"/>
-      <c r="AL1" s="46"/>
-      <c r="AM1" s="46"/>
-      <c r="AN1" s="46"/>
-      <c r="AO1" s="46"/>
-      <c r="AP1" s="46"/>
-    </row>
-    <row r="2" spans="1:70" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="60"/>
+      <c r="T1" s="60"/>
+      <c r="U1" s="60"/>
+      <c r="V1" s="60"/>
+      <c r="W1" s="60"/>
+      <c r="X1" s="60"/>
+      <c r="Y1" s="60"/>
+      <c r="Z1" s="60"/>
+      <c r="AA1" s="60"/>
+      <c r="AB1" s="60"/>
+      <c r="AC1" s="60"/>
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="60"/>
+      <c r="AF1" s="60"/>
+      <c r="AG1" s="60"/>
+      <c r="AH1" s="60"/>
+      <c r="AI1" s="60"/>
+      <c r="AJ1" s="60"/>
+      <c r="AK1" s="60"/>
+      <c r="AL1" s="60"/>
+      <c r="AM1" s="60"/>
+      <c r="AN1" s="60"/>
+      <c r="AO1" s="60"/>
+      <c r="AP1" s="60"/>
+      <c r="AQ1" s="60"/>
+      <c r="AR1" s="60"/>
+      <c r="AS1" s="60"/>
+    </row>
+    <row r="2" spans="1:73" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="57" t="s">
+      <c r="B2" s="58"/>
+      <c r="C2" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="38">
+      <c r="D2" s="56">
         <v>46268</v>
       </c>
-      <c r="E2" s="38">
+      <c r="E2" s="56">
         <v>46272</v>
       </c>
-      <c r="F2" s="38">
+      <c r="F2" s="56">
         <v>46273</v>
       </c>
-      <c r="G2" s="38">
+      <c r="G2" s="56">
         <v>46275</v>
       </c>
-      <c r="H2" s="38">
+      <c r="H2" s="56">
         <v>46279</v>
       </c>
-      <c r="I2" s="48">
+      <c r="I2" s="42">
         <v>46282</v>
       </c>
-      <c r="J2" s="38">
+      <c r="J2" s="56">
         <v>46286</v>
       </c>
-      <c r="K2" s="38">
+      <c r="K2" s="56">
         <v>46287</v>
       </c>
-      <c r="L2" s="48">
+      <c r="L2" s="42">
         <v>46289</v>
       </c>
-      <c r="M2" s="38">
+      <c r="M2" s="56">
         <v>46293</v>
       </c>
-      <c r="N2" s="48">
+      <c r="N2" s="42">
         <v>46296</v>
       </c>
-      <c r="O2" s="38">
+      <c r="O2" s="56">
         <v>46300</v>
       </c>
-      <c r="P2" s="48">
+      <c r="P2" s="56">
+        <v>46301</v>
+      </c>
+      <c r="Q2" s="42">
         <v>46303</v>
       </c>
-      <c r="Q2" s="38">
+      <c r="R2" s="56">
         <v>46307</v>
       </c>
-      <c r="R2" s="48">
+      <c r="S2" s="42">
         <v>46310</v>
       </c>
-      <c r="S2" s="38">
+      <c r="T2" s="56">
         <v>46314</v>
       </c>
-      <c r="T2" s="48">
+      <c r="U2" s="56">
+        <v>46315</v>
+      </c>
+      <c r="V2" s="42">
         <v>46317</v>
       </c>
-      <c r="U2" s="38">
+      <c r="W2" s="56">
         <v>46321</v>
       </c>
-      <c r="V2" s="38">
+      <c r="X2" s="56">
         <v>46324</v>
       </c>
-      <c r="W2" s="38">
+      <c r="Y2" s="56">
         <v>46328</v>
       </c>
-      <c r="X2" s="38">
+      <c r="Z2" s="56">
+        <v>46328</v>
+      </c>
+      <c r="AA2" s="56">
         <v>46331</v>
       </c>
-      <c r="Y2" s="38">
+      <c r="AB2" s="56">
         <v>46335</v>
       </c>
-      <c r="Z2" s="38">
+      <c r="AC2" s="56">
         <v>46338</v>
       </c>
-      <c r="AA2" s="38">
+      <c r="AD2" s="56">
         <v>46342</v>
       </c>
-      <c r="AB2" s="38">
+      <c r="AE2" s="56">
         <v>46345</v>
       </c>
-      <c r="AC2" s="38">
+      <c r="AF2" s="56">
         <v>46349</v>
       </c>
-      <c r="AD2" s="38">
+      <c r="AG2" s="56">
         <v>46352</v>
       </c>
-      <c r="AE2" s="38">
+      <c r="AH2" s="56">
         <v>46356</v>
       </c>
-      <c r="AF2" s="48">
+      <c r="AI2" s="42">
         <v>46359</v>
       </c>
-      <c r="AG2" s="48">
+      <c r="AJ2" s="42">
         <v>46363</v>
       </c>
-      <c r="AH2" s="48">
+      <c r="AK2" s="42">
         <v>46366</v>
       </c>
-      <c r="AI2" s="48">
+      <c r="AL2" s="42">
         <v>46370</v>
       </c>
-      <c r="AJ2" s="48">
+      <c r="AM2" s="42">
         <v>46373</v>
       </c>
-      <c r="AK2" s="48">
+      <c r="AN2" s="42">
         <v>46377</v>
       </c>
-      <c r="AL2" s="47" t="s">
+      <c r="AO2" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="AM2" s="47"/>
-      <c r="AN2" s="40" t="s">
+      <c r="AP2" s="58"/>
+      <c r="AQ2" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="AO2" s="41"/>
-      <c r="AP2" s="42"/>
-      <c r="AQ2" s="40" t="s">
+      <c r="AR2" s="45"/>
+      <c r="AS2" s="46"/>
+      <c r="AT2" s="44" t="s">
         <v>169</v>
       </c>
-      <c r="AR2" s="41"/>
-      <c r="AS2" s="42"/>
-      <c r="AT2" s="40" t="s">
+      <c r="AU2" s="45"/>
+      <c r="AV2" s="46"/>
+      <c r="AW2" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="AU2" s="41"/>
-      <c r="AV2" s="42"/>
-      <c r="AW2" s="40" t="s">
+      <c r="AX2" s="45"/>
+      <c r="AY2" s="46"/>
+      <c r="AZ2" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="AX2" s="41"/>
-      <c r="AY2" s="42"/>
-      <c r="AZ2" s="40" t="s">
+      <c r="BA2" s="45"/>
+      <c r="BB2" s="46"/>
+      <c r="BC2" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="BA2" s="41"/>
-      <c r="BB2" s="41"/>
-      <c r="BC2" s="42"/>
-      <c r="BD2" s="40" t="s">
+      <c r="BD2" s="45"/>
+      <c r="BE2" s="45"/>
+      <c r="BF2" s="46"/>
+      <c r="BG2" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="BE2" s="41"/>
-      <c r="BF2" s="41"/>
-      <c r="BG2" s="42" t="s">
+      <c r="BH2" s="45"/>
+      <c r="BI2" s="45"/>
+      <c r="BJ2" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="BH2" s="40" t="s">
+      <c r="BK2" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="BI2" s="41"/>
-      <c r="BJ2" s="42"/>
-      <c r="BK2" s="40" t="s">
+      <c r="BL2" s="45"/>
+      <c r="BM2" s="46"/>
+      <c r="BN2" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="BL2" s="41"/>
-      <c r="BM2" s="42"/>
-    </row>
-    <row r="3" spans="1:70" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BO2" s="45"/>
+      <c r="BP2" s="46"/>
+    </row>
+    <row r="3" spans="1:73" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="49"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="49"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="49"/>
-      <c r="S3" s="39"/>
-      <c r="T3" s="49"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="39"/>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="39"/>
-      <c r="AB3" s="39"/>
-      <c r="AC3" s="39"/>
-      <c r="AD3" s="39"/>
-      <c r="AE3" s="39"/>
-      <c r="AF3" s="49"/>
-      <c r="AG3" s="49"/>
-      <c r="AH3" s="49"/>
-      <c r="AI3" s="49"/>
-      <c r="AJ3" s="49"/>
-      <c r="AK3" s="49"/>
-      <c r="AL3" s="47"/>
-      <c r="AM3" s="47"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="57"/>
+      <c r="X3" s="57"/>
+      <c r="Y3" s="57"/>
+      <c r="Z3" s="57"/>
+      <c r="AA3" s="57"/>
+      <c r="AB3" s="57"/>
+      <c r="AC3" s="57"/>
+      <c r="AD3" s="57"/>
+      <c r="AE3" s="57"/>
+      <c r="AF3" s="57"/>
+      <c r="AG3" s="57"/>
+      <c r="AH3" s="57"/>
+      <c r="AI3" s="43"/>
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
       <c r="AN3" s="43"/>
-      <c r="AO3" s="50"/>
-      <c r="AP3" s="45"/>
-      <c r="AQ3" s="43"/>
-      <c r="AR3" s="44"/>
-      <c r="AS3" s="45"/>
-      <c r="AT3" s="43"/>
-      <c r="AU3" s="44"/>
-      <c r="AV3" s="45"/>
-      <c r="AW3" s="43"/>
-      <c r="AX3" s="44"/>
-      <c r="AY3" s="45"/>
-      <c r="AZ3" s="43"/>
-      <c r="BA3" s="44"/>
-      <c r="BB3" s="44"/>
-      <c r="BC3" s="45"/>
-      <c r="BD3" s="43"/>
-      <c r="BE3" s="44"/>
-      <c r="BF3" s="44"/>
-      <c r="BG3" s="45"/>
-      <c r="BH3" s="43"/>
-      <c r="BI3" s="44"/>
-      <c r="BJ3" s="45"/>
-      <c r="BK3" s="43"/>
-      <c r="BL3" s="44"/>
-      <c r="BM3" s="45"/>
-    </row>
-    <row r="4" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="AO3" s="58"/>
+      <c r="AP3" s="58"/>
+      <c r="AQ3" s="47"/>
+      <c r="AR3" s="61"/>
+      <c r="AS3" s="49"/>
+      <c r="AT3" s="47"/>
+      <c r="AU3" s="48"/>
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="47"/>
+      <c r="AX3" s="48"/>
+      <c r="AY3" s="49"/>
+      <c r="AZ3" s="47"/>
+      <c r="BA3" s="48"/>
+      <c r="BB3" s="49"/>
+      <c r="BC3" s="47"/>
+      <c r="BD3" s="48"/>
+      <c r="BE3" s="48"/>
+      <c r="BF3" s="49"/>
+      <c r="BG3" s="47"/>
+      <c r="BH3" s="48"/>
+      <c r="BI3" s="48"/>
+      <c r="BJ3" s="49"/>
+      <c r="BK3" s="47"/>
+      <c r="BL3" s="48"/>
+      <c r="BM3" s="49"/>
+      <c r="BN3" s="47"/>
+      <c r="BO3" s="48"/>
+      <c r="BP3" s="49"/>
+    </row>
+    <row r="4" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -1633,10 +1653,12 @@
       <c r="L4" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="M4" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="N4" s="17"/>
+      <c r="M4" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="O4" s="17"/>
       <c r="P4" s="17"/>
       <c r="Q4" s="17"/>
@@ -1660,48 +1682,51 @@
       <c r="AI4" s="17"/>
       <c r="AJ4" s="17"/>
       <c r="AK4" s="17"/>
-      <c r="AL4" s="18"/>
+      <c r="AL4" s="17"/>
       <c r="AM4" s="17"/>
-      <c r="AN4" s="19"/>
-      <c r="AO4" s="19"/>
-      <c r="AP4" s="18"/>
-      <c r="AQ4" s="33" t="s">
+      <c r="AN4" s="17"/>
+      <c r="AO4" s="18"/>
+      <c r="AP4" s="17"/>
+      <c r="AQ4" s="19"/>
+      <c r="AR4" s="19"/>
+      <c r="AS4" s="18"/>
+      <c r="AT4" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="AR4" s="34" t="s">
+      <c r="AU4" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="AS4" s="21"/>
-      <c r="AT4" s="21" t="s">
+      <c r="AV4" s="21"/>
+      <c r="AW4" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="AU4" s="21" t="s">
+      <c r="AX4" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="AV4" s="18"/>
-      <c r="AW4" s="34" t="s">
+      <c r="AY4" s="18"/>
+      <c r="AZ4" s="34" t="s">
         <v>178</v>
       </c>
-      <c r="AX4" s="34" t="s">
+      <c r="BA4" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="AY4" s="34"/>
-      <c r="AZ4" s="17"/>
-      <c r="BA4" s="17"/>
-      <c r="BB4" s="17"/>
-      <c r="BC4" s="18"/>
+      <c r="BB4" s="34"/>
+      <c r="BC4" s="17"/>
       <c r="BD4" s="17"/>
       <c r="BE4" s="17"/>
-      <c r="BF4" s="17"/>
-      <c r="BG4" s="18"/>
-      <c r="BH4" s="18"/>
+      <c r="BF4" s="18"/>
+      <c r="BG4" s="17"/>
+      <c r="BH4" s="17"/>
       <c r="BI4" s="17"/>
-      <c r="BJ4" s="17"/>
-      <c r="BK4" s="17"/>
+      <c r="BJ4" s="18"/>
+      <c r="BK4" s="18"/>
       <c r="BL4" s="17"/>
       <c r="BM4" s="17"/>
-    </row>
-    <row r="5" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="BN4" s="17"/>
+      <c r="BO4" s="17"/>
+      <c r="BP4" s="17"/>
+    </row>
+    <row r="5" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -1735,7 +1760,9 @@
       <c r="M5" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="N5" s="17"/>
+      <c r="N5" s="17" t="s">
+        <v>130</v>
+      </c>
       <c r="O5" s="17"/>
       <c r="P5" s="17"/>
       <c r="Q5" s="17"/>
@@ -1759,63 +1786,66 @@
       <c r="AI5" s="17"/>
       <c r="AJ5" s="17"/>
       <c r="AK5" s="17"/>
-      <c r="AL5" s="18"/>
+      <c r="AL5" s="17"/>
       <c r="AM5" s="17"/>
-      <c r="AN5" s="19"/>
-      <c r="AO5" s="19"/>
-      <c r="AP5" s="21"/>
-      <c r="AQ5" s="33" t="s">
+      <c r="AN5" s="17"/>
+      <c r="AO5" s="18"/>
+      <c r="AP5" s="17"/>
+      <c r="AQ5" s="19"/>
+      <c r="AR5" s="19"/>
+      <c r="AS5" s="21"/>
+      <c r="AT5" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="AR5" s="34" t="s">
+      <c r="AU5" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="AS5" s="21"/>
-      <c r="AT5" s="21" t="s">
+      <c r="AV5" s="21"/>
+      <c r="AW5" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="AU5" s="21" t="s">
+      <c r="AX5" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="AV5" s="18"/>
-      <c r="AW5" s="34" t="s">
+      <c r="AY5" s="18"/>
+      <c r="AZ5" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="AX5" s="34" t="s">
+      <c r="BA5" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="AY5" s="34"/>
-      <c r="AZ5" s="17"/>
-      <c r="BA5" s="17"/>
-      <c r="BB5" s="17"/>
-      <c r="BC5" s="18"/>
+      <c r="BB5" s="34"/>
+      <c r="BC5" s="17"/>
       <c r="BD5" s="17"/>
       <c r="BE5" s="17"/>
-      <c r="BF5" s="17"/>
-      <c r="BG5" s="18"/>
-      <c r="BH5" s="18"/>
+      <c r="BF5" s="18"/>
+      <c r="BG5" s="17"/>
+      <c r="BH5" s="17"/>
       <c r="BI5" s="17"/>
-      <c r="BJ5" s="17"/>
-      <c r="BK5" s="17"/>
+      <c r="BJ5" s="18"/>
+      <c r="BK5" s="18"/>
       <c r="BL5" s="17"/>
       <c r="BM5" s="17"/>
-      <c r="BN5">
+      <c r="BN5" s="17"/>
+      <c r="BO5" s="17"/>
+      <c r="BP5" s="17"/>
+      <c r="BQ5">
         <v>1</v>
       </c>
-      <c r="BO5" t="s">
+      <c r="BR5" t="s">
         <v>17</v>
       </c>
-      <c r="BP5" s="7" t="s">
+      <c r="BS5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="BQ5" t="s">
+      <c r="BT5" t="s">
         <v>19</v>
       </c>
-      <c r="BR5" t="s">
+      <c r="BU5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:70" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:73" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -1846,10 +1876,12 @@
       <c r="L6" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="M6" s="60" t="s">
-        <v>126</v>
-      </c>
-      <c r="N6" s="17"/>
+      <c r="M6" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="N6" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
       <c r="Q6" s="17"/>
@@ -1873,52 +1905,55 @@
       <c r="AI6" s="17"/>
       <c r="AJ6" s="17"/>
       <c r="AK6" s="17"/>
-      <c r="AL6" s="18"/>
+      <c r="AL6" s="17"/>
       <c r="AM6" s="17"/>
-      <c r="AN6" s="19"/>
-      <c r="AO6" s="19"/>
-      <c r="AP6" s="21"/>
-      <c r="AQ6" s="33" t="s">
+      <c r="AN6" s="17"/>
+      <c r="AO6" s="18"/>
+      <c r="AP6" s="17"/>
+      <c r="AQ6" s="19"/>
+      <c r="AR6" s="19"/>
+      <c r="AS6" s="21"/>
+      <c r="AT6" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="AR6" s="34" t="s">
+      <c r="AU6" s="34" t="s">
         <v>142</v>
       </c>
-      <c r="AS6" s="21"/>
-      <c r="AT6" s="11" t="s">
+      <c r="AV6" s="21"/>
+      <c r="AW6" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="AU6" s="8" t="s">
+      <c r="AX6" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AV6" s="18"/>
-      <c r="AW6" s="8" t="s">
+      <c r="AY6" s="18"/>
+      <c r="AZ6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="AX6" s="34"/>
-      <c r="AY6" s="34"/>
-      <c r="AZ6" s="17"/>
-      <c r="BA6" s="22"/>
-      <c r="BB6" s="17"/>
-      <c r="BC6" s="18"/>
-      <c r="BD6" s="17"/>
+      <c r="BA6" s="34"/>
+      <c r="BB6" s="34"/>
+      <c r="BC6" s="17"/>
+      <c r="BD6" s="22"/>
       <c r="BE6" s="17"/>
-      <c r="BF6" s="17"/>
-      <c r="BG6" s="18"/>
-      <c r="BH6" s="18"/>
+      <c r="BF6" s="18"/>
+      <c r="BG6" s="17"/>
+      <c r="BH6" s="17"/>
       <c r="BI6" s="17"/>
-      <c r="BJ6" s="17"/>
-      <c r="BK6" s="17"/>
+      <c r="BJ6" s="18"/>
+      <c r="BK6" s="18"/>
       <c r="BL6" s="17"/>
       <c r="BM6" s="17"/>
-      <c r="BN6">
+      <c r="BN6" s="17"/>
+      <c r="BO6" s="17"/>
+      <c r="BP6" s="17"/>
+      <c r="BQ6">
         <v>2</v>
       </c>
-      <c r="BP6" s="7" t="s">
+      <c r="BS6" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:70" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:73" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -1949,12 +1984,14 @@
       <c r="L7" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="M7" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="N7" s="17"/>
+      <c r="M7" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="O7" s="24"/>
-      <c r="P7" s="17"/>
+      <c r="P7" s="24"/>
       <c r="Q7" s="17"/>
       <c r="R7" s="17"/>
       <c r="S7" s="17"/>
@@ -1978,33 +2015,33 @@
       <c r="AK7" s="17"/>
       <c r="AL7" s="17"/>
       <c r="AM7" s="17"/>
-      <c r="AN7" s="19"/>
-      <c r="AO7" s="61"/>
-      <c r="AP7" s="25"/>
-      <c r="AQ7" s="20" t="s">
+      <c r="AN7" s="17"/>
+      <c r="AO7" s="17"/>
+      <c r="AP7" s="17"/>
+      <c r="AQ7" s="19"/>
+      <c r="AR7" s="41"/>
+      <c r="AS7" s="25"/>
+      <c r="AT7" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="AR7" s="19" t="s">
+      <c r="AU7" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="AS7" s="17"/>
-      <c r="AT7" s="34">
+      <c r="AV7" s="17"/>
+      <c r="AW7" s="34">
         <v>9.3000000000000007</v>
       </c>
-      <c r="AU7" s="7" t="s">
+      <c r="AX7" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="AV7" s="17"/>
-      <c r="AW7" s="11" t="s">
+      <c r="AY7" s="17"/>
+      <c r="AZ7" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="AX7" s="34"/>
-      <c r="AY7" s="34"/>
-      <c r="AZ7" s="17"/>
-      <c r="BA7" s="22"/>
-      <c r="BB7" s="17"/>
+      <c r="BA7" s="34"/>
+      <c r="BB7" s="34"/>
       <c r="BC7" s="17"/>
-      <c r="BD7" s="17"/>
+      <c r="BD7" s="22"/>
       <c r="BE7" s="17"/>
       <c r="BF7" s="17"/>
       <c r="BG7" s="17"/>
@@ -2014,14 +2051,17 @@
       <c r="BK7" s="17"/>
       <c r="BL7" s="17"/>
       <c r="BM7" s="17"/>
-      <c r="BN7" s="16">
+      <c r="BN7" s="17"/>
+      <c r="BO7" s="17"/>
+      <c r="BP7" s="17"/>
+      <c r="BQ7" s="16">
         <v>3</v>
       </c>
-      <c r="BP7" s="7" t="s">
+      <c r="BS7" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -2055,7 +2095,9 @@
       <c r="M8" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="N8" s="17"/>
+      <c r="N8" s="17" t="s">
+        <v>130</v>
+      </c>
       <c r="O8" s="17"/>
       <c r="P8" s="17"/>
       <c r="Q8" s="17"/>
@@ -2081,29 +2123,29 @@
       <c r="AK8" s="17"/>
       <c r="AL8" s="17"/>
       <c r="AM8" s="17"/>
-      <c r="AN8" s="19"/>
-      <c r="AO8" s="19"/>
-      <c r="AP8" s="25"/>
-      <c r="AQ8" s="36" t="s">
+      <c r="AN8" s="17"/>
+      <c r="AO8" s="17"/>
+      <c r="AP8" s="17"/>
+      <c r="AQ8" s="19"/>
+      <c r="AR8" s="19"/>
+      <c r="AS8" s="25"/>
+      <c r="AT8" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="AR8" s="34" t="s">
+      <c r="AU8" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="AS8" s="17"/>
-      <c r="AT8" s="34">
+      <c r="AV8" s="17"/>
+      <c r="AW8" s="34">
         <v>9.4</v>
       </c>
-      <c r="AU8" s="7" t="s">
+      <c r="AX8" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="AV8" s="17"/>
-      <c r="AW8" s="37" t="s">
+      <c r="AY8" s="17"/>
+      <c r="AZ8" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="AX8" s="17"/>
-      <c r="AY8" s="17"/>
-      <c r="AZ8" s="17"/>
       <c r="BA8" s="17"/>
       <c r="BB8" s="17"/>
       <c r="BC8" s="17"/>
@@ -2117,14 +2159,17 @@
       <c r="BK8" s="17"/>
       <c r="BL8" s="17"/>
       <c r="BM8" s="17"/>
-      <c r="BN8">
+      <c r="BN8" s="17"/>
+      <c r="BO8" s="17"/>
+      <c r="BP8" s="17"/>
+      <c r="BQ8">
         <v>4</v>
       </c>
-      <c r="BP8" t="s">
+      <c r="BS8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -2155,10 +2200,12 @@
       <c r="L9" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="M9" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="N9" s="17"/>
+      <c r="M9" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="O9" s="17"/>
       <c r="P9" s="17"/>
       <c r="Q9" s="17"/>
@@ -2182,50 +2229,53 @@
       <c r="AI9" s="17"/>
       <c r="AJ9" s="17"/>
       <c r="AK9" s="17"/>
-      <c r="AL9" s="18"/>
+      <c r="AL9" s="17"/>
       <c r="AM9" s="17"/>
-      <c r="AN9" s="19"/>
-      <c r="AO9" s="19"/>
-      <c r="AP9" s="21"/>
-      <c r="AQ9" s="27" t="s">
+      <c r="AN9" s="17"/>
+      <c r="AO9" s="18"/>
+      <c r="AP9" s="17"/>
+      <c r="AQ9" s="19"/>
+      <c r="AR9" s="19"/>
+      <c r="AS9" s="21"/>
+      <c r="AT9" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="AR9" s="19" t="s">
+      <c r="AU9" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="AS9" s="21"/>
-      <c r="AT9" s="34">
+      <c r="AV9" s="21"/>
+      <c r="AW9" s="34">
         <v>9.1</v>
       </c>
-      <c r="AU9" s="7" t="s">
+      <c r="AX9" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="AV9" s="18"/>
-      <c r="AW9" s="17"/>
-      <c r="AX9" s="17"/>
       <c r="AY9" s="18"/>
       <c r="AZ9" s="17"/>
       <c r="BA9" s="17"/>
-      <c r="BB9" s="17"/>
-      <c r="BC9" s="18"/>
+      <c r="BB9" s="18"/>
+      <c r="BC9" s="17"/>
       <c r="BD9" s="17"/>
       <c r="BE9" s="17"/>
-      <c r="BF9" s="17"/>
-      <c r="BG9" s="18"/>
-      <c r="BH9" s="18"/>
+      <c r="BF9" s="18"/>
+      <c r="BG9" s="17"/>
+      <c r="BH9" s="17"/>
       <c r="BI9" s="17"/>
-      <c r="BJ9" s="17"/>
-      <c r="BK9" s="17"/>
+      <c r="BJ9" s="18"/>
+      <c r="BK9" s="18"/>
       <c r="BL9" s="17"/>
       <c r="BM9" s="17"/>
-      <c r="BN9">
+      <c r="BN9" s="17"/>
+      <c r="BO9" s="17"/>
+      <c r="BP9" s="17"/>
+      <c r="BQ9">
         <v>5</v>
       </c>
-      <c r="BP9" t="s">
+      <c r="BS9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -2259,7 +2309,9 @@
       <c r="M10" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="N10" s="17"/>
+      <c r="N10" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="O10" s="17"/>
       <c r="P10" s="17"/>
       <c r="Q10" s="17"/>
@@ -2283,50 +2335,53 @@
       <c r="AI10" s="17"/>
       <c r="AJ10" s="17"/>
       <c r="AK10" s="17"/>
-      <c r="AL10" s="18"/>
+      <c r="AL10" s="17"/>
       <c r="AM10" s="17"/>
-      <c r="AN10" s="19"/>
-      <c r="AO10" s="19"/>
-      <c r="AP10" s="21"/>
-      <c r="AQ10" s="33" t="s">
+      <c r="AN10" s="17"/>
+      <c r="AO10" s="18"/>
+      <c r="AP10" s="17"/>
+      <c r="AQ10" s="19"/>
+      <c r="AR10" s="19"/>
+      <c r="AS10" s="21"/>
+      <c r="AT10" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="AR10" s="34" t="s">
+      <c r="AU10" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="AS10" s="18"/>
-      <c r="AT10" s="34" t="s">
+      <c r="AV10" s="18"/>
+      <c r="AW10" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="AU10" s="34" t="s">
+      <c r="AX10" s="34" t="s">
         <v>174</v>
       </c>
-      <c r="AV10" s="34"/>
-      <c r="AW10" s="17"/>
-      <c r="AX10" s="17"/>
-      <c r="AY10" s="17"/>
+      <c r="AY10" s="34"/>
       <c r="AZ10" s="17"/>
       <c r="BA10" s="17"/>
       <c r="BB10" s="17"/>
-      <c r="BC10" s="18"/>
+      <c r="BC10" s="17"/>
       <c r="BD10" s="17"/>
       <c r="BE10" s="17"/>
-      <c r="BF10" s="17"/>
-      <c r="BG10" s="18"/>
-      <c r="BH10" s="18"/>
+      <c r="BF10" s="18"/>
+      <c r="BG10" s="17"/>
+      <c r="BH10" s="17"/>
       <c r="BI10" s="17"/>
-      <c r="BJ10" s="17"/>
-      <c r="BK10" s="17"/>
+      <c r="BJ10" s="18"/>
+      <c r="BK10" s="18"/>
       <c r="BL10" s="17"/>
       <c r="BM10" s="17"/>
-      <c r="BN10">
+      <c r="BN10" s="17"/>
+      <c r="BO10" s="17"/>
+      <c r="BP10" s="17"/>
+      <c r="BQ10">
         <v>6</v>
       </c>
-      <c r="BP10" t="s">
+      <c r="BS10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -2360,7 +2415,9 @@
       <c r="M11" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="N11" s="17"/>
+      <c r="N11" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="O11" s="17"/>
       <c r="P11" s="17"/>
       <c r="Q11" s="17"/>
@@ -2384,50 +2441,53 @@
       <c r="AI11" s="17"/>
       <c r="AJ11" s="17"/>
       <c r="AK11" s="17"/>
-      <c r="AL11" s="18"/>
+      <c r="AL11" s="17"/>
       <c r="AM11" s="17"/>
-      <c r="AN11" s="19"/>
-      <c r="AO11" s="61"/>
-      <c r="AP11" s="21"/>
-      <c r="AQ11" s="33" t="s">
+      <c r="AN11" s="17"/>
+      <c r="AO11" s="18"/>
+      <c r="AP11" s="17"/>
+      <c r="AQ11" s="19"/>
+      <c r="AR11" s="41"/>
+      <c r="AS11" s="21"/>
+      <c r="AT11" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="AR11" s="34" t="s">
+      <c r="AU11" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="AS11" s="18"/>
-      <c r="AT11" s="34" t="s">
+      <c r="AV11" s="18"/>
+      <c r="AW11" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="AU11" s="34" t="s">
+      <c r="AX11" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="AV11" s="34"/>
-      <c r="AW11" s="17"/>
-      <c r="AX11" s="17"/>
-      <c r="AY11" s="18"/>
+      <c r="AY11" s="34"/>
       <c r="AZ11" s="17"/>
       <c r="BA11" s="17"/>
-      <c r="BB11" s="17"/>
-      <c r="BC11" s="18"/>
+      <c r="BB11" s="18"/>
+      <c r="BC11" s="17"/>
       <c r="BD11" s="17"/>
       <c r="BE11" s="17"/>
-      <c r="BF11" s="17"/>
-      <c r="BG11" s="18"/>
-      <c r="BH11" s="18"/>
+      <c r="BF11" s="18"/>
+      <c r="BG11" s="17"/>
+      <c r="BH11" s="17"/>
       <c r="BI11" s="17"/>
-      <c r="BJ11" s="17"/>
-      <c r="BK11" s="17"/>
+      <c r="BJ11" s="18"/>
+      <c r="BK11" s="18"/>
       <c r="BL11" s="17"/>
       <c r="BM11" s="17"/>
-      <c r="BN11">
+      <c r="BN11" s="17"/>
+      <c r="BO11" s="17"/>
+      <c r="BP11" s="17"/>
+      <c r="BQ11">
         <v>7</v>
       </c>
-      <c r="BP11" t="s">
+      <c r="BS11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -2463,7 +2523,9 @@
       <c r="M12" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="N12" s="17"/>
+      <c r="N12" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="O12" s="17"/>
       <c r="P12" s="17"/>
       <c r="Q12" s="17"/>
@@ -2487,48 +2549,51 @@
       <c r="AI12" s="17"/>
       <c r="AJ12" s="17"/>
       <c r="AK12" s="17"/>
-      <c r="AL12" s="18"/>
+      <c r="AL12" s="17"/>
       <c r="AM12" s="17"/>
-      <c r="AN12" s="19"/>
-      <c r="AO12" s="61"/>
-      <c r="AP12" s="21"/>
-      <c r="AQ12" s="20" t="s">
+      <c r="AN12" s="17"/>
+      <c r="AO12" s="18"/>
+      <c r="AP12" s="17"/>
+      <c r="AQ12" s="19"/>
+      <c r="AR12" s="41"/>
+      <c r="AS12" s="21"/>
+      <c r="AT12" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="AR12" s="19" t="s">
+      <c r="AU12" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="AS12" s="21"/>
-      <c r="AT12" s="34" t="s">
+      <c r="AV12" s="21"/>
+      <c r="AW12" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="AU12" s="34"/>
-      <c r="AV12" s="34"/>
-      <c r="AW12" s="17"/>
-      <c r="AX12" s="17"/>
-      <c r="AY12" s="18"/>
+      <c r="AX12" s="34"/>
+      <c r="AY12" s="34"/>
       <c r="AZ12" s="17"/>
       <c r="BA12" s="17"/>
-      <c r="BB12" s="17"/>
-      <c r="BC12" s="18"/>
+      <c r="BB12" s="18"/>
+      <c r="BC12" s="17"/>
       <c r="BD12" s="17"/>
       <c r="BE12" s="17"/>
-      <c r="BF12" s="17"/>
-      <c r="BG12" s="18"/>
-      <c r="BH12" s="18"/>
+      <c r="BF12" s="18"/>
+      <c r="BG12" s="17"/>
+      <c r="BH12" s="17"/>
       <c r="BI12" s="17"/>
-      <c r="BJ12" s="17"/>
-      <c r="BK12" s="17"/>
+      <c r="BJ12" s="18"/>
+      <c r="BK12" s="18"/>
       <c r="BL12" s="17"/>
       <c r="BM12" s="17"/>
-      <c r="BN12">
+      <c r="BN12" s="17"/>
+      <c r="BO12" s="17"/>
+      <c r="BP12" s="17"/>
+      <c r="BQ12">
         <v>8</v>
       </c>
-      <c r="BP12" t="s">
+      <c r="BS12" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -2562,7 +2627,9 @@
       <c r="M13" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="N13" s="17"/>
+      <c r="N13" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="O13" s="17"/>
       <c r="P13" s="17"/>
       <c r="Q13" s="17"/>
@@ -2586,46 +2653,49 @@
       <c r="AI13" s="17"/>
       <c r="AJ13" s="17"/>
       <c r="AK13" s="17"/>
-      <c r="AL13" s="18"/>
+      <c r="AL13" s="17"/>
       <c r="AM13" s="17"/>
-      <c r="AN13" s="19"/>
-      <c r="AO13" s="19"/>
-      <c r="AP13" s="21"/>
-      <c r="AQ13" s="33" t="s">
+      <c r="AN13" s="17"/>
+      <c r="AO13" s="18"/>
+      <c r="AP13" s="17"/>
+      <c r="AQ13" s="19"/>
+      <c r="AR13" s="19"/>
+      <c r="AS13" s="21"/>
+      <c r="AT13" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="AR13" s="34" t="s">
+      <c r="AU13" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="AS13" s="18"/>
-      <c r="AT13" s="17"/>
-      <c r="AU13" s="22"/>
       <c r="AV13" s="18"/>
       <c r="AW13" s="17"/>
-      <c r="AX13" s="17"/>
+      <c r="AX13" s="22"/>
       <c r="AY13" s="18"/>
       <c r="AZ13" s="17"/>
       <c r="BA13" s="17"/>
-      <c r="BB13" s="17"/>
-      <c r="BC13" s="18"/>
+      <c r="BB13" s="18"/>
+      <c r="BC13" s="17"/>
       <c r="BD13" s="17"/>
       <c r="BE13" s="17"/>
-      <c r="BF13" s="17"/>
-      <c r="BG13" s="18"/>
-      <c r="BH13" s="18"/>
+      <c r="BF13" s="18"/>
+      <c r="BG13" s="17"/>
+      <c r="BH13" s="17"/>
       <c r="BI13" s="17"/>
-      <c r="BJ13" s="17"/>
-      <c r="BK13" s="17"/>
+      <c r="BJ13" s="18"/>
+      <c r="BK13" s="18"/>
       <c r="BL13" s="17"/>
       <c r="BM13" s="17"/>
-      <c r="BN13">
+      <c r="BN13" s="17"/>
+      <c r="BO13" s="17"/>
+      <c r="BP13" s="17"/>
+      <c r="BQ13">
         <v>9</v>
       </c>
-      <c r="BP13" t="s">
+      <c r="BS13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -2656,13 +2726,15 @@
       <c r="L14" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="M14" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="N14" s="17"/>
+      <c r="M14" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="O14" s="17"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="23"/>
       <c r="R14" s="17"/>
       <c r="S14" s="17"/>
       <c r="T14" s="17"/>
@@ -2685,18 +2757,18 @@
       <c r="AK14" s="17"/>
       <c r="AL14" s="17"/>
       <c r="AM14" s="17"/>
-      <c r="AN14" s="19"/>
-      <c r="AO14" s="19"/>
-      <c r="AP14" s="25"/>
-      <c r="AQ14" s="36" t="s">
+      <c r="AN14" s="17"/>
+      <c r="AO14" s="17"/>
+      <c r="AP14" s="17"/>
+      <c r="AQ14" s="19"/>
+      <c r="AR14" s="19"/>
+      <c r="AS14" s="25"/>
+      <c r="AT14" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="AR14" s="34" t="s">
+      <c r="AU14" s="34" t="s">
         <v>160</v>
       </c>
-      <c r="AS14" s="17"/>
-      <c r="AT14" s="17"/>
-      <c r="AU14" s="17"/>
       <c r="AV14" s="17"/>
       <c r="AW14" s="17"/>
       <c r="AX14" s="17"/>
@@ -2715,14 +2787,17 @@
       <c r="BK14" s="17"/>
       <c r="BL14" s="17"/>
       <c r="BM14" s="17"/>
-      <c r="BN14">
+      <c r="BN14" s="17"/>
+      <c r="BO14" s="17"/>
+      <c r="BP14" s="17"/>
+      <c r="BQ14">
         <v>10</v>
       </c>
-      <c r="BP14" t="s">
+      <c r="BS14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -2756,7 +2831,9 @@
       <c r="M15" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="N15" s="17"/>
+      <c r="N15" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="O15" s="17"/>
       <c r="P15" s="17"/>
       <c r="Q15" s="17"/>
@@ -2780,46 +2857,49 @@
       <c r="AI15" s="17"/>
       <c r="AJ15" s="17"/>
       <c r="AK15" s="17"/>
-      <c r="AL15" s="18"/>
+      <c r="AL15" s="17"/>
       <c r="AM15" s="17"/>
-      <c r="AN15" s="19"/>
-      <c r="AO15" s="19"/>
-      <c r="AP15" s="18"/>
-      <c r="AQ15" s="33" t="s">
+      <c r="AN15" s="17"/>
+      <c r="AO15" s="18"/>
+      <c r="AP15" s="17"/>
+      <c r="AQ15" s="19"/>
+      <c r="AR15" s="19"/>
+      <c r="AS15" s="18"/>
+      <c r="AT15" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="AR15" s="34" t="s">
+      <c r="AU15" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="AS15" s="21"/>
-      <c r="AT15" s="17"/>
-      <c r="AU15" s="22"/>
-      <c r="AV15" s="18"/>
+      <c r="AV15" s="21"/>
       <c r="AW15" s="17"/>
       <c r="AX15" s="22"/>
-      <c r="AY15" s="21"/>
+      <c r="AY15" s="18"/>
       <c r="AZ15" s="17"/>
-      <c r="BA15" s="17"/>
-      <c r="BB15" s="17"/>
-      <c r="BC15" s="18"/>
+      <c r="BA15" s="22"/>
+      <c r="BB15" s="21"/>
+      <c r="BC15" s="17"/>
       <c r="BD15" s="17"/>
       <c r="BE15" s="17"/>
-      <c r="BF15" s="17"/>
+      <c r="BF15" s="18"/>
       <c r="BG15" s="17"/>
-      <c r="BH15" s="18"/>
+      <c r="BH15" s="17"/>
       <c r="BI15" s="17"/>
       <c r="BJ15" s="17"/>
-      <c r="BK15" s="17"/>
+      <c r="BK15" s="18"/>
       <c r="BL15" s="17"/>
       <c r="BM15" s="17"/>
-      <c r="BN15">
+      <c r="BN15" s="17"/>
+      <c r="BO15" s="17"/>
+      <c r="BP15" s="17"/>
+      <c r="BQ15">
         <v>11</v>
       </c>
-      <c r="BP15" t="s">
+      <c r="BS15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:70" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -2850,10 +2930,12 @@
       <c r="L16" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="M16" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="N16" s="17"/>
+      <c r="M16" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="O16" s="17"/>
       <c r="P16" s="17"/>
       <c r="Q16" s="17"/>
@@ -2877,50 +2959,53 @@
       <c r="AI16" s="17"/>
       <c r="AJ16" s="17"/>
       <c r="AK16" s="17"/>
-      <c r="AL16" s="18"/>
+      <c r="AL16" s="17"/>
       <c r="AM16" s="17"/>
-      <c r="AN16" s="18"/>
-      <c r="AO16" s="19"/>
-      <c r="AP16" s="25"/>
-      <c r="AQ16" s="33" t="s">
+      <c r="AN16" s="17"/>
+      <c r="AO16" s="18"/>
+      <c r="AP16" s="17"/>
+      <c r="AQ16" s="18"/>
+      <c r="AR16" s="19"/>
+      <c r="AS16" s="25"/>
+      <c r="AT16" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="AR16" s="34" t="s">
+      <c r="AU16" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="AS16" s="18"/>
-      <c r="AT16" s="21" t="s">
+      <c r="AV16" s="18"/>
+      <c r="AW16" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="AU16" s="21" t="s">
+      <c r="AX16" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="AV16" s="18"/>
-      <c r="AW16" s="17"/>
-      <c r="AX16" s="22"/>
       <c r="AY16" s="18"/>
       <c r="AZ16" s="17"/>
-      <c r="BA16" s="26"/>
-      <c r="BB16" s="17"/>
-      <c r="BC16" s="18"/>
-      <c r="BD16" s="17"/>
+      <c r="BA16" s="22"/>
+      <c r="BB16" s="18"/>
+      <c r="BC16" s="17"/>
+      <c r="BD16" s="26"/>
       <c r="BE16" s="17"/>
-      <c r="BF16" s="17"/>
-      <c r="BG16" s="18"/>
-      <c r="BH16" s="18"/>
+      <c r="BF16" s="18"/>
+      <c r="BG16" s="17"/>
+      <c r="BH16" s="17"/>
       <c r="BI16" s="17"/>
-      <c r="BJ16" s="17"/>
-      <c r="BK16" s="17"/>
+      <c r="BJ16" s="18"/>
+      <c r="BK16" s="18"/>
       <c r="BL16" s="17"/>
       <c r="BM16" s="17"/>
-      <c r="BN16">
+      <c r="BN16" s="17"/>
+      <c r="BO16" s="17"/>
+      <c r="BP16" s="17"/>
+      <c r="BQ16">
         <v>12</v>
       </c>
-      <c r="BP16" t="s">
+      <c r="BS16" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -2954,7 +3039,9 @@
       <c r="M17" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="N17" s="17"/>
+      <c r="N17" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="O17" s="17"/>
       <c r="P17" s="17"/>
       <c r="Q17" s="17"/>
@@ -2978,46 +3065,49 @@
       <c r="AI17" s="17"/>
       <c r="AJ17" s="17"/>
       <c r="AK17" s="17"/>
-      <c r="AL17" s="18"/>
+      <c r="AL17" s="17"/>
       <c r="AM17" s="17"/>
-      <c r="AN17" s="19"/>
-      <c r="AO17" s="19"/>
-      <c r="AP17" s="21"/>
-      <c r="AQ17" s="33" t="s">
+      <c r="AN17" s="17"/>
+      <c r="AO17" s="18"/>
+      <c r="AP17" s="17"/>
+      <c r="AQ17" s="19"/>
+      <c r="AR17" s="19"/>
+      <c r="AS17" s="21"/>
+      <c r="AT17" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="AR17" s="34" t="s">
+      <c r="AU17" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="AS17" s="18"/>
-      <c r="AT17" s="17"/>
-      <c r="AU17" s="17"/>
       <c r="AV17" s="18"/>
       <c r="AW17" s="17"/>
       <c r="AX17" s="17"/>
       <c r="AY17" s="18"/>
       <c r="AZ17" s="17"/>
       <c r="BA17" s="17"/>
-      <c r="BB17" s="17"/>
-      <c r="BC17" s="18"/>
+      <c r="BB17" s="18"/>
+      <c r="BC17" s="17"/>
       <c r="BD17" s="17"/>
       <c r="BE17" s="17"/>
-      <c r="BF17" s="17"/>
-      <c r="BG17" s="18"/>
-      <c r="BH17" s="18"/>
+      <c r="BF17" s="18"/>
+      <c r="BG17" s="17"/>
+      <c r="BH17" s="17"/>
       <c r="BI17" s="17"/>
-      <c r="BJ17" s="17"/>
-      <c r="BK17" s="17"/>
+      <c r="BJ17" s="18"/>
+      <c r="BK17" s="18"/>
       <c r="BL17" s="17"/>
       <c r="BM17" s="17"/>
-      <c r="BN17">
+      <c r="BN17" s="17"/>
+      <c r="BO17" s="17"/>
+      <c r="BP17" s="17"/>
+      <c r="BQ17">
         <v>13</v>
       </c>
-      <c r="BP17" t="s">
+      <c r="BS17" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -3050,10 +3140,12 @@
       <c r="L18" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="M18" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="N18" s="17"/>
+      <c r="M18" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="O18" s="17"/>
       <c r="P18" s="17"/>
       <c r="Q18" s="17"/>
@@ -3077,46 +3169,49 @@
       <c r="AI18" s="17"/>
       <c r="AJ18" s="17"/>
       <c r="AK18" s="17"/>
-      <c r="AL18" s="18"/>
+      <c r="AL18" s="17"/>
       <c r="AM18" s="17"/>
-      <c r="AN18" s="19"/>
-      <c r="AO18" s="19"/>
-      <c r="AP18" s="21"/>
-      <c r="AQ18" s="35" t="s">
+      <c r="AN18" s="17"/>
+      <c r="AO18" s="18"/>
+      <c r="AP18" s="17"/>
+      <c r="AQ18" s="19"/>
+      <c r="AR18" s="19"/>
+      <c r="AS18" s="21"/>
+      <c r="AT18" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="AR18" s="34" t="s">
+      <c r="AU18" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="AS18" s="21"/>
-      <c r="AT18" s="17"/>
-      <c r="AU18" s="22"/>
-      <c r="AV18" s="18"/>
+      <c r="AV18" s="21"/>
       <c r="AW18" s="17"/>
-      <c r="AX18" s="17"/>
+      <c r="AX18" s="22"/>
       <c r="AY18" s="18"/>
       <c r="AZ18" s="17"/>
       <c r="BA18" s="17"/>
-      <c r="BB18" s="17"/>
-      <c r="BC18" s="18"/>
+      <c r="BB18" s="18"/>
+      <c r="BC18" s="17"/>
       <c r="BD18" s="17"/>
       <c r="BE18" s="17"/>
-      <c r="BF18" s="17"/>
-      <c r="BG18" s="18"/>
-      <c r="BH18" s="18"/>
+      <c r="BF18" s="18"/>
+      <c r="BG18" s="17"/>
+      <c r="BH18" s="17"/>
       <c r="BI18" s="17"/>
-      <c r="BJ18" s="17"/>
-      <c r="BK18" s="17"/>
+      <c r="BJ18" s="18"/>
+      <c r="BK18" s="18"/>
       <c r="BL18" s="17"/>
       <c r="BM18" s="17"/>
-      <c r="BN18">
+      <c r="BN18" s="17"/>
+      <c r="BO18" s="17"/>
+      <c r="BP18" s="17"/>
+      <c r="BQ18">
         <v>14</v>
       </c>
-      <c r="BP18" t="s">
+      <c r="BS18" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -3147,10 +3242,12 @@
       <c r="L19" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="M19" s="60" t="s">
-        <v>126</v>
-      </c>
-      <c r="N19" s="17"/>
+      <c r="M19" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="O19" s="17"/>
       <c r="P19" s="17"/>
       <c r="Q19" s="17"/>
@@ -3174,46 +3271,49 @@
       <c r="AI19" s="17"/>
       <c r="AJ19" s="17"/>
       <c r="AK19" s="17"/>
-      <c r="AL19" s="18"/>
+      <c r="AL19" s="17"/>
       <c r="AM19" s="17"/>
-      <c r="AN19" s="19"/>
-      <c r="AO19" s="61"/>
-      <c r="AP19" s="21"/>
-      <c r="AQ19" s="33" t="s">
+      <c r="AN19" s="17"/>
+      <c r="AO19" s="18"/>
+      <c r="AP19" s="17"/>
+      <c r="AQ19" s="19"/>
+      <c r="AR19" s="41"/>
+      <c r="AS19" s="21"/>
+      <c r="AT19" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="AR19" s="34" t="s">
+      <c r="AU19" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="AS19" s="18"/>
-      <c r="AT19" s="17"/>
-      <c r="AU19" s="22"/>
-      <c r="AV19" s="21"/>
+      <c r="AV19" s="18"/>
       <c r="AW19" s="17"/>
-      <c r="AX19" s="17"/>
+      <c r="AX19" s="22"/>
       <c r="AY19" s="21"/>
       <c r="AZ19" s="17"/>
       <c r="BA19" s="17"/>
-      <c r="BB19" s="17"/>
-      <c r="BC19" s="18"/>
+      <c r="BB19" s="21"/>
+      <c r="BC19" s="17"/>
       <c r="BD19" s="17"/>
       <c r="BE19" s="17"/>
-      <c r="BF19" s="17"/>
-      <c r="BG19" s="18"/>
-      <c r="BH19" s="18"/>
+      <c r="BF19" s="18"/>
+      <c r="BG19" s="17"/>
+      <c r="BH19" s="17"/>
       <c r="BI19" s="17"/>
-      <c r="BJ19" s="17"/>
-      <c r="BK19" s="17"/>
+      <c r="BJ19" s="18"/>
+      <c r="BK19" s="18"/>
       <c r="BL19" s="17"/>
       <c r="BM19" s="17"/>
-      <c r="BN19">
+      <c r="BN19" s="17"/>
+      <c r="BO19" s="17"/>
+      <c r="BP19" s="17"/>
+      <c r="BQ19">
         <v>15</v>
       </c>
-      <c r="BP19" t="s">
+      <c r="BS19" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -3244,10 +3344,12 @@
       <c r="L20" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="M20" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="N20" s="17"/>
+      <c r="M20" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="O20" s="17"/>
       <c r="P20" s="17"/>
       <c r="Q20" s="17"/>
@@ -3271,46 +3373,49 @@
       <c r="AI20" s="17"/>
       <c r="AJ20" s="17"/>
       <c r="AK20" s="17"/>
-      <c r="AL20" s="18"/>
+      <c r="AL20" s="17"/>
       <c r="AM20" s="17"/>
-      <c r="AN20" s="19"/>
-      <c r="AO20" s="19"/>
-      <c r="AP20" s="21"/>
-      <c r="AQ20" s="27" t="s">
+      <c r="AN20" s="17"/>
+      <c r="AO20" s="18"/>
+      <c r="AP20" s="17"/>
+      <c r="AQ20" s="19"/>
+      <c r="AR20" s="19"/>
+      <c r="AS20" s="21"/>
+      <c r="AT20" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="AR20" s="19" t="s">
+      <c r="AU20" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="AS20" s="18"/>
-      <c r="AT20" s="17"/>
-      <c r="AU20" s="28"/>
-      <c r="AV20" s="17"/>
+      <c r="AV20" s="18"/>
       <c r="AW20" s="17"/>
-      <c r="AX20" s="17"/>
-      <c r="AY20" s="18"/>
+      <c r="AX20" s="28"/>
+      <c r="AY20" s="17"/>
       <c r="AZ20" s="17"/>
       <c r="BA20" s="17"/>
-      <c r="BB20" s="17"/>
-      <c r="BC20" s="18"/>
+      <c r="BB20" s="18"/>
+      <c r="BC20" s="17"/>
       <c r="BD20" s="17"/>
       <c r="BE20" s="17"/>
-      <c r="BF20" s="17"/>
-      <c r="BG20" s="18"/>
-      <c r="BH20" s="18"/>
+      <c r="BF20" s="18"/>
+      <c r="BG20" s="17"/>
+      <c r="BH20" s="17"/>
       <c r="BI20" s="17"/>
-      <c r="BJ20" s="17"/>
-      <c r="BK20" s="17"/>
+      <c r="BJ20" s="18"/>
+      <c r="BK20" s="18"/>
       <c r="BL20" s="17"/>
       <c r="BM20" s="17"/>
-      <c r="BN20">
+      <c r="BN20" s="17"/>
+      <c r="BO20" s="17"/>
+      <c r="BP20" s="17"/>
+      <c r="BQ20">
         <v>16</v>
       </c>
-      <c r="BP20" t="s">
+      <c r="BS20" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -3344,7 +3449,9 @@
       <c r="M21" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="N21" s="17"/>
+      <c r="N21" s="17" t="s">
+        <v>130</v>
+      </c>
       <c r="O21" s="17"/>
       <c r="P21" s="17"/>
       <c r="Q21" s="17"/>
@@ -3368,46 +3475,49 @@
       <c r="AI21" s="17"/>
       <c r="AJ21" s="17"/>
       <c r="AK21" s="17"/>
-      <c r="AL21" s="18"/>
+      <c r="AL21" s="17"/>
       <c r="AM21" s="17"/>
-      <c r="AN21" s="19"/>
-      <c r="AO21" s="19"/>
-      <c r="AP21" s="21"/>
-      <c r="AQ21" s="36" t="s">
+      <c r="AN21" s="17"/>
+      <c r="AO21" s="18"/>
+      <c r="AP21" s="17"/>
+      <c r="AQ21" s="19"/>
+      <c r="AR21" s="19"/>
+      <c r="AS21" s="21"/>
+      <c r="AT21" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="AR21" s="34" t="s">
+      <c r="AU21" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="AS21" s="21"/>
-      <c r="AT21" s="17"/>
-      <c r="AU21" s="17"/>
-      <c r="AV21" s="18"/>
+      <c r="AV21" s="21"/>
       <c r="AW21" s="17"/>
       <c r="AX21" s="17"/>
       <c r="AY21" s="18"/>
       <c r="AZ21" s="17"/>
       <c r="BA21" s="17"/>
-      <c r="BB21" s="17"/>
-      <c r="BC21" s="18"/>
+      <c r="BB21" s="18"/>
+      <c r="BC21" s="17"/>
       <c r="BD21" s="17"/>
       <c r="BE21" s="17"/>
-      <c r="BF21" s="17"/>
-      <c r="BG21" s="18"/>
-      <c r="BH21" s="18"/>
+      <c r="BF21" s="18"/>
+      <c r="BG21" s="17"/>
+      <c r="BH21" s="17"/>
       <c r="BI21" s="17"/>
-      <c r="BJ21" s="17"/>
-      <c r="BK21" s="17"/>
+      <c r="BJ21" s="18"/>
+      <c r="BK21" s="18"/>
       <c r="BL21" s="17"/>
       <c r="BM21" s="17"/>
-      <c r="BN21" s="16">
+      <c r="BN21" s="17"/>
+      <c r="BO21" s="17"/>
+      <c r="BP21" s="17"/>
+      <c r="BQ21" s="16">
         <v>17</v>
       </c>
-      <c r="BP21" t="s">
+      <c r="BS21" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -3441,7 +3551,9 @@
       <c r="M22" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="N22" s="17"/>
+      <c r="N22" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="O22" s="17"/>
       <c r="P22" s="17"/>
       <c r="Q22" s="17"/>
@@ -3465,46 +3577,49 @@
       <c r="AI22" s="17"/>
       <c r="AJ22" s="17"/>
       <c r="AK22" s="17"/>
-      <c r="AL22" s="18"/>
+      <c r="AL22" s="17"/>
       <c r="AM22" s="17"/>
-      <c r="AN22" s="19"/>
-      <c r="AO22" s="19"/>
-      <c r="AP22" s="21"/>
-      <c r="AQ22" s="27" t="s">
+      <c r="AN22" s="17"/>
+      <c r="AO22" s="18"/>
+      <c r="AP22" s="17"/>
+      <c r="AQ22" s="19"/>
+      <c r="AR22" s="19"/>
+      <c r="AS22" s="21"/>
+      <c r="AT22" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="AR22" s="7" t="s">
+      <c r="AU22" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="AS22" s="21"/>
-      <c r="AT22" s="17"/>
-      <c r="AU22" s="22"/>
-      <c r="AV22" s="18"/>
+      <c r="AV22" s="21"/>
       <c r="AW22" s="17"/>
       <c r="AX22" s="22"/>
       <c r="AY22" s="18"/>
       <c r="AZ22" s="17"/>
-      <c r="BA22" s="17"/>
-      <c r="BB22" s="17"/>
-      <c r="BC22" s="18"/>
+      <c r="BA22" s="22"/>
+      <c r="BB22" s="18"/>
+      <c r="BC22" s="17"/>
       <c r="BD22" s="17"/>
       <c r="BE22" s="17"/>
-      <c r="BF22" s="17"/>
-      <c r="BG22" s="18"/>
-      <c r="BH22" s="18"/>
+      <c r="BF22" s="18"/>
+      <c r="BG22" s="17"/>
+      <c r="BH22" s="17"/>
       <c r="BI22" s="17"/>
-      <c r="BJ22" s="17"/>
-      <c r="BK22" s="17"/>
+      <c r="BJ22" s="18"/>
+      <c r="BK22" s="18"/>
       <c r="BL22" s="17"/>
       <c r="BM22" s="17"/>
-      <c r="BN22">
+      <c r="BN22" s="17"/>
+      <c r="BO22" s="17"/>
+      <c r="BP22" s="17"/>
+      <c r="BQ22">
         <v>18</v>
       </c>
-      <c r="BP22" t="s">
+      <c r="BS22" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:68" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:71" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -3538,11 +3653,13 @@
       <c r="M23" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="N23" s="17"/>
+      <c r="N23" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="O23" s="17"/>
       <c r="P23" s="17"/>
-      <c r="Q23" s="23"/>
-      <c r="R23" s="17"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="23"/>
       <c r="S23" s="17"/>
       <c r="T23" s="17"/>
       <c r="U23" s="17"/>
@@ -3562,44 +3679,47 @@
       <c r="AI23" s="17"/>
       <c r="AJ23" s="17"/>
       <c r="AK23" s="17"/>
-      <c r="AL23" s="18"/>
+      <c r="AL23" s="17"/>
       <c r="AM23" s="17"/>
-      <c r="AN23" s="18"/>
-      <c r="AO23" s="19"/>
-      <c r="AP23" s="21"/>
-      <c r="AQ23" s="26" t="s">
+      <c r="AN23" s="17"/>
+      <c r="AO23" s="18"/>
+      <c r="AP23" s="17"/>
+      <c r="AQ23" s="18"/>
+      <c r="AR23" s="19"/>
+      <c r="AS23" s="21"/>
+      <c r="AT23" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="AR23" s="19"/>
-      <c r="AS23" s="18"/>
-      <c r="AT23" s="17"/>
-      <c r="AU23" s="22"/>
-      <c r="AV23" s="17"/>
+      <c r="AU23" s="19"/>
+      <c r="AV23" s="18"/>
       <c r="AW23" s="17"/>
       <c r="AX23" s="22"/>
-      <c r="AY23" s="18"/>
+      <c r="AY23" s="17"/>
       <c r="AZ23" s="17"/>
-      <c r="BA23" s="26"/>
-      <c r="BB23" s="17"/>
-      <c r="BC23" s="18"/>
-      <c r="BD23" s="17"/>
+      <c r="BA23" s="22"/>
+      <c r="BB23" s="18"/>
+      <c r="BC23" s="17"/>
+      <c r="BD23" s="26"/>
       <c r="BE23" s="17"/>
-      <c r="BF23" s="17"/>
-      <c r="BG23" s="18"/>
-      <c r="BH23" s="18"/>
+      <c r="BF23" s="18"/>
+      <c r="BG23" s="17"/>
+      <c r="BH23" s="17"/>
       <c r="BI23" s="17"/>
-      <c r="BJ23" s="17"/>
-      <c r="BK23" s="17"/>
+      <c r="BJ23" s="18"/>
+      <c r="BK23" s="18"/>
       <c r="BL23" s="17"/>
       <c r="BM23" s="17"/>
-      <c r="BN23">
+      <c r="BN23" s="17"/>
+      <c r="BO23" s="17"/>
+      <c r="BP23" s="17"/>
+      <c r="BQ23">
         <v>19</v>
       </c>
-      <c r="BP23" t="s">
+      <c r="BS23" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:68" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:71" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -3633,7 +3753,9 @@
       <c r="M24" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="N24" s="17"/>
+      <c r="N24" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="O24" s="17"/>
       <c r="P24" s="17"/>
       <c r="Q24" s="17"/>
@@ -3659,15 +3781,15 @@
       <c r="AK24" s="17"/>
       <c r="AL24" s="17"/>
       <c r="AM24" s="17"/>
-      <c r="AN24" s="19"/>
-      <c r="AO24" s="19"/>
-      <c r="AP24" s="25"/>
-      <c r="AQ24" s="26" t="s">
+      <c r="AN24" s="17"/>
+      <c r="AO24" s="17"/>
+      <c r="AP24" s="17"/>
+      <c r="AQ24" s="19"/>
+      <c r="AR24" s="19"/>
+      <c r="AS24" s="25"/>
+      <c r="AT24" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="AR24" s="17"/>
-      <c r="AS24" s="17"/>
-      <c r="AT24" s="17"/>
       <c r="AU24" s="17"/>
       <c r="AV24" s="17"/>
       <c r="AW24" s="17"/>
@@ -3687,14 +3809,17 @@
       <c r="BK24" s="17"/>
       <c r="BL24" s="17"/>
       <c r="BM24" s="17"/>
-      <c r="BN24">
+      <c r="BN24" s="17"/>
+      <c r="BO24" s="17"/>
+      <c r="BP24" s="17"/>
+      <c r="BQ24">
         <v>20</v>
       </c>
-      <c r="BP24" t="s">
+      <c r="BS24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:68" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:71" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -3730,7 +3855,9 @@
       <c r="M25" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="N25" s="17"/>
+      <c r="N25" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="O25" s="17"/>
       <c r="P25" s="17"/>
       <c r="Q25" s="17"/>
@@ -3754,44 +3881,47 @@
       <c r="AI25" s="17"/>
       <c r="AJ25" s="17"/>
       <c r="AK25" s="17"/>
-      <c r="AL25" s="18"/>
+      <c r="AL25" s="17"/>
       <c r="AM25" s="17"/>
-      <c r="AN25" s="19"/>
-      <c r="AO25" s="19"/>
-      <c r="AP25" s="21"/>
-      <c r="AQ25" s="26" t="s">
-        <v>51</v>
-      </c>
+      <c r="AN25" s="17"/>
+      <c r="AO25" s="18"/>
+      <c r="AP25" s="17"/>
+      <c r="AQ25" s="19"/>
       <c r="AR25" s="19"/>
       <c r="AS25" s="21"/>
-      <c r="AT25" s="17"/>
+      <c r="AT25" s="26" t="s">
+        <v>51</v>
+      </c>
       <c r="AU25" s="19"/>
-      <c r="AV25" s="18"/>
+      <c r="AV25" s="21"/>
       <c r="AW25" s="17"/>
-      <c r="AX25" s="22"/>
+      <c r="AX25" s="19"/>
       <c r="AY25" s="18"/>
       <c r="AZ25" s="17"/>
       <c r="BA25" s="22"/>
-      <c r="BB25" s="17"/>
-      <c r="BC25" s="18"/>
-      <c r="BD25" s="17"/>
+      <c r="BB25" s="18"/>
+      <c r="BC25" s="17"/>
+      <c r="BD25" s="22"/>
       <c r="BE25" s="17"/>
-      <c r="BF25" s="17"/>
-      <c r="BG25" s="18"/>
-      <c r="BH25" s="18"/>
+      <c r="BF25" s="18"/>
+      <c r="BG25" s="17"/>
+      <c r="BH25" s="17"/>
       <c r="BI25" s="17"/>
-      <c r="BJ25" s="17"/>
-      <c r="BK25" s="17"/>
+      <c r="BJ25" s="18"/>
+      <c r="BK25" s="18"/>
       <c r="BL25" s="17"/>
       <c r="BM25" s="17"/>
-      <c r="BN25">
+      <c r="BN25" s="17"/>
+      <c r="BO25" s="17"/>
+      <c r="BP25" s="17"/>
+      <c r="BQ25">
         <v>21</v>
       </c>
-      <c r="BP25" t="s">
+      <c r="BS25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -3825,11 +3955,13 @@
       <c r="M26" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="N26" s="29"/>
+      <c r="N26" s="29" t="s">
+        <v>126</v>
+      </c>
       <c r="O26" s="29"/>
       <c r="P26" s="29"/>
-      <c r="Q26" s="23"/>
-      <c r="R26" s="29"/>
+      <c r="Q26" s="29"/>
+      <c r="R26" s="23"/>
       <c r="S26" s="29"/>
       <c r="T26" s="29"/>
       <c r="U26" s="29"/>
@@ -3849,49 +3981,52 @@
       <c r="AI26" s="29"/>
       <c r="AJ26" s="29"/>
       <c r="AK26" s="29"/>
-      <c r="AL26" s="18"/>
+      <c r="AL26" s="29"/>
       <c r="AM26" s="29"/>
-      <c r="AN26" s="19"/>
-      <c r="AO26" s="19"/>
-      <c r="AP26" s="21"/>
-      <c r="AQ26" s="20" t="s">
+      <c r="AN26" s="29"/>
+      <c r="AO26" s="18"/>
+      <c r="AP26" s="29"/>
+      <c r="AQ26" s="19"/>
+      <c r="AR26" s="19"/>
+      <c r="AS26" s="21"/>
+      <c r="AT26" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="AR26" s="34" t="s">
+      <c r="AU26" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="AS26" s="18"/>
-      <c r="AT26" s="17"/>
-      <c r="AU26" s="22"/>
       <c r="AV26" s="18"/>
       <c r="AW26" s="17"/>
-      <c r="AX26" s="17"/>
-      <c r="AY26" s="29"/>
+      <c r="AX26" s="22"/>
+      <c r="AY26" s="18"/>
       <c r="AZ26" s="17"/>
       <c r="BA26" s="17"/>
-      <c r="BB26" s="17"/>
-      <c r="BC26" s="18"/>
+      <c r="BB26" s="29"/>
+      <c r="BC26" s="17"/>
       <c r="BD26" s="17"/>
       <c r="BE26" s="17"/>
-      <c r="BF26" s="17"/>
-      <c r="BG26" s="18"/>
-      <c r="BH26" s="18"/>
-      <c r="BI26" s="29"/>
-      <c r="BJ26" s="29"/>
-      <c r="BK26" s="29"/>
+      <c r="BF26" s="18"/>
+      <c r="BG26" s="17"/>
+      <c r="BH26" s="17"/>
+      <c r="BI26" s="17"/>
+      <c r="BJ26" s="18"/>
+      <c r="BK26" s="18"/>
       <c r="BL26" s="29"/>
       <c r="BM26" s="29"/>
-      <c r="BN26" s="14">
+      <c r="BN26" s="29"/>
+      <c r="BO26" s="29"/>
+      <c r="BP26" s="29"/>
+      <c r="BQ26" s="14">
         <v>22</v>
       </c>
-      <c r="BO26" s="15" t="s">
+      <c r="BR26" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="BP26" s="14" t="s">
+      <c r="BS26" s="14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -3925,7 +4060,9 @@
       <c r="M27" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="N27" s="30"/>
+      <c r="N27" s="30" t="s">
+        <v>126</v>
+      </c>
       <c r="O27" s="30"/>
       <c r="P27" s="30"/>
       <c r="Q27" s="30"/>
@@ -3949,50 +4086,53 @@
       <c r="AI27" s="30"/>
       <c r="AJ27" s="30"/>
       <c r="AK27" s="30"/>
-      <c r="AL27" s="18"/>
+      <c r="AL27" s="30"/>
       <c r="AM27" s="30"/>
-      <c r="AN27" s="19"/>
-      <c r="AO27" s="19"/>
-      <c r="AP27" s="18"/>
-      <c r="AQ27" s="20" t="s">
+      <c r="AN27" s="30"/>
+      <c r="AO27" s="18"/>
+      <c r="AP27" s="30"/>
+      <c r="AQ27" s="19"/>
+      <c r="AR27" s="19"/>
+      <c r="AS27" s="18"/>
+      <c r="AT27" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="AR27" s="34" t="s">
+      <c r="AU27" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="AS27" s="18"/>
-      <c r="AT27" s="21" t="s">
+      <c r="AV27" s="18"/>
+      <c r="AW27" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="AU27" s="21" t="s">
+      <c r="AX27" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="AV27" s="17"/>
-      <c r="AW27" s="17"/>
-      <c r="AX27" s="17"/>
-      <c r="AY27" s="18"/>
+      <c r="AY27" s="17"/>
       <c r="AZ27" s="17"/>
       <c r="BA27" s="17"/>
-      <c r="BB27" s="17"/>
-      <c r="BC27" s="18"/>
+      <c r="BB27" s="18"/>
+      <c r="BC27" s="17"/>
       <c r="BD27" s="17"/>
       <c r="BE27" s="17"/>
-      <c r="BF27" s="17"/>
-      <c r="BG27" s="18"/>
-      <c r="BH27" s="18"/>
-      <c r="BI27" s="30"/>
-      <c r="BJ27" s="30"/>
-      <c r="BK27" s="30"/>
+      <c r="BF27" s="18"/>
+      <c r="BG27" s="17"/>
+      <c r="BH27" s="17"/>
+      <c r="BI27" s="17"/>
+      <c r="BJ27" s="18"/>
+      <c r="BK27" s="18"/>
       <c r="BL27" s="30"/>
       <c r="BM27" s="30"/>
-      <c r="BN27">
+      <c r="BN27" s="30"/>
+      <c r="BO27" s="30"/>
+      <c r="BP27" s="30"/>
+      <c r="BQ27">
         <v>23</v>
       </c>
-      <c r="BP27" t="s">
+      <c r="BS27" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -4028,7 +4168,9 @@
       <c r="M28" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="N28" s="30"/>
+      <c r="N28" s="30" t="s">
+        <v>126</v>
+      </c>
       <c r="O28" s="30"/>
       <c r="P28" s="30"/>
       <c r="Q28" s="30"/>
@@ -4052,40 +4194,43 @@
       <c r="AI28" s="30"/>
       <c r="AJ28" s="30"/>
       <c r="AK28" s="30"/>
-      <c r="AL28" s="18"/>
+      <c r="AL28" s="30"/>
       <c r="AM28" s="30"/>
-      <c r="AN28" s="19"/>
-      <c r="AO28" s="19"/>
-      <c r="AP28" s="32"/>
-      <c r="AQ28" s="27" t="s">
+      <c r="AN28" s="30"/>
+      <c r="AO28" s="18"/>
+      <c r="AP28" s="30"/>
+      <c r="AQ28" s="19"/>
+      <c r="AR28" s="19"/>
+      <c r="AS28" s="32"/>
+      <c r="AT28" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="AR28" s="7" t="s">
+      <c r="AU28" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="AS28" s="18"/>
-      <c r="AT28" s="17"/>
-      <c r="AU28" s="28"/>
-      <c r="AV28" s="17"/>
+      <c r="AV28" s="18"/>
       <c r="AW28" s="17"/>
-      <c r="AX28" s="17"/>
-      <c r="AY28" s="18"/>
+      <c r="AX28" s="28"/>
+      <c r="AY28" s="17"/>
       <c r="AZ28" s="17"/>
       <c r="BA28" s="17"/>
-      <c r="BB28" s="17"/>
-      <c r="BC28" s="18"/>
+      <c r="BB28" s="18"/>
+      <c r="BC28" s="17"/>
       <c r="BD28" s="17"/>
       <c r="BE28" s="17"/>
-      <c r="BF28" s="17"/>
-      <c r="BG28" s="18"/>
-      <c r="BH28" s="18"/>
-      <c r="BI28" s="30"/>
-      <c r="BJ28" s="30"/>
-      <c r="BK28" s="30"/>
+      <c r="BF28" s="18"/>
+      <c r="BG28" s="17"/>
+      <c r="BH28" s="17"/>
+      <c r="BI28" s="17"/>
+      <c r="BJ28" s="18"/>
+      <c r="BK28" s="18"/>
       <c r="BL28" s="30"/>
       <c r="BM28" s="30"/>
-    </row>
-    <row r="29" spans="1:68" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="BN28" s="30"/>
+      <c r="BO28" s="30"/>
+      <c r="BP28" s="30"/>
+    </row>
+    <row r="29" spans="1:71" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -4119,7 +4264,9 @@
       <c r="M29" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="N29" s="30"/>
+      <c r="N29" s="30" t="s">
+        <v>126</v>
+      </c>
       <c r="O29" s="30"/>
       <c r="P29" s="30"/>
       <c r="Q29" s="30"/>
@@ -4143,38 +4290,41 @@
       <c r="AI29" s="30"/>
       <c r="AJ29" s="30"/>
       <c r="AK29" s="30"/>
-      <c r="AL29" s="18"/>
+      <c r="AL29" s="30"/>
       <c r="AM29" s="30"/>
-      <c r="AN29" s="19"/>
-      <c r="AO29" s="19"/>
-      <c r="AP29" s="32"/>
-      <c r="AQ29" s="26" t="s">
+      <c r="AN29" s="30"/>
+      <c r="AO29" s="18"/>
+      <c r="AP29" s="30"/>
+      <c r="AQ29" s="19"/>
+      <c r="AR29" s="19"/>
+      <c r="AS29" s="32"/>
+      <c r="AT29" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="AR29" s="19"/>
-      <c r="AS29" s="18"/>
-      <c r="AT29" s="17"/>
-      <c r="AU29" s="28"/>
-      <c r="AV29" s="17"/>
+      <c r="AU29" s="19"/>
+      <c r="AV29" s="18"/>
       <c r="AW29" s="17"/>
-      <c r="AX29" s="17"/>
-      <c r="AY29" s="18"/>
+      <c r="AX29" s="28"/>
+      <c r="AY29" s="17"/>
       <c r="AZ29" s="17"/>
       <c r="BA29" s="17"/>
-      <c r="BB29" s="17"/>
-      <c r="BC29" s="18"/>
+      <c r="BB29" s="18"/>
+      <c r="BC29" s="17"/>
       <c r="BD29" s="17"/>
       <c r="BE29" s="17"/>
-      <c r="BF29" s="17"/>
-      <c r="BG29" s="18"/>
-      <c r="BH29" s="18"/>
-      <c r="BI29" s="30"/>
-      <c r="BJ29" s="30"/>
-      <c r="BK29" s="30"/>
+      <c r="BF29" s="18"/>
+      <c r="BG29" s="17"/>
+      <c r="BH29" s="17"/>
+      <c r="BI29" s="17"/>
+      <c r="BJ29" s="18"/>
+      <c r="BK29" s="18"/>
       <c r="BL29" s="30"/>
       <c r="BM29" s="30"/>
-    </row>
-    <row r="30" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="BN29" s="30"/>
+      <c r="BO29" s="30"/>
+      <c r="BP29" s="30"/>
+    </row>
+    <row r="30" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -4205,10 +4355,12 @@
       <c r="L30" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="M30" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="N30" s="30"/>
+      <c r="M30" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="N30" s="30" t="s">
+        <v>126</v>
+      </c>
       <c r="O30" s="30"/>
       <c r="P30" s="30"/>
       <c r="Q30" s="30"/>
@@ -4232,40 +4384,43 @@
       <c r="AI30" s="30"/>
       <c r="AJ30" s="30"/>
       <c r="AK30" s="30"/>
-      <c r="AL30" s="18"/>
+      <c r="AL30" s="30"/>
       <c r="AM30" s="30"/>
-      <c r="AN30" s="19"/>
-      <c r="AO30" s="19"/>
-      <c r="AP30" s="32"/>
-      <c r="AQ30" s="35" t="s">
+      <c r="AN30" s="30"/>
+      <c r="AO30" s="18"/>
+      <c r="AP30" s="30"/>
+      <c r="AQ30" s="19"/>
+      <c r="AR30" s="19"/>
+      <c r="AS30" s="32"/>
+      <c r="AT30" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="AR30" s="34" t="s">
+      <c r="AU30" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="AS30" s="18"/>
-      <c r="AT30" s="17"/>
-      <c r="AU30" s="28"/>
-      <c r="AV30" s="17"/>
+      <c r="AV30" s="18"/>
       <c r="AW30" s="17"/>
-      <c r="AX30" s="17"/>
-      <c r="AY30" s="18"/>
+      <c r="AX30" s="28"/>
+      <c r="AY30" s="17"/>
       <c r="AZ30" s="17"/>
       <c r="BA30" s="17"/>
-      <c r="BB30" s="17"/>
-      <c r="BC30" s="18"/>
+      <c r="BB30" s="18"/>
+      <c r="BC30" s="17"/>
       <c r="BD30" s="17"/>
       <c r="BE30" s="17"/>
-      <c r="BF30" s="17"/>
-      <c r="BG30" s="18"/>
-      <c r="BH30" s="18"/>
-      <c r="BI30" s="30"/>
-      <c r="BJ30" s="30"/>
-      <c r="BK30" s="30"/>
+      <c r="BF30" s="18"/>
+      <c r="BG30" s="17"/>
+      <c r="BH30" s="17"/>
+      <c r="BI30" s="17"/>
+      <c r="BJ30" s="18"/>
+      <c r="BK30" s="18"/>
       <c r="BL30" s="30"/>
       <c r="BM30" s="30"/>
-    </row>
-    <row r="31" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="BN30" s="30"/>
+      <c r="BO30" s="30"/>
+      <c r="BP30" s="30"/>
+    </row>
+    <row r="31" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -4296,10 +4451,12 @@
       <c r="L31" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="M31" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="N31" s="30"/>
+      <c r="M31" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="N31" s="30" t="s">
+        <v>126</v>
+      </c>
       <c r="O31" s="30"/>
       <c r="P31" s="30"/>
       <c r="Q31" s="30"/>
@@ -4323,40 +4480,43 @@
       <c r="AI31" s="30"/>
       <c r="AJ31" s="30"/>
       <c r="AK31" s="30"/>
-      <c r="AL31" s="18"/>
+      <c r="AL31" s="30"/>
       <c r="AM31" s="30"/>
-      <c r="AN31" s="19"/>
-      <c r="AO31" s="19"/>
-      <c r="AP31" s="32"/>
-      <c r="AQ31" s="20" t="s">
+      <c r="AN31" s="30"/>
+      <c r="AO31" s="18"/>
+      <c r="AP31" s="30"/>
+      <c r="AQ31" s="19"/>
+      <c r="AR31" s="19"/>
+      <c r="AS31" s="32"/>
+      <c r="AT31" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="AR31" s="19" t="s">
+      <c r="AU31" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="AS31" s="18"/>
-      <c r="AT31" s="17"/>
-      <c r="AU31" s="28"/>
-      <c r="AV31" s="17"/>
+      <c r="AV31" s="18"/>
       <c r="AW31" s="17"/>
-      <c r="AX31" s="17"/>
-      <c r="AY31" s="18"/>
+      <c r="AX31" s="28"/>
+      <c r="AY31" s="17"/>
       <c r="AZ31" s="17"/>
       <c r="BA31" s="17"/>
-      <c r="BB31" s="17"/>
-      <c r="BC31" s="18"/>
+      <c r="BB31" s="18"/>
+      <c r="BC31" s="17"/>
       <c r="BD31" s="17"/>
       <c r="BE31" s="17"/>
-      <c r="BF31" s="17"/>
-      <c r="BG31" s="18"/>
-      <c r="BH31" s="18"/>
-      <c r="BI31" s="30"/>
-      <c r="BJ31" s="30"/>
-      <c r="BK31" s="30"/>
+      <c r="BF31" s="18"/>
+      <c r="BG31" s="17"/>
+      <c r="BH31" s="17"/>
+      <c r="BI31" s="17"/>
+      <c r="BJ31" s="18"/>
+      <c r="BK31" s="18"/>
       <c r="BL31" s="30"/>
       <c r="BM31" s="30"/>
-    </row>
-    <row r="32" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="BN31" s="30"/>
+      <c r="BO31" s="30"/>
+      <c r="BP31" s="30"/>
+    </row>
+    <row r="32" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -4387,10 +4547,12 @@
       <c r="L32" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="M32" s="60" t="s">
-        <v>126</v>
-      </c>
-      <c r="N32" s="30"/>
+      <c r="M32" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="N32" s="30" t="s">
+        <v>126</v>
+      </c>
       <c r="O32" s="30"/>
       <c r="P32" s="30"/>
       <c r="Q32" s="30"/>
@@ -4414,44 +4576,47 @@
       <c r="AI32" s="30"/>
       <c r="AJ32" s="30"/>
       <c r="AK32" s="30"/>
-      <c r="AL32" s="18"/>
+      <c r="AL32" s="30"/>
       <c r="AM32" s="30"/>
-      <c r="AN32" s="19"/>
-      <c r="AO32" s="19"/>
-      <c r="AP32" s="32"/>
-      <c r="AQ32" s="33" t="s">
+      <c r="AN32" s="30"/>
+      <c r="AO32" s="18"/>
+      <c r="AP32" s="30"/>
+      <c r="AQ32" s="19"/>
+      <c r="AR32" s="19"/>
+      <c r="AS32" s="32"/>
+      <c r="AT32" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="AR32" s="34" t="s">
+      <c r="AU32" s="34" t="s">
         <v>142</v>
       </c>
-      <c r="AS32" s="18"/>
-      <c r="AT32" s="17" t="s">
+      <c r="AV32" s="18"/>
+      <c r="AW32" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="AU32" s="28" t="s">
+      <c r="AX32" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="AV32" s="17"/>
-      <c r="AW32" s="17"/>
-      <c r="AX32" s="17"/>
-      <c r="AY32" s="18"/>
+      <c r="AY32" s="17"/>
       <c r="AZ32" s="17"/>
       <c r="BA32" s="17"/>
-      <c r="BB32" s="17"/>
-      <c r="BC32" s="18"/>
+      <c r="BB32" s="18"/>
+      <c r="BC32" s="17"/>
       <c r="BD32" s="17"/>
       <c r="BE32" s="17"/>
-      <c r="BF32" s="17"/>
-      <c r="BG32" s="18"/>
-      <c r="BH32" s="18"/>
-      <c r="BI32" s="30"/>
-      <c r="BJ32" s="30"/>
-      <c r="BK32" s="30"/>
+      <c r="BF32" s="18"/>
+      <c r="BG32" s="17"/>
+      <c r="BH32" s="17"/>
+      <c r="BI32" s="17"/>
+      <c r="BJ32" s="18"/>
+      <c r="BK32" s="18"/>
       <c r="BL32" s="30"/>
       <c r="BM32" s="30"/>
-    </row>
-    <row r="33" spans="1:68" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="BN32" s="30"/>
+      <c r="BO32" s="30"/>
+      <c r="BP32" s="30"/>
+    </row>
+    <row r="33" spans="1:71" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -4485,7 +4650,9 @@
       <c r="M33" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="N33" s="30"/>
+      <c r="N33" s="30" t="s">
+        <v>126</v>
+      </c>
       <c r="O33" s="30"/>
       <c r="P33" s="30"/>
       <c r="Q33" s="30"/>
@@ -4509,38 +4676,41 @@
       <c r="AI33" s="30"/>
       <c r="AJ33" s="30"/>
       <c r="AK33" s="30"/>
-      <c r="AL33" s="18"/>
+      <c r="AL33" s="30"/>
       <c r="AM33" s="30"/>
-      <c r="AN33" s="19"/>
-      <c r="AO33" s="19"/>
-      <c r="AP33" s="32"/>
-      <c r="AQ33" s="26" t="s">
+      <c r="AN33" s="30"/>
+      <c r="AO33" s="18"/>
+      <c r="AP33" s="30"/>
+      <c r="AQ33" s="19"/>
+      <c r="AR33" s="19"/>
+      <c r="AS33" s="32"/>
+      <c r="AT33" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="AR33" s="19"/>
-      <c r="AS33" s="18"/>
-      <c r="AT33" s="17"/>
-      <c r="AU33" s="28"/>
-      <c r="AV33" s="17"/>
+      <c r="AU33" s="19"/>
+      <c r="AV33" s="18"/>
       <c r="AW33" s="17"/>
-      <c r="AX33" s="17"/>
-      <c r="AY33" s="18"/>
+      <c r="AX33" s="28"/>
+      <c r="AY33" s="17"/>
       <c r="AZ33" s="17"/>
       <c r="BA33" s="17"/>
-      <c r="BB33" s="17"/>
-      <c r="BC33" s="18"/>
+      <c r="BB33" s="18"/>
+      <c r="BC33" s="17"/>
       <c r="BD33" s="17"/>
       <c r="BE33" s="17"/>
-      <c r="BF33" s="17"/>
-      <c r="BG33" s="18"/>
-      <c r="BH33" s="18"/>
-      <c r="BI33" s="30"/>
-      <c r="BJ33" s="30"/>
-      <c r="BK33" s="30"/>
+      <c r="BF33" s="18"/>
+      <c r="BG33" s="17"/>
+      <c r="BH33" s="17"/>
+      <c r="BI33" s="17"/>
+      <c r="BJ33" s="18"/>
+      <c r="BK33" s="18"/>
       <c r="BL33" s="30"/>
       <c r="BM33" s="30"/>
-    </row>
-    <row r="34" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="BN33" s="30"/>
+      <c r="BO33" s="30"/>
+      <c r="BP33" s="30"/>
+    </row>
+    <row r="34" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -4574,7 +4744,9 @@
       <c r="M34" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="N34" s="30"/>
+      <c r="N34" s="30" t="s">
+        <v>126</v>
+      </c>
       <c r="O34" s="30"/>
       <c r="P34" s="30"/>
       <c r="Q34" s="30"/>
@@ -4598,40 +4770,43 @@
       <c r="AI34" s="30"/>
       <c r="AJ34" s="30"/>
       <c r="AK34" s="30"/>
-      <c r="AL34" s="18"/>
+      <c r="AL34" s="30"/>
       <c r="AM34" s="30"/>
-      <c r="AN34" s="19"/>
-      <c r="AO34" s="19"/>
-      <c r="AP34" s="32"/>
-      <c r="AQ34" s="20" t="s">
+      <c r="AN34" s="30"/>
+      <c r="AO34" s="18"/>
+      <c r="AP34" s="30"/>
+      <c r="AQ34" s="19"/>
+      <c r="AR34" s="19"/>
+      <c r="AS34" s="32"/>
+      <c r="AT34" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="AR34" s="19" t="s">
+      <c r="AU34" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="AS34" s="18"/>
-      <c r="AT34" s="17"/>
-      <c r="AU34" s="28"/>
-      <c r="AV34" s="17"/>
+      <c r="AV34" s="18"/>
       <c r="AW34" s="17"/>
-      <c r="AX34" s="17"/>
-      <c r="AY34" s="18"/>
+      <c r="AX34" s="28"/>
+      <c r="AY34" s="17"/>
       <c r="AZ34" s="17"/>
       <c r="BA34" s="17"/>
-      <c r="BB34" s="17"/>
-      <c r="BC34" s="18"/>
+      <c r="BB34" s="18"/>
+      <c r="BC34" s="17"/>
       <c r="BD34" s="17"/>
       <c r="BE34" s="17"/>
-      <c r="BF34" s="17"/>
-      <c r="BG34" s="18"/>
-      <c r="BH34" s="18"/>
-      <c r="BI34" s="30"/>
-      <c r="BJ34" s="30"/>
-      <c r="BK34" s="30"/>
+      <c r="BF34" s="18"/>
+      <c r="BG34" s="17"/>
+      <c r="BH34" s="17"/>
+      <c r="BI34" s="17"/>
+      <c r="BJ34" s="18"/>
+      <c r="BK34" s="18"/>
       <c r="BL34" s="30"/>
       <c r="BM34" s="30"/>
-    </row>
-    <row r="35" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="BN34" s="30"/>
+      <c r="BO34" s="30"/>
+      <c r="BP34" s="30"/>
+    </row>
+    <row r="35" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -4662,10 +4837,12 @@
       <c r="L35" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="M35" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="N35" s="30"/>
+      <c r="M35" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="N35" s="30" t="s">
+        <v>126</v>
+      </c>
       <c r="O35" s="30"/>
       <c r="P35" s="30"/>
       <c r="Q35" s="30"/>
@@ -4689,40 +4866,43 @@
       <c r="AI35" s="30"/>
       <c r="AJ35" s="30"/>
       <c r="AK35" s="30"/>
-      <c r="AL35" s="18"/>
+      <c r="AL35" s="30"/>
       <c r="AM35" s="30"/>
-      <c r="AN35" s="19"/>
-      <c r="AO35" s="19"/>
-      <c r="AP35" s="32"/>
-      <c r="AQ35" s="36" t="s">
+      <c r="AN35" s="30"/>
+      <c r="AO35" s="18"/>
+      <c r="AP35" s="30"/>
+      <c r="AQ35" s="19"/>
+      <c r="AR35" s="19"/>
+      <c r="AS35" s="32"/>
+      <c r="AT35" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="AR35" s="34" t="s">
+      <c r="AU35" s="34" t="s">
         <v>160</v>
       </c>
-      <c r="AS35" s="18"/>
-      <c r="AT35" s="17"/>
-      <c r="AU35" s="28"/>
-      <c r="AV35" s="17"/>
+      <c r="AV35" s="18"/>
       <c r="AW35" s="17"/>
-      <c r="AX35" s="17"/>
-      <c r="AY35" s="18"/>
+      <c r="AX35" s="28"/>
+      <c r="AY35" s="17"/>
       <c r="AZ35" s="17"/>
       <c r="BA35" s="17"/>
-      <c r="BB35" s="17"/>
-      <c r="BC35" s="18"/>
+      <c r="BB35" s="18"/>
+      <c r="BC35" s="17"/>
       <c r="BD35" s="17"/>
       <c r="BE35" s="17"/>
-      <c r="BF35" s="17"/>
-      <c r="BG35" s="18"/>
-      <c r="BH35" s="18"/>
-      <c r="BI35" s="30"/>
-      <c r="BJ35" s="30"/>
-      <c r="BK35" s="30"/>
+      <c r="BF35" s="18"/>
+      <c r="BG35" s="17"/>
+      <c r="BH35" s="17"/>
+      <c r="BI35" s="17"/>
+      <c r="BJ35" s="18"/>
+      <c r="BK35" s="18"/>
       <c r="BL35" s="30"/>
       <c r="BM35" s="30"/>
-    </row>
-    <row r="36" spans="1:68" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="BN35" s="30"/>
+      <c r="BO35" s="30"/>
+      <c r="BP35" s="30"/>
+    </row>
+    <row r="36" spans="1:71" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -4756,12 +4936,14 @@
       <c r="M36" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="N36" s="30"/>
+      <c r="N36" s="30" t="s">
+        <v>126</v>
+      </c>
       <c r="O36" s="30"/>
       <c r="P36" s="30"/>
       <c r="Q36" s="30"/>
-      <c r="R36" s="17"/>
-      <c r="S36" s="30"/>
+      <c r="R36" s="30"/>
+      <c r="S36" s="17"/>
       <c r="T36" s="30"/>
       <c r="U36" s="30"/>
       <c r="V36" s="30"/>
@@ -4782,36 +4964,39 @@
       <c r="AK36" s="30"/>
       <c r="AL36" s="30"/>
       <c r="AM36" s="30"/>
-      <c r="AN36" s="19"/>
-      <c r="AO36" s="19"/>
-      <c r="AP36" s="25"/>
-      <c r="AQ36" s="26" t="s">
+      <c r="AN36" s="30"/>
+      <c r="AO36" s="30"/>
+      <c r="AP36" s="30"/>
+      <c r="AQ36" s="19"/>
+      <c r="AR36" s="19"/>
+      <c r="AS36" s="25"/>
+      <c r="AT36" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="AR36" s="19"/>
-      <c r="AS36" s="17"/>
-      <c r="AT36" s="17"/>
-      <c r="AU36" s="17"/>
+      <c r="AU36" s="19"/>
       <c r="AV36" s="17"/>
       <c r="AW36" s="17"/>
       <c r="AX36" s="17"/>
       <c r="AY36" s="17"/>
       <c r="AZ36" s="17"/>
-      <c r="BA36" s="30"/>
-      <c r="BB36" s="30"/>
-      <c r="BC36" s="30"/>
-      <c r="BD36" s="17"/>
-      <c r="BE36" s="17"/>
-      <c r="BF36" s="17"/>
-      <c r="BG36" s="30"/>
-      <c r="BH36" s="30"/>
-      <c r="BI36" s="30"/>
+      <c r="BA36" s="17"/>
+      <c r="BB36" s="17"/>
+      <c r="BC36" s="17"/>
+      <c r="BD36" s="30"/>
+      <c r="BE36" s="30"/>
+      <c r="BF36" s="30"/>
+      <c r="BG36" s="17"/>
+      <c r="BH36" s="17"/>
+      <c r="BI36" s="17"/>
       <c r="BJ36" s="30"/>
       <c r="BK36" s="30"/>
       <c r="BL36" s="30"/>
       <c r="BM36" s="30"/>
-    </row>
-    <row r="37" spans="1:68" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="BN36" s="30"/>
+      <c r="BO36" s="30"/>
+      <c r="BP36" s="30"/>
+    </row>
+    <row r="37" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -4847,12 +5032,14 @@
       <c r="M37" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="N37" s="30"/>
+      <c r="N37" s="30" t="s">
+        <v>130</v>
+      </c>
       <c r="O37" s="30"/>
       <c r="P37" s="30"/>
       <c r="Q37" s="30"/>
-      <c r="R37" s="17"/>
-      <c r="S37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="S37" s="17"/>
       <c r="T37" s="30"/>
       <c r="U37" s="30"/>
       <c r="V37" s="30"/>
@@ -4873,85 +5060,88 @@
       <c r="AK37" s="30"/>
       <c r="AL37" s="30"/>
       <c r="AM37" s="30"/>
-      <c r="AN37" s="19"/>
-      <c r="AO37" s="19"/>
-      <c r="AP37" s="25"/>
-      <c r="AQ37" s="33" t="s">
+      <c r="AN37" s="30"/>
+      <c r="AO37" s="30"/>
+      <c r="AP37" s="30"/>
+      <c r="AQ37" s="19"/>
+      <c r="AR37" s="19"/>
+      <c r="AS37" s="25"/>
+      <c r="AT37" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="AR37" s="34" t="s">
+      <c r="AU37" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="AS37" s="17"/>
-      <c r="AT37" s="17"/>
-      <c r="AU37" s="17"/>
       <c r="AV37" s="17"/>
       <c r="AW37" s="17"/>
       <c r="AX37" s="17"/>
       <c r="AY37" s="17"/>
       <c r="AZ37" s="17"/>
-      <c r="BA37" s="30"/>
-      <c r="BB37" s="30"/>
-      <c r="BC37" s="30"/>
-      <c r="BD37" s="17"/>
-      <c r="BE37" s="17"/>
-      <c r="BF37" s="17"/>
-      <c r="BG37" s="30"/>
-      <c r="BH37" s="30"/>
-      <c r="BI37" s="30"/>
+      <c r="BA37" s="17"/>
+      <c r="BB37" s="17"/>
+      <c r="BC37" s="17"/>
+      <c r="BD37" s="30"/>
+      <c r="BE37" s="30"/>
+      <c r="BF37" s="30"/>
+      <c r="BG37" s="17"/>
+      <c r="BH37" s="17"/>
+      <c r="BI37" s="17"/>
       <c r="BJ37" s="30"/>
       <c r="BK37" s="30"/>
       <c r="BL37" s="30"/>
       <c r="BM37" s="30"/>
-    </row>
-    <row r="38" spans="1:68" x14ac:dyDescent="0.25">
-      <c r="A38" s="51" t="s">
+      <c r="BN37" s="30"/>
+      <c r="BO37" s="30"/>
+      <c r="BP37" s="30"/>
+    </row>
+    <row r="38" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="A38" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="B38" s="52"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="52"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="52"/>
-      <c r="K38" s="52"/>
-      <c r="L38" s="52"/>
-      <c r="M38" s="52"/>
-      <c r="N38" s="52"/>
-      <c r="O38" s="52"/>
-      <c r="P38" s="52"/>
-      <c r="Q38" s="52"/>
-      <c r="R38" s="52"/>
-      <c r="S38" s="52"/>
-      <c r="T38" s="52"/>
-      <c r="U38" s="52"/>
-      <c r="V38" s="52"/>
-      <c r="W38" s="52"/>
-      <c r="X38" s="52"/>
-      <c r="Y38" s="52"/>
-      <c r="Z38" s="52"/>
-      <c r="AA38" s="52"/>
-      <c r="AB38" s="52"/>
-      <c r="AC38" s="52"/>
-      <c r="AD38" s="52"/>
-      <c r="AE38" s="52"/>
-      <c r="AF38" s="52"/>
-      <c r="AG38" s="52"/>
-      <c r="AH38" s="52"/>
-      <c r="AI38" s="52"/>
-      <c r="AJ38" s="52"/>
-      <c r="AK38" s="52"/>
-      <c r="AL38" s="52"/>
-      <c r="AM38" s="52"/>
-      <c r="AN38" s="52"/>
-      <c r="AO38" s="52"/>
-      <c r="AP38" s="53"/>
-      <c r="AQ38" s="2"/>
-      <c r="AR38" s="2"/>
-      <c r="AS38" s="2"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="51"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="51"/>
+      <c r="G38" s="51"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="51"/>
+      <c r="J38" s="51"/>
+      <c r="K38" s="51"/>
+      <c r="L38" s="51"/>
+      <c r="M38" s="51"/>
+      <c r="N38" s="51"/>
+      <c r="O38" s="51"/>
+      <c r="P38" s="51"/>
+      <c r="Q38" s="51"/>
+      <c r="R38" s="51"/>
+      <c r="S38" s="51"/>
+      <c r="T38" s="51"/>
+      <c r="U38" s="51"/>
+      <c r="V38" s="51"/>
+      <c r="W38" s="51"/>
+      <c r="X38" s="51"/>
+      <c r="Y38" s="51"/>
+      <c r="Z38" s="51"/>
+      <c r="AA38" s="51"/>
+      <c r="AB38" s="51"/>
+      <c r="AC38" s="51"/>
+      <c r="AD38" s="51"/>
+      <c r="AE38" s="51"/>
+      <c r="AF38" s="51"/>
+      <c r="AG38" s="51"/>
+      <c r="AH38" s="51"/>
+      <c r="AI38" s="51"/>
+      <c r="AJ38" s="51"/>
+      <c r="AK38" s="51"/>
+      <c r="AL38" s="51"/>
+      <c r="AM38" s="51"/>
+      <c r="AN38" s="51"/>
+      <c r="AO38" s="51"/>
+      <c r="AP38" s="51"/>
+      <c r="AQ38" s="51"/>
+      <c r="AR38" s="51"/>
+      <c r="AS38" s="52"/>
       <c r="AT38" s="2"/>
       <c r="AU38" s="2"/>
       <c r="AV38" s="2"/>
@@ -4972,61 +5162,64 @@
       <c r="BK38" s="2"/>
       <c r="BL38" s="2"/>
       <c r="BM38" s="2"/>
-      <c r="BN38">
+      <c r="BN38" s="2"/>
+      <c r="BO38" s="2"/>
+      <c r="BP38" s="2"/>
+      <c r="BQ38">
         <v>24</v>
       </c>
-      <c r="BP38" t="s">
+      <c r="BS38" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:68" x14ac:dyDescent="0.25">
-      <c r="A39" s="54" t="s">
+    <row r="39" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="A39" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="B39" s="55"/>
-      <c r="C39" s="55"/>
-      <c r="D39" s="55"/>
-      <c r="E39" s="55"/>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55"/>
-      <c r="H39" s="55"/>
-      <c r="I39" s="55"/>
-      <c r="J39" s="55"/>
-      <c r="K39" s="55"/>
-      <c r="L39" s="55"/>
-      <c r="M39" s="55"/>
-      <c r="N39" s="55"/>
-      <c r="O39" s="55"/>
-      <c r="P39" s="55"/>
-      <c r="Q39" s="55"/>
-      <c r="R39" s="55"/>
-      <c r="S39" s="55"/>
-      <c r="T39" s="55"/>
-      <c r="U39" s="55"/>
-      <c r="V39" s="55"/>
-      <c r="W39" s="55"/>
-      <c r="X39" s="55"/>
-      <c r="Y39" s="55"/>
-      <c r="Z39" s="55"/>
-      <c r="AA39" s="55"/>
-      <c r="AB39" s="55"/>
-      <c r="AC39" s="55"/>
-      <c r="AD39" s="55"/>
-      <c r="AE39" s="55"/>
-      <c r="AF39" s="55"/>
-      <c r="AG39" s="55"/>
-      <c r="AH39" s="55"/>
-      <c r="AI39" s="55"/>
-      <c r="AJ39" s="55"/>
-      <c r="AK39" s="55"/>
-      <c r="AL39" s="55"/>
-      <c r="AM39" s="55"/>
-      <c r="AN39" s="55"/>
-      <c r="AO39" s="55"/>
-      <c r="AP39" s="56"/>
-      <c r="AQ39" s="2"/>
-      <c r="AR39" s="2"/>
-      <c r="AS39" s="2"/>
+      <c r="B39" s="54"/>
+      <c r="C39" s="54"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="54"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="54"/>
+      <c r="I39" s="54"/>
+      <c r="J39" s="54"/>
+      <c r="K39" s="54"/>
+      <c r="L39" s="54"/>
+      <c r="M39" s="54"/>
+      <c r="N39" s="54"/>
+      <c r="O39" s="54"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54"/>
+      <c r="R39" s="54"/>
+      <c r="S39" s="54"/>
+      <c r="T39" s="54"/>
+      <c r="U39" s="54"/>
+      <c r="V39" s="54"/>
+      <c r="W39" s="54"/>
+      <c r="X39" s="54"/>
+      <c r="Y39" s="54"/>
+      <c r="Z39" s="54"/>
+      <c r="AA39" s="54"/>
+      <c r="AB39" s="54"/>
+      <c r="AC39" s="54"/>
+      <c r="AD39" s="54"/>
+      <c r="AE39" s="54"/>
+      <c r="AF39" s="54"/>
+      <c r="AG39" s="54"/>
+      <c r="AH39" s="54"/>
+      <c r="AI39" s="54"/>
+      <c r="AJ39" s="54"/>
+      <c r="AK39" s="54"/>
+      <c r="AL39" s="54"/>
+      <c r="AM39" s="54"/>
+      <c r="AN39" s="54"/>
+      <c r="AO39" s="54"/>
+      <c r="AP39" s="54"/>
+      <c r="AQ39" s="54"/>
+      <c r="AR39" s="54"/>
+      <c r="AS39" s="55"/>
       <c r="AT39" s="2"/>
       <c r="AU39" s="2"/>
       <c r="AV39" s="2"/>
@@ -5047,24 +5240,27 @@
       <c r="BK39" s="2"/>
       <c r="BL39" s="2"/>
       <c r="BM39" s="2"/>
-      <c r="BN39">
+      <c r="BN39" s="2"/>
+      <c r="BO39" s="2"/>
+      <c r="BP39" s="2"/>
+      <c r="BQ39">
         <v>25</v>
       </c>
-      <c r="BP39" t="s">
+      <c r="BS39" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:71" x14ac:dyDescent="0.25">
       <c r="D40">
         <v>1</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="16">
         <v>2</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="16">
         <v>3</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="16">
         <v>4</v>
       </c>
       <c r="H40">
@@ -5073,13 +5269,13 @@
       <c r="I40">
         <v>6</v>
       </c>
-      <c r="J40">
+      <c r="J40" s="16">
         <v>7</v>
       </c>
-      <c r="K40">
+      <c r="K40" s="16">
         <v>8</v>
       </c>
-      <c r="L40">
+      <c r="L40" s="16">
         <v>9</v>
       </c>
       <c r="M40">
@@ -5088,13 +5284,13 @@
       <c r="N40">
         <v>11</v>
       </c>
-      <c r="O40">
+      <c r="O40" s="16">
         <v>12</v>
       </c>
-      <c r="P40">
+      <c r="P40" s="16">
         <v>13</v>
       </c>
-      <c r="Q40">
+      <c r="Q40" s="16">
         <v>14</v>
       </c>
       <c r="R40">
@@ -5103,13 +5299,13 @@
       <c r="S40">
         <v>16</v>
       </c>
-      <c r="T40">
+      <c r="T40" s="16">
         <v>17</v>
       </c>
-      <c r="U40">
+      <c r="U40" s="16">
         <v>18</v>
       </c>
-      <c r="V40">
+      <c r="V40" s="16">
         <v>19</v>
       </c>
       <c r="W40">
@@ -5121,50 +5317,56 @@
       <c r="Y40">
         <v>22</v>
       </c>
-      <c r="Z40">
+      <c r="AA40">
         <v>23</v>
       </c>
-      <c r="AA40">
+      <c r="AB40">
         <v>24</v>
       </c>
-      <c r="AB40">
+      <c r="AC40">
         <v>25</v>
       </c>
-      <c r="AC40">
+      <c r="AD40">
         <v>26</v>
       </c>
-      <c r="AD40">
+      <c r="AE40">
         <v>27</v>
       </c>
-      <c r="AE40">
+      <c r="AF40">
         <v>28</v>
       </c>
-      <c r="AF40">
+      <c r="AG40">
         <v>29</v>
       </c>
-      <c r="AG40">
+      <c r="AH40">
         <v>30</v>
       </c>
-      <c r="AH40">
+      <c r="AI40">
+        <v>29</v>
+      </c>
+      <c r="AJ40">
+        <v>30</v>
+      </c>
+      <c r="AK40">
         <v>31</v>
       </c>
-      <c r="AI40">
+      <c r="AL40">
         <v>32</v>
       </c>
-      <c r="AJ40">
+      <c r="AM40">
         <v>33</v>
       </c>
-      <c r="AK40">
+      <c r="AN40">
         <v>34</v>
       </c>
-      <c r="BN40">
+      <c r="BQ40">
         <v>26</v>
       </c>
-      <c r="BP40" t="s">
+      <c r="BS40" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" t="s">
         <v>131</v>
       </c>
@@ -5205,29 +5407,80 @@
         <v>131</v>
       </c>
       <c r="Q41" t="s">
+        <v>131</v>
+      </c>
+      <c r="R41" t="s">
         <v>132</v>
       </c>
-      <c r="R41" t="s">
+      <c r="S41" t="s">
         <v>131</v>
       </c>
-      <c r="S41" t="s">
+      <c r="T41" t="s">
         <v>132</v>
       </c>
-      <c r="T41" t="s">
+      <c r="U41" t="s">
         <v>131</v>
       </c>
-      <c r="U41" t="s">
+      <c r="V41" t="s">
+        <v>131</v>
+      </c>
+      <c r="W41" t="s">
         <v>132</v>
       </c>
-      <c r="AX41"/>
-      <c r="BN41">
+      <c r="X41" t="s">
+        <v>131</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>132</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>131</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>131</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>132</v>
+      </c>
+      <c r="AD41" t="s">
+        <v>131</v>
+      </c>
+      <c r="AE41" t="s">
+        <v>132</v>
+      </c>
+      <c r="AF41" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG41" t="s">
+        <v>131</v>
+      </c>
+      <c r="AH41" t="s">
+        <v>132</v>
+      </c>
+      <c r="AI41" t="s">
+        <v>131</v>
+      </c>
+      <c r="AJ41" t="s">
+        <v>132</v>
+      </c>
+      <c r="AK41" t="s">
+        <v>131</v>
+      </c>
+      <c r="AL41" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM41" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA41"/>
+      <c r="BQ41">
         <v>27</v>
       </c>
-      <c r="BP41" t="s">
+      <c r="BS41" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="16" t="s">
         <v>134</v>
       </c>
@@ -5246,23 +5499,23 @@
       <c r="O42" t="s">
         <v>68</v>
       </c>
-      <c r="P42" t="s">
+      <c r="Q42" t="s">
         <v>68</v>
       </c>
-      <c r="Q42" t="s">
+      <c r="R42" t="s">
         <v>69</v>
       </c>
-      <c r="AZ42" t="s">
+      <c r="BC42" t="s">
         <v>72</v>
       </c>
-      <c r="BN42">
+      <c r="BQ42">
         <v>28</v>
       </c>
-      <c r="BP42" t="s">
+      <c r="BS42" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E43" s="16" t="s">
         <v>133</v>
       </c>
@@ -5279,21 +5532,21 @@
       <c r="N43" t="s">
         <v>74</v>
       </c>
-      <c r="R43" t="s">
+      <c r="S43" t="s">
         <v>75</v>
       </c>
-      <c r="AZ43" t="s">
+      <c r="BC43" t="s">
         <v>76</v>
       </c>
-      <c r="BN43" s="14">
+      <c r="BQ43" s="14">
         <v>29</v>
       </c>
-      <c r="BO43" s="14"/>
-      <c r="BP43" s="14" t="s">
+      <c r="BR43" s="14"/>
+      <c r="BS43" s="14" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" t="s">
         <v>77</v>
       </c>
@@ -5303,265 +5556,269 @@
       <c r="N44" t="s">
         <v>78</v>
       </c>
-      <c r="S44" t="s">
+      <c r="T44" t="s">
         <v>79</v>
       </c>
-      <c r="AN44" t="s">
+      <c r="AQ44" t="s">
         <v>62</v>
       </c>
-      <c r="AO44" s="5" t="s">
+      <c r="AR44" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="BN44">
+      <c r="BQ44">
         <v>30</v>
       </c>
-      <c r="BP44" t="s">
+      <c r="BS44" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" t="s">
         <v>80</v>
       </c>
-      <c r="T45" t="s">
+      <c r="V45" t="s">
         <v>81</v>
       </c>
-      <c r="AN45" t="s">
+      <c r="AQ45" t="s">
         <v>64</v>
       </c>
-      <c r="AO45" t="s">
+      <c r="AR45" t="s">
         <v>65</v>
       </c>
-      <c r="BN45">
+      <c r="BQ45">
         <v>31</v>
       </c>
-      <c r="BP45" t="s">
+      <c r="BS45" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="46" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" t="s">
         <v>83</v>
       </c>
-      <c r="AN46" t="s">
+      <c r="AQ46" t="s">
         <v>70</v>
       </c>
-      <c r="AO46" t="s">
+      <c r="AR46" t="s">
         <v>71</v>
       </c>
-      <c r="BN46" s="14">
+      <c r="BQ46" s="14">
         <v>32</v>
       </c>
-      <c r="BO46" s="14"/>
-      <c r="BP46" s="14" t="s">
+      <c r="BR46" s="14"/>
+      <c r="BS46" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN47">
+    <row r="47" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BQ47">
         <v>33</v>
       </c>
-      <c r="BP47" t="s">
+      <c r="BS47" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN48">
+    <row r="48" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BQ48">
         <v>34</v>
       </c>
-      <c r="BP48" s="6" t="s">
+      <c r="BS48" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="49" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN49">
+    <row r="49" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BQ49">
         <v>35</v>
       </c>
-      <c r="BP49" t="s">
+      <c r="BS49" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN50" s="37">
+    <row r="50" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BQ50" s="37">
         <v>36</v>
       </c>
-      <c r="BO50" s="37"/>
-      <c r="BP50" s="37" t="s">
+      <c r="BR50" s="37"/>
+      <c r="BS50" s="37" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BP51" t="s">
+    <row r="51" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BS51" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="53" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BP53" s="8"/>
-      <c r="BQ53" s="9"/>
-      <c r="BR53" s="8"/>
-    </row>
-    <row r="54" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BN54">
+    <row r="53" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BS53" s="8"/>
+      <c r="BT53" s="9"/>
+      <c r="BU53" s="8"/>
+    </row>
+    <row r="54" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BQ54">
         <v>37</v>
       </c>
-      <c r="BP54" s="13" t="s">
+      <c r="BS54" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="BQ54" s="10"/>
-      <c r="BR54" s="10"/>
-    </row>
-    <row r="55" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BN55">
+      <c r="BT54" s="10"/>
+      <c r="BU54" s="10"/>
+    </row>
+    <row r="55" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BQ55">
         <v>38</v>
       </c>
-      <c r="BP55" s="13" t="s">
+      <c r="BS55" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="BQ55" s="11" t="s">
+      <c r="BT55" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="BR55" s="8" t="s">
+      <c r="BU55" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="BS55">
+      <c r="BV55">
         <v>49</v>
       </c>
     </row>
-    <row r="56" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BP56" s="10"/>
-      <c r="BQ56" s="11" t="s">
+    <row r="56" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BS56" s="10"/>
+      <c r="BT56" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="BR56" s="8" t="s">
+      <c r="BU56" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="BS56">
+      <c r="BV56">
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BN57">
+    <row r="57" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BQ57">
         <v>39</v>
       </c>
-      <c r="BP57" s="8" t="s">
+      <c r="BS57" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="BQ57" s="11" t="s">
+      <c r="BT57" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="BR57" s="8" t="s">
+      <c r="BU57" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="BS57">
+      <c r="BV57">
         <v>51</v>
       </c>
     </row>
-    <row r="58" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BN58">
+    <row r="58" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BQ58">
         <v>40</v>
       </c>
-      <c r="BP58" s="11" t="s">
+      <c r="BS58" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="BQ58" s="10"/>
-      <c r="BR58" s="10"/>
-    </row>
-    <row r="59" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BN59" s="16">
+      <c r="BT58" s="10"/>
+      <c r="BU58" s="10"/>
+    </row>
+    <row r="59" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BQ59" s="16">
         <v>41</v>
       </c>
-      <c r="BP59" s="8" t="s">
+      <c r="BS59" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="BQ59" s="10"/>
-      <c r="BR59" s="10"/>
-    </row>
-    <row r="60" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BN60">
+      <c r="BT59" s="10"/>
+      <c r="BU59" s="10"/>
+    </row>
+    <row r="60" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BQ60">
         <v>42</v>
       </c>
-      <c r="BP60" s="8" t="s">
+      <c r="BS60" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="BQ60" s="10"/>
-      <c r="BR60" s="10"/>
-    </row>
-    <row r="61" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BN61">
+      <c r="BT60" s="10"/>
+      <c r="BU60" s="10"/>
+    </row>
+    <row r="61" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BQ61">
         <v>43</v>
       </c>
-      <c r="BP61" s="8" t="s">
+      <c r="BS61" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="BQ61" s="10"/>
-      <c r="BR61" s="10"/>
-    </row>
-    <row r="62" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BN62">
+      <c r="BT61" s="10"/>
+      <c r="BU61" s="10"/>
+    </row>
+    <row r="62" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BQ62">
         <v>44</v>
       </c>
-      <c r="BP62" s="8" t="s">
+      <c r="BS62" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="BQ62" s="10"/>
-      <c r="BR62" s="10"/>
-    </row>
-    <row r="63" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BN63">
+      <c r="BT62" s="10"/>
+      <c r="BU62" s="10"/>
+    </row>
+    <row r="63" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BQ63">
         <v>45</v>
       </c>
-      <c r="BP63" s="8" t="s">
+      <c r="BS63" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="BQ63" s="10"/>
-      <c r="BR63" s="10"/>
-    </row>
-    <row r="64" spans="66:71" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BN64" s="16">
+      <c r="BT63" s="10"/>
+      <c r="BU63" s="10"/>
+    </row>
+    <row r="64" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BQ64" s="16">
         <v>46</v>
       </c>
-      <c r="BP64" s="8" t="s">
+      <c r="BS64" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="BQ64" s="10"/>
-      <c r="BR64" s="10"/>
-    </row>
-    <row r="65" spans="66:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN65">
+      <c r="BT64" s="10"/>
+      <c r="BU64" s="10"/>
+    </row>
+    <row r="65" spans="69:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BQ65">
         <v>47</v>
       </c>
-      <c r="BP65" t="s">
+      <c r="BS65" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="66" spans="66:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN66">
+    <row r="66" spans="69:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BQ66">
         <v>48</v>
       </c>
-      <c r="BP66" t="s">
+      <c r="BS66" t="s">
         <v>92</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="49">
-    <mergeCell ref="AK2:AK3"/>
-    <mergeCell ref="BK2:BM3"/>
-    <mergeCell ref="A38:AP38"/>
-    <mergeCell ref="A39:AP39"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="AL2:AL3"/>
+  <mergeCells count="52">
     <mergeCell ref="AM2:AM3"/>
     <mergeCell ref="P2:P3"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="AZ2:BC3"/>
-    <mergeCell ref="BD2:BG3"/>
-    <mergeCell ref="BH2:BJ3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="A1:AP1"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="AZ2:BB3"/>
+    <mergeCell ref="AT2:AV3"/>
+    <mergeCell ref="AW2:AY3"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="AH2:AH3"/>
+    <mergeCell ref="AI2:AI3"/>
+    <mergeCell ref="AJ2:AJ3"/>
+    <mergeCell ref="AK2:AK3"/>
+    <mergeCell ref="AL2:AL3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="A1:AS1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
@@ -5573,31 +5830,30 @@
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
-    <mergeCell ref="AN2:AP3"/>
+    <mergeCell ref="AQ2:AS3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="AN2:AN3"/>
+    <mergeCell ref="BN2:BP3"/>
+    <mergeCell ref="A38:AS38"/>
+    <mergeCell ref="A39:AS39"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="AO2:AO3"/>
+    <mergeCell ref="AP2:AP3"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="S2:S3"/>
     <mergeCell ref="V2:V3"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="AW2:AY3"/>
-    <mergeCell ref="AQ2:AS3"/>
-    <mergeCell ref="AT2:AV3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="AH2:AH3"/>
-    <mergeCell ref="AI2:AI3"/>
-    <mergeCell ref="AJ2:AJ3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="BC2:BF3"/>
+    <mergeCell ref="BG2:BJ3"/>
+    <mergeCell ref="BK2:BM3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="BP6" r:id="rId1" display="Прикладная дискретная математика. Приложение. 2016. № 9. С. 68-70."/>
-    <hyperlink ref="BO26" r:id="rId2"/>
-    <hyperlink ref="BP48" r:id="rId3"/>
+    <hyperlink ref="BS6" r:id="rId1" display="Прикладная дискретная математика. Приложение. 2016. № 9. С. 68-70." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="BR26" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="BS48" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId4"/>
@@ -5606,14 +5862,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b78dbef7-f85b-47b5-8738-6377d50f4027" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bffb7b91-0466-4de0-9379-f5c53c3acedf">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5818,21 +6072,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b78dbef7-f85b-47b5-8738-6377d50f4027" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bffb7b91-0466-4de0-9379-f5c53c3acedf">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12ECB55F-B88E-4FE2-9AD5-5CA5D433F306}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00280879-8A9A-4335-93BC-405126DC8F0C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b78dbef7-f85b-47b5-8738-6377d50f4027"/>
-    <ds:schemaRef ds:uri="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5857,9 +6110,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00280879-8A9A-4335-93BC-405126DC8F0C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12ECB55F-B88E-4FE2-9AD5-5CA5D433F306}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b78dbef7-f85b-47b5-8738-6377d50f4027"/>
+    <ds:schemaRef ds:uri="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Ведомость ТКИ-441 2026-2027.xlsx
+++ b/Ведомость ТКИ-441 2026-2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\StegMethods\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7294C5F-390D-4784-84A7-EE088D54566A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756FC710-54A7-424C-BCAA-0AA3A6CF73F2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="186">
   <si>
     <t>Ведомость посещаемости занятий студентами группы ТКИ РУТ МИИТ</t>
   </si>
@@ -581,6 +581,9 @@
   </si>
   <si>
     <t>ДПФ</t>
+  </si>
+  <si>
+    <t>Тесты</t>
   </si>
 </sst>
 </file>
@@ -846,7 +849,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -929,12 +932,25 @@
     <xf numFmtId="14" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -953,22 +969,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -991,16 +995,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>166255</xdr:rowOff>
+      <xdr:col>58</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>98219</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>638175</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>78427</xdr:rowOff>
+      <xdr:col>65</xdr:col>
+      <xdr:colOff>406853</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>119248</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1023,8 +1027,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29307559" y="8714510"/>
-          <a:ext cx="4761634" cy="4913662"/>
+          <a:off x="44122521" y="3799362"/>
+          <a:ext cx="4644118" cy="4865172"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1332,153 +1336,153 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="60"/>
-      <c r="T1" s="60"/>
-      <c r="U1" s="60"/>
-      <c r="V1" s="60"/>
-      <c r="W1" s="60"/>
-      <c r="X1" s="60"/>
-      <c r="Y1" s="60"/>
-      <c r="Z1" s="60"/>
-      <c r="AA1" s="60"/>
-      <c r="AB1" s="60"/>
-      <c r="AC1" s="60"/>
-      <c r="AD1" s="60"/>
-      <c r="AE1" s="60"/>
-      <c r="AF1" s="60"/>
-      <c r="AG1" s="60"/>
-      <c r="AH1" s="60"/>
-      <c r="AI1" s="60"/>
-      <c r="AJ1" s="60"/>
-      <c r="AK1" s="60"/>
-      <c r="AL1" s="60"/>
-      <c r="AM1" s="60"/>
-      <c r="AN1" s="60"/>
-      <c r="AO1" s="60"/>
-      <c r="AP1" s="60"/>
-      <c r="AQ1" s="60"/>
-      <c r="AR1" s="60"/>
-      <c r="AS1" s="60"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="52"/>
+      <c r="V1" s="52"/>
+      <c r="W1" s="52"/>
+      <c r="X1" s="52"/>
+      <c r="Y1" s="52"/>
+      <c r="Z1" s="52"/>
+      <c r="AA1" s="52"/>
+      <c r="AB1" s="52"/>
+      <c r="AC1" s="52"/>
+      <c r="AD1" s="52"/>
+      <c r="AE1" s="52"/>
+      <c r="AF1" s="52"/>
+      <c r="AG1" s="52"/>
+      <c r="AH1" s="52"/>
+      <c r="AI1" s="52"/>
+      <c r="AJ1" s="52"/>
+      <c r="AK1" s="52"/>
+      <c r="AL1" s="52"/>
+      <c r="AM1" s="52"/>
+      <c r="AN1" s="52"/>
+      <c r="AO1" s="52"/>
+      <c r="AP1" s="52"/>
+      <c r="AQ1" s="52"/>
+      <c r="AR1" s="52"/>
+      <c r="AS1" s="52"/>
     </row>
     <row r="2" spans="1:73" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="59" t="s">
+      <c r="B2" s="53"/>
+      <c r="C2" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="56">
+      <c r="D2" s="44">
         <v>46268</v>
       </c>
-      <c r="E2" s="56">
+      <c r="E2" s="44">
         <v>46272</v>
       </c>
-      <c r="F2" s="56">
+      <c r="F2" s="44">
         <v>46273</v>
       </c>
-      <c r="G2" s="56">
+      <c r="G2" s="44">
         <v>46275</v>
       </c>
-      <c r="H2" s="56">
+      <c r="H2" s="44">
         <v>46279</v>
       </c>
       <c r="I2" s="42">
         <v>46282</v>
       </c>
-      <c r="J2" s="56">
+      <c r="J2" s="44">
         <v>46286</v>
       </c>
-      <c r="K2" s="56">
+      <c r="K2" s="44">
         <v>46287</v>
       </c>
       <c r="L2" s="42">
         <v>46289</v>
       </c>
-      <c r="M2" s="56">
+      <c r="M2" s="44">
         <v>46293</v>
       </c>
       <c r="N2" s="42">
         <v>46296</v>
       </c>
-      <c r="O2" s="56">
+      <c r="O2" s="44">
         <v>46300</v>
       </c>
-      <c r="P2" s="56">
+      <c r="P2" s="44">
         <v>46301</v>
       </c>
       <c r="Q2" s="42">
         <v>46303</v>
       </c>
-      <c r="R2" s="56">
+      <c r="R2" s="44">
         <v>46307</v>
       </c>
       <c r="S2" s="42">
         <v>46310</v>
       </c>
-      <c r="T2" s="56">
+      <c r="T2" s="44">
         <v>46314</v>
       </c>
-      <c r="U2" s="56">
+      <c r="U2" s="44">
         <v>46315</v>
       </c>
       <c r="V2" s="42">
         <v>46317</v>
       </c>
-      <c r="W2" s="56">
+      <c r="W2" s="44">
         <v>46321</v>
       </c>
-      <c r="X2" s="56">
+      <c r="X2" s="44">
         <v>46324</v>
       </c>
-      <c r="Y2" s="56">
+      <c r="Y2" s="44">
         <v>46328</v>
       </c>
-      <c r="Z2" s="56">
+      <c r="Z2" s="44">
         <v>46328</v>
       </c>
-      <c r="AA2" s="56">
+      <c r="AA2" s="44">
         <v>46331</v>
       </c>
-      <c r="AB2" s="56">
+      <c r="AB2" s="44">
         <v>46335</v>
       </c>
-      <c r="AC2" s="56">
+      <c r="AC2" s="44">
         <v>46338</v>
       </c>
-      <c r="AD2" s="56">
+      <c r="AD2" s="44">
         <v>46342</v>
       </c>
-      <c r="AE2" s="56">
+      <c r="AE2" s="44">
         <v>46345</v>
       </c>
-      <c r="AF2" s="56">
+      <c r="AF2" s="44">
         <v>46349</v>
       </c>
-      <c r="AG2" s="56">
+      <c r="AG2" s="44">
         <v>46352</v>
       </c>
-      <c r="AH2" s="56">
+      <c r="AH2" s="44">
         <v>46356</v>
       </c>
       <c r="AI2" s="42">
@@ -1499,54 +1503,54 @@
       <c r="AN2" s="42">
         <v>46377</v>
       </c>
-      <c r="AO2" s="58" t="s">
+      <c r="AO2" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="AP2" s="58"/>
-      <c r="AQ2" s="44" t="s">
+      <c r="AP2" s="53"/>
+      <c r="AQ2" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="AR2" s="45"/>
-      <c r="AS2" s="46"/>
-      <c r="AT2" s="44" t="s">
+      <c r="AR2" s="47"/>
+      <c r="AS2" s="48"/>
+      <c r="AT2" s="46" t="s">
         <v>169</v>
       </c>
-      <c r="AU2" s="45"/>
-      <c r="AV2" s="46"/>
-      <c r="AW2" s="44" t="s">
+      <c r="AU2" s="47"/>
+      <c r="AV2" s="48"/>
+      <c r="AW2" s="46" t="s">
         <v>170</v>
       </c>
-      <c r="AX2" s="45"/>
-      <c r="AY2" s="46"/>
-      <c r="AZ2" s="44" t="s">
+      <c r="AX2" s="47"/>
+      <c r="AY2" s="48"/>
+      <c r="AZ2" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="BA2" s="45"/>
-      <c r="BB2" s="46"/>
-      <c r="BC2" s="44" t="s">
+      <c r="BA2" s="47"/>
+      <c r="BB2" s="48"/>
+      <c r="BC2" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="BD2" s="45"/>
-      <c r="BE2" s="45"/>
-      <c r="BF2" s="46"/>
-      <c r="BG2" s="44" t="s">
+      <c r="BD2" s="47"/>
+      <c r="BE2" s="47"/>
+      <c r="BF2" s="48"/>
+      <c r="BG2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="BH2" s="45"/>
-      <c r="BI2" s="45"/>
-      <c r="BJ2" s="46" t="s">
+      <c r="BH2" s="47"/>
+      <c r="BI2" s="47"/>
+      <c r="BJ2" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="BK2" s="44" t="s">
+      <c r="BK2" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="BL2" s="45"/>
-      <c r="BM2" s="46"/>
-      <c r="BN2" s="44" t="s">
+      <c r="BL2" s="47"/>
+      <c r="BM2" s="48"/>
+      <c r="BN2" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="BO2" s="45"/>
-      <c r="BP2" s="46"/>
+      <c r="BO2" s="47"/>
+      <c r="BP2" s="48"/>
     </row>
     <row r="3" spans="1:73" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1555,72 +1559,72 @@
       <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
       <c r="I3" s="43"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
       <c r="L3" s="43"/>
-      <c r="M3" s="57"/>
+      <c r="M3" s="45"/>
       <c r="N3" s="43"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="57"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="45"/>
       <c r="Q3" s="43"/>
-      <c r="R3" s="57"/>
+      <c r="R3" s="45"/>
       <c r="S3" s="43"/>
-      <c r="T3" s="57"/>
-      <c r="U3" s="57"/>
+      <c r="T3" s="45"/>
+      <c r="U3" s="45"/>
       <c r="V3" s="43"/>
-      <c r="W3" s="57"/>
-      <c r="X3" s="57"/>
-      <c r="Y3" s="57"/>
-      <c r="Z3" s="57"/>
-      <c r="AA3" s="57"/>
-      <c r="AB3" s="57"/>
-      <c r="AC3" s="57"/>
-      <c r="AD3" s="57"/>
-      <c r="AE3" s="57"/>
-      <c r="AF3" s="57"/>
-      <c r="AG3" s="57"/>
-      <c r="AH3" s="57"/>
+      <c r="W3" s="45"/>
+      <c r="X3" s="45"/>
+      <c r="Y3" s="45"/>
+      <c r="Z3" s="45"/>
+      <c r="AA3" s="45"/>
+      <c r="AB3" s="45"/>
+      <c r="AC3" s="45"/>
+      <c r="AD3" s="45"/>
+      <c r="AE3" s="45"/>
+      <c r="AF3" s="45"/>
+      <c r="AG3" s="45"/>
+      <c r="AH3" s="45"/>
       <c r="AI3" s="43"/>
       <c r="AJ3" s="43"/>
       <c r="AK3" s="43"/>
       <c r="AL3" s="43"/>
       <c r="AM3" s="43"/>
       <c r="AN3" s="43"/>
-      <c r="AO3" s="58"/>
-      <c r="AP3" s="58"/>
-      <c r="AQ3" s="47"/>
-      <c r="AR3" s="61"/>
-      <c r="AS3" s="49"/>
-      <c r="AT3" s="47"/>
-      <c r="AU3" s="48"/>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="47"/>
-      <c r="AX3" s="48"/>
-      <c r="AY3" s="49"/>
-      <c r="AZ3" s="47"/>
-      <c r="BA3" s="48"/>
-      <c r="BB3" s="49"/>
-      <c r="BC3" s="47"/>
-      <c r="BD3" s="48"/>
-      <c r="BE3" s="48"/>
-      <c r="BF3" s="49"/>
-      <c r="BG3" s="47"/>
-      <c r="BH3" s="48"/>
-      <c r="BI3" s="48"/>
-      <c r="BJ3" s="49"/>
-      <c r="BK3" s="47"/>
-      <c r="BL3" s="48"/>
-      <c r="BM3" s="49"/>
-      <c r="BN3" s="47"/>
-      <c r="BO3" s="48"/>
-      <c r="BP3" s="49"/>
+      <c r="AO3" s="53"/>
+      <c r="AP3" s="53"/>
+      <c r="AQ3" s="49"/>
+      <c r="AR3" s="54"/>
+      <c r="AS3" s="51"/>
+      <c r="AT3" s="49"/>
+      <c r="AU3" s="50"/>
+      <c r="AV3" s="51"/>
+      <c r="AW3" s="49"/>
+      <c r="AX3" s="50"/>
+      <c r="AY3" s="51"/>
+      <c r="AZ3" s="49"/>
+      <c r="BA3" s="50"/>
+      <c r="BB3" s="51"/>
+      <c r="BC3" s="49"/>
+      <c r="BD3" s="50"/>
+      <c r="BE3" s="50"/>
+      <c r="BF3" s="51"/>
+      <c r="BG3" s="49"/>
+      <c r="BH3" s="50"/>
+      <c r="BI3" s="50"/>
+      <c r="BJ3" s="51"/>
+      <c r="BK3" s="49"/>
+      <c r="BL3" s="50"/>
+      <c r="BM3" s="51"/>
+      <c r="BN3" s="49"/>
+      <c r="BO3" s="50"/>
+      <c r="BP3" s="51"/>
     </row>
     <row r="4" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
@@ -1659,7 +1663,9 @@
       <c r="N4" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="O4" s="17"/>
+      <c r="O4" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P4" s="17"/>
       <c r="Q4" s="17"/>
       <c r="R4" s="17"/>
@@ -1763,7 +1769,9 @@
       <c r="N5" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="O5" s="17"/>
+      <c r="O5" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P5" s="17"/>
       <c r="Q5" s="17"/>
       <c r="R5" s="17"/>
@@ -1792,7 +1800,9 @@
       <c r="AO5" s="18"/>
       <c r="AP5" s="17"/>
       <c r="AQ5" s="19"/>
-      <c r="AR5" s="19"/>
+      <c r="AR5" s="41" t="s">
+        <v>185</v>
+      </c>
       <c r="AS5" s="21"/>
       <c r="AT5" s="33" t="s">
         <v>139</v>
@@ -1882,7 +1892,9 @@
       <c r="N6" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="O6" s="17"/>
+      <c r="O6" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P6" s="17"/>
       <c r="Q6" s="17"/>
       <c r="R6" s="17"/>
@@ -1911,7 +1923,9 @@
       <c r="AO6" s="18"/>
       <c r="AP6" s="17"/>
       <c r="AQ6" s="19"/>
-      <c r="AR6" s="19"/>
+      <c r="AR6" s="62" t="s">
+        <v>185</v>
+      </c>
       <c r="AS6" s="21"/>
       <c r="AT6" s="33" t="s">
         <v>141</v>
@@ -1990,7 +2004,9 @@
       <c r="N7" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="O7" s="24"/>
+      <c r="O7" s="24" t="s">
+        <v>126</v>
+      </c>
       <c r="P7" s="24"/>
       <c r="Q7" s="17"/>
       <c r="R7" s="17"/>
@@ -2019,7 +2035,9 @@
       <c r="AO7" s="17"/>
       <c r="AP7" s="17"/>
       <c r="AQ7" s="19"/>
-      <c r="AR7" s="41"/>
+      <c r="AR7" s="41" t="s">
+        <v>185</v>
+      </c>
       <c r="AS7" s="25"/>
       <c r="AT7" s="20" t="s">
         <v>144</v>
@@ -2098,7 +2116,9 @@
       <c r="N8" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="O8" s="17"/>
+      <c r="O8" s="17" t="s">
+        <v>127</v>
+      </c>
       <c r="P8" s="17"/>
       <c r="Q8" s="17"/>
       <c r="R8" s="17"/>
@@ -2206,7 +2226,9 @@
       <c r="N9" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="O9" s="17"/>
+      <c r="O9" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P9" s="17"/>
       <c r="Q9" s="17"/>
       <c r="R9" s="17"/>
@@ -2235,7 +2257,7 @@
       <c r="AO9" s="18"/>
       <c r="AP9" s="17"/>
       <c r="AQ9" s="19"/>
-      <c r="AR9" s="19"/>
+      <c r="AR9" s="41"/>
       <c r="AS9" s="21"/>
       <c r="AT9" s="27" t="s">
         <v>147</v>
@@ -2312,7 +2334,9 @@
       <c r="N10" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="O10" s="17"/>
+      <c r="O10" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P10" s="17"/>
       <c r="Q10" s="17"/>
       <c r="R10" s="17"/>
@@ -2341,7 +2365,7 @@
       <c r="AO10" s="18"/>
       <c r="AP10" s="17"/>
       <c r="AQ10" s="19"/>
-      <c r="AR10" s="19"/>
+      <c r="AR10" s="62"/>
       <c r="AS10" s="21"/>
       <c r="AT10" s="33" t="s">
         <v>145</v>
@@ -2418,7 +2442,9 @@
       <c r="N11" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="O11" s="17"/>
+      <c r="O11" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P11" s="17"/>
       <c r="Q11" s="17"/>
       <c r="R11" s="17"/>
@@ -2447,7 +2473,9 @@
       <c r="AO11" s="18"/>
       <c r="AP11" s="17"/>
       <c r="AQ11" s="19"/>
-      <c r="AR11" s="41"/>
+      <c r="AR11" s="41" t="s">
+        <v>185</v>
+      </c>
       <c r="AS11" s="21"/>
       <c r="AT11" s="33" t="s">
         <v>153</v>
@@ -2526,7 +2554,9 @@
       <c r="N12" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="O12" s="17"/>
+      <c r="O12" s="17" t="s">
+        <v>127</v>
+      </c>
       <c r="P12" s="17"/>
       <c r="Q12" s="17"/>
       <c r="R12" s="17"/>
@@ -2630,7 +2660,9 @@
       <c r="N13" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="O13" s="17"/>
+      <c r="O13" s="17" t="s">
+        <v>127</v>
+      </c>
       <c r="P13" s="17"/>
       <c r="Q13" s="17"/>
       <c r="R13" s="17"/>
@@ -2732,7 +2764,9 @@
       <c r="N14" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="O14" s="17"/>
+      <c r="O14" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P14" s="17"/>
       <c r="Q14" s="23"/>
       <c r="R14" s="17"/>
@@ -2761,7 +2795,7 @@
       <c r="AO14" s="17"/>
       <c r="AP14" s="17"/>
       <c r="AQ14" s="19"/>
-      <c r="AR14" s="19"/>
+      <c r="AR14" s="41"/>
       <c r="AS14" s="25"/>
       <c r="AT14" s="36" t="s">
         <v>159</v>
@@ -2834,7 +2868,9 @@
       <c r="N15" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="O15" s="17"/>
+      <c r="O15" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P15" s="17"/>
       <c r="Q15" s="17"/>
       <c r="R15" s="17"/>
@@ -2863,7 +2899,9 @@
       <c r="AO15" s="18"/>
       <c r="AP15" s="17"/>
       <c r="AQ15" s="19"/>
-      <c r="AR15" s="19"/>
+      <c r="AR15" s="41" t="s">
+        <v>185</v>
+      </c>
       <c r="AS15" s="18"/>
       <c r="AT15" s="33" t="s">
         <v>153</v>
@@ -2936,7 +2974,9 @@
       <c r="N16" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="O16" s="17"/>
+      <c r="O16" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P16" s="17"/>
       <c r="Q16" s="17"/>
       <c r="R16" s="17"/>
@@ -3042,7 +3082,9 @@
       <c r="N17" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="O17" s="17"/>
+      <c r="O17" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P17" s="17"/>
       <c r="Q17" s="17"/>
       <c r="R17" s="17"/>
@@ -3071,7 +3113,9 @@
       <c r="AO17" s="18"/>
       <c r="AP17" s="17"/>
       <c r="AQ17" s="19"/>
-      <c r="AR17" s="19"/>
+      <c r="AR17" s="62" t="s">
+        <v>185</v>
+      </c>
       <c r="AS17" s="21"/>
       <c r="AT17" s="33" t="s">
         <v>161</v>
@@ -3146,7 +3190,9 @@
       <c r="N18" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="O18" s="17"/>
+      <c r="O18" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P18" s="17"/>
       <c r="Q18" s="17"/>
       <c r="R18" s="17"/>
@@ -3175,7 +3221,7 @@
       <c r="AO18" s="18"/>
       <c r="AP18" s="17"/>
       <c r="AQ18" s="19"/>
-      <c r="AR18" s="19"/>
+      <c r="AR18" s="62"/>
       <c r="AS18" s="21"/>
       <c r="AT18" s="35" t="s">
         <v>163</v>
@@ -3248,7 +3294,9 @@
       <c r="N19" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="O19" s="17"/>
+      <c r="O19" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P19" s="17"/>
       <c r="Q19" s="17"/>
       <c r="R19" s="17"/>
@@ -3277,7 +3325,9 @@
       <c r="AO19" s="18"/>
       <c r="AP19" s="17"/>
       <c r="AQ19" s="19"/>
-      <c r="AR19" s="41"/>
+      <c r="AR19" s="62" t="s">
+        <v>185</v>
+      </c>
       <c r="AS19" s="21"/>
       <c r="AT19" s="33" t="s">
         <v>161</v>
@@ -3350,7 +3400,9 @@
       <c r="N20" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="O20" s="17"/>
+      <c r="O20" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P20" s="17"/>
       <c r="Q20" s="17"/>
       <c r="R20" s="17"/>
@@ -3379,7 +3431,7 @@
       <c r="AO20" s="18"/>
       <c r="AP20" s="17"/>
       <c r="AQ20" s="19"/>
-      <c r="AR20" s="19"/>
+      <c r="AR20" s="41"/>
       <c r="AS20" s="21"/>
       <c r="AT20" s="27" t="s">
         <v>147</v>
@@ -3452,7 +3504,9 @@
       <c r="N21" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="O21" s="17"/>
+      <c r="O21" s="17" t="s">
+        <v>127</v>
+      </c>
       <c r="P21" s="17"/>
       <c r="Q21" s="17"/>
       <c r="R21" s="17"/>
@@ -3554,7 +3608,9 @@
       <c r="N22" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="O22" s="17"/>
+      <c r="O22" s="17" t="s">
+        <v>127</v>
+      </c>
       <c r="P22" s="17"/>
       <c r="Q22" s="17"/>
       <c r="R22" s="17"/>
@@ -3656,7 +3712,9 @@
       <c r="N23" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="O23" s="17"/>
+      <c r="O23" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P23" s="17"/>
       <c r="Q23" s="17"/>
       <c r="R23" s="23"/>
@@ -3756,7 +3814,9 @@
       <c r="N24" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="O24" s="17"/>
+      <c r="O24" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P24" s="17"/>
       <c r="Q24" s="17"/>
       <c r="R24" s="17"/>
@@ -3785,7 +3845,9 @@
       <c r="AO24" s="17"/>
       <c r="AP24" s="17"/>
       <c r="AQ24" s="19"/>
-      <c r="AR24" s="19"/>
+      <c r="AR24" s="41" t="s">
+        <v>185</v>
+      </c>
       <c r="AS24" s="25"/>
       <c r="AT24" s="26" t="s">
         <v>168</v>
@@ -3858,7 +3920,9 @@
       <c r="N25" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="O25" s="17"/>
+      <c r="O25" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P25" s="17"/>
       <c r="Q25" s="17"/>
       <c r="R25" s="17"/>
@@ -3958,7 +4022,9 @@
       <c r="N26" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="O26" s="29"/>
+      <c r="O26" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P26" s="29"/>
       <c r="Q26" s="29"/>
       <c r="R26" s="23"/>
@@ -4060,10 +4126,12 @@
       <c r="M27" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="N27" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="O27" s="30"/>
+      <c r="N27" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="O27" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P27" s="30"/>
       <c r="Q27" s="30"/>
       <c r="R27" s="30"/>
@@ -4092,7 +4160,9 @@
       <c r="AO27" s="18"/>
       <c r="AP27" s="30"/>
       <c r="AQ27" s="19"/>
-      <c r="AR27" s="19"/>
+      <c r="AR27" s="41" t="s">
+        <v>185</v>
+      </c>
       <c r="AS27" s="18"/>
       <c r="AT27" s="20" t="s">
         <v>139</v>
@@ -4168,10 +4238,12 @@
       <c r="M28" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="N28" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="O28" s="30"/>
+      <c r="N28" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="O28" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P28" s="30"/>
       <c r="Q28" s="30"/>
       <c r="R28" s="30"/>
@@ -4264,10 +4336,12 @@
       <c r="M29" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="N29" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="O29" s="30"/>
+      <c r="N29" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="O29" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P29" s="30"/>
       <c r="Q29" s="30"/>
       <c r="R29" s="30"/>
@@ -4296,7 +4370,9 @@
       <c r="AO29" s="18"/>
       <c r="AP29" s="30"/>
       <c r="AQ29" s="19"/>
-      <c r="AR29" s="19"/>
+      <c r="AR29" s="41" t="s">
+        <v>185</v>
+      </c>
       <c r="AS29" s="32"/>
       <c r="AT29" s="26" t="s">
         <v>168</v>
@@ -4358,10 +4434,12 @@
       <c r="M30" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="N30" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="O30" s="30"/>
+      <c r="N30" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="O30" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P30" s="30"/>
       <c r="Q30" s="30"/>
       <c r="R30" s="30"/>
@@ -4390,7 +4468,7 @@
       <c r="AO30" s="18"/>
       <c r="AP30" s="30"/>
       <c r="AQ30" s="19"/>
-      <c r="AR30" s="19"/>
+      <c r="AR30" s="62"/>
       <c r="AS30" s="32"/>
       <c r="AT30" s="35" t="s">
         <v>163</v>
@@ -4454,10 +4532,12 @@
       <c r="M31" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="N31" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="O31" s="30"/>
+      <c r="N31" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="O31" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P31" s="30"/>
       <c r="Q31" s="30"/>
       <c r="R31" s="30"/>
@@ -4486,7 +4566,9 @@
       <c r="AO31" s="18"/>
       <c r="AP31" s="30"/>
       <c r="AQ31" s="19"/>
-      <c r="AR31" s="19"/>
+      <c r="AR31" s="41" t="s">
+        <v>185</v>
+      </c>
       <c r="AS31" s="32"/>
       <c r="AT31" s="20" t="s">
         <v>144</v>
@@ -4550,10 +4632,12 @@
       <c r="M32" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="N32" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="O32" s="30"/>
+      <c r="N32" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="O32" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P32" s="30"/>
       <c r="Q32" s="30"/>
       <c r="R32" s="30"/>
@@ -4582,7 +4666,9 @@
       <c r="AO32" s="18"/>
       <c r="AP32" s="30"/>
       <c r="AQ32" s="19"/>
-      <c r="AR32" s="19"/>
+      <c r="AR32" s="62" t="s">
+        <v>185</v>
+      </c>
       <c r="AS32" s="32"/>
       <c r="AT32" s="33" t="s">
         <v>141</v>
@@ -4650,10 +4736,12 @@
       <c r="M33" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="N33" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="O33" s="30"/>
+      <c r="N33" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="O33" s="17" t="s">
+        <v>127</v>
+      </c>
       <c r="P33" s="30"/>
       <c r="Q33" s="30"/>
       <c r="R33" s="30"/>
@@ -4744,10 +4832,12 @@
       <c r="M34" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="N34" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="O34" s="30"/>
+      <c r="N34" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="O34" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P34" s="30"/>
       <c r="Q34" s="30"/>
       <c r="R34" s="30"/>
@@ -4840,10 +4930,12 @@
       <c r="M35" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="N35" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="O35" s="30"/>
+      <c r="N35" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="O35" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P35" s="30"/>
       <c r="Q35" s="30"/>
       <c r="R35" s="30"/>
@@ -4872,7 +4964,7 @@
       <c r="AO35" s="18"/>
       <c r="AP35" s="30"/>
       <c r="AQ35" s="19"/>
-      <c r="AR35" s="19"/>
+      <c r="AR35" s="41"/>
       <c r="AS35" s="32"/>
       <c r="AT35" s="36" t="s">
         <v>159</v>
@@ -4936,10 +5028,12 @@
       <c r="M36" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="N36" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="O36" s="30"/>
+      <c r="N36" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="O36" s="17" t="s">
+        <v>126</v>
+      </c>
       <c r="P36" s="30"/>
       <c r="Q36" s="30"/>
       <c r="R36" s="30"/>
@@ -5032,10 +5126,12 @@
       <c r="M37" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="N37" s="30" t="s">
+      <c r="N37" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="O37" s="30"/>
+      <c r="O37" s="17" t="s">
+        <v>127</v>
+      </c>
       <c r="P37" s="30"/>
       <c r="Q37" s="30"/>
       <c r="R37" s="30"/>
@@ -5095,53 +5191,53 @@
       <c r="BP37" s="30"/>
     </row>
     <row r="38" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A38" s="50" t="s">
+      <c r="A38" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="B38" s="51"/>
-      <c r="C38" s="51"/>
-      <c r="D38" s="51"/>
-      <c r="E38" s="51"/>
-      <c r="F38" s="51"/>
-      <c r="G38" s="51"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="51"/>
-      <c r="J38" s="51"/>
-      <c r="K38" s="51"/>
-      <c r="L38" s="51"/>
-      <c r="M38" s="51"/>
-      <c r="N38" s="51"/>
-      <c r="O38" s="51"/>
-      <c r="P38" s="51"/>
-      <c r="Q38" s="51"/>
-      <c r="R38" s="51"/>
-      <c r="S38" s="51"/>
-      <c r="T38" s="51"/>
-      <c r="U38" s="51"/>
-      <c r="V38" s="51"/>
-      <c r="W38" s="51"/>
-      <c r="X38" s="51"/>
-      <c r="Y38" s="51"/>
-      <c r="Z38" s="51"/>
-      <c r="AA38" s="51"/>
-      <c r="AB38" s="51"/>
-      <c r="AC38" s="51"/>
-      <c r="AD38" s="51"/>
-      <c r="AE38" s="51"/>
-      <c r="AF38" s="51"/>
-      <c r="AG38" s="51"/>
-      <c r="AH38" s="51"/>
-      <c r="AI38" s="51"/>
-      <c r="AJ38" s="51"/>
-      <c r="AK38" s="51"/>
-      <c r="AL38" s="51"/>
-      <c r="AM38" s="51"/>
-      <c r="AN38" s="51"/>
-      <c r="AO38" s="51"/>
-      <c r="AP38" s="51"/>
-      <c r="AQ38" s="51"/>
-      <c r="AR38" s="51"/>
-      <c r="AS38" s="52"/>
+      <c r="B38" s="56"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="56"/>
+      <c r="H38" s="56"/>
+      <c r="I38" s="56"/>
+      <c r="J38" s="56"/>
+      <c r="K38" s="56"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="56"/>
+      <c r="N38" s="56"/>
+      <c r="O38" s="56"/>
+      <c r="P38" s="56"/>
+      <c r="Q38" s="56"/>
+      <c r="R38" s="56"/>
+      <c r="S38" s="56"/>
+      <c r="T38" s="56"/>
+      <c r="U38" s="56"/>
+      <c r="V38" s="56"/>
+      <c r="W38" s="56"/>
+      <c r="X38" s="56"/>
+      <c r="Y38" s="56"/>
+      <c r="Z38" s="56"/>
+      <c r="AA38" s="56"/>
+      <c r="AB38" s="56"/>
+      <c r="AC38" s="56"/>
+      <c r="AD38" s="56"/>
+      <c r="AE38" s="56"/>
+      <c r="AF38" s="56"/>
+      <c r="AG38" s="56"/>
+      <c r="AH38" s="56"/>
+      <c r="AI38" s="56"/>
+      <c r="AJ38" s="56"/>
+      <c r="AK38" s="56"/>
+      <c r="AL38" s="56"/>
+      <c r="AM38" s="56"/>
+      <c r="AN38" s="56"/>
+      <c r="AO38" s="56"/>
+      <c r="AP38" s="56"/>
+      <c r="AQ38" s="56"/>
+      <c r="AR38" s="56"/>
+      <c r="AS38" s="57"/>
       <c r="AT38" s="2"/>
       <c r="AU38" s="2"/>
       <c r="AV38" s="2"/>
@@ -5173,53 +5269,53 @@
       </c>
     </row>
     <row r="39" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A39" s="53" t="s">
+      <c r="A39" s="58" t="s">
         <v>93</v>
       </c>
-      <c r="B39" s="54"/>
-      <c r="C39" s="54"/>
-      <c r="D39" s="54"/>
-      <c r="E39" s="54"/>
-      <c r="F39" s="54"/>
-      <c r="G39" s="54"/>
-      <c r="H39" s="54"/>
-      <c r="I39" s="54"/>
-      <c r="J39" s="54"/>
-      <c r="K39" s="54"/>
-      <c r="L39" s="54"/>
-      <c r="M39" s="54"/>
-      <c r="N39" s="54"/>
-      <c r="O39" s="54"/>
-      <c r="P39" s="54"/>
-      <c r="Q39" s="54"/>
-      <c r="R39" s="54"/>
-      <c r="S39" s="54"/>
-      <c r="T39" s="54"/>
-      <c r="U39" s="54"/>
-      <c r="V39" s="54"/>
-      <c r="W39" s="54"/>
-      <c r="X39" s="54"/>
-      <c r="Y39" s="54"/>
-      <c r="Z39" s="54"/>
-      <c r="AA39" s="54"/>
-      <c r="AB39" s="54"/>
-      <c r="AC39" s="54"/>
-      <c r="AD39" s="54"/>
-      <c r="AE39" s="54"/>
-      <c r="AF39" s="54"/>
-      <c r="AG39" s="54"/>
-      <c r="AH39" s="54"/>
-      <c r="AI39" s="54"/>
-      <c r="AJ39" s="54"/>
-      <c r="AK39" s="54"/>
-      <c r="AL39" s="54"/>
-      <c r="AM39" s="54"/>
-      <c r="AN39" s="54"/>
-      <c r="AO39" s="54"/>
-      <c r="AP39" s="54"/>
-      <c r="AQ39" s="54"/>
-      <c r="AR39" s="54"/>
-      <c r="AS39" s="55"/>
+      <c r="B39" s="59"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="59"/>
+      <c r="F39" s="59"/>
+      <c r="G39" s="59"/>
+      <c r="H39" s="59"/>
+      <c r="I39" s="59"/>
+      <c r="J39" s="59"/>
+      <c r="K39" s="59"/>
+      <c r="L39" s="59"/>
+      <c r="M39" s="59"/>
+      <c r="N39" s="59"/>
+      <c r="O39" s="59"/>
+      <c r="P39" s="59"/>
+      <c r="Q39" s="59"/>
+      <c r="R39" s="59"/>
+      <c r="S39" s="59"/>
+      <c r="T39" s="59"/>
+      <c r="U39" s="59"/>
+      <c r="V39" s="59"/>
+      <c r="W39" s="59"/>
+      <c r="X39" s="59"/>
+      <c r="Y39" s="59"/>
+      <c r="Z39" s="59"/>
+      <c r="AA39" s="59"/>
+      <c r="AB39" s="59"/>
+      <c r="AC39" s="59"/>
+      <c r="AD39" s="59"/>
+      <c r="AE39" s="59"/>
+      <c r="AF39" s="59"/>
+      <c r="AG39" s="59"/>
+      <c r="AH39" s="59"/>
+      <c r="AI39" s="59"/>
+      <c r="AJ39" s="59"/>
+      <c r="AK39" s="59"/>
+      <c r="AL39" s="59"/>
+      <c r="AM39" s="59"/>
+      <c r="AN39" s="59"/>
+      <c r="AO39" s="59"/>
+      <c r="AP39" s="59"/>
+      <c r="AQ39" s="59"/>
+      <c r="AR39" s="59"/>
+      <c r="AS39" s="60"/>
       <c r="AT39" s="2"/>
       <c r="AU39" s="2"/>
       <c r="AV39" s="2"/>
@@ -5797,11 +5893,37 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="AM2:AM3"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="BN2:BP3"/>
+    <mergeCell ref="A38:AS38"/>
+    <mergeCell ref="A39:AS39"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="AO2:AO3"/>
+    <mergeCell ref="AP2:AP3"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="BC2:BF3"/>
+    <mergeCell ref="BG2:BJ3"/>
+    <mergeCell ref="BK2:BM3"/>
+    <mergeCell ref="A1:AS1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="AQ2:AS3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="AN2:AN3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="AZ2:BB3"/>
@@ -5818,37 +5940,11 @@
     <mergeCell ref="AK2:AK3"/>
     <mergeCell ref="AL2:AL3"/>
     <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="A1:AS1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="AQ2:AS3"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="AN2:AN3"/>
-    <mergeCell ref="BN2:BP3"/>
-    <mergeCell ref="A38:AS38"/>
-    <mergeCell ref="A39:AS39"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="AO2:AO3"/>
-    <mergeCell ref="AP2:AP3"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="BC2:BF3"/>
-    <mergeCell ref="BG2:BJ3"/>
-    <mergeCell ref="BK2:BM3"/>
+    <mergeCell ref="AM2:AM3"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AB2:AB3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="BS6" r:id="rId1" display="Прикладная дискретная математика. Приложение. 2016. № 9. С. 68-70." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -5862,15 +5958,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Документ" ma:contentTypeID="0x0101004F6380A0290AF84484F859C9FFD97568" ma:contentTypeVersion="12" ma:contentTypeDescription="Создание документа." ma:contentTypeScope="" ma:versionID="1ee9877c88efff51dfb0d3a4b3e8ad1b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bffb7b91-0466-4de0-9379-f5c53c3acedf" xmlns:ns3="b78dbef7-f85b-47b5-8738-6377d50f4027" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="532d4df54980d57387e1b5dc96a6a32c" ns2:_="" ns3:_="">
     <xsd:import namespace="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
@@ -6071,6 +6158,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -6083,14 +6179,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00280879-8A9A-4335-93BC-405126DC8F0C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B6A6DF3-AE59-43BA-A5FF-CF9B7C54D4B8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6109,6 +6197,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00280879-8A9A-4335-93BC-405126DC8F0C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12ECB55F-B88E-4FE2-9AD5-5CA5D433F306}">
   <ds:schemaRefs>

--- a/Ведомость ТКИ-441 2026-2027.xlsx
+++ b/Ведомость ТКИ-441 2026-2027.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\StegMethods\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\StegMethods\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756FC710-54A7-424C-BCAA-0AA3A6CF73F2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="179">
   <si>
     <t>Ведомость посещаемости занятий студентами группы ТКИ РУТ МИИТ</t>
   </si>
@@ -229,15 +228,6 @@
     <t>НОВЫЙ МЕТОД СТЕГОАНАЛИЗА ТЕКСТОВЫХ ДАННЫХ, ПОЛУЧЕННЫХ КОДИРОВАНИЕМ ДЛИН СЕРИЙ СИНОНИМОВ / Нечта И.В. // Безопасность информационных технологий. 2018. Т. 25. № 2. С. 114-120.</t>
   </si>
   <si>
-    <t>ортогональные функции</t>
-  </si>
-  <si>
-    <t>вейвлеты</t>
-  </si>
-  <si>
-    <t>Стегоанализ. Равномерное распределение</t>
-  </si>
-  <si>
     <t>Пусто</t>
   </si>
   <si>
@@ -250,30 +240,15 @@
     <t>БПФ</t>
   </si>
   <si>
-    <t>качество энергии, высокие гармоники</t>
-  </si>
-  <si>
-    <t>Равномерное распределение. Исаков.</t>
-  </si>
-  <si>
     <t>Отдельное задание про  portable executive</t>
   </si>
   <si>
     <t>Д/з</t>
   </si>
   <si>
-    <t>прямоугольные импульсы</t>
-  </si>
-  <si>
-    <t>Талатин. АКФ и ВКФ</t>
-  </si>
-  <si>
     <t>Из предметов, связанных с криптографией вспомнить все про БПФ и связанные с ним алгоримты и про ГПСЧ</t>
   </si>
   <si>
-    <t>Автоношкин. АКФ и ВКФ</t>
-  </si>
-  <si>
     <t>ПРИМЕНЕНИЕ СТАТИСТИЧЕСКОГО АНАЛИЗА ДЛЯ ОБНАРУЖЕНИЯ СКРЫТЫХ СООБЩЕНИЙ В ТЕКСТОВЫХ ДАННЫХ / Нечта И.В. // Вестник СибГУТИ. 2012. № 1 (17). С. 23-29.</t>
   </si>
   <si>
@@ -584,12 +559,15 @@
   </si>
   <si>
     <t>Тесты</t>
+  </si>
+  <si>
+    <t>Фильм</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -926,31 +904,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -969,13 +929,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Hyperlink" xfId="1"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1011,7 +989,7 @@
         <xdr:cNvPr id="3" name="Рисунок 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13645ABC-C350-4C12-BD87-CB39C6C63ABA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{13645ABC-C350-4C12-BD87-CB39C6C63ABA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1302,7 +1280,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BV66"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1336,221 +1314,221 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="52"/>
-      <c r="V1" s="52"/>
-      <c r="W1" s="52"/>
-      <c r="X1" s="52"/>
-      <c r="Y1" s="52"/>
-      <c r="Z1" s="52"/>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="52"/>
-      <c r="AC1" s="52"/>
-      <c r="AD1" s="52"/>
-      <c r="AE1" s="52"/>
-      <c r="AF1" s="52"/>
-      <c r="AG1" s="52"/>
-      <c r="AH1" s="52"/>
-      <c r="AI1" s="52"/>
-      <c r="AJ1" s="52"/>
-      <c r="AK1" s="52"/>
-      <c r="AL1" s="52"/>
-      <c r="AM1" s="52"/>
-      <c r="AN1" s="52"/>
-      <c r="AO1" s="52"/>
-      <c r="AP1" s="52"/>
-      <c r="AQ1" s="52"/>
-      <c r="AR1" s="52"/>
-      <c r="AS1" s="52"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
+      <c r="S1" s="61"/>
+      <c r="T1" s="61"/>
+      <c r="U1" s="61"/>
+      <c r="V1" s="61"/>
+      <c r="W1" s="61"/>
+      <c r="X1" s="61"/>
+      <c r="Y1" s="61"/>
+      <c r="Z1" s="61"/>
+      <c r="AA1" s="61"/>
+      <c r="AB1" s="61"/>
+      <c r="AC1" s="61"/>
+      <c r="AD1" s="61"/>
+      <c r="AE1" s="61"/>
+      <c r="AF1" s="61"/>
+      <c r="AG1" s="61"/>
+      <c r="AH1" s="61"/>
+      <c r="AI1" s="61"/>
+      <c r="AJ1" s="61"/>
+      <c r="AK1" s="61"/>
+      <c r="AL1" s="61"/>
+      <c r="AM1" s="61"/>
+      <c r="AN1" s="61"/>
+      <c r="AO1" s="61"/>
+      <c r="AP1" s="61"/>
+      <c r="AQ1" s="61"/>
+      <c r="AR1" s="61"/>
+      <c r="AS1" s="61"/>
     </row>
     <row r="2" spans="1:73" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="61" t="s">
+      <c r="B2" s="57"/>
+      <c r="C2" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="44">
+      <c r="D2" s="55">
         <v>46268</v>
       </c>
-      <c r="E2" s="44">
+      <c r="E2" s="55">
         <v>46272</v>
       </c>
-      <c r="F2" s="44">
+      <c r="F2" s="55">
         <v>46273</v>
       </c>
-      <c r="G2" s="44">
+      <c r="G2" s="55">
         <v>46275</v>
       </c>
-      <c r="H2" s="44">
+      <c r="H2" s="55">
         <v>46279</v>
       </c>
-      <c r="I2" s="42">
+      <c r="I2" s="58">
         <v>46282</v>
       </c>
-      <c r="J2" s="44">
+      <c r="J2" s="55">
         <v>46286</v>
       </c>
-      <c r="K2" s="44">
+      <c r="K2" s="55">
         <v>46287</v>
       </c>
-      <c r="L2" s="42">
+      <c r="L2" s="58">
         <v>46289</v>
       </c>
-      <c r="M2" s="44">
+      <c r="M2" s="55">
         <v>46293</v>
       </c>
-      <c r="N2" s="42">
+      <c r="N2" s="58">
         <v>46296</v>
       </c>
-      <c r="O2" s="44">
+      <c r="O2" s="55">
         <v>46300</v>
       </c>
-      <c r="P2" s="44">
+      <c r="P2" s="55">
         <v>46301</v>
       </c>
-      <c r="Q2" s="42">
+      <c r="Q2" s="58">
         <v>46303</v>
       </c>
-      <c r="R2" s="44">
+      <c r="R2" s="55">
         <v>46307</v>
       </c>
-      <c r="S2" s="42">
+      <c r="S2" s="58">
         <v>46310</v>
       </c>
-      <c r="T2" s="44">
+      <c r="T2" s="55">
         <v>46314</v>
       </c>
-      <c r="U2" s="44">
+      <c r="U2" s="55">
         <v>46315</v>
       </c>
-      <c r="V2" s="42">
+      <c r="V2" s="58">
         <v>46317</v>
       </c>
-      <c r="W2" s="44">
+      <c r="W2" s="55">
         <v>46321</v>
       </c>
-      <c r="X2" s="44">
+      <c r="X2" s="55">
         <v>46324</v>
       </c>
-      <c r="Y2" s="44">
+      <c r="Y2" s="55">
         <v>46328</v>
       </c>
-      <c r="Z2" s="44">
+      <c r="Z2" s="55">
         <v>46328</v>
       </c>
-      <c r="AA2" s="44">
+      <c r="AA2" s="55">
         <v>46331</v>
       </c>
-      <c r="AB2" s="44">
+      <c r="AB2" s="55">
         <v>46335</v>
       </c>
-      <c r="AC2" s="44">
+      <c r="AC2" s="55">
         <v>46338</v>
       </c>
-      <c r="AD2" s="44">
+      <c r="AD2" s="55">
         <v>46342</v>
       </c>
-      <c r="AE2" s="44">
+      <c r="AE2" s="55">
         <v>46345</v>
       </c>
-      <c r="AF2" s="44">
+      <c r="AF2" s="55">
         <v>46349</v>
       </c>
-      <c r="AG2" s="44">
+      <c r="AG2" s="55">
         <v>46352</v>
       </c>
-      <c r="AH2" s="44">
+      <c r="AH2" s="55">
         <v>46356</v>
       </c>
-      <c r="AI2" s="42">
+      <c r="AI2" s="58">
         <v>46359</v>
       </c>
-      <c r="AJ2" s="42">
+      <c r="AJ2" s="58">
         <v>46363</v>
       </c>
-      <c r="AK2" s="42">
+      <c r="AK2" s="58">
         <v>46366</v>
       </c>
-      <c r="AL2" s="42">
+      <c r="AL2" s="58">
         <v>46370</v>
       </c>
-      <c r="AM2" s="42">
+      <c r="AM2" s="58">
         <v>46373</v>
       </c>
-      <c r="AN2" s="42">
+      <c r="AN2" s="58">
         <v>46377</v>
       </c>
-      <c r="AO2" s="53" t="s">
+      <c r="AO2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="AP2" s="53"/>
-      <c r="AQ2" s="46" t="s">
-        <v>128</v>
-      </c>
-      <c r="AR2" s="47"/>
-      <c r="AS2" s="48"/>
-      <c r="AT2" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="AU2" s="47"/>
-      <c r="AV2" s="48"/>
-      <c r="AW2" s="46" t="s">
-        <v>170</v>
-      </c>
-      <c r="AX2" s="47"/>
-      <c r="AY2" s="48"/>
-      <c r="AZ2" s="46" t="s">
+      <c r="AP2" s="57"/>
+      <c r="AQ2" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="AR2" s="44"/>
+      <c r="AS2" s="45"/>
+      <c r="AT2" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="AU2" s="44"/>
+      <c r="AV2" s="45"/>
+      <c r="AW2" s="43" t="s">
+        <v>162</v>
+      </c>
+      <c r="AX2" s="44"/>
+      <c r="AY2" s="45"/>
+      <c r="AZ2" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="BA2" s="47"/>
-      <c r="BB2" s="48"/>
-      <c r="BC2" s="46" t="s">
+      <c r="BA2" s="44"/>
+      <c r="BB2" s="45"/>
+      <c r="BC2" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="BD2" s="47"/>
-      <c r="BE2" s="47"/>
-      <c r="BF2" s="48"/>
-      <c r="BG2" s="46" t="s">
+      <c r="BD2" s="44"/>
+      <c r="BE2" s="44"/>
+      <c r="BF2" s="45"/>
+      <c r="BG2" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="BH2" s="47"/>
-      <c r="BI2" s="47"/>
-      <c r="BJ2" s="48" t="s">
+      <c r="BH2" s="44"/>
+      <c r="BI2" s="44"/>
+      <c r="BJ2" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="BK2" s="46" t="s">
+      <c r="BK2" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="BL2" s="47"/>
-      <c r="BM2" s="48"/>
-      <c r="BN2" s="46" t="s">
+      <c r="BL2" s="44"/>
+      <c r="BM2" s="45"/>
+      <c r="BN2" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="BO2" s="47"/>
-      <c r="BP2" s="48"/>
+      <c r="BO2" s="44"/>
+      <c r="BP2" s="45"/>
     </row>
     <row r="3" spans="1:73" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1559,114 +1537,116 @@
       <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
-      <c r="V3" s="43"/>
-      <c r="W3" s="45"/>
-      <c r="X3" s="45"/>
-      <c r="Y3" s="45"/>
-      <c r="Z3" s="45"/>
-      <c r="AA3" s="45"/>
-      <c r="AB3" s="45"/>
-      <c r="AC3" s="45"/>
-      <c r="AD3" s="45"/>
-      <c r="AE3" s="45"/>
-      <c r="AF3" s="45"/>
-      <c r="AG3" s="45"/>
-      <c r="AH3" s="45"/>
-      <c r="AI3" s="43"/>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="53"/>
-      <c r="AP3" s="53"/>
-      <c r="AQ3" s="49"/>
-      <c r="AR3" s="54"/>
-      <c r="AS3" s="51"/>
-      <c r="AT3" s="49"/>
-      <c r="AU3" s="50"/>
-      <c r="AV3" s="51"/>
-      <c r="AW3" s="49"/>
-      <c r="AX3" s="50"/>
-      <c r="AY3" s="51"/>
-      <c r="AZ3" s="49"/>
-      <c r="BA3" s="50"/>
-      <c r="BB3" s="51"/>
-      <c r="BC3" s="49"/>
-      <c r="BD3" s="50"/>
-      <c r="BE3" s="50"/>
-      <c r="BF3" s="51"/>
-      <c r="BG3" s="49"/>
-      <c r="BH3" s="50"/>
-      <c r="BI3" s="50"/>
-      <c r="BJ3" s="51"/>
-      <c r="BK3" s="49"/>
-      <c r="BL3" s="50"/>
-      <c r="BM3" s="51"/>
-      <c r="BN3" s="49"/>
-      <c r="BO3" s="50"/>
-      <c r="BP3" s="51"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="59"/>
+      <c r="M3" s="56"/>
+      <c r="N3" s="59"/>
+      <c r="O3" s="56"/>
+      <c r="P3" s="56"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="56"/>
+      <c r="S3" s="59"/>
+      <c r="T3" s="56"/>
+      <c r="U3" s="56"/>
+      <c r="V3" s="59"/>
+      <c r="W3" s="56"/>
+      <c r="X3" s="56"/>
+      <c r="Y3" s="56"/>
+      <c r="Z3" s="56"/>
+      <c r="AA3" s="56"/>
+      <c r="AB3" s="56"/>
+      <c r="AC3" s="56"/>
+      <c r="AD3" s="56"/>
+      <c r="AE3" s="56"/>
+      <c r="AF3" s="56"/>
+      <c r="AG3" s="56"/>
+      <c r="AH3" s="56"/>
+      <c r="AI3" s="59"/>
+      <c r="AJ3" s="59"/>
+      <c r="AK3" s="59"/>
+      <c r="AL3" s="59"/>
+      <c r="AM3" s="59"/>
+      <c r="AN3" s="59"/>
+      <c r="AO3" s="57"/>
+      <c r="AP3" s="57"/>
+      <c r="AQ3" s="46"/>
+      <c r="AR3" s="62"/>
+      <c r="AS3" s="48"/>
+      <c r="AT3" s="46"/>
+      <c r="AU3" s="47"/>
+      <c r="AV3" s="48"/>
+      <c r="AW3" s="46"/>
+      <c r="AX3" s="47"/>
+      <c r="AY3" s="48"/>
+      <c r="AZ3" s="46"/>
+      <c r="BA3" s="47"/>
+      <c r="BB3" s="48"/>
+      <c r="BC3" s="46"/>
+      <c r="BD3" s="47"/>
+      <c r="BE3" s="47"/>
+      <c r="BF3" s="48"/>
+      <c r="BG3" s="46"/>
+      <c r="BH3" s="47"/>
+      <c r="BI3" s="47"/>
+      <c r="BJ3" s="48"/>
+      <c r="BK3" s="46"/>
+      <c r="BL3" s="47"/>
+      <c r="BM3" s="48"/>
+      <c r="BN3" s="46"/>
+      <c r="BO3" s="47"/>
+      <c r="BP3" s="48"/>
     </row>
     <row r="4" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C4" s="4">
         <v>1</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F4" s="17"/>
       <c r="G4" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I4" s="17"/>
       <c r="J4" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K4" s="17"/>
       <c r="L4" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M4" s="39" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="N4" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O4" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P4" s="17"/>
+        <v>118</v>
+      </c>
+      <c r="P4" s="17" t="s">
+        <v>119</v>
+      </c>
       <c r="Q4" s="17"/>
       <c r="R4" s="17"/>
       <c r="S4" s="17"/>
@@ -1697,24 +1677,24 @@
       <c r="AR4" s="19"/>
       <c r="AS4" s="18"/>
       <c r="AT4" s="33" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="AU4" s="34" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="AV4" s="21"/>
       <c r="AW4" s="21" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AX4" s="21" t="s">
         <v>36</v>
       </c>
       <c r="AY4" s="18"/>
       <c r="AZ4" s="34" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="BA4" s="34" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="BB4" s="34"/>
       <c r="BC4" s="17"/>
@@ -1737,42 +1717,44 @@
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C5" s="4">
         <v>2</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F5" s="17"/>
       <c r="G5" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I5" s="17"/>
       <c r="J5" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K5" s="17"/>
       <c r="L5" s="17" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="M5" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="N5" s="17" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="O5" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P5" s="17"/>
+        <v>118</v>
+      </c>
+      <c r="P5" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="Q5" s="17"/>
       <c r="R5" s="17"/>
       <c r="S5" s="17"/>
@@ -1801,28 +1783,28 @@
       <c r="AP5" s="17"/>
       <c r="AQ5" s="19"/>
       <c r="AR5" s="41" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="AS5" s="21"/>
       <c r="AT5" s="33" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="AU5" s="34" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="AV5" s="21"/>
       <c r="AW5" s="21" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AX5" s="21" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AY5" s="18"/>
       <c r="AZ5" s="34" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="BA5" s="34" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="BB5" s="34"/>
       <c r="BC5" s="17"/>
@@ -1860,42 +1842,44 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C6" s="4">
         <v>3</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F6" s="17"/>
       <c r="G6" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I6" s="17"/>
       <c r="J6" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K6" s="17"/>
       <c r="L6" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M6" s="40" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="N6" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O6" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P6" s="17"/>
+        <v>118</v>
+      </c>
+      <c r="P6" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="Q6" s="17"/>
       <c r="R6" s="17"/>
       <c r="S6" s="17"/>
@@ -1923,19 +1907,19 @@
       <c r="AO6" s="18"/>
       <c r="AP6" s="17"/>
       <c r="AQ6" s="19"/>
-      <c r="AR6" s="62" t="s">
-        <v>185</v>
+      <c r="AR6" s="42" t="s">
+        <v>177</v>
       </c>
       <c r="AS6" s="21"/>
       <c r="AT6" s="33" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="AU6" s="34" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="AV6" s="21"/>
       <c r="AW6" s="11" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AX6" s="8" t="s">
         <v>47</v>
@@ -1972,42 +1956,44 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C7" s="4">
         <v>4</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F7" s="17"/>
       <c r="G7" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I7" s="17"/>
       <c r="J7" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K7" s="17"/>
       <c r="L7" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M7" s="38" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O7" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="P7" s="24"/>
+        <v>118</v>
+      </c>
+      <c r="P7" s="24" t="s">
+        <v>118</v>
+      </c>
       <c r="Q7" s="17"/>
       <c r="R7" s="17"/>
       <c r="S7" s="17"/>
@@ -2036,21 +2022,21 @@
       <c r="AP7" s="17"/>
       <c r="AQ7" s="19"/>
       <c r="AR7" s="41" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="AS7" s="25"/>
       <c r="AT7" s="20" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="AU7" s="19" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="AV7" s="17"/>
       <c r="AW7" s="34">
         <v>9.3000000000000007</v>
       </c>
       <c r="AX7" s="7" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="AY7" s="17"/>
       <c r="AZ7" s="11" t="s">
@@ -2084,42 +2070,44 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C8" s="4">
         <v>17</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="F8" s="17"/>
       <c r="G8" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="K8" s="17"/>
       <c r="L8" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="O8" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="P8" s="17"/>
+        <v>119</v>
+      </c>
+      <c r="P8" s="17" t="s">
+        <v>119</v>
+      </c>
       <c r="Q8" s="17"/>
       <c r="R8" s="17"/>
       <c r="S8" s="17"/>
@@ -2150,17 +2138,17 @@
       <c r="AR8" s="19"/>
       <c r="AS8" s="25"/>
       <c r="AT8" s="36" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="AU8" s="34" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="AV8" s="17"/>
       <c r="AW8" s="34">
         <v>9.4</v>
       </c>
       <c r="AX8" s="7" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="AY8" s="17"/>
       <c r="AZ8" s="37" t="s">
@@ -2194,42 +2182,44 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C9" s="4">
         <v>5</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F9" s="17"/>
       <c r="G9" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I9" s="17"/>
       <c r="J9" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="K9" s="17"/>
       <c r="L9" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M9" s="39" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P9" s="17"/>
+        <v>118</v>
+      </c>
+      <c r="P9" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="Q9" s="17"/>
       <c r="R9" s="17"/>
       <c r="S9" s="17"/>
@@ -2260,17 +2250,17 @@
       <c r="AR9" s="41"/>
       <c r="AS9" s="21"/>
       <c r="AT9" s="27" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="AU9" s="19" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="AV9" s="21"/>
       <c r="AW9" s="34">
         <v>9.1</v>
       </c>
       <c r="AX9" s="7" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="AY9" s="18"/>
       <c r="AZ9" s="17"/>
@@ -2308,36 +2298,38 @@
         <v>6</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F10" s="17"/>
       <c r="G10" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K10" s="17"/>
       <c r="L10" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M10" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P10" s="17"/>
+        <v>118</v>
+      </c>
+      <c r="P10" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="Q10" s="17"/>
       <c r="R10" s="17"/>
       <c r="S10" s="17"/>
@@ -2365,20 +2357,20 @@
       <c r="AO10" s="18"/>
       <c r="AP10" s="17"/>
       <c r="AQ10" s="19"/>
-      <c r="AR10" s="62"/>
+      <c r="AR10" s="42"/>
       <c r="AS10" s="21"/>
       <c r="AT10" s="33" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="AU10" s="34" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="AV10" s="18"/>
       <c r="AW10" s="34" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="AX10" s="34" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="AY10" s="34"/>
       <c r="AZ10" s="17"/>
@@ -2410,42 +2402,44 @@
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C11" s="4">
         <v>7</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F11" s="17"/>
       <c r="G11" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I11" s="17"/>
       <c r="J11" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K11" s="17"/>
       <c r="L11" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M11" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P11" s="17"/>
+        <v>118</v>
+      </c>
+      <c r="P11" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="Q11" s="17"/>
       <c r="R11" s="17"/>
       <c r="S11" s="17"/>
@@ -2474,21 +2468,21 @@
       <c r="AP11" s="17"/>
       <c r="AQ11" s="19"/>
       <c r="AR11" s="41" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="AS11" s="21"/>
       <c r="AT11" s="33" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="AU11" s="34" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="AV11" s="18"/>
       <c r="AW11" s="34" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="AX11" s="34" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="AY11" s="34"/>
       <c r="AZ11" s="17"/>
@@ -2520,44 +2514,46 @@
         <v>9</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C12" s="4">
         <v>8</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F12" s="17"/>
       <c r="G12" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K12" s="17"/>
       <c r="L12" s="17" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="M12" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="P12" s="17"/>
+        <v>119</v>
+      </c>
+      <c r="P12" s="17" t="s">
+        <v>119</v>
+      </c>
       <c r="Q12" s="17"/>
       <c r="R12" s="17"/>
       <c r="S12" s="17"/>
@@ -2588,14 +2584,14 @@
       <c r="AR12" s="41"/>
       <c r="AS12" s="21"/>
       <c r="AT12" s="20" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AU12" s="19" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="AV12" s="21"/>
       <c r="AW12" s="34" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="AX12" s="34"/>
       <c r="AY12" s="34"/>
@@ -2628,42 +2624,44 @@
         <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C13" s="4">
         <v>9</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F13" s="17"/>
       <c r="G13" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I13" s="17"/>
       <c r="J13" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K13" s="17"/>
       <c r="L13" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M13" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="P13" s="17"/>
+        <v>119</v>
+      </c>
+      <c r="P13" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="Q13" s="17"/>
       <c r="R13" s="17"/>
       <c r="S13" s="17"/>
@@ -2694,10 +2692,10 @@
       <c r="AR13" s="19"/>
       <c r="AS13" s="21"/>
       <c r="AT13" s="33" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="AU13" s="34" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="AV13" s="18"/>
       <c r="AW13" s="17"/>
@@ -2732,42 +2730,44 @@
         <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C14" s="4">
         <v>10</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F14" s="17"/>
       <c r="G14" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I14" s="17"/>
       <c r="J14" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="K14" s="17"/>
       <c r="L14" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M14" s="38" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O14" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P14" s="17"/>
+        <v>118</v>
+      </c>
+      <c r="P14" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="Q14" s="23"/>
       <c r="R14" s="17"/>
       <c r="S14" s="17"/>
@@ -2798,10 +2798,10 @@
       <c r="AR14" s="41"/>
       <c r="AS14" s="25"/>
       <c r="AT14" s="36" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="AU14" s="34" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="AV14" s="17"/>
       <c r="AW14" s="17"/>
@@ -2836,42 +2836,44 @@
         <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C15" s="4">
         <v>7</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F15" s="17"/>
       <c r="G15" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I15" s="17"/>
       <c r="J15" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M15" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O15" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P15" s="17"/>
+        <v>118</v>
+      </c>
+      <c r="P15" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="Q15" s="17"/>
       <c r="R15" s="17"/>
       <c r="S15" s="17"/>
@@ -2900,14 +2902,14 @@
       <c r="AP15" s="17"/>
       <c r="AQ15" s="19"/>
       <c r="AR15" s="41" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="AS15" s="18"/>
       <c r="AT15" s="33" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="AU15" s="34" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="AV15" s="21"/>
       <c r="AW15" s="17"/>
@@ -2942,42 +2944,44 @@
         <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C16" s="4">
         <v>1</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F16" s="17"/>
       <c r="G16" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I16" s="17"/>
       <c r="J16" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K16" s="17"/>
       <c r="L16" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M16" s="39" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P16" s="17"/>
+        <v>118</v>
+      </c>
+      <c r="P16" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="Q16" s="17"/>
       <c r="R16" s="17"/>
       <c r="S16" s="17"/>
@@ -3008,14 +3012,14 @@
       <c r="AR16" s="19"/>
       <c r="AS16" s="25"/>
       <c r="AT16" s="33" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="AU16" s="34" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="AV16" s="18"/>
       <c r="AW16" s="21" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AX16" s="21" t="s">
         <v>36</v>
@@ -3050,42 +3054,44 @@
         <v>14</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C17" s="4">
         <v>11</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F17" s="17"/>
       <c r="G17" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I17" s="17"/>
       <c r="J17" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M17" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P17" s="17"/>
+        <v>118</v>
+      </c>
+      <c r="P17" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="Q17" s="17"/>
       <c r="R17" s="17"/>
       <c r="S17" s="17"/>
@@ -3113,15 +3119,15 @@
       <c r="AO17" s="18"/>
       <c r="AP17" s="17"/>
       <c r="AQ17" s="19"/>
-      <c r="AR17" s="62" t="s">
-        <v>185</v>
+      <c r="AR17" s="42" t="s">
+        <v>177</v>
       </c>
       <c r="AS17" s="21"/>
       <c r="AT17" s="33" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="AU17" s="34" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="AV17" s="18"/>
       <c r="AW17" s="17"/>
@@ -3156,44 +3162,46 @@
         <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C18" s="4">
         <v>12</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F18" s="17"/>
       <c r="G18" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K18" s="17"/>
       <c r="L18" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M18" s="39" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P18" s="17"/>
+        <v>118</v>
+      </c>
+      <c r="P18" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="Q18" s="17"/>
       <c r="R18" s="17"/>
       <c r="S18" s="17"/>
@@ -3221,13 +3229,13 @@
       <c r="AO18" s="18"/>
       <c r="AP18" s="17"/>
       <c r="AQ18" s="19"/>
-      <c r="AR18" s="62"/>
+      <c r="AR18" s="42"/>
       <c r="AS18" s="21"/>
       <c r="AT18" s="35" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="AU18" s="34" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="AV18" s="21"/>
       <c r="AW18" s="17"/>
@@ -3262,42 +3270,44 @@
         <v>16</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C19" s="4">
         <v>11</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F19" s="17"/>
       <c r="G19" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I19" s="17"/>
       <c r="J19" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K19" s="17"/>
       <c r="L19" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M19" s="40" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P19" s="17"/>
+        <v>118</v>
+      </c>
+      <c r="P19" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="Q19" s="17"/>
       <c r="R19" s="17"/>
       <c r="S19" s="17"/>
@@ -3325,15 +3335,15 @@
       <c r="AO19" s="18"/>
       <c r="AP19" s="17"/>
       <c r="AQ19" s="19"/>
-      <c r="AR19" s="62" t="s">
-        <v>185</v>
+      <c r="AR19" s="42" t="s">
+        <v>177</v>
       </c>
       <c r="AS19" s="21"/>
       <c r="AT19" s="33" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="AU19" s="34" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="AV19" s="18"/>
       <c r="AW19" s="17"/>
@@ -3368,42 +3378,44 @@
         <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C20" s="4">
         <v>5</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F20" s="17"/>
       <c r="G20" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I20" s="17"/>
       <c r="J20" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K20" s="17"/>
       <c r="L20" s="17" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="M20" s="39" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P20" s="17"/>
+        <v>118</v>
+      </c>
+      <c r="P20" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="Q20" s="17"/>
       <c r="R20" s="17"/>
       <c r="S20" s="17"/>
@@ -3434,10 +3446,10 @@
       <c r="AR20" s="41"/>
       <c r="AS20" s="21"/>
       <c r="AT20" s="27" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="AU20" s="19" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="AV20" s="18"/>
       <c r="AW20" s="17"/>
@@ -3472,42 +3484,44 @@
         <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C21" s="4">
         <v>17</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="F21" s="17"/>
       <c r="G21" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I21" s="17"/>
       <c r="J21" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="K21" s="17"/>
       <c r="L21" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M21" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="O21" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="P21" s="17"/>
+        <v>119</v>
+      </c>
+      <c r="P21" s="17" t="s">
+        <v>119</v>
+      </c>
       <c r="Q21" s="17"/>
       <c r="R21" s="17"/>
       <c r="S21" s="17"/>
@@ -3538,10 +3552,10 @@
       <c r="AR21" s="19"/>
       <c r="AS21" s="21"/>
       <c r="AT21" s="36" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="AU21" s="34" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="AV21" s="21"/>
       <c r="AW21" s="17"/>
@@ -3576,42 +3590,44 @@
         <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C22" s="4">
         <v>13</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F22" s="17"/>
       <c r="G22" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I22" s="17"/>
       <c r="J22" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="K22" s="17"/>
       <c r="L22" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M22" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O22" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="P22" s="17"/>
+        <v>119</v>
+      </c>
+      <c r="P22" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="Q22" s="17"/>
       <c r="R22" s="17"/>
       <c r="S22" s="17"/>
@@ -3642,10 +3658,10 @@
       <c r="AR22" s="19"/>
       <c r="AS22" s="21"/>
       <c r="AT22" s="27" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="AU22" s="7" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="AV22" s="21"/>
       <c r="AW22" s="17"/>
@@ -3680,42 +3696,44 @@
         <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C23" s="4">
         <v>14</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F23" s="17"/>
       <c r="G23" s="17" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="H23" s="17" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="I23" s="17"/>
       <c r="J23" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K23" s="17"/>
       <c r="L23" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M23" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O23" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P23" s="17"/>
+        <v>118</v>
+      </c>
+      <c r="P23" s="17" t="s">
+        <v>119</v>
+      </c>
       <c r="Q23" s="17"/>
       <c r="R23" s="23"/>
       <c r="S23" s="17"/>
@@ -3746,7 +3764,7 @@
       <c r="AR23" s="19"/>
       <c r="AS23" s="21"/>
       <c r="AT23" s="26" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="AU23" s="19"/>
       <c r="AV23" s="18"/>
@@ -3782,42 +3800,44 @@
         <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C24" s="4">
         <v>15</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F24" s="17"/>
       <c r="G24" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I24" s="17"/>
       <c r="J24" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K24" s="17"/>
       <c r="L24" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M24" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O24" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P24" s="17"/>
+        <v>118</v>
+      </c>
+      <c r="P24" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="Q24" s="17"/>
       <c r="R24" s="17"/>
       <c r="S24" s="17"/>
@@ -3846,11 +3866,11 @@
       <c r="AP24" s="17"/>
       <c r="AQ24" s="19"/>
       <c r="AR24" s="41" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="AS24" s="25"/>
       <c r="AT24" s="26" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="AU24" s="17"/>
       <c r="AV24" s="17"/>
@@ -3886,44 +3906,46 @@
         <v>22</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C25" s="4">
         <v>16</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F25" s="17"/>
       <c r="G25" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I25" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K25" s="17"/>
       <c r="L25" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M25" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O25" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P25" s="17"/>
+        <v>118</v>
+      </c>
+      <c r="P25" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="Q25" s="17"/>
       <c r="R25" s="17"/>
       <c r="S25" s="17"/>
@@ -3990,42 +4012,44 @@
         <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C26" s="4">
         <v>9</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F26" s="17"/>
       <c r="G26" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="I26" s="17"/>
       <c r="J26" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K26" s="17"/>
       <c r="L26" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M26" s="29" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N26" s="29" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O26" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P26" s="29"/>
+        <v>118</v>
+      </c>
+      <c r="P26" s="29" t="s">
+        <v>119</v>
+      </c>
       <c r="Q26" s="29"/>
       <c r="R26" s="23"/>
       <c r="S26" s="29"/>
@@ -4056,10 +4080,10 @@
       <c r="AR26" s="19"/>
       <c r="AS26" s="21"/>
       <c r="AT26" s="20" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="AU26" s="34" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="AV26" s="18"/>
       <c r="AW26" s="17"/>
@@ -4097,42 +4121,44 @@
         <v>24</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C27" s="4">
         <v>2</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F27" s="17"/>
       <c r="G27" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I27" s="17"/>
       <c r="J27" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K27" s="17"/>
       <c r="L27" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O27" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P27" s="30"/>
+        <v>118</v>
+      </c>
+      <c r="P27" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="Q27" s="30"/>
       <c r="R27" s="30"/>
       <c r="S27" s="30"/>
@@ -4161,21 +4187,21 @@
       <c r="AP27" s="30"/>
       <c r="AQ27" s="19"/>
       <c r="AR27" s="41" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="AS27" s="18"/>
       <c r="AT27" s="20" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="AU27" s="34" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="AV27" s="18"/>
       <c r="AW27" s="21" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AX27" s="21" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AY27" s="17"/>
       <c r="AZ27" s="17"/>
@@ -4207,44 +4233,46 @@
         <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C28" s="4">
         <v>13</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F28" s="17"/>
       <c r="G28" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="I28" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="J28" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="K28" s="17"/>
       <c r="L28" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O28" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P28" s="30"/>
+        <v>118</v>
+      </c>
+      <c r="P28" s="30" t="s">
+        <v>119</v>
+      </c>
       <c r="Q28" s="30"/>
       <c r="R28" s="30"/>
       <c r="S28" s="30"/>
@@ -4275,10 +4303,10 @@
       <c r="AR28" s="19"/>
       <c r="AS28" s="32"/>
       <c r="AT28" s="27" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="AU28" s="7" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="AV28" s="18"/>
       <c r="AW28" s="17"/>
@@ -4307,42 +4335,44 @@
         <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C29" s="4">
         <v>15</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F29" s="17"/>
       <c r="G29" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I29" s="17"/>
       <c r="J29" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K29" s="17"/>
       <c r="L29" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O29" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P29" s="30"/>
+        <v>118</v>
+      </c>
+      <c r="P29" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="Q29" s="30"/>
       <c r="R29" s="30"/>
       <c r="S29" s="30"/>
@@ -4371,11 +4401,11 @@
       <c r="AP29" s="30"/>
       <c r="AQ29" s="19"/>
       <c r="AR29" s="41" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="AS29" s="32"/>
       <c r="AT29" s="26" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="AU29" s="19"/>
       <c r="AV29" s="18"/>
@@ -4405,42 +4435,44 @@
         <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C30" s="4">
         <v>12</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F30" s="17"/>
       <c r="G30" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I30" s="17"/>
       <c r="J30" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K30" s="17"/>
       <c r="L30" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M30" s="39" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O30" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P30" s="30"/>
+        <v>118</v>
+      </c>
+      <c r="P30" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="Q30" s="30"/>
       <c r="R30" s="30"/>
       <c r="S30" s="30"/>
@@ -4468,13 +4500,13 @@
       <c r="AO30" s="18"/>
       <c r="AP30" s="30"/>
       <c r="AQ30" s="19"/>
-      <c r="AR30" s="62"/>
+      <c r="AR30" s="42"/>
       <c r="AS30" s="32"/>
       <c r="AT30" s="35" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="AU30" s="34" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="AV30" s="18"/>
       <c r="AW30" s="17"/>
@@ -4503,42 +4535,44 @@
         <v>28</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C31" s="4">
         <v>4</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F31" s="17"/>
       <c r="G31" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I31" s="17"/>
       <c r="J31" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K31" s="17"/>
       <c r="L31" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M31" s="38" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O31" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P31" s="30"/>
+        <v>118</v>
+      </c>
+      <c r="P31" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="Q31" s="30"/>
       <c r="R31" s="30"/>
       <c r="S31" s="30"/>
@@ -4567,14 +4601,14 @@
       <c r="AP31" s="30"/>
       <c r="AQ31" s="19"/>
       <c r="AR31" s="41" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="AS31" s="32"/>
       <c r="AT31" s="20" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="AU31" s="19" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="AV31" s="18"/>
       <c r="AW31" s="17"/>
@@ -4603,42 +4637,44 @@
         <v>29</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C32" s="4">
         <v>3</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F32" s="17"/>
       <c r="G32" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I32" s="17"/>
       <c r="J32" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K32" s="17"/>
       <c r="L32" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M32" s="40" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O32" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P32" s="30"/>
+        <v>118</v>
+      </c>
+      <c r="P32" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="Q32" s="30"/>
       <c r="R32" s="30"/>
       <c r="S32" s="30"/>
@@ -4666,19 +4702,19 @@
       <c r="AO32" s="18"/>
       <c r="AP32" s="30"/>
       <c r="AQ32" s="19"/>
-      <c r="AR32" s="62" t="s">
-        <v>185</v>
+      <c r="AR32" s="42" t="s">
+        <v>177</v>
       </c>
       <c r="AS32" s="32"/>
       <c r="AT32" s="33" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="AU32" s="34" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="AV32" s="18"/>
       <c r="AW32" s="17" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AX32" s="28" t="s">
         <v>47</v>
@@ -4707,42 +4743,44 @@
         <v>30</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C33" s="4">
         <v>16</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="F33" s="17"/>
       <c r="G33" s="17" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="I33" s="17"/>
       <c r="J33" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="K33" s="17"/>
       <c r="L33" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O33" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="P33" s="30"/>
+        <v>119</v>
+      </c>
+      <c r="P33" s="30" t="s">
+        <v>119</v>
+      </c>
       <c r="Q33" s="30"/>
       <c r="R33" s="30"/>
       <c r="S33" s="30"/>
@@ -4803,42 +4841,44 @@
         <v>31</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C34" s="4">
         <v>8</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F34" s="17"/>
       <c r="G34" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I34" s="17"/>
       <c r="J34" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K34" s="17"/>
       <c r="L34" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O34" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P34" s="30"/>
+        <v>118</v>
+      </c>
+      <c r="P34" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="Q34" s="30"/>
       <c r="R34" s="30"/>
       <c r="S34" s="30"/>
@@ -4869,10 +4909,10 @@
       <c r="AR34" s="19"/>
       <c r="AS34" s="32"/>
       <c r="AT34" s="20" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AU34" s="19" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="AV34" s="18"/>
       <c r="AW34" s="17"/>
@@ -4901,42 +4941,44 @@
         <v>32</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C35" s="4">
         <v>10</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F35" s="17"/>
       <c r="G35" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I35" s="17"/>
       <c r="J35" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K35" s="17"/>
       <c r="L35" s="17" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="M35" s="38" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O35" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P35" s="30"/>
+        <v>118</v>
+      </c>
+      <c r="P35" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="Q35" s="30"/>
       <c r="R35" s="30"/>
       <c r="S35" s="30"/>
@@ -4967,10 +5009,10 @@
       <c r="AR35" s="41"/>
       <c r="AS35" s="32"/>
       <c r="AT35" s="36" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="AU35" s="34" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="AV35" s="18"/>
       <c r="AW35" s="17"/>
@@ -4999,42 +5041,44 @@
         <v>33</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C36" s="4">
         <v>14</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F36" s="17"/>
       <c r="G36" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I36" s="17"/>
       <c r="J36" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K36" s="17"/>
       <c r="L36" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O36" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P36" s="30"/>
+        <v>118</v>
+      </c>
+      <c r="P36" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="Q36" s="30"/>
       <c r="R36" s="30"/>
       <c r="S36" s="17"/>
@@ -5065,7 +5109,7 @@
       <c r="AR36" s="19"/>
       <c r="AS36" s="25"/>
       <c r="AT36" s="26" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="AU36" s="19"/>
       <c r="AV36" s="17"/>
@@ -5095,44 +5139,46 @@
         <v>34</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C37" s="4">
         <v>18</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="F37" s="17"/>
       <c r="G37" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K37" s="17"/>
       <c r="L37" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="O37" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="P37" s="30"/>
+        <v>119</v>
+      </c>
+      <c r="P37" s="30" t="s">
+        <v>119</v>
+      </c>
       <c r="Q37" s="30"/>
       <c r="R37" s="30"/>
       <c r="S37" s="17"/>
@@ -5163,10 +5209,10 @@
       <c r="AR37" s="19"/>
       <c r="AS37" s="25"/>
       <c r="AT37" s="33" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="AU37" s="34" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="AV37" s="17"/>
       <c r="AW37" s="17"/>
@@ -5191,53 +5237,53 @@
       <c r="BP37" s="30"/>
     </row>
     <row r="38" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A38" s="55" t="s">
+      <c r="A38" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="B38" s="56"/>
-      <c r="C38" s="56"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="56"/>
-      <c r="G38" s="56"/>
-      <c r="H38" s="56"/>
-      <c r="I38" s="56"/>
-      <c r="J38" s="56"/>
-      <c r="K38" s="56"/>
-      <c r="L38" s="56"/>
-      <c r="M38" s="56"/>
-      <c r="N38" s="56"/>
-      <c r="O38" s="56"/>
-      <c r="P38" s="56"/>
-      <c r="Q38" s="56"/>
-      <c r="R38" s="56"/>
-      <c r="S38" s="56"/>
-      <c r="T38" s="56"/>
-      <c r="U38" s="56"/>
-      <c r="V38" s="56"/>
-      <c r="W38" s="56"/>
-      <c r="X38" s="56"/>
-      <c r="Y38" s="56"/>
-      <c r="Z38" s="56"/>
-      <c r="AA38" s="56"/>
-      <c r="AB38" s="56"/>
-      <c r="AC38" s="56"/>
-      <c r="AD38" s="56"/>
-      <c r="AE38" s="56"/>
-      <c r="AF38" s="56"/>
-      <c r="AG38" s="56"/>
-      <c r="AH38" s="56"/>
-      <c r="AI38" s="56"/>
-      <c r="AJ38" s="56"/>
-      <c r="AK38" s="56"/>
-      <c r="AL38" s="56"/>
-      <c r="AM38" s="56"/>
-      <c r="AN38" s="56"/>
-      <c r="AO38" s="56"/>
-      <c r="AP38" s="56"/>
-      <c r="AQ38" s="56"/>
-      <c r="AR38" s="56"/>
-      <c r="AS38" s="57"/>
+      <c r="B38" s="50"/>
+      <c r="C38" s="50"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="50"/>
+      <c r="F38" s="50"/>
+      <c r="G38" s="50"/>
+      <c r="H38" s="50"/>
+      <c r="I38" s="50"/>
+      <c r="J38" s="50"/>
+      <c r="K38" s="50"/>
+      <c r="L38" s="50"/>
+      <c r="M38" s="50"/>
+      <c r="N38" s="50"/>
+      <c r="O38" s="50"/>
+      <c r="P38" s="50"/>
+      <c r="Q38" s="50"/>
+      <c r="R38" s="50"/>
+      <c r="S38" s="50"/>
+      <c r="T38" s="50"/>
+      <c r="U38" s="50"/>
+      <c r="V38" s="50"/>
+      <c r="W38" s="50"/>
+      <c r="X38" s="50"/>
+      <c r="Y38" s="50"/>
+      <c r="Z38" s="50"/>
+      <c r="AA38" s="50"/>
+      <c r="AB38" s="50"/>
+      <c r="AC38" s="50"/>
+      <c r="AD38" s="50"/>
+      <c r="AE38" s="50"/>
+      <c r="AF38" s="50"/>
+      <c r="AG38" s="50"/>
+      <c r="AH38" s="50"/>
+      <c r="AI38" s="50"/>
+      <c r="AJ38" s="50"/>
+      <c r="AK38" s="50"/>
+      <c r="AL38" s="50"/>
+      <c r="AM38" s="50"/>
+      <c r="AN38" s="50"/>
+      <c r="AO38" s="50"/>
+      <c r="AP38" s="50"/>
+      <c r="AQ38" s="50"/>
+      <c r="AR38" s="50"/>
+      <c r="AS38" s="51"/>
       <c r="AT38" s="2"/>
       <c r="AU38" s="2"/>
       <c r="AV38" s="2"/>
@@ -5269,53 +5315,53 @@
       </c>
     </row>
     <row r="39" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A39" s="58" t="s">
-        <v>93</v>
-      </c>
-      <c r="B39" s="59"/>
-      <c r="C39" s="59"/>
-      <c r="D39" s="59"/>
-      <c r="E39" s="59"/>
-      <c r="F39" s="59"/>
-      <c r="G39" s="59"/>
-      <c r="H39" s="59"/>
-      <c r="I39" s="59"/>
-      <c r="J39" s="59"/>
-      <c r="K39" s="59"/>
-      <c r="L39" s="59"/>
-      <c r="M39" s="59"/>
-      <c r="N39" s="59"/>
-      <c r="O39" s="59"/>
-      <c r="P39" s="59"/>
-      <c r="Q39" s="59"/>
-      <c r="R39" s="59"/>
-      <c r="S39" s="59"/>
-      <c r="T39" s="59"/>
-      <c r="U39" s="59"/>
-      <c r="V39" s="59"/>
-      <c r="W39" s="59"/>
-      <c r="X39" s="59"/>
-      <c r="Y39" s="59"/>
-      <c r="Z39" s="59"/>
-      <c r="AA39" s="59"/>
-      <c r="AB39" s="59"/>
-      <c r="AC39" s="59"/>
-      <c r="AD39" s="59"/>
-      <c r="AE39" s="59"/>
-      <c r="AF39" s="59"/>
-      <c r="AG39" s="59"/>
-      <c r="AH39" s="59"/>
-      <c r="AI39" s="59"/>
-      <c r="AJ39" s="59"/>
-      <c r="AK39" s="59"/>
-      <c r="AL39" s="59"/>
-      <c r="AM39" s="59"/>
-      <c r="AN39" s="59"/>
-      <c r="AO39" s="59"/>
-      <c r="AP39" s="59"/>
-      <c r="AQ39" s="59"/>
-      <c r="AR39" s="59"/>
-      <c r="AS39" s="60"/>
+      <c r="A39" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="B39" s="53"/>
+      <c r="C39" s="53"/>
+      <c r="D39" s="53"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="53"/>
+      <c r="G39" s="53"/>
+      <c r="H39" s="53"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="53"/>
+      <c r="L39" s="53"/>
+      <c r="M39" s="53"/>
+      <c r="N39" s="53"/>
+      <c r="O39" s="53"/>
+      <c r="P39" s="53"/>
+      <c r="Q39" s="53"/>
+      <c r="R39" s="53"/>
+      <c r="S39" s="53"/>
+      <c r="T39" s="53"/>
+      <c r="U39" s="53"/>
+      <c r="V39" s="53"/>
+      <c r="W39" s="53"/>
+      <c r="X39" s="53"/>
+      <c r="Y39" s="53"/>
+      <c r="Z39" s="53"/>
+      <c r="AA39" s="53"/>
+      <c r="AB39" s="53"/>
+      <c r="AC39" s="53"/>
+      <c r="AD39" s="53"/>
+      <c r="AE39" s="53"/>
+      <c r="AF39" s="53"/>
+      <c r="AG39" s="53"/>
+      <c r="AH39" s="53"/>
+      <c r="AI39" s="53"/>
+      <c r="AJ39" s="53"/>
+      <c r="AK39" s="53"/>
+      <c r="AL39" s="53"/>
+      <c r="AM39" s="53"/>
+      <c r="AN39" s="53"/>
+      <c r="AO39" s="53"/>
+      <c r="AP39" s="53"/>
+      <c r="AQ39" s="53"/>
+      <c r="AR39" s="53"/>
+      <c r="AS39" s="54"/>
       <c r="AT39" s="2"/>
       <c r="AU39" s="2"/>
       <c r="AV39" s="2"/>
@@ -5464,109 +5510,109 @@
     </row>
     <row r="41" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E41" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="F41" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="G41" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="H41" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="I41" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="J41" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="K41" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="L41" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="M41" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="N41" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="O41" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="P41" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="Q41" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="R41" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="S41" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="T41" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="U41" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="V41" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="W41" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="X41" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="Y41" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="AA41" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="AB41" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="AC41" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="AD41" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="AE41" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="AF41" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="AG41" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="AH41" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="AI41" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="AJ41" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="AK41" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="AL41" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="AM41" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="BA41"/>
       <c r="BQ41">
@@ -5578,31 +5624,25 @@
     </row>
     <row r="42" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="16" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="J42" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="K42" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="L42" t="s">
-        <v>183</v>
-      </c>
-      <c r="M42" t="s">
-        <v>67</v>
-      </c>
-      <c r="O42" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>68</v>
-      </c>
-      <c r="R42" t="s">
+        <v>175</v>
+      </c>
+      <c r="N42" t="s">
+        <v>178</v>
+      </c>
+      <c r="P42" t="s">
+        <v>70</v>
+      </c>
+      <c r="BC42" t="s">
         <v>69</v>
-      </c>
-      <c r="BC42" t="s">
-        <v>72</v>
       </c>
       <c r="BQ42">
         <v>28</v>
@@ -5613,26 +5653,20 @@
     </row>
     <row r="43" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E43" s="16" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F43" s="16"/>
       <c r="H43" s="16" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="I43" s="16" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="L43" t="s">
-        <v>73</v>
-      </c>
-      <c r="N43" t="s">
-        <v>74</v>
-      </c>
-      <c r="S43" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BC43" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="BQ43" s="14">
         <v>29</v>
@@ -5644,16 +5678,10 @@
     </row>
     <row r="44" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="N44" t="s">
-        <v>78</v>
-      </c>
-      <c r="T44" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="AQ44" t="s">
         <v>62</v>
@@ -5670,10 +5698,7 @@
     </row>
     <row r="45" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" t="s">
-        <v>80</v>
-      </c>
-      <c r="V45" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AQ45" t="s">
         <v>64</v>
@@ -5685,18 +5710,18 @@
         <v>31</v>
       </c>
       <c r="BS45" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AQ46" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="AR46" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="BQ46" s="14">
         <v>32</v>
@@ -5741,7 +5766,7 @@
     </row>
     <row r="51" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BS51" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="53" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5764,10 +5789,10 @@
         <v>38</v>
       </c>
       <c r="BS55" s="13" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="BT55" s="11" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="BU55" s="8" t="s">
         <v>36</v>
@@ -5779,10 +5804,10 @@
     <row r="56" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BS56" s="10"/>
       <c r="BT56" s="11" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="BU56" s="8" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="BV56">
         <v>50</v>
@@ -5793,10 +5818,10 @@
         <v>39</v>
       </c>
       <c r="BS57" s="8" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="BT57" s="11" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="BU57" s="8" t="s">
         <v>47</v>
@@ -5880,7 +5905,7 @@
         <v>47</v>
       </c>
       <c r="BS65" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="66" spans="69:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5888,26 +5913,31 @@
         <v>48</v>
       </c>
       <c r="BS66" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="BN2:BP3"/>
-    <mergeCell ref="A38:AS38"/>
-    <mergeCell ref="A39:AS39"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="AO2:AO3"/>
-    <mergeCell ref="AP2:AP3"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="BC2:BF3"/>
-    <mergeCell ref="BG2:BJ3"/>
-    <mergeCell ref="BK2:BM3"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="AZ2:BB3"/>
+    <mergeCell ref="AT2:AV3"/>
+    <mergeCell ref="AW2:AY3"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="AH2:AH3"/>
+    <mergeCell ref="AI2:AI3"/>
+    <mergeCell ref="AJ2:AJ3"/>
+    <mergeCell ref="AK2:AK3"/>
+    <mergeCell ref="AL2:AL3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="AM2:AM3"/>
     <mergeCell ref="A1:AS1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="D2:D3"/>
@@ -5924,32 +5954,27 @@
     <mergeCell ref="X2:X3"/>
     <mergeCell ref="AA2:AA3"/>
     <mergeCell ref="AN2:AN3"/>
+    <mergeCell ref="BN2:BP3"/>
+    <mergeCell ref="A38:AS38"/>
+    <mergeCell ref="A39:AS39"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="AO2:AO3"/>
+    <mergeCell ref="AP2:AP3"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="BC2:BF3"/>
+    <mergeCell ref="BG2:BJ3"/>
+    <mergeCell ref="BK2:BM3"/>
     <mergeCell ref="K2:K3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="AZ2:BB3"/>
-    <mergeCell ref="AT2:AV3"/>
-    <mergeCell ref="AW2:AY3"/>
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="AH2:AH3"/>
-    <mergeCell ref="AI2:AI3"/>
-    <mergeCell ref="AJ2:AJ3"/>
-    <mergeCell ref="AK2:AK3"/>
-    <mergeCell ref="AL2:AL3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="AM2:AM3"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AB2:AB3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="BS6" r:id="rId1" display="Прикладная дискретная математика. Приложение. 2016. № 9. С. 68-70." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="BR26" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="BS48" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="BS6" r:id="rId1" display="Прикладная дискретная математика. Приложение. 2016. № 9. С. 68-70."/>
+    <hyperlink ref="BR26" r:id="rId2"/>
+    <hyperlink ref="BS48" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId4"/>
@@ -6159,15 +6184,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="b78dbef7-f85b-47b5-8738-6377d50f4027" xsi:nil="true"/>
@@ -6176,6 +6192,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6198,14 +6223,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00280879-8A9A-4335-93BC-405126DC8F0C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12ECB55F-B88E-4FE2-9AD5-5CA5D433F306}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -6214,4 +6231,12 @@
     <ds:schemaRef ds:uri="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00280879-8A9A-4335-93BC-405126DC8F0C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Ведомость ТКИ-441 2026-2027.xlsx
+++ b/Ведомость ТКИ-441 2026-2027.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\StegMethods\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\StegMethods\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BE4F90-D776-42AC-BE96-2A88F2748415}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="180">
   <si>
     <t>Ведомость посещаемости занятий студентами группы ТКИ РУТ МИИТ</t>
   </si>
@@ -562,12 +563,15 @@
   </si>
   <si>
     <t>Фильм</t>
+  </si>
+  <si>
+    <t>8ПЧ2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -827,7 +831,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -905,12 +909,31 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -929,31 +952,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="16" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1"/>
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -973,14 +981,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>58</xdr:col>
+      <xdr:col>62</xdr:col>
       <xdr:colOff>361950</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>98219</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>65</xdr:col>
-      <xdr:colOff>406853</xdr:colOff>
+      <xdr:col>69</xdr:col>
+      <xdr:colOff>406854</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>119248</xdr:rowOff>
     </xdr:to>
@@ -989,7 +997,7 @@
         <xdr:cNvPr id="3" name="Рисунок 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{13645ABC-C350-4C12-BD87-CB39C6C63ABA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13645ABC-C350-4C12-BD87-CB39C6C63ABA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1280,8 +1288,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BV66"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BZ66"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="35.5703125" customWidth="1"/>
@@ -1295,316 +1303,337 @@
     <col min="17" max="20" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.85546875" customWidth="1"/>
     <col min="22" max="23" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="40" width="10.85546875" customWidth="1"/>
-    <col min="41" max="41" width="11.5703125" customWidth="1"/>
-    <col min="44" max="44" width="12.28515625" customWidth="1"/>
-    <col min="45" max="45" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="15.7109375" customWidth="1"/>
-    <col min="47" max="47" width="11.85546875" customWidth="1"/>
-    <col min="48" max="48" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="9.140625" style="12"/>
-    <col min="54" max="54" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="44" width="10.85546875" customWidth="1"/>
+    <col min="45" max="45" width="11.5703125" customWidth="1"/>
+    <col min="48" max="48" width="12.28515625" customWidth="1"/>
+    <col min="49" max="49" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="15.7109375" customWidth="1"/>
+    <col min="51" max="51" width="11.85546875" customWidth="1"/>
+    <col min="52" max="52" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="9.140625" style="12"/>
+    <col min="58" max="58" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="62" max="62" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="11.5703125" customWidth="1"/>
-    <col min="71" max="71" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="11.5703125" customWidth="1"/>
+    <col min="75" max="75" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="34.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
+    <row r="1" spans="1:77" x14ac:dyDescent="0.25">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
-      <c r="S1" s="61"/>
-      <c r="T1" s="61"/>
-      <c r="U1" s="61"/>
-      <c r="V1" s="61"/>
-      <c r="W1" s="61"/>
-      <c r="X1" s="61"/>
-      <c r="Y1" s="61"/>
-      <c r="Z1" s="61"/>
-      <c r="AA1" s="61"/>
-      <c r="AB1" s="61"/>
-      <c r="AC1" s="61"/>
-      <c r="AD1" s="61"/>
-      <c r="AE1" s="61"/>
-      <c r="AF1" s="61"/>
-      <c r="AG1" s="61"/>
-      <c r="AH1" s="61"/>
-      <c r="AI1" s="61"/>
-      <c r="AJ1" s="61"/>
-      <c r="AK1" s="61"/>
-      <c r="AL1" s="61"/>
-      <c r="AM1" s="61"/>
-      <c r="AN1" s="61"/>
-      <c r="AO1" s="61"/>
-      <c r="AP1" s="61"/>
-      <c r="AQ1" s="61"/>
-      <c r="AR1" s="61"/>
-      <c r="AS1" s="61"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="53"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="53"/>
+      <c r="X1" s="53"/>
+      <c r="Y1" s="53"/>
+      <c r="Z1" s="53"/>
+      <c r="AA1" s="53"/>
+      <c r="AB1" s="53"/>
+      <c r="AC1" s="53"/>
+      <c r="AD1" s="53"/>
+      <c r="AE1" s="53"/>
+      <c r="AF1" s="53"/>
+      <c r="AG1" s="53"/>
+      <c r="AH1" s="53"/>
+      <c r="AI1" s="53"/>
+      <c r="AJ1" s="53"/>
+      <c r="AK1" s="53"/>
+      <c r="AL1" s="53"/>
+      <c r="AM1" s="53"/>
+      <c r="AN1" s="53"/>
+      <c r="AO1" s="53"/>
+      <c r="AP1" s="53"/>
+      <c r="AQ1" s="53"/>
+      <c r="AR1" s="53"/>
+      <c r="AS1" s="53"/>
+      <c r="AT1" s="53"/>
+      <c r="AU1" s="53"/>
+      <c r="AV1" s="53"/>
+      <c r="AW1" s="53"/>
     </row>
-    <row r="2" spans="1:73" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
+    <row r="2" spans="1:77" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="60" t="s">
+      <c r="B2" s="54"/>
+      <c r="C2" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="55">
+      <c r="D2" s="43">
         <v>46268</v>
       </c>
-      <c r="E2" s="55">
+      <c r="E2" s="43">
         <v>46272</v>
       </c>
-      <c r="F2" s="55">
+      <c r="F2" s="43">
         <v>46273</v>
       </c>
-      <c r="G2" s="55">
+      <c r="G2" s="43">
         <v>46275</v>
       </c>
-      <c r="H2" s="55">
+      <c r="H2" s="43">
         <v>46279</v>
       </c>
-      <c r="I2" s="58">
+      <c r="I2" s="51">
         <v>46282</v>
       </c>
-      <c r="J2" s="55">
+      <c r="J2" s="43">
         <v>46286</v>
       </c>
-      <c r="K2" s="55">
+      <c r="K2" s="43">
         <v>46287</v>
       </c>
-      <c r="L2" s="58">
+      <c r="L2" s="51">
         <v>46289</v>
       </c>
-      <c r="M2" s="55">
+      <c r="M2" s="43">
         <v>46293</v>
       </c>
-      <c r="N2" s="58">
+      <c r="N2" s="51">
         <v>46296</v>
       </c>
-      <c r="O2" s="55">
+      <c r="O2" s="43">
         <v>46300</v>
       </c>
-      <c r="P2" s="55">
+      <c r="P2" s="43">
         <v>46301</v>
       </c>
-      <c r="Q2" s="58">
+      <c r="Q2" s="51">
         <v>46303</v>
       </c>
-      <c r="R2" s="55">
+      <c r="R2" s="43">
         <v>46307</v>
       </c>
-      <c r="S2" s="58">
+      <c r="S2" s="51">
         <v>46310</v>
       </c>
-      <c r="T2" s="55">
+      <c r="T2" s="43">
         <v>46314</v>
       </c>
-      <c r="U2" s="55">
+      <c r="U2" s="43">
         <v>46315</v>
       </c>
-      <c r="V2" s="58">
+      <c r="V2" s="51">
         <v>46317</v>
       </c>
-      <c r="W2" s="55">
+      <c r="W2" s="43">
         <v>46321</v>
       </c>
-      <c r="X2" s="55">
+      <c r="X2" s="43">
         <v>46324</v>
       </c>
-      <c r="Y2" s="55">
+      <c r="Y2" s="43">
         <v>46328</v>
       </c>
-      <c r="Z2" s="55">
-        <v>46328</v>
-      </c>
-      <c r="AA2" s="55">
+      <c r="Z2" s="43">
+        <v>46329</v>
+      </c>
+      <c r="AA2" s="43">
         <v>46331</v>
       </c>
-      <c r="AB2" s="55">
+      <c r="AB2" s="43">
         <v>46335</v>
       </c>
-      <c r="AC2" s="55">
+      <c r="AC2" s="43">
         <v>46338</v>
       </c>
-      <c r="AD2" s="55">
+      <c r="AD2" s="43">
         <v>46342</v>
       </c>
-      <c r="AE2" s="55">
+      <c r="AE2" s="43">
+        <v>46343</v>
+      </c>
+      <c r="AF2" s="43">
         <v>46345</v>
       </c>
-      <c r="AF2" s="55">
+      <c r="AG2" s="43">
         <v>46349</v>
       </c>
-      <c r="AG2" s="55">
+      <c r="AH2" s="43">
         <v>46352</v>
       </c>
-      <c r="AH2" s="55">
+      <c r="AI2" s="43">
         <v>46356</v>
       </c>
-      <c r="AI2" s="58">
+      <c r="AJ2" s="51">
+        <v>46357</v>
+      </c>
+      <c r="AK2" s="51">
         <v>46359</v>
       </c>
-      <c r="AJ2" s="58">
+      <c r="AL2" s="51">
         <v>46363</v>
       </c>
-      <c r="AK2" s="58">
+      <c r="AM2" s="51">
         <v>46366</v>
       </c>
-      <c r="AL2" s="58">
+      <c r="AN2" s="51">
         <v>46370</v>
       </c>
-      <c r="AM2" s="58">
+      <c r="AO2" s="51">
+        <v>46371</v>
+      </c>
+      <c r="AP2" s="51">
         <v>46373</v>
       </c>
-      <c r="AN2" s="58">
+      <c r="AQ2" s="51">
         <v>46377</v>
       </c>
-      <c r="AO2" s="57" t="s">
+      <c r="AR2" s="51">
+        <v>46380</v>
+      </c>
+      <c r="AS2" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="AP2" s="57"/>
-      <c r="AQ2" s="43" t="s">
+      <c r="AT2" s="54"/>
+      <c r="AU2" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="AR2" s="44"/>
-      <c r="AS2" s="45"/>
-      <c r="AT2" s="43" t="s">
+      <c r="AV2" s="46"/>
+      <c r="AW2" s="47"/>
+      <c r="AX2" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="AU2" s="44"/>
-      <c r="AV2" s="45"/>
-      <c r="AW2" s="43" t="s">
+      <c r="AY2" s="46"/>
+      <c r="AZ2" s="47"/>
+      <c r="BA2" s="45" t="s">
         <v>162</v>
       </c>
-      <c r="AX2" s="44"/>
-      <c r="AY2" s="45"/>
-      <c r="AZ2" s="43" t="s">
+      <c r="BB2" s="46"/>
+      <c r="BC2" s="47"/>
+      <c r="BD2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="BA2" s="44"/>
-      <c r="BB2" s="45"/>
-      <c r="BC2" s="43" t="s">
+      <c r="BE2" s="46"/>
+      <c r="BF2" s="47"/>
+      <c r="BG2" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="BD2" s="44"/>
-      <c r="BE2" s="44"/>
-      <c r="BF2" s="45"/>
-      <c r="BG2" s="43" t="s">
+      <c r="BH2" s="46"/>
+      <c r="BI2" s="46"/>
+      <c r="BJ2" s="47"/>
+      <c r="BK2" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="BH2" s="44"/>
-      <c r="BI2" s="44"/>
-      <c r="BJ2" s="45" t="s">
+      <c r="BL2" s="46"/>
+      <c r="BM2" s="46"/>
+      <c r="BN2" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="BK2" s="43" t="s">
+      <c r="BO2" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="BL2" s="44"/>
-      <c r="BM2" s="45"/>
-      <c r="BN2" s="43" t="s">
+      <c r="BP2" s="46"/>
+      <c r="BQ2" s="47"/>
+      <c r="BR2" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="BO2" s="44"/>
-      <c r="BP2" s="45"/>
+      <c r="BS2" s="46"/>
+      <c r="BT2" s="47"/>
     </row>
-    <row r="3" spans="1:73" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:77" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="57"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="59"/>
-      <c r="M3" s="56"/>
-      <c r="N3" s="59"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="56"/>
-      <c r="Q3" s="59"/>
-      <c r="R3" s="56"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="56"/>
-      <c r="U3" s="56"/>
-      <c r="V3" s="59"/>
-      <c r="W3" s="56"/>
-      <c r="X3" s="56"/>
-      <c r="Y3" s="56"/>
-      <c r="Z3" s="56"/>
-      <c r="AA3" s="56"/>
-      <c r="AB3" s="56"/>
-      <c r="AC3" s="56"/>
-      <c r="AD3" s="56"/>
-      <c r="AE3" s="56"/>
-      <c r="AF3" s="56"/>
-      <c r="AG3" s="56"/>
-      <c r="AH3" s="56"/>
-      <c r="AI3" s="59"/>
-      <c r="AJ3" s="59"/>
-      <c r="AK3" s="59"/>
-      <c r="AL3" s="59"/>
-      <c r="AM3" s="59"/>
-      <c r="AN3" s="59"/>
-      <c r="AO3" s="57"/>
-      <c r="AP3" s="57"/>
-      <c r="AQ3" s="46"/>
-      <c r="AR3" s="62"/>
-      <c r="AS3" s="48"/>
-      <c r="AT3" s="46"/>
-      <c r="AU3" s="47"/>
-      <c r="AV3" s="48"/>
-      <c r="AW3" s="46"/>
-      <c r="AX3" s="47"/>
-      <c r="AY3" s="48"/>
-      <c r="AZ3" s="46"/>
-      <c r="BA3" s="47"/>
-      <c r="BB3" s="48"/>
-      <c r="BC3" s="46"/>
-      <c r="BD3" s="47"/>
-      <c r="BE3" s="47"/>
-      <c r="BF3" s="48"/>
-      <c r="BG3" s="46"/>
-      <c r="BH3" s="47"/>
-      <c r="BI3" s="47"/>
-      <c r="BJ3" s="48"/>
-      <c r="BK3" s="46"/>
-      <c r="BL3" s="47"/>
-      <c r="BM3" s="48"/>
-      <c r="BN3" s="46"/>
-      <c r="BO3" s="47"/>
-      <c r="BP3" s="48"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="44"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="44"/>
+      <c r="P3" s="44"/>
+      <c r="Q3" s="52"/>
+      <c r="R3" s="44"/>
+      <c r="S3" s="52"/>
+      <c r="T3" s="44"/>
+      <c r="U3" s="44"/>
+      <c r="V3" s="52"/>
+      <c r="W3" s="44"/>
+      <c r="X3" s="44"/>
+      <c r="Y3" s="44"/>
+      <c r="Z3" s="44"/>
+      <c r="AA3" s="44"/>
+      <c r="AB3" s="44"/>
+      <c r="AC3" s="44"/>
+      <c r="AD3" s="44"/>
+      <c r="AE3" s="44"/>
+      <c r="AF3" s="44"/>
+      <c r="AG3" s="44"/>
+      <c r="AH3" s="44"/>
+      <c r="AI3" s="44"/>
+      <c r="AJ3" s="52"/>
+      <c r="AK3" s="52"/>
+      <c r="AL3" s="52"/>
+      <c r="AM3" s="52"/>
+      <c r="AN3" s="52"/>
+      <c r="AO3" s="52"/>
+      <c r="AP3" s="52"/>
+      <c r="AQ3" s="52"/>
+      <c r="AR3" s="52"/>
+      <c r="AS3" s="54"/>
+      <c r="AT3" s="54"/>
+      <c r="AU3" s="48"/>
+      <c r="AV3" s="55"/>
+      <c r="AW3" s="50"/>
+      <c r="AX3" s="48"/>
+      <c r="AY3" s="49"/>
+      <c r="AZ3" s="50"/>
+      <c r="BA3" s="48"/>
+      <c r="BB3" s="49"/>
+      <c r="BC3" s="50"/>
+      <c r="BD3" s="48"/>
+      <c r="BE3" s="49"/>
+      <c r="BF3" s="50"/>
+      <c r="BG3" s="48"/>
+      <c r="BH3" s="49"/>
+      <c r="BI3" s="49"/>
+      <c r="BJ3" s="50"/>
+      <c r="BK3" s="48"/>
+      <c r="BL3" s="49"/>
+      <c r="BM3" s="49"/>
+      <c r="BN3" s="50"/>
+      <c r="BO3" s="48"/>
+      <c r="BP3" s="49"/>
+      <c r="BQ3" s="50"/>
+      <c r="BR3" s="48"/>
+      <c r="BS3" s="49"/>
+      <c r="BT3" s="50"/>
     </row>
-    <row r="4" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -1647,7 +1676,9 @@
       <c r="P4" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="Q4" s="17"/>
+      <c r="Q4" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="R4" s="17"/>
       <c r="S4" s="17"/>
       <c r="T4" s="17"/>
@@ -1671,48 +1702,52 @@
       <c r="AL4" s="17"/>
       <c r="AM4" s="17"/>
       <c r="AN4" s="17"/>
-      <c r="AO4" s="18"/>
+      <c r="AO4" s="17"/>
       <c r="AP4" s="17"/>
-      <c r="AQ4" s="19"/>
-      <c r="AR4" s="19"/>
+      <c r="AQ4" s="17"/>
+      <c r="AR4" s="17"/>
       <c r="AS4" s="18"/>
-      <c r="AT4" s="33" t="s">
+      <c r="AT4" s="17"/>
+      <c r="AU4" s="19"/>
+      <c r="AV4" s="19"/>
+      <c r="AW4" s="18"/>
+      <c r="AX4" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="AU4" s="34" t="s">
+      <c r="AY4" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="AV4" s="21"/>
-      <c r="AW4" s="21" t="s">
+      <c r="AZ4" s="21"/>
+      <c r="BA4" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="AX4" s="21" t="s">
+      <c r="BB4" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="AY4" s="18"/>
-      <c r="AZ4" s="34" t="s">
+      <c r="BC4" s="18"/>
+      <c r="BD4" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="BA4" s="34" t="s">
+      <c r="BE4" s="34" t="s">
         <v>167</v>
       </c>
-      <c r="BB4" s="34"/>
-      <c r="BC4" s="17"/>
-      <c r="BD4" s="17"/>
-      <c r="BE4" s="17"/>
-      <c r="BF4" s="18"/>
+      <c r="BF4" s="34"/>
       <c r="BG4" s="17"/>
       <c r="BH4" s="17"/>
       <c r="BI4" s="17"/>
       <c r="BJ4" s="18"/>
-      <c r="BK4" s="18"/>
+      <c r="BK4" s="17"/>
       <c r="BL4" s="17"/>
       <c r="BM4" s="17"/>
-      <c r="BN4" s="17"/>
-      <c r="BO4" s="17"/>
+      <c r="BN4" s="18"/>
+      <c r="BO4" s="18"/>
       <c r="BP4" s="17"/>
+      <c r="BQ4" s="17"/>
+      <c r="BR4" s="17"/>
+      <c r="BS4" s="17"/>
+      <c r="BT4" s="17"/>
     </row>
-    <row r="5" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -1755,7 +1790,9 @@
       <c r="P5" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="Q5" s="17"/>
+      <c r="Q5" s="38" t="s">
+        <v>118</v>
+      </c>
       <c r="R5" s="17"/>
       <c r="S5" s="17"/>
       <c r="T5" s="17"/>
@@ -1779,65 +1816,69 @@
       <c r="AL5" s="17"/>
       <c r="AM5" s="17"/>
       <c r="AN5" s="17"/>
-      <c r="AO5" s="18"/>
+      <c r="AO5" s="17"/>
       <c r="AP5" s="17"/>
-      <c r="AQ5" s="19"/>
-      <c r="AR5" s="41" t="s">
+      <c r="AQ5" s="17"/>
+      <c r="AR5" s="17"/>
+      <c r="AS5" s="18"/>
+      <c r="AT5" s="17"/>
+      <c r="AU5" s="19"/>
+      <c r="AV5" s="41" t="s">
         <v>177</v>
       </c>
-      <c r="AS5" s="21"/>
-      <c r="AT5" s="33" t="s">
+      <c r="AW5" s="21"/>
+      <c r="AX5" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="AU5" s="34" t="s">
+      <c r="AY5" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="AV5" s="21"/>
-      <c r="AW5" s="21" t="s">
+      <c r="AZ5" s="21"/>
+      <c r="BA5" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="AX5" s="21" t="s">
+      <c r="BB5" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="AY5" s="18"/>
-      <c r="AZ5" s="34" t="s">
+      <c r="BC5" s="18"/>
+      <c r="BD5" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="BA5" s="34" t="s">
+      <c r="BE5" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="BB5" s="34"/>
-      <c r="BC5" s="17"/>
-      <c r="BD5" s="17"/>
-      <c r="BE5" s="17"/>
-      <c r="BF5" s="18"/>
+      <c r="BF5" s="34"/>
       <c r="BG5" s="17"/>
       <c r="BH5" s="17"/>
       <c r="BI5" s="17"/>
       <c r="BJ5" s="18"/>
-      <c r="BK5" s="18"/>
+      <c r="BK5" s="17"/>
       <c r="BL5" s="17"/>
       <c r="BM5" s="17"/>
-      <c r="BN5" s="17"/>
-      <c r="BO5" s="17"/>
+      <c r="BN5" s="18"/>
+      <c r="BO5" s="18"/>
       <c r="BP5" s="17"/>
-      <c r="BQ5">
+      <c r="BQ5" s="17"/>
+      <c r="BR5" s="17"/>
+      <c r="BS5" s="17"/>
+      <c r="BT5" s="17"/>
+      <c r="BU5">
         <v>1</v>
       </c>
-      <c r="BR5" t="s">
+      <c r="BV5" t="s">
         <v>17</v>
       </c>
-      <c r="BS5" s="7" t="s">
+      <c r="BW5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="BT5" t="s">
+      <c r="BX5" t="s">
         <v>19</v>
       </c>
-      <c r="BU5" t="s">
+      <c r="BY5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:73" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:77" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -1880,7 +1921,9 @@
       <c r="P6" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="Q6" s="17"/>
+      <c r="Q6" s="38" t="s">
+        <v>118</v>
+      </c>
       <c r="R6" s="17"/>
       <c r="S6" s="17"/>
       <c r="T6" s="17"/>
@@ -1904,54 +1947,58 @@
       <c r="AL6" s="17"/>
       <c r="AM6" s="17"/>
       <c r="AN6" s="17"/>
-      <c r="AO6" s="18"/>
+      <c r="AO6" s="17"/>
       <c r="AP6" s="17"/>
-      <c r="AQ6" s="19"/>
-      <c r="AR6" s="42" t="s">
+      <c r="AQ6" s="17"/>
+      <c r="AR6" s="17"/>
+      <c r="AS6" s="18"/>
+      <c r="AT6" s="17"/>
+      <c r="AU6" s="19"/>
+      <c r="AV6" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="AS6" s="21"/>
-      <c r="AT6" s="33" t="s">
+      <c r="AW6" s="21"/>
+      <c r="AX6" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="AU6" s="34" t="s">
+      <c r="AY6" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="AV6" s="21"/>
-      <c r="AW6" s="11" t="s">
+      <c r="AZ6" s="21"/>
+      <c r="BA6" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="AX6" s="8" t="s">
+      <c r="BB6" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AY6" s="18"/>
-      <c r="AZ6" s="8" t="s">
+      <c r="BC6" s="18"/>
+      <c r="BD6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="BA6" s="34"/>
-      <c r="BB6" s="34"/>
-      <c r="BC6" s="17"/>
-      <c r="BD6" s="22"/>
-      <c r="BE6" s="17"/>
-      <c r="BF6" s="18"/>
+      <c r="BE6" s="34"/>
+      <c r="BF6" s="34"/>
       <c r="BG6" s="17"/>
-      <c r="BH6" s="17"/>
+      <c r="BH6" s="22"/>
       <c r="BI6" s="17"/>
       <c r="BJ6" s="18"/>
-      <c r="BK6" s="18"/>
+      <c r="BK6" s="17"/>
       <c r="BL6" s="17"/>
       <c r="BM6" s="17"/>
-      <c r="BN6" s="17"/>
-      <c r="BO6" s="17"/>
+      <c r="BN6" s="18"/>
+      <c r="BO6" s="18"/>
       <c r="BP6" s="17"/>
-      <c r="BQ6">
+      <c r="BQ6" s="17"/>
+      <c r="BR6" s="17"/>
+      <c r="BS6" s="17"/>
+      <c r="BT6" s="17"/>
+      <c r="BU6">
         <v>2</v>
       </c>
-      <c r="BS6" s="7" t="s">
+      <c r="BW6" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:73" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:77" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -1994,7 +2041,9 @@
       <c r="P7" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="Q7" s="17"/>
+      <c r="Q7" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="R7" s="17"/>
       <c r="S7" s="17"/>
       <c r="T7" s="17"/>
@@ -2020,36 +2069,36 @@
       <c r="AN7" s="17"/>
       <c r="AO7" s="17"/>
       <c r="AP7" s="17"/>
-      <c r="AQ7" s="19"/>
-      <c r="AR7" s="41" t="s">
+      <c r="AQ7" s="17"/>
+      <c r="AR7" s="17"/>
+      <c r="AS7" s="17"/>
+      <c r="AT7" s="17"/>
+      <c r="AU7" s="19"/>
+      <c r="AV7" s="41" t="s">
         <v>177</v>
       </c>
-      <c r="AS7" s="25"/>
-      <c r="AT7" s="20" t="s">
+      <c r="AW7" s="25"/>
+      <c r="AX7" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="AU7" s="19" t="s">
+      <c r="AY7" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="AV7" s="17"/>
-      <c r="AW7" s="34">
+      <c r="AZ7" s="17"/>
+      <c r="BA7" s="34">
         <v>9.3000000000000007</v>
       </c>
-      <c r="AX7" s="7" t="s">
+      <c r="BB7" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="AY7" s="17"/>
-      <c r="AZ7" s="11" t="s">
+      <c r="BC7" s="17"/>
+      <c r="BD7" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="BA7" s="34"/>
-      <c r="BB7" s="34"/>
-      <c r="BC7" s="17"/>
-      <c r="BD7" s="22"/>
-      <c r="BE7" s="17"/>
-      <c r="BF7" s="17"/>
+      <c r="BE7" s="34"/>
+      <c r="BF7" s="34"/>
       <c r="BG7" s="17"/>
-      <c r="BH7" s="17"/>
+      <c r="BH7" s="22"/>
       <c r="BI7" s="17"/>
       <c r="BJ7" s="17"/>
       <c r="BK7" s="17"/>
@@ -2058,14 +2107,18 @@
       <c r="BN7" s="17"/>
       <c r="BO7" s="17"/>
       <c r="BP7" s="17"/>
-      <c r="BQ7" s="16">
+      <c r="BQ7" s="17"/>
+      <c r="BR7" s="17"/>
+      <c r="BS7" s="17"/>
+      <c r="BT7" s="17"/>
+      <c r="BU7" s="16">
         <v>3</v>
       </c>
-      <c r="BS7" s="7" t="s">
+      <c r="BW7" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -2108,7 +2161,9 @@
       <c r="P8" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="Q8" s="17"/>
+      <c r="Q8" s="17" t="s">
+        <v>119</v>
+      </c>
       <c r="R8" s="17"/>
       <c r="S8" s="17"/>
       <c r="T8" s="17"/>
@@ -2134,30 +2189,30 @@
       <c r="AN8" s="17"/>
       <c r="AO8" s="17"/>
       <c r="AP8" s="17"/>
-      <c r="AQ8" s="19"/>
-      <c r="AR8" s="19"/>
-      <c r="AS8" s="25"/>
-      <c r="AT8" s="36" t="s">
+      <c r="AQ8" s="17"/>
+      <c r="AR8" s="17"/>
+      <c r="AS8" s="17"/>
+      <c r="AT8" s="17"/>
+      <c r="AU8" s="19"/>
+      <c r="AV8" s="19"/>
+      <c r="AW8" s="25"/>
+      <c r="AX8" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="AU8" s="34" t="s">
+      <c r="AY8" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="AV8" s="17"/>
-      <c r="AW8" s="34">
+      <c r="AZ8" s="17"/>
+      <c r="BA8" s="34">
         <v>9.4</v>
       </c>
-      <c r="AX8" s="7" t="s">
+      <c r="BB8" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="AY8" s="17"/>
-      <c r="AZ8" s="37" t="s">
+      <c r="BC8" s="17"/>
+      <c r="BD8" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="BA8" s="17"/>
-      <c r="BB8" s="17"/>
-      <c r="BC8" s="17"/>
-      <c r="BD8" s="17"/>
       <c r="BE8" s="17"/>
       <c r="BF8" s="17"/>
       <c r="BG8" s="17"/>
@@ -2170,14 +2225,18 @@
       <c r="BN8" s="17"/>
       <c r="BO8" s="17"/>
       <c r="BP8" s="17"/>
-      <c r="BQ8">
+      <c r="BQ8" s="17"/>
+      <c r="BR8" s="17"/>
+      <c r="BS8" s="17"/>
+      <c r="BT8" s="17"/>
+      <c r="BU8">
         <v>4</v>
       </c>
-      <c r="BS8" t="s">
+      <c r="BW8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -2220,7 +2279,9 @@
       <c r="P9" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="Q9" s="17"/>
+      <c r="Q9" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="R9" s="17"/>
       <c r="S9" s="17"/>
       <c r="T9" s="17"/>
@@ -2244,29 +2305,29 @@
       <c r="AL9" s="17"/>
       <c r="AM9" s="17"/>
       <c r="AN9" s="17"/>
-      <c r="AO9" s="18"/>
+      <c r="AO9" s="17"/>
       <c r="AP9" s="17"/>
-      <c r="AQ9" s="19"/>
-      <c r="AR9" s="41"/>
-      <c r="AS9" s="21"/>
-      <c r="AT9" s="27" t="s">
+      <c r="AQ9" s="17"/>
+      <c r="AR9" s="17"/>
+      <c r="AS9" s="18"/>
+      <c r="AT9" s="17"/>
+      <c r="AU9" s="19"/>
+      <c r="AV9" s="41"/>
+      <c r="AW9" s="21"/>
+      <c r="AX9" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="AU9" s="19" t="s">
+      <c r="AY9" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="AV9" s="21"/>
-      <c r="AW9" s="34">
+      <c r="AZ9" s="21"/>
+      <c r="BA9" s="34">
         <v>9.1</v>
       </c>
-      <c r="AX9" s="7" t="s">
+      <c r="BB9" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="AY9" s="18"/>
-      <c r="AZ9" s="17"/>
-      <c r="BA9" s="17"/>
-      <c r="BB9" s="18"/>
-      <c r="BC9" s="17"/>
+      <c r="BC9" s="18"/>
       <c r="BD9" s="17"/>
       <c r="BE9" s="17"/>
       <c r="BF9" s="18"/>
@@ -2274,20 +2335,24 @@
       <c r="BH9" s="17"/>
       <c r="BI9" s="17"/>
       <c r="BJ9" s="18"/>
-      <c r="BK9" s="18"/>
+      <c r="BK9" s="17"/>
       <c r="BL9" s="17"/>
       <c r="BM9" s="17"/>
-      <c r="BN9" s="17"/>
-      <c r="BO9" s="17"/>
+      <c r="BN9" s="18"/>
+      <c r="BO9" s="18"/>
       <c r="BP9" s="17"/>
-      <c r="BQ9">
+      <c r="BQ9" s="17"/>
+      <c r="BR9" s="17"/>
+      <c r="BS9" s="17"/>
+      <c r="BT9" s="17"/>
+      <c r="BU9">
         <v>5</v>
       </c>
-      <c r="BS9" t="s">
+      <c r="BW9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -2330,7 +2395,9 @@
       <c r="P10" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="Q10" s="17"/>
+      <c r="Q10" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="R10" s="17"/>
       <c r="S10" s="17"/>
       <c r="T10" s="17"/>
@@ -2354,50 +2421,54 @@
       <c r="AL10" s="17"/>
       <c r="AM10" s="17"/>
       <c r="AN10" s="17"/>
-      <c r="AO10" s="18"/>
+      <c r="AO10" s="17"/>
       <c r="AP10" s="17"/>
-      <c r="AQ10" s="19"/>
-      <c r="AR10" s="42"/>
-      <c r="AS10" s="21"/>
-      <c r="AT10" s="33" t="s">
+      <c r="AQ10" s="17"/>
+      <c r="AR10" s="17"/>
+      <c r="AS10" s="18"/>
+      <c r="AT10" s="17"/>
+      <c r="AU10" s="19"/>
+      <c r="AV10" s="42"/>
+      <c r="AW10" s="21"/>
+      <c r="AX10" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="AU10" s="34" t="s">
+      <c r="AY10" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="AV10" s="18"/>
-      <c r="AW10" s="34" t="s">
+      <c r="AZ10" s="18"/>
+      <c r="BA10" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="AX10" s="34" t="s">
+      <c r="BB10" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="AY10" s="34"/>
-      <c r="AZ10" s="17"/>
-      <c r="BA10" s="17"/>
-      <c r="BB10" s="17"/>
-      <c r="BC10" s="17"/>
+      <c r="BC10" s="34"/>
       <c r="BD10" s="17"/>
       <c r="BE10" s="17"/>
-      <c r="BF10" s="18"/>
+      <c r="BF10" s="17"/>
       <c r="BG10" s="17"/>
       <c r="BH10" s="17"/>
       <c r="BI10" s="17"/>
       <c r="BJ10" s="18"/>
-      <c r="BK10" s="18"/>
+      <c r="BK10" s="17"/>
       <c r="BL10" s="17"/>
       <c r="BM10" s="17"/>
-      <c r="BN10" s="17"/>
-      <c r="BO10" s="17"/>
+      <c r="BN10" s="18"/>
+      <c r="BO10" s="18"/>
       <c r="BP10" s="17"/>
-      <c r="BQ10">
+      <c r="BQ10" s="17"/>
+      <c r="BR10" s="17"/>
+      <c r="BS10" s="17"/>
+      <c r="BT10" s="17"/>
+      <c r="BU10">
         <v>6</v>
       </c>
-      <c r="BS10" t="s">
+      <c r="BW10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -2440,7 +2511,9 @@
       <c r="P11" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="Q11" s="17"/>
+      <c r="Q11" s="38" t="s">
+        <v>118</v>
+      </c>
       <c r="R11" s="17"/>
       <c r="S11" s="17"/>
       <c r="T11" s="17"/>
@@ -2464,31 +2537,31 @@
       <c r="AL11" s="17"/>
       <c r="AM11" s="17"/>
       <c r="AN11" s="17"/>
-      <c r="AO11" s="18"/>
+      <c r="AO11" s="17"/>
       <c r="AP11" s="17"/>
-      <c r="AQ11" s="19"/>
-      <c r="AR11" s="41" t="s">
+      <c r="AQ11" s="17"/>
+      <c r="AR11" s="17"/>
+      <c r="AS11" s="18"/>
+      <c r="AT11" s="17"/>
+      <c r="AU11" s="19"/>
+      <c r="AV11" s="41" t="s">
         <v>177</v>
       </c>
-      <c r="AS11" s="21"/>
-      <c r="AT11" s="33" t="s">
+      <c r="AW11" s="21"/>
+      <c r="AX11" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="AU11" s="34" t="s">
+      <c r="AY11" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="AV11" s="18"/>
-      <c r="AW11" s="34" t="s">
+      <c r="AZ11" s="18"/>
+      <c r="BA11" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="AX11" s="34" t="s">
+      <c r="BB11" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="AY11" s="34"/>
-      <c r="AZ11" s="17"/>
-      <c r="BA11" s="17"/>
-      <c r="BB11" s="18"/>
-      <c r="BC11" s="17"/>
+      <c r="BC11" s="34"/>
       <c r="BD11" s="17"/>
       <c r="BE11" s="17"/>
       <c r="BF11" s="18"/>
@@ -2496,20 +2569,24 @@
       <c r="BH11" s="17"/>
       <c r="BI11" s="17"/>
       <c r="BJ11" s="18"/>
-      <c r="BK11" s="18"/>
+      <c r="BK11" s="17"/>
       <c r="BL11" s="17"/>
       <c r="BM11" s="17"/>
-      <c r="BN11" s="17"/>
-      <c r="BO11" s="17"/>
+      <c r="BN11" s="18"/>
+      <c r="BO11" s="18"/>
       <c r="BP11" s="17"/>
-      <c r="BQ11">
+      <c r="BQ11" s="17"/>
+      <c r="BR11" s="17"/>
+      <c r="BS11" s="17"/>
+      <c r="BT11" s="17"/>
+      <c r="BU11">
         <v>7</v>
       </c>
-      <c r="BS11" t="s">
+      <c r="BW11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -2554,7 +2631,9 @@
       <c r="P12" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="Q12" s="17"/>
+      <c r="Q12" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="R12" s="17"/>
       <c r="S12" s="17"/>
       <c r="T12" s="17"/>
@@ -2578,27 +2657,27 @@
       <c r="AL12" s="17"/>
       <c r="AM12" s="17"/>
       <c r="AN12" s="17"/>
-      <c r="AO12" s="18"/>
+      <c r="AO12" s="17"/>
       <c r="AP12" s="17"/>
-      <c r="AQ12" s="19"/>
-      <c r="AR12" s="41"/>
-      <c r="AS12" s="21"/>
-      <c r="AT12" s="20" t="s">
+      <c r="AQ12" s="17"/>
+      <c r="AR12" s="17"/>
+      <c r="AS12" s="18"/>
+      <c r="AT12" s="17"/>
+      <c r="AU12" s="19"/>
+      <c r="AV12" s="41"/>
+      <c r="AW12" s="21"/>
+      <c r="AX12" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="AU12" s="19" t="s">
+      <c r="AY12" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="AV12" s="21"/>
-      <c r="AW12" s="34" t="s">
+      <c r="AZ12" s="21"/>
+      <c r="BA12" s="34" t="s">
         <v>174</v>
       </c>
-      <c r="AX12" s="34"/>
-      <c r="AY12" s="34"/>
-      <c r="AZ12" s="17"/>
-      <c r="BA12" s="17"/>
-      <c r="BB12" s="18"/>
-      <c r="BC12" s="17"/>
+      <c r="BB12" s="34"/>
+      <c r="BC12" s="34"/>
       <c r="BD12" s="17"/>
       <c r="BE12" s="17"/>
       <c r="BF12" s="18"/>
@@ -2606,20 +2685,24 @@
       <c r="BH12" s="17"/>
       <c r="BI12" s="17"/>
       <c r="BJ12" s="18"/>
-      <c r="BK12" s="18"/>
+      <c r="BK12" s="17"/>
       <c r="BL12" s="17"/>
       <c r="BM12" s="17"/>
-      <c r="BN12" s="17"/>
-      <c r="BO12" s="17"/>
+      <c r="BN12" s="18"/>
+      <c r="BO12" s="18"/>
       <c r="BP12" s="17"/>
-      <c r="BQ12">
+      <c r="BQ12" s="17"/>
+      <c r="BR12" s="17"/>
+      <c r="BS12" s="17"/>
+      <c r="BT12" s="17"/>
+      <c r="BU12">
         <v>8</v>
       </c>
-      <c r="BS12" t="s">
+      <c r="BW12" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -2662,7 +2745,9 @@
       <c r="P13" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="Q13" s="17"/>
+      <c r="Q13" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="R13" s="17"/>
       <c r="S13" s="17"/>
       <c r="T13" s="17"/>
@@ -2686,25 +2771,25 @@
       <c r="AL13" s="17"/>
       <c r="AM13" s="17"/>
       <c r="AN13" s="17"/>
-      <c r="AO13" s="18"/>
+      <c r="AO13" s="17"/>
       <c r="AP13" s="17"/>
-      <c r="AQ13" s="19"/>
-      <c r="AR13" s="19"/>
-      <c r="AS13" s="21"/>
-      <c r="AT13" s="33" t="s">
+      <c r="AQ13" s="17"/>
+      <c r="AR13" s="17"/>
+      <c r="AS13" s="18"/>
+      <c r="AT13" s="17"/>
+      <c r="AU13" s="19"/>
+      <c r="AV13" s="19"/>
+      <c r="AW13" s="21"/>
+      <c r="AX13" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="AU13" s="34" t="s">
+      <c r="AY13" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="AV13" s="18"/>
-      <c r="AW13" s="17"/>
-      <c r="AX13" s="22"/>
-      <c r="AY13" s="18"/>
-      <c r="AZ13" s="17"/>
+      <c r="AZ13" s="18"/>
       <c r="BA13" s="17"/>
-      <c r="BB13" s="18"/>
-      <c r="BC13" s="17"/>
+      <c r="BB13" s="22"/>
+      <c r="BC13" s="18"/>
       <c r="BD13" s="17"/>
       <c r="BE13" s="17"/>
       <c r="BF13" s="18"/>
@@ -2712,20 +2797,24 @@
       <c r="BH13" s="17"/>
       <c r="BI13" s="17"/>
       <c r="BJ13" s="18"/>
-      <c r="BK13" s="18"/>
+      <c r="BK13" s="17"/>
       <c r="BL13" s="17"/>
       <c r="BM13" s="17"/>
-      <c r="BN13" s="17"/>
-      <c r="BO13" s="17"/>
+      <c r="BN13" s="18"/>
+      <c r="BO13" s="18"/>
       <c r="BP13" s="17"/>
-      <c r="BQ13">
+      <c r="BQ13" s="17"/>
+      <c r="BR13" s="17"/>
+      <c r="BS13" s="17"/>
+      <c r="BT13" s="17"/>
+      <c r="BU13">
         <v>9</v>
       </c>
-      <c r="BS13" t="s">
+      <c r="BW13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -2768,7 +2857,9 @@
       <c r="P14" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="Q14" s="23"/>
+      <c r="Q14" s="64" t="s">
+        <v>118</v>
+      </c>
       <c r="R14" s="17"/>
       <c r="S14" s="17"/>
       <c r="T14" s="17"/>
@@ -2794,19 +2885,19 @@
       <c r="AN14" s="17"/>
       <c r="AO14" s="17"/>
       <c r="AP14" s="17"/>
-      <c r="AQ14" s="19"/>
-      <c r="AR14" s="41"/>
-      <c r="AS14" s="25"/>
-      <c r="AT14" s="36" t="s">
+      <c r="AQ14" s="17"/>
+      <c r="AR14" s="17"/>
+      <c r="AS14" s="17"/>
+      <c r="AT14" s="17"/>
+      <c r="AU14" s="19"/>
+      <c r="AV14" s="41"/>
+      <c r="AW14" s="25"/>
+      <c r="AX14" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="AU14" s="34" t="s">
+      <c r="AY14" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="AV14" s="17"/>
-      <c r="AW14" s="17"/>
-      <c r="AX14" s="17"/>
-      <c r="AY14" s="17"/>
       <c r="AZ14" s="17"/>
       <c r="BA14" s="17"/>
       <c r="BB14" s="17"/>
@@ -2824,14 +2915,18 @@
       <c r="BN14" s="17"/>
       <c r="BO14" s="17"/>
       <c r="BP14" s="17"/>
-      <c r="BQ14">
+      <c r="BQ14" s="17"/>
+      <c r="BR14" s="17"/>
+      <c r="BS14" s="17"/>
+      <c r="BT14" s="17"/>
+      <c r="BU14">
         <v>10</v>
       </c>
-      <c r="BS14" t="s">
+      <c r="BW14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -2874,7 +2969,9 @@
       <c r="P15" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="Q15" s="17"/>
+      <c r="Q15" s="38" t="s">
+        <v>118</v>
+      </c>
       <c r="R15" s="17"/>
       <c r="S15" s="17"/>
       <c r="T15" s="17"/>
@@ -2898,48 +2995,52 @@
       <c r="AL15" s="17"/>
       <c r="AM15" s="17"/>
       <c r="AN15" s="17"/>
-      <c r="AO15" s="18"/>
+      <c r="AO15" s="17"/>
       <c r="AP15" s="17"/>
-      <c r="AQ15" s="19"/>
-      <c r="AR15" s="41" t="s">
+      <c r="AQ15" s="17"/>
+      <c r="AR15" s="17"/>
+      <c r="AS15" s="18"/>
+      <c r="AT15" s="17"/>
+      <c r="AU15" s="19"/>
+      <c r="AV15" s="41" t="s">
         <v>177</v>
       </c>
-      <c r="AS15" s="18"/>
-      <c r="AT15" s="33" t="s">
+      <c r="AW15" s="18"/>
+      <c r="AX15" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="AU15" s="34" t="s">
+      <c r="AY15" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="AV15" s="21"/>
-      <c r="AW15" s="17"/>
-      <c r="AX15" s="22"/>
-      <c r="AY15" s="18"/>
-      <c r="AZ15" s="17"/>
-      <c r="BA15" s="22"/>
-      <c r="BB15" s="21"/>
-      <c r="BC15" s="17"/>
+      <c r="AZ15" s="21"/>
+      <c r="BA15" s="17"/>
+      <c r="BB15" s="22"/>
+      <c r="BC15" s="18"/>
       <c r="BD15" s="17"/>
-      <c r="BE15" s="17"/>
-      <c r="BF15" s="18"/>
+      <c r="BE15" s="22"/>
+      <c r="BF15" s="21"/>
       <c r="BG15" s="17"/>
       <c r="BH15" s="17"/>
       <c r="BI15" s="17"/>
-      <c r="BJ15" s="17"/>
-      <c r="BK15" s="18"/>
+      <c r="BJ15" s="18"/>
+      <c r="BK15" s="17"/>
       <c r="BL15" s="17"/>
       <c r="BM15" s="17"/>
       <c r="BN15" s="17"/>
-      <c r="BO15" s="17"/>
+      <c r="BO15" s="18"/>
       <c r="BP15" s="17"/>
-      <c r="BQ15">
+      <c r="BQ15" s="17"/>
+      <c r="BR15" s="17"/>
+      <c r="BS15" s="17"/>
+      <c r="BT15" s="17"/>
+      <c r="BU15">
         <v>11</v>
       </c>
-      <c r="BS15" t="s">
+      <c r="BW15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -2982,7 +3083,9 @@
       <c r="P16" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="Q16" s="17"/>
+      <c r="Q16" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="R16" s="17"/>
       <c r="S16" s="17"/>
       <c r="T16" s="17"/>
@@ -3006,50 +3109,54 @@
       <c r="AL16" s="17"/>
       <c r="AM16" s="17"/>
       <c r="AN16" s="17"/>
-      <c r="AO16" s="18"/>
+      <c r="AO16" s="17"/>
       <c r="AP16" s="17"/>
-      <c r="AQ16" s="18"/>
-      <c r="AR16" s="19"/>
-      <c r="AS16" s="25"/>
-      <c r="AT16" s="33" t="s">
+      <c r="AQ16" s="17"/>
+      <c r="AR16" s="17"/>
+      <c r="AS16" s="18"/>
+      <c r="AT16" s="17"/>
+      <c r="AU16" s="18"/>
+      <c r="AV16" s="19"/>
+      <c r="AW16" s="25"/>
+      <c r="AX16" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="AU16" s="34" t="s">
+      <c r="AY16" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="AV16" s="18"/>
-      <c r="AW16" s="21" t="s">
+      <c r="AZ16" s="18"/>
+      <c r="BA16" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="AX16" s="21" t="s">
+      <c r="BB16" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="AY16" s="18"/>
-      <c r="AZ16" s="17"/>
-      <c r="BA16" s="22"/>
-      <c r="BB16" s="18"/>
-      <c r="BC16" s="17"/>
-      <c r="BD16" s="26"/>
-      <c r="BE16" s="17"/>
+      <c r="BC16" s="18"/>
+      <c r="BD16" s="17"/>
+      <c r="BE16" s="22"/>
       <c r="BF16" s="18"/>
       <c r="BG16" s="17"/>
-      <c r="BH16" s="17"/>
+      <c r="BH16" s="26"/>
       <c r="BI16" s="17"/>
       <c r="BJ16" s="18"/>
-      <c r="BK16" s="18"/>
+      <c r="BK16" s="17"/>
       <c r="BL16" s="17"/>
       <c r="BM16" s="17"/>
-      <c r="BN16" s="17"/>
-      <c r="BO16" s="17"/>
+      <c r="BN16" s="18"/>
+      <c r="BO16" s="18"/>
       <c r="BP16" s="17"/>
-      <c r="BQ16">
+      <c r="BQ16" s="17"/>
+      <c r="BR16" s="17"/>
+      <c r="BS16" s="17"/>
+      <c r="BT16" s="17"/>
+      <c r="BU16">
         <v>12</v>
       </c>
-      <c r="BS16" t="s">
+      <c r="BW16" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -3092,7 +3199,9 @@
       <c r="P17" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="Q17" s="17"/>
+      <c r="Q17" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="R17" s="17"/>
       <c r="S17" s="17"/>
       <c r="T17" s="17"/>
@@ -3116,27 +3225,27 @@
       <c r="AL17" s="17"/>
       <c r="AM17" s="17"/>
       <c r="AN17" s="17"/>
-      <c r="AO17" s="18"/>
+      <c r="AO17" s="17"/>
       <c r="AP17" s="17"/>
-      <c r="AQ17" s="19"/>
-      <c r="AR17" s="42" t="s">
+      <c r="AQ17" s="17"/>
+      <c r="AR17" s="17"/>
+      <c r="AS17" s="18"/>
+      <c r="AT17" s="17"/>
+      <c r="AU17" s="19"/>
+      <c r="AV17" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="AS17" s="21"/>
-      <c r="AT17" s="33" t="s">
+      <c r="AW17" s="21"/>
+      <c r="AX17" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="AU17" s="34" t="s">
+      <c r="AY17" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="AV17" s="18"/>
-      <c r="AW17" s="17"/>
-      <c r="AX17" s="17"/>
-      <c r="AY17" s="18"/>
-      <c r="AZ17" s="17"/>
+      <c r="AZ17" s="18"/>
       <c r="BA17" s="17"/>
-      <c r="BB17" s="18"/>
-      <c r="BC17" s="17"/>
+      <c r="BB17" s="17"/>
+      <c r="BC17" s="18"/>
       <c r="BD17" s="17"/>
       <c r="BE17" s="17"/>
       <c r="BF17" s="18"/>
@@ -3144,20 +3253,24 @@
       <c r="BH17" s="17"/>
       <c r="BI17" s="17"/>
       <c r="BJ17" s="18"/>
-      <c r="BK17" s="18"/>
+      <c r="BK17" s="17"/>
       <c r="BL17" s="17"/>
       <c r="BM17" s="17"/>
-      <c r="BN17" s="17"/>
-      <c r="BO17" s="17"/>
+      <c r="BN17" s="18"/>
+      <c r="BO17" s="18"/>
       <c r="BP17" s="17"/>
-      <c r="BQ17">
+      <c r="BQ17" s="17"/>
+      <c r="BR17" s="17"/>
+      <c r="BS17" s="17"/>
+      <c r="BT17" s="17"/>
+      <c r="BU17">
         <v>13</v>
       </c>
-      <c r="BS17" t="s">
+      <c r="BW17" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -3202,7 +3315,9 @@
       <c r="P18" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="Q18" s="17"/>
+      <c r="Q18" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="R18" s="17"/>
       <c r="S18" s="17"/>
       <c r="T18" s="17"/>
@@ -3226,25 +3341,25 @@
       <c r="AL18" s="17"/>
       <c r="AM18" s="17"/>
       <c r="AN18" s="17"/>
-      <c r="AO18" s="18"/>
+      <c r="AO18" s="17"/>
       <c r="AP18" s="17"/>
-      <c r="AQ18" s="19"/>
-      <c r="AR18" s="42"/>
-      <c r="AS18" s="21"/>
-      <c r="AT18" s="35" t="s">
+      <c r="AQ18" s="17"/>
+      <c r="AR18" s="17"/>
+      <c r="AS18" s="18"/>
+      <c r="AT18" s="17"/>
+      <c r="AU18" s="19"/>
+      <c r="AV18" s="42"/>
+      <c r="AW18" s="21"/>
+      <c r="AX18" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="AU18" s="34" t="s">
+      <c r="AY18" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="AV18" s="21"/>
-      <c r="AW18" s="17"/>
-      <c r="AX18" s="22"/>
-      <c r="AY18" s="18"/>
-      <c r="AZ18" s="17"/>
+      <c r="AZ18" s="21"/>
       <c r="BA18" s="17"/>
-      <c r="BB18" s="18"/>
-      <c r="BC18" s="17"/>
+      <c r="BB18" s="22"/>
+      <c r="BC18" s="18"/>
       <c r="BD18" s="17"/>
       <c r="BE18" s="17"/>
       <c r="BF18" s="18"/>
@@ -3252,20 +3367,24 @@
       <c r="BH18" s="17"/>
       <c r="BI18" s="17"/>
       <c r="BJ18" s="18"/>
-      <c r="BK18" s="18"/>
+      <c r="BK18" s="17"/>
       <c r="BL18" s="17"/>
       <c r="BM18" s="17"/>
-      <c r="BN18" s="17"/>
-      <c r="BO18" s="17"/>
+      <c r="BN18" s="18"/>
+      <c r="BO18" s="18"/>
       <c r="BP18" s="17"/>
-      <c r="BQ18">
+      <c r="BQ18" s="17"/>
+      <c r="BR18" s="17"/>
+      <c r="BS18" s="17"/>
+      <c r="BT18" s="17"/>
+      <c r="BU18">
         <v>14</v>
       </c>
-      <c r="BS18" t="s">
+      <c r="BW18" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -3308,7 +3427,9 @@
       <c r="P19" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="Q19" s="17"/>
+      <c r="Q19" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="R19" s="17"/>
       <c r="S19" s="17"/>
       <c r="T19" s="17"/>
@@ -3332,48 +3453,52 @@
       <c r="AL19" s="17"/>
       <c r="AM19" s="17"/>
       <c r="AN19" s="17"/>
-      <c r="AO19" s="18"/>
+      <c r="AO19" s="17"/>
       <c r="AP19" s="17"/>
-      <c r="AQ19" s="19"/>
-      <c r="AR19" s="42" t="s">
+      <c r="AQ19" s="17"/>
+      <c r="AR19" s="17"/>
+      <c r="AS19" s="18"/>
+      <c r="AT19" s="17"/>
+      <c r="AU19" s="19"/>
+      <c r="AV19" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="AS19" s="21"/>
-      <c r="AT19" s="33" t="s">
+      <c r="AW19" s="21"/>
+      <c r="AX19" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="AU19" s="34" t="s">
+      <c r="AY19" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="AV19" s="18"/>
-      <c r="AW19" s="17"/>
-      <c r="AX19" s="22"/>
-      <c r="AY19" s="21"/>
-      <c r="AZ19" s="17"/>
+      <c r="AZ19" s="18"/>
       <c r="BA19" s="17"/>
-      <c r="BB19" s="21"/>
-      <c r="BC19" s="17"/>
+      <c r="BB19" s="22"/>
+      <c r="BC19" s="21"/>
       <c r="BD19" s="17"/>
       <c r="BE19" s="17"/>
-      <c r="BF19" s="18"/>
+      <c r="BF19" s="21"/>
       <c r="BG19" s="17"/>
       <c r="BH19" s="17"/>
       <c r="BI19" s="17"/>
       <c r="BJ19" s="18"/>
-      <c r="BK19" s="18"/>
+      <c r="BK19" s="17"/>
       <c r="BL19" s="17"/>
       <c r="BM19" s="17"/>
-      <c r="BN19" s="17"/>
-      <c r="BO19" s="17"/>
+      <c r="BN19" s="18"/>
+      <c r="BO19" s="18"/>
       <c r="BP19" s="17"/>
-      <c r="BQ19">
+      <c r="BQ19" s="17"/>
+      <c r="BR19" s="17"/>
+      <c r="BS19" s="17"/>
+      <c r="BT19" s="17"/>
+      <c r="BU19">
         <v>15</v>
       </c>
-      <c r="BS19" t="s">
+      <c r="BW19" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -3416,7 +3541,9 @@
       <c r="P20" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="Q20" s="17"/>
+      <c r="Q20" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="R20" s="17"/>
       <c r="S20" s="17"/>
       <c r="T20" s="17"/>
@@ -3440,24 +3567,24 @@
       <c r="AL20" s="17"/>
       <c r="AM20" s="17"/>
       <c r="AN20" s="17"/>
-      <c r="AO20" s="18"/>
+      <c r="AO20" s="17"/>
       <c r="AP20" s="17"/>
-      <c r="AQ20" s="19"/>
-      <c r="AR20" s="41"/>
-      <c r="AS20" s="21"/>
-      <c r="AT20" s="27" t="s">
+      <c r="AQ20" s="17"/>
+      <c r="AR20" s="17"/>
+      <c r="AS20" s="18"/>
+      <c r="AT20" s="17"/>
+      <c r="AU20" s="19"/>
+      <c r="AV20" s="41"/>
+      <c r="AW20" s="21"/>
+      <c r="AX20" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="AU20" s="19" t="s">
+      <c r="AY20" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="AV20" s="18"/>
-      <c r="AW20" s="17"/>
-      <c r="AX20" s="28"/>
-      <c r="AY20" s="17"/>
-      <c r="AZ20" s="17"/>
+      <c r="AZ20" s="18"/>
       <c r="BA20" s="17"/>
-      <c r="BB20" s="18"/>
+      <c r="BB20" s="28"/>
       <c r="BC20" s="17"/>
       <c r="BD20" s="17"/>
       <c r="BE20" s="17"/>
@@ -3466,20 +3593,24 @@
       <c r="BH20" s="17"/>
       <c r="BI20" s="17"/>
       <c r="BJ20" s="18"/>
-      <c r="BK20" s="18"/>
+      <c r="BK20" s="17"/>
       <c r="BL20" s="17"/>
       <c r="BM20" s="17"/>
-      <c r="BN20" s="17"/>
-      <c r="BO20" s="17"/>
+      <c r="BN20" s="18"/>
+      <c r="BO20" s="18"/>
       <c r="BP20" s="17"/>
-      <c r="BQ20">
+      <c r="BQ20" s="17"/>
+      <c r="BR20" s="17"/>
+      <c r="BS20" s="17"/>
+      <c r="BT20" s="17"/>
+      <c r="BU20">
         <v>16</v>
       </c>
-      <c r="BS20" t="s">
+      <c r="BW20" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -3522,7 +3653,9 @@
       <c r="P21" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="Q21" s="17"/>
+      <c r="Q21" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="R21" s="17"/>
       <c r="S21" s="17"/>
       <c r="T21" s="17"/>
@@ -3546,25 +3679,25 @@
       <c r="AL21" s="17"/>
       <c r="AM21" s="17"/>
       <c r="AN21" s="17"/>
-      <c r="AO21" s="18"/>
+      <c r="AO21" s="17"/>
       <c r="AP21" s="17"/>
-      <c r="AQ21" s="19"/>
-      <c r="AR21" s="19"/>
-      <c r="AS21" s="21"/>
-      <c r="AT21" s="36" t="s">
+      <c r="AQ21" s="17"/>
+      <c r="AR21" s="17"/>
+      <c r="AS21" s="18"/>
+      <c r="AT21" s="17"/>
+      <c r="AU21" s="19"/>
+      <c r="AV21" s="19"/>
+      <c r="AW21" s="21"/>
+      <c r="AX21" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="AU21" s="34" t="s">
+      <c r="AY21" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="AV21" s="21"/>
-      <c r="AW21" s="17"/>
-      <c r="AX21" s="17"/>
-      <c r="AY21" s="18"/>
-      <c r="AZ21" s="17"/>
+      <c r="AZ21" s="21"/>
       <c r="BA21" s="17"/>
-      <c r="BB21" s="18"/>
-      <c r="BC21" s="17"/>
+      <c r="BB21" s="17"/>
+      <c r="BC21" s="18"/>
       <c r="BD21" s="17"/>
       <c r="BE21" s="17"/>
       <c r="BF21" s="18"/>
@@ -3572,20 +3705,24 @@
       <c r="BH21" s="17"/>
       <c r="BI21" s="17"/>
       <c r="BJ21" s="18"/>
-      <c r="BK21" s="18"/>
+      <c r="BK21" s="17"/>
       <c r="BL21" s="17"/>
       <c r="BM21" s="17"/>
-      <c r="BN21" s="17"/>
-      <c r="BO21" s="17"/>
+      <c r="BN21" s="18"/>
+      <c r="BO21" s="18"/>
       <c r="BP21" s="17"/>
-      <c r="BQ21" s="16">
+      <c r="BQ21" s="17"/>
+      <c r="BR21" s="17"/>
+      <c r="BS21" s="17"/>
+      <c r="BT21" s="17"/>
+      <c r="BU21" s="16">
         <v>17</v>
       </c>
-      <c r="BS21" t="s">
+      <c r="BW21" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -3628,7 +3765,9 @@
       <c r="P22" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="Q22" s="17"/>
+      <c r="Q22" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="R22" s="17"/>
       <c r="S22" s="17"/>
       <c r="T22" s="17"/>
@@ -3652,46 +3791,50 @@
       <c r="AL22" s="17"/>
       <c r="AM22" s="17"/>
       <c r="AN22" s="17"/>
-      <c r="AO22" s="18"/>
+      <c r="AO22" s="17"/>
       <c r="AP22" s="17"/>
-      <c r="AQ22" s="19"/>
-      <c r="AR22" s="19"/>
-      <c r="AS22" s="21"/>
-      <c r="AT22" s="27" t="s">
+      <c r="AQ22" s="17"/>
+      <c r="AR22" s="17"/>
+      <c r="AS22" s="18"/>
+      <c r="AT22" s="17"/>
+      <c r="AU22" s="19"/>
+      <c r="AV22" s="19"/>
+      <c r="AW22" s="21"/>
+      <c r="AX22" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="AU22" s="7" t="s">
+      <c r="AY22" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="AV22" s="21"/>
-      <c r="AW22" s="17"/>
-      <c r="AX22" s="22"/>
-      <c r="AY22" s="18"/>
-      <c r="AZ22" s="17"/>
-      <c r="BA22" s="22"/>
-      <c r="BB22" s="18"/>
-      <c r="BC22" s="17"/>
+      <c r="AZ22" s="21"/>
+      <c r="BA22" s="17"/>
+      <c r="BB22" s="22"/>
+      <c r="BC22" s="18"/>
       <c r="BD22" s="17"/>
-      <c r="BE22" s="17"/>
+      <c r="BE22" s="22"/>
       <c r="BF22" s="18"/>
       <c r="BG22" s="17"/>
       <c r="BH22" s="17"/>
       <c r="BI22" s="17"/>
       <c r="BJ22" s="18"/>
-      <c r="BK22" s="18"/>
+      <c r="BK22" s="17"/>
       <c r="BL22" s="17"/>
       <c r="BM22" s="17"/>
-      <c r="BN22" s="17"/>
-      <c r="BO22" s="17"/>
+      <c r="BN22" s="18"/>
+      <c r="BO22" s="18"/>
       <c r="BP22" s="17"/>
-      <c r="BQ22">
+      <c r="BQ22" s="17"/>
+      <c r="BR22" s="17"/>
+      <c r="BS22" s="17"/>
+      <c r="BT22" s="17"/>
+      <c r="BU22">
         <v>18</v>
       </c>
-      <c r="BS22" t="s">
+      <c r="BW22" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:71" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:75" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -3734,7 +3877,9 @@
       <c r="P23" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="Q23" s="17"/>
+      <c r="Q23" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="R23" s="23"/>
       <c r="S23" s="17"/>
       <c r="T23" s="17"/>
@@ -3758,44 +3903,48 @@
       <c r="AL23" s="17"/>
       <c r="AM23" s="17"/>
       <c r="AN23" s="17"/>
-      <c r="AO23" s="18"/>
+      <c r="AO23" s="17"/>
       <c r="AP23" s="17"/>
-      <c r="AQ23" s="18"/>
-      <c r="AR23" s="19"/>
-      <c r="AS23" s="21"/>
-      <c r="AT23" s="26" t="s">
+      <c r="AQ23" s="17"/>
+      <c r="AR23" s="17"/>
+      <c r="AS23" s="18"/>
+      <c r="AT23" s="17"/>
+      <c r="AU23" s="18"/>
+      <c r="AV23" s="19"/>
+      <c r="AW23" s="21"/>
+      <c r="AX23" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="AU23" s="19"/>
-      <c r="AV23" s="18"/>
-      <c r="AW23" s="17"/>
-      <c r="AX23" s="22"/>
-      <c r="AY23" s="17"/>
-      <c r="AZ23" s="17"/>
-      <c r="BA23" s="22"/>
-      <c r="BB23" s="18"/>
+      <c r="AY23" s="19"/>
+      <c r="AZ23" s="18"/>
+      <c r="BA23" s="17"/>
+      <c r="BB23" s="22"/>
       <c r="BC23" s="17"/>
-      <c r="BD23" s="26"/>
-      <c r="BE23" s="17"/>
+      <c r="BD23" s="17"/>
+      <c r="BE23" s="22"/>
       <c r="BF23" s="18"/>
       <c r="BG23" s="17"/>
-      <c r="BH23" s="17"/>
+      <c r="BH23" s="26"/>
       <c r="BI23" s="17"/>
       <c r="BJ23" s="18"/>
-      <c r="BK23" s="18"/>
+      <c r="BK23" s="17"/>
       <c r="BL23" s="17"/>
       <c r="BM23" s="17"/>
-      <c r="BN23" s="17"/>
-      <c r="BO23" s="17"/>
+      <c r="BN23" s="18"/>
+      <c r="BO23" s="18"/>
       <c r="BP23" s="17"/>
-      <c r="BQ23">
+      <c r="BQ23" s="17"/>
+      <c r="BR23" s="17"/>
+      <c r="BS23" s="17"/>
+      <c r="BT23" s="17"/>
+      <c r="BU23">
         <v>19</v>
       </c>
-      <c r="BS23" t="s">
+      <c r="BW23" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:71" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:75" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -3838,7 +3987,9 @@
       <c r="P24" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="Q24" s="17"/>
+      <c r="Q24" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="R24" s="17"/>
       <c r="S24" s="17"/>
       <c r="T24" s="17"/>
@@ -3864,18 +4015,18 @@
       <c r="AN24" s="17"/>
       <c r="AO24" s="17"/>
       <c r="AP24" s="17"/>
-      <c r="AQ24" s="19"/>
-      <c r="AR24" s="41" t="s">
+      <c r="AQ24" s="17"/>
+      <c r="AR24" s="17"/>
+      <c r="AS24" s="17"/>
+      <c r="AT24" s="17"/>
+      <c r="AU24" s="19"/>
+      <c r="AV24" s="41" t="s">
         <v>177</v>
       </c>
-      <c r="AS24" s="25"/>
-      <c r="AT24" s="26" t="s">
+      <c r="AW24" s="25"/>
+      <c r="AX24" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="AU24" s="17"/>
-      <c r="AV24" s="17"/>
-      <c r="AW24" s="17"/>
-      <c r="AX24" s="17"/>
       <c r="AY24" s="17"/>
       <c r="AZ24" s="17"/>
       <c r="BA24" s="17"/>
@@ -3884,8 +4035,12 @@
       <c r="BD24" s="17"/>
       <c r="BE24" s="17"/>
       <c r="BF24" s="17"/>
-      <c r="BG24" s="17"/>
-      <c r="BH24" s="17"/>
+      <c r="BG24" s="18">
+        <v>46303</v>
+      </c>
+      <c r="BH24" s="17" t="s">
+        <v>179</v>
+      </c>
       <c r="BI24" s="17"/>
       <c r="BJ24" s="17"/>
       <c r="BK24" s="17"/>
@@ -3894,14 +4049,18 @@
       <c r="BN24" s="17"/>
       <c r="BO24" s="17"/>
       <c r="BP24" s="17"/>
-      <c r="BQ24">
+      <c r="BQ24" s="17"/>
+      <c r="BR24" s="17"/>
+      <c r="BS24" s="17"/>
+      <c r="BT24" s="17"/>
+      <c r="BU24">
         <v>20</v>
       </c>
-      <c r="BS24" t="s">
+      <c r="BW24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:71" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:75" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -3946,7 +4105,9 @@
       <c r="P25" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="Q25" s="17"/>
+      <c r="Q25" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="R25" s="17"/>
       <c r="S25" s="17"/>
       <c r="T25" s="17"/>
@@ -3970,44 +4131,48 @@
       <c r="AL25" s="17"/>
       <c r="AM25" s="17"/>
       <c r="AN25" s="17"/>
-      <c r="AO25" s="18"/>
+      <c r="AO25" s="17"/>
       <c r="AP25" s="17"/>
-      <c r="AQ25" s="19"/>
-      <c r="AR25" s="19"/>
-      <c r="AS25" s="21"/>
-      <c r="AT25" s="26" t="s">
+      <c r="AQ25" s="17"/>
+      <c r="AR25" s="17"/>
+      <c r="AS25" s="18"/>
+      <c r="AT25" s="17"/>
+      <c r="AU25" s="19"/>
+      <c r="AV25" s="19"/>
+      <c r="AW25" s="21"/>
+      <c r="AX25" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="AU25" s="19"/>
-      <c r="AV25" s="21"/>
-      <c r="AW25" s="17"/>
-      <c r="AX25" s="19"/>
-      <c r="AY25" s="18"/>
-      <c r="AZ25" s="17"/>
-      <c r="BA25" s="22"/>
-      <c r="BB25" s="18"/>
-      <c r="BC25" s="17"/>
-      <c r="BD25" s="22"/>
-      <c r="BE25" s="17"/>
+      <c r="AY25" s="19"/>
+      <c r="AZ25" s="21"/>
+      <c r="BA25" s="17"/>
+      <c r="BB25" s="19"/>
+      <c r="BC25" s="18"/>
+      <c r="BD25" s="17"/>
+      <c r="BE25" s="22"/>
       <c r="BF25" s="18"/>
       <c r="BG25" s="17"/>
-      <c r="BH25" s="17"/>
+      <c r="BH25" s="22"/>
       <c r="BI25" s="17"/>
       <c r="BJ25" s="18"/>
-      <c r="BK25" s="18"/>
+      <c r="BK25" s="17"/>
       <c r="BL25" s="17"/>
       <c r="BM25" s="17"/>
-      <c r="BN25" s="17"/>
-      <c r="BO25" s="17"/>
+      <c r="BN25" s="18"/>
+      <c r="BO25" s="18"/>
       <c r="BP25" s="17"/>
-      <c r="BQ25">
+      <c r="BQ25" s="17"/>
+      <c r="BR25" s="17"/>
+      <c r="BS25" s="17"/>
+      <c r="BT25" s="17"/>
+      <c r="BU25">
         <v>21</v>
       </c>
-      <c r="BS25" t="s">
+      <c r="BW25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -4050,7 +4215,9 @@
       <c r="P26" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="Q26" s="29"/>
+      <c r="Q26" s="29" t="s">
+        <v>118</v>
+      </c>
       <c r="R26" s="23"/>
       <c r="S26" s="29"/>
       <c r="T26" s="29"/>
@@ -4074,49 +4241,53 @@
       <c r="AL26" s="29"/>
       <c r="AM26" s="29"/>
       <c r="AN26" s="29"/>
-      <c r="AO26" s="18"/>
+      <c r="AO26" s="29"/>
       <c r="AP26" s="29"/>
-      <c r="AQ26" s="19"/>
-      <c r="AR26" s="19"/>
-      <c r="AS26" s="21"/>
-      <c r="AT26" s="20" t="s">
+      <c r="AQ26" s="29"/>
+      <c r="AR26" s="29"/>
+      <c r="AS26" s="18"/>
+      <c r="AT26" s="29"/>
+      <c r="AU26" s="19"/>
+      <c r="AV26" s="19"/>
+      <c r="AW26" s="21"/>
+      <c r="AX26" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="AU26" s="34" t="s">
+      <c r="AY26" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="AV26" s="18"/>
-      <c r="AW26" s="17"/>
-      <c r="AX26" s="22"/>
-      <c r="AY26" s="18"/>
-      <c r="AZ26" s="17"/>
+      <c r="AZ26" s="18"/>
       <c r="BA26" s="17"/>
-      <c r="BB26" s="29"/>
-      <c r="BC26" s="17"/>
+      <c r="BB26" s="22"/>
+      <c r="BC26" s="18"/>
       <c r="BD26" s="17"/>
       <c r="BE26" s="17"/>
-      <c r="BF26" s="18"/>
+      <c r="BF26" s="29"/>
       <c r="BG26" s="17"/>
       <c r="BH26" s="17"/>
       <c r="BI26" s="17"/>
       <c r="BJ26" s="18"/>
-      <c r="BK26" s="18"/>
-      <c r="BL26" s="29"/>
-      <c r="BM26" s="29"/>
-      <c r="BN26" s="29"/>
-      <c r="BO26" s="29"/>
+      <c r="BK26" s="17"/>
+      <c r="BL26" s="17"/>
+      <c r="BM26" s="17"/>
+      <c r="BN26" s="18"/>
+      <c r="BO26" s="18"/>
       <c r="BP26" s="29"/>
-      <c r="BQ26" s="14">
+      <c r="BQ26" s="29"/>
+      <c r="BR26" s="29"/>
+      <c r="BS26" s="29"/>
+      <c r="BT26" s="29"/>
+      <c r="BU26" s="14">
         <v>22</v>
       </c>
-      <c r="BR26" s="15" t="s">
+      <c r="BV26" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="BS26" s="14" t="s">
+      <c r="BW26" s="14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -4159,7 +4330,9 @@
       <c r="P27" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="Q27" s="30"/>
+      <c r="Q27" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="R27" s="30"/>
       <c r="S27" s="30"/>
       <c r="T27" s="30"/>
@@ -4183,30 +4356,30 @@
       <c r="AL27" s="30"/>
       <c r="AM27" s="30"/>
       <c r="AN27" s="30"/>
-      <c r="AO27" s="18"/>
+      <c r="AO27" s="30"/>
       <c r="AP27" s="30"/>
-      <c r="AQ27" s="19"/>
-      <c r="AR27" s="41" t="s">
+      <c r="AQ27" s="30"/>
+      <c r="AR27" s="30"/>
+      <c r="AS27" s="18"/>
+      <c r="AT27" s="30"/>
+      <c r="AU27" s="19"/>
+      <c r="AV27" s="41" t="s">
         <v>177</v>
       </c>
-      <c r="AS27" s="18"/>
-      <c r="AT27" s="20" t="s">
+      <c r="AW27" s="18"/>
+      <c r="AX27" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="AU27" s="34" t="s">
+      <c r="AY27" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="AV27" s="18"/>
-      <c r="AW27" s="21" t="s">
+      <c r="AZ27" s="18"/>
+      <c r="BA27" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="AX27" s="21" t="s">
+      <c r="BB27" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="AY27" s="17"/>
-      <c r="AZ27" s="17"/>
-      <c r="BA27" s="17"/>
-      <c r="BB27" s="18"/>
       <c r="BC27" s="17"/>
       <c r="BD27" s="17"/>
       <c r="BE27" s="17"/>
@@ -4215,20 +4388,24 @@
       <c r="BH27" s="17"/>
       <c r="BI27" s="17"/>
       <c r="BJ27" s="18"/>
-      <c r="BK27" s="18"/>
-      <c r="BL27" s="30"/>
-      <c r="BM27" s="30"/>
-      <c r="BN27" s="30"/>
-      <c r="BO27" s="30"/>
+      <c r="BK27" s="17"/>
+      <c r="BL27" s="17"/>
+      <c r="BM27" s="17"/>
+      <c r="BN27" s="18"/>
+      <c r="BO27" s="18"/>
       <c r="BP27" s="30"/>
-      <c r="BQ27">
+      <c r="BQ27" s="30"/>
+      <c r="BR27" s="30"/>
+      <c r="BS27" s="30"/>
+      <c r="BT27" s="30"/>
+      <c r="BU27">
         <v>23</v>
       </c>
-      <c r="BS27" t="s">
+      <c r="BW27" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -4273,7 +4450,9 @@
       <c r="P28" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="Q28" s="30"/>
+      <c r="Q28" s="30" t="s">
+        <v>119</v>
+      </c>
       <c r="R28" s="30"/>
       <c r="S28" s="30"/>
       <c r="T28" s="30"/>
@@ -4297,24 +4476,24 @@
       <c r="AL28" s="30"/>
       <c r="AM28" s="30"/>
       <c r="AN28" s="30"/>
-      <c r="AO28" s="18"/>
+      <c r="AO28" s="30"/>
       <c r="AP28" s="30"/>
-      <c r="AQ28" s="19"/>
-      <c r="AR28" s="19"/>
-      <c r="AS28" s="32"/>
-      <c r="AT28" s="27" t="s">
+      <c r="AQ28" s="30"/>
+      <c r="AR28" s="30"/>
+      <c r="AS28" s="18"/>
+      <c r="AT28" s="30"/>
+      <c r="AU28" s="19"/>
+      <c r="AV28" s="19"/>
+      <c r="AW28" s="32"/>
+      <c r="AX28" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="AU28" s="7" t="s">
+      <c r="AY28" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="AV28" s="18"/>
-      <c r="AW28" s="17"/>
-      <c r="AX28" s="28"/>
-      <c r="AY28" s="17"/>
-      <c r="AZ28" s="17"/>
+      <c r="AZ28" s="18"/>
       <c r="BA28" s="17"/>
-      <c r="BB28" s="18"/>
+      <c r="BB28" s="28"/>
       <c r="BC28" s="17"/>
       <c r="BD28" s="17"/>
       <c r="BE28" s="17"/>
@@ -4323,14 +4502,18 @@
       <c r="BH28" s="17"/>
       <c r="BI28" s="17"/>
       <c r="BJ28" s="18"/>
-      <c r="BK28" s="18"/>
-      <c r="BL28" s="30"/>
-      <c r="BM28" s="30"/>
-      <c r="BN28" s="30"/>
-      <c r="BO28" s="30"/>
+      <c r="BK28" s="17"/>
+      <c r="BL28" s="17"/>
+      <c r="BM28" s="17"/>
+      <c r="BN28" s="18"/>
+      <c r="BO28" s="18"/>
       <c r="BP28" s="30"/>
+      <c r="BQ28" s="30"/>
+      <c r="BR28" s="30"/>
+      <c r="BS28" s="30"/>
+      <c r="BT28" s="30"/>
     </row>
-    <row r="29" spans="1:71" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:75" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -4373,7 +4556,9 @@
       <c r="P29" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="Q29" s="30"/>
+      <c r="Q29" s="30" t="s">
+        <v>119</v>
+      </c>
       <c r="R29" s="30"/>
       <c r="S29" s="30"/>
       <c r="T29" s="30"/>
@@ -4397,24 +4582,24 @@
       <c r="AL29" s="30"/>
       <c r="AM29" s="30"/>
       <c r="AN29" s="30"/>
-      <c r="AO29" s="18"/>
+      <c r="AO29" s="30"/>
       <c r="AP29" s="30"/>
-      <c r="AQ29" s="19"/>
-      <c r="AR29" s="41" t="s">
+      <c r="AQ29" s="30"/>
+      <c r="AR29" s="30"/>
+      <c r="AS29" s="18"/>
+      <c r="AT29" s="30"/>
+      <c r="AU29" s="19"/>
+      <c r="AV29" s="41" t="s">
         <v>177</v>
       </c>
-      <c r="AS29" s="32"/>
-      <c r="AT29" s="26" t="s">
+      <c r="AW29" s="32"/>
+      <c r="AX29" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="AU29" s="19"/>
-      <c r="AV29" s="18"/>
-      <c r="AW29" s="17"/>
-      <c r="AX29" s="28"/>
-      <c r="AY29" s="17"/>
-      <c r="AZ29" s="17"/>
+      <c r="AY29" s="19"/>
+      <c r="AZ29" s="18"/>
       <c r="BA29" s="17"/>
-      <c r="BB29" s="18"/>
+      <c r="BB29" s="28"/>
       <c r="BC29" s="17"/>
       <c r="BD29" s="17"/>
       <c r="BE29" s="17"/>
@@ -4423,14 +4608,18 @@
       <c r="BH29" s="17"/>
       <c r="BI29" s="17"/>
       <c r="BJ29" s="18"/>
-      <c r="BK29" s="18"/>
-      <c r="BL29" s="30"/>
-      <c r="BM29" s="30"/>
-      <c r="BN29" s="30"/>
-      <c r="BO29" s="30"/>
+      <c r="BK29" s="17"/>
+      <c r="BL29" s="17"/>
+      <c r="BM29" s="17"/>
+      <c r="BN29" s="18"/>
+      <c r="BO29" s="18"/>
       <c r="BP29" s="30"/>
+      <c r="BQ29" s="30"/>
+      <c r="BR29" s="30"/>
+      <c r="BS29" s="30"/>
+      <c r="BT29" s="30"/>
     </row>
-    <row r="30" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -4473,7 +4662,9 @@
       <c r="P30" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="Q30" s="30"/>
+      <c r="Q30" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="R30" s="30"/>
       <c r="S30" s="30"/>
       <c r="T30" s="30"/>
@@ -4497,24 +4688,24 @@
       <c r="AL30" s="30"/>
       <c r="AM30" s="30"/>
       <c r="AN30" s="30"/>
-      <c r="AO30" s="18"/>
+      <c r="AO30" s="30"/>
       <c r="AP30" s="30"/>
-      <c r="AQ30" s="19"/>
-      <c r="AR30" s="42"/>
-      <c r="AS30" s="32"/>
-      <c r="AT30" s="35" t="s">
+      <c r="AQ30" s="30"/>
+      <c r="AR30" s="30"/>
+      <c r="AS30" s="18"/>
+      <c r="AT30" s="30"/>
+      <c r="AU30" s="19"/>
+      <c r="AV30" s="42"/>
+      <c r="AW30" s="32"/>
+      <c r="AX30" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="AU30" s="34" t="s">
+      <c r="AY30" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="AV30" s="18"/>
-      <c r="AW30" s="17"/>
-      <c r="AX30" s="28"/>
-      <c r="AY30" s="17"/>
-      <c r="AZ30" s="17"/>
+      <c r="AZ30" s="18"/>
       <c r="BA30" s="17"/>
-      <c r="BB30" s="18"/>
+      <c r="BB30" s="28"/>
       <c r="BC30" s="17"/>
       <c r="BD30" s="17"/>
       <c r="BE30" s="17"/>
@@ -4523,14 +4714,18 @@
       <c r="BH30" s="17"/>
       <c r="BI30" s="17"/>
       <c r="BJ30" s="18"/>
-      <c r="BK30" s="18"/>
-      <c r="BL30" s="30"/>
-      <c r="BM30" s="30"/>
-      <c r="BN30" s="30"/>
-      <c r="BO30" s="30"/>
+      <c r="BK30" s="17"/>
+      <c r="BL30" s="17"/>
+      <c r="BM30" s="17"/>
+      <c r="BN30" s="18"/>
+      <c r="BO30" s="18"/>
       <c r="BP30" s="30"/>
+      <c r="BQ30" s="30"/>
+      <c r="BR30" s="30"/>
+      <c r="BS30" s="30"/>
+      <c r="BT30" s="30"/>
     </row>
-    <row r="31" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -4573,7 +4768,9 @@
       <c r="P31" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="Q31" s="30"/>
+      <c r="Q31" s="63" t="s">
+        <v>118</v>
+      </c>
       <c r="R31" s="30"/>
       <c r="S31" s="30"/>
       <c r="T31" s="30"/>
@@ -4597,26 +4794,26 @@
       <c r="AL31" s="30"/>
       <c r="AM31" s="30"/>
       <c r="AN31" s="30"/>
-      <c r="AO31" s="18"/>
+      <c r="AO31" s="30"/>
       <c r="AP31" s="30"/>
-      <c r="AQ31" s="19"/>
-      <c r="AR31" s="41" t="s">
+      <c r="AQ31" s="30"/>
+      <c r="AR31" s="30"/>
+      <c r="AS31" s="18"/>
+      <c r="AT31" s="30"/>
+      <c r="AU31" s="19"/>
+      <c r="AV31" s="41" t="s">
         <v>177</v>
       </c>
-      <c r="AS31" s="32"/>
-      <c r="AT31" s="20" t="s">
+      <c r="AW31" s="32"/>
+      <c r="AX31" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="AU31" s="19" t="s">
+      <c r="AY31" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="AV31" s="18"/>
-      <c r="AW31" s="17"/>
-      <c r="AX31" s="28"/>
-      <c r="AY31" s="17"/>
-      <c r="AZ31" s="17"/>
+      <c r="AZ31" s="18"/>
       <c r="BA31" s="17"/>
-      <c r="BB31" s="18"/>
+      <c r="BB31" s="28"/>
       <c r="BC31" s="17"/>
       <c r="BD31" s="17"/>
       <c r="BE31" s="17"/>
@@ -4625,14 +4822,18 @@
       <c r="BH31" s="17"/>
       <c r="BI31" s="17"/>
       <c r="BJ31" s="18"/>
-      <c r="BK31" s="18"/>
-      <c r="BL31" s="30"/>
-      <c r="BM31" s="30"/>
-      <c r="BN31" s="30"/>
-      <c r="BO31" s="30"/>
+      <c r="BK31" s="17"/>
+      <c r="BL31" s="17"/>
+      <c r="BM31" s="17"/>
+      <c r="BN31" s="18"/>
+      <c r="BO31" s="18"/>
       <c r="BP31" s="30"/>
+      <c r="BQ31" s="30"/>
+      <c r="BR31" s="30"/>
+      <c r="BS31" s="30"/>
+      <c r="BT31" s="30"/>
     </row>
-    <row r="32" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -4675,7 +4876,9 @@
       <c r="P32" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="Q32" s="30"/>
+      <c r="Q32" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="R32" s="30"/>
       <c r="S32" s="30"/>
       <c r="T32" s="30"/>
@@ -4699,30 +4902,30 @@
       <c r="AL32" s="30"/>
       <c r="AM32" s="30"/>
       <c r="AN32" s="30"/>
-      <c r="AO32" s="18"/>
+      <c r="AO32" s="30"/>
       <c r="AP32" s="30"/>
-      <c r="AQ32" s="19"/>
-      <c r="AR32" s="42" t="s">
+      <c r="AQ32" s="30"/>
+      <c r="AR32" s="30"/>
+      <c r="AS32" s="18"/>
+      <c r="AT32" s="30"/>
+      <c r="AU32" s="19"/>
+      <c r="AV32" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="AS32" s="32"/>
-      <c r="AT32" s="33" t="s">
+      <c r="AW32" s="32"/>
+      <c r="AX32" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="AU32" s="34" t="s">
+      <c r="AY32" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="AV32" s="18"/>
-      <c r="AW32" s="17" t="s">
+      <c r="AZ32" s="18"/>
+      <c r="BA32" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="AX32" s="28" t="s">
+      <c r="BB32" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="AY32" s="17"/>
-      <c r="AZ32" s="17"/>
-      <c r="BA32" s="17"/>
-      <c r="BB32" s="18"/>
       <c r="BC32" s="17"/>
       <c r="BD32" s="17"/>
       <c r="BE32" s="17"/>
@@ -4731,14 +4934,18 @@
       <c r="BH32" s="17"/>
       <c r="BI32" s="17"/>
       <c r="BJ32" s="18"/>
-      <c r="BK32" s="18"/>
-      <c r="BL32" s="30"/>
-      <c r="BM32" s="30"/>
-      <c r="BN32" s="30"/>
-      <c r="BO32" s="30"/>
+      <c r="BK32" s="17"/>
+      <c r="BL32" s="17"/>
+      <c r="BM32" s="17"/>
+      <c r="BN32" s="18"/>
+      <c r="BO32" s="18"/>
       <c r="BP32" s="30"/>
+      <c r="BQ32" s="30"/>
+      <c r="BR32" s="30"/>
+      <c r="BS32" s="30"/>
+      <c r="BT32" s="30"/>
     </row>
-    <row r="33" spans="1:71" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:75" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -4781,7 +4988,9 @@
       <c r="P33" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="Q33" s="30"/>
+      <c r="Q33" s="63" t="s">
+        <v>118</v>
+      </c>
       <c r="R33" s="30"/>
       <c r="S33" s="30"/>
       <c r="T33" s="30"/>
@@ -4805,22 +5014,22 @@
       <c r="AL33" s="30"/>
       <c r="AM33" s="30"/>
       <c r="AN33" s="30"/>
-      <c r="AO33" s="18"/>
+      <c r="AO33" s="30"/>
       <c r="AP33" s="30"/>
-      <c r="AQ33" s="19"/>
-      <c r="AR33" s="19"/>
-      <c r="AS33" s="32"/>
-      <c r="AT33" s="26" t="s">
+      <c r="AQ33" s="30"/>
+      <c r="AR33" s="30"/>
+      <c r="AS33" s="18"/>
+      <c r="AT33" s="30"/>
+      <c r="AU33" s="19"/>
+      <c r="AV33" s="19"/>
+      <c r="AW33" s="32"/>
+      <c r="AX33" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="AU33" s="19"/>
-      <c r="AV33" s="18"/>
-      <c r="AW33" s="17"/>
-      <c r="AX33" s="28"/>
-      <c r="AY33" s="17"/>
-      <c r="AZ33" s="17"/>
+      <c r="AY33" s="19"/>
+      <c r="AZ33" s="18"/>
       <c r="BA33" s="17"/>
-      <c r="BB33" s="18"/>
+      <c r="BB33" s="28"/>
       <c r="BC33" s="17"/>
       <c r="BD33" s="17"/>
       <c r="BE33" s="17"/>
@@ -4829,14 +5038,18 @@
       <c r="BH33" s="17"/>
       <c r="BI33" s="17"/>
       <c r="BJ33" s="18"/>
-      <c r="BK33" s="18"/>
-      <c r="BL33" s="30"/>
-      <c r="BM33" s="30"/>
-      <c r="BN33" s="30"/>
-      <c r="BO33" s="30"/>
+      <c r="BK33" s="17"/>
+      <c r="BL33" s="17"/>
+      <c r="BM33" s="17"/>
+      <c r="BN33" s="18"/>
+      <c r="BO33" s="18"/>
       <c r="BP33" s="30"/>
+      <c r="BQ33" s="30"/>
+      <c r="BR33" s="30"/>
+      <c r="BS33" s="30"/>
+      <c r="BT33" s="30"/>
     </row>
-    <row r="34" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -4879,7 +5092,9 @@
       <c r="P34" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="Q34" s="30"/>
+      <c r="Q34" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="R34" s="30"/>
       <c r="S34" s="30"/>
       <c r="T34" s="30"/>
@@ -4903,24 +5118,24 @@
       <c r="AL34" s="30"/>
       <c r="AM34" s="30"/>
       <c r="AN34" s="30"/>
-      <c r="AO34" s="18"/>
+      <c r="AO34" s="30"/>
       <c r="AP34" s="30"/>
-      <c r="AQ34" s="19"/>
-      <c r="AR34" s="19"/>
-      <c r="AS34" s="32"/>
-      <c r="AT34" s="20" t="s">
+      <c r="AQ34" s="30"/>
+      <c r="AR34" s="30"/>
+      <c r="AS34" s="18"/>
+      <c r="AT34" s="30"/>
+      <c r="AU34" s="19"/>
+      <c r="AV34" s="19"/>
+      <c r="AW34" s="32"/>
+      <c r="AX34" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="AU34" s="19" t="s">
+      <c r="AY34" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="AV34" s="18"/>
-      <c r="AW34" s="17"/>
-      <c r="AX34" s="28"/>
-      <c r="AY34" s="17"/>
-      <c r="AZ34" s="17"/>
+      <c r="AZ34" s="18"/>
       <c r="BA34" s="17"/>
-      <c r="BB34" s="18"/>
+      <c r="BB34" s="28"/>
       <c r="BC34" s="17"/>
       <c r="BD34" s="17"/>
       <c r="BE34" s="17"/>
@@ -4929,14 +5144,18 @@
       <c r="BH34" s="17"/>
       <c r="BI34" s="17"/>
       <c r="BJ34" s="18"/>
-      <c r="BK34" s="18"/>
-      <c r="BL34" s="30"/>
-      <c r="BM34" s="30"/>
-      <c r="BN34" s="30"/>
-      <c r="BO34" s="30"/>
+      <c r="BK34" s="17"/>
+      <c r="BL34" s="17"/>
+      <c r="BM34" s="17"/>
+      <c r="BN34" s="18"/>
+      <c r="BO34" s="18"/>
       <c r="BP34" s="30"/>
+      <c r="BQ34" s="30"/>
+      <c r="BR34" s="30"/>
+      <c r="BS34" s="30"/>
+      <c r="BT34" s="30"/>
     </row>
-    <row r="35" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -4979,7 +5198,9 @@
       <c r="P35" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="Q35" s="30"/>
+      <c r="Q35" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="R35" s="30"/>
       <c r="S35" s="30"/>
       <c r="T35" s="30"/>
@@ -5003,24 +5224,24 @@
       <c r="AL35" s="30"/>
       <c r="AM35" s="30"/>
       <c r="AN35" s="30"/>
-      <c r="AO35" s="18"/>
+      <c r="AO35" s="30"/>
       <c r="AP35" s="30"/>
-      <c r="AQ35" s="19"/>
-      <c r="AR35" s="41"/>
-      <c r="AS35" s="32"/>
-      <c r="AT35" s="36" t="s">
+      <c r="AQ35" s="30"/>
+      <c r="AR35" s="30"/>
+      <c r="AS35" s="18"/>
+      <c r="AT35" s="30"/>
+      <c r="AU35" s="19"/>
+      <c r="AV35" s="41"/>
+      <c r="AW35" s="32"/>
+      <c r="AX35" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="AU35" s="34" t="s">
+      <c r="AY35" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="AV35" s="18"/>
-      <c r="AW35" s="17"/>
-      <c r="AX35" s="28"/>
-      <c r="AY35" s="17"/>
-      <c r="AZ35" s="17"/>
+      <c r="AZ35" s="18"/>
       <c r="BA35" s="17"/>
-      <c r="BB35" s="18"/>
+      <c r="BB35" s="28"/>
       <c r="BC35" s="17"/>
       <c r="BD35" s="17"/>
       <c r="BE35" s="17"/>
@@ -5029,14 +5250,18 @@
       <c r="BH35" s="17"/>
       <c r="BI35" s="17"/>
       <c r="BJ35" s="18"/>
-      <c r="BK35" s="18"/>
-      <c r="BL35" s="30"/>
-      <c r="BM35" s="30"/>
-      <c r="BN35" s="30"/>
-      <c r="BO35" s="30"/>
+      <c r="BK35" s="17"/>
+      <c r="BL35" s="17"/>
+      <c r="BM35" s="17"/>
+      <c r="BN35" s="18"/>
+      <c r="BO35" s="18"/>
       <c r="BP35" s="30"/>
+      <c r="BQ35" s="30"/>
+      <c r="BR35" s="30"/>
+      <c r="BS35" s="30"/>
+      <c r="BT35" s="30"/>
     </row>
-    <row r="36" spans="1:71" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:75" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -5079,7 +5304,9 @@
       <c r="P36" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="Q36" s="30"/>
+      <c r="Q36" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="R36" s="30"/>
       <c r="S36" s="17"/>
       <c r="T36" s="30"/>
@@ -5105,36 +5332,40 @@
       <c r="AN36" s="30"/>
       <c r="AO36" s="30"/>
       <c r="AP36" s="30"/>
-      <c r="AQ36" s="19"/>
-      <c r="AR36" s="19"/>
-      <c r="AS36" s="25"/>
-      <c r="AT36" s="26" t="s">
+      <c r="AQ36" s="30"/>
+      <c r="AR36" s="30"/>
+      <c r="AS36" s="30"/>
+      <c r="AT36" s="30"/>
+      <c r="AU36" s="19"/>
+      <c r="AV36" s="19"/>
+      <c r="AW36" s="25"/>
+      <c r="AX36" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="AU36" s="19"/>
-      <c r="AV36" s="17"/>
-      <c r="AW36" s="17"/>
-      <c r="AX36" s="17"/>
-      <c r="AY36" s="17"/>
+      <c r="AY36" s="19"/>
       <c r="AZ36" s="17"/>
       <c r="BA36" s="17"/>
       <c r="BB36" s="17"/>
       <c r="BC36" s="17"/>
-      <c r="BD36" s="30"/>
-      <c r="BE36" s="30"/>
-      <c r="BF36" s="30"/>
+      <c r="BD36" s="17"/>
+      <c r="BE36" s="17"/>
+      <c r="BF36" s="17"/>
       <c r="BG36" s="17"/>
-      <c r="BH36" s="17"/>
-      <c r="BI36" s="17"/>
+      <c r="BH36" s="30"/>
+      <c r="BI36" s="30"/>
       <c r="BJ36" s="30"/>
-      <c r="BK36" s="30"/>
-      <c r="BL36" s="30"/>
-      <c r="BM36" s="30"/>
+      <c r="BK36" s="17"/>
+      <c r="BL36" s="17"/>
+      <c r="BM36" s="17"/>
       <c r="BN36" s="30"/>
       <c r="BO36" s="30"/>
       <c r="BP36" s="30"/>
+      <c r="BQ36" s="30"/>
+      <c r="BR36" s="30"/>
+      <c r="BS36" s="30"/>
+      <c r="BT36" s="30"/>
     </row>
-    <row r="37" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -5179,7 +5410,9 @@
       <c r="P37" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="Q37" s="30"/>
+      <c r="Q37" s="30" t="s">
+        <v>119</v>
+      </c>
       <c r="R37" s="30"/>
       <c r="S37" s="17"/>
       <c r="T37" s="30"/>
@@ -5205,89 +5438,93 @@
       <c r="AN37" s="30"/>
       <c r="AO37" s="30"/>
       <c r="AP37" s="30"/>
-      <c r="AQ37" s="19"/>
-      <c r="AR37" s="19"/>
-      <c r="AS37" s="25"/>
-      <c r="AT37" s="33" t="s">
+      <c r="AQ37" s="30"/>
+      <c r="AR37" s="30"/>
+      <c r="AS37" s="30"/>
+      <c r="AT37" s="30"/>
+      <c r="AU37" s="19"/>
+      <c r="AV37" s="19"/>
+      <c r="AW37" s="25"/>
+      <c r="AX37" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="AU37" s="34" t="s">
+      <c r="AY37" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="AV37" s="17"/>
-      <c r="AW37" s="17"/>
-      <c r="AX37" s="17"/>
-      <c r="AY37" s="17"/>
       <c r="AZ37" s="17"/>
       <c r="BA37" s="17"/>
       <c r="BB37" s="17"/>
       <c r="BC37" s="17"/>
-      <c r="BD37" s="30"/>
-      <c r="BE37" s="30"/>
-      <c r="BF37" s="30"/>
+      <c r="BD37" s="17"/>
+      <c r="BE37" s="17"/>
+      <c r="BF37" s="17"/>
       <c r="BG37" s="17"/>
-      <c r="BH37" s="17"/>
-      <c r="BI37" s="17"/>
+      <c r="BH37" s="30"/>
+      <c r="BI37" s="30"/>
       <c r="BJ37" s="30"/>
-      <c r="BK37" s="30"/>
-      <c r="BL37" s="30"/>
-      <c r="BM37" s="30"/>
+      <c r="BK37" s="17"/>
+      <c r="BL37" s="17"/>
+      <c r="BM37" s="17"/>
       <c r="BN37" s="30"/>
       <c r="BO37" s="30"/>
       <c r="BP37" s="30"/>
+      <c r="BQ37" s="30"/>
+      <c r="BR37" s="30"/>
+      <c r="BS37" s="30"/>
+      <c r="BT37" s="30"/>
     </row>
-    <row r="38" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A38" s="49" t="s">
+    <row r="38" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A38" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="B38" s="50"/>
-      <c r="C38" s="50"/>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="50"/>
-      <c r="I38" s="50"/>
-      <c r="J38" s="50"/>
-      <c r="K38" s="50"/>
-      <c r="L38" s="50"/>
-      <c r="M38" s="50"/>
-      <c r="N38" s="50"/>
-      <c r="O38" s="50"/>
-      <c r="P38" s="50"/>
-      <c r="Q38" s="50"/>
-      <c r="R38" s="50"/>
-      <c r="S38" s="50"/>
-      <c r="T38" s="50"/>
-      <c r="U38" s="50"/>
-      <c r="V38" s="50"/>
-      <c r="W38" s="50"/>
-      <c r="X38" s="50"/>
-      <c r="Y38" s="50"/>
-      <c r="Z38" s="50"/>
-      <c r="AA38" s="50"/>
-      <c r="AB38" s="50"/>
-      <c r="AC38" s="50"/>
-      <c r="AD38" s="50"/>
-      <c r="AE38" s="50"/>
-      <c r="AF38" s="50"/>
-      <c r="AG38" s="50"/>
-      <c r="AH38" s="50"/>
-      <c r="AI38" s="50"/>
-      <c r="AJ38" s="50"/>
-      <c r="AK38" s="50"/>
-      <c r="AL38" s="50"/>
-      <c r="AM38" s="50"/>
-      <c r="AN38" s="50"/>
-      <c r="AO38" s="50"/>
-      <c r="AP38" s="50"/>
-      <c r="AQ38" s="50"/>
-      <c r="AR38" s="50"/>
-      <c r="AS38" s="51"/>
-      <c r="AT38" s="2"/>
-      <c r="AU38" s="2"/>
-      <c r="AV38" s="2"/>
-      <c r="AW38" s="2"/>
+      <c r="B38" s="57"/>
+      <c r="C38" s="57"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="57"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="57"/>
+      <c r="L38" s="57"/>
+      <c r="M38" s="57"/>
+      <c r="N38" s="57"/>
+      <c r="O38" s="57"/>
+      <c r="P38" s="57"/>
+      <c r="Q38" s="57"/>
+      <c r="R38" s="57"/>
+      <c r="S38" s="57"/>
+      <c r="T38" s="57"/>
+      <c r="U38" s="57"/>
+      <c r="V38" s="57"/>
+      <c r="W38" s="57"/>
+      <c r="X38" s="57"/>
+      <c r="Y38" s="57"/>
+      <c r="Z38" s="57"/>
+      <c r="AA38" s="57"/>
+      <c r="AB38" s="57"/>
+      <c r="AC38" s="57"/>
+      <c r="AD38" s="57"/>
+      <c r="AE38" s="57"/>
+      <c r="AF38" s="57"/>
+      <c r="AG38" s="57"/>
+      <c r="AH38" s="57"/>
+      <c r="AI38" s="57"/>
+      <c r="AJ38" s="57"/>
+      <c r="AK38" s="57"/>
+      <c r="AL38" s="57"/>
+      <c r="AM38" s="57"/>
+      <c r="AN38" s="57"/>
+      <c r="AO38" s="57"/>
+      <c r="AP38" s="57"/>
+      <c r="AQ38" s="57"/>
+      <c r="AR38" s="57"/>
+      <c r="AS38" s="57"/>
+      <c r="AT38" s="57"/>
+      <c r="AU38" s="57"/>
+      <c r="AV38" s="57"/>
+      <c r="AW38" s="58"/>
       <c r="AX38" s="2"/>
       <c r="AY38" s="2"/>
       <c r="AZ38" s="2"/>
@@ -5307,65 +5544,69 @@
       <c r="BN38" s="2"/>
       <c r="BO38" s="2"/>
       <c r="BP38" s="2"/>
-      <c r="BQ38">
+      <c r="BQ38" s="2"/>
+      <c r="BR38" s="2"/>
+      <c r="BS38" s="2"/>
+      <c r="BT38" s="2"/>
+      <c r="BU38">
         <v>24</v>
       </c>
-      <c r="BS38" t="s">
+      <c r="BW38" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A39" s="52" t="s">
+    <row r="39" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A39" s="59" t="s">
         <v>85</v>
       </c>
-      <c r="B39" s="53"/>
-      <c r="C39" s="53"/>
-      <c r="D39" s="53"/>
-      <c r="E39" s="53"/>
-      <c r="F39" s="53"/>
-      <c r="G39" s="53"/>
-      <c r="H39" s="53"/>
-      <c r="I39" s="53"/>
-      <c r="J39" s="53"/>
-      <c r="K39" s="53"/>
-      <c r="L39" s="53"/>
-      <c r="M39" s="53"/>
-      <c r="N39" s="53"/>
-      <c r="O39" s="53"/>
-      <c r="P39" s="53"/>
-      <c r="Q39" s="53"/>
-      <c r="R39" s="53"/>
-      <c r="S39" s="53"/>
-      <c r="T39" s="53"/>
-      <c r="U39" s="53"/>
-      <c r="V39" s="53"/>
-      <c r="W39" s="53"/>
-      <c r="X39" s="53"/>
-      <c r="Y39" s="53"/>
-      <c r="Z39" s="53"/>
-      <c r="AA39" s="53"/>
-      <c r="AB39" s="53"/>
-      <c r="AC39" s="53"/>
-      <c r="AD39" s="53"/>
-      <c r="AE39" s="53"/>
-      <c r="AF39" s="53"/>
-      <c r="AG39" s="53"/>
-      <c r="AH39" s="53"/>
-      <c r="AI39" s="53"/>
-      <c r="AJ39" s="53"/>
-      <c r="AK39" s="53"/>
-      <c r="AL39" s="53"/>
-      <c r="AM39" s="53"/>
-      <c r="AN39" s="53"/>
-      <c r="AO39" s="53"/>
-      <c r="AP39" s="53"/>
-      <c r="AQ39" s="53"/>
-      <c r="AR39" s="53"/>
-      <c r="AS39" s="54"/>
-      <c r="AT39" s="2"/>
-      <c r="AU39" s="2"/>
-      <c r="AV39" s="2"/>
-      <c r="AW39" s="2"/>
+      <c r="B39" s="60"/>
+      <c r="C39" s="60"/>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="60"/>
+      <c r="H39" s="60"/>
+      <c r="I39" s="60"/>
+      <c r="J39" s="60"/>
+      <c r="K39" s="60"/>
+      <c r="L39" s="60"/>
+      <c r="M39" s="60"/>
+      <c r="N39" s="60"/>
+      <c r="O39" s="60"/>
+      <c r="P39" s="60"/>
+      <c r="Q39" s="60"/>
+      <c r="R39" s="60"/>
+      <c r="S39" s="60"/>
+      <c r="T39" s="60"/>
+      <c r="U39" s="60"/>
+      <c r="V39" s="60"/>
+      <c r="W39" s="60"/>
+      <c r="X39" s="60"/>
+      <c r="Y39" s="60"/>
+      <c r="Z39" s="60"/>
+      <c r="AA39" s="60"/>
+      <c r="AB39" s="60"/>
+      <c r="AC39" s="60"/>
+      <c r="AD39" s="60"/>
+      <c r="AE39" s="60"/>
+      <c r="AF39" s="60"/>
+      <c r="AG39" s="60"/>
+      <c r="AH39" s="60"/>
+      <c r="AI39" s="60"/>
+      <c r="AJ39" s="60"/>
+      <c r="AK39" s="60"/>
+      <c r="AL39" s="60"/>
+      <c r="AM39" s="60"/>
+      <c r="AN39" s="60"/>
+      <c r="AO39" s="60"/>
+      <c r="AP39" s="60"/>
+      <c r="AQ39" s="60"/>
+      <c r="AR39" s="60"/>
+      <c r="AS39" s="60"/>
+      <c r="AT39" s="60"/>
+      <c r="AU39" s="60"/>
+      <c r="AV39" s="60"/>
+      <c r="AW39" s="61"/>
       <c r="AX39" s="2"/>
       <c r="AY39" s="2"/>
       <c r="AZ39" s="2"/>
@@ -5385,14 +5626,18 @@
       <c r="BN39" s="2"/>
       <c r="BO39" s="2"/>
       <c r="BP39" s="2"/>
-      <c r="BQ39">
+      <c r="BQ39" s="2"/>
+      <c r="BR39" s="2"/>
+      <c r="BS39" s="2"/>
+      <c r="BT39" s="2"/>
+      <c r="BU39">
         <v>25</v>
       </c>
-      <c r="BS39" t="s">
+      <c r="BW39" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:75" x14ac:dyDescent="0.25">
       <c r="D40">
         <v>1</v>
       </c>
@@ -5459,56 +5704,71 @@
       <c r="Y40">
         <v>22</v>
       </c>
+      <c r="Z40">
+        <v>23</v>
+      </c>
       <c r="AA40">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB40">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC40">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AD40">
+        <v>27</v>
+      </c>
+      <c r="AE40">
+        <v>28</v>
+      </c>
+      <c r="AF40">
+        <v>29</v>
+      </c>
+      <c r="AG40">
+        <v>30</v>
+      </c>
+      <c r="AH40">
+        <v>31</v>
+      </c>
+      <c r="AI40">
+        <v>32</v>
+      </c>
+      <c r="AJ40">
+        <v>33</v>
+      </c>
+      <c r="AK40">
+        <v>34</v>
+      </c>
+      <c r="AL40">
+        <v>35</v>
+      </c>
+      <c r="AM40">
+        <v>36</v>
+      </c>
+      <c r="AN40">
+        <v>36</v>
+      </c>
+      <c r="AO40">
+        <v>37</v>
+      </c>
+      <c r="AP40">
+        <v>38</v>
+      </c>
+      <c r="AQ40">
+        <v>39</v>
+      </c>
+      <c r="AR40">
+        <v>40</v>
+      </c>
+      <c r="BU40">
         <v>26</v>
       </c>
-      <c r="AE40">
-        <v>27</v>
-      </c>
-      <c r="AF40">
-        <v>28</v>
-      </c>
-      <c r="AG40">
-        <v>29</v>
-      </c>
-      <c r="AH40">
-        <v>30</v>
-      </c>
-      <c r="AI40">
-        <v>29</v>
-      </c>
-      <c r="AJ40">
-        <v>30</v>
-      </c>
-      <c r="AK40">
-        <v>31</v>
-      </c>
-      <c r="AL40">
-        <v>32</v>
-      </c>
-      <c r="AM40">
-        <v>33</v>
-      </c>
-      <c r="AN40">
-        <v>34</v>
-      </c>
-      <c r="BQ40">
-        <v>26</v>
-      </c>
-      <c r="BS40" t="s">
+      <c r="BW40" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:75" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" t="s">
         <v>123</v>
       </c>
@@ -5575,6 +5835,9 @@
       <c r="Y41" t="s">
         <v>124</v>
       </c>
+      <c r="Z41" t="s">
+        <v>124</v>
+      </c>
       <c r="AA41" t="s">
         <v>123</v>
       </c>
@@ -5591,38 +5854,53 @@
         <v>124</v>
       </c>
       <c r="AF41" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG41" t="s">
         <v>123</v>
       </c>
       <c r="AH41" t="s">
+        <v>123</v>
+      </c>
+      <c r="AI41" t="s">
         <v>124</v>
       </c>
-      <c r="AI41" t="s">
+      <c r="AJ41" t="s">
         <v>123</v>
       </c>
-      <c r="AJ41" t="s">
+      <c r="AK41" t="s">
         <v>124</v>
       </c>
-      <c r="AK41" t="s">
+      <c r="AL41" t="s">
+        <v>124</v>
+      </c>
+      <c r="AM41" t="s">
         <v>123</v>
       </c>
-      <c r="AL41" t="s">
+      <c r="AN41" t="s">
         <v>123</v>
       </c>
-      <c r="AM41" t="s">
+      <c r="AO41" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP41" t="s">
         <v>124</v>
       </c>
-      <c r="BA41"/>
-      <c r="BQ41">
+      <c r="AQ41" t="s">
+        <v>123</v>
+      </c>
+      <c r="AR41" t="s">
+        <v>124</v>
+      </c>
+      <c r="BE41"/>
+      <c r="BU41">
         <v>27</v>
       </c>
-      <c r="BS41" t="s">
+      <c r="BW41" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:75" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="16" t="s">
         <v>126</v>
       </c>
@@ -5641,17 +5919,20 @@
       <c r="P42" t="s">
         <v>70</v>
       </c>
-      <c r="BC42" t="s">
+      <c r="Q42" t="s">
+        <v>70</v>
+      </c>
+      <c r="BG42" t="s">
         <v>69</v>
       </c>
-      <c r="BQ42">
+      <c r="BU42">
         <v>28</v>
       </c>
-      <c r="BS42" t="s">
+      <c r="BW42" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:75" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E43" s="16" t="s">
         <v>125</v>
       </c>
@@ -5665,280 +5946,278 @@
       <c r="L43" t="s">
         <v>70</v>
       </c>
-      <c r="BC43" t="s">
+      <c r="BG43" t="s">
         <v>71</v>
       </c>
-      <c r="BQ43" s="14">
+      <c r="BU43" s="14">
         <v>29</v>
       </c>
-      <c r="BR43" s="14"/>
-      <c r="BS43" s="14" t="s">
+      <c r="BV43" s="14"/>
+      <c r="BW43" s="14" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:75" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" t="s">
         <v>72</v>
       </c>
       <c r="G44" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="AQ44" t="s">
+      <c r="AU44" t="s">
         <v>62</v>
       </c>
-      <c r="AR44" s="5" t="s">
+      <c r="AV44" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="BQ44">
+      <c r="BU44">
         <v>30</v>
       </c>
-      <c r="BS44" t="s">
+      <c r="BW44" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:75" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" t="s">
         <v>73</v>
       </c>
-      <c r="AQ45" t="s">
+      <c r="AU45" t="s">
         <v>64</v>
       </c>
-      <c r="AR45" t="s">
+      <c r="AV45" t="s">
         <v>65</v>
       </c>
-      <c r="BQ45">
+      <c r="BU45">
         <v>31</v>
       </c>
-      <c r="BS45" t="s">
+      <c r="BW45" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="46" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:75" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" t="s">
         <v>75</v>
       </c>
-      <c r="AQ46" t="s">
+      <c r="AU46" t="s">
         <v>67</v>
       </c>
-      <c r="AR46" t="s">
+      <c r="AV46" t="s">
         <v>68</v>
       </c>
-      <c r="BQ46" s="14">
+      <c r="BU46" s="14">
         <v>32</v>
       </c>
-      <c r="BR46" s="14"/>
-      <c r="BS46" s="14" t="s">
+      <c r="BV46" s="14"/>
+      <c r="BW46" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BQ47">
+    <row r="47" spans="1:75" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BU47">
         <v>33</v>
       </c>
-      <c r="BS47" t="s">
+      <c r="BW47" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BQ48">
+    <row r="48" spans="1:75" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BU48">
         <v>34</v>
       </c>
-      <c r="BS48" s="6" t="s">
+      <c r="BW48" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="49" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BQ49">
+    <row r="49" spans="73:78" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BU49">
         <v>35</v>
       </c>
-      <c r="BS49" t="s">
+      <c r="BW49" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BQ50" s="37">
+    <row r="50" spans="73:78" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BU50" s="37">
         <v>36</v>
       </c>
-      <c r="BR50" s="37"/>
-      <c r="BS50" s="37" t="s">
+      <c r="BV50" s="37"/>
+      <c r="BW50" s="37" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BS51" t="s">
+    <row r="51" spans="73:78" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BW51" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="53" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BS53" s="8"/>
-      <c r="BT53" s="9"/>
-      <c r="BU53" s="8"/>
+    <row r="53" spans="73:78" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BW53" s="8"/>
+      <c r="BX53" s="9"/>
+      <c r="BY53" s="8"/>
     </row>
-    <row r="54" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BQ54">
+    <row r="54" spans="73:78" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BU54">
         <v>37</v>
       </c>
-      <c r="BS54" s="13" t="s">
+      <c r="BW54" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="BT54" s="10"/>
-      <c r="BU54" s="10"/>
+      <c r="BX54" s="10"/>
+      <c r="BY54" s="10"/>
     </row>
-    <row r="55" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BQ55">
+    <row r="55" spans="73:78" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BU55">
         <v>38</v>
       </c>
-      <c r="BS55" s="13" t="s">
+      <c r="BW55" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="BT55" s="11" t="s">
+      <c r="BX55" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="BU55" s="8" t="s">
+      <c r="BY55" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="BV55">
+      <c r="BZ55">
         <v>49</v>
       </c>
     </row>
-    <row r="56" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BS56" s="10"/>
-      <c r="BT56" s="11" t="s">
+    <row r="56" spans="73:78" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BW56" s="10"/>
+      <c r="BX56" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="BU56" s="8" t="s">
+      <c r="BY56" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="BV56">
+      <c r="BZ56">
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BQ57">
+    <row r="57" spans="73:78" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BU57">
         <v>39</v>
       </c>
-      <c r="BS57" s="8" t="s">
+      <c r="BW57" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="BT57" s="11" t="s">
+      <c r="BX57" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="BU57" s="8" t="s">
+      <c r="BY57" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="BV57">
+      <c r="BZ57">
         <v>51</v>
       </c>
     </row>
-    <row r="58" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BQ58">
+    <row r="58" spans="73:78" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BU58">
         <v>40</v>
       </c>
-      <c r="BS58" s="11" t="s">
+      <c r="BW58" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="BT58" s="10"/>
-      <c r="BU58" s="10"/>
+      <c r="BX58" s="10"/>
+      <c r="BY58" s="10"/>
     </row>
-    <row r="59" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BQ59" s="16">
+    <row r="59" spans="73:78" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BU59" s="16">
         <v>41</v>
       </c>
-      <c r="BS59" s="8" t="s">
+      <c r="BW59" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="BT59" s="10"/>
-      <c r="BU59" s="10"/>
+      <c r="BX59" s="10"/>
+      <c r="BY59" s="10"/>
     </row>
-    <row r="60" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BQ60">
+    <row r="60" spans="73:78" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BU60">
         <v>42</v>
       </c>
-      <c r="BS60" s="8" t="s">
+      <c r="BW60" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="BT60" s="10"/>
-      <c r="BU60" s="10"/>
+      <c r="BX60" s="10"/>
+      <c r="BY60" s="10"/>
     </row>
-    <row r="61" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BQ61">
+    <row r="61" spans="73:78" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BU61">
         <v>43</v>
       </c>
-      <c r="BS61" s="8" t="s">
+      <c r="BW61" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="BT61" s="10"/>
-      <c r="BU61" s="10"/>
+      <c r="BX61" s="10"/>
+      <c r="BY61" s="10"/>
     </row>
-    <row r="62" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BQ62">
+    <row r="62" spans="73:78" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BU62">
         <v>44</v>
       </c>
-      <c r="BS62" s="8" t="s">
+      <c r="BW62" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="BT62" s="10"/>
-      <c r="BU62" s="10"/>
+      <c r="BX62" s="10"/>
+      <c r="BY62" s="10"/>
     </row>
-    <row r="63" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BQ63">
+    <row r="63" spans="73:78" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BU63">
         <v>45</v>
       </c>
-      <c r="BS63" s="8" t="s">
+      <c r="BW63" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="BT63" s="10"/>
-      <c r="BU63" s="10"/>
+      <c r="BX63" s="10"/>
+      <c r="BY63" s="10"/>
     </row>
-    <row r="64" spans="69:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BQ64" s="16">
+    <row r="64" spans="73:78" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BU64" s="16">
         <v>46</v>
       </c>
-      <c r="BS64" s="8" t="s">
+      <c r="BW64" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="BT64" s="10"/>
-      <c r="BU64" s="10"/>
+      <c r="BX64" s="10"/>
+      <c r="BY64" s="10"/>
     </row>
-    <row r="65" spans="69:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BQ65">
+    <row r="65" spans="73:75" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BU65">
         <v>47</v>
       </c>
-      <c r="BS65" t="s">
+      <c r="BW65" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="66" spans="69:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BQ66">
+    <row r="66" spans="73:75" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BU66">
         <v>48</v>
       </c>
-      <c r="BS66" t="s">
+      <c r="BW66" t="s">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="52">
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="AZ2:BB3"/>
-    <mergeCell ref="AT2:AV3"/>
-    <mergeCell ref="AW2:AY3"/>
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="AH2:AH3"/>
-    <mergeCell ref="AI2:AI3"/>
-    <mergeCell ref="AJ2:AJ3"/>
-    <mergeCell ref="AK2:AK3"/>
-    <mergeCell ref="AL2:AL3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="AM2:AM3"/>
-    <mergeCell ref="A1:AS1"/>
+  <mergeCells count="56">
+    <mergeCell ref="AO2:AO3"/>
+    <mergeCell ref="AR2:AR3"/>
+    <mergeCell ref="BR2:BT3"/>
+    <mergeCell ref="A38:AW38"/>
+    <mergeCell ref="A39:AW39"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="AS2:AS3"/>
+    <mergeCell ref="AT2:AT3"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="BG2:BJ3"/>
+    <mergeCell ref="BK2:BN3"/>
+    <mergeCell ref="BO2:BQ3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="A1:AW1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
@@ -5950,31 +6229,37 @@
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
-    <mergeCell ref="AQ2:AS3"/>
+    <mergeCell ref="AU2:AW3"/>
     <mergeCell ref="X2:X3"/>
     <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="AQ2:AQ3"/>
+    <mergeCell ref="BD2:BF3"/>
+    <mergeCell ref="AX2:AZ3"/>
+    <mergeCell ref="BA2:BC3"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="AH2:AH3"/>
+    <mergeCell ref="AI2:AI3"/>
+    <mergeCell ref="AK2:AK3"/>
+    <mergeCell ref="AL2:AL3"/>
+    <mergeCell ref="AM2:AM3"/>
     <mergeCell ref="AN2:AN3"/>
-    <mergeCell ref="BN2:BP3"/>
-    <mergeCell ref="A38:AS38"/>
-    <mergeCell ref="A39:AS39"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="AO2:AO3"/>
     <mergeCell ref="AP2:AP3"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="BC2:BF3"/>
-    <mergeCell ref="BG2:BJ3"/>
-    <mergeCell ref="BK2:BM3"/>
-    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AJ2:AJ3"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="Y2:Y3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="BS6" r:id="rId1" display="Прикладная дискретная математика. Приложение. 2016. № 9. С. 68-70."/>
-    <hyperlink ref="BR26" r:id="rId2"/>
-    <hyperlink ref="BS48" r:id="rId3"/>
+    <hyperlink ref="BW6" r:id="rId1" display="Прикладная дискретная математика. Приложение. 2016. № 9. С. 68-70." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="BV26" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="BW48" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId4"/>
@@ -5983,6 +6268,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b78dbef7-f85b-47b5-8738-6377d50f4027" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bffb7b91-0466-4de0-9379-f5c53c3acedf">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Документ" ma:contentTypeID="0x0101004F6380A0290AF84484F859C9FFD97568" ma:contentTypeVersion="12" ma:contentTypeDescription="Создание документа." ma:contentTypeScope="" ma:versionID="1ee9877c88efff51dfb0d3a4b3e8ad1b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bffb7b91-0466-4de0-9379-f5c53c3acedf" xmlns:ns3="b78dbef7-f85b-47b5-8738-6377d50f4027" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="532d4df54980d57387e1b5dc96a6a32c" ns2:_="" ns3:_="">
     <xsd:import namespace="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
@@ -6183,17 +6479,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b78dbef7-f85b-47b5-8738-6377d50f4027" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bffb7b91-0466-4de0-9379-f5c53c3acedf">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -6204,6 +6489,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12ECB55F-B88E-4FE2-9AD5-5CA5D433F306}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b78dbef7-f85b-47b5-8738-6377d50f4027"/>
+    <ds:schemaRef ds:uri="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B6A6DF3-AE59-43BA-A5FF-CF9B7C54D4B8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6222,17 +6518,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12ECB55F-B88E-4FE2-9AD5-5CA5D433F306}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b78dbef7-f85b-47b5-8738-6377d50f4027"/>
-    <ds:schemaRef ds:uri="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00280879-8A9A-4335-93BC-405126DC8F0C}">
   <ds:schemaRefs>

--- a/Ведомость ТКИ-441 2026-2027.xlsx
+++ b/Ведомость ТКИ-441 2026-2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\StegMethods\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BE4F90-D776-42AC-BE96-2A88F2748415}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B96CFC-8D45-4FE8-9F76-16CBB51F492E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="184">
   <si>
     <t>Ведомость посещаемости занятий студентами группы ТКИ РУТ МИИТ</t>
   </si>
@@ -566,13 +566,25 @@
   </si>
   <si>
     <t>8ПЧ2</t>
+  </si>
+  <si>
+    <t>Суммирующий генератор</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Линейный конгруэнтный генератор </t>
+  </si>
+  <si>
+    <t>Генератор Рюппеля</t>
+  </si>
+  <si>
+    <t>Генератор Дженнингса</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -617,6 +629,13 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="8">
@@ -831,7 +850,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -909,10 +928,14 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -921,19 +944,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -952,13 +962,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1323,237 +1347,237 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:77" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="53"/>
-      <c r="W1" s="53"/>
-      <c r="X1" s="53"/>
-      <c r="Y1" s="53"/>
-      <c r="Z1" s="53"/>
-      <c r="AA1" s="53"/>
-      <c r="AB1" s="53"/>
-      <c r="AC1" s="53"/>
-      <c r="AD1" s="53"/>
-      <c r="AE1" s="53"/>
-      <c r="AF1" s="53"/>
-      <c r="AG1" s="53"/>
-      <c r="AH1" s="53"/>
-      <c r="AI1" s="53"/>
-      <c r="AJ1" s="53"/>
-      <c r="AK1" s="53"/>
-      <c r="AL1" s="53"/>
-      <c r="AM1" s="53"/>
-      <c r="AN1" s="53"/>
-      <c r="AO1" s="53"/>
-      <c r="AP1" s="53"/>
-      <c r="AQ1" s="53"/>
-      <c r="AR1" s="53"/>
-      <c r="AS1" s="53"/>
-      <c r="AT1" s="53"/>
-      <c r="AU1" s="53"/>
-      <c r="AV1" s="53"/>
-      <c r="AW1" s="53"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
+      <c r="U1" s="63"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="63"/>
+      <c r="Y1" s="63"/>
+      <c r="Z1" s="63"/>
+      <c r="AA1" s="63"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="63"/>
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
+      <c r="AH1" s="63"/>
+      <c r="AI1" s="63"/>
+      <c r="AJ1" s="63"/>
+      <c r="AK1" s="63"/>
+      <c r="AL1" s="63"/>
+      <c r="AM1" s="63"/>
+      <c r="AN1" s="63"/>
+      <c r="AO1" s="63"/>
+      <c r="AP1" s="63"/>
+      <c r="AQ1" s="63"/>
+      <c r="AR1" s="63"/>
+      <c r="AS1" s="63"/>
+      <c r="AT1" s="63"/>
+      <c r="AU1" s="63"/>
+      <c r="AV1" s="63"/>
+      <c r="AW1" s="63"/>
     </row>
     <row r="2" spans="1:77" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="54"/>
+      <c r="B2" s="61"/>
       <c r="C2" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="43">
+      <c r="D2" s="59">
         <v>46268</v>
       </c>
-      <c r="E2" s="43">
+      <c r="E2" s="59">
         <v>46272</v>
       </c>
-      <c r="F2" s="43">
+      <c r="F2" s="59">
         <v>46273</v>
       </c>
-      <c r="G2" s="43">
+      <c r="G2" s="59">
         <v>46275</v>
       </c>
-      <c r="H2" s="43">
+      <c r="H2" s="59">
         <v>46279</v>
       </c>
-      <c r="I2" s="51">
+      <c r="I2" s="45">
         <v>46282</v>
       </c>
-      <c r="J2" s="43">
+      <c r="J2" s="59">
         <v>46286</v>
       </c>
-      <c r="K2" s="43">
+      <c r="K2" s="59">
         <v>46287</v>
       </c>
-      <c r="L2" s="51">
+      <c r="L2" s="45">
         <v>46289</v>
       </c>
-      <c r="M2" s="43">
+      <c r="M2" s="59">
         <v>46293</v>
       </c>
-      <c r="N2" s="51">
+      <c r="N2" s="45">
         <v>46296</v>
       </c>
-      <c r="O2" s="43">
+      <c r="O2" s="59">
         <v>46300</v>
       </c>
-      <c r="P2" s="43">
+      <c r="P2" s="59">
         <v>46301</v>
       </c>
-      <c r="Q2" s="51">
+      <c r="Q2" s="45">
         <v>46303</v>
       </c>
-      <c r="R2" s="43">
+      <c r="R2" s="59">
         <v>46307</v>
       </c>
-      <c r="S2" s="51">
+      <c r="S2" s="45">
         <v>46310</v>
       </c>
-      <c r="T2" s="43">
+      <c r="T2" s="59">
         <v>46314</v>
       </c>
-      <c r="U2" s="43">
+      <c r="U2" s="59">
         <v>46315</v>
       </c>
-      <c r="V2" s="51">
+      <c r="V2" s="45">
         <v>46317</v>
       </c>
-      <c r="W2" s="43">
+      <c r="W2" s="59">
         <v>46321</v>
       </c>
-      <c r="X2" s="43">
+      <c r="X2" s="59">
         <v>46324</v>
       </c>
-      <c r="Y2" s="43">
+      <c r="Y2" s="59">
         <v>46328</v>
       </c>
-      <c r="Z2" s="43">
+      <c r="Z2" s="59">
         <v>46329</v>
       </c>
-      <c r="AA2" s="43">
+      <c r="AA2" s="59">
         <v>46331</v>
       </c>
-      <c r="AB2" s="43">
+      <c r="AB2" s="59">
         <v>46335</v>
       </c>
-      <c r="AC2" s="43">
+      <c r="AC2" s="59">
         <v>46338</v>
       </c>
-      <c r="AD2" s="43">
+      <c r="AD2" s="59">
         <v>46342</v>
       </c>
-      <c r="AE2" s="43">
+      <c r="AE2" s="59">
         <v>46343</v>
       </c>
-      <c r="AF2" s="43">
+      <c r="AF2" s="59">
         <v>46345</v>
       </c>
-      <c r="AG2" s="43">
+      <c r="AG2" s="59">
         <v>46349</v>
       </c>
-      <c r="AH2" s="43">
+      <c r="AH2" s="59">
         <v>46352</v>
       </c>
-      <c r="AI2" s="43">
+      <c r="AI2" s="59">
         <v>46356</v>
       </c>
-      <c r="AJ2" s="51">
+      <c r="AJ2" s="45">
         <v>46357</v>
       </c>
-      <c r="AK2" s="51">
+      <c r="AK2" s="45">
         <v>46359</v>
       </c>
-      <c r="AL2" s="51">
+      <c r="AL2" s="45">
         <v>46363</v>
       </c>
-      <c r="AM2" s="51">
+      <c r="AM2" s="45">
         <v>46366</v>
       </c>
-      <c r="AN2" s="51">
+      <c r="AN2" s="45">
         <v>46370</v>
       </c>
-      <c r="AO2" s="51">
+      <c r="AO2" s="45">
         <v>46371</v>
       </c>
-      <c r="AP2" s="51">
+      <c r="AP2" s="45">
         <v>46373</v>
       </c>
-      <c r="AQ2" s="51">
+      <c r="AQ2" s="45">
         <v>46377</v>
       </c>
-      <c r="AR2" s="51">
+      <c r="AR2" s="45">
         <v>46380</v>
       </c>
-      <c r="AS2" s="54" t="s">
+      <c r="AS2" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="AT2" s="54"/>
-      <c r="AU2" s="45" t="s">
+      <c r="AT2" s="61"/>
+      <c r="AU2" s="47" t="s">
         <v>120</v>
       </c>
-      <c r="AV2" s="46"/>
-      <c r="AW2" s="47"/>
-      <c r="AX2" s="45" t="s">
+      <c r="AV2" s="48"/>
+      <c r="AW2" s="49"/>
+      <c r="AX2" s="47" t="s">
         <v>161</v>
       </c>
-      <c r="AY2" s="46"/>
-      <c r="AZ2" s="47"/>
-      <c r="BA2" s="45" t="s">
+      <c r="AY2" s="48"/>
+      <c r="AZ2" s="49"/>
+      <c r="BA2" s="47" t="s">
         <v>162</v>
       </c>
-      <c r="BB2" s="46"/>
-      <c r="BC2" s="47"/>
-      <c r="BD2" s="45" t="s">
+      <c r="BB2" s="48"/>
+      <c r="BC2" s="49"/>
+      <c r="BD2" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="BE2" s="46"/>
-      <c r="BF2" s="47"/>
-      <c r="BG2" s="45" t="s">
+      <c r="BE2" s="48"/>
+      <c r="BF2" s="49"/>
+      <c r="BG2" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="BH2" s="46"/>
-      <c r="BI2" s="46"/>
-      <c r="BJ2" s="47"/>
-      <c r="BK2" s="45" t="s">
+      <c r="BH2" s="48"/>
+      <c r="BI2" s="48"/>
+      <c r="BJ2" s="49"/>
+      <c r="BK2" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="BL2" s="46"/>
-      <c r="BM2" s="46"/>
-      <c r="BN2" s="47" t="s">
+      <c r="BL2" s="48"/>
+      <c r="BM2" s="48"/>
+      <c r="BN2" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="BO2" s="45" t="s">
+      <c r="BO2" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="BP2" s="46"/>
-      <c r="BQ2" s="47"/>
-      <c r="BR2" s="45" t="s">
+      <c r="BP2" s="48"/>
+      <c r="BQ2" s="49"/>
+      <c r="BR2" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="BS2" s="46"/>
-      <c r="BT2" s="47"/>
+      <c r="BS2" s="48"/>
+      <c r="BT2" s="49"/>
     </row>
     <row r="3" spans="1:77" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1562,76 +1586,76 @@
       <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="44"/>
-      <c r="P3" s="44"/>
-      <c r="Q3" s="52"/>
-      <c r="R3" s="44"/>
-      <c r="S3" s="52"/>
-      <c r="T3" s="44"/>
-      <c r="U3" s="44"/>
-      <c r="V3" s="52"/>
-      <c r="W3" s="44"/>
-      <c r="X3" s="44"/>
-      <c r="Y3" s="44"/>
-      <c r="Z3" s="44"/>
-      <c r="AA3" s="44"/>
-      <c r="AB3" s="44"/>
-      <c r="AC3" s="44"/>
-      <c r="AD3" s="44"/>
-      <c r="AE3" s="44"/>
-      <c r="AF3" s="44"/>
-      <c r="AG3" s="44"/>
-      <c r="AH3" s="44"/>
-      <c r="AI3" s="44"/>
-      <c r="AJ3" s="52"/>
-      <c r="AK3" s="52"/>
-      <c r="AL3" s="52"/>
-      <c r="AM3" s="52"/>
-      <c r="AN3" s="52"/>
-      <c r="AO3" s="52"/>
-      <c r="AP3" s="52"/>
-      <c r="AQ3" s="52"/>
-      <c r="AR3" s="52"/>
-      <c r="AS3" s="54"/>
-      <c r="AT3" s="54"/>
-      <c r="AU3" s="48"/>
-      <c r="AV3" s="55"/>
-      <c r="AW3" s="50"/>
-      <c r="AX3" s="48"/>
-      <c r="AY3" s="49"/>
-      <c r="AZ3" s="50"/>
-      <c r="BA3" s="48"/>
-      <c r="BB3" s="49"/>
-      <c r="BC3" s="50"/>
-      <c r="BD3" s="48"/>
-      <c r="BE3" s="49"/>
-      <c r="BF3" s="50"/>
-      <c r="BG3" s="48"/>
-      <c r="BH3" s="49"/>
-      <c r="BI3" s="49"/>
-      <c r="BJ3" s="50"/>
-      <c r="BK3" s="48"/>
-      <c r="BL3" s="49"/>
-      <c r="BM3" s="49"/>
-      <c r="BN3" s="50"/>
-      <c r="BO3" s="48"/>
-      <c r="BP3" s="49"/>
-      <c r="BQ3" s="50"/>
-      <c r="BR3" s="48"/>
-      <c r="BS3" s="49"/>
-      <c r="BT3" s="50"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="60"/>
+      <c r="P3" s="60"/>
+      <c r="Q3" s="46"/>
+      <c r="R3" s="60"/>
+      <c r="S3" s="46"/>
+      <c r="T3" s="60"/>
+      <c r="U3" s="60"/>
+      <c r="V3" s="46"/>
+      <c r="W3" s="60"/>
+      <c r="X3" s="60"/>
+      <c r="Y3" s="60"/>
+      <c r="Z3" s="60"/>
+      <c r="AA3" s="60"/>
+      <c r="AB3" s="60"/>
+      <c r="AC3" s="60"/>
+      <c r="AD3" s="60"/>
+      <c r="AE3" s="60"/>
+      <c r="AF3" s="60"/>
+      <c r="AG3" s="60"/>
+      <c r="AH3" s="60"/>
+      <c r="AI3" s="60"/>
+      <c r="AJ3" s="46"/>
+      <c r="AK3" s="46"/>
+      <c r="AL3" s="46"/>
+      <c r="AM3" s="46"/>
+      <c r="AN3" s="46"/>
+      <c r="AO3" s="46"/>
+      <c r="AP3" s="46"/>
+      <c r="AQ3" s="46"/>
+      <c r="AR3" s="46"/>
+      <c r="AS3" s="61"/>
+      <c r="AT3" s="61"/>
+      <c r="AU3" s="50"/>
+      <c r="AV3" s="64"/>
+      <c r="AW3" s="52"/>
+      <c r="AX3" s="50"/>
+      <c r="AY3" s="51"/>
+      <c r="AZ3" s="52"/>
+      <c r="BA3" s="50"/>
+      <c r="BB3" s="51"/>
+      <c r="BC3" s="52"/>
+      <c r="BD3" s="50"/>
+      <c r="BE3" s="51"/>
+      <c r="BF3" s="52"/>
+      <c r="BG3" s="50"/>
+      <c r="BH3" s="51"/>
+      <c r="BI3" s="51"/>
+      <c r="BJ3" s="52"/>
+      <c r="BK3" s="50"/>
+      <c r="BL3" s="51"/>
+      <c r="BM3" s="51"/>
+      <c r="BN3" s="52"/>
+      <c r="BO3" s="50"/>
+      <c r="BP3" s="51"/>
+      <c r="BQ3" s="52"/>
+      <c r="BR3" s="50"/>
+      <c r="BS3" s="51"/>
+      <c r="BT3" s="52"/>
     </row>
     <row r="4" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
@@ -1679,7 +1703,9 @@
       <c r="Q4" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="R4" s="17"/>
+      <c r="R4" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="S4" s="17"/>
       <c r="T4" s="17"/>
       <c r="U4" s="17"/>
@@ -1709,7 +1735,9 @@
       <c r="AS4" s="18"/>
       <c r="AT4" s="17"/>
       <c r="AU4" s="19"/>
-      <c r="AV4" s="19"/>
+      <c r="AV4" s="41" t="s">
+        <v>177</v>
+      </c>
       <c r="AW4" s="18"/>
       <c r="AX4" s="33" t="s">
         <v>129</v>
@@ -1793,7 +1821,9 @@
       <c r="Q5" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="R5" s="17"/>
+      <c r="R5" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="S5" s="17"/>
       <c r="T5" s="17"/>
       <c r="U5" s="17"/>
@@ -1822,11 +1852,15 @@
       <c r="AR5" s="17"/>
       <c r="AS5" s="18"/>
       <c r="AT5" s="17"/>
-      <c r="AU5" s="19"/>
-      <c r="AV5" s="41" t="s">
+      <c r="AU5" s="65" t="s">
+        <v>181</v>
+      </c>
+      <c r="AV5" s="66" t="s">
         <v>177</v>
       </c>
-      <c r="AW5" s="21"/>
+      <c r="AW5" s="67">
+        <v>46307</v>
+      </c>
       <c r="AX5" s="33" t="s">
         <v>131</v>
       </c>
@@ -1924,7 +1958,9 @@
       <c r="Q6" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="R6" s="17"/>
+      <c r="R6" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="S6" s="17"/>
       <c r="T6" s="17"/>
       <c r="U6" s="17"/>
@@ -2044,7 +2080,9 @@
       <c r="Q7" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="R7" s="17"/>
+      <c r="R7" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="S7" s="17"/>
       <c r="T7" s="17"/>
       <c r="U7" s="17"/>
@@ -2164,7 +2202,9 @@
       <c r="Q8" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="R8" s="17"/>
+      <c r="R8" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="S8" s="17"/>
       <c r="T8" s="17"/>
       <c r="U8" s="17"/>
@@ -2282,7 +2322,9 @@
       <c r="Q9" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="R9" s="17"/>
+      <c r="R9" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="S9" s="17"/>
       <c r="T9" s="17"/>
       <c r="U9" s="17"/>
@@ -2312,7 +2354,9 @@
       <c r="AS9" s="18"/>
       <c r="AT9" s="17"/>
       <c r="AU9" s="19"/>
-      <c r="AV9" s="41"/>
+      <c r="AV9" s="41" t="s">
+        <v>177</v>
+      </c>
       <c r="AW9" s="21"/>
       <c r="AX9" s="27" t="s">
         <v>139</v>
@@ -2398,7 +2442,9 @@
       <c r="Q10" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="R10" s="17"/>
+      <c r="R10" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="S10" s="17"/>
       <c r="T10" s="17"/>
       <c r="U10" s="17"/>
@@ -2514,7 +2560,9 @@
       <c r="Q11" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="R11" s="17"/>
+      <c r="R11" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="S11" s="17"/>
       <c r="T11" s="17"/>
       <c r="U11" s="17"/>
@@ -2634,7 +2682,9 @@
       <c r="Q12" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="R12" s="17"/>
+      <c r="R12" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="S12" s="17"/>
       <c r="T12" s="17"/>
       <c r="U12" s="17"/>
@@ -2663,9 +2713,15 @@
       <c r="AR12" s="17"/>
       <c r="AS12" s="18"/>
       <c r="AT12" s="17"/>
-      <c r="AU12" s="19"/>
-      <c r="AV12" s="41"/>
-      <c r="AW12" s="21"/>
+      <c r="AU12" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="AV12" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="AW12" s="67">
+        <v>46307</v>
+      </c>
       <c r="AX12" s="20" t="s">
         <v>147</v>
       </c>
@@ -2748,7 +2804,9 @@
       <c r="Q13" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="R13" s="17"/>
+      <c r="R13" s="17" t="s">
+        <v>119</v>
+      </c>
       <c r="S13" s="17"/>
       <c r="T13" s="17"/>
       <c r="U13" s="17"/>
@@ -2857,10 +2915,12 @@
       <c r="P14" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="Q14" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="R14" s="17"/>
+      <c r="Q14" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="R14" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="S14" s="17"/>
       <c r="T14" s="17"/>
       <c r="U14" s="17"/>
@@ -2890,7 +2950,9 @@
       <c r="AS14" s="17"/>
       <c r="AT14" s="17"/>
       <c r="AU14" s="19"/>
-      <c r="AV14" s="41"/>
+      <c r="AV14" s="41" t="s">
+        <v>177</v>
+      </c>
       <c r="AW14" s="25"/>
       <c r="AX14" s="36" t="s">
         <v>151</v>
@@ -2972,7 +3034,9 @@
       <c r="Q15" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="R15" s="17"/>
+      <c r="R15" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="S15" s="17"/>
       <c r="T15" s="17"/>
       <c r="U15" s="17"/>
@@ -3086,7 +3150,9 @@
       <c r="Q16" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="R16" s="17"/>
+      <c r="R16" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="S16" s="17"/>
       <c r="T16" s="17"/>
       <c r="U16" s="17"/>
@@ -3116,7 +3182,9 @@
       <c r="AS16" s="18"/>
       <c r="AT16" s="17"/>
       <c r="AU16" s="18"/>
-      <c r="AV16" s="19"/>
+      <c r="AV16" s="41" t="s">
+        <v>177</v>
+      </c>
       <c r="AW16" s="25"/>
       <c r="AX16" s="33" t="s">
         <v>129</v>
@@ -3202,7 +3270,9 @@
       <c r="Q17" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="R17" s="17"/>
+      <c r="R17" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="S17" s="17"/>
       <c r="T17" s="17"/>
       <c r="U17" s="17"/>
@@ -3318,7 +3388,9 @@
       <c r="Q18" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="R18" s="17"/>
+      <c r="R18" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="S18" s="17"/>
       <c r="T18" s="17"/>
       <c r="U18" s="17"/>
@@ -3347,9 +3419,15 @@
       <c r="AR18" s="17"/>
       <c r="AS18" s="18"/>
       <c r="AT18" s="17"/>
-      <c r="AU18" s="19"/>
-      <c r="AV18" s="42"/>
-      <c r="AW18" s="21"/>
+      <c r="AU18" s="65" t="s">
+        <v>182</v>
+      </c>
+      <c r="AV18" s="66" t="s">
+        <v>177</v>
+      </c>
+      <c r="AW18" s="67">
+        <v>46307</v>
+      </c>
       <c r="AX18" s="35" t="s">
         <v>155</v>
       </c>
@@ -3430,7 +3508,9 @@
       <c r="Q19" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="R19" s="17"/>
+      <c r="R19" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="S19" s="17"/>
       <c r="T19" s="17"/>
       <c r="U19" s="17"/>
@@ -3544,7 +3624,9 @@
       <c r="Q20" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="R20" s="17"/>
+      <c r="R20" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="S20" s="17"/>
       <c r="T20" s="17"/>
       <c r="U20" s="17"/>
@@ -3574,7 +3656,9 @@
       <c r="AS20" s="18"/>
       <c r="AT20" s="17"/>
       <c r="AU20" s="19"/>
-      <c r="AV20" s="41"/>
+      <c r="AV20" s="41" t="s">
+        <v>177</v>
+      </c>
       <c r="AW20" s="21"/>
       <c r="AX20" s="27" t="s">
         <v>139</v>
@@ -3656,7 +3740,9 @@
       <c r="Q21" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="R21" s="17"/>
+      <c r="R21" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="S21" s="17"/>
       <c r="T21" s="17"/>
       <c r="U21" s="17"/>
@@ -3768,7 +3854,9 @@
       <c r="Q22" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="R22" s="17"/>
+      <c r="R22" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="S22" s="17"/>
       <c r="T22" s="17"/>
       <c r="U22" s="17"/>
@@ -3880,7 +3968,9 @@
       <c r="Q23" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="R23" s="23"/>
+      <c r="R23" s="23" t="s">
+        <v>118</v>
+      </c>
       <c r="S23" s="17"/>
       <c r="T23" s="17"/>
       <c r="U23" s="17"/>
@@ -3990,7 +4080,9 @@
       <c r="Q24" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="R24" s="17"/>
+      <c r="R24" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="S24" s="17"/>
       <c r="T24" s="17"/>
       <c r="U24" s="17"/>
@@ -4019,11 +4111,15 @@
       <c r="AR24" s="17"/>
       <c r="AS24" s="17"/>
       <c r="AT24" s="17"/>
-      <c r="AU24" s="19"/>
-      <c r="AV24" s="41" t="s">
+      <c r="AU24" s="65" t="s">
+        <v>180</v>
+      </c>
+      <c r="AV24" s="66" t="s">
         <v>177</v>
       </c>
-      <c r="AW24" s="25"/>
+      <c r="AW24" s="67">
+        <v>46307</v>
+      </c>
       <c r="AX24" s="26" t="s">
         <v>160</v>
       </c>
@@ -4108,7 +4204,9 @@
       <c r="Q25" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="R25" s="17"/>
+      <c r="R25" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="S25" s="17"/>
       <c r="T25" s="17"/>
       <c r="U25" s="17"/>
@@ -4218,7 +4316,9 @@
       <c r="Q26" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="R26" s="23"/>
+      <c r="R26" s="23" t="s">
+        <v>118</v>
+      </c>
       <c r="S26" s="29"/>
       <c r="T26" s="29"/>
       <c r="U26" s="29"/>
@@ -4333,7 +4433,9 @@
       <c r="Q27" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="R27" s="30"/>
+      <c r="R27" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="S27" s="30"/>
       <c r="T27" s="30"/>
       <c r="U27" s="30"/>
@@ -4362,11 +4464,15 @@
       <c r="AR27" s="30"/>
       <c r="AS27" s="18"/>
       <c r="AT27" s="30"/>
-      <c r="AU27" s="19"/>
-      <c r="AV27" s="41" t="s">
+      <c r="AU27" s="65" t="s">
+        <v>181</v>
+      </c>
+      <c r="AV27" s="66" t="s">
         <v>177</v>
       </c>
-      <c r="AW27" s="18"/>
+      <c r="AW27" s="67">
+        <v>46307</v>
+      </c>
       <c r="AX27" s="20" t="s">
         <v>131</v>
       </c>
@@ -4453,7 +4559,9 @@
       <c r="Q28" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="R28" s="30"/>
+      <c r="R28" s="30" t="s">
+        <v>119</v>
+      </c>
       <c r="S28" s="30"/>
       <c r="T28" s="30"/>
       <c r="U28" s="30"/>
@@ -4559,7 +4667,9 @@
       <c r="Q29" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="R29" s="30"/>
+      <c r="R29" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="S29" s="30"/>
       <c r="T29" s="30"/>
       <c r="U29" s="30"/>
@@ -4588,11 +4698,15 @@
       <c r="AR29" s="30"/>
       <c r="AS29" s="18"/>
       <c r="AT29" s="30"/>
-      <c r="AU29" s="19"/>
-      <c r="AV29" s="41" t="s">
+      <c r="AU29" s="65" t="s">
+        <v>180</v>
+      </c>
+      <c r="AV29" s="66" t="s">
         <v>177</v>
       </c>
-      <c r="AW29" s="32"/>
+      <c r="AW29" s="67">
+        <v>46307</v>
+      </c>
       <c r="AX29" s="26" t="s">
         <v>160</v>
       </c>
@@ -4665,7 +4779,9 @@
       <c r="Q30" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="R30" s="30"/>
+      <c r="R30" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="S30" s="30"/>
       <c r="T30" s="30"/>
       <c r="U30" s="30"/>
@@ -4694,9 +4810,15 @@
       <c r="AR30" s="30"/>
       <c r="AS30" s="18"/>
       <c r="AT30" s="30"/>
-      <c r="AU30" s="19"/>
-      <c r="AV30" s="42"/>
-      <c r="AW30" s="32"/>
+      <c r="AU30" s="65" t="s">
+        <v>182</v>
+      </c>
+      <c r="AV30" s="66" t="s">
+        <v>177</v>
+      </c>
+      <c r="AW30" s="67">
+        <v>46307</v>
+      </c>
       <c r="AX30" s="35" t="s">
         <v>155</v>
       </c>
@@ -4768,10 +4890,12 @@
       <c r="P31" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="Q31" s="63" t="s">
-        <v>118</v>
-      </c>
-      <c r="R31" s="30"/>
+      <c r="Q31" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="R31" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="S31" s="30"/>
       <c r="T31" s="30"/>
       <c r="U31" s="30"/>
@@ -4879,7 +5003,9 @@
       <c r="Q32" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="R32" s="30"/>
+      <c r="R32" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="S32" s="30"/>
       <c r="T32" s="30"/>
       <c r="U32" s="30"/>
@@ -4988,10 +5114,12 @@
       <c r="P33" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="Q33" s="63" t="s">
-        <v>118</v>
-      </c>
-      <c r="R33" s="30"/>
+      <c r="Q33" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="R33" s="30" t="s">
+        <v>119</v>
+      </c>
       <c r="S33" s="30"/>
       <c r="T33" s="30"/>
       <c r="U33" s="30"/>
@@ -5095,7 +5223,9 @@
       <c r="Q34" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="R34" s="30"/>
+      <c r="R34" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="S34" s="30"/>
       <c r="T34" s="30"/>
       <c r="U34" s="30"/>
@@ -5124,9 +5254,15 @@
       <c r="AR34" s="30"/>
       <c r="AS34" s="18"/>
       <c r="AT34" s="30"/>
-      <c r="AU34" s="19"/>
-      <c r="AV34" s="19"/>
-      <c r="AW34" s="32"/>
+      <c r="AU34" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="AV34" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="AW34" s="67">
+        <v>46307</v>
+      </c>
       <c r="AX34" s="20" t="s">
         <v>147</v>
       </c>
@@ -5201,7 +5337,9 @@
       <c r="Q35" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="R35" s="30"/>
+      <c r="R35" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="S35" s="30"/>
       <c r="T35" s="30"/>
       <c r="U35" s="30"/>
@@ -5231,7 +5369,9 @@
       <c r="AS35" s="18"/>
       <c r="AT35" s="30"/>
       <c r="AU35" s="19"/>
-      <c r="AV35" s="41"/>
+      <c r="AV35" s="41" t="s">
+        <v>177</v>
+      </c>
       <c r="AW35" s="32"/>
       <c r="AX35" s="36" t="s">
         <v>151</v>
@@ -5307,7 +5447,9 @@
       <c r="Q36" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="R36" s="30"/>
+      <c r="R36" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="S36" s="17"/>
       <c r="T36" s="30"/>
       <c r="U36" s="30"/>
@@ -5413,7 +5555,9 @@
       <c r="Q37" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="R37" s="30"/>
+      <c r="R37" s="30" t="s">
+        <v>119</v>
+      </c>
       <c r="S37" s="17"/>
       <c r="T37" s="30"/>
       <c r="U37" s="30"/>
@@ -5474,57 +5618,57 @@
       <c r="BT37" s="30"/>
     </row>
     <row r="38" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A38" s="56" t="s">
+      <c r="A38" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="B38" s="57"/>
-      <c r="C38" s="57"/>
-      <c r="D38" s="57"/>
-      <c r="E38" s="57"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="57"/>
-      <c r="H38" s="57"/>
-      <c r="I38" s="57"/>
-      <c r="J38" s="57"/>
-      <c r="K38" s="57"/>
-      <c r="L38" s="57"/>
-      <c r="M38" s="57"/>
-      <c r="N38" s="57"/>
-      <c r="O38" s="57"/>
-      <c r="P38" s="57"/>
-      <c r="Q38" s="57"/>
-      <c r="R38" s="57"/>
-      <c r="S38" s="57"/>
-      <c r="T38" s="57"/>
-      <c r="U38" s="57"/>
-      <c r="V38" s="57"/>
-      <c r="W38" s="57"/>
-      <c r="X38" s="57"/>
-      <c r="Y38" s="57"/>
-      <c r="Z38" s="57"/>
-      <c r="AA38" s="57"/>
-      <c r="AB38" s="57"/>
-      <c r="AC38" s="57"/>
-      <c r="AD38" s="57"/>
-      <c r="AE38" s="57"/>
-      <c r="AF38" s="57"/>
-      <c r="AG38" s="57"/>
-      <c r="AH38" s="57"/>
-      <c r="AI38" s="57"/>
-      <c r="AJ38" s="57"/>
-      <c r="AK38" s="57"/>
-      <c r="AL38" s="57"/>
-      <c r="AM38" s="57"/>
-      <c r="AN38" s="57"/>
-      <c r="AO38" s="57"/>
-      <c r="AP38" s="57"/>
-      <c r="AQ38" s="57"/>
-      <c r="AR38" s="57"/>
-      <c r="AS38" s="57"/>
-      <c r="AT38" s="57"/>
-      <c r="AU38" s="57"/>
-      <c r="AV38" s="57"/>
-      <c r="AW38" s="58"/>
+      <c r="B38" s="54"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="54"/>
+      <c r="I38" s="54"/>
+      <c r="J38" s="54"/>
+      <c r="K38" s="54"/>
+      <c r="L38" s="54"/>
+      <c r="M38" s="54"/>
+      <c r="N38" s="54"/>
+      <c r="O38" s="54"/>
+      <c r="P38" s="54"/>
+      <c r="Q38" s="54"/>
+      <c r="R38" s="54"/>
+      <c r="S38" s="54"/>
+      <c r="T38" s="54"/>
+      <c r="U38" s="54"/>
+      <c r="V38" s="54"/>
+      <c r="W38" s="54"/>
+      <c r="X38" s="54"/>
+      <c r="Y38" s="54"/>
+      <c r="Z38" s="54"/>
+      <c r="AA38" s="54"/>
+      <c r="AB38" s="54"/>
+      <c r="AC38" s="54"/>
+      <c r="AD38" s="54"/>
+      <c r="AE38" s="54"/>
+      <c r="AF38" s="54"/>
+      <c r="AG38" s="54"/>
+      <c r="AH38" s="54"/>
+      <c r="AI38" s="54"/>
+      <c r="AJ38" s="54"/>
+      <c r="AK38" s="54"/>
+      <c r="AL38" s="54"/>
+      <c r="AM38" s="54"/>
+      <c r="AN38" s="54"/>
+      <c r="AO38" s="54"/>
+      <c r="AP38" s="54"/>
+      <c r="AQ38" s="54"/>
+      <c r="AR38" s="54"/>
+      <c r="AS38" s="54"/>
+      <c r="AT38" s="54"/>
+      <c r="AU38" s="54"/>
+      <c r="AV38" s="54"/>
+      <c r="AW38" s="55"/>
       <c r="AX38" s="2"/>
       <c r="AY38" s="2"/>
       <c r="AZ38" s="2"/>
@@ -5556,57 +5700,57 @@
       </c>
     </row>
     <row r="39" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A39" s="59" t="s">
+      <c r="A39" s="56" t="s">
         <v>85</v>
       </c>
-      <c r="B39" s="60"/>
-      <c r="C39" s="60"/>
-      <c r="D39" s="60"/>
-      <c r="E39" s="60"/>
-      <c r="F39" s="60"/>
-      <c r="G39" s="60"/>
-      <c r="H39" s="60"/>
-      <c r="I39" s="60"/>
-      <c r="J39" s="60"/>
-      <c r="K39" s="60"/>
-      <c r="L39" s="60"/>
-      <c r="M39" s="60"/>
-      <c r="N39" s="60"/>
-      <c r="O39" s="60"/>
-      <c r="P39" s="60"/>
-      <c r="Q39" s="60"/>
-      <c r="R39" s="60"/>
-      <c r="S39" s="60"/>
-      <c r="T39" s="60"/>
-      <c r="U39" s="60"/>
-      <c r="V39" s="60"/>
-      <c r="W39" s="60"/>
-      <c r="X39" s="60"/>
-      <c r="Y39" s="60"/>
-      <c r="Z39" s="60"/>
-      <c r="AA39" s="60"/>
-      <c r="AB39" s="60"/>
-      <c r="AC39" s="60"/>
-      <c r="AD39" s="60"/>
-      <c r="AE39" s="60"/>
-      <c r="AF39" s="60"/>
-      <c r="AG39" s="60"/>
-      <c r="AH39" s="60"/>
-      <c r="AI39" s="60"/>
-      <c r="AJ39" s="60"/>
-      <c r="AK39" s="60"/>
-      <c r="AL39" s="60"/>
-      <c r="AM39" s="60"/>
-      <c r="AN39" s="60"/>
-      <c r="AO39" s="60"/>
-      <c r="AP39" s="60"/>
-      <c r="AQ39" s="60"/>
-      <c r="AR39" s="60"/>
-      <c r="AS39" s="60"/>
-      <c r="AT39" s="60"/>
-      <c r="AU39" s="60"/>
-      <c r="AV39" s="60"/>
-      <c r="AW39" s="61"/>
+      <c r="B39" s="57"/>
+      <c r="C39" s="57"/>
+      <c r="D39" s="57"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="57"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="57"/>
+      <c r="L39" s="57"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="57"/>
+      <c r="O39" s="57"/>
+      <c r="P39" s="57"/>
+      <c r="Q39" s="57"/>
+      <c r="R39" s="57"/>
+      <c r="S39" s="57"/>
+      <c r="T39" s="57"/>
+      <c r="U39" s="57"/>
+      <c r="V39" s="57"/>
+      <c r="W39" s="57"/>
+      <c r="X39" s="57"/>
+      <c r="Y39" s="57"/>
+      <c r="Z39" s="57"/>
+      <c r="AA39" s="57"/>
+      <c r="AB39" s="57"/>
+      <c r="AC39" s="57"/>
+      <c r="AD39" s="57"/>
+      <c r="AE39" s="57"/>
+      <c r="AF39" s="57"/>
+      <c r="AG39" s="57"/>
+      <c r="AH39" s="57"/>
+      <c r="AI39" s="57"/>
+      <c r="AJ39" s="57"/>
+      <c r="AK39" s="57"/>
+      <c r="AL39" s="57"/>
+      <c r="AM39" s="57"/>
+      <c r="AN39" s="57"/>
+      <c r="AO39" s="57"/>
+      <c r="AP39" s="57"/>
+      <c r="AQ39" s="57"/>
+      <c r="AR39" s="57"/>
+      <c r="AS39" s="57"/>
+      <c r="AT39" s="57"/>
+      <c r="AU39" s="57"/>
+      <c r="AV39" s="57"/>
+      <c r="AW39" s="58"/>
       <c r="AX39" s="2"/>
       <c r="AY39" s="2"/>
       <c r="AZ39" s="2"/>
@@ -6199,6 +6343,46 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AJ2:AJ3"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="AQ2:AQ3"/>
+    <mergeCell ref="BD2:BF3"/>
+    <mergeCell ref="AX2:AZ3"/>
+    <mergeCell ref="BA2:BC3"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="AH2:AH3"/>
+    <mergeCell ref="AI2:AI3"/>
+    <mergeCell ref="AK2:AK3"/>
+    <mergeCell ref="AL2:AL3"/>
+    <mergeCell ref="AM2:AM3"/>
+    <mergeCell ref="AN2:AN3"/>
+    <mergeCell ref="AP2:AP3"/>
+    <mergeCell ref="BO2:BQ3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="A1:AW1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="AU2:AW3"/>
+    <mergeCell ref="X2:X3"/>
     <mergeCell ref="AO2:AO3"/>
     <mergeCell ref="AR2:AR3"/>
     <mergeCell ref="BR2:BT3"/>
@@ -6215,46 +6399,6 @@
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="BG2:BJ3"/>
     <mergeCell ref="BK2:BN3"/>
-    <mergeCell ref="BO2:BQ3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="A1:AW1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="AU2:AW3"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="AQ2:AQ3"/>
-    <mergeCell ref="BD2:BF3"/>
-    <mergeCell ref="AX2:AZ3"/>
-    <mergeCell ref="BA2:BC3"/>
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="AH2:AH3"/>
-    <mergeCell ref="AI2:AI3"/>
-    <mergeCell ref="AK2:AK3"/>
-    <mergeCell ref="AL2:AL3"/>
-    <mergeCell ref="AM2:AM3"/>
-    <mergeCell ref="AN2:AN3"/>
-    <mergeCell ref="AP2:AP3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AJ2:AJ3"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="Y2:Y3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="BW6" r:id="rId1" display="Прикладная дискретная математика. Приложение. 2016. № 9. С. 68-70." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -6268,17 +6412,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b78dbef7-f85b-47b5-8738-6377d50f4027" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bffb7b91-0466-4de0-9379-f5c53c3acedf">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Документ" ma:contentTypeID="0x0101004F6380A0290AF84484F859C9FFD97568" ma:contentTypeVersion="12" ma:contentTypeDescription="Создание документа." ma:contentTypeScope="" ma:versionID="1ee9877c88efff51dfb0d3a4b3e8ad1b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bffb7b91-0466-4de0-9379-f5c53c3acedf" xmlns:ns3="b78dbef7-f85b-47b5-8738-6377d50f4027" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="532d4df54980d57387e1b5dc96a6a32c" ns2:_="" ns3:_="">
     <xsd:import namespace="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
@@ -6479,6 +6612,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b78dbef7-f85b-47b5-8738-6377d50f4027" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bffb7b91-0466-4de0-9379-f5c53c3acedf">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -6489,17 +6633,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12ECB55F-B88E-4FE2-9AD5-5CA5D433F306}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b78dbef7-f85b-47b5-8738-6377d50f4027"/>
-    <ds:schemaRef ds:uri="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B6A6DF3-AE59-43BA-A5FF-CF9B7C54D4B8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6518,6 +6651,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12ECB55F-B88E-4FE2-9AD5-5CA5D433F306}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b78dbef7-f85b-47b5-8738-6377d50f4027"/>
+    <ds:schemaRef ds:uri="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00280879-8A9A-4335-93BC-405126DC8F0C}">
   <ds:schemaRefs>

--- a/Ведомость ТКИ-441 2026-2027.xlsx
+++ b/Ведомость ТКИ-441 2026-2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\StegMethods\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B96CFC-8D45-4FE8-9F76-16CBB51F492E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F33564-50E6-4403-9A9D-FB8BBECB1388}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="188">
   <si>
     <t>Ведомость посещаемости занятий студентами группы ТКИ РУТ МИИТ</t>
   </si>
@@ -40,9 +40,6 @@
   </si>
   <si>
     <t>Творческое задание</t>
-  </si>
-  <si>
-    <t>БПФ, курсовая</t>
   </si>
   <si>
     <t>Равномерное распределение</t>
@@ -578,6 +575,21 @@
   </si>
   <si>
     <t>Генератор Дженнингса</t>
+  </si>
+  <si>
+    <t>1,2 лаба</t>
+  </si>
+  <si>
+    <t>Бабочка ПЧ2</t>
+  </si>
+  <si>
+    <t>Алгоритм</t>
+  </si>
+  <si>
+    <t>ПВ4</t>
+  </si>
+  <si>
+    <t>ОВ2</t>
   </si>
 </sst>
 </file>
@@ -850,7 +862,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -931,7 +943,17 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -944,6 +966,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -962,25 +991,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1005,16 +1016,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>62</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
+      <xdr:col>64</xdr:col>
+      <xdr:colOff>525236</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>98219</xdr:rowOff>
+      <xdr:rowOff>139041</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>69</xdr:col>
-      <xdr:colOff>406854</xdr:colOff>
+      <xdr:col>71</xdr:col>
+      <xdr:colOff>570140</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>119248</xdr:rowOff>
+      <xdr:rowOff>160070</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1037,7 +1048,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="44122521" y="3799362"/>
+          <a:off x="48504022" y="3840184"/>
           <a:ext cx="4644118" cy="4865172"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1347,366 +1358,368 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:77" x14ac:dyDescent="0.25">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="63"/>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="63"/>
-      <c r="R1" s="63"/>
-      <c r="S1" s="63"/>
-      <c r="T1" s="63"/>
-      <c r="U1" s="63"/>
-      <c r="V1" s="63"/>
-      <c r="W1" s="63"/>
-      <c r="X1" s="63"/>
-      <c r="Y1" s="63"/>
-      <c r="Z1" s="63"/>
-      <c r="AA1" s="63"/>
-      <c r="AB1" s="63"/>
-      <c r="AC1" s="63"/>
-      <c r="AD1" s="63"/>
-      <c r="AE1" s="63"/>
-      <c r="AF1" s="63"/>
-      <c r="AG1" s="63"/>
-      <c r="AH1" s="63"/>
-      <c r="AI1" s="63"/>
-      <c r="AJ1" s="63"/>
-      <c r="AK1" s="63"/>
-      <c r="AL1" s="63"/>
-      <c r="AM1" s="63"/>
-      <c r="AN1" s="63"/>
-      <c r="AO1" s="63"/>
-      <c r="AP1" s="63"/>
-      <c r="AQ1" s="63"/>
-      <c r="AR1" s="63"/>
-      <c r="AS1" s="63"/>
-      <c r="AT1" s="63"/>
-      <c r="AU1" s="63"/>
-      <c r="AV1" s="63"/>
-      <c r="AW1" s="63"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="57"/>
+      <c r="P1" s="57"/>
+      <c r="Q1" s="57"/>
+      <c r="R1" s="57"/>
+      <c r="S1" s="57"/>
+      <c r="T1" s="57"/>
+      <c r="U1" s="57"/>
+      <c r="V1" s="57"/>
+      <c r="W1" s="57"/>
+      <c r="X1" s="57"/>
+      <c r="Y1" s="57"/>
+      <c r="Z1" s="57"/>
+      <c r="AA1" s="57"/>
+      <c r="AB1" s="57"/>
+      <c r="AC1" s="57"/>
+      <c r="AD1" s="57"/>
+      <c r="AE1" s="57"/>
+      <c r="AF1" s="57"/>
+      <c r="AG1" s="57"/>
+      <c r="AH1" s="57"/>
+      <c r="AI1" s="57"/>
+      <c r="AJ1" s="57"/>
+      <c r="AK1" s="57"/>
+      <c r="AL1" s="57"/>
+      <c r="AM1" s="57"/>
+      <c r="AN1" s="57"/>
+      <c r="AO1" s="57"/>
+      <c r="AP1" s="57"/>
+      <c r="AQ1" s="57"/>
+      <c r="AR1" s="57"/>
+      <c r="AS1" s="57"/>
+      <c r="AT1" s="57"/>
+      <c r="AU1" s="57"/>
+      <c r="AV1" s="57"/>
+      <c r="AW1" s="57"/>
     </row>
     <row r="2" spans="1:77" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="62" t="s">
+      <c r="B2" s="58"/>
+      <c r="C2" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="59">
+      <c r="D2" s="47">
         <v>46268</v>
       </c>
-      <c r="E2" s="59">
+      <c r="E2" s="47">
         <v>46272</v>
       </c>
-      <c r="F2" s="59">
+      <c r="F2" s="47">
         <v>46273</v>
       </c>
-      <c r="G2" s="59">
+      <c r="G2" s="47">
         <v>46275</v>
       </c>
-      <c r="H2" s="59">
+      <c r="H2" s="47">
         <v>46279</v>
       </c>
-      <c r="I2" s="45">
+      <c r="I2" s="49">
         <v>46282</v>
       </c>
-      <c r="J2" s="59">
+      <c r="J2" s="47">
         <v>46286</v>
       </c>
-      <c r="K2" s="59">
+      <c r="K2" s="47">
         <v>46287</v>
       </c>
-      <c r="L2" s="45">
+      <c r="L2" s="49">
         <v>46289</v>
       </c>
-      <c r="M2" s="59">
+      <c r="M2" s="47">
         <v>46293</v>
       </c>
-      <c r="N2" s="45">
+      <c r="N2" s="49">
         <v>46296</v>
       </c>
-      <c r="O2" s="59">
+      <c r="O2" s="47">
         <v>46300</v>
       </c>
-      <c r="P2" s="59">
+      <c r="P2" s="47">
         <v>46301</v>
       </c>
-      <c r="Q2" s="45">
+      <c r="Q2" s="49">
         <v>46303</v>
       </c>
-      <c r="R2" s="59">
+      <c r="R2" s="47">
         <v>46307</v>
       </c>
-      <c r="S2" s="45">
+      <c r="S2" s="49">
         <v>46310</v>
       </c>
-      <c r="T2" s="59">
+      <c r="T2" s="47">
         <v>46314</v>
       </c>
-      <c r="U2" s="59">
+      <c r="U2" s="47">
         <v>46315</v>
       </c>
-      <c r="V2" s="45">
+      <c r="V2" s="49">
         <v>46317</v>
       </c>
-      <c r="W2" s="59">
+      <c r="W2" s="47">
         <v>46321</v>
       </c>
-      <c r="X2" s="59">
+      <c r="X2" s="47">
         <v>46324</v>
       </c>
-      <c r="Y2" s="59">
+      <c r="Y2" s="47">
         <v>46328</v>
       </c>
-      <c r="Z2" s="59">
+      <c r="Z2" s="47">
         <v>46329</v>
       </c>
-      <c r="AA2" s="59">
+      <c r="AA2" s="47">
         <v>46331</v>
       </c>
-      <c r="AB2" s="59">
+      <c r="AB2" s="47">
         <v>46335</v>
       </c>
-      <c r="AC2" s="59">
+      <c r="AC2" s="47">
         <v>46338</v>
       </c>
-      <c r="AD2" s="59">
+      <c r="AD2" s="47">
         <v>46342</v>
       </c>
-      <c r="AE2" s="59">
+      <c r="AE2" s="47">
         <v>46343</v>
       </c>
-      <c r="AF2" s="59">
+      <c r="AF2" s="47">
         <v>46345</v>
       </c>
-      <c r="AG2" s="59">
+      <c r="AG2" s="47">
         <v>46349</v>
       </c>
-      <c r="AH2" s="59">
+      <c r="AH2" s="47">
         <v>46352</v>
       </c>
-      <c r="AI2" s="59">
+      <c r="AI2" s="47">
         <v>46356</v>
       </c>
-      <c r="AJ2" s="45">
+      <c r="AJ2" s="49">
         <v>46357</v>
       </c>
-      <c r="AK2" s="45">
+      <c r="AK2" s="49">
         <v>46359</v>
       </c>
-      <c r="AL2" s="45">
+      <c r="AL2" s="49">
         <v>46363</v>
       </c>
-      <c r="AM2" s="45">
+      <c r="AM2" s="49">
         <v>46366</v>
       </c>
-      <c r="AN2" s="45">
+      <c r="AN2" s="49">
         <v>46370</v>
       </c>
-      <c r="AO2" s="45">
+      <c r="AO2" s="49">
         <v>46371</v>
       </c>
-      <c r="AP2" s="45">
+      <c r="AP2" s="49">
         <v>46373</v>
       </c>
-      <c r="AQ2" s="45">
+      <c r="AQ2" s="49">
         <v>46377</v>
       </c>
-      <c r="AR2" s="45">
+      <c r="AR2" s="49">
         <v>46380</v>
       </c>
-      <c r="AS2" s="61" t="s">
+      <c r="AS2" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="AT2" s="61"/>
-      <c r="AU2" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="AV2" s="48"/>
-      <c r="AW2" s="49"/>
-      <c r="AX2" s="47" t="s">
+      <c r="AT2" s="58"/>
+      <c r="AU2" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="AV2" s="52"/>
+      <c r="AW2" s="53"/>
+      <c r="AX2" s="51" t="s">
+        <v>160</v>
+      </c>
+      <c r="AY2" s="52"/>
+      <c r="AZ2" s="53"/>
+      <c r="BA2" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="AY2" s="48"/>
-      <c r="AZ2" s="49"/>
-      <c r="BA2" s="47" t="s">
-        <v>162</v>
-      </c>
-      <c r="BB2" s="48"/>
-      <c r="BC2" s="49"/>
-      <c r="BD2" s="47" t="s">
+      <c r="BB2" s="52"/>
+      <c r="BC2" s="53"/>
+      <c r="BD2" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="BE2" s="48"/>
-      <c r="BF2" s="49"/>
-      <c r="BG2" s="47" t="s">
+      <c r="BE2" s="52"/>
+      <c r="BF2" s="53"/>
+      <c r="BG2" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH2" s="52"/>
+      <c r="BI2" s="52"/>
+      <c r="BJ2" s="53"/>
+      <c r="BK2" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="BH2" s="48"/>
-      <c r="BI2" s="48"/>
-      <c r="BJ2" s="49"/>
-      <c r="BK2" s="47" t="s">
+      <c r="BL2" s="52"/>
+      <c r="BM2" s="52"/>
+      <c r="BN2" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="BL2" s="48"/>
-      <c r="BM2" s="48"/>
-      <c r="BN2" s="49" t="s">
+      <c r="BO2" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="BO2" s="47" t="s">
+      <c r="BP2" s="52"/>
+      <c r="BQ2" s="53"/>
+      <c r="BR2" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="BP2" s="48"/>
-      <c r="BQ2" s="49"/>
-      <c r="BR2" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="BS2" s="48"/>
-      <c r="BT2" s="49"/>
+      <c r="BS2" s="52"/>
+      <c r="BT2" s="53"/>
     </row>
     <row r="3" spans="1:77" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="46"/>
-      <c r="O3" s="60"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="46"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="46"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="46"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="60"/>
-      <c r="Y3" s="60"/>
-      <c r="Z3" s="60"/>
-      <c r="AA3" s="60"/>
-      <c r="AB3" s="60"/>
-      <c r="AC3" s="60"/>
-      <c r="AD3" s="60"/>
-      <c r="AE3" s="60"/>
-      <c r="AF3" s="60"/>
-      <c r="AG3" s="60"/>
-      <c r="AH3" s="60"/>
-      <c r="AI3" s="60"/>
-      <c r="AJ3" s="46"/>
-      <c r="AK3" s="46"/>
-      <c r="AL3" s="46"/>
-      <c r="AM3" s="46"/>
-      <c r="AN3" s="46"/>
-      <c r="AO3" s="46"/>
-      <c r="AP3" s="46"/>
-      <c r="AQ3" s="46"/>
-      <c r="AR3" s="46"/>
-      <c r="AS3" s="61"/>
-      <c r="AT3" s="61"/>
-      <c r="AU3" s="50"/>
-      <c r="AV3" s="64"/>
-      <c r="AW3" s="52"/>
-      <c r="AX3" s="50"/>
-      <c r="AY3" s="51"/>
-      <c r="AZ3" s="52"/>
-      <c r="BA3" s="50"/>
-      <c r="BB3" s="51"/>
-      <c r="BC3" s="52"/>
-      <c r="BD3" s="50"/>
-      <c r="BE3" s="51"/>
-      <c r="BF3" s="52"/>
-      <c r="BG3" s="50"/>
-      <c r="BH3" s="51"/>
-      <c r="BI3" s="51"/>
-      <c r="BJ3" s="52"/>
-      <c r="BK3" s="50"/>
-      <c r="BL3" s="51"/>
-      <c r="BM3" s="51"/>
-      <c r="BN3" s="52"/>
-      <c r="BO3" s="50"/>
-      <c r="BP3" s="51"/>
-      <c r="BQ3" s="52"/>
-      <c r="BR3" s="50"/>
-      <c r="BS3" s="51"/>
-      <c r="BT3" s="52"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="50"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="50"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="50"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="50"/>
+      <c r="W3" s="48"/>
+      <c r="X3" s="48"/>
+      <c r="Y3" s="48"/>
+      <c r="Z3" s="48"/>
+      <c r="AA3" s="48"/>
+      <c r="AB3" s="48"/>
+      <c r="AC3" s="48"/>
+      <c r="AD3" s="48"/>
+      <c r="AE3" s="48"/>
+      <c r="AF3" s="48"/>
+      <c r="AG3" s="48"/>
+      <c r="AH3" s="48"/>
+      <c r="AI3" s="48"/>
+      <c r="AJ3" s="50"/>
+      <c r="AK3" s="50"/>
+      <c r="AL3" s="50"/>
+      <c r="AM3" s="50"/>
+      <c r="AN3" s="50"/>
+      <c r="AO3" s="50"/>
+      <c r="AP3" s="50"/>
+      <c r="AQ3" s="50"/>
+      <c r="AR3" s="50"/>
+      <c r="AS3" s="58"/>
+      <c r="AT3" s="58"/>
+      <c r="AU3" s="54"/>
+      <c r="AV3" s="59"/>
+      <c r="AW3" s="56"/>
+      <c r="AX3" s="54"/>
+      <c r="AY3" s="55"/>
+      <c r="AZ3" s="56"/>
+      <c r="BA3" s="54"/>
+      <c r="BB3" s="55"/>
+      <c r="BC3" s="56"/>
+      <c r="BD3" s="54"/>
+      <c r="BE3" s="55"/>
+      <c r="BF3" s="56"/>
+      <c r="BG3" s="54"/>
+      <c r="BH3" s="55"/>
+      <c r="BI3" s="55"/>
+      <c r="BJ3" s="56"/>
+      <c r="BK3" s="54"/>
+      <c r="BL3" s="55"/>
+      <c r="BM3" s="55"/>
+      <c r="BN3" s="56"/>
+      <c r="BO3" s="54"/>
+      <c r="BP3" s="55"/>
+      <c r="BQ3" s="56"/>
+      <c r="BR3" s="54"/>
+      <c r="BS3" s="55"/>
+      <c r="BT3" s="56"/>
     </row>
     <row r="4" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C4" s="4">
         <v>1</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F4" s="17"/>
       <c r="G4" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I4" s="17"/>
       <c r="J4" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K4" s="17"/>
       <c r="L4" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M4" s="39" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N4" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O4" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P4" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q4" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="S4" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="S4" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="T4" s="17"/>
       <c r="U4" s="17"/>
       <c r="V4" s="17"/>
@@ -1736,28 +1749,28 @@
       <c r="AT4" s="17"/>
       <c r="AU4" s="19"/>
       <c r="AV4" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AW4" s="18"/>
       <c r="AX4" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="AY4" s="34" t="s">
         <v>129</v>
-      </c>
-      <c r="AY4" s="34" t="s">
-        <v>130</v>
       </c>
       <c r="AZ4" s="21"/>
       <c r="BA4" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="BB4" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="BC4" s="18"/>
       <c r="BD4" s="34" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="BE4" s="34" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="BF4" s="34"/>
       <c r="BG4" s="17"/>
@@ -1780,51 +1793,53 @@
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C5" s="4">
         <v>2</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F5" s="17"/>
       <c r="G5" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I5" s="17"/>
       <c r="J5" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K5" s="17"/>
       <c r="L5" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M5" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N5" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O5" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q5" s="38" t="s">
-        <v>118</v>
+        <v>117</v>
+      </c>
+      <c r="Q5" s="17" t="s">
+        <v>117</v>
       </c>
       <c r="R5" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="S5" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="S5" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="T5" s="17"/>
       <c r="U5" s="17"/>
       <c r="V5" s="17"/>
@@ -1852,38 +1867,42 @@
       <c r="AR5" s="17"/>
       <c r="AS5" s="18"/>
       <c r="AT5" s="17"/>
-      <c r="AU5" s="65" t="s">
-        <v>181</v>
-      </c>
-      <c r="AV5" s="66" t="s">
-        <v>177</v>
-      </c>
-      <c r="AW5" s="67">
+      <c r="AU5" s="44" t="s">
+        <v>180</v>
+      </c>
+      <c r="AV5" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="AW5" s="46">
         <v>46307</v>
       </c>
       <c r="AX5" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="AY5" s="34" t="s">
         <v>131</v>
-      </c>
-      <c r="AY5" s="34" t="s">
-        <v>132</v>
       </c>
       <c r="AZ5" s="21"/>
       <c r="BA5" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="BB5" s="21" t="s">
         <v>79</v>
-      </c>
-      <c r="BB5" s="21" t="s">
-        <v>80</v>
       </c>
       <c r="BC5" s="18"/>
       <c r="BD5" s="34" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="BE5" s="34" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="BF5" s="34"/>
-      <c r="BG5" s="17"/>
-      <c r="BH5" s="17"/>
+      <c r="BG5" s="18">
+        <v>46310</v>
+      </c>
+      <c r="BH5" s="17" t="s">
+        <v>185</v>
+      </c>
       <c r="BI5" s="17"/>
       <c r="BJ5" s="18"/>
       <c r="BK5" s="17"/>
@@ -1900,16 +1919,16 @@
         <v>1</v>
       </c>
       <c r="BV5" t="s">
+        <v>16</v>
+      </c>
+      <c r="BW5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="BW5" s="7" t="s">
+      <c r="BX5" t="s">
         <v>18</v>
       </c>
-      <c r="BX5" t="s">
+      <c r="BY5" t="s">
         <v>19</v>
-      </c>
-      <c r="BY5" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:77" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1917,51 +1936,53 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C6" s="4">
         <v>3</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F6" s="17"/>
       <c r="G6" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I6" s="17"/>
       <c r="J6" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K6" s="17"/>
       <c r="L6" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M6" s="40" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N6" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O6" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q6" s="38" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R6" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="S6" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="S6" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="T6" s="17"/>
       <c r="U6" s="17"/>
       <c r="V6" s="17"/>
@@ -1991,25 +2012,25 @@
       <c r="AT6" s="17"/>
       <c r="AU6" s="19"/>
       <c r="AV6" s="42" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AW6" s="21"/>
       <c r="AX6" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="AY6" s="34" t="s">
         <v>133</v>
-      </c>
-      <c r="AY6" s="34" t="s">
-        <v>134</v>
       </c>
       <c r="AZ6" s="21"/>
       <c r="BA6" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="BB6" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="BC6" s="18"/>
       <c r="BD6" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE6" s="34"/>
       <c r="BF6" s="34"/>
@@ -2031,7 +2052,7 @@
         <v>2</v>
       </c>
       <c r="BW6" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:77" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -2039,51 +2060,53 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C7" s="4">
         <v>4</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F7" s="17"/>
       <c r="G7" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I7" s="17"/>
       <c r="J7" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K7" s="17"/>
       <c r="L7" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M7" s="38" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O7" s="24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P7" s="24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q7" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R7" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="S7" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="S7" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="T7" s="17"/>
       <c r="U7" s="17"/>
       <c r="V7" s="17"/>
@@ -2113,30 +2136,34 @@
       <c r="AT7" s="17"/>
       <c r="AU7" s="19"/>
       <c r="AV7" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AW7" s="25"/>
       <c r="AX7" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AY7" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AZ7" s="17"/>
       <c r="BA7" s="34">
         <v>9.3000000000000007</v>
       </c>
       <c r="BB7" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="BC7" s="17"/>
       <c r="BD7" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="BE7" s="34"/>
       <c r="BF7" s="34"/>
-      <c r="BG7" s="17"/>
-      <c r="BH7" s="22"/>
+      <c r="BG7" s="18">
+        <v>46310</v>
+      </c>
+      <c r="BH7" s="22" t="s">
+        <v>186</v>
+      </c>
       <c r="BI7" s="17"/>
       <c r="BJ7" s="17"/>
       <c r="BK7" s="17"/>
@@ -2153,7 +2180,7 @@
         <v>3</v>
       </c>
       <c r="BW7" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
@@ -2161,51 +2188,53 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C8" s="4">
         <v>17</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F8" s="17"/>
       <c r="G8" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K8" s="17"/>
       <c r="L8" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O8" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q8" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R8" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="S8" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="S8" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="T8" s="17"/>
       <c r="U8" s="17"/>
       <c r="V8" s="17"/>
@@ -2237,21 +2266,21 @@
       <c r="AV8" s="19"/>
       <c r="AW8" s="25"/>
       <c r="AX8" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="AY8" s="34" t="s">
         <v>157</v>
-      </c>
-      <c r="AY8" s="34" t="s">
-        <v>158</v>
       </c>
       <c r="AZ8" s="17"/>
       <c r="BA8" s="34">
         <v>9.4</v>
       </c>
       <c r="BB8" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="BC8" s="17"/>
       <c r="BD8" s="37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE8" s="17"/>
       <c r="BF8" s="17"/>
@@ -2273,7 +2302,7 @@
         <v>4</v>
       </c>
       <c r="BW8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
@@ -2281,51 +2310,53 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" s="4">
         <v>5</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F9" s="17"/>
       <c r="G9" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I9" s="17"/>
       <c r="J9" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K9" s="17"/>
       <c r="L9" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M9" s="39" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q9" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R9" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="S9" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="S9" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="T9" s="17"/>
       <c r="U9" s="17"/>
       <c r="V9" s="17"/>
@@ -2355,21 +2386,21 @@
       <c r="AT9" s="17"/>
       <c r="AU9" s="19"/>
       <c r="AV9" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AW9" s="21"/>
       <c r="AX9" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="AY9" s="19" t="s">
         <v>139</v>
-      </c>
-      <c r="AY9" s="19" t="s">
-        <v>140</v>
       </c>
       <c r="AZ9" s="21"/>
       <c r="BA9" s="34">
         <v>9.1</v>
       </c>
       <c r="BB9" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="BC9" s="18"/>
       <c r="BD9" s="17"/>
@@ -2393,7 +2424,7 @@
         <v>5</v>
       </c>
       <c r="BW9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
@@ -2401,51 +2432,53 @@
         <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" s="4">
         <v>6</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F10" s="17"/>
       <c r="G10" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K10" s="17"/>
       <c r="L10" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M10" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q10" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R10" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="S10" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="S10" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="T10" s="17"/>
       <c r="U10" s="17"/>
       <c r="V10" s="17"/>
@@ -2477,17 +2510,17 @@
       <c r="AV10" s="42"/>
       <c r="AW10" s="21"/>
       <c r="AX10" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="AY10" s="34" t="s">
         <v>137</v>
-      </c>
-      <c r="AY10" s="34" t="s">
-        <v>138</v>
       </c>
       <c r="AZ10" s="18"/>
       <c r="BA10" s="34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="BB10" s="34" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="BC10" s="34"/>
       <c r="BD10" s="17"/>
@@ -2511,7 +2544,7 @@
         <v>6</v>
       </c>
       <c r="BW10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
@@ -2519,51 +2552,53 @@
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C11" s="4">
         <v>7</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F11" s="17"/>
       <c r="G11" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I11" s="17"/>
       <c r="J11" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K11" s="17"/>
       <c r="L11" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M11" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P11" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q11" s="38" t="s">
-        <v>118</v>
+        <v>117</v>
+      </c>
+      <c r="Q11" s="17" t="s">
+        <v>117</v>
       </c>
       <c r="R11" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="S11" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="S11" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="T11" s="17"/>
       <c r="U11" s="17"/>
       <c r="V11" s="17"/>
@@ -2593,28 +2628,32 @@
       <c r="AT11" s="17"/>
       <c r="AU11" s="19"/>
       <c r="AV11" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AW11" s="21"/>
       <c r="AX11" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="AY11" s="34" t="s">
         <v>145</v>
-      </c>
-      <c r="AY11" s="34" t="s">
-        <v>146</v>
       </c>
       <c r="AZ11" s="18"/>
       <c r="BA11" s="34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="BB11" s="34" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="BC11" s="34"/>
       <c r="BD11" s="17"/>
       <c r="BE11" s="17"/>
       <c r="BF11" s="18"/>
-      <c r="BG11" s="17"/>
-      <c r="BH11" s="17"/>
+      <c r="BG11" s="18">
+        <v>46310</v>
+      </c>
+      <c r="BH11" s="17" t="s">
+        <v>184</v>
+      </c>
       <c r="BI11" s="17"/>
       <c r="BJ11" s="18"/>
       <c r="BK11" s="17"/>
@@ -2631,7 +2670,7 @@
         <v>7</v>
       </c>
       <c r="BW11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
@@ -2639,53 +2678,55 @@
         <v>9</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C12" s="4">
         <v>8</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F12" s="17"/>
       <c r="G12" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K12" s="17"/>
       <c r="L12" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M12" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q12" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R12" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="S12" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="S12" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="T12" s="17"/>
       <c r="U12" s="17"/>
       <c r="V12" s="17"/>
@@ -2714,23 +2755,23 @@
       <c r="AS12" s="18"/>
       <c r="AT12" s="17"/>
       <c r="AU12" s="19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AV12" s="41" t="s">
-        <v>177</v>
-      </c>
-      <c r="AW12" s="67">
+        <v>176</v>
+      </c>
+      <c r="AW12" s="46">
         <v>46307</v>
       </c>
       <c r="AX12" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="AY12" s="19" t="s">
         <v>147</v>
-      </c>
-      <c r="AY12" s="19" t="s">
-        <v>148</v>
       </c>
       <c r="AZ12" s="21"/>
       <c r="BA12" s="34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="BB12" s="34"/>
       <c r="BC12" s="34"/>
@@ -2755,7 +2796,7 @@
         <v>8</v>
       </c>
       <c r="BW12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
@@ -2763,51 +2804,53 @@
         <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C13" s="4">
         <v>9</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F13" s="17"/>
       <c r="G13" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I13" s="17"/>
       <c r="J13" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K13" s="17"/>
       <c r="L13" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M13" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P13" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q13" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R13" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="S13" s="17"/>
+        <v>118</v>
+      </c>
+      <c r="S13" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="T13" s="17"/>
       <c r="U13" s="17"/>
       <c r="V13" s="17"/>
@@ -2839,10 +2882,10 @@
       <c r="AV13" s="19"/>
       <c r="AW13" s="21"/>
       <c r="AX13" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="AY13" s="34" t="s">
         <v>149</v>
-      </c>
-      <c r="AY13" s="34" t="s">
-        <v>150</v>
       </c>
       <c r="AZ13" s="18"/>
       <c r="BA13" s="17"/>
@@ -2869,7 +2912,7 @@
         <v>9</v>
       </c>
       <c r="BW13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
@@ -2877,51 +2920,53 @@
         <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C14" s="4">
         <v>10</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F14" s="17"/>
       <c r="G14" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I14" s="17"/>
       <c r="J14" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K14" s="17"/>
       <c r="L14" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M14" s="38" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O14" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q14" s="44" t="s">
-        <v>118</v>
+        <v>117</v>
+      </c>
+      <c r="Q14" s="23" t="s">
+        <v>117</v>
       </c>
       <c r="R14" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="S14" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="S14" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="T14" s="17"/>
       <c r="U14" s="17"/>
       <c r="V14" s="17"/>
@@ -2951,14 +2996,14 @@
       <c r="AT14" s="17"/>
       <c r="AU14" s="19"/>
       <c r="AV14" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AW14" s="25"/>
       <c r="AX14" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="AY14" s="34" t="s">
         <v>151</v>
-      </c>
-      <c r="AY14" s="34" t="s">
-        <v>152</v>
       </c>
       <c r="AZ14" s="17"/>
       <c r="BA14" s="17"/>
@@ -2967,8 +3012,12 @@
       <c r="BD14" s="17"/>
       <c r="BE14" s="17"/>
       <c r="BF14" s="17"/>
-      <c r="BG14" s="17"/>
-      <c r="BH14" s="17"/>
+      <c r="BG14" s="18">
+        <v>46310</v>
+      </c>
+      <c r="BH14" s="17" t="s">
+        <v>184</v>
+      </c>
       <c r="BI14" s="17"/>
       <c r="BJ14" s="17"/>
       <c r="BK14" s="17"/>
@@ -2985,7 +3034,7 @@
         <v>10</v>
       </c>
       <c r="BW14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
@@ -2993,51 +3042,53 @@
         <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C15" s="4">
         <v>7</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F15" s="17"/>
       <c r="G15" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I15" s="17"/>
       <c r="J15" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M15" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O15" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q15" s="38" t="s">
-        <v>118</v>
+        <v>117</v>
+      </c>
+      <c r="Q15" s="17" t="s">
+        <v>117</v>
       </c>
       <c r="R15" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="S15" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="S15" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="T15" s="17"/>
       <c r="U15" s="17"/>
       <c r="V15" s="17"/>
@@ -3067,14 +3118,14 @@
       <c r="AT15" s="17"/>
       <c r="AU15" s="19"/>
       <c r="AV15" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AW15" s="18"/>
       <c r="AX15" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="AY15" s="34" t="s">
         <v>145</v>
-      </c>
-      <c r="AY15" s="34" t="s">
-        <v>146</v>
       </c>
       <c r="AZ15" s="21"/>
       <c r="BA15" s="17"/>
@@ -3083,8 +3134,12 @@
       <c r="BD15" s="17"/>
       <c r="BE15" s="22"/>
       <c r="BF15" s="21"/>
-      <c r="BG15" s="17"/>
-      <c r="BH15" s="17"/>
+      <c r="BG15" s="18">
+        <v>46310</v>
+      </c>
+      <c r="BH15" s="17" t="s">
+        <v>184</v>
+      </c>
       <c r="BI15" s="17"/>
       <c r="BJ15" s="18"/>
       <c r="BK15" s="17"/>
@@ -3101,7 +3156,7 @@
         <v>11</v>
       </c>
       <c r="BW15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
@@ -3109,51 +3164,53 @@
         <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C16" s="4">
         <v>1</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F16" s="17"/>
       <c r="G16" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I16" s="17"/>
       <c r="J16" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K16" s="17"/>
       <c r="L16" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M16" s="39" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q16" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R16" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="S16" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="S16" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="T16" s="17"/>
       <c r="U16" s="17"/>
       <c r="V16" s="17"/>
@@ -3183,21 +3240,21 @@
       <c r="AT16" s="17"/>
       <c r="AU16" s="18"/>
       <c r="AV16" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AW16" s="25"/>
       <c r="AX16" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="AY16" s="34" t="s">
         <v>129</v>
-      </c>
-      <c r="AY16" s="34" t="s">
-        <v>130</v>
       </c>
       <c r="AZ16" s="18"/>
       <c r="BA16" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="BB16" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="BC16" s="18"/>
       <c r="BD16" s="17"/>
@@ -3221,7 +3278,7 @@
         <v>12</v>
       </c>
       <c r="BW16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
@@ -3229,51 +3286,53 @@
         <v>14</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C17" s="4">
         <v>11</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F17" s="17"/>
       <c r="G17" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I17" s="17"/>
       <c r="J17" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M17" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q17" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R17" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="S17" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="S17" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="T17" s="17"/>
       <c r="U17" s="17"/>
       <c r="V17" s="17"/>
@@ -3303,14 +3362,14 @@
       <c r="AT17" s="17"/>
       <c r="AU17" s="19"/>
       <c r="AV17" s="42" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AW17" s="21"/>
       <c r="AX17" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="AY17" s="34" t="s">
         <v>153</v>
-      </c>
-      <c r="AY17" s="34" t="s">
-        <v>154</v>
       </c>
       <c r="AZ17" s="18"/>
       <c r="BA17" s="17"/>
@@ -3337,7 +3396,7 @@
         <v>13</v>
       </c>
       <c r="BW17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
@@ -3345,53 +3404,55 @@
         <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C18" s="4">
         <v>12</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F18" s="17"/>
       <c r="G18" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K18" s="17"/>
       <c r="L18" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M18" s="39" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q18" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R18" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="S18" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="S18" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="T18" s="17"/>
       <c r="U18" s="17"/>
       <c r="V18" s="17"/>
@@ -3419,20 +3480,20 @@
       <c r="AR18" s="17"/>
       <c r="AS18" s="18"/>
       <c r="AT18" s="17"/>
-      <c r="AU18" s="65" t="s">
-        <v>182</v>
-      </c>
-      <c r="AV18" s="66" t="s">
-        <v>177</v>
-      </c>
-      <c r="AW18" s="67">
+      <c r="AU18" s="44" t="s">
+        <v>181</v>
+      </c>
+      <c r="AV18" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="AW18" s="46">
         <v>46307</v>
       </c>
       <c r="AX18" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="AY18" s="34" t="s">
         <v>155</v>
-      </c>
-      <c r="AY18" s="34" t="s">
-        <v>156</v>
       </c>
       <c r="AZ18" s="21"/>
       <c r="BA18" s="17"/>
@@ -3459,7 +3520,7 @@
         <v>14</v>
       </c>
       <c r="BW18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
@@ -3467,51 +3528,53 @@
         <v>16</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C19" s="4">
         <v>11</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F19" s="17"/>
       <c r="G19" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I19" s="17"/>
       <c r="J19" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K19" s="17"/>
       <c r="L19" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M19" s="40" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P19" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q19" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R19" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="S19" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="S19" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="T19" s="17"/>
       <c r="U19" s="17"/>
       <c r="V19" s="17"/>
@@ -3541,14 +3604,14 @@
       <c r="AT19" s="17"/>
       <c r="AU19" s="19"/>
       <c r="AV19" s="42" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AW19" s="21"/>
       <c r="AX19" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="AY19" s="34" t="s">
         <v>153</v>
-      </c>
-      <c r="AY19" s="34" t="s">
-        <v>154</v>
       </c>
       <c r="AZ19" s="18"/>
       <c r="BA19" s="17"/>
@@ -3575,7 +3638,7 @@
         <v>15</v>
       </c>
       <c r="BW19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
@@ -3583,51 +3646,53 @@
         <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C20" s="4">
         <v>5</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F20" s="17"/>
       <c r="G20" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I20" s="17"/>
       <c r="J20" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K20" s="17"/>
       <c r="L20" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M20" s="39" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P20" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q20" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R20" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="S20" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="S20" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="T20" s="17"/>
       <c r="U20" s="17"/>
       <c r="V20" s="17"/>
@@ -3657,14 +3722,14 @@
       <c r="AT20" s="17"/>
       <c r="AU20" s="19"/>
       <c r="AV20" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AW20" s="21"/>
       <c r="AX20" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="AY20" s="19" t="s">
         <v>139</v>
-      </c>
-      <c r="AY20" s="19" t="s">
-        <v>140</v>
       </c>
       <c r="AZ20" s="18"/>
       <c r="BA20" s="17"/>
@@ -3691,7 +3756,7 @@
         <v>16</v>
       </c>
       <c r="BW20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
@@ -3699,51 +3764,53 @@
         <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C21" s="4">
         <v>17</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F21" s="17"/>
       <c r="G21" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I21" s="17"/>
       <c r="J21" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K21" s="17"/>
       <c r="L21" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M21" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O21" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P21" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q21" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R21" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="S21" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="S21" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="T21" s="17"/>
       <c r="U21" s="17"/>
       <c r="V21" s="17"/>
@@ -3775,10 +3842,10 @@
       <c r="AV21" s="19"/>
       <c r="AW21" s="21"/>
       <c r="AX21" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="AY21" s="34" t="s">
         <v>157</v>
-      </c>
-      <c r="AY21" s="34" t="s">
-        <v>158</v>
       </c>
       <c r="AZ21" s="21"/>
       <c r="BA21" s="17"/>
@@ -3805,7 +3872,7 @@
         <v>17</v>
       </c>
       <c r="BW21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
@@ -3813,51 +3880,53 @@
         <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C22" s="4">
         <v>13</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F22" s="17"/>
       <c r="G22" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I22" s="17"/>
       <c r="J22" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K22" s="17"/>
       <c r="L22" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M22" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O22" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q22" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R22" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="S22" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="S22" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="T22" s="17"/>
       <c r="U22" s="17"/>
       <c r="V22" s="17"/>
@@ -3889,10 +3958,10 @@
       <c r="AV22" s="19"/>
       <c r="AW22" s="21"/>
       <c r="AX22" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="AY22" s="7" t="s">
         <v>141</v>
-      </c>
-      <c r="AY22" s="7" t="s">
-        <v>142</v>
       </c>
       <c r="AZ22" s="21"/>
       <c r="BA22" s="17"/>
@@ -3919,7 +3988,7 @@
         <v>18</v>
       </c>
       <c r="BW22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:75" ht="37.5" x14ac:dyDescent="0.3">
@@ -3927,51 +3996,53 @@
         <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C23" s="4">
         <v>14</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F23" s="17"/>
       <c r="G23" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H23" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I23" s="17"/>
       <c r="J23" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K23" s="17"/>
       <c r="L23" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M23" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O23" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q23" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R23" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="S23" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="S23" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="T23" s="17"/>
       <c r="U23" s="17"/>
       <c r="V23" s="17"/>
@@ -4003,7 +4074,7 @@
       <c r="AV23" s="19"/>
       <c r="AW23" s="21"/>
       <c r="AX23" s="26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AY23" s="19"/>
       <c r="AZ23" s="18"/>
@@ -4031,7 +4102,7 @@
         <v>19</v>
       </c>
       <c r="BW23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:75" ht="37.5" x14ac:dyDescent="0.3">
@@ -4039,51 +4110,53 @@
         <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C24" s="4">
         <v>15</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F24" s="17"/>
       <c r="G24" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I24" s="17"/>
       <c r="J24" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K24" s="17"/>
       <c r="L24" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M24" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O24" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P24" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q24" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R24" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="S24" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="S24" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="T24" s="17"/>
       <c r="U24" s="17"/>
       <c r="V24" s="17"/>
@@ -4111,17 +4184,17 @@
       <c r="AR24" s="17"/>
       <c r="AS24" s="17"/>
       <c r="AT24" s="17"/>
-      <c r="AU24" s="65" t="s">
-        <v>180</v>
-      </c>
-      <c r="AV24" s="66" t="s">
-        <v>177</v>
-      </c>
-      <c r="AW24" s="67">
+      <c r="AU24" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="AV24" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="AW24" s="46">
         <v>46307</v>
       </c>
       <c r="AX24" s="26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AY24" s="17"/>
       <c r="AZ24" s="17"/>
@@ -4135,7 +4208,7 @@
         <v>46303</v>
       </c>
       <c r="BH24" s="17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="BI24" s="17"/>
       <c r="BJ24" s="17"/>
@@ -4153,7 +4226,7 @@
         <v>20</v>
       </c>
       <c r="BW24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:75" ht="37.5" x14ac:dyDescent="0.3">
@@ -4161,53 +4234,55 @@
         <v>22</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C25" s="4">
         <v>16</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F25" s="17"/>
       <c r="G25" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I25" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K25" s="17"/>
       <c r="L25" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M25" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O25" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P25" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q25" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
+      </c>
+      <c r="Q25" s="38" t="s">
+        <v>117</v>
       </c>
       <c r="R25" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="S25" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="S25" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="T25" s="17"/>
       <c r="U25" s="17"/>
       <c r="V25" s="17"/>
@@ -4239,7 +4314,7 @@
       <c r="AV25" s="19"/>
       <c r="AW25" s="21"/>
       <c r="AX25" s="26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AY25" s="19"/>
       <c r="AZ25" s="21"/>
@@ -4267,7 +4342,7 @@
         <v>21</v>
       </c>
       <c r="BW25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
@@ -4275,51 +4350,53 @@
         <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C26" s="4">
         <v>9</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F26" s="17"/>
       <c r="G26" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I26" s="17"/>
       <c r="J26" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K26" s="17"/>
       <c r="L26" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M26" s="29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N26" s="29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O26" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P26" s="29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q26" s="29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R26" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="S26" s="29"/>
+        <v>117</v>
+      </c>
+      <c r="S26" s="29" t="s">
+        <v>117</v>
+      </c>
       <c r="T26" s="29"/>
       <c r="U26" s="29"/>
       <c r="V26" s="29"/>
@@ -4351,10 +4428,10 @@
       <c r="AV26" s="19"/>
       <c r="AW26" s="21"/>
       <c r="AX26" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="AY26" s="34" t="s">
         <v>149</v>
-      </c>
-      <c r="AY26" s="34" t="s">
-        <v>150</v>
       </c>
       <c r="AZ26" s="18"/>
       <c r="BA26" s="17"/>
@@ -4381,10 +4458,10 @@
         <v>22</v>
       </c>
       <c r="BV26" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="BW26" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
@@ -4392,51 +4469,53 @@
         <v>24</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C27" s="4">
         <v>2</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F27" s="17"/>
       <c r="G27" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I27" s="17"/>
       <c r="J27" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K27" s="17"/>
       <c r="L27" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O27" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P27" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q27" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R27" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="S27" s="30"/>
+        <v>117</v>
+      </c>
+      <c r="S27" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="T27" s="30"/>
       <c r="U27" s="30"/>
       <c r="V27" s="30"/>
@@ -4464,27 +4543,27 @@
       <c r="AR27" s="30"/>
       <c r="AS27" s="18"/>
       <c r="AT27" s="30"/>
-      <c r="AU27" s="65" t="s">
-        <v>181</v>
-      </c>
-      <c r="AV27" s="66" t="s">
-        <v>177</v>
-      </c>
-      <c r="AW27" s="67">
+      <c r="AU27" s="44" t="s">
+        <v>180</v>
+      </c>
+      <c r="AV27" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="AW27" s="46">
         <v>46307</v>
       </c>
       <c r="AX27" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="AY27" s="34" t="s">
         <v>131</v>
-      </c>
-      <c r="AY27" s="34" t="s">
-        <v>132</v>
       </c>
       <c r="AZ27" s="18"/>
       <c r="BA27" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="BB27" s="21" t="s">
         <v>79</v>
-      </c>
-      <c r="BB27" s="21" t="s">
-        <v>80</v>
       </c>
       <c r="BC27" s="17"/>
       <c r="BD27" s="17"/>
@@ -4508,7 +4587,7 @@
         <v>23</v>
       </c>
       <c r="BW27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
@@ -4516,53 +4595,55 @@
         <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C28" s="4">
         <v>13</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F28" s="17"/>
       <c r="G28" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I28" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J28" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K28" s="17"/>
       <c r="L28" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O28" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P28" s="30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q28" s="30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R28" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="S28" s="30"/>
+        <v>118</v>
+      </c>
+      <c r="S28" s="30" t="s">
+        <v>117</v>
+      </c>
       <c r="T28" s="30"/>
       <c r="U28" s="30"/>
       <c r="V28" s="30"/>
@@ -4594,10 +4675,10 @@
       <c r="AV28" s="19"/>
       <c r="AW28" s="32"/>
       <c r="AX28" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="AY28" s="7" t="s">
         <v>141</v>
-      </c>
-      <c r="AY28" s="7" t="s">
-        <v>142</v>
       </c>
       <c r="AZ28" s="18"/>
       <c r="BA28" s="17"/>
@@ -4626,51 +4707,53 @@
         <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C29" s="4">
         <v>15</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F29" s="17"/>
       <c r="G29" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I29" s="17"/>
       <c r="J29" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K29" s="17"/>
       <c r="L29" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O29" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P29" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q29" s="30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R29" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="S29" s="30"/>
+        <v>117</v>
+      </c>
+      <c r="S29" s="30" t="s">
+        <v>117</v>
+      </c>
       <c r="T29" s="30"/>
       <c r="U29" s="30"/>
       <c r="V29" s="30"/>
@@ -4698,17 +4781,17 @@
       <c r="AR29" s="30"/>
       <c r="AS29" s="18"/>
       <c r="AT29" s="30"/>
-      <c r="AU29" s="65" t="s">
-        <v>180</v>
-      </c>
-      <c r="AV29" s="66" t="s">
-        <v>177</v>
-      </c>
-      <c r="AW29" s="67">
+      <c r="AU29" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="AV29" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="AW29" s="46">
         <v>46307</v>
       </c>
       <c r="AX29" s="26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AY29" s="19"/>
       <c r="AZ29" s="18"/>
@@ -4738,51 +4821,53 @@
         <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C30" s="4">
         <v>12</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F30" s="17"/>
       <c r="G30" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I30" s="17"/>
       <c r="J30" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K30" s="17"/>
       <c r="L30" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M30" s="39" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O30" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P30" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R30" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="S30" s="30"/>
+        <v>117</v>
+      </c>
+      <c r="S30" s="30" t="s">
+        <v>117</v>
+      </c>
       <c r="T30" s="30"/>
       <c r="U30" s="30"/>
       <c r="V30" s="30"/>
@@ -4810,20 +4895,20 @@
       <c r="AR30" s="30"/>
       <c r="AS30" s="18"/>
       <c r="AT30" s="30"/>
-      <c r="AU30" s="65" t="s">
-        <v>182</v>
-      </c>
-      <c r="AV30" s="66" t="s">
-        <v>177</v>
-      </c>
-      <c r="AW30" s="67">
+      <c r="AU30" s="44" t="s">
+        <v>181</v>
+      </c>
+      <c r="AV30" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="AW30" s="46">
         <v>46307</v>
       </c>
       <c r="AX30" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="AY30" s="34" t="s">
         <v>155</v>
-      </c>
-      <c r="AY30" s="34" t="s">
-        <v>156</v>
       </c>
       <c r="AZ30" s="18"/>
       <c r="BA30" s="17"/>
@@ -4852,51 +4937,53 @@
         <v>28</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C31" s="4">
         <v>4</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F31" s="17"/>
       <c r="G31" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I31" s="17"/>
       <c r="J31" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K31" s="17"/>
       <c r="L31" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M31" s="38" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O31" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P31" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q31" s="43" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R31" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="S31" s="30"/>
+        <v>117</v>
+      </c>
+      <c r="S31" s="30" t="s">
+        <v>117</v>
+      </c>
       <c r="T31" s="30"/>
       <c r="U31" s="30"/>
       <c r="V31" s="30"/>
@@ -4926,14 +5013,14 @@
       <c r="AT31" s="30"/>
       <c r="AU31" s="19"/>
       <c r="AV31" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AW31" s="32"/>
       <c r="AX31" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AY31" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AZ31" s="18"/>
       <c r="BA31" s="17"/>
@@ -4942,8 +5029,12 @@
       <c r="BD31" s="17"/>
       <c r="BE31" s="17"/>
       <c r="BF31" s="18"/>
-      <c r="BG31" s="17"/>
-      <c r="BH31" s="17"/>
+      <c r="BG31" s="18">
+        <v>46310</v>
+      </c>
+      <c r="BH31" s="22" t="s">
+        <v>186</v>
+      </c>
       <c r="BI31" s="17"/>
       <c r="BJ31" s="18"/>
       <c r="BK31" s="17"/>
@@ -4962,51 +5053,53 @@
         <v>29</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C32" s="4">
         <v>3</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F32" s="17"/>
       <c r="G32" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I32" s="17"/>
       <c r="J32" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K32" s="17"/>
       <c r="L32" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M32" s="40" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O32" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P32" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q32" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R32" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="S32" s="30"/>
+        <v>117</v>
+      </c>
+      <c r="S32" s="30" t="s">
+        <v>117</v>
+      </c>
       <c r="T32" s="30"/>
       <c r="U32" s="30"/>
       <c r="V32" s="30"/>
@@ -5036,21 +5129,21 @@
       <c r="AT32" s="30"/>
       <c r="AU32" s="19"/>
       <c r="AV32" s="42" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AW32" s="32"/>
       <c r="AX32" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="AY32" s="34" t="s">
         <v>133</v>
-      </c>
-      <c r="AY32" s="34" t="s">
-        <v>134</v>
       </c>
       <c r="AZ32" s="18"/>
       <c r="BA32" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="BB32" s="28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="BC32" s="17"/>
       <c r="BD32" s="17"/>
@@ -5076,51 +5169,53 @@
         <v>30</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C33" s="4">
         <v>16</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F33" s="17"/>
       <c r="G33" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I33" s="17"/>
       <c r="J33" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K33" s="17"/>
       <c r="L33" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O33" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P33" s="30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q33" s="43" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R33" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="S33" s="30"/>
+        <v>118</v>
+      </c>
+      <c r="S33" s="30" t="s">
+        <v>117</v>
+      </c>
       <c r="T33" s="30"/>
       <c r="U33" s="30"/>
       <c r="V33" s="30"/>
@@ -5152,7 +5247,7 @@
       <c r="AV33" s="19"/>
       <c r="AW33" s="32"/>
       <c r="AX33" s="26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AY33" s="19"/>
       <c r="AZ33" s="18"/>
@@ -5182,51 +5277,53 @@
         <v>31</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C34" s="4">
         <v>8</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F34" s="17"/>
       <c r="G34" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I34" s="17"/>
       <c r="J34" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K34" s="17"/>
       <c r="L34" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O34" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P34" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q34" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R34" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="S34" s="30"/>
+        <v>117</v>
+      </c>
+      <c r="S34" s="30" t="s">
+        <v>117</v>
+      </c>
       <c r="T34" s="30"/>
       <c r="U34" s="30"/>
       <c r="V34" s="30"/>
@@ -5255,19 +5352,19 @@
       <c r="AS34" s="18"/>
       <c r="AT34" s="30"/>
       <c r="AU34" s="19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AV34" s="41" t="s">
-        <v>177</v>
-      </c>
-      <c r="AW34" s="67">
+        <v>176</v>
+      </c>
+      <c r="AW34" s="46">
         <v>46307</v>
       </c>
       <c r="AX34" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="AY34" s="19" t="s">
         <v>147</v>
-      </c>
-      <c r="AY34" s="19" t="s">
-        <v>148</v>
       </c>
       <c r="AZ34" s="18"/>
       <c r="BA34" s="17"/>
@@ -5296,51 +5393,53 @@
         <v>32</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C35" s="4">
         <v>10</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F35" s="17"/>
       <c r="G35" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I35" s="17"/>
       <c r="J35" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K35" s="17"/>
       <c r="L35" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M35" s="38" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O35" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P35" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q35" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R35" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="S35" s="30"/>
+        <v>117</v>
+      </c>
+      <c r="S35" s="30" t="s">
+        <v>117</v>
+      </c>
       <c r="T35" s="30"/>
       <c r="U35" s="30"/>
       <c r="V35" s="30"/>
@@ -5370,14 +5469,14 @@
       <c r="AT35" s="30"/>
       <c r="AU35" s="19"/>
       <c r="AV35" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AW35" s="32"/>
       <c r="AX35" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="AY35" s="34" t="s">
         <v>151</v>
-      </c>
-      <c r="AY35" s="34" t="s">
-        <v>152</v>
       </c>
       <c r="AZ35" s="18"/>
       <c r="BA35" s="17"/>
@@ -5386,8 +5485,12 @@
       <c r="BD35" s="17"/>
       <c r="BE35" s="17"/>
       <c r="BF35" s="18"/>
-      <c r="BG35" s="17"/>
-      <c r="BH35" s="17"/>
+      <c r="BG35" s="18">
+        <v>46310</v>
+      </c>
+      <c r="BH35" s="17" t="s">
+        <v>187</v>
+      </c>
       <c r="BI35" s="17"/>
       <c r="BJ35" s="18"/>
       <c r="BK35" s="17"/>
@@ -5406,51 +5509,53 @@
         <v>33</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C36" s="4">
         <v>14</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F36" s="17"/>
       <c r="G36" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I36" s="17"/>
       <c r="J36" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K36" s="17"/>
       <c r="L36" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O36" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P36" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q36" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R36" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="S36" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="S36" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="T36" s="30"/>
       <c r="U36" s="30"/>
       <c r="V36" s="30"/>
@@ -5482,7 +5587,7 @@
       <c r="AV36" s="19"/>
       <c r="AW36" s="25"/>
       <c r="AX36" s="26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AY36" s="19"/>
       <c r="AZ36" s="17"/>
@@ -5512,53 +5617,55 @@
         <v>34</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C37" s="4">
         <v>18</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F37" s="17"/>
       <c r="G37" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K37" s="17"/>
       <c r="L37" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O37" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P37" s="30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q37" s="30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R37" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="S37" s="17"/>
+        <v>118</v>
+      </c>
+      <c r="S37" s="17" t="s">
+        <v>118</v>
+      </c>
       <c r="T37" s="30"/>
       <c r="U37" s="30"/>
       <c r="V37" s="30"/>
@@ -5590,10 +5697,10 @@
       <c r="AV37" s="19"/>
       <c r="AW37" s="25"/>
       <c r="AX37" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="AY37" s="34" t="s">
         <v>145</v>
-      </c>
-      <c r="AY37" s="34" t="s">
-        <v>146</v>
       </c>
       <c r="AZ37" s="17"/>
       <c r="BA37" s="17"/>
@@ -5618,57 +5725,57 @@
       <c r="BT37" s="30"/>
     </row>
     <row r="38" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A38" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="B38" s="54"/>
-      <c r="C38" s="54"/>
-      <c r="D38" s="54"/>
-      <c r="E38" s="54"/>
-      <c r="F38" s="54"/>
-      <c r="G38" s="54"/>
-      <c r="H38" s="54"/>
-      <c r="I38" s="54"/>
-      <c r="J38" s="54"/>
-      <c r="K38" s="54"/>
-      <c r="L38" s="54"/>
-      <c r="M38" s="54"/>
-      <c r="N38" s="54"/>
-      <c r="O38" s="54"/>
-      <c r="P38" s="54"/>
-      <c r="Q38" s="54"/>
-      <c r="R38" s="54"/>
-      <c r="S38" s="54"/>
-      <c r="T38" s="54"/>
-      <c r="U38" s="54"/>
-      <c r="V38" s="54"/>
-      <c r="W38" s="54"/>
-      <c r="X38" s="54"/>
-      <c r="Y38" s="54"/>
-      <c r="Z38" s="54"/>
-      <c r="AA38" s="54"/>
-      <c r="AB38" s="54"/>
-      <c r="AC38" s="54"/>
-      <c r="AD38" s="54"/>
-      <c r="AE38" s="54"/>
-      <c r="AF38" s="54"/>
-      <c r="AG38" s="54"/>
-      <c r="AH38" s="54"/>
-      <c r="AI38" s="54"/>
-      <c r="AJ38" s="54"/>
-      <c r="AK38" s="54"/>
-      <c r="AL38" s="54"/>
-      <c r="AM38" s="54"/>
-      <c r="AN38" s="54"/>
-      <c r="AO38" s="54"/>
-      <c r="AP38" s="54"/>
-      <c r="AQ38" s="54"/>
-      <c r="AR38" s="54"/>
-      <c r="AS38" s="54"/>
-      <c r="AT38" s="54"/>
-      <c r="AU38" s="54"/>
-      <c r="AV38" s="54"/>
-      <c r="AW38" s="55"/>
+      <c r="A38" s="60" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38" s="61"/>
+      <c r="C38" s="61"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="61"/>
+      <c r="F38" s="61"/>
+      <c r="G38" s="61"/>
+      <c r="H38" s="61"/>
+      <c r="I38" s="61"/>
+      <c r="J38" s="61"/>
+      <c r="K38" s="61"/>
+      <c r="L38" s="61"/>
+      <c r="M38" s="61"/>
+      <c r="N38" s="61"/>
+      <c r="O38" s="61"/>
+      <c r="P38" s="61"/>
+      <c r="Q38" s="61"/>
+      <c r="R38" s="61"/>
+      <c r="S38" s="61"/>
+      <c r="T38" s="61"/>
+      <c r="U38" s="61"/>
+      <c r="V38" s="61"/>
+      <c r="W38" s="61"/>
+      <c r="X38" s="61"/>
+      <c r="Y38" s="61"/>
+      <c r="Z38" s="61"/>
+      <c r="AA38" s="61"/>
+      <c r="AB38" s="61"/>
+      <c r="AC38" s="61"/>
+      <c r="AD38" s="61"/>
+      <c r="AE38" s="61"/>
+      <c r="AF38" s="61"/>
+      <c r="AG38" s="61"/>
+      <c r="AH38" s="61"/>
+      <c r="AI38" s="61"/>
+      <c r="AJ38" s="61"/>
+      <c r="AK38" s="61"/>
+      <c r="AL38" s="61"/>
+      <c r="AM38" s="61"/>
+      <c r="AN38" s="61"/>
+      <c r="AO38" s="61"/>
+      <c r="AP38" s="61"/>
+      <c r="AQ38" s="61"/>
+      <c r="AR38" s="61"/>
+      <c r="AS38" s="61"/>
+      <c r="AT38" s="61"/>
+      <c r="AU38" s="61"/>
+      <c r="AV38" s="61"/>
+      <c r="AW38" s="62"/>
       <c r="AX38" s="2"/>
       <c r="AY38" s="2"/>
       <c r="AZ38" s="2"/>
@@ -5696,61 +5803,61 @@
         <v>24</v>
       </c>
       <c r="BW38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A39" s="56" t="s">
-        <v>85</v>
-      </c>
-      <c r="B39" s="57"/>
-      <c r="C39" s="57"/>
-      <c r="D39" s="57"/>
-      <c r="E39" s="57"/>
-      <c r="F39" s="57"/>
-      <c r="G39" s="57"/>
-      <c r="H39" s="57"/>
-      <c r="I39" s="57"/>
-      <c r="J39" s="57"/>
-      <c r="K39" s="57"/>
-      <c r="L39" s="57"/>
-      <c r="M39" s="57"/>
-      <c r="N39" s="57"/>
-      <c r="O39" s="57"/>
-      <c r="P39" s="57"/>
-      <c r="Q39" s="57"/>
-      <c r="R39" s="57"/>
-      <c r="S39" s="57"/>
-      <c r="T39" s="57"/>
-      <c r="U39" s="57"/>
-      <c r="V39" s="57"/>
-      <c r="W39" s="57"/>
-      <c r="X39" s="57"/>
-      <c r="Y39" s="57"/>
-      <c r="Z39" s="57"/>
-      <c r="AA39" s="57"/>
-      <c r="AB39" s="57"/>
-      <c r="AC39" s="57"/>
-      <c r="AD39" s="57"/>
-      <c r="AE39" s="57"/>
-      <c r="AF39" s="57"/>
-      <c r="AG39" s="57"/>
-      <c r="AH39" s="57"/>
-      <c r="AI39" s="57"/>
-      <c r="AJ39" s="57"/>
-      <c r="AK39" s="57"/>
-      <c r="AL39" s="57"/>
-      <c r="AM39" s="57"/>
-      <c r="AN39" s="57"/>
-      <c r="AO39" s="57"/>
-      <c r="AP39" s="57"/>
-      <c r="AQ39" s="57"/>
-      <c r="AR39" s="57"/>
-      <c r="AS39" s="57"/>
-      <c r="AT39" s="57"/>
-      <c r="AU39" s="57"/>
-      <c r="AV39" s="57"/>
-      <c r="AW39" s="58"/>
+      <c r="A39" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" s="64"/>
+      <c r="C39" s="64"/>
+      <c r="D39" s="64"/>
+      <c r="E39" s="64"/>
+      <c r="F39" s="64"/>
+      <c r="G39" s="64"/>
+      <c r="H39" s="64"/>
+      <c r="I39" s="64"/>
+      <c r="J39" s="64"/>
+      <c r="K39" s="64"/>
+      <c r="L39" s="64"/>
+      <c r="M39" s="64"/>
+      <c r="N39" s="64"/>
+      <c r="O39" s="64"/>
+      <c r="P39" s="64"/>
+      <c r="Q39" s="64"/>
+      <c r="R39" s="64"/>
+      <c r="S39" s="64"/>
+      <c r="T39" s="64"/>
+      <c r="U39" s="64"/>
+      <c r="V39" s="64"/>
+      <c r="W39" s="64"/>
+      <c r="X39" s="64"/>
+      <c r="Y39" s="64"/>
+      <c r="Z39" s="64"/>
+      <c r="AA39" s="64"/>
+      <c r="AB39" s="64"/>
+      <c r="AC39" s="64"/>
+      <c r="AD39" s="64"/>
+      <c r="AE39" s="64"/>
+      <c r="AF39" s="64"/>
+      <c r="AG39" s="64"/>
+      <c r="AH39" s="64"/>
+      <c r="AI39" s="64"/>
+      <c r="AJ39" s="64"/>
+      <c r="AK39" s="64"/>
+      <c r="AL39" s="64"/>
+      <c r="AM39" s="64"/>
+      <c r="AN39" s="64"/>
+      <c r="AO39" s="64"/>
+      <c r="AP39" s="64"/>
+      <c r="AQ39" s="64"/>
+      <c r="AR39" s="64"/>
+      <c r="AS39" s="64"/>
+      <c r="AT39" s="64"/>
+      <c r="AU39" s="64"/>
+      <c r="AV39" s="64"/>
+      <c r="AW39" s="65"/>
       <c r="AX39" s="2"/>
       <c r="AY39" s="2"/>
       <c r="AZ39" s="2"/>
@@ -5778,7 +5885,7 @@
         <v>25</v>
       </c>
       <c r="BW39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:75" x14ac:dyDescent="0.25">
@@ -5909,251 +6016,257 @@
         <v>26</v>
       </c>
       <c r="BW40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:75" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" t="s">
+        <v>122</v>
+      </c>
+      <c r="E41" t="s">
         <v>123</v>
       </c>
-      <c r="E41" t="s">
-        <v>124</v>
-      </c>
       <c r="F41" t="s">
+        <v>122</v>
+      </c>
+      <c r="G41" t="s">
+        <v>122</v>
+      </c>
+      <c r="H41" t="s">
         <v>123</v>
       </c>
-      <c r="G41" t="s">
+      <c r="I41" t="s">
+        <v>122</v>
+      </c>
+      <c r="J41" t="s">
         <v>123</v>
       </c>
-      <c r="H41" t="s">
-        <v>124</v>
-      </c>
-      <c r="I41" t="s">
+      <c r="K41" t="s">
+        <v>122</v>
+      </c>
+      <c r="L41" t="s">
+        <v>122</v>
+      </c>
+      <c r="M41" t="s">
         <v>123</v>
       </c>
-      <c r="J41" t="s">
-        <v>124</v>
-      </c>
-      <c r="K41" t="s">
+      <c r="N41" t="s">
+        <v>122</v>
+      </c>
+      <c r="O41" t="s">
         <v>123</v>
       </c>
-      <c r="L41" t="s">
+      <c r="P41" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>122</v>
+      </c>
+      <c r="R41" t="s">
         <v>123</v>
       </c>
-      <c r="M41" t="s">
-        <v>124</v>
-      </c>
-      <c r="N41" t="s">
+      <c r="S41" t="s">
+        <v>122</v>
+      </c>
+      <c r="T41" t="s">
         <v>123</v>
       </c>
-      <c r="O41" t="s">
-        <v>124</v>
-      </c>
-      <c r="P41" t="s">
+      <c r="U41" t="s">
+        <v>122</v>
+      </c>
+      <c r="V41" t="s">
+        <v>122</v>
+      </c>
+      <c r="W41" t="s">
         <v>123</v>
       </c>
-      <c r="Q41" t="s">
+      <c r="X41" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y41" t="s">
         <v>123</v>
       </c>
-      <c r="R41" t="s">
-        <v>124</v>
-      </c>
-      <c r="S41" t="s">
+      <c r="Z41" t="s">
         <v>123</v>
       </c>
-      <c r="T41" t="s">
-        <v>124</v>
-      </c>
-      <c r="U41" t="s">
+      <c r="AA41" t="s">
+        <v>122</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC41" t="s">
         <v>123</v>
       </c>
-      <c r="V41" t="s">
+      <c r="AD41" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE41" t="s">
         <v>123</v>
       </c>
-      <c r="W41" t="s">
-        <v>124</v>
-      </c>
-      <c r="X41" t="s">
+      <c r="AF41" t="s">
         <v>123</v>
       </c>
-      <c r="Y41" t="s">
-        <v>124</v>
-      </c>
-      <c r="Z41" t="s">
-        <v>124</v>
-      </c>
-      <c r="AA41" t="s">
+      <c r="AG41" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH41" t="s">
+        <v>122</v>
+      </c>
+      <c r="AI41" t="s">
         <v>123</v>
       </c>
-      <c r="AB41" t="s">
+      <c r="AJ41" t="s">
+        <v>122</v>
+      </c>
+      <c r="AK41" t="s">
         <v>123</v>
       </c>
-      <c r="AC41" t="s">
-        <v>124</v>
-      </c>
-      <c r="AD41" t="s">
+      <c r="AL41" t="s">
         <v>123</v>
       </c>
-      <c r="AE41" t="s">
-        <v>124</v>
-      </c>
-      <c r="AF41" t="s">
-        <v>124</v>
-      </c>
-      <c r="AG41" t="s">
+      <c r="AM41" t="s">
+        <v>122</v>
+      </c>
+      <c r="AN41" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO41" t="s">
+        <v>122</v>
+      </c>
+      <c r="AP41" t="s">
         <v>123</v>
       </c>
-      <c r="AH41" t="s">
+      <c r="AQ41" t="s">
+        <v>122</v>
+      </c>
+      <c r="AR41" t="s">
         <v>123</v>
-      </c>
-      <c r="AI41" t="s">
-        <v>124</v>
-      </c>
-      <c r="AJ41" t="s">
-        <v>123</v>
-      </c>
-      <c r="AK41" t="s">
-        <v>124</v>
-      </c>
-      <c r="AL41" t="s">
-        <v>124</v>
-      </c>
-      <c r="AM41" t="s">
-        <v>123</v>
-      </c>
-      <c r="AN41" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO41" t="s">
-        <v>123</v>
-      </c>
-      <c r="AP41" t="s">
-        <v>124</v>
-      </c>
-      <c r="AQ41" t="s">
-        <v>123</v>
-      </c>
-      <c r="AR41" t="s">
-        <v>124</v>
       </c>
       <c r="BE41"/>
       <c r="BU41">
         <v>27</v>
       </c>
       <c r="BW41" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:75" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J42" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L42" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P42" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q42" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="R42" t="s">
+        <v>183</v>
+      </c>
+      <c r="S42" t="s">
+        <v>69</v>
       </c>
       <c r="BG42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="BU42">
         <v>28</v>
       </c>
       <c r="BW42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:75" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E43" s="16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F43" s="16"/>
       <c r="H43" s="16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I43" s="16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L43" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG43" t="s">
         <v>70</v>
-      </c>
-      <c r="BG43" t="s">
-        <v>71</v>
       </c>
       <c r="BU43" s="14">
         <v>29</v>
       </c>
       <c r="BV43" s="14"/>
       <c r="BW43" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:75" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AU44" t="s">
+        <v>61</v>
+      </c>
+      <c r="AV44" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="AV44" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="BU44">
         <v>30</v>
       </c>
       <c r="BW44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:75" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AU45" t="s">
+        <v>63</v>
+      </c>
+      <c r="AV45" t="s">
         <v>64</v>
-      </c>
-      <c r="AV45" t="s">
-        <v>65</v>
       </c>
       <c r="BU45">
         <v>31</v>
       </c>
       <c r="BW45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46" spans="1:75" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AU46" t="s">
+        <v>66</v>
+      </c>
+      <c r="AV46" t="s">
         <v>67</v>
-      </c>
-      <c r="AV46" t="s">
-        <v>68</v>
       </c>
       <c r="BU46" s="14">
         <v>32</v>
       </c>
       <c r="BV46" s="14"/>
       <c r="BW46" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47" spans="1:75" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6161,7 +6274,7 @@
         <v>33</v>
       </c>
       <c r="BW47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:75" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6169,7 +6282,7 @@
         <v>34</v>
       </c>
       <c r="BW48" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="49" spans="73:78" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6177,7 +6290,7 @@
         <v>35</v>
       </c>
       <c r="BW49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="73:78" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6186,12 +6299,12 @@
       </c>
       <c r="BV50" s="37"/>
       <c r="BW50" s="37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" spans="73:78" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BW51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53" spans="73:78" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -6204,7 +6317,7 @@
         <v>37</v>
       </c>
       <c r="BW54" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="BX54" s="10"/>
       <c r="BY54" s="10"/>
@@ -6214,13 +6327,13 @@
         <v>38</v>
       </c>
       <c r="BW55" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="BX55" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="BX55" s="11" t="s">
-        <v>78</v>
-      </c>
       <c r="BY55" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="BZ55">
         <v>49</v>
@@ -6229,10 +6342,10 @@
     <row r="56" spans="73:78" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BW56" s="10"/>
       <c r="BX56" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="BY56" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="BY56" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="BZ56">
         <v>50</v>
@@ -6243,13 +6356,13 @@
         <v>39</v>
       </c>
       <c r="BW57" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="BX57" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="BX57" s="11" t="s">
-        <v>82</v>
-      </c>
       <c r="BY57" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="BZ57">
         <v>51</v>
@@ -6260,7 +6373,7 @@
         <v>40</v>
       </c>
       <c r="BW58" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="BX58" s="10"/>
       <c r="BY58" s="10"/>
@@ -6270,7 +6383,7 @@
         <v>41</v>
       </c>
       <c r="BW59" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BX59" s="10"/>
       <c r="BY59" s="10"/>
@@ -6280,7 +6393,7 @@
         <v>42</v>
       </c>
       <c r="BW60" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="BX60" s="10"/>
       <c r="BY60" s="10"/>
@@ -6290,7 +6403,7 @@
         <v>43</v>
       </c>
       <c r="BW61" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="BX61" s="10"/>
       <c r="BY61" s="10"/>
@@ -6300,7 +6413,7 @@
         <v>44</v>
       </c>
       <c r="BW62" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="BX62" s="10"/>
       <c r="BY62" s="10"/>
@@ -6310,7 +6423,7 @@
         <v>45</v>
       </c>
       <c r="BW63" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BX63" s="10"/>
       <c r="BY63" s="10"/>
@@ -6320,7 +6433,7 @@
         <v>46</v>
       </c>
       <c r="BW64" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BX64" s="10"/>
       <c r="BY64" s="10"/>
@@ -6330,7 +6443,7 @@
         <v>47</v>
       </c>
       <c r="BW65" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66" spans="73:75" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6338,35 +6451,26 @@
         <v>48</v>
       </c>
       <c r="BW66" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AJ2:AJ3"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="AQ2:AQ3"/>
-    <mergeCell ref="BD2:BF3"/>
-    <mergeCell ref="AX2:AZ3"/>
-    <mergeCell ref="BA2:BC3"/>
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="AH2:AH3"/>
-    <mergeCell ref="AI2:AI3"/>
-    <mergeCell ref="AK2:AK3"/>
-    <mergeCell ref="AL2:AL3"/>
-    <mergeCell ref="AM2:AM3"/>
-    <mergeCell ref="AN2:AN3"/>
-    <mergeCell ref="AP2:AP3"/>
+    <mergeCell ref="AR2:AR3"/>
+    <mergeCell ref="BR2:BT3"/>
+    <mergeCell ref="A38:AW38"/>
+    <mergeCell ref="A39:AW39"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="AS2:AS3"/>
+    <mergeCell ref="AT2:AT3"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="BG2:BJ3"/>
+    <mergeCell ref="BK2:BN3"/>
     <mergeCell ref="BO2:BQ3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="A1:AW1"/>
@@ -6383,22 +6487,31 @@
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="AU2:AW3"/>
     <mergeCell ref="X2:X3"/>
+    <mergeCell ref="AQ2:AQ3"/>
+    <mergeCell ref="BD2:BF3"/>
+    <mergeCell ref="AX2:AZ3"/>
+    <mergeCell ref="BA2:BC3"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="AH2:AH3"/>
+    <mergeCell ref="AI2:AI3"/>
+    <mergeCell ref="AK2:AK3"/>
+    <mergeCell ref="AL2:AL3"/>
+    <mergeCell ref="AM2:AM3"/>
+    <mergeCell ref="AN2:AN3"/>
+    <mergeCell ref="AP2:AP3"/>
     <mergeCell ref="AO2:AO3"/>
-    <mergeCell ref="AR2:AR3"/>
-    <mergeCell ref="BR2:BT3"/>
-    <mergeCell ref="A38:AW38"/>
-    <mergeCell ref="A39:AW39"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="AS2:AS3"/>
-    <mergeCell ref="AT2:AT3"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="BG2:BJ3"/>
-    <mergeCell ref="BK2:BN3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AJ2:AJ3"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="AA2:AA3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="BW6" r:id="rId1" display="Прикладная дискретная математика. Приложение. 2016. № 9. С. 68-70." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -6412,6 +6525,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b78dbef7-f85b-47b5-8738-6377d50f4027" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bffb7b91-0466-4de0-9379-f5c53c3acedf">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Документ" ma:contentTypeID="0x0101004F6380A0290AF84484F859C9FFD97568" ma:contentTypeVersion="12" ma:contentTypeDescription="Создание документа." ma:contentTypeScope="" ma:versionID="1ee9877c88efff51dfb0d3a4b3e8ad1b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bffb7b91-0466-4de0-9379-f5c53c3acedf" xmlns:ns3="b78dbef7-f85b-47b5-8738-6377d50f4027" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="532d4df54980d57387e1b5dc96a6a32c" ns2:_="" ns3:_="">
     <xsd:import namespace="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
@@ -6612,17 +6736,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b78dbef7-f85b-47b5-8738-6377d50f4027" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bffb7b91-0466-4de0-9379-f5c53c3acedf">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -6633,6 +6746,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12ECB55F-B88E-4FE2-9AD5-5CA5D433F306}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b78dbef7-f85b-47b5-8738-6377d50f4027"/>
+    <ds:schemaRef ds:uri="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B6A6DF3-AE59-43BA-A5FF-CF9B7C54D4B8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6651,17 +6775,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12ECB55F-B88E-4FE2-9AD5-5CA5D433F306}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b78dbef7-f85b-47b5-8738-6377d50f4027"/>
-    <ds:schemaRef ds:uri="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00280879-8A9A-4335-93BC-405126DC8F0C}">
   <ds:schemaRefs>

--- a/Ведомость ТКИ-441 2026-2027.xlsx
+++ b/Ведомость ТКИ-441 2026-2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\StegMethods\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F33564-50E6-4403-9A9D-FB8BBECB1388}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95823E5-3E3B-4CC4-B662-05D5E1379167}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="188">
   <si>
     <t>Ведомость посещаемости занятий студентами группы ТКИ РУТ МИИТ</t>
   </si>
@@ -862,7 +862,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -906,7 +906,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -940,18 +939,9 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -966,13 +956,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -991,8 +974,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1358,237 +1363,237 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:77" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="57"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="57"/>
-      <c r="V1" s="57"/>
-      <c r="W1" s="57"/>
-      <c r="X1" s="57"/>
-      <c r="Y1" s="57"/>
-      <c r="Z1" s="57"/>
-      <c r="AA1" s="57"/>
-      <c r="AB1" s="57"/>
-      <c r="AC1" s="57"/>
-      <c r="AD1" s="57"/>
-      <c r="AE1" s="57"/>
-      <c r="AF1" s="57"/>
-      <c r="AG1" s="57"/>
-      <c r="AH1" s="57"/>
-      <c r="AI1" s="57"/>
-      <c r="AJ1" s="57"/>
-      <c r="AK1" s="57"/>
-      <c r="AL1" s="57"/>
-      <c r="AM1" s="57"/>
-      <c r="AN1" s="57"/>
-      <c r="AO1" s="57"/>
-      <c r="AP1" s="57"/>
-      <c r="AQ1" s="57"/>
-      <c r="AR1" s="57"/>
-      <c r="AS1" s="57"/>
-      <c r="AT1" s="57"/>
-      <c r="AU1" s="57"/>
-      <c r="AV1" s="57"/>
-      <c r="AW1" s="57"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
+      <c r="U1" s="63"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="63"/>
+      <c r="Y1" s="63"/>
+      <c r="Z1" s="63"/>
+      <c r="AA1" s="63"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="63"/>
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
+      <c r="AH1" s="63"/>
+      <c r="AI1" s="63"/>
+      <c r="AJ1" s="63"/>
+      <c r="AK1" s="63"/>
+      <c r="AL1" s="63"/>
+      <c r="AM1" s="63"/>
+      <c r="AN1" s="63"/>
+      <c r="AO1" s="63"/>
+      <c r="AP1" s="63"/>
+      <c r="AQ1" s="63"/>
+      <c r="AR1" s="63"/>
+      <c r="AS1" s="63"/>
+      <c r="AT1" s="63"/>
+      <c r="AU1" s="63"/>
+      <c r="AV1" s="63"/>
+      <c r="AW1" s="63"/>
     </row>
     <row r="2" spans="1:77" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="66" t="s">
+      <c r="B2" s="61"/>
+      <c r="C2" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="47">
+      <c r="D2" s="59">
         <v>46268</v>
       </c>
-      <c r="E2" s="47">
+      <c r="E2" s="59">
         <v>46272</v>
       </c>
-      <c r="F2" s="47">
+      <c r="F2" s="59">
         <v>46273</v>
       </c>
-      <c r="G2" s="47">
+      <c r="G2" s="59">
         <v>46275</v>
       </c>
-      <c r="H2" s="47">
+      <c r="H2" s="59">
         <v>46279</v>
       </c>
-      <c r="I2" s="49">
+      <c r="I2" s="45">
         <v>46282</v>
       </c>
-      <c r="J2" s="47">
+      <c r="J2" s="59">
         <v>46286</v>
       </c>
-      <c r="K2" s="47">
+      <c r="K2" s="59">
         <v>46287</v>
       </c>
-      <c r="L2" s="49">
+      <c r="L2" s="45">
         <v>46289</v>
       </c>
-      <c r="M2" s="47">
+      <c r="M2" s="59">
         <v>46293</v>
       </c>
-      <c r="N2" s="49">
+      <c r="N2" s="45">
         <v>46296</v>
       </c>
-      <c r="O2" s="47">
+      <c r="O2" s="59">
         <v>46300</v>
       </c>
-      <c r="P2" s="47">
+      <c r="P2" s="59">
         <v>46301</v>
       </c>
-      <c r="Q2" s="49">
+      <c r="Q2" s="45">
         <v>46303</v>
       </c>
-      <c r="R2" s="47">
+      <c r="R2" s="59">
         <v>46307</v>
       </c>
-      <c r="S2" s="49">
+      <c r="S2" s="45">
         <v>46310</v>
       </c>
-      <c r="T2" s="47">
+      <c r="T2" s="59">
         <v>46314</v>
       </c>
-      <c r="U2" s="47">
+      <c r="U2" s="59">
         <v>46315</v>
       </c>
-      <c r="V2" s="49">
+      <c r="V2" s="45">
         <v>46317</v>
       </c>
-      <c r="W2" s="47">
+      <c r="W2" s="59">
         <v>46321</v>
       </c>
-      <c r="X2" s="47">
+      <c r="X2" s="59">
         <v>46324</v>
       </c>
-      <c r="Y2" s="47">
+      <c r="Y2" s="59">
         <v>46328</v>
       </c>
-      <c r="Z2" s="47">
+      <c r="Z2" s="59">
         <v>46329</v>
       </c>
-      <c r="AA2" s="47">
+      <c r="AA2" s="59">
         <v>46331</v>
       </c>
-      <c r="AB2" s="47">
+      <c r="AB2" s="59">
         <v>46335</v>
       </c>
-      <c r="AC2" s="47">
+      <c r="AC2" s="59">
         <v>46338</v>
       </c>
-      <c r="AD2" s="47">
+      <c r="AD2" s="59">
         <v>46342</v>
       </c>
-      <c r="AE2" s="47">
+      <c r="AE2" s="59">
         <v>46343</v>
       </c>
-      <c r="AF2" s="47">
+      <c r="AF2" s="59">
         <v>46345</v>
       </c>
-      <c r="AG2" s="47">
+      <c r="AG2" s="59">
         <v>46349</v>
       </c>
-      <c r="AH2" s="47">
+      <c r="AH2" s="59">
         <v>46352</v>
       </c>
-      <c r="AI2" s="47">
+      <c r="AI2" s="59">
         <v>46356</v>
       </c>
-      <c r="AJ2" s="49">
+      <c r="AJ2" s="45">
         <v>46357</v>
       </c>
-      <c r="AK2" s="49">
+      <c r="AK2" s="45">
         <v>46359</v>
       </c>
-      <c r="AL2" s="49">
+      <c r="AL2" s="45">
         <v>46363</v>
       </c>
-      <c r="AM2" s="49">
+      <c r="AM2" s="45">
         <v>46366</v>
       </c>
-      <c r="AN2" s="49">
+      <c r="AN2" s="45">
         <v>46370</v>
       </c>
-      <c r="AO2" s="49">
+      <c r="AO2" s="45">
         <v>46371</v>
       </c>
-      <c r="AP2" s="49">
+      <c r="AP2" s="45">
         <v>46373</v>
       </c>
-      <c r="AQ2" s="49">
+      <c r="AQ2" s="45">
         <v>46377</v>
       </c>
-      <c r="AR2" s="49">
+      <c r="AR2" s="45">
         <v>46380</v>
       </c>
-      <c r="AS2" s="58" t="s">
+      <c r="AS2" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="AT2" s="58"/>
-      <c r="AU2" s="51" t="s">
+      <c r="AT2" s="61"/>
+      <c r="AU2" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="AV2" s="52"/>
-      <c r="AW2" s="53"/>
-      <c r="AX2" s="51" t="s">
+      <c r="AV2" s="48"/>
+      <c r="AW2" s="49"/>
+      <c r="AX2" s="47" t="s">
         <v>160</v>
       </c>
-      <c r="AY2" s="52"/>
-      <c r="AZ2" s="53"/>
-      <c r="BA2" s="51" t="s">
+      <c r="AY2" s="48"/>
+      <c r="AZ2" s="49"/>
+      <c r="BA2" s="47" t="s">
         <v>161</v>
       </c>
-      <c r="BB2" s="52"/>
-      <c r="BC2" s="53"/>
-      <c r="BD2" s="51" t="s">
+      <c r="BB2" s="48"/>
+      <c r="BC2" s="49"/>
+      <c r="BD2" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="BE2" s="52"/>
-      <c r="BF2" s="53"/>
-      <c r="BG2" s="51" t="s">
+      <c r="BE2" s="48"/>
+      <c r="BF2" s="49"/>
+      <c r="BG2" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="BH2" s="52"/>
-      <c r="BI2" s="52"/>
-      <c r="BJ2" s="53"/>
-      <c r="BK2" s="51" t="s">
+      <c r="BH2" s="48"/>
+      <c r="BI2" s="48"/>
+      <c r="BJ2" s="49"/>
+      <c r="BK2" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="BL2" s="52"/>
-      <c r="BM2" s="52"/>
-      <c r="BN2" s="53" t="s">
+      <c r="BL2" s="48"/>
+      <c r="BM2" s="48"/>
+      <c r="BN2" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="BO2" s="51" t="s">
+      <c r="BO2" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="BP2" s="52"/>
-      <c r="BQ2" s="53"/>
-      <c r="BR2" s="51" t="s">
+      <c r="BP2" s="48"/>
+      <c r="BQ2" s="49"/>
+      <c r="BR2" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="BS2" s="52"/>
-      <c r="BT2" s="53"/>
+      <c r="BS2" s="48"/>
+      <c r="BT2" s="49"/>
     </row>
     <row r="3" spans="1:77" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1597,76 +1602,76 @@
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="48"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="50"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="50"/>
-      <c r="W3" s="48"/>
-      <c r="X3" s="48"/>
-      <c r="Y3" s="48"/>
-      <c r="Z3" s="48"/>
-      <c r="AA3" s="48"/>
-      <c r="AB3" s="48"/>
-      <c r="AC3" s="48"/>
-      <c r="AD3" s="48"/>
-      <c r="AE3" s="48"/>
-      <c r="AF3" s="48"/>
-      <c r="AG3" s="48"/>
-      <c r="AH3" s="48"/>
-      <c r="AI3" s="48"/>
-      <c r="AJ3" s="50"/>
-      <c r="AK3" s="50"/>
-      <c r="AL3" s="50"/>
-      <c r="AM3" s="50"/>
-      <c r="AN3" s="50"/>
-      <c r="AO3" s="50"/>
-      <c r="AP3" s="50"/>
-      <c r="AQ3" s="50"/>
-      <c r="AR3" s="50"/>
-      <c r="AS3" s="58"/>
-      <c r="AT3" s="58"/>
-      <c r="AU3" s="54"/>
-      <c r="AV3" s="59"/>
-      <c r="AW3" s="56"/>
-      <c r="AX3" s="54"/>
-      <c r="AY3" s="55"/>
-      <c r="AZ3" s="56"/>
-      <c r="BA3" s="54"/>
-      <c r="BB3" s="55"/>
-      <c r="BC3" s="56"/>
-      <c r="BD3" s="54"/>
-      <c r="BE3" s="55"/>
-      <c r="BF3" s="56"/>
-      <c r="BG3" s="54"/>
-      <c r="BH3" s="55"/>
-      <c r="BI3" s="55"/>
-      <c r="BJ3" s="56"/>
-      <c r="BK3" s="54"/>
-      <c r="BL3" s="55"/>
-      <c r="BM3" s="55"/>
-      <c r="BN3" s="56"/>
-      <c r="BO3" s="54"/>
-      <c r="BP3" s="55"/>
-      <c r="BQ3" s="56"/>
-      <c r="BR3" s="54"/>
-      <c r="BS3" s="55"/>
-      <c r="BT3" s="56"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="60"/>
+      <c r="P3" s="60"/>
+      <c r="Q3" s="46"/>
+      <c r="R3" s="60"/>
+      <c r="S3" s="46"/>
+      <c r="T3" s="60"/>
+      <c r="U3" s="60"/>
+      <c r="V3" s="46"/>
+      <c r="W3" s="60"/>
+      <c r="X3" s="60"/>
+      <c r="Y3" s="60"/>
+      <c r="Z3" s="60"/>
+      <c r="AA3" s="60"/>
+      <c r="AB3" s="60"/>
+      <c r="AC3" s="60"/>
+      <c r="AD3" s="60"/>
+      <c r="AE3" s="60"/>
+      <c r="AF3" s="60"/>
+      <c r="AG3" s="60"/>
+      <c r="AH3" s="60"/>
+      <c r="AI3" s="60"/>
+      <c r="AJ3" s="46"/>
+      <c r="AK3" s="46"/>
+      <c r="AL3" s="46"/>
+      <c r="AM3" s="46"/>
+      <c r="AN3" s="46"/>
+      <c r="AO3" s="46"/>
+      <c r="AP3" s="46"/>
+      <c r="AQ3" s="46"/>
+      <c r="AR3" s="46"/>
+      <c r="AS3" s="61"/>
+      <c r="AT3" s="61"/>
+      <c r="AU3" s="50"/>
+      <c r="AV3" s="64"/>
+      <c r="AW3" s="52"/>
+      <c r="AX3" s="50"/>
+      <c r="AY3" s="51"/>
+      <c r="AZ3" s="52"/>
+      <c r="BA3" s="50"/>
+      <c r="BB3" s="51"/>
+      <c r="BC3" s="52"/>
+      <c r="BD3" s="50"/>
+      <c r="BE3" s="51"/>
+      <c r="BF3" s="52"/>
+      <c r="BG3" s="50"/>
+      <c r="BH3" s="51"/>
+      <c r="BI3" s="51"/>
+      <c r="BJ3" s="52"/>
+      <c r="BK3" s="50"/>
+      <c r="BL3" s="51"/>
+      <c r="BM3" s="51"/>
+      <c r="BN3" s="52"/>
+      <c r="BO3" s="50"/>
+      <c r="BP3" s="51"/>
+      <c r="BQ3" s="52"/>
+      <c r="BR3" s="50"/>
+      <c r="BS3" s="51"/>
+      <c r="BT3" s="52"/>
     </row>
     <row r="4" spans="1:77" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
@@ -1699,7 +1704,7 @@
       <c r="L4" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="M4" s="39" t="s">
+      <c r="M4" s="38" t="s">
         <v>117</v>
       </c>
       <c r="N4" s="17" t="s">
@@ -1708,19 +1713,21 @@
       <c r="O4" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P4" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q4" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="R4" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="S4" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="T4" s="17"/>
+      <c r="P4" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q4" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R4" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S4" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T4" s="65" t="s">
+        <v>117</v>
+      </c>
       <c r="U4" s="17"/>
       <c r="V4" s="17"/>
       <c r="W4" s="17"/>
@@ -1748,14 +1755,14 @@
       <c r="AS4" s="18"/>
       <c r="AT4" s="17"/>
       <c r="AU4" s="19"/>
-      <c r="AV4" s="41" t="s">
+      <c r="AV4" s="40" t="s">
         <v>176</v>
       </c>
       <c r="AW4" s="18"/>
-      <c r="AX4" s="33" t="s">
+      <c r="AX4" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="AY4" s="34" t="s">
+      <c r="AY4" s="33" t="s">
         <v>129</v>
       </c>
       <c r="AZ4" s="21"/>
@@ -1766,13 +1773,13 @@
         <v>35</v>
       </c>
       <c r="BC4" s="18"/>
-      <c r="BD4" s="34" t="s">
+      <c r="BD4" s="33" t="s">
         <v>169</v>
       </c>
-      <c r="BE4" s="34" t="s">
+      <c r="BE4" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="BF4" s="34"/>
+      <c r="BF4" s="33"/>
       <c r="BG4" s="17"/>
       <c r="BH4" s="17"/>
       <c r="BI4" s="17"/>
@@ -1828,19 +1835,21 @@
       <c r="O5" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P5" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q5" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="R5" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="S5" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="T5" s="17"/>
+      <c r="P5" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q5" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R5" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S5" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T5" s="28" t="s">
+        <v>117</v>
+      </c>
       <c r="U5" s="17"/>
       <c r="V5" s="17"/>
       <c r="W5" s="17"/>
@@ -1867,19 +1876,19 @@
       <c r="AR5" s="17"/>
       <c r="AS5" s="18"/>
       <c r="AT5" s="17"/>
-      <c r="AU5" s="44" t="s">
+      <c r="AU5" s="42" t="s">
         <v>180</v>
       </c>
-      <c r="AV5" s="45" t="s">
+      <c r="AV5" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="AW5" s="46">
+      <c r="AW5" s="44">
         <v>46307</v>
       </c>
-      <c r="AX5" s="33" t="s">
+      <c r="AX5" s="32" t="s">
         <v>130</v>
       </c>
-      <c r="AY5" s="34" t="s">
+      <c r="AY5" s="33" t="s">
         <v>131</v>
       </c>
       <c r="AZ5" s="21"/>
@@ -1890,13 +1899,13 @@
         <v>79</v>
       </c>
       <c r="BC5" s="18"/>
-      <c r="BD5" s="34" t="s">
+      <c r="BD5" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="BE5" s="34" t="s">
+      <c r="BE5" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="BF5" s="34"/>
+      <c r="BF5" s="33"/>
       <c r="BG5" s="18">
         <v>46310</v>
       </c>
@@ -1962,7 +1971,7 @@
       <c r="L6" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="M6" s="40" t="s">
+      <c r="M6" s="39" t="s">
         <v>117</v>
       </c>
       <c r="N6" s="17" t="s">
@@ -1971,19 +1980,21 @@
       <c r="O6" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P6" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q6" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="R6" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="S6" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="T6" s="17"/>
+      <c r="P6" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q6" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="R6" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S6" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T6" s="65" t="s">
+        <v>117</v>
+      </c>
       <c r="U6" s="17"/>
       <c r="V6" s="17"/>
       <c r="W6" s="17"/>
@@ -2011,14 +2022,14 @@
       <c r="AS6" s="18"/>
       <c r="AT6" s="17"/>
       <c r="AU6" s="19"/>
-      <c r="AV6" s="42" t="s">
+      <c r="AV6" s="41" t="s">
         <v>176</v>
       </c>
       <c r="AW6" s="21"/>
-      <c r="AX6" s="33" t="s">
+      <c r="AX6" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="AY6" s="34" t="s">
+      <c r="AY6" s="33" t="s">
         <v>133</v>
       </c>
       <c r="AZ6" s="21"/>
@@ -2032,8 +2043,8 @@
       <c r="BD6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="BE6" s="34"/>
-      <c r="BF6" s="34"/>
+      <c r="BE6" s="33"/>
+      <c r="BF6" s="33"/>
       <c r="BG6" s="17"/>
       <c r="BH6" s="22"/>
       <c r="BI6" s="17"/>
@@ -2086,28 +2097,30 @@
       <c r="L7" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="M7" s="38" t="s">
+      <c r="M7" s="37" t="s">
         <v>117</v>
       </c>
       <c r="N7" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="O7" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="P7" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q7" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="R7" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="S7" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="T7" s="17"/>
+      <c r="O7" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="P7" s="66" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q7" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R7" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S7" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T7" s="28" t="s">
+        <v>117</v>
+      </c>
       <c r="U7" s="17"/>
       <c r="V7" s="17"/>
       <c r="W7" s="17"/>
@@ -2135,10 +2148,10 @@
       <c r="AS7" s="17"/>
       <c r="AT7" s="17"/>
       <c r="AU7" s="19"/>
-      <c r="AV7" s="41" t="s">
+      <c r="AV7" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="AW7" s="25"/>
+      <c r="AW7" s="24"/>
       <c r="AX7" s="20" t="s">
         <v>135</v>
       </c>
@@ -2146,7 +2159,7 @@
         <v>134</v>
       </c>
       <c r="AZ7" s="17"/>
-      <c r="BA7" s="34">
+      <c r="BA7" s="33">
         <v>9.3000000000000007</v>
       </c>
       <c r="BB7" s="7" t="s">
@@ -2156,8 +2169,8 @@
       <c r="BD7" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="BE7" s="34"/>
-      <c r="BF7" s="34"/>
+      <c r="BE7" s="33"/>
+      <c r="BF7" s="33"/>
       <c r="BG7" s="18">
         <v>46310</v>
       </c>
@@ -2223,19 +2236,21 @@
       <c r="O8" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="P8" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q8" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="R8" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="S8" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="T8" s="17"/>
+      <c r="P8" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q8" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="R8" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S8" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="T8" s="28" t="s">
+        <v>117</v>
+      </c>
       <c r="U8" s="17"/>
       <c r="V8" s="17"/>
       <c r="W8" s="17"/>
@@ -2264,22 +2279,22 @@
       <c r="AT8" s="17"/>
       <c r="AU8" s="19"/>
       <c r="AV8" s="19"/>
-      <c r="AW8" s="25"/>
-      <c r="AX8" s="36" t="s">
+      <c r="AW8" s="24"/>
+      <c r="AX8" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="AY8" s="34" t="s">
+      <c r="AY8" s="33" t="s">
         <v>157</v>
       </c>
       <c r="AZ8" s="17"/>
-      <c r="BA8" s="34">
+      <c r="BA8" s="33">
         <v>9.4</v>
       </c>
       <c r="BB8" s="7" t="s">
         <v>163</v>
       </c>
       <c r="BC8" s="17"/>
-      <c r="BD8" s="37" t="s">
+      <c r="BD8" s="36" t="s">
         <v>21</v>
       </c>
       <c r="BE8" s="17"/>
@@ -2336,7 +2351,7 @@
       <c r="L9" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="M9" s="39" t="s">
+      <c r="M9" s="38" t="s">
         <v>117</v>
       </c>
       <c r="N9" s="17" t="s">
@@ -2345,19 +2360,21 @@
       <c r="O9" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P9" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q9" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="R9" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="S9" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="T9" s="17"/>
+      <c r="P9" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q9" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R9" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S9" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T9" s="28" t="s">
+        <v>117</v>
+      </c>
       <c r="U9" s="17"/>
       <c r="V9" s="17"/>
       <c r="W9" s="17"/>
@@ -2385,18 +2402,18 @@
       <c r="AS9" s="18"/>
       <c r="AT9" s="17"/>
       <c r="AU9" s="19"/>
-      <c r="AV9" s="41" t="s">
+      <c r="AV9" s="40" t="s">
         <v>176</v>
       </c>
       <c r="AW9" s="21"/>
-      <c r="AX9" s="27" t="s">
+      <c r="AX9" s="26" t="s">
         <v>138</v>
       </c>
       <c r="AY9" s="19" t="s">
         <v>139</v>
       </c>
       <c r="AZ9" s="21"/>
-      <c r="BA9" s="34">
+      <c r="BA9" s="33">
         <v>9.1</v>
       </c>
       <c r="BB9" s="7" t="s">
@@ -2467,19 +2484,21 @@
       <c r="O10" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P10" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q10" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="R10" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="S10" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="T10" s="17"/>
+      <c r="P10" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q10" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R10" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S10" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T10" s="28" t="s">
+        <v>118</v>
+      </c>
       <c r="U10" s="17"/>
       <c r="V10" s="17"/>
       <c r="W10" s="17"/>
@@ -2507,22 +2526,22 @@
       <c r="AS10" s="18"/>
       <c r="AT10" s="17"/>
       <c r="AU10" s="19"/>
-      <c r="AV10" s="42"/>
+      <c r="AV10" s="41"/>
       <c r="AW10" s="21"/>
-      <c r="AX10" s="33" t="s">
+      <c r="AX10" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="AY10" s="34" t="s">
+      <c r="AY10" s="33" t="s">
         <v>137</v>
       </c>
       <c r="AZ10" s="18"/>
-      <c r="BA10" s="34" t="s">
+      <c r="BA10" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="BB10" s="34" t="s">
+      <c r="BB10" s="33" t="s">
         <v>165</v>
       </c>
-      <c r="BC10" s="34"/>
+      <c r="BC10" s="33"/>
       <c r="BD10" s="17"/>
       <c r="BE10" s="17"/>
       <c r="BF10" s="17"/>
@@ -2587,19 +2606,21 @@
       <c r="O11" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P11" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q11" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="R11" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="S11" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="T11" s="17"/>
+      <c r="P11" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q11" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R11" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S11" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T11" s="28" t="s">
+        <v>117</v>
+      </c>
       <c r="U11" s="17"/>
       <c r="V11" s="17"/>
       <c r="W11" s="17"/>
@@ -2627,24 +2648,24 @@
       <c r="AS11" s="18"/>
       <c r="AT11" s="17"/>
       <c r="AU11" s="19"/>
-      <c r="AV11" s="41" t="s">
+      <c r="AV11" s="40" t="s">
         <v>176</v>
       </c>
       <c r="AW11" s="21"/>
-      <c r="AX11" s="33" t="s">
+      <c r="AX11" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="AY11" s="34" t="s">
+      <c r="AY11" s="33" t="s">
         <v>145</v>
       </c>
       <c r="AZ11" s="18"/>
-      <c r="BA11" s="34" t="s">
+      <c r="BA11" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="BB11" s="34" t="s">
+      <c r="BB11" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="BC11" s="34"/>
+      <c r="BC11" s="33"/>
       <c r="BD11" s="17"/>
       <c r="BE11" s="17"/>
       <c r="BF11" s="18"/>
@@ -2677,7 +2698,7 @@
       <c r="A12" s="3">
         <v>9</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="30" t="s">
         <v>92</v>
       </c>
       <c r="C12" s="4">
@@ -2715,19 +2736,21 @@
       <c r="O12" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="P12" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q12" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="R12" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="S12" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="T12" s="17"/>
+      <c r="P12" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q12" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R12" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S12" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T12" s="28" t="s">
+        <v>117</v>
+      </c>
       <c r="U12" s="17"/>
       <c r="V12" s="17"/>
       <c r="W12" s="17"/>
@@ -2757,10 +2780,10 @@
       <c r="AU12" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="AV12" s="41" t="s">
+      <c r="AV12" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="AW12" s="46">
+      <c r="AW12" s="44">
         <v>46307</v>
       </c>
       <c r="AX12" s="20" t="s">
@@ -2770,11 +2793,11 @@
         <v>147</v>
       </c>
       <c r="AZ12" s="21"/>
-      <c r="BA12" s="34" t="s">
+      <c r="BA12" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="BB12" s="34"/>
-      <c r="BC12" s="34"/>
+      <c r="BB12" s="33"/>
+      <c r="BC12" s="33"/>
       <c r="BD12" s="17"/>
       <c r="BE12" s="17"/>
       <c r="BF12" s="18"/>
@@ -2839,19 +2862,21 @@
       <c r="O13" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="P13" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q13" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="R13" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="S13" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="T13" s="17"/>
+      <c r="P13" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q13" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R13" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="S13" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T13" s="65" t="s">
+        <v>117</v>
+      </c>
       <c r="U13" s="17"/>
       <c r="V13" s="17"/>
       <c r="W13" s="17"/>
@@ -2881,10 +2906,10 @@
       <c r="AU13" s="19"/>
       <c r="AV13" s="19"/>
       <c r="AW13" s="21"/>
-      <c r="AX13" s="33" t="s">
+      <c r="AX13" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="AY13" s="34" t="s">
+      <c r="AY13" s="33" t="s">
         <v>149</v>
       </c>
       <c r="AZ13" s="18"/>
@@ -2946,7 +2971,7 @@
       <c r="L14" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="M14" s="38" t="s">
+      <c r="M14" s="37" t="s">
         <v>117</v>
       </c>
       <c r="N14" s="17" t="s">
@@ -2955,19 +2980,21 @@
       <c r="O14" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P14" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q14" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="R14" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="S14" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="T14" s="17"/>
+      <c r="P14" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q14" s="67" t="s">
+        <v>117</v>
+      </c>
+      <c r="R14" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S14" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T14" s="65" t="s">
+        <v>117</v>
+      </c>
       <c r="U14" s="17"/>
       <c r="V14" s="17"/>
       <c r="W14" s="17"/>
@@ -2995,14 +3022,14 @@
       <c r="AS14" s="17"/>
       <c r="AT14" s="17"/>
       <c r="AU14" s="19"/>
-      <c r="AV14" s="41" t="s">
+      <c r="AV14" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="AW14" s="25"/>
-      <c r="AX14" s="36" t="s">
+      <c r="AW14" s="24"/>
+      <c r="AX14" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="AY14" s="34" t="s">
+      <c r="AY14" s="33" t="s">
         <v>151</v>
       </c>
       <c r="AZ14" s="17"/>
@@ -3077,19 +3104,21 @@
       <c r="O15" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P15" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q15" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="R15" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="S15" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="T15" s="17"/>
+      <c r="P15" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q15" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R15" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S15" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T15" s="28" t="s">
+        <v>117</v>
+      </c>
       <c r="U15" s="17"/>
       <c r="V15" s="17"/>
       <c r="W15" s="17"/>
@@ -3117,14 +3146,14 @@
       <c r="AS15" s="18"/>
       <c r="AT15" s="17"/>
       <c r="AU15" s="19"/>
-      <c r="AV15" s="41" t="s">
+      <c r="AV15" s="40" t="s">
         <v>176</v>
       </c>
       <c r="AW15" s="18"/>
-      <c r="AX15" s="33" t="s">
+      <c r="AX15" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="AY15" s="34" t="s">
+      <c r="AY15" s="33" t="s">
         <v>145</v>
       </c>
       <c r="AZ15" s="21"/>
@@ -3190,7 +3219,7 @@
       <c r="L16" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="M16" s="39" t="s">
+      <c r="M16" s="38" t="s">
         <v>117</v>
       </c>
       <c r="N16" s="17" t="s">
@@ -3199,19 +3228,21 @@
       <c r="O16" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P16" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q16" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="R16" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="S16" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="T16" s="17"/>
+      <c r="P16" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q16" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R16" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S16" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T16" s="65" t="s">
+        <v>117</v>
+      </c>
       <c r="U16" s="17"/>
       <c r="V16" s="17"/>
       <c r="W16" s="17"/>
@@ -3239,14 +3270,14 @@
       <c r="AS16" s="18"/>
       <c r="AT16" s="17"/>
       <c r="AU16" s="18"/>
-      <c r="AV16" s="41" t="s">
+      <c r="AV16" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="AW16" s="25"/>
-      <c r="AX16" s="33" t="s">
+      <c r="AW16" s="24"/>
+      <c r="AX16" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="AY16" s="34" t="s">
+      <c r="AY16" s="33" t="s">
         <v>129</v>
       </c>
       <c r="AZ16" s="18"/>
@@ -3261,7 +3292,7 @@
       <c r="BE16" s="22"/>
       <c r="BF16" s="18"/>
       <c r="BG16" s="17"/>
-      <c r="BH16" s="26"/>
+      <c r="BH16" s="25"/>
       <c r="BI16" s="17"/>
       <c r="BJ16" s="18"/>
       <c r="BK16" s="17"/>
@@ -3321,19 +3352,21 @@
       <c r="O17" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P17" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q17" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="R17" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="S17" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="T17" s="17"/>
+      <c r="P17" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q17" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R17" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S17" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T17" s="65" t="s">
+        <v>117</v>
+      </c>
       <c r="U17" s="17"/>
       <c r="V17" s="17"/>
       <c r="W17" s="17"/>
@@ -3361,14 +3394,14 @@
       <c r="AS17" s="18"/>
       <c r="AT17" s="17"/>
       <c r="AU17" s="19"/>
-      <c r="AV17" s="42" t="s">
+      <c r="AV17" s="41" t="s">
         <v>176</v>
       </c>
       <c r="AW17" s="21"/>
-      <c r="AX17" s="33" t="s">
+      <c r="AX17" s="32" t="s">
         <v>152</v>
       </c>
-      <c r="AY17" s="34" t="s">
+      <c r="AY17" s="33" t="s">
         <v>153</v>
       </c>
       <c r="AZ17" s="18"/>
@@ -3432,7 +3465,7 @@
       <c r="L18" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="M18" s="39" t="s">
+      <c r="M18" s="38" t="s">
         <v>117</v>
       </c>
       <c r="N18" s="17" t="s">
@@ -3441,19 +3474,21 @@
       <c r="O18" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P18" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q18" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="R18" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="S18" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="T18" s="17"/>
+      <c r="P18" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q18" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R18" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S18" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T18" s="28" t="s">
+        <v>117</v>
+      </c>
       <c r="U18" s="17"/>
       <c r="V18" s="17"/>
       <c r="W18" s="17"/>
@@ -3480,19 +3515,19 @@
       <c r="AR18" s="17"/>
       <c r="AS18" s="18"/>
       <c r="AT18" s="17"/>
-      <c r="AU18" s="44" t="s">
+      <c r="AU18" s="42" t="s">
         <v>181</v>
       </c>
-      <c r="AV18" s="45" t="s">
+      <c r="AV18" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="AW18" s="46">
+      <c r="AW18" s="44">
         <v>46307</v>
       </c>
-      <c r="AX18" s="35" t="s">
+      <c r="AX18" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="AY18" s="34" t="s">
+      <c r="AY18" s="33" t="s">
         <v>155</v>
       </c>
       <c r="AZ18" s="21"/>
@@ -3527,7 +3562,7 @@
       <c r="A19" s="3">
         <v>16</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="30" t="s">
         <v>99</v>
       </c>
       <c r="C19" s="4">
@@ -3554,7 +3589,7 @@
       <c r="L19" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="M19" s="40" t="s">
+      <c r="M19" s="39" t="s">
         <v>117</v>
       </c>
       <c r="N19" s="17" t="s">
@@ -3563,19 +3598,21 @@
       <c r="O19" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P19" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q19" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="R19" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="S19" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="T19" s="17"/>
+      <c r="P19" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q19" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R19" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S19" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T19" s="65" t="s">
+        <v>117</v>
+      </c>
       <c r="U19" s="17"/>
       <c r="V19" s="17"/>
       <c r="W19" s="17"/>
@@ -3603,14 +3640,14 @@
       <c r="AS19" s="18"/>
       <c r="AT19" s="17"/>
       <c r="AU19" s="19"/>
-      <c r="AV19" s="42" t="s">
+      <c r="AV19" s="41" t="s">
         <v>176</v>
       </c>
       <c r="AW19" s="21"/>
-      <c r="AX19" s="33" t="s">
+      <c r="AX19" s="32" t="s">
         <v>152</v>
       </c>
-      <c r="AY19" s="34" t="s">
+      <c r="AY19" s="33" t="s">
         <v>153</v>
       </c>
       <c r="AZ19" s="18"/>
@@ -3672,7 +3709,7 @@
       <c r="L20" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="M20" s="39" t="s">
+      <c r="M20" s="38" t="s">
         <v>117</v>
       </c>
       <c r="N20" s="17" t="s">
@@ -3681,19 +3718,21 @@
       <c r="O20" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P20" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q20" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="R20" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="S20" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="T20" s="17"/>
+      <c r="P20" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q20" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R20" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S20" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T20" s="28" t="s">
+        <v>117</v>
+      </c>
       <c r="U20" s="17"/>
       <c r="V20" s="17"/>
       <c r="W20" s="17"/>
@@ -3721,11 +3760,11 @@
       <c r="AS20" s="18"/>
       <c r="AT20" s="17"/>
       <c r="AU20" s="19"/>
-      <c r="AV20" s="41" t="s">
+      <c r="AV20" s="40" t="s">
         <v>176</v>
       </c>
       <c r="AW20" s="21"/>
-      <c r="AX20" s="27" t="s">
+      <c r="AX20" s="26" t="s">
         <v>138</v>
       </c>
       <c r="AY20" s="19" t="s">
@@ -3733,7 +3772,7 @@
       </c>
       <c r="AZ20" s="18"/>
       <c r="BA20" s="17"/>
-      <c r="BB20" s="28"/>
+      <c r="BB20" s="27"/>
       <c r="BC20" s="17"/>
       <c r="BD20" s="17"/>
       <c r="BE20" s="17"/>
@@ -3799,19 +3838,21 @@
       <c r="O21" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="P21" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q21" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="R21" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="S21" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="T21" s="17"/>
+      <c r="P21" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q21" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R21" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S21" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="T21" s="28" t="s">
+        <v>117</v>
+      </c>
       <c r="U21" s="17"/>
       <c r="V21" s="17"/>
       <c r="W21" s="17"/>
@@ -3841,10 +3882,10 @@
       <c r="AU21" s="19"/>
       <c r="AV21" s="19"/>
       <c r="AW21" s="21"/>
-      <c r="AX21" s="36" t="s">
+      <c r="AX21" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="AY21" s="34" t="s">
+      <c r="AY21" s="33" t="s">
         <v>157</v>
       </c>
       <c r="AZ21" s="21"/>
@@ -3915,19 +3956,21 @@
       <c r="O22" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="P22" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q22" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="R22" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="S22" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="T22" s="17"/>
+      <c r="P22" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q22" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R22" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S22" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="T22" s="28" t="s">
+        <v>117</v>
+      </c>
       <c r="U22" s="17"/>
       <c r="V22" s="17"/>
       <c r="W22" s="17"/>
@@ -3957,7 +4000,7 @@
       <c r="AU22" s="19"/>
       <c r="AV22" s="19"/>
       <c r="AW22" s="21"/>
-      <c r="AX22" s="27" t="s">
+      <c r="AX22" s="26" t="s">
         <v>140</v>
       </c>
       <c r="AY22" s="7" t="s">
@@ -4031,19 +4074,21 @@
       <c r="O23" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P23" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q23" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="R23" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="S23" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="T23" s="17"/>
+      <c r="P23" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q23" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R23" s="67" t="s">
+        <v>117</v>
+      </c>
+      <c r="S23" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T23" s="28" t="s">
+        <v>117</v>
+      </c>
       <c r="U23" s="17"/>
       <c r="V23" s="17"/>
       <c r="W23" s="17"/>
@@ -4073,7 +4118,7 @@
       <c r="AU23" s="18"/>
       <c r="AV23" s="19"/>
       <c r="AW23" s="21"/>
-      <c r="AX23" s="26" t="s">
+      <c r="AX23" s="25" t="s">
         <v>158</v>
       </c>
       <c r="AY23" s="19"/>
@@ -4085,7 +4130,7 @@
       <c r="BE23" s="22"/>
       <c r="BF23" s="18"/>
       <c r="BG23" s="17"/>
-      <c r="BH23" s="26"/>
+      <c r="BH23" s="25"/>
       <c r="BI23" s="17"/>
       <c r="BJ23" s="18"/>
       <c r="BK23" s="17"/>
@@ -4145,19 +4190,21 @@
       <c r="O24" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P24" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q24" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="R24" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="S24" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="T24" s="17"/>
+      <c r="P24" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q24" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R24" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S24" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T24" s="28" t="s">
+        <v>118</v>
+      </c>
       <c r="U24" s="17"/>
       <c r="V24" s="17"/>
       <c r="W24" s="17"/>
@@ -4184,16 +4231,16 @@
       <c r="AR24" s="17"/>
       <c r="AS24" s="17"/>
       <c r="AT24" s="17"/>
-      <c r="AU24" s="44" t="s">
+      <c r="AU24" s="42" t="s">
         <v>179</v>
       </c>
-      <c r="AV24" s="45" t="s">
+      <c r="AV24" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="AW24" s="46">
+      <c r="AW24" s="44">
         <v>46307</v>
       </c>
-      <c r="AX24" s="26" t="s">
+      <c r="AX24" s="25" t="s">
         <v>159</v>
       </c>
       <c r="AY24" s="17"/>
@@ -4271,19 +4318,21 @@
       <c r="O25" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P25" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q25" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="R25" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="S25" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="T25" s="17"/>
+      <c r="P25" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q25" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="R25" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S25" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T25" s="28" t="s">
+        <v>117</v>
+      </c>
       <c r="U25" s="17"/>
       <c r="V25" s="17"/>
       <c r="W25" s="17"/>
@@ -4313,7 +4362,7 @@
       <c r="AU25" s="19"/>
       <c r="AV25" s="19"/>
       <c r="AW25" s="21"/>
-      <c r="AX25" s="26" t="s">
+      <c r="AX25" s="25" t="s">
         <v>50</v>
       </c>
       <c r="AY25" s="19"/>
@@ -4376,61 +4425,63 @@
       <c r="L26" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="M26" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="N26" s="29" t="s">
+      <c r="M26" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="N26" s="28" t="s">
         <v>117</v>
       </c>
       <c r="O26" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P26" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q26" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="R26" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="S26" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-      <c r="W26" s="29"/>
-      <c r="X26" s="29"/>
-      <c r="Y26" s="29"/>
-      <c r="Z26" s="29"/>
-      <c r="AA26" s="29"/>
-      <c r="AB26" s="29"/>
-      <c r="AC26" s="29"/>
-      <c r="AD26" s="29"/>
-      <c r="AE26" s="29"/>
-      <c r="AF26" s="29"/>
-      <c r="AG26" s="29"/>
-      <c r="AH26" s="29"/>
-      <c r="AI26" s="29"/>
-      <c r="AJ26" s="29"/>
-      <c r="AK26" s="29"/>
-      <c r="AL26" s="29"/>
-      <c r="AM26" s="29"/>
-      <c r="AN26" s="29"/>
-      <c r="AO26" s="29"/>
-      <c r="AP26" s="29"/>
-      <c r="AQ26" s="29"/>
-      <c r="AR26" s="29"/>
+      <c r="P26" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q26" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R26" s="67" t="s">
+        <v>117</v>
+      </c>
+      <c r="S26" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T26" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="U26" s="28"/>
+      <c r="V26" s="28"/>
+      <c r="W26" s="28"/>
+      <c r="X26" s="28"/>
+      <c r="Y26" s="28"/>
+      <c r="Z26" s="28"/>
+      <c r="AA26" s="28"/>
+      <c r="AB26" s="28"/>
+      <c r="AC26" s="28"/>
+      <c r="AD26" s="28"/>
+      <c r="AE26" s="28"/>
+      <c r="AF26" s="28"/>
+      <c r="AG26" s="28"/>
+      <c r="AH26" s="28"/>
+      <c r="AI26" s="28"/>
+      <c r="AJ26" s="28"/>
+      <c r="AK26" s="28"/>
+      <c r="AL26" s="28"/>
+      <c r="AM26" s="28"/>
+      <c r="AN26" s="28"/>
+      <c r="AO26" s="28"/>
+      <c r="AP26" s="28"/>
+      <c r="AQ26" s="28"/>
+      <c r="AR26" s="28"/>
       <c r="AS26" s="18"/>
-      <c r="AT26" s="29"/>
+      <c r="AT26" s="28"/>
       <c r="AU26" s="19"/>
       <c r="AV26" s="19"/>
       <c r="AW26" s="21"/>
       <c r="AX26" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="AY26" s="34" t="s">
+      <c r="AY26" s="33" t="s">
         <v>149</v>
       </c>
       <c r="AZ26" s="18"/>
@@ -4439,7 +4490,7 @@
       <c r="BC26" s="18"/>
       <c r="BD26" s="17"/>
       <c r="BE26" s="17"/>
-      <c r="BF26" s="29"/>
+      <c r="BF26" s="28"/>
       <c r="BG26" s="17"/>
       <c r="BH26" s="17"/>
       <c r="BI26" s="17"/>
@@ -4449,11 +4500,11 @@
       <c r="BM26" s="17"/>
       <c r="BN26" s="18"/>
       <c r="BO26" s="18"/>
-      <c r="BP26" s="29"/>
-      <c r="BQ26" s="29"/>
-      <c r="BR26" s="29"/>
-      <c r="BS26" s="29"/>
-      <c r="BT26" s="29"/>
+      <c r="BP26" s="28"/>
+      <c r="BQ26" s="28"/>
+      <c r="BR26" s="28"/>
+      <c r="BS26" s="28"/>
+      <c r="BT26" s="28"/>
       <c r="BU26" s="14">
         <v>22</v>
       </c>
@@ -4504,58 +4555,60 @@
       <c r="O27" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P27" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q27" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="R27" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="S27" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="T27" s="30"/>
-      <c r="U27" s="30"/>
-      <c r="V27" s="30"/>
-      <c r="W27" s="30"/>
-      <c r="X27" s="30"/>
-      <c r="Y27" s="30"/>
-      <c r="Z27" s="30"/>
-      <c r="AA27" s="30"/>
-      <c r="AB27" s="30"/>
-      <c r="AC27" s="30"/>
-      <c r="AD27" s="30"/>
-      <c r="AE27" s="30"/>
-      <c r="AF27" s="30"/>
-      <c r="AG27" s="30"/>
-      <c r="AH27" s="30"/>
-      <c r="AI27" s="30"/>
-      <c r="AJ27" s="30"/>
-      <c r="AK27" s="30"/>
-      <c r="AL27" s="30"/>
-      <c r="AM27" s="30"/>
-      <c r="AN27" s="30"/>
-      <c r="AO27" s="30"/>
-      <c r="AP27" s="30"/>
-      <c r="AQ27" s="30"/>
-      <c r="AR27" s="30"/>
+      <c r="P27" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q27" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R27" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S27" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="T27" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="U27" s="29"/>
+      <c r="V27" s="29"/>
+      <c r="W27" s="29"/>
+      <c r="X27" s="29"/>
+      <c r="Y27" s="29"/>
+      <c r="Z27" s="29"/>
+      <c r="AA27" s="29"/>
+      <c r="AB27" s="29"/>
+      <c r="AC27" s="29"/>
+      <c r="AD27" s="29"/>
+      <c r="AE27" s="29"/>
+      <c r="AF27" s="29"/>
+      <c r="AG27" s="29"/>
+      <c r="AH27" s="29"/>
+      <c r="AI27" s="29"/>
+      <c r="AJ27" s="29"/>
+      <c r="AK27" s="29"/>
+      <c r="AL27" s="29"/>
+      <c r="AM27" s="29"/>
+      <c r="AN27" s="29"/>
+      <c r="AO27" s="29"/>
+      <c r="AP27" s="29"/>
+      <c r="AQ27" s="29"/>
+      <c r="AR27" s="29"/>
       <c r="AS27" s="18"/>
-      <c r="AT27" s="30"/>
-      <c r="AU27" s="44" t="s">
+      <c r="AT27" s="29"/>
+      <c r="AU27" s="42" t="s">
         <v>180</v>
       </c>
-      <c r="AV27" s="45" t="s">
+      <c r="AV27" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="AW27" s="46">
+      <c r="AW27" s="44">
         <v>46307</v>
       </c>
       <c r="AX27" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="AY27" s="34" t="s">
+      <c r="AY27" s="33" t="s">
         <v>131</v>
       </c>
       <c r="AZ27" s="18"/>
@@ -4578,11 +4631,11 @@
       <c r="BM27" s="17"/>
       <c r="BN27" s="18"/>
       <c r="BO27" s="18"/>
-      <c r="BP27" s="30"/>
-      <c r="BQ27" s="30"/>
-      <c r="BR27" s="30"/>
-      <c r="BS27" s="30"/>
-      <c r="BT27" s="30"/>
+      <c r="BP27" s="29"/>
+      <c r="BQ27" s="29"/>
+      <c r="BR27" s="29"/>
+      <c r="BS27" s="29"/>
+      <c r="BT27" s="29"/>
       <c r="BU27">
         <v>23</v>
       </c>
@@ -4632,49 +4685,51 @@
       <c r="O28" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P28" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q28" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="R28" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="S28" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="T28" s="30"/>
-      <c r="U28" s="30"/>
-      <c r="V28" s="30"/>
-      <c r="W28" s="30"/>
-      <c r="X28" s="30"/>
-      <c r="Y28" s="30"/>
-      <c r="Z28" s="30"/>
-      <c r="AA28" s="30"/>
-      <c r="AB28" s="30"/>
-      <c r="AC28" s="30"/>
-      <c r="AD28" s="30"/>
-      <c r="AE28" s="30"/>
-      <c r="AF28" s="30"/>
-      <c r="AG28" s="30"/>
-      <c r="AH28" s="30"/>
-      <c r="AI28" s="30"/>
-      <c r="AJ28" s="30"/>
-      <c r="AK28" s="30"/>
-      <c r="AL28" s="30"/>
-      <c r="AM28" s="30"/>
-      <c r="AN28" s="30"/>
-      <c r="AO28" s="30"/>
-      <c r="AP28" s="30"/>
-      <c r="AQ28" s="30"/>
-      <c r="AR28" s="30"/>
+      <c r="P28" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q28" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="R28" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="S28" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T28" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="U28" s="29"/>
+      <c r="V28" s="29"/>
+      <c r="W28" s="29"/>
+      <c r="X28" s="29"/>
+      <c r="Y28" s="29"/>
+      <c r="Z28" s="29"/>
+      <c r="AA28" s="29"/>
+      <c r="AB28" s="29"/>
+      <c r="AC28" s="29"/>
+      <c r="AD28" s="29"/>
+      <c r="AE28" s="29"/>
+      <c r="AF28" s="29"/>
+      <c r="AG28" s="29"/>
+      <c r="AH28" s="29"/>
+      <c r="AI28" s="29"/>
+      <c r="AJ28" s="29"/>
+      <c r="AK28" s="29"/>
+      <c r="AL28" s="29"/>
+      <c r="AM28" s="29"/>
+      <c r="AN28" s="29"/>
+      <c r="AO28" s="29"/>
+      <c r="AP28" s="29"/>
+      <c r="AQ28" s="29"/>
+      <c r="AR28" s="29"/>
       <c r="AS28" s="18"/>
-      <c r="AT28" s="30"/>
+      <c r="AT28" s="29"/>
       <c r="AU28" s="19"/>
       <c r="AV28" s="19"/>
-      <c r="AW28" s="32"/>
-      <c r="AX28" s="27" t="s">
+      <c r="AW28" s="31"/>
+      <c r="AX28" s="26" t="s">
         <v>140</v>
       </c>
       <c r="AY28" s="7" t="s">
@@ -4682,7 +4737,7 @@
       </c>
       <c r="AZ28" s="18"/>
       <c r="BA28" s="17"/>
-      <c r="BB28" s="28"/>
+      <c r="BB28" s="27"/>
       <c r="BC28" s="17"/>
       <c r="BD28" s="17"/>
       <c r="BE28" s="17"/>
@@ -4696,11 +4751,11 @@
       <c r="BM28" s="17"/>
       <c r="BN28" s="18"/>
       <c r="BO28" s="18"/>
-      <c r="BP28" s="30"/>
-      <c r="BQ28" s="30"/>
-      <c r="BR28" s="30"/>
-      <c r="BS28" s="30"/>
-      <c r="BT28" s="30"/>
+      <c r="BP28" s="29"/>
+      <c r="BQ28" s="29"/>
+      <c r="BR28" s="29"/>
+      <c r="BS28" s="29"/>
+      <c r="BT28" s="29"/>
     </row>
     <row r="29" spans="1:75" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
@@ -4742,61 +4797,63 @@
       <c r="O29" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P29" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q29" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="R29" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="S29" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="T29" s="30"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="30"/>
-      <c r="W29" s="30"/>
-      <c r="X29" s="30"/>
-      <c r="Y29" s="30"/>
-      <c r="Z29" s="30"/>
-      <c r="AA29" s="30"/>
-      <c r="AB29" s="30"/>
-      <c r="AC29" s="30"/>
-      <c r="AD29" s="30"/>
-      <c r="AE29" s="30"/>
-      <c r="AF29" s="30"/>
-      <c r="AG29" s="30"/>
-      <c r="AH29" s="30"/>
-      <c r="AI29" s="30"/>
-      <c r="AJ29" s="30"/>
-      <c r="AK29" s="30"/>
-      <c r="AL29" s="30"/>
-      <c r="AM29" s="30"/>
-      <c r="AN29" s="30"/>
-      <c r="AO29" s="30"/>
-      <c r="AP29" s="30"/>
-      <c r="AQ29" s="30"/>
-      <c r="AR29" s="30"/>
+      <c r="P29" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q29" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="R29" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S29" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T29" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="U29" s="29"/>
+      <c r="V29" s="29"/>
+      <c r="W29" s="29"/>
+      <c r="X29" s="29"/>
+      <c r="Y29" s="29"/>
+      <c r="Z29" s="29"/>
+      <c r="AA29" s="29"/>
+      <c r="AB29" s="29"/>
+      <c r="AC29" s="29"/>
+      <c r="AD29" s="29"/>
+      <c r="AE29" s="29"/>
+      <c r="AF29" s="29"/>
+      <c r="AG29" s="29"/>
+      <c r="AH29" s="29"/>
+      <c r="AI29" s="29"/>
+      <c r="AJ29" s="29"/>
+      <c r="AK29" s="29"/>
+      <c r="AL29" s="29"/>
+      <c r="AM29" s="29"/>
+      <c r="AN29" s="29"/>
+      <c r="AO29" s="29"/>
+      <c r="AP29" s="29"/>
+      <c r="AQ29" s="29"/>
+      <c r="AR29" s="29"/>
       <c r="AS29" s="18"/>
-      <c r="AT29" s="30"/>
-      <c r="AU29" s="44" t="s">
+      <c r="AT29" s="29"/>
+      <c r="AU29" s="42" t="s">
         <v>179</v>
       </c>
-      <c r="AV29" s="45" t="s">
+      <c r="AV29" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="AW29" s="46">
+      <c r="AW29" s="44">
         <v>46307</v>
       </c>
-      <c r="AX29" s="26" t="s">
+      <c r="AX29" s="25" t="s">
         <v>159</v>
       </c>
       <c r="AY29" s="19"/>
       <c r="AZ29" s="18"/>
       <c r="BA29" s="17"/>
-      <c r="BB29" s="28"/>
+      <c r="BB29" s="27"/>
       <c r="BC29" s="17"/>
       <c r="BD29" s="17"/>
       <c r="BE29" s="17"/>
@@ -4810,11 +4867,11 @@
       <c r="BM29" s="17"/>
       <c r="BN29" s="18"/>
       <c r="BO29" s="18"/>
-      <c r="BP29" s="30"/>
-      <c r="BQ29" s="30"/>
-      <c r="BR29" s="30"/>
-      <c r="BS29" s="30"/>
-      <c r="BT29" s="30"/>
+      <c r="BP29" s="29"/>
+      <c r="BQ29" s="29"/>
+      <c r="BR29" s="29"/>
+      <c r="BS29" s="29"/>
+      <c r="BT29" s="29"/>
     </row>
     <row r="30" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
@@ -4847,7 +4904,7 @@
       <c r="L30" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="M30" s="39" t="s">
+      <c r="M30" s="38" t="s">
         <v>117</v>
       </c>
       <c r="N30" s="17" t="s">
@@ -4856,63 +4913,65 @@
       <c r="O30" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P30" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q30" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="R30" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="S30" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="T30" s="30"/>
-      <c r="U30" s="30"/>
-      <c r="V30" s="30"/>
-      <c r="W30" s="30"/>
-      <c r="X30" s="30"/>
-      <c r="Y30" s="30"/>
-      <c r="Z30" s="30"/>
-      <c r="AA30" s="30"/>
-      <c r="AB30" s="30"/>
-      <c r="AC30" s="30"/>
-      <c r="AD30" s="30"/>
-      <c r="AE30" s="30"/>
-      <c r="AF30" s="30"/>
-      <c r="AG30" s="30"/>
-      <c r="AH30" s="30"/>
-      <c r="AI30" s="30"/>
-      <c r="AJ30" s="30"/>
-      <c r="AK30" s="30"/>
-      <c r="AL30" s="30"/>
-      <c r="AM30" s="30"/>
-      <c r="AN30" s="30"/>
-      <c r="AO30" s="30"/>
-      <c r="AP30" s="30"/>
-      <c r="AQ30" s="30"/>
-      <c r="AR30" s="30"/>
+      <c r="P30" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q30" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R30" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S30" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T30" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="U30" s="29"/>
+      <c r="V30" s="29"/>
+      <c r="W30" s="29"/>
+      <c r="X30" s="29"/>
+      <c r="Y30" s="29"/>
+      <c r="Z30" s="29"/>
+      <c r="AA30" s="29"/>
+      <c r="AB30" s="29"/>
+      <c r="AC30" s="29"/>
+      <c r="AD30" s="29"/>
+      <c r="AE30" s="29"/>
+      <c r="AF30" s="29"/>
+      <c r="AG30" s="29"/>
+      <c r="AH30" s="29"/>
+      <c r="AI30" s="29"/>
+      <c r="AJ30" s="29"/>
+      <c r="AK30" s="29"/>
+      <c r="AL30" s="29"/>
+      <c r="AM30" s="29"/>
+      <c r="AN30" s="29"/>
+      <c r="AO30" s="29"/>
+      <c r="AP30" s="29"/>
+      <c r="AQ30" s="29"/>
+      <c r="AR30" s="29"/>
       <c r="AS30" s="18"/>
-      <c r="AT30" s="30"/>
-      <c r="AU30" s="44" t="s">
+      <c r="AT30" s="29"/>
+      <c r="AU30" s="42" t="s">
         <v>181</v>
       </c>
-      <c r="AV30" s="45" t="s">
+      <c r="AV30" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="AW30" s="46">
+      <c r="AW30" s="44">
         <v>46307</v>
       </c>
-      <c r="AX30" s="35" t="s">
+      <c r="AX30" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="AY30" s="34" t="s">
+      <c r="AY30" s="33" t="s">
         <v>155</v>
       </c>
       <c r="AZ30" s="18"/>
       <c r="BA30" s="17"/>
-      <c r="BB30" s="28"/>
+      <c r="BB30" s="27"/>
       <c r="BC30" s="17"/>
       <c r="BD30" s="17"/>
       <c r="BE30" s="17"/>
@@ -4926,11 +4985,11 @@
       <c r="BM30" s="17"/>
       <c r="BN30" s="18"/>
       <c r="BO30" s="18"/>
-      <c r="BP30" s="30"/>
-      <c r="BQ30" s="30"/>
-      <c r="BR30" s="30"/>
-      <c r="BS30" s="30"/>
-      <c r="BT30" s="30"/>
+      <c r="BP30" s="29"/>
+      <c r="BQ30" s="29"/>
+      <c r="BR30" s="29"/>
+      <c r="BS30" s="29"/>
+      <c r="BT30" s="29"/>
     </row>
     <row r="31" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
@@ -4963,7 +5022,7 @@
       <c r="L31" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="M31" s="38" t="s">
+      <c r="M31" s="37" t="s">
         <v>117</v>
       </c>
       <c r="N31" s="17" t="s">
@@ -4972,50 +5031,52 @@
       <c r="O31" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P31" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q31" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="R31" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="S31" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="T31" s="30"/>
-      <c r="U31" s="30"/>
-      <c r="V31" s="30"/>
-      <c r="W31" s="30"/>
-      <c r="X31" s="30"/>
-      <c r="Y31" s="30"/>
-      <c r="Z31" s="30"/>
-      <c r="AA31" s="30"/>
-      <c r="AB31" s="30"/>
-      <c r="AC31" s="30"/>
-      <c r="AD31" s="30"/>
-      <c r="AE31" s="30"/>
-      <c r="AF31" s="30"/>
-      <c r="AG31" s="30"/>
-      <c r="AH31" s="30"/>
-      <c r="AI31" s="30"/>
-      <c r="AJ31" s="30"/>
-      <c r="AK31" s="30"/>
-      <c r="AL31" s="30"/>
-      <c r="AM31" s="30"/>
-      <c r="AN31" s="30"/>
-      <c r="AO31" s="30"/>
-      <c r="AP31" s="30"/>
-      <c r="AQ31" s="30"/>
-      <c r="AR31" s="30"/>
+      <c r="P31" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q31" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="R31" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S31" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T31" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="U31" s="29"/>
+      <c r="V31" s="29"/>
+      <c r="W31" s="29"/>
+      <c r="X31" s="29"/>
+      <c r="Y31" s="29"/>
+      <c r="Z31" s="29"/>
+      <c r="AA31" s="29"/>
+      <c r="AB31" s="29"/>
+      <c r="AC31" s="29"/>
+      <c r="AD31" s="29"/>
+      <c r="AE31" s="29"/>
+      <c r="AF31" s="29"/>
+      <c r="AG31" s="29"/>
+      <c r="AH31" s="29"/>
+      <c r="AI31" s="29"/>
+      <c r="AJ31" s="29"/>
+      <c r="AK31" s="29"/>
+      <c r="AL31" s="29"/>
+      <c r="AM31" s="29"/>
+      <c r="AN31" s="29"/>
+      <c r="AO31" s="29"/>
+      <c r="AP31" s="29"/>
+      <c r="AQ31" s="29"/>
+      <c r="AR31" s="29"/>
       <c r="AS31" s="18"/>
-      <c r="AT31" s="30"/>
+      <c r="AT31" s="29"/>
       <c r="AU31" s="19"/>
-      <c r="AV31" s="41" t="s">
+      <c r="AV31" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="AW31" s="32"/>
+      <c r="AW31" s="31"/>
       <c r="AX31" s="20" t="s">
         <v>135</v>
       </c>
@@ -5024,7 +5085,7 @@
       </c>
       <c r="AZ31" s="18"/>
       <c r="BA31" s="17"/>
-      <c r="BB31" s="28"/>
+      <c r="BB31" s="27"/>
       <c r="BC31" s="17"/>
       <c r="BD31" s="17"/>
       <c r="BE31" s="17"/>
@@ -5042,11 +5103,11 @@
       <c r="BM31" s="17"/>
       <c r="BN31" s="18"/>
       <c r="BO31" s="18"/>
-      <c r="BP31" s="30"/>
-      <c r="BQ31" s="30"/>
-      <c r="BR31" s="30"/>
-      <c r="BS31" s="30"/>
-      <c r="BT31" s="30"/>
+      <c r="BP31" s="29"/>
+      <c r="BQ31" s="29"/>
+      <c r="BR31" s="29"/>
+      <c r="BS31" s="29"/>
+      <c r="BT31" s="29"/>
     </row>
     <row r="32" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
@@ -5079,7 +5140,7 @@
       <c r="L32" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="M32" s="40" t="s">
+      <c r="M32" s="39" t="s">
         <v>117</v>
       </c>
       <c r="N32" s="17" t="s">
@@ -5088,61 +5149,63 @@
       <c r="O32" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P32" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q32" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="R32" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="S32" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="T32" s="30"/>
-      <c r="U32" s="30"/>
-      <c r="V32" s="30"/>
-      <c r="W32" s="30"/>
-      <c r="X32" s="30"/>
-      <c r="Y32" s="30"/>
-      <c r="Z32" s="30"/>
-      <c r="AA32" s="30"/>
-      <c r="AB32" s="30"/>
-      <c r="AC32" s="30"/>
-      <c r="AD32" s="30"/>
-      <c r="AE32" s="30"/>
-      <c r="AF32" s="30"/>
-      <c r="AG32" s="30"/>
-      <c r="AH32" s="30"/>
-      <c r="AI32" s="30"/>
-      <c r="AJ32" s="30"/>
-      <c r="AK32" s="30"/>
-      <c r="AL32" s="30"/>
-      <c r="AM32" s="30"/>
-      <c r="AN32" s="30"/>
-      <c r="AO32" s="30"/>
-      <c r="AP32" s="30"/>
-      <c r="AQ32" s="30"/>
-      <c r="AR32" s="30"/>
+      <c r="P32" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q32" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R32" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S32" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T32" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="U32" s="29"/>
+      <c r="V32" s="29"/>
+      <c r="W32" s="29"/>
+      <c r="X32" s="29"/>
+      <c r="Y32" s="29"/>
+      <c r="Z32" s="29"/>
+      <c r="AA32" s="29"/>
+      <c r="AB32" s="29"/>
+      <c r="AC32" s="29"/>
+      <c r="AD32" s="29"/>
+      <c r="AE32" s="29"/>
+      <c r="AF32" s="29"/>
+      <c r="AG32" s="29"/>
+      <c r="AH32" s="29"/>
+      <c r="AI32" s="29"/>
+      <c r="AJ32" s="29"/>
+      <c r="AK32" s="29"/>
+      <c r="AL32" s="29"/>
+      <c r="AM32" s="29"/>
+      <c r="AN32" s="29"/>
+      <c r="AO32" s="29"/>
+      <c r="AP32" s="29"/>
+      <c r="AQ32" s="29"/>
+      <c r="AR32" s="29"/>
       <c r="AS32" s="18"/>
-      <c r="AT32" s="30"/>
+      <c r="AT32" s="29"/>
       <c r="AU32" s="19"/>
-      <c r="AV32" s="42" t="s">
+      <c r="AV32" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="AW32" s="32"/>
-      <c r="AX32" s="33" t="s">
+      <c r="AW32" s="31"/>
+      <c r="AX32" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="AY32" s="34" t="s">
+      <c r="AY32" s="33" t="s">
         <v>133</v>
       </c>
       <c r="AZ32" s="18"/>
       <c r="BA32" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="BB32" s="28" t="s">
+      <c r="BB32" s="27" t="s">
         <v>46</v>
       </c>
       <c r="BC32" s="17"/>
@@ -5158,11 +5221,11 @@
       <c r="BM32" s="17"/>
       <c r="BN32" s="18"/>
       <c r="BO32" s="18"/>
-      <c r="BP32" s="30"/>
-      <c r="BQ32" s="30"/>
-      <c r="BR32" s="30"/>
-      <c r="BS32" s="30"/>
-      <c r="BT32" s="30"/>
+      <c r="BP32" s="29"/>
+      <c r="BQ32" s="29"/>
+      <c r="BR32" s="29"/>
+      <c r="BS32" s="29"/>
+      <c r="BT32" s="29"/>
     </row>
     <row r="33" spans="1:75" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
@@ -5204,55 +5267,57 @@
       <c r="O33" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="P33" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q33" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="R33" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="S33" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="T33" s="30"/>
-      <c r="U33" s="30"/>
-      <c r="V33" s="30"/>
-      <c r="W33" s="30"/>
-      <c r="X33" s="30"/>
-      <c r="Y33" s="30"/>
-      <c r="Z33" s="30"/>
-      <c r="AA33" s="30"/>
-      <c r="AB33" s="30"/>
-      <c r="AC33" s="30"/>
-      <c r="AD33" s="30"/>
-      <c r="AE33" s="30"/>
-      <c r="AF33" s="30"/>
-      <c r="AG33" s="30"/>
-      <c r="AH33" s="30"/>
-      <c r="AI33" s="30"/>
-      <c r="AJ33" s="30"/>
-      <c r="AK33" s="30"/>
-      <c r="AL33" s="30"/>
-      <c r="AM33" s="30"/>
-      <c r="AN33" s="30"/>
-      <c r="AO33" s="30"/>
-      <c r="AP33" s="30"/>
-      <c r="AQ33" s="30"/>
-      <c r="AR33" s="30"/>
+      <c r="P33" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q33" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="R33" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="S33" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T33" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="U33" s="29"/>
+      <c r="V33" s="29"/>
+      <c r="W33" s="29"/>
+      <c r="X33" s="29"/>
+      <c r="Y33" s="29"/>
+      <c r="Z33" s="29"/>
+      <c r="AA33" s="29"/>
+      <c r="AB33" s="29"/>
+      <c r="AC33" s="29"/>
+      <c r="AD33" s="29"/>
+      <c r="AE33" s="29"/>
+      <c r="AF33" s="29"/>
+      <c r="AG33" s="29"/>
+      <c r="AH33" s="29"/>
+      <c r="AI33" s="29"/>
+      <c r="AJ33" s="29"/>
+      <c r="AK33" s="29"/>
+      <c r="AL33" s="29"/>
+      <c r="AM33" s="29"/>
+      <c r="AN33" s="29"/>
+      <c r="AO33" s="29"/>
+      <c r="AP33" s="29"/>
+      <c r="AQ33" s="29"/>
+      <c r="AR33" s="29"/>
       <c r="AS33" s="18"/>
-      <c r="AT33" s="30"/>
+      <c r="AT33" s="29"/>
       <c r="AU33" s="19"/>
       <c r="AV33" s="19"/>
-      <c r="AW33" s="32"/>
-      <c r="AX33" s="26" t="s">
+      <c r="AW33" s="31"/>
+      <c r="AX33" s="25" t="s">
         <v>50</v>
       </c>
       <c r="AY33" s="19"/>
       <c r="AZ33" s="18"/>
       <c r="BA33" s="17"/>
-      <c r="BB33" s="28"/>
+      <c r="BB33" s="27"/>
       <c r="BC33" s="17"/>
       <c r="BD33" s="17"/>
       <c r="BE33" s="17"/>
@@ -5266,11 +5331,11 @@
       <c r="BM33" s="17"/>
       <c r="BN33" s="18"/>
       <c r="BO33" s="18"/>
-      <c r="BP33" s="30"/>
-      <c r="BQ33" s="30"/>
-      <c r="BR33" s="30"/>
-      <c r="BS33" s="30"/>
-      <c r="BT33" s="30"/>
+      <c r="BP33" s="29"/>
+      <c r="BQ33" s="29"/>
+      <c r="BR33" s="29"/>
+      <c r="BS33" s="29"/>
+      <c r="BT33" s="29"/>
     </row>
     <row r="34" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
@@ -5312,52 +5377,54 @@
       <c r="O34" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P34" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q34" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="R34" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="S34" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="T34" s="30"/>
-      <c r="U34" s="30"/>
-      <c r="V34" s="30"/>
-      <c r="W34" s="30"/>
-      <c r="X34" s="30"/>
-      <c r="Y34" s="30"/>
-      <c r="Z34" s="30"/>
-      <c r="AA34" s="30"/>
-      <c r="AB34" s="30"/>
-      <c r="AC34" s="30"/>
-      <c r="AD34" s="30"/>
-      <c r="AE34" s="30"/>
-      <c r="AF34" s="30"/>
-      <c r="AG34" s="30"/>
-      <c r="AH34" s="30"/>
-      <c r="AI34" s="30"/>
-      <c r="AJ34" s="30"/>
-      <c r="AK34" s="30"/>
-      <c r="AL34" s="30"/>
-      <c r="AM34" s="30"/>
-      <c r="AN34" s="30"/>
-      <c r="AO34" s="30"/>
-      <c r="AP34" s="30"/>
-      <c r="AQ34" s="30"/>
-      <c r="AR34" s="30"/>
+      <c r="P34" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q34" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R34" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S34" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T34" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="U34" s="29"/>
+      <c r="V34" s="29"/>
+      <c r="W34" s="29"/>
+      <c r="X34" s="29"/>
+      <c r="Y34" s="29"/>
+      <c r="Z34" s="29"/>
+      <c r="AA34" s="29"/>
+      <c r="AB34" s="29"/>
+      <c r="AC34" s="29"/>
+      <c r="AD34" s="29"/>
+      <c r="AE34" s="29"/>
+      <c r="AF34" s="29"/>
+      <c r="AG34" s="29"/>
+      <c r="AH34" s="29"/>
+      <c r="AI34" s="29"/>
+      <c r="AJ34" s="29"/>
+      <c r="AK34" s="29"/>
+      <c r="AL34" s="29"/>
+      <c r="AM34" s="29"/>
+      <c r="AN34" s="29"/>
+      <c r="AO34" s="29"/>
+      <c r="AP34" s="29"/>
+      <c r="AQ34" s="29"/>
+      <c r="AR34" s="29"/>
       <c r="AS34" s="18"/>
-      <c r="AT34" s="30"/>
+      <c r="AT34" s="29"/>
       <c r="AU34" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="AV34" s="41" t="s">
+      <c r="AV34" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="AW34" s="46">
+      <c r="AW34" s="44">
         <v>46307</v>
       </c>
       <c r="AX34" s="20" t="s">
@@ -5368,7 +5435,7 @@
       </c>
       <c r="AZ34" s="18"/>
       <c r="BA34" s="17"/>
-      <c r="BB34" s="28"/>
+      <c r="BB34" s="27"/>
       <c r="BC34" s="17"/>
       <c r="BD34" s="17"/>
       <c r="BE34" s="17"/>
@@ -5382,11 +5449,11 @@
       <c r="BM34" s="17"/>
       <c r="BN34" s="18"/>
       <c r="BO34" s="18"/>
-      <c r="BP34" s="30"/>
-      <c r="BQ34" s="30"/>
-      <c r="BR34" s="30"/>
-      <c r="BS34" s="30"/>
-      <c r="BT34" s="30"/>
+      <c r="BP34" s="29"/>
+      <c r="BQ34" s="29"/>
+      <c r="BR34" s="29"/>
+      <c r="BS34" s="29"/>
+      <c r="BT34" s="29"/>
     </row>
     <row r="35" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
@@ -5419,7 +5486,7 @@
       <c r="L35" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="M35" s="38" t="s">
+      <c r="M35" s="37" t="s">
         <v>117</v>
       </c>
       <c r="N35" s="17" t="s">
@@ -5428,59 +5495,61 @@
       <c r="O35" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P35" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q35" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="R35" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="S35" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="T35" s="30"/>
-      <c r="U35" s="30"/>
-      <c r="V35" s="30"/>
-      <c r="W35" s="30"/>
-      <c r="X35" s="30"/>
-      <c r="Y35" s="30"/>
-      <c r="Z35" s="30"/>
-      <c r="AA35" s="30"/>
-      <c r="AB35" s="30"/>
-      <c r="AC35" s="30"/>
-      <c r="AD35" s="30"/>
-      <c r="AE35" s="30"/>
-      <c r="AF35" s="30"/>
-      <c r="AG35" s="30"/>
-      <c r="AH35" s="30"/>
-      <c r="AI35" s="30"/>
-      <c r="AJ35" s="30"/>
-      <c r="AK35" s="30"/>
-      <c r="AL35" s="30"/>
-      <c r="AM35" s="30"/>
-      <c r="AN35" s="30"/>
-      <c r="AO35" s="30"/>
-      <c r="AP35" s="30"/>
-      <c r="AQ35" s="30"/>
-      <c r="AR35" s="30"/>
+      <c r="P35" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q35" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R35" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S35" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="T35" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="U35" s="29"/>
+      <c r="V35" s="29"/>
+      <c r="W35" s="29"/>
+      <c r="X35" s="29"/>
+      <c r="Y35" s="29"/>
+      <c r="Z35" s="29"/>
+      <c r="AA35" s="29"/>
+      <c r="AB35" s="29"/>
+      <c r="AC35" s="29"/>
+      <c r="AD35" s="29"/>
+      <c r="AE35" s="29"/>
+      <c r="AF35" s="29"/>
+      <c r="AG35" s="29"/>
+      <c r="AH35" s="29"/>
+      <c r="AI35" s="29"/>
+      <c r="AJ35" s="29"/>
+      <c r="AK35" s="29"/>
+      <c r="AL35" s="29"/>
+      <c r="AM35" s="29"/>
+      <c r="AN35" s="29"/>
+      <c r="AO35" s="29"/>
+      <c r="AP35" s="29"/>
+      <c r="AQ35" s="29"/>
+      <c r="AR35" s="29"/>
       <c r="AS35" s="18"/>
-      <c r="AT35" s="30"/>
+      <c r="AT35" s="29"/>
       <c r="AU35" s="19"/>
-      <c r="AV35" s="41" t="s">
+      <c r="AV35" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="AW35" s="32"/>
-      <c r="AX35" s="36" t="s">
+      <c r="AW35" s="31"/>
+      <c r="AX35" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="AY35" s="34" t="s">
+      <c r="AY35" s="33" t="s">
         <v>151</v>
       </c>
       <c r="AZ35" s="18"/>
       <c r="BA35" s="17"/>
-      <c r="BB35" s="28"/>
+      <c r="BB35" s="27"/>
       <c r="BC35" s="17"/>
       <c r="BD35" s="17"/>
       <c r="BE35" s="17"/>
@@ -5498,11 +5567,11 @@
       <c r="BM35" s="17"/>
       <c r="BN35" s="18"/>
       <c r="BO35" s="18"/>
-      <c r="BP35" s="30"/>
-      <c r="BQ35" s="30"/>
-      <c r="BR35" s="30"/>
-      <c r="BS35" s="30"/>
-      <c r="BT35" s="30"/>
+      <c r="BP35" s="29"/>
+      <c r="BQ35" s="29"/>
+      <c r="BR35" s="29"/>
+      <c r="BS35" s="29"/>
+      <c r="BT35" s="29"/>
     </row>
     <row r="36" spans="1:75" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
@@ -5544,49 +5613,51 @@
       <c r="O36" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="P36" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q36" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="R36" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="S36" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="T36" s="30"/>
-      <c r="U36" s="30"/>
-      <c r="V36" s="30"/>
-      <c r="W36" s="30"/>
-      <c r="X36" s="30"/>
-      <c r="Y36" s="30"/>
-      <c r="Z36" s="30"/>
-      <c r="AA36" s="30"/>
-      <c r="AB36" s="30"/>
-      <c r="AC36" s="30"/>
-      <c r="AD36" s="30"/>
-      <c r="AE36" s="30"/>
-      <c r="AF36" s="30"/>
-      <c r="AG36" s="30"/>
-      <c r="AH36" s="30"/>
-      <c r="AI36" s="30"/>
-      <c r="AJ36" s="30"/>
-      <c r="AK36" s="30"/>
-      <c r="AL36" s="30"/>
-      <c r="AM36" s="30"/>
-      <c r="AN36" s="30"/>
-      <c r="AO36" s="30"/>
-      <c r="AP36" s="30"/>
-      <c r="AQ36" s="30"/>
-      <c r="AR36" s="30"/>
-      <c r="AS36" s="30"/>
-      <c r="AT36" s="30"/>
+      <c r="P36" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q36" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R36" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S36" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="T36" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="U36" s="29"/>
+      <c r="V36" s="29"/>
+      <c r="W36" s="29"/>
+      <c r="X36" s="29"/>
+      <c r="Y36" s="29"/>
+      <c r="Z36" s="29"/>
+      <c r="AA36" s="29"/>
+      <c r="AB36" s="29"/>
+      <c r="AC36" s="29"/>
+      <c r="AD36" s="29"/>
+      <c r="AE36" s="29"/>
+      <c r="AF36" s="29"/>
+      <c r="AG36" s="29"/>
+      <c r="AH36" s="29"/>
+      <c r="AI36" s="29"/>
+      <c r="AJ36" s="29"/>
+      <c r="AK36" s="29"/>
+      <c r="AL36" s="29"/>
+      <c r="AM36" s="29"/>
+      <c r="AN36" s="29"/>
+      <c r="AO36" s="29"/>
+      <c r="AP36" s="29"/>
+      <c r="AQ36" s="29"/>
+      <c r="AR36" s="29"/>
+      <c r="AS36" s="29"/>
+      <c r="AT36" s="29"/>
       <c r="AU36" s="19"/>
       <c r="AV36" s="19"/>
-      <c r="AW36" s="25"/>
-      <c r="AX36" s="26" t="s">
+      <c r="AW36" s="24"/>
+      <c r="AX36" s="25" t="s">
         <v>158</v>
       </c>
       <c r="AY36" s="19"/>
@@ -5598,19 +5669,19 @@
       <c r="BE36" s="17"/>
       <c r="BF36" s="17"/>
       <c r="BG36" s="17"/>
-      <c r="BH36" s="30"/>
-      <c r="BI36" s="30"/>
-      <c r="BJ36" s="30"/>
+      <c r="BH36" s="29"/>
+      <c r="BI36" s="29"/>
+      <c r="BJ36" s="29"/>
       <c r="BK36" s="17"/>
       <c r="BL36" s="17"/>
       <c r="BM36" s="17"/>
-      <c r="BN36" s="30"/>
-      <c r="BO36" s="30"/>
-      <c r="BP36" s="30"/>
-      <c r="BQ36" s="30"/>
-      <c r="BR36" s="30"/>
-      <c r="BS36" s="30"/>
-      <c r="BT36" s="30"/>
+      <c r="BN36" s="29"/>
+      <c r="BO36" s="29"/>
+      <c r="BP36" s="29"/>
+      <c r="BQ36" s="29"/>
+      <c r="BR36" s="29"/>
+      <c r="BS36" s="29"/>
+      <c r="BT36" s="29"/>
     </row>
     <row r="37" spans="1:75" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
@@ -5654,52 +5725,54 @@
       <c r="O37" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="P37" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q37" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="R37" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="S37" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="T37" s="30"/>
-      <c r="U37" s="30"/>
-      <c r="V37" s="30"/>
-      <c r="W37" s="30"/>
-      <c r="X37" s="30"/>
-      <c r="Y37" s="30"/>
-      <c r="Z37" s="30"/>
-      <c r="AA37" s="30"/>
-      <c r="AB37" s="30"/>
-      <c r="AC37" s="30"/>
-      <c r="AD37" s="30"/>
-      <c r="AE37" s="30"/>
-      <c r="AF37" s="30"/>
-      <c r="AG37" s="30"/>
-      <c r="AH37" s="30"/>
-      <c r="AI37" s="30"/>
-      <c r="AJ37" s="30"/>
-      <c r="AK37" s="30"/>
-      <c r="AL37" s="30"/>
-      <c r="AM37" s="30"/>
-      <c r="AN37" s="30"/>
-      <c r="AO37" s="30"/>
-      <c r="AP37" s="30"/>
-      <c r="AQ37" s="30"/>
-      <c r="AR37" s="30"/>
-      <c r="AS37" s="30"/>
-      <c r="AT37" s="30"/>
+      <c r="P37" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q37" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="R37" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="S37" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="T37" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="U37" s="29"/>
+      <c r="V37" s="29"/>
+      <c r="W37" s="29"/>
+      <c r="X37" s="29"/>
+      <c r="Y37" s="29"/>
+      <c r="Z37" s="29"/>
+      <c r="AA37" s="29"/>
+      <c r="AB37" s="29"/>
+      <c r="AC37" s="29"/>
+      <c r="AD37" s="29"/>
+      <c r="AE37" s="29"/>
+      <c r="AF37" s="29"/>
+      <c r="AG37" s="29"/>
+      <c r="AH37" s="29"/>
+      <c r="AI37" s="29"/>
+      <c r="AJ37" s="29"/>
+      <c r="AK37" s="29"/>
+      <c r="AL37" s="29"/>
+      <c r="AM37" s="29"/>
+      <c r="AN37" s="29"/>
+      <c r="AO37" s="29"/>
+      <c r="AP37" s="29"/>
+      <c r="AQ37" s="29"/>
+      <c r="AR37" s="29"/>
+      <c r="AS37" s="29"/>
+      <c r="AT37" s="29"/>
       <c r="AU37" s="19"/>
       <c r="AV37" s="19"/>
-      <c r="AW37" s="25"/>
-      <c r="AX37" s="33" t="s">
+      <c r="AW37" s="24"/>
+      <c r="AX37" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="AY37" s="34" t="s">
+      <c r="AY37" s="33" t="s">
         <v>145</v>
       </c>
       <c r="AZ37" s="17"/>
@@ -5710,72 +5783,72 @@
       <c r="BE37" s="17"/>
       <c r="BF37" s="17"/>
       <c r="BG37" s="17"/>
-      <c r="BH37" s="30"/>
-      <c r="BI37" s="30"/>
-      <c r="BJ37" s="30"/>
+      <c r="BH37" s="29"/>
+      <c r="BI37" s="29"/>
+      <c r="BJ37" s="29"/>
       <c r="BK37" s="17"/>
       <c r="BL37" s="17"/>
       <c r="BM37" s="17"/>
-      <c r="BN37" s="30"/>
-      <c r="BO37" s="30"/>
-      <c r="BP37" s="30"/>
-      <c r="BQ37" s="30"/>
-      <c r="BR37" s="30"/>
-      <c r="BS37" s="30"/>
-      <c r="BT37" s="30"/>
+      <c r="BN37" s="29"/>
+      <c r="BO37" s="29"/>
+      <c r="BP37" s="29"/>
+      <c r="BQ37" s="29"/>
+      <c r="BR37" s="29"/>
+      <c r="BS37" s="29"/>
+      <c r="BT37" s="29"/>
     </row>
     <row r="38" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A38" s="60" t="s">
+      <c r="A38" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="B38" s="61"/>
-      <c r="C38" s="61"/>
-      <c r="D38" s="61"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="61"/>
-      <c r="G38" s="61"/>
-      <c r="H38" s="61"/>
-      <c r="I38" s="61"/>
-      <c r="J38" s="61"/>
-      <c r="K38" s="61"/>
-      <c r="L38" s="61"/>
-      <c r="M38" s="61"/>
-      <c r="N38" s="61"/>
-      <c r="O38" s="61"/>
-      <c r="P38" s="61"/>
-      <c r="Q38" s="61"/>
-      <c r="R38" s="61"/>
-      <c r="S38" s="61"/>
-      <c r="T38" s="61"/>
-      <c r="U38" s="61"/>
-      <c r="V38" s="61"/>
-      <c r="W38" s="61"/>
-      <c r="X38" s="61"/>
-      <c r="Y38" s="61"/>
-      <c r="Z38" s="61"/>
-      <c r="AA38" s="61"/>
-      <c r="AB38" s="61"/>
-      <c r="AC38" s="61"/>
-      <c r="AD38" s="61"/>
-      <c r="AE38" s="61"/>
-      <c r="AF38" s="61"/>
-      <c r="AG38" s="61"/>
-      <c r="AH38" s="61"/>
-      <c r="AI38" s="61"/>
-      <c r="AJ38" s="61"/>
-      <c r="AK38" s="61"/>
-      <c r="AL38" s="61"/>
-      <c r="AM38" s="61"/>
-      <c r="AN38" s="61"/>
-      <c r="AO38" s="61"/>
-      <c r="AP38" s="61"/>
-      <c r="AQ38" s="61"/>
-      <c r="AR38" s="61"/>
-      <c r="AS38" s="61"/>
-      <c r="AT38" s="61"/>
-      <c r="AU38" s="61"/>
-      <c r="AV38" s="61"/>
-      <c r="AW38" s="62"/>
+      <c r="B38" s="54"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="54"/>
+      <c r="I38" s="54"/>
+      <c r="J38" s="54"/>
+      <c r="K38" s="54"/>
+      <c r="L38" s="54"/>
+      <c r="M38" s="54"/>
+      <c r="N38" s="54"/>
+      <c r="O38" s="54"/>
+      <c r="P38" s="54"/>
+      <c r="Q38" s="54"/>
+      <c r="R38" s="54"/>
+      <c r="S38" s="54"/>
+      <c r="T38" s="54"/>
+      <c r="U38" s="54"/>
+      <c r="V38" s="54"/>
+      <c r="W38" s="54"/>
+      <c r="X38" s="54"/>
+      <c r="Y38" s="54"/>
+      <c r="Z38" s="54"/>
+      <c r="AA38" s="54"/>
+      <c r="AB38" s="54"/>
+      <c r="AC38" s="54"/>
+      <c r="AD38" s="54"/>
+      <c r="AE38" s="54"/>
+      <c r="AF38" s="54"/>
+      <c r="AG38" s="54"/>
+      <c r="AH38" s="54"/>
+      <c r="AI38" s="54"/>
+      <c r="AJ38" s="54"/>
+      <c r="AK38" s="54"/>
+      <c r="AL38" s="54"/>
+      <c r="AM38" s="54"/>
+      <c r="AN38" s="54"/>
+      <c r="AO38" s="54"/>
+      <c r="AP38" s="54"/>
+      <c r="AQ38" s="54"/>
+      <c r="AR38" s="54"/>
+      <c r="AS38" s="54"/>
+      <c r="AT38" s="54"/>
+      <c r="AU38" s="54"/>
+      <c r="AV38" s="54"/>
+      <c r="AW38" s="55"/>
       <c r="AX38" s="2"/>
       <c r="AY38" s="2"/>
       <c r="AZ38" s="2"/>
@@ -5807,57 +5880,57 @@
       </c>
     </row>
     <row r="39" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A39" s="63" t="s">
+      <c r="A39" s="56" t="s">
         <v>84</v>
       </c>
-      <c r="B39" s="64"/>
-      <c r="C39" s="64"/>
-      <c r="D39" s="64"/>
-      <c r="E39" s="64"/>
-      <c r="F39" s="64"/>
-      <c r="G39" s="64"/>
-      <c r="H39" s="64"/>
-      <c r="I39" s="64"/>
-      <c r="J39" s="64"/>
-      <c r="K39" s="64"/>
-      <c r="L39" s="64"/>
-      <c r="M39" s="64"/>
-      <c r="N39" s="64"/>
-      <c r="O39" s="64"/>
-      <c r="P39" s="64"/>
-      <c r="Q39" s="64"/>
-      <c r="R39" s="64"/>
-      <c r="S39" s="64"/>
-      <c r="T39" s="64"/>
-      <c r="U39" s="64"/>
-      <c r="V39" s="64"/>
-      <c r="W39" s="64"/>
-      <c r="X39" s="64"/>
-      <c r="Y39" s="64"/>
-      <c r="Z39" s="64"/>
-      <c r="AA39" s="64"/>
-      <c r="AB39" s="64"/>
-      <c r="AC39" s="64"/>
-      <c r="AD39" s="64"/>
-      <c r="AE39" s="64"/>
-      <c r="AF39" s="64"/>
-      <c r="AG39" s="64"/>
-      <c r="AH39" s="64"/>
-      <c r="AI39" s="64"/>
-      <c r="AJ39" s="64"/>
-      <c r="AK39" s="64"/>
-      <c r="AL39" s="64"/>
-      <c r="AM39" s="64"/>
-      <c r="AN39" s="64"/>
-      <c r="AO39" s="64"/>
-      <c r="AP39" s="64"/>
-      <c r="AQ39" s="64"/>
-      <c r="AR39" s="64"/>
-      <c r="AS39" s="64"/>
-      <c r="AT39" s="64"/>
-      <c r="AU39" s="64"/>
-      <c r="AV39" s="64"/>
-      <c r="AW39" s="65"/>
+      <c r="B39" s="57"/>
+      <c r="C39" s="57"/>
+      <c r="D39" s="57"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="57"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="57"/>
+      <c r="L39" s="57"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="57"/>
+      <c r="O39" s="57"/>
+      <c r="P39" s="57"/>
+      <c r="Q39" s="57"/>
+      <c r="R39" s="57"/>
+      <c r="S39" s="57"/>
+      <c r="T39" s="57"/>
+      <c r="U39" s="57"/>
+      <c r="V39" s="57"/>
+      <c r="W39" s="57"/>
+      <c r="X39" s="57"/>
+      <c r="Y39" s="57"/>
+      <c r="Z39" s="57"/>
+      <c r="AA39" s="57"/>
+      <c r="AB39" s="57"/>
+      <c r="AC39" s="57"/>
+      <c r="AD39" s="57"/>
+      <c r="AE39" s="57"/>
+      <c r="AF39" s="57"/>
+      <c r="AG39" s="57"/>
+      <c r="AH39" s="57"/>
+      <c r="AI39" s="57"/>
+      <c r="AJ39" s="57"/>
+      <c r="AK39" s="57"/>
+      <c r="AL39" s="57"/>
+      <c r="AM39" s="57"/>
+      <c r="AN39" s="57"/>
+      <c r="AO39" s="57"/>
+      <c r="AP39" s="57"/>
+      <c r="AQ39" s="57"/>
+      <c r="AR39" s="57"/>
+      <c r="AS39" s="57"/>
+      <c r="AT39" s="57"/>
+      <c r="AU39" s="57"/>
+      <c r="AV39" s="57"/>
+      <c r="AW39" s="58"/>
       <c r="AX39" s="2"/>
       <c r="AY39" s="2"/>
       <c r="AZ39" s="2"/>
@@ -6294,11 +6367,11 @@
       </c>
     </row>
     <row r="50" spans="73:78" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BU50" s="37">
+      <c r="BU50" s="36">
         <v>36</v>
       </c>
-      <c r="BV50" s="37"/>
-      <c r="BW50" s="37" t="s">
+      <c r="BV50" s="36"/>
+      <c r="BW50" s="36" t="s">
         <v>21</v>
       </c>
     </row>
@@ -6456,6 +6529,46 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AJ2:AJ3"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="BD2:BF3"/>
+    <mergeCell ref="AX2:AZ3"/>
+    <mergeCell ref="BA2:BC3"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="AH2:AH3"/>
+    <mergeCell ref="AI2:AI3"/>
+    <mergeCell ref="AK2:AK3"/>
+    <mergeCell ref="AL2:AL3"/>
+    <mergeCell ref="AM2:AM3"/>
+    <mergeCell ref="AN2:AN3"/>
+    <mergeCell ref="AP2:AP3"/>
+    <mergeCell ref="AO2:AO3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="A1:AW1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="AU2:AW3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="AQ2:AQ3"/>
     <mergeCell ref="AR2:AR3"/>
     <mergeCell ref="BR2:BT3"/>
     <mergeCell ref="A38:AW38"/>
@@ -6472,46 +6585,6 @@
     <mergeCell ref="BG2:BJ3"/>
     <mergeCell ref="BK2:BN3"/>
     <mergeCell ref="BO2:BQ3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="A1:AW1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="AU2:AW3"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="AQ2:AQ3"/>
-    <mergeCell ref="BD2:BF3"/>
-    <mergeCell ref="AX2:AZ3"/>
-    <mergeCell ref="BA2:BC3"/>
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="AH2:AH3"/>
-    <mergeCell ref="AI2:AI3"/>
-    <mergeCell ref="AK2:AK3"/>
-    <mergeCell ref="AL2:AL3"/>
-    <mergeCell ref="AM2:AM3"/>
-    <mergeCell ref="AN2:AN3"/>
-    <mergeCell ref="AP2:AP3"/>
-    <mergeCell ref="AO2:AO3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AJ2:AJ3"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="AA2:AA3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="BW6" r:id="rId1" display="Прикладная дискретная математика. Приложение. 2016. № 9. С. 68-70." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -6525,17 +6598,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b78dbef7-f85b-47b5-8738-6377d50f4027" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bffb7b91-0466-4de0-9379-f5c53c3acedf">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Документ" ma:contentTypeID="0x0101004F6380A0290AF84484F859C9FFD97568" ma:contentTypeVersion="12" ma:contentTypeDescription="Создание документа." ma:contentTypeScope="" ma:versionID="1ee9877c88efff51dfb0d3a4b3e8ad1b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bffb7b91-0466-4de0-9379-f5c53c3acedf" xmlns:ns3="b78dbef7-f85b-47b5-8738-6377d50f4027" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="532d4df54980d57387e1b5dc96a6a32c" ns2:_="" ns3:_="">
     <xsd:import namespace="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
@@ -6736,6 +6798,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b78dbef7-f85b-47b5-8738-6377d50f4027" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bffb7b91-0466-4de0-9379-f5c53c3acedf">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -6746,17 +6819,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12ECB55F-B88E-4FE2-9AD5-5CA5D433F306}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b78dbef7-f85b-47b5-8738-6377d50f4027"/>
-    <ds:schemaRef ds:uri="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B6A6DF3-AE59-43BA-A5FF-CF9B7C54D4B8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6775,6 +6837,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12ECB55F-B88E-4FE2-9AD5-5CA5D433F306}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b78dbef7-f85b-47b5-8738-6377d50f4027"/>
+    <ds:schemaRef ds:uri="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00280879-8A9A-4335-93BC-405126DC8F0C}">
   <ds:schemaRefs>

--- a/Ведомость ТКИ-441 2026-2027.xlsx
+++ b/Ведомость ТКИ-441 2026-2027.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\StegMethods\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\StegMethods\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB19ED5B-03E7-4540-9581-22EA0E9DED93}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="192">
   <si>
     <t>Ведомость посещаемости занятий студентами группы ТКИ РУТ МИИТ</t>
   </si>
@@ -589,13 +590,25 @@
   </si>
   <si>
     <t>Пороговый</t>
+  </si>
+  <si>
+    <t>9.3</t>
+  </si>
+  <si>
+    <t>9.4</t>
+  </si>
+  <si>
+    <t>9.1</t>
+  </si>
+  <si>
+    <t>Стоп-пошёл</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -644,6 +657,19 @@
     <font>
       <sz val="14"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
@@ -699,7 +725,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -862,12 +888,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -907,7 +946,6 @@
     <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -918,7 +956,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -955,31 +992,7 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -998,14 +1011,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1"/>
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1041,7 +1092,7 @@
         <xdr:cNvPr id="3" name="Рисунок 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{13645ABC-C350-4C12-BD87-CB39C6C63ABA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13645ABC-C350-4C12-BD87-CB39C6C63ABA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1332,7 +1383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BT66"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1355,7 +1406,7 @@
     <col min="51" max="51" width="33.5703125" customWidth="1"/>
     <col min="52" max="52" width="24.42578125" customWidth="1"/>
     <col min="55" max="55" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="59" max="59" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="63" max="63" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="64" max="64" width="11.5703125" customWidth="1"/>
@@ -1365,227 +1416,227 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="57"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="57"/>
-      <c r="V1" s="57"/>
-      <c r="W1" s="57"/>
-      <c r="X1" s="57"/>
-      <c r="Y1" s="57"/>
-      <c r="Z1" s="57"/>
-      <c r="AA1" s="57"/>
-      <c r="AB1" s="57"/>
-      <c r="AC1" s="57"/>
-      <c r="AD1" s="57"/>
-      <c r="AE1" s="57"/>
-      <c r="AF1" s="57"/>
-      <c r="AG1" s="57"/>
-      <c r="AH1" s="57"/>
-      <c r="AI1" s="57"/>
-      <c r="AJ1" s="57"/>
-      <c r="AK1" s="57"/>
-      <c r="AL1" s="57"/>
-      <c r="AM1" s="57"/>
-      <c r="AN1" s="57"/>
-      <c r="AO1" s="57"/>
-      <c r="AP1" s="57"/>
-      <c r="AQ1" s="57"/>
-      <c r="AR1" s="57"/>
-      <c r="AS1" s="57"/>
-      <c r="AT1" s="57"/>
-      <c r="AU1" s="57"/>
-      <c r="AV1" s="57"/>
-      <c r="AW1" s="57"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="64"/>
+      <c r="U1" s="64"/>
+      <c r="V1" s="64"/>
+      <c r="W1" s="64"/>
+      <c r="X1" s="64"/>
+      <c r="Y1" s="64"/>
+      <c r="Z1" s="64"/>
+      <c r="AA1" s="64"/>
+      <c r="AB1" s="64"/>
+      <c r="AC1" s="64"/>
+      <c r="AD1" s="64"/>
+      <c r="AE1" s="64"/>
+      <c r="AF1" s="64"/>
+      <c r="AG1" s="64"/>
+      <c r="AH1" s="64"/>
+      <c r="AI1" s="64"/>
+      <c r="AJ1" s="64"/>
+      <c r="AK1" s="64"/>
+      <c r="AL1" s="64"/>
+      <c r="AM1" s="64"/>
+      <c r="AN1" s="64"/>
+      <c r="AO1" s="64"/>
+      <c r="AP1" s="64"/>
+      <c r="AQ1" s="64"/>
+      <c r="AR1" s="64"/>
+      <c r="AS1" s="64"/>
+      <c r="AT1" s="64"/>
+      <c r="AU1" s="64"/>
+      <c r="AV1" s="64"/>
+      <c r="AW1" s="64"/>
     </row>
     <row r="2" spans="1:71" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="66" t="s">
+      <c r="B2" s="54"/>
+      <c r="C2" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="47">
+      <c r="D2" s="52">
         <v>46268</v>
       </c>
-      <c r="E2" s="47">
+      <c r="E2" s="52">
         <v>46272</v>
       </c>
-      <c r="F2" s="47">
+      <c r="F2" s="52">
         <v>46273</v>
       </c>
-      <c r="G2" s="47">
+      <c r="G2" s="52">
         <v>46275</v>
       </c>
-      <c r="H2" s="47">
+      <c r="H2" s="52">
         <v>46279</v>
       </c>
-      <c r="I2" s="49">
+      <c r="I2" s="55">
         <v>46282</v>
       </c>
-      <c r="J2" s="47">
+      <c r="J2" s="52">
         <v>46286</v>
       </c>
-      <c r="K2" s="47">
+      <c r="K2" s="52">
         <v>46287</v>
       </c>
-      <c r="L2" s="49">
+      <c r="L2" s="55">
         <v>46289</v>
       </c>
-      <c r="M2" s="47">
+      <c r="M2" s="52">
         <v>46293</v>
       </c>
-      <c r="N2" s="49">
+      <c r="N2" s="55">
         <v>46296</v>
       </c>
-      <c r="O2" s="47">
+      <c r="O2" s="52">
         <v>46300</v>
       </c>
-      <c r="P2" s="47">
+      <c r="P2" s="52">
         <v>46301</v>
       </c>
-      <c r="Q2" s="49">
+      <c r="Q2" s="55">
         <v>46303</v>
       </c>
-      <c r="R2" s="47">
+      <c r="R2" s="52">
         <v>46307</v>
       </c>
-      <c r="S2" s="49">
+      <c r="S2" s="55">
         <v>46310</v>
       </c>
-      <c r="T2" s="47">
+      <c r="T2" s="52">
         <v>46314</v>
       </c>
-      <c r="U2" s="47">
+      <c r="U2" s="52">
         <v>46315</v>
       </c>
-      <c r="V2" s="49">
+      <c r="V2" s="55">
         <v>46317</v>
       </c>
-      <c r="W2" s="47">
+      <c r="W2" s="52">
         <v>46321</v>
       </c>
-      <c r="X2" s="47">
+      <c r="X2" s="52">
         <v>46324</v>
       </c>
-      <c r="Y2" s="47">
+      <c r="Y2" s="52">
         <v>46328</v>
       </c>
-      <c r="Z2" s="47">
+      <c r="Z2" s="52">
         <v>46329</v>
       </c>
-      <c r="AA2" s="47">
+      <c r="AA2" s="52">
         <v>46331</v>
       </c>
-      <c r="AB2" s="47">
+      <c r="AB2" s="52">
         <v>46335</v>
       </c>
-      <c r="AC2" s="47">
+      <c r="AC2" s="52">
         <v>46338</v>
       </c>
-      <c r="AD2" s="47">
+      <c r="AD2" s="52">
         <v>46342</v>
       </c>
-      <c r="AE2" s="47">
+      <c r="AE2" s="52">
         <v>46343</v>
       </c>
-      <c r="AF2" s="47">
+      <c r="AF2" s="52">
         <v>46345</v>
       </c>
-      <c r="AG2" s="47">
+      <c r="AG2" s="52">
         <v>46349</v>
       </c>
-      <c r="AH2" s="47">
+      <c r="AH2" s="52">
         <v>46352</v>
       </c>
-      <c r="AI2" s="47">
+      <c r="AI2" s="52">
         <v>46356</v>
       </c>
-      <c r="AJ2" s="49">
+      <c r="AJ2" s="55">
         <v>46357</v>
       </c>
-      <c r="AK2" s="49">
+      <c r="AK2" s="55">
         <v>46359</v>
       </c>
-      <c r="AL2" s="49">
+      <c r="AL2" s="55">
         <v>46363</v>
       </c>
-      <c r="AM2" s="49">
+      <c r="AM2" s="55">
         <v>46366</v>
       </c>
-      <c r="AN2" s="49">
+      <c r="AN2" s="55">
         <v>46370</v>
       </c>
-      <c r="AO2" s="49">
+      <c r="AO2" s="55">
         <v>46371</v>
       </c>
-      <c r="AP2" s="49">
+      <c r="AP2" s="55">
         <v>46373</v>
       </c>
-      <c r="AQ2" s="49">
+      <c r="AQ2" s="55">
         <v>46377</v>
       </c>
-      <c r="AR2" s="49">
+      <c r="AR2" s="55">
         <v>46380</v>
       </c>
-      <c r="AS2" s="58" t="s">
+      <c r="AS2" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="AT2" s="58"/>
-      <c r="AU2" s="51" t="s">
+      <c r="AT2" s="54"/>
+      <c r="AU2" s="58" t="s">
         <v>117</v>
       </c>
-      <c r="AV2" s="52"/>
-      <c r="AW2" s="53"/>
-      <c r="AX2" s="51" t="s">
+      <c r="AV2" s="59"/>
+      <c r="AW2" s="60"/>
+      <c r="AX2" s="58" t="s">
         <v>158</v>
       </c>
-      <c r="AY2" s="52"/>
-      <c r="AZ2" s="53"/>
-      <c r="BA2" s="51" t="s">
+      <c r="AY2" s="59"/>
+      <c r="AZ2" s="60"/>
+      <c r="BA2" s="58" t="s">
         <v>159</v>
       </c>
-      <c r="BB2" s="52"/>
-      <c r="BC2" s="53"/>
-      <c r="BD2" s="51" t="s">
+      <c r="BB2" s="59"/>
+      <c r="BC2" s="60"/>
+      <c r="BD2" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="BE2" s="52"/>
-      <c r="BF2" s="52"/>
-      <c r="BG2" s="53"/>
-      <c r="BH2" s="51" t="s">
+      <c r="BE2" s="59"/>
+      <c r="BF2" s="59"/>
+      <c r="BG2" s="60"/>
+      <c r="BH2" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="BI2" s="52"/>
-      <c r="BJ2" s="52"/>
-      <c r="BK2" s="53" t="s">
+      <c r="BI2" s="59"/>
+      <c r="BJ2" s="59"/>
+      <c r="BK2" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="BL2" s="51" t="s">
+      <c r="BL2" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="BM2" s="52"/>
-      <c r="BN2" s="53"/>
+      <c r="BM2" s="59"/>
+      <c r="BN2" s="60"/>
     </row>
     <row r="3" spans="1:71" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1594,70 +1645,70 @@
       <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="48"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="50"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="50"/>
-      <c r="W3" s="48"/>
-      <c r="X3" s="48"/>
-      <c r="Y3" s="48"/>
-      <c r="Z3" s="48"/>
-      <c r="AA3" s="48"/>
-      <c r="AB3" s="48"/>
-      <c r="AC3" s="48"/>
-      <c r="AD3" s="48"/>
-      <c r="AE3" s="48"/>
-      <c r="AF3" s="48"/>
-      <c r="AG3" s="48"/>
-      <c r="AH3" s="48"/>
-      <c r="AI3" s="48"/>
-      <c r="AJ3" s="50"/>
-      <c r="AK3" s="50"/>
-      <c r="AL3" s="50"/>
-      <c r="AM3" s="50"/>
-      <c r="AN3" s="50"/>
-      <c r="AO3" s="50"/>
-      <c r="AP3" s="50"/>
-      <c r="AQ3" s="50"/>
-      <c r="AR3" s="50"/>
-      <c r="AS3" s="58"/>
-      <c r="AT3" s="58"/>
-      <c r="AU3" s="54"/>
-      <c r="AV3" s="59"/>
-      <c r="AW3" s="56"/>
-      <c r="AX3" s="54"/>
-      <c r="AY3" s="55"/>
-      <c r="AZ3" s="56"/>
-      <c r="BA3" s="54"/>
-      <c r="BB3" s="55"/>
-      <c r="BC3" s="56"/>
-      <c r="BD3" s="54"/>
-      <c r="BE3" s="55"/>
-      <c r="BF3" s="55"/>
-      <c r="BG3" s="56"/>
-      <c r="BH3" s="54"/>
-      <c r="BI3" s="55"/>
-      <c r="BJ3" s="55"/>
-      <c r="BK3" s="56"/>
-      <c r="BL3" s="54"/>
-      <c r="BM3" s="55"/>
-      <c r="BN3" s="56"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="56"/>
+      <c r="O3" s="53"/>
+      <c r="P3" s="53"/>
+      <c r="Q3" s="56"/>
+      <c r="R3" s="53"/>
+      <c r="S3" s="56"/>
+      <c r="T3" s="53"/>
+      <c r="U3" s="53"/>
+      <c r="V3" s="56"/>
+      <c r="W3" s="53"/>
+      <c r="X3" s="53"/>
+      <c r="Y3" s="53"/>
+      <c r="Z3" s="53"/>
+      <c r="AA3" s="53"/>
+      <c r="AB3" s="53"/>
+      <c r="AC3" s="53"/>
+      <c r="AD3" s="53"/>
+      <c r="AE3" s="53"/>
+      <c r="AF3" s="53"/>
+      <c r="AG3" s="53"/>
+      <c r="AH3" s="53"/>
+      <c r="AI3" s="53"/>
+      <c r="AJ3" s="56"/>
+      <c r="AK3" s="56"/>
+      <c r="AL3" s="56"/>
+      <c r="AM3" s="56"/>
+      <c r="AN3" s="56"/>
+      <c r="AO3" s="56"/>
+      <c r="AP3" s="56"/>
+      <c r="AQ3" s="56"/>
+      <c r="AR3" s="56"/>
+      <c r="AS3" s="54"/>
+      <c r="AT3" s="54"/>
+      <c r="AU3" s="61"/>
+      <c r="AV3" s="65"/>
+      <c r="AW3" s="63"/>
+      <c r="AX3" s="61"/>
+      <c r="AY3" s="62"/>
+      <c r="AZ3" s="63"/>
+      <c r="BA3" s="61"/>
+      <c r="BB3" s="62"/>
+      <c r="BC3" s="63"/>
+      <c r="BD3" s="61"/>
+      <c r="BE3" s="62"/>
+      <c r="BF3" s="62"/>
+      <c r="BG3" s="63"/>
+      <c r="BH3" s="61"/>
+      <c r="BI3" s="62"/>
+      <c r="BJ3" s="62"/>
+      <c r="BK3" s="63"/>
+      <c r="BL3" s="61"/>
+      <c r="BM3" s="62"/>
+      <c r="BN3" s="63"/>
     </row>
     <row r="4" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
@@ -1690,7 +1741,7 @@
       <c r="L4" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="M4" s="37" t="s">
+      <c r="M4" s="35" t="s">
         <v>115</v>
       </c>
       <c r="N4" s="16" t="s">
@@ -1699,26 +1750,28 @@
       <c r="O4" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P4" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q4" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R4" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S4" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T4" s="44" t="s">
+      <c r="P4" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q4" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R4" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S4" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T4" s="42" t="s">
         <v>115</v>
       </c>
       <c r="U4" s="16" t="s">
         <v>115</v>
       </c>
       <c r="V4" s="16"/>
-      <c r="W4" s="16"/>
+      <c r="W4" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="X4" s="16"/>
       <c r="Y4" s="16"/>
       <c r="Z4" s="16"/>
@@ -1745,26 +1798,26 @@
       <c r="AU4" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="AV4" s="39" t="s">
+      <c r="AV4" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="AW4" s="43">
+      <c r="AW4" s="41">
         <v>46315</v>
       </c>
-      <c r="AX4" s="31" t="s">
+      <c r="AX4" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="AY4" s="32" t="s">
+      <c r="AY4" s="30" t="s">
         <v>127</v>
       </c>
       <c r="AZ4" s="20"/>
       <c r="BA4" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="BB4" s="20" t="s">
+      <c r="BB4" s="72" t="s">
         <v>33</v>
       </c>
-      <c r="BC4" s="17"/>
+      <c r="BC4" s="73"/>
       <c r="BD4" s="16"/>
       <c r="BE4" s="16"/>
       <c r="BF4" s="16"/>
@@ -1817,26 +1870,28 @@
       <c r="O5" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P5" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q5" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R5" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S5" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T5" s="27" t="s">
+      <c r="P5" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q5" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R5" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S5" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T5" s="25" t="s">
         <v>115</v>
       </c>
       <c r="U5" s="16" t="s">
         <v>115</v>
       </c>
       <c r="V5" s="16"/>
-      <c r="W5" s="16"/>
+      <c r="W5" s="16" t="s">
+        <v>116</v>
+      </c>
       <c r="X5" s="16"/>
       <c r="Y5" s="16"/>
       <c r="Z5" s="16"/>
@@ -1860,33 +1915,33 @@
       <c r="AR5" s="16"/>
       <c r="AS5" s="17"/>
       <c r="AT5" s="16"/>
-      <c r="AU5" s="41" t="s">
+      <c r="AU5" s="39" t="s">
         <v>175</v>
       </c>
-      <c r="AV5" s="42" t="s">
+      <c r="AV5" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="AW5" s="43">
+      <c r="AW5" s="41">
         <v>46307</v>
       </c>
-      <c r="AX5" s="31" t="s">
+      <c r="AX5" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AY5" s="32" t="s">
+      <c r="AY5" s="30" t="s">
         <v>129</v>
       </c>
       <c r="AZ5" s="20"/>
-      <c r="BA5" s="20" t="s">
+      <c r="BA5" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="BB5" s="20" t="s">
+      <c r="BB5" s="66" t="s">
         <v>77</v>
       </c>
       <c r="BC5" s="17"/>
-      <c r="BD5" s="17">
+      <c r="BD5" s="67">
         <v>46310</v>
       </c>
-      <c r="BE5" s="16" t="s">
+      <c r="BE5" s="68" t="s">
         <v>180</v>
       </c>
       <c r="BF5" s="16"/>
@@ -1945,7 +2000,7 @@
       <c r="L6" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="M6" s="38" t="s">
+      <c r="M6" s="36" t="s">
         <v>115</v>
       </c>
       <c r="N6" s="16" t="s">
@@ -1954,26 +2009,28 @@
       <c r="O6" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P6" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q6" s="44" t="s">
-        <v>115</v>
-      </c>
-      <c r="R6" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S6" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T6" s="44" t="s">
+      <c r="P6" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q6" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="R6" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S6" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T6" s="42" t="s">
         <v>115</v>
       </c>
       <c r="U6" s="16" t="s">
         <v>115</v>
       </c>
       <c r="V6" s="16"/>
-      <c r="W6" s="16"/>
+      <c r="W6" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="X6" s="16"/>
       <c r="Y6" s="16"/>
       <c r="Z6" s="16"/>
@@ -1997,31 +2054,31 @@
       <c r="AR6" s="16"/>
       <c r="AS6" s="17"/>
       <c r="AT6" s="16"/>
-      <c r="AU6" s="41" t="s">
+      <c r="AU6" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="AV6" s="40" t="s">
+      <c r="AV6" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="AW6" s="43">
+      <c r="AW6" s="41">
         <v>46315</v>
       </c>
-      <c r="AX6" s="31" t="s">
+      <c r="AX6" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="AY6" s="32" t="s">
+      <c r="AY6" s="30" t="s">
         <v>131</v>
       </c>
       <c r="AZ6" s="20"/>
-      <c r="BA6" s="24" t="s">
+      <c r="BA6" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="BB6" s="24" t="s">
+      <c r="BB6" s="23" t="s">
         <v>44</v>
       </c>
       <c r="BC6" s="17"/>
-      <c r="BD6" s="16"/>
-      <c r="BE6" s="21"/>
+      <c r="BD6" s="68"/>
+      <c r="BE6" s="69"/>
       <c r="BF6" s="16"/>
       <c r="BG6" s="17"/>
       <c r="BH6" s="16"/>
@@ -2069,35 +2126,37 @@
       <c r="L7" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="M7" s="36" t="s">
+      <c r="M7" s="34" t="s">
         <v>115</v>
       </c>
       <c r="N7" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="O7" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="P7" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q7" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R7" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S7" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T7" s="27" t="s">
+      <c r="O7" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="P7" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q7" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R7" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S7" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T7" s="25" t="s">
         <v>115</v>
       </c>
       <c r="U7" s="16" t="s">
         <v>115</v>
       </c>
       <c r="V7" s="16"/>
-      <c r="W7" s="16"/>
+      <c r="W7" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="X7" s="16"/>
       <c r="Y7" s="16"/>
       <c r="Z7" s="16"/>
@@ -2122,10 +2181,10 @@
       <c r="AS7" s="16"/>
       <c r="AT7" s="16"/>
       <c r="AU7" s="18"/>
-      <c r="AV7" s="39" t="s">
+      <c r="AV7" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="AW7" s="23"/>
+      <c r="AW7" s="22"/>
       <c r="AX7" s="19" t="s">
         <v>133</v>
       </c>
@@ -2133,17 +2192,17 @@
         <v>132</v>
       </c>
       <c r="AZ7" s="16"/>
-      <c r="BA7" s="18">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="BB7" s="18" t="s">
+      <c r="BA7" s="71" t="s">
+        <v>188</v>
+      </c>
+      <c r="BB7" s="66" t="s">
         <v>160</v>
       </c>
       <c r="BC7" s="16"/>
-      <c r="BD7" s="17">
+      <c r="BD7" s="67">
         <v>46310</v>
       </c>
-      <c r="BE7" s="21" t="s">
+      <c r="BE7" s="69" t="s">
         <v>181</v>
       </c>
       <c r="BF7" s="16"/>
@@ -2202,26 +2261,28 @@
       <c r="O8" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="P8" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q8" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="R8" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S8" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="T8" s="27" t="s">
+      <c r="P8" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q8" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="R8" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S8" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="T8" s="25" t="s">
         <v>115</v>
       </c>
       <c r="U8" s="16" t="s">
         <v>116</v>
       </c>
       <c r="V8" s="16"/>
-      <c r="W8" s="16"/>
+      <c r="W8" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="X8" s="16"/>
       <c r="Y8" s="16"/>
       <c r="Z8" s="16"/>
@@ -2247,23 +2308,23 @@
       <c r="AT8" s="16"/>
       <c r="AU8" s="18"/>
       <c r="AV8" s="18"/>
-      <c r="AW8" s="23"/>
-      <c r="AX8" s="34" t="s">
+      <c r="AW8" s="22"/>
+      <c r="AX8" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="AY8" s="32" t="s">
+      <c r="AY8" s="30" t="s">
         <v>155</v>
       </c>
       <c r="AZ8" s="16"/>
-      <c r="BA8" s="18">
-        <v>9.4</v>
-      </c>
-      <c r="BB8" s="18" t="s">
+      <c r="BA8" s="71" t="s">
+        <v>189</v>
+      </c>
+      <c r="BB8" s="66" t="s">
         <v>161</v>
       </c>
       <c r="BC8" s="16"/>
-      <c r="BD8" s="16"/>
-      <c r="BE8" s="16"/>
+      <c r="BD8" s="68"/>
+      <c r="BE8" s="68"/>
       <c r="BF8" s="16"/>
       <c r="BG8" s="16"/>
       <c r="BH8" s="16"/>
@@ -2311,7 +2372,7 @@
       <c r="L9" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="M9" s="37" t="s">
+      <c r="M9" s="35" t="s">
         <v>115</v>
       </c>
       <c r="N9" s="16" t="s">
@@ -2320,26 +2381,28 @@
       <c r="O9" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P9" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q9" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R9" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S9" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T9" s="27" t="s">
+      <c r="P9" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q9" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R9" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S9" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T9" s="25" t="s">
         <v>115</v>
       </c>
       <c r="U9" s="16" t="s">
         <v>115</v>
       </c>
       <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
+      <c r="W9" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="X9" s="16"/>
       <c r="Y9" s="16"/>
       <c r="Z9" s="16"/>
@@ -2364,26 +2427,26 @@
       <c r="AS9" s="17"/>
       <c r="AT9" s="16"/>
       <c r="AU9" s="18"/>
-      <c r="AV9" s="39" t="s">
+      <c r="AV9" s="37" t="s">
         <v>171</v>
       </c>
       <c r="AW9" s="20"/>
-      <c r="AX9" s="25" t="s">
+      <c r="AX9" s="24" t="s">
         <v>136</v>
       </c>
       <c r="AY9" s="18" t="s">
         <v>137</v>
       </c>
       <c r="AZ9" s="20"/>
-      <c r="BA9" s="18">
-        <v>9.1</v>
-      </c>
-      <c r="BB9" s="18" t="s">
+      <c r="BA9" s="71" t="s">
+        <v>190</v>
+      </c>
+      <c r="BB9" s="66" t="s">
         <v>162</v>
       </c>
       <c r="BC9" s="17"/>
-      <c r="BD9" s="16"/>
-      <c r="BE9" s="16"/>
+      <c r="BD9" s="68"/>
+      <c r="BE9" s="68"/>
       <c r="BF9" s="16"/>
       <c r="BG9" s="17"/>
       <c r="BH9" s="16"/>
@@ -2440,26 +2503,28 @@
       <c r="O10" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P10" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q10" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R10" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S10" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T10" s="27" t="s">
+      <c r="P10" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q10" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R10" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S10" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T10" s="25" t="s">
         <v>116</v>
       </c>
       <c r="U10" s="16" t="s">
         <v>116</v>
       </c>
       <c r="V10" s="16"/>
-      <c r="W10" s="16"/>
+      <c r="W10" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="X10" s="16"/>
       <c r="Y10" s="16"/>
       <c r="Z10" s="16"/>
@@ -2484,24 +2549,24 @@
       <c r="AS10" s="17"/>
       <c r="AT10" s="16"/>
       <c r="AU10" s="18"/>
-      <c r="AV10" s="40"/>
+      <c r="AV10" s="38"/>
       <c r="AW10" s="20"/>
-      <c r="AX10" s="31" t="s">
+      <c r="AX10" s="29" t="s">
         <v>134</v>
       </c>
-      <c r="AY10" s="32" t="s">
+      <c r="AY10" s="30" t="s">
         <v>135</v>
       </c>
       <c r="AZ10" s="17"/>
       <c r="BA10" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="BB10" s="18" t="s">
+      <c r="BB10" s="66" t="s">
         <v>163</v>
       </c>
-      <c r="BC10" s="18"/>
-      <c r="BD10" s="16"/>
-      <c r="BE10" s="16"/>
+      <c r="BC10" s="19"/>
+      <c r="BD10" s="68"/>
+      <c r="BE10" s="68"/>
       <c r="BF10" s="16"/>
       <c r="BG10" s="17"/>
       <c r="BH10" s="16"/>
@@ -2558,26 +2623,28 @@
       <c r="O11" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P11" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q11" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R11" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S11" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T11" s="27" t="s">
+      <c r="P11" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q11" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R11" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S11" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T11" s="25" t="s">
         <v>115</v>
       </c>
       <c r="U11" s="16" t="s">
         <v>115</v>
       </c>
       <c r="V11" s="16"/>
-      <c r="W11" s="16"/>
+      <c r="W11" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="X11" s="16"/>
       <c r="Y11" s="16"/>
       <c r="Z11" s="16"/>
@@ -2602,28 +2669,28 @@
       <c r="AS11" s="17"/>
       <c r="AT11" s="16"/>
       <c r="AU11" s="18"/>
-      <c r="AV11" s="39" t="s">
+      <c r="AV11" s="37" t="s">
         <v>171</v>
       </c>
       <c r="AW11" s="20"/>
-      <c r="AX11" s="31" t="s">
+      <c r="AX11" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="AY11" s="32" t="s">
+      <c r="AY11" s="30" t="s">
         <v>143</v>
       </c>
       <c r="AZ11" s="17"/>
       <c r="BA11" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="BB11" s="18" t="s">
+      <c r="BB11" s="66" t="s">
         <v>167</v>
       </c>
-      <c r="BC11" s="18"/>
-      <c r="BD11" s="17">
+      <c r="BC11" s="19"/>
+      <c r="BD11" s="67">
         <v>46310</v>
       </c>
-      <c r="BE11" s="16" t="s">
+      <c r="BE11" s="68" t="s">
         <v>179</v>
       </c>
       <c r="BF11" s="16"/>
@@ -2646,7 +2713,7 @@
       <c r="A12" s="3">
         <v>9</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="27" t="s">
         <v>90</v>
       </c>
       <c r="C12" s="4">
@@ -2684,26 +2751,28 @@
       <c r="O12" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="P12" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q12" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R12" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S12" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T12" s="27" t="s">
+      <c r="P12" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q12" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R12" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S12" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T12" s="25" t="s">
         <v>115</v>
       </c>
       <c r="U12" s="16" t="s">
         <v>115</v>
       </c>
       <c r="V12" s="16"/>
-      <c r="W12" s="16"/>
+      <c r="W12" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="X12" s="16"/>
       <c r="Y12" s="16"/>
       <c r="Z12" s="16"/>
@@ -2730,10 +2799,10 @@
       <c r="AU12" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="AV12" s="39" t="s">
+      <c r="AV12" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="AW12" s="43">
+      <c r="AW12" s="41">
         <v>46307</v>
       </c>
       <c r="AX12" s="19" t="s">
@@ -2746,12 +2815,12 @@
       <c r="BA12" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="BB12" s="18"/>
-      <c r="BC12" s="18"/>
-      <c r="BD12" s="17">
+      <c r="BB12" s="66"/>
+      <c r="BC12" s="19"/>
+      <c r="BD12" s="67">
         <v>46315</v>
       </c>
-      <c r="BE12" s="21" t="s">
+      <c r="BE12" s="69" t="s">
         <v>181</v>
       </c>
       <c r="BF12" s="16"/>
@@ -2810,26 +2879,28 @@
       <c r="O13" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="P13" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q13" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R13" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="S13" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T13" s="44" t="s">
+      <c r="P13" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q13" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R13" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="S13" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T13" s="42" t="s">
         <v>115</v>
       </c>
       <c r="U13" s="16" t="s">
         <v>115</v>
       </c>
       <c r="V13" s="16"/>
-      <c r="W13" s="16"/>
+      <c r="W13" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="X13" s="16"/>
       <c r="Y13" s="16"/>
       <c r="Z13" s="16"/>
@@ -2853,25 +2924,31 @@
       <c r="AR13" s="16"/>
       <c r="AS13" s="17"/>
       <c r="AT13" s="16"/>
-      <c r="AU13" s="18"/>
-      <c r="AV13" s="18"/>
-      <c r="AW13" s="20"/>
-      <c r="AX13" s="31" t="s">
+      <c r="AU13" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="AV13" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="AW13" s="20">
+        <v>46314</v>
+      </c>
+      <c r="AX13" s="29" t="s">
         <v>146</v>
       </c>
-      <c r="AY13" s="32" t="s">
+      <c r="AY13" s="30" t="s">
         <v>147</v>
       </c>
       <c r="AZ13" s="17"/>
       <c r="BA13" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="BB13" s="21"/>
+      <c r="BB13" s="66"/>
       <c r="BC13" s="17"/>
-      <c r="BD13" s="17">
+      <c r="BD13" s="67">
         <v>46315</v>
       </c>
-      <c r="BE13" s="16" t="s">
+      <c r="BE13" s="68" t="s">
         <v>183</v>
       </c>
       <c r="BF13" s="16"/>
@@ -2921,7 +2998,7 @@
       <c r="L14" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="M14" s="36" t="s">
+      <c r="M14" s="34" t="s">
         <v>115</v>
       </c>
       <c r="N14" s="16" t="s">
@@ -2930,26 +3007,28 @@
       <c r="O14" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P14" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q14" s="46" t="s">
-        <v>115</v>
-      </c>
-      <c r="R14" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S14" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T14" s="44" t="s">
+      <c r="P14" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q14" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="R14" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S14" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T14" s="42" t="s">
         <v>115</v>
       </c>
       <c r="U14" s="16" t="s">
         <v>115</v>
       </c>
       <c r="V14" s="16"/>
-      <c r="W14" s="16"/>
+      <c r="W14" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="X14" s="16"/>
       <c r="Y14" s="16"/>
       <c r="Z14" s="16"/>
@@ -2974,28 +3053,28 @@
       <c r="AS14" s="16"/>
       <c r="AT14" s="16"/>
       <c r="AU14" s="18"/>
-      <c r="AV14" s="39" t="s">
+      <c r="AV14" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="AW14" s="23"/>
-      <c r="AX14" s="34" t="s">
+      <c r="AW14" s="22"/>
+      <c r="AX14" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="AY14" s="32" t="s">
+      <c r="AY14" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="AZ14" s="43">
+      <c r="AZ14" s="41">
         <v>46315</v>
       </c>
-      <c r="BA14" s="24" t="s">
+      <c r="BA14" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="BB14" s="16"/>
+      <c r="BB14" s="66"/>
       <c r="BC14" s="16"/>
-      <c r="BD14" s="17">
+      <c r="BD14" s="67">
         <v>46310</v>
       </c>
-      <c r="BE14" s="16" t="s">
+      <c r="BE14" s="68" t="s">
         <v>179</v>
       </c>
       <c r="BF14" s="16"/>
@@ -3054,26 +3133,28 @@
       <c r="O15" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P15" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q15" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R15" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S15" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T15" s="27" t="s">
+      <c r="P15" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q15" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R15" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S15" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T15" s="25" t="s">
         <v>115</v>
       </c>
       <c r="U15" s="16" t="s">
         <v>115</v>
       </c>
       <c r="V15" s="16"/>
-      <c r="W15" s="16"/>
+      <c r="W15" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="X15" s="16"/>
       <c r="Y15" s="16"/>
       <c r="Z15" s="16"/>
@@ -3098,28 +3179,28 @@
       <c r="AS15" s="17"/>
       <c r="AT15" s="16"/>
       <c r="AU15" s="18"/>
-      <c r="AV15" s="39" t="s">
+      <c r="AV15" s="37" t="s">
         <v>171</v>
       </c>
       <c r="AW15" s="17"/>
-      <c r="AX15" s="31" t="s">
+      <c r="AX15" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="AY15" s="32" t="s">
+      <c r="AY15" s="30" t="s">
         <v>143</v>
       </c>
       <c r="AZ15" s="20"/>
       <c r="BA15" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="BB15" s="18" t="s">
+      <c r="BB15" s="66" t="s">
         <v>167</v>
       </c>
       <c r="BC15" s="17"/>
-      <c r="BD15" s="17">
+      <c r="BD15" s="67">
         <v>46310</v>
       </c>
-      <c r="BE15" s="16" t="s">
+      <c r="BE15" s="68" t="s">
         <v>179</v>
       </c>
       <c r="BF15" s="16"/>
@@ -3169,7 +3250,7 @@
       <c r="L16" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="M16" s="37" t="s">
+      <c r="M16" s="35" t="s">
         <v>115</v>
       </c>
       <c r="N16" s="16" t="s">
@@ -3178,26 +3259,28 @@
       <c r="O16" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P16" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q16" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R16" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S16" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T16" s="44" t="s">
+      <c r="P16" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q16" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R16" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S16" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T16" s="42" t="s">
         <v>115</v>
       </c>
       <c r="U16" s="16" t="s">
         <v>115</v>
       </c>
       <c r="V16" s="16"/>
-      <c r="W16" s="16"/>
+      <c r="W16" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="X16" s="16"/>
       <c r="Y16" s="16"/>
       <c r="Z16" s="16"/>
@@ -3224,28 +3307,28 @@
       <c r="AU16" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="AV16" s="39" t="s">
+      <c r="AV16" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="AW16" s="43">
+      <c r="AW16" s="41">
         <v>46315</v>
       </c>
-      <c r="AX16" s="31" t="s">
+      <c r="AX16" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="AY16" s="32" t="s">
+      <c r="AY16" s="30" t="s">
         <v>127</v>
       </c>
       <c r="AZ16" s="17"/>
-      <c r="BA16" s="20" t="s">
+      <c r="BA16" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="BB16" s="20" t="s">
+      <c r="BB16" s="66" t="s">
         <v>33</v>
       </c>
       <c r="BC16" s="17"/>
-      <c r="BD16" s="16"/>
-      <c r="BE16" s="24"/>
+      <c r="BD16" s="68"/>
+      <c r="BE16" s="70"/>
       <c r="BF16" s="16"/>
       <c r="BG16" s="17"/>
       <c r="BH16" s="16"/>
@@ -3302,26 +3385,28 @@
       <c r="O17" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P17" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q17" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R17" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S17" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T17" s="44" t="s">
+      <c r="P17" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q17" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R17" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S17" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T17" s="42" t="s">
         <v>115</v>
       </c>
       <c r="U17" s="16" t="s">
         <v>115</v>
       </c>
       <c r="V17" s="16"/>
-      <c r="W17" s="16"/>
+      <c r="W17" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="X17" s="16"/>
       <c r="Y17" s="16"/>
       <c r="Z17" s="16"/>
@@ -3348,26 +3433,26 @@
       <c r="AU17" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="AV17" s="40" t="s">
+      <c r="AV17" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="AW17" s="43">
+      <c r="AW17" s="41">
         <v>46315</v>
       </c>
-      <c r="AX17" s="31" t="s">
+      <c r="AX17" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="AY17" s="32" t="s">
+      <c r="AY17" s="30" t="s">
         <v>151</v>
       </c>
       <c r="AZ17" s="17"/>
-      <c r="BA17" s="24" t="s">
+      <c r="BA17" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="BB17" s="16"/>
+      <c r="BB17" s="66"/>
       <c r="BC17" s="17"/>
-      <c r="BD17" s="16"/>
-      <c r="BE17" s="16"/>
+      <c r="BD17" s="68"/>
+      <c r="BE17" s="68"/>
       <c r="BF17" s="16"/>
       <c r="BG17" s="17"/>
       <c r="BH17" s="16"/>
@@ -3417,7 +3502,7 @@
       <c r="L18" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="M18" s="37" t="s">
+      <c r="M18" s="35" t="s">
         <v>115</v>
       </c>
       <c r="N18" s="16" t="s">
@@ -3426,26 +3511,28 @@
       <c r="O18" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P18" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q18" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R18" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S18" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T18" s="27" t="s">
+      <c r="P18" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q18" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R18" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S18" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T18" s="25" t="s">
         <v>115</v>
       </c>
       <c r="U18" s="16" t="s">
         <v>115</v>
       </c>
       <c r="V18" s="16"/>
-      <c r="W18" s="16"/>
+      <c r="W18" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="X18" s="16"/>
       <c r="Y18" s="16"/>
       <c r="Z18" s="16"/>
@@ -3469,29 +3556,29 @@
       <c r="AR18" s="16"/>
       <c r="AS18" s="17"/>
       <c r="AT18" s="16"/>
-      <c r="AU18" s="41" t="s">
+      <c r="AU18" s="39" t="s">
         <v>176</v>
       </c>
-      <c r="AV18" s="42" t="s">
+      <c r="AV18" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="AW18" s="43">
+      <c r="AW18" s="41">
         <v>46307</v>
       </c>
-      <c r="AX18" s="33" t="s">
+      <c r="AX18" s="31" t="s">
         <v>152</v>
       </c>
-      <c r="AY18" s="32" t="s">
+      <c r="AY18" s="30" t="s">
         <v>153</v>
       </c>
       <c r="AZ18" s="20"/>
-      <c r="BA18" s="21" t="s">
+      <c r="BA18" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="BB18" s="21"/>
+      <c r="BB18" s="66"/>
       <c r="BC18" s="17"/>
-      <c r="BD18" s="16"/>
-      <c r="BE18" s="16"/>
+      <c r="BD18" s="68"/>
+      <c r="BE18" s="68"/>
       <c r="BF18" s="16"/>
       <c r="BG18" s="17"/>
       <c r="BH18" s="16"/>
@@ -3501,7 +3588,7 @@
       <c r="BL18" s="17"/>
       <c r="BM18" s="16"/>
       <c r="BN18" s="16"/>
-      <c r="BO18" s="67">
+      <c r="BO18" s="45">
         <v>14</v>
       </c>
       <c r="BQ18" t="s">
@@ -3512,7 +3599,7 @@
       <c r="A19" s="3">
         <v>16</v>
       </c>
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="27" t="s">
         <v>97</v>
       </c>
       <c r="C19" s="4">
@@ -3539,7 +3626,7 @@
       <c r="L19" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="M19" s="38" t="s">
+      <c r="M19" s="36" t="s">
         <v>115</v>
       </c>
       <c r="N19" s="16" t="s">
@@ -3548,26 +3635,28 @@
       <c r="O19" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P19" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q19" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R19" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S19" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T19" s="44" t="s">
+      <c r="P19" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q19" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R19" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S19" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T19" s="42" t="s">
         <v>115</v>
       </c>
       <c r="U19" s="16" t="s">
         <v>115</v>
       </c>
       <c r="V19" s="16"/>
-      <c r="W19" s="16"/>
+      <c r="W19" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="X19" s="16"/>
       <c r="Y19" s="16"/>
       <c r="Z19" s="16"/>
@@ -3594,28 +3683,28 @@
       <c r="AU19" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="AV19" s="40" t="s">
+      <c r="AV19" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="AW19" s="43">
+      <c r="AW19" s="41">
         <v>46315</v>
       </c>
-      <c r="AX19" s="31" t="s">
+      <c r="AX19" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="AY19" s="32" t="s">
+      <c r="AY19" s="30" t="s">
         <v>151</v>
       </c>
       <c r="AZ19" s="17"/>
-      <c r="BA19" s="24" t="s">
+      <c r="BA19" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="BB19" s="21"/>
-      <c r="BC19" s="20"/>
-      <c r="BD19" s="17">
+      <c r="BB19" s="66"/>
+      <c r="BC19" s="74"/>
+      <c r="BD19" s="67">
         <v>46315</v>
       </c>
-      <c r="BE19" s="21" t="s">
+      <c r="BE19" s="69" t="s">
         <v>181</v>
       </c>
       <c r="BF19" s="16"/>
@@ -3665,7 +3754,7 @@
       <c r="L20" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="M20" s="37" t="s">
+      <c r="M20" s="35" t="s">
         <v>115</v>
       </c>
       <c r="N20" s="16" t="s">
@@ -3674,26 +3763,28 @@
       <c r="O20" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P20" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q20" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R20" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S20" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T20" s="27" t="s">
+      <c r="P20" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q20" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R20" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S20" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T20" s="25" t="s">
         <v>115</v>
       </c>
       <c r="U20" s="16" t="s">
         <v>115</v>
       </c>
       <c r="V20" s="16"/>
-      <c r="W20" s="16"/>
+      <c r="W20" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="X20" s="16"/>
       <c r="Y20" s="16"/>
       <c r="Z20" s="16"/>
@@ -3718,26 +3809,26 @@
       <c r="AS20" s="17"/>
       <c r="AT20" s="16"/>
       <c r="AU20" s="18"/>
-      <c r="AV20" s="39" t="s">
+      <c r="AV20" s="37" t="s">
         <v>171</v>
       </c>
       <c r="AW20" s="20"/>
-      <c r="AX20" s="25" t="s">
+      <c r="AX20" s="24" t="s">
         <v>136</v>
       </c>
       <c r="AY20" s="18" t="s">
         <v>137</v>
       </c>
       <c r="AZ20" s="17"/>
-      <c r="BA20" s="18">
-        <v>9.1</v>
-      </c>
-      <c r="BB20" s="18" t="s">
+      <c r="BA20" s="71" t="s">
+        <v>190</v>
+      </c>
+      <c r="BB20" s="66" t="s">
         <v>162</v>
       </c>
       <c r="BC20" s="16"/>
-      <c r="BD20" s="16"/>
-      <c r="BE20" s="16"/>
+      <c r="BD20" s="68"/>
+      <c r="BE20" s="68"/>
       <c r="BF20" s="16"/>
       <c r="BG20" s="17"/>
       <c r="BH20" s="16"/>
@@ -3794,26 +3885,28 @@
       <c r="O21" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="P21" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q21" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R21" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S21" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="T21" s="27" t="s">
+      <c r="P21" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q21" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R21" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S21" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="T21" s="25" t="s">
         <v>115</v>
       </c>
       <c r="U21" s="16" t="s">
         <v>116</v>
       </c>
       <c r="V21" s="16"/>
-      <c r="W21" s="16"/>
+      <c r="W21" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="X21" s="16"/>
       <c r="Y21" s="16"/>
       <c r="Z21" s="16"/>
@@ -3840,22 +3933,22 @@
       <c r="AU21" s="18"/>
       <c r="AV21" s="18"/>
       <c r="AW21" s="20"/>
-      <c r="AX21" s="34" t="s">
+      <c r="AX21" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="AY21" s="32" t="s">
+      <c r="AY21" s="30" t="s">
         <v>155</v>
       </c>
       <c r="AZ21" s="20"/>
-      <c r="BA21" s="18">
-        <v>9.4</v>
-      </c>
-      <c r="BB21" s="18" t="s">
+      <c r="BA21" s="71" t="s">
+        <v>189</v>
+      </c>
+      <c r="BB21" s="66" t="s">
         <v>161</v>
       </c>
       <c r="BC21" s="17"/>
-      <c r="BD21" s="16"/>
-      <c r="BE21" s="16"/>
+      <c r="BD21" s="68"/>
+      <c r="BE21" s="68"/>
       <c r="BF21" s="16"/>
       <c r="BG21" s="17"/>
       <c r="BH21" s="16"/>
@@ -3912,26 +4005,28 @@
       <c r="O22" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="P22" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q22" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R22" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S22" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="T22" s="27" t="s">
+      <c r="P22" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q22" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R22" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S22" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="T22" s="25" t="s">
         <v>115</v>
       </c>
       <c r="U22" s="16" t="s">
         <v>115</v>
       </c>
       <c r="V22" s="16"/>
-      <c r="W22" s="16"/>
+      <c r="W22" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="X22" s="16"/>
       <c r="Y22" s="16"/>
       <c r="Z22" s="16"/>
@@ -3958,22 +4053,22 @@
       <c r="AU22" s="18"/>
       <c r="AV22" s="18"/>
       <c r="AW22" s="20"/>
-      <c r="AX22" s="25" t="s">
+      <c r="AX22" s="24" t="s">
         <v>138</v>
       </c>
       <c r="AY22" s="7" t="s">
         <v>139</v>
       </c>
       <c r="AZ22" s="20"/>
-      <c r="BA22" s="21" t="s">
+      <c r="BA22" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="BB22" s="21"/>
+      <c r="BB22" s="66"/>
       <c r="BC22" s="17"/>
-      <c r="BD22" s="17">
+      <c r="BD22" s="67">
         <v>46315</v>
       </c>
-      <c r="BE22" s="16" t="s">
+      <c r="BE22" s="68" t="s">
         <v>184</v>
       </c>
       <c r="BF22" s="16"/>
@@ -4032,26 +4127,28 @@
       <c r="O23" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P23" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q23" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R23" s="46" t="s">
-        <v>115</v>
-      </c>
-      <c r="S23" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T23" s="27" t="s">
+      <c r="P23" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q23" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R23" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="S23" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T23" s="25" t="s">
         <v>115</v>
       </c>
       <c r="U23" s="16" t="s">
         <v>115</v>
       </c>
       <c r="V23" s="16"/>
-      <c r="W23" s="16"/>
+      <c r="W23" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="X23" s="16"/>
       <c r="Y23" s="16"/>
       <c r="Z23" s="16"/>
@@ -4078,20 +4175,20 @@
       <c r="AU23" s="17"/>
       <c r="AV23" s="18"/>
       <c r="AW23" s="20"/>
-      <c r="AX23" s="24" t="s">
+      <c r="AX23" s="23" t="s">
         <v>156</v>
       </c>
       <c r="AY23" s="18"/>
       <c r="AZ23" s="17"/>
-      <c r="BA23" t="s">
+      <c r="BA23" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="BB23" s="21"/>
+      <c r="BB23" s="66"/>
       <c r="BC23" s="16"/>
-      <c r="BD23" s="17">
+      <c r="BD23" s="67">
         <v>46315</v>
       </c>
-      <c r="BE23" s="16" t="s">
+      <c r="BE23" s="68" t="s">
         <v>183</v>
       </c>
       <c r="BF23" s="16"/>
@@ -4150,26 +4247,28 @@
       <c r="O24" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P24" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q24" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R24" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S24" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T24" s="27" t="s">
+      <c r="P24" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q24" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R24" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S24" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T24" s="25" t="s">
         <v>116</v>
       </c>
       <c r="U24" s="16" t="s">
         <v>115</v>
       </c>
       <c r="V24" s="16"/>
-      <c r="W24" s="16"/>
+      <c r="W24" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="X24" s="16"/>
       <c r="Y24" s="16"/>
       <c r="Z24" s="16"/>
@@ -4193,31 +4292,31 @@
       <c r="AR24" s="16"/>
       <c r="AS24" s="16"/>
       <c r="AT24" s="16"/>
-      <c r="AU24" s="41" t="s">
+      <c r="AU24" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="AV24" s="42" t="s">
+      <c r="AV24" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="AW24" s="43">
+      <c r="AW24" s="41">
         <v>46307</v>
       </c>
-      <c r="AX24" s="24" t="s">
+      <c r="AX24" s="23" t="s">
         <v>157</v>
       </c>
       <c r="AY24" s="16"/>
       <c r="AZ24" s="16"/>
-      <c r="BA24" s="68" t="s">
+      <c r="BA24" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="BB24" s="21" t="s">
+      <c r="BB24" s="66" t="s">
         <v>37</v>
       </c>
       <c r="BC24" s="16"/>
-      <c r="BD24" s="17">
+      <c r="BD24" s="67">
         <v>46303</v>
       </c>
-      <c r="BE24" s="16" t="s">
+      <c r="BE24" s="68" t="s">
         <v>173</v>
       </c>
       <c r="BF24" s="16"/>
@@ -4229,7 +4328,7 @@
       <c r="BL24" s="16"/>
       <c r="BM24" s="16"/>
       <c r="BN24" s="16"/>
-      <c r="BO24" s="67">
+      <c r="BO24" s="45">
         <v>20</v>
       </c>
       <c r="BQ24" t="s">
@@ -4278,26 +4377,28 @@
       <c r="O25" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P25" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q25" s="44" t="s">
-        <v>115</v>
-      </c>
-      <c r="R25" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S25" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T25" s="27" t="s">
+      <c r="P25" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q25" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="R25" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S25" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T25" s="25" t="s">
         <v>115</v>
       </c>
       <c r="U25" s="16" t="s">
         <v>115</v>
       </c>
       <c r="V25" s="16"/>
-      <c r="W25" s="16"/>
+      <c r="W25" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="X25" s="16"/>
       <c r="Y25" s="16"/>
       <c r="Z25" s="16"/>
@@ -4324,20 +4425,20 @@
       <c r="AU25" s="18"/>
       <c r="AV25" s="18"/>
       <c r="AW25" s="20"/>
-      <c r="AX25" s="24" t="s">
+      <c r="AX25" s="23" t="s">
         <v>48</v>
       </c>
       <c r="AY25" s="18"/>
       <c r="AZ25" s="20"/>
-      <c r="BA25" s="21" t="s">
+      <c r="BA25" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="BB25" s="18"/>
+      <c r="BB25" s="66"/>
       <c r="BC25" s="17"/>
-      <c r="BD25" s="17">
+      <c r="BD25" s="67">
         <v>46315</v>
       </c>
-      <c r="BE25" s="16" t="s">
+      <c r="BE25" s="68" t="s">
         <v>183</v>
       </c>
       <c r="BF25" s="16"/>
@@ -4387,77 +4488,85 @@
       <c r="L26" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="M26" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="N26" s="27" t="s">
+      <c r="M26" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="N26" s="25" t="s">
         <v>115</v>
       </c>
       <c r="O26" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P26" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q26" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R26" s="46" t="s">
-        <v>115</v>
-      </c>
-      <c r="S26" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T26" s="44" t="s">
-        <v>115</v>
-      </c>
-      <c r="U26" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="V26" s="27"/>
-      <c r="W26" s="27"/>
-      <c r="X26" s="27"/>
-      <c r="Y26" s="27"/>
-      <c r="Z26" s="27"/>
-      <c r="AA26" s="27"/>
-      <c r="AB26" s="27"/>
-      <c r="AC26" s="27"/>
-      <c r="AD26" s="27"/>
-      <c r="AE26" s="27"/>
-      <c r="AF26" s="27"/>
-      <c r="AG26" s="27"/>
-      <c r="AH26" s="27"/>
-      <c r="AI26" s="27"/>
-      <c r="AJ26" s="27"/>
-      <c r="AK26" s="27"/>
-      <c r="AL26" s="27"/>
-      <c r="AM26" s="27"/>
-      <c r="AN26" s="27"/>
-      <c r="AO26" s="27"/>
-      <c r="AP26" s="27"/>
-      <c r="AQ26" s="27"/>
-      <c r="AR26" s="27"/>
+      <c r="P26" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q26" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R26" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="S26" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T26" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="U26" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="V26" s="25"/>
+      <c r="W26" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="X26" s="25"/>
+      <c r="Y26" s="25"/>
+      <c r="Z26" s="25"/>
+      <c r="AA26" s="25"/>
+      <c r="AB26" s="25"/>
+      <c r="AC26" s="25"/>
+      <c r="AD26" s="25"/>
+      <c r="AE26" s="25"/>
+      <c r="AF26" s="25"/>
+      <c r="AG26" s="25"/>
+      <c r="AH26" s="25"/>
+      <c r="AI26" s="25"/>
+      <c r="AJ26" s="25"/>
+      <c r="AK26" s="25"/>
+      <c r="AL26" s="25"/>
+      <c r="AM26" s="25"/>
+      <c r="AN26" s="25"/>
+      <c r="AO26" s="25"/>
+      <c r="AP26" s="25"/>
+      <c r="AQ26" s="25"/>
+      <c r="AR26" s="25"/>
       <c r="AS26" s="17"/>
-      <c r="AT26" s="27"/>
-      <c r="AU26" s="18"/>
-      <c r="AV26" s="18"/>
-      <c r="AW26" s="20"/>
+      <c r="AT26" s="25"/>
+      <c r="AU26" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="AV26" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="AW26" s="20">
+        <v>46314</v>
+      </c>
       <c r="AX26" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AY26" s="32" t="s">
+      <c r="AY26" s="30" t="s">
         <v>147</v>
       </c>
       <c r="AZ26" s="17"/>
       <c r="BA26" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="BB26" s="21"/>
+      <c r="BB26" s="66"/>
       <c r="BC26" s="17"/>
-      <c r="BD26" s="17">
+      <c r="BD26" s="67">
         <v>46315</v>
       </c>
-      <c r="BE26" s="16" t="s">
+      <c r="BE26" s="68" t="s">
         <v>183</v>
       </c>
       <c r="BF26" s="16"/>
@@ -4467,9 +4576,9 @@
       <c r="BJ26" s="16"/>
       <c r="BK26" s="17"/>
       <c r="BL26" s="17"/>
-      <c r="BM26" s="27"/>
-      <c r="BN26" s="27"/>
-      <c r="BO26" s="67">
+      <c r="BM26" s="25"/>
+      <c r="BN26" s="25"/>
+      <c r="BO26" s="45">
         <v>22</v>
       </c>
       <c r="BP26" s="14" t="s">
@@ -4519,74 +4628,74 @@
       <c r="O27" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P27" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q27" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R27" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S27" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="T27" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="U27" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="V27" s="28"/>
-      <c r="W27" s="28"/>
-      <c r="X27" s="28"/>
-      <c r="Y27" s="28"/>
-      <c r="Z27" s="28"/>
-      <c r="AA27" s="28"/>
-      <c r="AB27" s="28"/>
-      <c r="AC27" s="28"/>
-      <c r="AD27" s="28"/>
-      <c r="AE27" s="28"/>
-      <c r="AF27" s="28"/>
-      <c r="AG27" s="28"/>
-      <c r="AH27" s="28"/>
-      <c r="AI27" s="28"/>
-      <c r="AJ27" s="28"/>
-      <c r="AK27" s="28"/>
-      <c r="AL27" s="28"/>
-      <c r="AM27" s="28"/>
-      <c r="AN27" s="28"/>
-      <c r="AO27" s="28"/>
-      <c r="AP27" s="28"/>
-      <c r="AQ27" s="28"/>
-      <c r="AR27" s="28"/>
+      <c r="P27" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q27" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R27" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S27" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="T27" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="U27" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="V27" s="25"/>
+      <c r="W27" s="25"/>
+      <c r="X27" s="26"/>
+      <c r="Y27" s="26"/>
+      <c r="Z27" s="26"/>
+      <c r="AA27" s="26"/>
+      <c r="AB27" s="26"/>
+      <c r="AC27" s="26"/>
+      <c r="AD27" s="26"/>
+      <c r="AE27" s="26"/>
+      <c r="AF27" s="26"/>
+      <c r="AG27" s="26"/>
+      <c r="AH27" s="26"/>
+      <c r="AI27" s="26"/>
+      <c r="AJ27" s="26"/>
+      <c r="AK27" s="26"/>
+      <c r="AL27" s="26"/>
+      <c r="AM27" s="26"/>
+      <c r="AN27" s="26"/>
+      <c r="AO27" s="26"/>
+      <c r="AP27" s="26"/>
+      <c r="AQ27" s="26"/>
+      <c r="AR27" s="26"/>
       <c r="AS27" s="17"/>
-      <c r="AT27" s="28"/>
-      <c r="AU27" s="41" t="s">
+      <c r="AT27" s="26"/>
+      <c r="AU27" s="39" t="s">
         <v>175</v>
       </c>
-      <c r="AV27" s="42" t="s">
+      <c r="AV27" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="AW27" s="43">
+      <c r="AW27" s="41">
         <v>46307</v>
       </c>
       <c r="AX27" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="AY27" s="32" t="s">
+      <c r="AY27" s="30" t="s">
         <v>129</v>
       </c>
       <c r="AZ27" s="17"/>
-      <c r="BA27" s="20" t="s">
+      <c r="BA27" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="BB27" s="20" t="s">
+      <c r="BB27" s="66" t="s">
         <v>77</v>
       </c>
       <c r="BC27" s="16"/>
-      <c r="BD27" s="16"/>
-      <c r="BE27" s="16"/>
+      <c r="BD27" s="68"/>
+      <c r="BE27" s="68"/>
       <c r="BF27" s="16"/>
       <c r="BG27" s="17"/>
       <c r="BH27" s="16"/>
@@ -4594,8 +4703,8 @@
       <c r="BJ27" s="16"/>
       <c r="BK27" s="17"/>
       <c r="BL27" s="17"/>
-      <c r="BM27" s="28"/>
-      <c r="BN27" s="28"/>
+      <c r="BM27" s="26"/>
+      <c r="BN27" s="26"/>
       <c r="BO27">
         <v>23</v>
       </c>
@@ -4645,66 +4754,68 @@
       <c r="O28" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P28" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q28" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="R28" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="S28" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T28" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="U28" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="V28" s="28"/>
-      <c r="W28" s="28"/>
-      <c r="X28" s="28"/>
-      <c r="Y28" s="28"/>
-      <c r="Z28" s="28"/>
-      <c r="AA28" s="28"/>
-      <c r="AB28" s="28"/>
-      <c r="AC28" s="28"/>
-      <c r="AD28" s="28"/>
-      <c r="AE28" s="28"/>
-      <c r="AF28" s="28"/>
-      <c r="AG28" s="28"/>
-      <c r="AH28" s="28"/>
-      <c r="AI28" s="28"/>
-      <c r="AJ28" s="28"/>
-      <c r="AK28" s="28"/>
-      <c r="AL28" s="28"/>
-      <c r="AM28" s="28"/>
-      <c r="AN28" s="28"/>
-      <c r="AO28" s="28"/>
-      <c r="AP28" s="28"/>
-      <c r="AQ28" s="28"/>
-      <c r="AR28" s="28"/>
+      <c r="P28" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q28" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="R28" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="S28" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T28" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="U28" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="V28" s="25"/>
+      <c r="W28" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="X28" s="26"/>
+      <c r="Y28" s="26"/>
+      <c r="Z28" s="26"/>
+      <c r="AA28" s="26"/>
+      <c r="AB28" s="26"/>
+      <c r="AC28" s="26"/>
+      <c r="AD28" s="26"/>
+      <c r="AE28" s="26"/>
+      <c r="AF28" s="26"/>
+      <c r="AG28" s="26"/>
+      <c r="AH28" s="26"/>
+      <c r="AI28" s="26"/>
+      <c r="AJ28" s="26"/>
+      <c r="AK28" s="26"/>
+      <c r="AL28" s="26"/>
+      <c r="AM28" s="26"/>
+      <c r="AN28" s="26"/>
+      <c r="AO28" s="26"/>
+      <c r="AP28" s="26"/>
+      <c r="AQ28" s="26"/>
+      <c r="AR28" s="26"/>
       <c r="AS28" s="17"/>
-      <c r="AT28" s="28"/>
+      <c r="AT28" s="26"/>
       <c r="AU28" s="18"/>
       <c r="AV28" s="18"/>
-      <c r="AW28" s="30"/>
-      <c r="AX28" s="25" t="s">
+      <c r="AW28" s="28"/>
+      <c r="AX28" s="24" t="s">
         <v>138</v>
       </c>
       <c r="AY28" s="7" t="s">
         <v>139</v>
       </c>
       <c r="AZ28" s="17"/>
-      <c r="BA28" s="21" t="s">
+      <c r="BA28" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="BB28" s="21"/>
+      <c r="BB28" s="66"/>
       <c r="BC28" s="16"/>
-      <c r="BD28" s="16"/>
-      <c r="BE28" s="16"/>
+      <c r="BD28" s="68"/>
+      <c r="BE28" s="68"/>
       <c r="BF28" s="16"/>
       <c r="BG28" s="17"/>
       <c r="BH28" s="16"/>
@@ -4712,8 +4823,8 @@
       <c r="BJ28" s="16"/>
       <c r="BK28" s="17"/>
       <c r="BL28" s="17"/>
-      <c r="BM28" s="28"/>
-      <c r="BN28" s="28"/>
+      <c r="BM28" s="26"/>
+      <c r="BN28" s="26"/>
     </row>
     <row r="29" spans="1:69" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
@@ -4755,72 +4866,74 @@
       <c r="O29" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P29" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q29" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="R29" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S29" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T29" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="U29" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="V29" s="28"/>
-      <c r="W29" s="28"/>
-      <c r="X29" s="28"/>
-      <c r="Y29" s="28"/>
-      <c r="Z29" s="28"/>
-      <c r="AA29" s="28"/>
-      <c r="AB29" s="28"/>
-      <c r="AC29" s="28"/>
-      <c r="AD29" s="28"/>
-      <c r="AE29" s="28"/>
-      <c r="AF29" s="28"/>
-      <c r="AG29" s="28"/>
-      <c r="AH29" s="28"/>
-      <c r="AI29" s="28"/>
-      <c r="AJ29" s="28"/>
-      <c r="AK29" s="28"/>
-      <c r="AL29" s="28"/>
-      <c r="AM29" s="28"/>
-      <c r="AN29" s="28"/>
-      <c r="AO29" s="28"/>
-      <c r="AP29" s="28"/>
-      <c r="AQ29" s="28"/>
-      <c r="AR29" s="28"/>
+      <c r="P29" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q29" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="R29" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S29" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T29" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="U29" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="V29" s="25"/>
+      <c r="W29" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="X29" s="26"/>
+      <c r="Y29" s="26"/>
+      <c r="Z29" s="26"/>
+      <c r="AA29" s="26"/>
+      <c r="AB29" s="26"/>
+      <c r="AC29" s="26"/>
+      <c r="AD29" s="26"/>
+      <c r="AE29" s="26"/>
+      <c r="AF29" s="26"/>
+      <c r="AG29" s="26"/>
+      <c r="AH29" s="26"/>
+      <c r="AI29" s="26"/>
+      <c r="AJ29" s="26"/>
+      <c r="AK29" s="26"/>
+      <c r="AL29" s="26"/>
+      <c r="AM29" s="26"/>
+      <c r="AN29" s="26"/>
+      <c r="AO29" s="26"/>
+      <c r="AP29" s="26"/>
+      <c r="AQ29" s="26"/>
+      <c r="AR29" s="26"/>
       <c r="AS29" s="17"/>
-      <c r="AT29" s="28"/>
-      <c r="AU29" s="41" t="s">
+      <c r="AT29" s="26"/>
+      <c r="AU29" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="AV29" s="42" t="s">
+      <c r="AV29" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="AW29" s="43">
+      <c r="AW29" s="41">
         <v>46307</v>
       </c>
-      <c r="AX29" s="24" t="s">
+      <c r="AX29" s="23" t="s">
         <v>157</v>
       </c>
       <c r="AY29" s="18"/>
       <c r="AZ29" s="17"/>
-      <c r="BA29" s="68" t="s">
+      <c r="BA29" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="BB29" s="21" t="s">
+      <c r="BB29" s="66" t="s">
         <v>37</v>
       </c>
       <c r="BC29" s="16"/>
-      <c r="BD29" s="16"/>
-      <c r="BE29" s="16"/>
+      <c r="BD29" s="68"/>
+      <c r="BE29" s="68"/>
       <c r="BF29" s="16"/>
       <c r="BG29" s="17"/>
       <c r="BH29" s="16"/>
@@ -4828,8 +4941,8 @@
       <c r="BJ29" s="16"/>
       <c r="BK29" s="17"/>
       <c r="BL29" s="17"/>
-      <c r="BM29" s="28"/>
-      <c r="BN29" s="28"/>
+      <c r="BM29" s="26"/>
+      <c r="BN29" s="26"/>
     </row>
     <row r="30" spans="1:69" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
@@ -4862,7 +4975,7 @@
       <c r="L30" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="M30" s="37" t="s">
+      <c r="M30" s="35" t="s">
         <v>115</v>
       </c>
       <c r="N30" s="16" t="s">
@@ -4871,72 +4984,74 @@
       <c r="O30" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P30" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q30" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R30" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S30" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T30" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="U30" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="V30" s="28"/>
-      <c r="W30" s="28"/>
-      <c r="X30" s="28"/>
-      <c r="Y30" s="28"/>
-      <c r="Z30" s="28"/>
-      <c r="AA30" s="28"/>
-      <c r="AB30" s="28"/>
-      <c r="AC30" s="28"/>
-      <c r="AD30" s="28"/>
-      <c r="AE30" s="28"/>
-      <c r="AF30" s="28"/>
-      <c r="AG30" s="28"/>
-      <c r="AH30" s="28"/>
-      <c r="AI30" s="28"/>
-      <c r="AJ30" s="28"/>
-      <c r="AK30" s="28"/>
-      <c r="AL30" s="28"/>
-      <c r="AM30" s="28"/>
-      <c r="AN30" s="28"/>
-      <c r="AO30" s="28"/>
-      <c r="AP30" s="28"/>
-      <c r="AQ30" s="28"/>
-      <c r="AR30" s="28"/>
+      <c r="P30" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q30" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R30" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S30" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T30" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="U30" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="V30" s="25"/>
+      <c r="W30" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="X30" s="26"/>
+      <c r="Y30" s="26"/>
+      <c r="Z30" s="26"/>
+      <c r="AA30" s="26"/>
+      <c r="AB30" s="26"/>
+      <c r="AC30" s="26"/>
+      <c r="AD30" s="26"/>
+      <c r="AE30" s="26"/>
+      <c r="AF30" s="26"/>
+      <c r="AG30" s="26"/>
+      <c r="AH30" s="26"/>
+      <c r="AI30" s="26"/>
+      <c r="AJ30" s="26"/>
+      <c r="AK30" s="26"/>
+      <c r="AL30" s="26"/>
+      <c r="AM30" s="26"/>
+      <c r="AN30" s="26"/>
+      <c r="AO30" s="26"/>
+      <c r="AP30" s="26"/>
+      <c r="AQ30" s="26"/>
+      <c r="AR30" s="26"/>
       <c r="AS30" s="17"/>
-      <c r="AT30" s="28"/>
-      <c r="AU30" s="41" t="s">
+      <c r="AT30" s="26"/>
+      <c r="AU30" s="39" t="s">
         <v>176</v>
       </c>
-      <c r="AV30" s="42" t="s">
+      <c r="AV30" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="AW30" s="43">
+      <c r="AW30" s="41">
         <v>46307</v>
       </c>
-      <c r="AX30" s="33" t="s">
+      <c r="AX30" s="31" t="s">
         <v>152</v>
       </c>
-      <c r="AY30" s="32" t="s">
+      <c r="AY30" s="30" t="s">
         <v>153</v>
       </c>
       <c r="AZ30" s="17"/>
-      <c r="BA30" s="21" t="s">
+      <c r="BA30" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="BB30" s="26"/>
+      <c r="BB30" s="66"/>
       <c r="BC30" s="16"/>
-      <c r="BD30" s="16"/>
-      <c r="BE30" s="16"/>
+      <c r="BD30" s="68"/>
+      <c r="BE30" s="68"/>
       <c r="BF30" s="16"/>
       <c r="BG30" s="17"/>
       <c r="BH30" s="16"/>
@@ -4944,8 +5059,8 @@
       <c r="BJ30" s="16"/>
       <c r="BK30" s="17"/>
       <c r="BL30" s="17"/>
-      <c r="BM30" s="28"/>
-      <c r="BN30" s="28"/>
+      <c r="BM30" s="26"/>
+      <c r="BN30" s="26"/>
     </row>
     <row r="31" spans="1:69" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
@@ -4978,7 +5093,7 @@
       <c r="L31" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="M31" s="36" t="s">
+      <c r="M31" s="34" t="s">
         <v>115</v>
       </c>
       <c r="N31" s="16" t="s">
@@ -4987,54 +5102,56 @@
       <c r="O31" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P31" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q31" s="44" t="s">
-        <v>115</v>
-      </c>
-      <c r="R31" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S31" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T31" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="U31" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="V31" s="28"/>
-      <c r="W31" s="28"/>
-      <c r="X31" s="28"/>
-      <c r="Y31" s="28"/>
-      <c r="Z31" s="28"/>
-      <c r="AA31" s="28"/>
-      <c r="AB31" s="28"/>
-      <c r="AC31" s="28"/>
-      <c r="AD31" s="28"/>
-      <c r="AE31" s="28"/>
-      <c r="AF31" s="28"/>
-      <c r="AG31" s="28"/>
-      <c r="AH31" s="28"/>
-      <c r="AI31" s="28"/>
-      <c r="AJ31" s="28"/>
-      <c r="AK31" s="28"/>
-      <c r="AL31" s="28"/>
-      <c r="AM31" s="28"/>
-      <c r="AN31" s="28"/>
-      <c r="AO31" s="28"/>
-      <c r="AP31" s="28"/>
-      <c r="AQ31" s="28"/>
-      <c r="AR31" s="28"/>
+      <c r="P31" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q31" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="R31" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S31" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T31" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="U31" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="V31" s="25"/>
+      <c r="W31" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="X31" s="26"/>
+      <c r="Y31" s="26"/>
+      <c r="Z31" s="26"/>
+      <c r="AA31" s="26"/>
+      <c r="AB31" s="26"/>
+      <c r="AC31" s="26"/>
+      <c r="AD31" s="26"/>
+      <c r="AE31" s="26"/>
+      <c r="AF31" s="26"/>
+      <c r="AG31" s="26"/>
+      <c r="AH31" s="26"/>
+      <c r="AI31" s="26"/>
+      <c r="AJ31" s="26"/>
+      <c r="AK31" s="26"/>
+      <c r="AL31" s="26"/>
+      <c r="AM31" s="26"/>
+      <c r="AN31" s="26"/>
+      <c r="AO31" s="26"/>
+      <c r="AP31" s="26"/>
+      <c r="AQ31" s="26"/>
+      <c r="AR31" s="26"/>
       <c r="AS31" s="17"/>
-      <c r="AT31" s="28"/>
+      <c r="AT31" s="26"/>
       <c r="AU31" s="18"/>
-      <c r="AV31" s="39" t="s">
+      <c r="AV31" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="AW31" s="30"/>
+      <c r="AW31" s="28"/>
       <c r="AX31" s="19" t="s">
         <v>133</v>
       </c>
@@ -5042,17 +5159,17 @@
         <v>132</v>
       </c>
       <c r="AZ31" s="17"/>
-      <c r="BA31" s="18">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="BB31" s="18" t="s">
+      <c r="BA31" s="71" t="s">
+        <v>188</v>
+      </c>
+      <c r="BB31" s="66" t="s">
         <v>160</v>
       </c>
       <c r="BC31" s="16"/>
-      <c r="BD31" s="17">
+      <c r="BD31" s="67">
         <v>46310</v>
       </c>
-      <c r="BE31" s="21" t="s">
+      <c r="BE31" s="69" t="s">
         <v>181</v>
       </c>
       <c r="BF31" s="16"/>
@@ -5062,8 +5179,8 @@
       <c r="BJ31" s="16"/>
       <c r="BK31" s="17"/>
       <c r="BL31" s="17"/>
-      <c r="BM31" s="28"/>
-      <c r="BN31" s="28"/>
+      <c r="BM31" s="26"/>
+      <c r="BN31" s="26"/>
     </row>
     <row r="32" spans="1:69" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
@@ -5096,7 +5213,7 @@
       <c r="L32" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="M32" s="38" t="s">
+      <c r="M32" s="36" t="s">
         <v>115</v>
       </c>
       <c r="N32" s="16" t="s">
@@ -5105,74 +5222,76 @@
       <c r="O32" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P32" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q32" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R32" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S32" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T32" s="44" t="s">
-        <v>115</v>
-      </c>
-      <c r="U32" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="V32" s="28"/>
-      <c r="W32" s="28"/>
-      <c r="X32" s="28"/>
-      <c r="Y32" s="28"/>
-      <c r="Z32" s="28"/>
-      <c r="AA32" s="28"/>
-      <c r="AB32" s="28"/>
-      <c r="AC32" s="28"/>
-      <c r="AD32" s="28"/>
-      <c r="AE32" s="28"/>
-      <c r="AF32" s="28"/>
-      <c r="AG32" s="28"/>
-      <c r="AH32" s="28"/>
-      <c r="AI32" s="28"/>
-      <c r="AJ32" s="28"/>
-      <c r="AK32" s="28"/>
-      <c r="AL32" s="28"/>
-      <c r="AM32" s="28"/>
-      <c r="AN32" s="28"/>
-      <c r="AO32" s="28"/>
-      <c r="AP32" s="28"/>
-      <c r="AQ32" s="28"/>
-      <c r="AR32" s="28"/>
+      <c r="P32" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q32" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R32" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S32" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T32" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="U32" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="V32" s="25"/>
+      <c r="W32" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="X32" s="26"/>
+      <c r="Y32" s="26"/>
+      <c r="Z32" s="26"/>
+      <c r="AA32" s="26"/>
+      <c r="AB32" s="26"/>
+      <c r="AC32" s="26"/>
+      <c r="AD32" s="26"/>
+      <c r="AE32" s="26"/>
+      <c r="AF32" s="26"/>
+      <c r="AG32" s="26"/>
+      <c r="AH32" s="26"/>
+      <c r="AI32" s="26"/>
+      <c r="AJ32" s="26"/>
+      <c r="AK32" s="26"/>
+      <c r="AL32" s="26"/>
+      <c r="AM32" s="26"/>
+      <c r="AN32" s="26"/>
+      <c r="AO32" s="26"/>
+      <c r="AP32" s="26"/>
+      <c r="AQ32" s="26"/>
+      <c r="AR32" s="26"/>
       <c r="AS32" s="17"/>
-      <c r="AT32" s="28"/>
-      <c r="AU32" s="41" t="s">
+      <c r="AT32" s="26"/>
+      <c r="AU32" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="AV32" s="40" t="s">
+      <c r="AV32" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="AW32" s="43">
+      <c r="AW32" s="41">
         <v>46315</v>
       </c>
-      <c r="AX32" s="31" t="s">
+      <c r="AX32" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="AY32" s="32" t="s">
+      <c r="AY32" s="30" t="s">
         <v>131</v>
       </c>
       <c r="AZ32" s="17"/>
-      <c r="BA32" s="16" t="s">
+      <c r="BA32" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="BB32" s="26" t="s">
+      <c r="BB32" s="66" t="s">
         <v>44</v>
       </c>
       <c r="BC32" s="16"/>
-      <c r="BD32" s="16"/>
-      <c r="BE32" s="16"/>
+      <c r="BD32" s="68"/>
+      <c r="BE32" s="68"/>
       <c r="BF32" s="16"/>
       <c r="BG32" s="17"/>
       <c r="BH32" s="16"/>
@@ -5180,8 +5299,8 @@
       <c r="BJ32" s="16"/>
       <c r="BK32" s="17"/>
       <c r="BL32" s="17"/>
-      <c r="BM32" s="28"/>
-      <c r="BN32" s="28"/>
+      <c r="BM32" s="26"/>
+      <c r="BN32" s="26"/>
     </row>
     <row r="33" spans="1:69" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
@@ -5223,64 +5342,66 @@
       <c r="O33" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="P33" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q33" s="44" t="s">
-        <v>115</v>
-      </c>
-      <c r="R33" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="S33" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T33" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="U33" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="V33" s="28"/>
-      <c r="W33" s="28"/>
-      <c r="X33" s="28"/>
-      <c r="Y33" s="28"/>
-      <c r="Z33" s="28"/>
-      <c r="AA33" s="28"/>
-      <c r="AB33" s="28"/>
-      <c r="AC33" s="28"/>
-      <c r="AD33" s="28"/>
-      <c r="AE33" s="28"/>
-      <c r="AF33" s="28"/>
-      <c r="AG33" s="28"/>
-      <c r="AH33" s="28"/>
-      <c r="AI33" s="28"/>
-      <c r="AJ33" s="28"/>
-      <c r="AK33" s="28"/>
-      <c r="AL33" s="28"/>
-      <c r="AM33" s="28"/>
-      <c r="AN33" s="28"/>
-      <c r="AO33" s="28"/>
-      <c r="AP33" s="28"/>
-      <c r="AQ33" s="28"/>
-      <c r="AR33" s="28"/>
+      <c r="P33" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q33" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="R33" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="S33" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T33" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="U33" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="V33" s="25"/>
+      <c r="W33" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="X33" s="26"/>
+      <c r="Y33" s="26"/>
+      <c r="Z33" s="26"/>
+      <c r="AA33" s="26"/>
+      <c r="AB33" s="26"/>
+      <c r="AC33" s="26"/>
+      <c r="AD33" s="26"/>
+      <c r="AE33" s="26"/>
+      <c r="AF33" s="26"/>
+      <c r="AG33" s="26"/>
+      <c r="AH33" s="26"/>
+      <c r="AI33" s="26"/>
+      <c r="AJ33" s="26"/>
+      <c r="AK33" s="26"/>
+      <c r="AL33" s="26"/>
+      <c r="AM33" s="26"/>
+      <c r="AN33" s="26"/>
+      <c r="AO33" s="26"/>
+      <c r="AP33" s="26"/>
+      <c r="AQ33" s="26"/>
+      <c r="AR33" s="26"/>
       <c r="AS33" s="17"/>
-      <c r="AT33" s="28"/>
+      <c r="AT33" s="26"/>
       <c r="AU33" s="18"/>
       <c r="AV33" s="18"/>
-      <c r="AW33" s="30"/>
-      <c r="AX33" s="24" t="s">
+      <c r="AW33" s="28"/>
+      <c r="AX33" s="23" t="s">
         <v>48</v>
       </c>
       <c r="AY33" s="18"/>
       <c r="AZ33" s="17"/>
-      <c r="BA33" s="21" t="s">
+      <c r="BA33" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="BB33" s="26"/>
+      <c r="BB33" s="66"/>
       <c r="BC33" s="16"/>
-      <c r="BD33" s="16"/>
-      <c r="BE33" s="16"/>
+      <c r="BD33" s="68"/>
+      <c r="BE33" s="68"/>
       <c r="BF33" s="16"/>
       <c r="BG33" s="17"/>
       <c r="BH33" s="16"/>
@@ -5288,8 +5409,8 @@
       <c r="BJ33" s="16"/>
       <c r="BK33" s="17"/>
       <c r="BL33" s="17"/>
-      <c r="BM33" s="28"/>
-      <c r="BN33" s="28"/>
+      <c r="BM33" s="26"/>
+      <c r="BN33" s="26"/>
     </row>
     <row r="34" spans="1:69" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
@@ -5331,56 +5452,58 @@
       <c r="O34" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P34" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q34" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R34" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S34" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T34" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="U34" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="V34" s="28"/>
-      <c r="W34" s="28"/>
-      <c r="X34" s="28"/>
-      <c r="Y34" s="28"/>
-      <c r="Z34" s="28"/>
-      <c r="AA34" s="28"/>
-      <c r="AB34" s="28"/>
-      <c r="AC34" s="28"/>
-      <c r="AD34" s="28"/>
-      <c r="AE34" s="28"/>
-      <c r="AF34" s="28"/>
-      <c r="AG34" s="28"/>
-      <c r="AH34" s="28"/>
-      <c r="AI34" s="28"/>
-      <c r="AJ34" s="28"/>
-      <c r="AK34" s="28"/>
-      <c r="AL34" s="28"/>
-      <c r="AM34" s="28"/>
-      <c r="AN34" s="28"/>
-      <c r="AO34" s="28"/>
-      <c r="AP34" s="28"/>
-      <c r="AQ34" s="28"/>
-      <c r="AR34" s="28"/>
+      <c r="P34" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q34" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R34" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S34" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T34" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="U34" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="V34" s="25"/>
+      <c r="W34" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="X34" s="26"/>
+      <c r="Y34" s="26"/>
+      <c r="Z34" s="26"/>
+      <c r="AA34" s="26"/>
+      <c r="AB34" s="26"/>
+      <c r="AC34" s="26"/>
+      <c r="AD34" s="26"/>
+      <c r="AE34" s="26"/>
+      <c r="AF34" s="26"/>
+      <c r="AG34" s="26"/>
+      <c r="AH34" s="26"/>
+      <c r="AI34" s="26"/>
+      <c r="AJ34" s="26"/>
+      <c r="AK34" s="26"/>
+      <c r="AL34" s="26"/>
+      <c r="AM34" s="26"/>
+      <c r="AN34" s="26"/>
+      <c r="AO34" s="26"/>
+      <c r="AP34" s="26"/>
+      <c r="AQ34" s="26"/>
+      <c r="AR34" s="26"/>
       <c r="AS34" s="17"/>
-      <c r="AT34" s="28"/>
+      <c r="AT34" s="26"/>
       <c r="AU34" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="AV34" s="39" t="s">
+      <c r="AV34" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="AW34" s="43">
+      <c r="AW34" s="41">
         <v>46307</v>
       </c>
       <c r="AX34" s="19" t="s">
@@ -5393,10 +5516,10 @@
       <c r="BA34" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="BB34" s="26"/>
+      <c r="BB34" s="66"/>
       <c r="BC34" s="16"/>
-      <c r="BD34" s="16"/>
-      <c r="BE34" s="16"/>
+      <c r="BD34" s="68"/>
+      <c r="BE34" s="68"/>
       <c r="BF34" s="16"/>
       <c r="BG34" s="17"/>
       <c r="BH34" s="16"/>
@@ -5404,8 +5527,8 @@
       <c r="BJ34" s="16"/>
       <c r="BK34" s="17"/>
       <c r="BL34" s="17"/>
-      <c r="BM34" s="28"/>
-      <c r="BN34" s="28"/>
+      <c r="BM34" s="26"/>
+      <c r="BN34" s="26"/>
     </row>
     <row r="35" spans="1:69" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
@@ -5438,7 +5561,7 @@
       <c r="L35" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="M35" s="36" t="s">
+      <c r="M35" s="34" t="s">
         <v>115</v>
       </c>
       <c r="N35" s="16" t="s">
@@ -5447,72 +5570,74 @@
       <c r="O35" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P35" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q35" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R35" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S35" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="T35" s="44" t="s">
-        <v>115</v>
-      </c>
-      <c r="U35" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="V35" s="28"/>
-      <c r="W35" s="28"/>
-      <c r="X35" s="28"/>
-      <c r="Y35" s="28"/>
-      <c r="Z35" s="28"/>
-      <c r="AA35" s="28"/>
-      <c r="AB35" s="28"/>
-      <c r="AC35" s="28"/>
-      <c r="AD35" s="28"/>
-      <c r="AE35" s="28"/>
-      <c r="AF35" s="28"/>
-      <c r="AG35" s="28"/>
-      <c r="AH35" s="28"/>
-      <c r="AI35" s="28"/>
-      <c r="AJ35" s="28"/>
-      <c r="AK35" s="28"/>
-      <c r="AL35" s="28"/>
-      <c r="AM35" s="28"/>
-      <c r="AN35" s="28"/>
-      <c r="AO35" s="28"/>
-      <c r="AP35" s="28"/>
-      <c r="AQ35" s="28"/>
-      <c r="AR35" s="28"/>
+      <c r="P35" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q35" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R35" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S35" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="T35" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="U35" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="V35" s="25"/>
+      <c r="W35" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="X35" s="26"/>
+      <c r="Y35" s="26"/>
+      <c r="Z35" s="26"/>
+      <c r="AA35" s="26"/>
+      <c r="AB35" s="26"/>
+      <c r="AC35" s="26"/>
+      <c r="AD35" s="26"/>
+      <c r="AE35" s="26"/>
+      <c r="AF35" s="26"/>
+      <c r="AG35" s="26"/>
+      <c r="AH35" s="26"/>
+      <c r="AI35" s="26"/>
+      <c r="AJ35" s="26"/>
+      <c r="AK35" s="26"/>
+      <c r="AL35" s="26"/>
+      <c r="AM35" s="26"/>
+      <c r="AN35" s="26"/>
+      <c r="AO35" s="26"/>
+      <c r="AP35" s="26"/>
+      <c r="AQ35" s="26"/>
+      <c r="AR35" s="26"/>
       <c r="AS35" s="17"/>
-      <c r="AT35" s="28"/>
+      <c r="AT35" s="26"/>
       <c r="AU35" s="18"/>
-      <c r="AV35" s="39" t="s">
+      <c r="AV35" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="AW35" s="30"/>
-      <c r="AX35" s="34" t="s">
+      <c r="AW35" s="28"/>
+      <c r="AX35" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="AY35" s="32" t="s">
+      <c r="AY35" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="AZ35" s="43">
+      <c r="AZ35" s="41">
         <v>46315</v>
       </c>
-      <c r="BA35" s="24" t="s">
+      <c r="BA35" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="BB35" s="26"/>
+      <c r="BB35" s="66"/>
       <c r="BC35" s="16"/>
-      <c r="BD35" s="17">
+      <c r="BD35" s="67">
         <v>46310</v>
       </c>
-      <c r="BE35" s="16" t="s">
+      <c r="BE35" s="68" t="s">
         <v>182</v>
       </c>
       <c r="BF35" s="16"/>
@@ -5522,8 +5647,8 @@
       <c r="BJ35" s="16"/>
       <c r="BK35" s="17"/>
       <c r="BL35" s="17"/>
-      <c r="BM35" s="28"/>
-      <c r="BN35" s="28"/>
+      <c r="BM35" s="26"/>
+      <c r="BN35" s="26"/>
     </row>
     <row r="36" spans="1:69" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
@@ -5565,77 +5690,79 @@
       <c r="O36" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="P36" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q36" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="R36" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="S36" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="T36" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="U36" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="V36" s="28"/>
-      <c r="W36" s="28"/>
-      <c r="X36" s="28"/>
-      <c r="Y36" s="28"/>
-      <c r="Z36" s="28"/>
-      <c r="AA36" s="28"/>
-      <c r="AB36" s="28"/>
-      <c r="AC36" s="28"/>
-      <c r="AD36" s="28"/>
-      <c r="AE36" s="28"/>
-      <c r="AF36" s="28"/>
-      <c r="AG36" s="28"/>
-      <c r="AH36" s="28"/>
-      <c r="AI36" s="28"/>
-      <c r="AJ36" s="28"/>
-      <c r="AK36" s="28"/>
-      <c r="AL36" s="28"/>
-      <c r="AM36" s="28"/>
-      <c r="AN36" s="28"/>
-      <c r="AO36" s="28"/>
-      <c r="AP36" s="28"/>
-      <c r="AQ36" s="28"/>
-      <c r="AR36" s="28"/>
-      <c r="AS36" s="28"/>
-      <c r="AT36" s="28"/>
+      <c r="P36" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q36" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R36" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="S36" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="T36" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="U36" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="V36" s="25"/>
+      <c r="W36" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="X36" s="26"/>
+      <c r="Y36" s="26"/>
+      <c r="Z36" s="26"/>
+      <c r="AA36" s="26"/>
+      <c r="AB36" s="26"/>
+      <c r="AC36" s="26"/>
+      <c r="AD36" s="26"/>
+      <c r="AE36" s="26"/>
+      <c r="AF36" s="26"/>
+      <c r="AG36" s="26"/>
+      <c r="AH36" s="26"/>
+      <c r="AI36" s="26"/>
+      <c r="AJ36" s="26"/>
+      <c r="AK36" s="26"/>
+      <c r="AL36" s="26"/>
+      <c r="AM36" s="26"/>
+      <c r="AN36" s="26"/>
+      <c r="AO36" s="26"/>
+      <c r="AP36" s="26"/>
+      <c r="AQ36" s="26"/>
+      <c r="AR36" s="26"/>
+      <c r="AS36" s="26"/>
+      <c r="AT36" s="26"/>
       <c r="AU36" s="18"/>
       <c r="AV36" s="18"/>
-      <c r="AW36" s="23"/>
-      <c r="AX36" s="24" t="s">
+      <c r="AW36" s="22"/>
+      <c r="AX36" s="23" t="s">
         <v>156</v>
       </c>
       <c r="AY36" s="18"/>
       <c r="AZ36" s="16"/>
-      <c r="BA36" t="s">
+      <c r="BA36" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="BB36" s="21"/>
+      <c r="BB36" s="66"/>
       <c r="BC36" s="16"/>
-      <c r="BD36" s="17">
+      <c r="BD36" s="67">
         <v>46315</v>
       </c>
-      <c r="BE36" s="16" t="s">
+      <c r="BE36" s="68" t="s">
         <v>183</v>
       </c>
-      <c r="BF36" s="28"/>
-      <c r="BG36" s="28"/>
+      <c r="BF36" s="26"/>
+      <c r="BG36" s="26"/>
       <c r="BH36" s="16"/>
       <c r="BI36" s="16"/>
       <c r="BJ36" s="16"/>
-      <c r="BK36" s="28"/>
-      <c r="BL36" s="28"/>
-      <c r="BM36" s="28"/>
-      <c r="BN36" s="28"/>
+      <c r="BK36" s="26"/>
+      <c r="BL36" s="26"/>
+      <c r="BM36" s="26"/>
+      <c r="BN36" s="26"/>
     </row>
     <row r="37" spans="1:69" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
@@ -5679,56 +5806,58 @@
       <c r="O37" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="P37" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q37" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="R37" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="S37" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="T37" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="U37" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="V37" s="28"/>
-      <c r="W37" s="28"/>
-      <c r="X37" s="28"/>
-      <c r="Y37" s="28"/>
-      <c r="Z37" s="28"/>
-      <c r="AA37" s="28"/>
-      <c r="AB37" s="28"/>
-      <c r="AC37" s="28"/>
-      <c r="AD37" s="28"/>
-      <c r="AE37" s="28"/>
-      <c r="AF37" s="28"/>
-      <c r="AG37" s="28"/>
-      <c r="AH37" s="28"/>
-      <c r="AI37" s="28"/>
-      <c r="AJ37" s="28"/>
-      <c r="AK37" s="28"/>
-      <c r="AL37" s="28"/>
-      <c r="AM37" s="28"/>
-      <c r="AN37" s="28"/>
-      <c r="AO37" s="28"/>
-      <c r="AP37" s="28"/>
-      <c r="AQ37" s="28"/>
-      <c r="AR37" s="28"/>
-      <c r="AS37" s="28"/>
-      <c r="AT37" s="28"/>
+      <c r="P37" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q37" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="R37" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="S37" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="T37" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="U37" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="V37" s="25"/>
+      <c r="W37" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="X37" s="26"/>
+      <c r="Y37" s="26"/>
+      <c r="Z37" s="26"/>
+      <c r="AA37" s="26"/>
+      <c r="AB37" s="26"/>
+      <c r="AC37" s="26"/>
+      <c r="AD37" s="26"/>
+      <c r="AE37" s="26"/>
+      <c r="AF37" s="26"/>
+      <c r="AG37" s="26"/>
+      <c r="AH37" s="26"/>
+      <c r="AI37" s="26"/>
+      <c r="AJ37" s="26"/>
+      <c r="AK37" s="26"/>
+      <c r="AL37" s="26"/>
+      <c r="AM37" s="26"/>
+      <c r="AN37" s="26"/>
+      <c r="AO37" s="26"/>
+      <c r="AP37" s="26"/>
+      <c r="AQ37" s="26"/>
+      <c r="AR37" s="26"/>
+      <c r="AS37" s="26"/>
+      <c r="AT37" s="26"/>
       <c r="AU37" s="18"/>
       <c r="AV37" s="18"/>
-      <c r="AW37" s="23"/>
-      <c r="AX37" s="31" t="s">
+      <c r="AW37" s="22"/>
+      <c r="AX37" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="AY37" s="32" t="s">
+      <c r="AY37" s="30" t="s">
         <v>143</v>
       </c>
       <c r="AZ37" s="16"/>
@@ -5736,69 +5865,69 @@
       <c r="BB37" s="16"/>
       <c r="BC37" s="16"/>
       <c r="BD37" s="16"/>
-      <c r="BE37" s="28"/>
-      <c r="BF37" s="28"/>
-      <c r="BG37" s="28"/>
+      <c r="BE37" s="26"/>
+      <c r="BF37" s="26"/>
+      <c r="BG37" s="26"/>
       <c r="BH37" s="16"/>
       <c r="BI37" s="16"/>
       <c r="BJ37" s="16"/>
-      <c r="BK37" s="28"/>
-      <c r="BL37" s="28"/>
-      <c r="BM37" s="28"/>
-      <c r="BN37" s="28"/>
+      <c r="BK37" s="26"/>
+      <c r="BL37" s="26"/>
+      <c r="BM37" s="26"/>
+      <c r="BN37" s="26"/>
     </row>
     <row r="38" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A38" s="60" t="s">
+      <c r="A38" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="B38" s="61"/>
-      <c r="C38" s="61"/>
-      <c r="D38" s="61"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="61"/>
-      <c r="G38" s="61"/>
-      <c r="H38" s="61"/>
-      <c r="I38" s="61"/>
-      <c r="J38" s="61"/>
-      <c r="K38" s="61"/>
-      <c r="L38" s="61"/>
-      <c r="M38" s="61"/>
-      <c r="N38" s="61"/>
-      <c r="O38" s="61"/>
-      <c r="P38" s="61"/>
-      <c r="Q38" s="61"/>
-      <c r="R38" s="61"/>
-      <c r="S38" s="61"/>
-      <c r="T38" s="61"/>
-      <c r="U38" s="61"/>
-      <c r="V38" s="61"/>
-      <c r="W38" s="61"/>
-      <c r="X38" s="61"/>
-      <c r="Y38" s="61"/>
-      <c r="Z38" s="61"/>
-      <c r="AA38" s="61"/>
-      <c r="AB38" s="61"/>
-      <c r="AC38" s="61"/>
-      <c r="AD38" s="61"/>
-      <c r="AE38" s="61"/>
-      <c r="AF38" s="61"/>
-      <c r="AG38" s="61"/>
-      <c r="AH38" s="61"/>
-      <c r="AI38" s="61"/>
-      <c r="AJ38" s="61"/>
-      <c r="AK38" s="61"/>
-      <c r="AL38" s="61"/>
-      <c r="AM38" s="61"/>
-      <c r="AN38" s="61"/>
-      <c r="AO38" s="61"/>
-      <c r="AP38" s="61"/>
-      <c r="AQ38" s="61"/>
-      <c r="AR38" s="61"/>
-      <c r="AS38" s="61"/>
-      <c r="AT38" s="61"/>
-      <c r="AU38" s="61"/>
-      <c r="AV38" s="61"/>
-      <c r="AW38" s="62"/>
+      <c r="B38" s="47"/>
+      <c r="C38" s="47"/>
+      <c r="D38" s="47"/>
+      <c r="E38" s="47"/>
+      <c r="F38" s="47"/>
+      <c r="G38" s="47"/>
+      <c r="H38" s="47"/>
+      <c r="I38" s="47"/>
+      <c r="J38" s="47"/>
+      <c r="K38" s="47"/>
+      <c r="L38" s="47"/>
+      <c r="M38" s="47"/>
+      <c r="N38" s="47"/>
+      <c r="O38" s="47"/>
+      <c r="P38" s="47"/>
+      <c r="Q38" s="47"/>
+      <c r="R38" s="47"/>
+      <c r="S38" s="47"/>
+      <c r="T38" s="47"/>
+      <c r="U38" s="47"/>
+      <c r="V38" s="47"/>
+      <c r="W38" s="47"/>
+      <c r="X38" s="47"/>
+      <c r="Y38" s="47"/>
+      <c r="Z38" s="47"/>
+      <c r="AA38" s="47"/>
+      <c r="AB38" s="47"/>
+      <c r="AC38" s="47"/>
+      <c r="AD38" s="47"/>
+      <c r="AE38" s="47"/>
+      <c r="AF38" s="47"/>
+      <c r="AG38" s="47"/>
+      <c r="AH38" s="47"/>
+      <c r="AI38" s="47"/>
+      <c r="AJ38" s="47"/>
+      <c r="AK38" s="47"/>
+      <c r="AL38" s="47"/>
+      <c r="AM38" s="47"/>
+      <c r="AN38" s="47"/>
+      <c r="AO38" s="47"/>
+      <c r="AP38" s="47"/>
+      <c r="AQ38" s="47"/>
+      <c r="AR38" s="47"/>
+      <c r="AS38" s="47"/>
+      <c r="AT38" s="47"/>
+      <c r="AU38" s="47"/>
+      <c r="AV38" s="47"/>
+      <c r="AW38" s="48"/>
       <c r="AX38" s="2"/>
       <c r="AY38" s="2"/>
       <c r="AZ38" s="2"/>
@@ -5824,57 +5953,57 @@
       </c>
     </row>
     <row r="39" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A39" s="63" t="s">
+      <c r="A39" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="B39" s="64"/>
-      <c r="C39" s="64"/>
-      <c r="D39" s="64"/>
-      <c r="E39" s="64"/>
-      <c r="F39" s="64"/>
-      <c r="G39" s="64"/>
-      <c r="H39" s="64"/>
-      <c r="I39" s="64"/>
-      <c r="J39" s="64"/>
-      <c r="K39" s="64"/>
-      <c r="L39" s="64"/>
-      <c r="M39" s="64"/>
-      <c r="N39" s="64"/>
-      <c r="O39" s="64"/>
-      <c r="P39" s="64"/>
-      <c r="Q39" s="64"/>
-      <c r="R39" s="64"/>
-      <c r="S39" s="64"/>
-      <c r="T39" s="64"/>
-      <c r="U39" s="64"/>
-      <c r="V39" s="64"/>
-      <c r="W39" s="64"/>
-      <c r="X39" s="64"/>
-      <c r="Y39" s="64"/>
-      <c r="Z39" s="64"/>
-      <c r="AA39" s="64"/>
-      <c r="AB39" s="64"/>
-      <c r="AC39" s="64"/>
-      <c r="AD39" s="64"/>
-      <c r="AE39" s="64"/>
-      <c r="AF39" s="64"/>
-      <c r="AG39" s="64"/>
-      <c r="AH39" s="64"/>
-      <c r="AI39" s="64"/>
-      <c r="AJ39" s="64"/>
-      <c r="AK39" s="64"/>
-      <c r="AL39" s="64"/>
-      <c r="AM39" s="64"/>
-      <c r="AN39" s="64"/>
-      <c r="AO39" s="64"/>
-      <c r="AP39" s="64"/>
-      <c r="AQ39" s="64"/>
-      <c r="AR39" s="64"/>
-      <c r="AS39" s="64"/>
-      <c r="AT39" s="64"/>
-      <c r="AU39" s="64"/>
-      <c r="AV39" s="64"/>
-      <c r="AW39" s="65"/>
+      <c r="B39" s="50"/>
+      <c r="C39" s="50"/>
+      <c r="D39" s="50"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="50"/>
+      <c r="G39" s="50"/>
+      <c r="H39" s="50"/>
+      <c r="I39" s="50"/>
+      <c r="J39" s="50"/>
+      <c r="K39" s="50"/>
+      <c r="L39" s="50"/>
+      <c r="M39" s="50"/>
+      <c r="N39" s="50"/>
+      <c r="O39" s="50"/>
+      <c r="P39" s="50"/>
+      <c r="Q39" s="50"/>
+      <c r="R39" s="50"/>
+      <c r="S39" s="50"/>
+      <c r="T39" s="50"/>
+      <c r="U39" s="50"/>
+      <c r="V39" s="50"/>
+      <c r="W39" s="50"/>
+      <c r="X39" s="50"/>
+      <c r="Y39" s="50"/>
+      <c r="Z39" s="50"/>
+      <c r="AA39" s="50"/>
+      <c r="AB39" s="50"/>
+      <c r="AC39" s="50"/>
+      <c r="AD39" s="50"/>
+      <c r="AE39" s="50"/>
+      <c r="AF39" s="50"/>
+      <c r="AG39" s="50"/>
+      <c r="AH39" s="50"/>
+      <c r="AI39" s="50"/>
+      <c r="AJ39" s="50"/>
+      <c r="AK39" s="50"/>
+      <c r="AL39" s="50"/>
+      <c r="AM39" s="50"/>
+      <c r="AN39" s="50"/>
+      <c r="AO39" s="50"/>
+      <c r="AP39" s="50"/>
+      <c r="AQ39" s="50"/>
+      <c r="AR39" s="50"/>
+      <c r="AS39" s="50"/>
+      <c r="AT39" s="50"/>
+      <c r="AU39" s="50"/>
+      <c r="AV39" s="50"/>
+      <c r="AW39" s="51"/>
       <c r="AX39" s="2"/>
       <c r="AY39" s="2"/>
       <c r="AZ39" s="2"/>
@@ -6310,11 +6439,11 @@
       </c>
     </row>
     <row r="50" spans="67:72" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BO50" s="35">
+      <c r="BO50" s="33">
         <v>36</v>
       </c>
-      <c r="BP50" s="35"/>
-      <c r="BQ50" s="35" t="s">
+      <c r="BP50" s="33"/>
+      <c r="BQ50" s="33" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6472,17 +6601,28 @@
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="A38:AW38"/>
-    <mergeCell ref="A39:AW39"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="AS2:AS3"/>
-    <mergeCell ref="AT2:AT3"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="AX2:AZ3"/>
+    <mergeCell ref="BA2:BC3"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="AH2:AH3"/>
+    <mergeCell ref="AI2:AI3"/>
+    <mergeCell ref="AK2:AK3"/>
+    <mergeCell ref="AL2:AL3"/>
+    <mergeCell ref="AM2:AM3"/>
+    <mergeCell ref="AN2:AN3"/>
+    <mergeCell ref="AP2:AP3"/>
+    <mergeCell ref="AO2:AO3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AJ2:AJ3"/>
     <mergeCell ref="BD2:BG3"/>
     <mergeCell ref="BH2:BK3"/>
     <mergeCell ref="BL2:BN3"/>
@@ -6499,40 +6639,29 @@
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="AU2:AW3"/>
+    <mergeCell ref="A38:AW38"/>
+    <mergeCell ref="A39:AW39"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="AS2:AS3"/>
+    <mergeCell ref="AT2:AT3"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="C2:C3"/>
     <mergeCell ref="X2:X3"/>
     <mergeCell ref="AQ2:AQ3"/>
     <mergeCell ref="AR2:AR3"/>
-    <mergeCell ref="AX2:AZ3"/>
-    <mergeCell ref="BA2:BC3"/>
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="AH2:AH3"/>
-    <mergeCell ref="AI2:AI3"/>
-    <mergeCell ref="AK2:AK3"/>
-    <mergeCell ref="AL2:AL3"/>
-    <mergeCell ref="AM2:AM3"/>
-    <mergeCell ref="AN2:AN3"/>
-    <mergeCell ref="AP2:AP3"/>
-    <mergeCell ref="AO2:AO3"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AJ2:AJ3"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="K2:K3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="BQ6" r:id="rId1" display="Прикладная дискретная математика. Приложение. 2016. № 9. С. 68-70."/>
-    <hyperlink ref="BP26" r:id="rId2"/>
-    <hyperlink ref="BQ48" r:id="rId3"/>
-    <hyperlink ref="BA24" r:id="rId4"/>
-    <hyperlink ref="BA29" r:id="rId5"/>
+    <hyperlink ref="BQ6" r:id="rId1" display="Прикладная дискретная математика. Приложение. 2016. № 9. С. 68-70." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="BP26" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="BQ48" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="BA24" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="BA29" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId6"/>
@@ -6541,6 +6670,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Документ" ma:contentTypeID="0x0101004F6380A0290AF84484F859C9FFD97568" ma:contentTypeVersion="12" ma:contentTypeDescription="Создание документа." ma:contentTypeScope="" ma:versionID="1ee9877c88efff51dfb0d3a4b3e8ad1b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bffb7b91-0466-4de0-9379-f5c53c3acedf" xmlns:ns3="b78dbef7-f85b-47b5-8738-6377d50f4027" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="532d4df54980d57387e1b5dc96a6a32c" ns2:_="" ns3:_="">
     <xsd:import namespace="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
@@ -6741,15 +6879,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -6762,6 +6891,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00280879-8A9A-4335-93BC-405126DC8F0C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B6A6DF3-AE59-43BA-A5FF-CF9B7C54D4B8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6780,14 +6917,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00280879-8A9A-4335-93BC-405126DC8F0C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12ECB55F-B88E-4FE2-9AD5-5CA5D433F306}">
   <ds:schemaRefs>

--- a/Ведомость ТКИ-441 2026-2027.xlsx
+++ b/Ведомость ТКИ-441 2026-2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\StegMethods\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB19ED5B-03E7-4540-9581-22EA0E9DED93}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3037D3F7-6097-4F22-BB59-82C18B9E02E1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="205">
   <si>
     <t>Ведомость посещаемости занятий студентами группы ТКИ РУТ МИИТ</t>
   </si>
@@ -602,13 +602,52 @@
   </si>
   <si>
     <t>Стоп-пошёл</t>
+  </si>
+  <si>
+    <t>Бабочка ППВ4</t>
+  </si>
+  <si>
+    <t>Бабочка ППЧ4</t>
+  </si>
+  <si>
+    <t>ПППВ4</t>
+  </si>
+  <si>
+    <t>ПППЧ4</t>
+  </si>
+  <si>
+    <t>16ППВ4</t>
+  </si>
+  <si>
+    <t>16ППЧ4</t>
+  </si>
+  <si>
+    <t>Бабочка ОПВ4</t>
+  </si>
+  <si>
+    <t>Бабочка ОПЧ4</t>
+  </si>
+  <si>
+    <t>ППОВ4</t>
+  </si>
+  <si>
+    <t>ППОЧ4</t>
+  </si>
+  <si>
+    <t>16ПОВ4</t>
+  </si>
+  <si>
+    <t>16ПОЧ4</t>
+  </si>
+  <si>
+    <t>Выражения для ПЧ4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -664,12 +703,6 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
@@ -993,6 +1026,43 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1011,49 +1081,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1469,174 +1500,174 @@
       <c r="AW1" s="64"/>
     </row>
     <row r="2" spans="1:71" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="57" t="s">
+      <c r="B2" s="65"/>
+      <c r="C2" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="52">
+      <c r="D2" s="54">
         <v>46268</v>
       </c>
-      <c r="E2" s="52">
+      <c r="E2" s="54">
         <v>46272</v>
       </c>
-      <c r="F2" s="52">
+      <c r="F2" s="54">
         <v>46273</v>
       </c>
-      <c r="G2" s="52">
+      <c r="G2" s="54">
         <v>46275</v>
       </c>
-      <c r="H2" s="52">
+      <c r="H2" s="54">
         <v>46279</v>
       </c>
-      <c r="I2" s="55">
+      <c r="I2" s="62">
         <v>46282</v>
       </c>
-      <c r="J2" s="52">
+      <c r="J2" s="54">
         <v>46286</v>
       </c>
-      <c r="K2" s="52">
+      <c r="K2" s="54">
         <v>46287</v>
       </c>
-      <c r="L2" s="55">
+      <c r="L2" s="62">
         <v>46289</v>
       </c>
-      <c r="M2" s="52">
+      <c r="M2" s="54">
         <v>46293</v>
       </c>
-      <c r="N2" s="55">
+      <c r="N2" s="62">
         <v>46296</v>
       </c>
-      <c r="O2" s="52">
+      <c r="O2" s="54">
         <v>46300</v>
       </c>
-      <c r="P2" s="52">
+      <c r="P2" s="54">
         <v>46301</v>
       </c>
-      <c r="Q2" s="55">
+      <c r="Q2" s="62">
         <v>46303</v>
       </c>
-      <c r="R2" s="52">
+      <c r="R2" s="54">
         <v>46307</v>
       </c>
-      <c r="S2" s="55">
+      <c r="S2" s="62">
         <v>46310</v>
       </c>
-      <c r="T2" s="52">
+      <c r="T2" s="54">
         <v>46314</v>
       </c>
-      <c r="U2" s="52">
+      <c r="U2" s="54">
         <v>46315</v>
       </c>
-      <c r="V2" s="55">
+      <c r="V2" s="62">
         <v>46317</v>
       </c>
-      <c r="W2" s="52">
+      <c r="W2" s="54">
         <v>46321</v>
       </c>
-      <c r="X2" s="52">
+      <c r="X2" s="54">
         <v>46324</v>
       </c>
-      <c r="Y2" s="52">
+      <c r="Y2" s="54">
         <v>46328</v>
       </c>
-      <c r="Z2" s="52">
+      <c r="Z2" s="54">
         <v>46329</v>
       </c>
-      <c r="AA2" s="52">
+      <c r="AA2" s="54">
         <v>46331</v>
       </c>
-      <c r="AB2" s="52">
+      <c r="AB2" s="54">
         <v>46335</v>
       </c>
-      <c r="AC2" s="52">
+      <c r="AC2" s="54">
         <v>46338</v>
       </c>
-      <c r="AD2" s="52">
+      <c r="AD2" s="54">
         <v>46342</v>
       </c>
-      <c r="AE2" s="52">
+      <c r="AE2" s="54">
         <v>46343</v>
       </c>
-      <c r="AF2" s="52">
+      <c r="AF2" s="54">
         <v>46345</v>
       </c>
-      <c r="AG2" s="52">
+      <c r="AG2" s="54">
         <v>46349</v>
       </c>
-      <c r="AH2" s="52">
+      <c r="AH2" s="54">
         <v>46352</v>
       </c>
-      <c r="AI2" s="52">
+      <c r="AI2" s="54">
         <v>46356</v>
       </c>
-      <c r="AJ2" s="55">
+      <c r="AJ2" s="62">
         <v>46357</v>
       </c>
-      <c r="AK2" s="55">
+      <c r="AK2" s="62">
         <v>46359</v>
       </c>
-      <c r="AL2" s="55">
+      <c r="AL2" s="62">
         <v>46363</v>
       </c>
-      <c r="AM2" s="55">
+      <c r="AM2" s="62">
         <v>46366</v>
       </c>
-      <c r="AN2" s="55">
+      <c r="AN2" s="62">
         <v>46370</v>
       </c>
-      <c r="AO2" s="55">
+      <c r="AO2" s="62">
         <v>46371</v>
       </c>
-      <c r="AP2" s="55">
+      <c r="AP2" s="62">
         <v>46373</v>
       </c>
-      <c r="AQ2" s="55">
+      <c r="AQ2" s="62">
         <v>46377</v>
       </c>
-      <c r="AR2" s="55">
+      <c r="AR2" s="62">
         <v>46380</v>
       </c>
-      <c r="AS2" s="54" t="s">
+      <c r="AS2" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="AT2" s="54"/>
-      <c r="AU2" s="58" t="s">
+      <c r="AT2" s="65"/>
+      <c r="AU2" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="AV2" s="59"/>
-      <c r="AW2" s="60"/>
-      <c r="AX2" s="58" t="s">
+      <c r="AV2" s="57"/>
+      <c r="AW2" s="58"/>
+      <c r="AX2" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="AY2" s="59"/>
-      <c r="AZ2" s="60"/>
-      <c r="BA2" s="58" t="s">
+      <c r="AY2" s="57"/>
+      <c r="AZ2" s="58"/>
+      <c r="BA2" s="56" t="s">
         <v>159</v>
       </c>
-      <c r="BB2" s="59"/>
-      <c r="BC2" s="60"/>
-      <c r="BD2" s="58" t="s">
+      <c r="BB2" s="57"/>
+      <c r="BC2" s="58"/>
+      <c r="BD2" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="BE2" s="59"/>
-      <c r="BF2" s="59"/>
-      <c r="BG2" s="60"/>
-      <c r="BH2" s="58" t="s">
+      <c r="BE2" s="57"/>
+      <c r="BF2" s="57"/>
+      <c r="BG2" s="58"/>
+      <c r="BH2" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="BI2" s="59"/>
-      <c r="BJ2" s="59"/>
-      <c r="BK2" s="60" t="s">
+      <c r="BI2" s="57"/>
+      <c r="BJ2" s="57"/>
+      <c r="BK2" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="BL2" s="58" t="s">
+      <c r="BL2" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="BM2" s="59"/>
-      <c r="BN2" s="60"/>
+      <c r="BM2" s="57"/>
+      <c r="BN2" s="58"/>
     </row>
     <row r="3" spans="1:71" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1645,70 +1676,70 @@
       <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="53"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="53"/>
-      <c r="P3" s="53"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="53"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="53"/>
-      <c r="U3" s="53"/>
-      <c r="V3" s="56"/>
-      <c r="W3" s="53"/>
-      <c r="X3" s="53"/>
-      <c r="Y3" s="53"/>
-      <c r="Z3" s="53"/>
-      <c r="AA3" s="53"/>
-      <c r="AB3" s="53"/>
-      <c r="AC3" s="53"/>
-      <c r="AD3" s="53"/>
-      <c r="AE3" s="53"/>
-      <c r="AF3" s="53"/>
-      <c r="AG3" s="53"/>
-      <c r="AH3" s="53"/>
-      <c r="AI3" s="53"/>
-      <c r="AJ3" s="56"/>
-      <c r="AK3" s="56"/>
-      <c r="AL3" s="56"/>
-      <c r="AM3" s="56"/>
-      <c r="AN3" s="56"/>
-      <c r="AO3" s="56"/>
-      <c r="AP3" s="56"/>
-      <c r="AQ3" s="56"/>
-      <c r="AR3" s="56"/>
-      <c r="AS3" s="54"/>
-      <c r="AT3" s="54"/>
-      <c r="AU3" s="61"/>
-      <c r="AV3" s="65"/>
-      <c r="AW3" s="63"/>
-      <c r="AX3" s="61"/>
-      <c r="AY3" s="62"/>
-      <c r="AZ3" s="63"/>
-      <c r="BA3" s="61"/>
-      <c r="BB3" s="62"/>
-      <c r="BC3" s="63"/>
-      <c r="BD3" s="61"/>
-      <c r="BE3" s="62"/>
-      <c r="BF3" s="62"/>
-      <c r="BG3" s="63"/>
-      <c r="BH3" s="61"/>
-      <c r="BI3" s="62"/>
-      <c r="BJ3" s="62"/>
-      <c r="BK3" s="63"/>
-      <c r="BL3" s="61"/>
-      <c r="BM3" s="62"/>
-      <c r="BN3" s="63"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="55"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="55"/>
+      <c r="P3" s="55"/>
+      <c r="Q3" s="63"/>
+      <c r="R3" s="55"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="55"/>
+      <c r="U3" s="55"/>
+      <c r="V3" s="63"/>
+      <c r="W3" s="55"/>
+      <c r="X3" s="55"/>
+      <c r="Y3" s="55"/>
+      <c r="Z3" s="55"/>
+      <c r="AA3" s="55"/>
+      <c r="AB3" s="55"/>
+      <c r="AC3" s="55"/>
+      <c r="AD3" s="55"/>
+      <c r="AE3" s="55"/>
+      <c r="AF3" s="55"/>
+      <c r="AG3" s="55"/>
+      <c r="AH3" s="55"/>
+      <c r="AI3" s="55"/>
+      <c r="AJ3" s="63"/>
+      <c r="AK3" s="63"/>
+      <c r="AL3" s="63"/>
+      <c r="AM3" s="63"/>
+      <c r="AN3" s="63"/>
+      <c r="AO3" s="63"/>
+      <c r="AP3" s="63"/>
+      <c r="AQ3" s="63"/>
+      <c r="AR3" s="63"/>
+      <c r="AS3" s="65"/>
+      <c r="AT3" s="65"/>
+      <c r="AU3" s="59"/>
+      <c r="AV3" s="66"/>
+      <c r="AW3" s="61"/>
+      <c r="AX3" s="59"/>
+      <c r="AY3" s="60"/>
+      <c r="AZ3" s="61"/>
+      <c r="BA3" s="59"/>
+      <c r="BB3" s="60"/>
+      <c r="BC3" s="61"/>
+      <c r="BD3" s="59"/>
+      <c r="BE3" s="60"/>
+      <c r="BF3" s="60"/>
+      <c r="BG3" s="61"/>
+      <c r="BH3" s="59"/>
+      <c r="BI3" s="60"/>
+      <c r="BJ3" s="60"/>
+      <c r="BK3" s="61"/>
+      <c r="BL3" s="59"/>
+      <c r="BM3" s="60"/>
+      <c r="BN3" s="61"/>
     </row>
     <row r="4" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
@@ -1814,12 +1845,14 @@
       <c r="BA4" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="BB4" s="72" t="s">
+      <c r="BB4" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="BC4" s="73"/>
+      <c r="BC4" s="52"/>
       <c r="BD4" s="16"/>
-      <c r="BE4" s="16"/>
+      <c r="BE4" s="74" t="s">
+        <v>193</v>
+      </c>
       <c r="BF4" s="16"/>
       <c r="BG4" s="17"/>
       <c r="BH4" s="16"/>
@@ -1934,14 +1967,14 @@
       <c r="BA5" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="BB5" s="66" t="s">
+      <c r="BB5" s="46" t="s">
         <v>77</v>
       </c>
       <c r="BC5" s="17"/>
-      <c r="BD5" s="67">
+      <c r="BD5" s="47">
         <v>46310</v>
       </c>
-      <c r="BE5" s="68" t="s">
+      <c r="BE5" s="48" t="s">
         <v>180</v>
       </c>
       <c r="BF5" s="16"/>
@@ -2077,8 +2110,10 @@
         <v>44</v>
       </c>
       <c r="BC6" s="17"/>
-      <c r="BD6" s="68"/>
-      <c r="BE6" s="69"/>
+      <c r="BD6" s="48"/>
+      <c r="BE6" s="74" t="s">
+        <v>194</v>
+      </c>
       <c r="BF6" s="16"/>
       <c r="BG6" s="17"/>
       <c r="BH6" s="16"/>
@@ -2192,21 +2227,21 @@
         <v>132</v>
       </c>
       <c r="AZ7" s="16"/>
-      <c r="BA7" s="71" t="s">
+      <c r="BA7" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="BB7" s="66" t="s">
+      <c r="BB7" s="46" t="s">
         <v>160</v>
       </c>
       <c r="BC7" s="16"/>
-      <c r="BD7" s="67">
+      <c r="BD7" s="47">
         <v>46310</v>
       </c>
-      <c r="BE7" s="69" t="s">
+      <c r="BE7" s="49" t="s">
         <v>181</v>
       </c>
       <c r="BF7" s="16"/>
-      <c r="BG7" s="16"/>
+      <c r="BG7" s="48"/>
       <c r="BH7" s="16"/>
       <c r="BI7" s="16"/>
       <c r="BJ7" s="16"/>
@@ -2316,17 +2351,18 @@
         <v>155</v>
       </c>
       <c r="AZ8" s="16"/>
-      <c r="BA8" s="71" t="s">
+      <c r="BA8" s="50" t="s">
         <v>189</v>
       </c>
-      <c r="BB8" s="66" t="s">
+      <c r="BB8" s="46" t="s">
         <v>161</v>
       </c>
       <c r="BC8" s="16"/>
-      <c r="BD8" s="68"/>
-      <c r="BE8" s="68"/>
+      <c r="BD8" s="48"/>
+      <c r="BE8" s="74" t="s">
+        <v>195</v>
+      </c>
       <c r="BF8" s="16"/>
-      <c r="BG8" s="16"/>
       <c r="BH8" s="16"/>
       <c r="BI8" s="16"/>
       <c r="BJ8" s="16"/>
@@ -2438,15 +2474,17 @@
         <v>137</v>
       </c>
       <c r="AZ9" s="20"/>
-      <c r="BA9" s="71" t="s">
+      <c r="BA9" s="50" t="s">
         <v>190</v>
       </c>
-      <c r="BB9" s="66" t="s">
+      <c r="BB9" s="46" t="s">
         <v>162</v>
       </c>
       <c r="BC9" s="17"/>
-      <c r="BD9" s="68"/>
-      <c r="BE9" s="68"/>
+      <c r="BD9" s="48"/>
+      <c r="BE9" s="74" t="s">
+        <v>196</v>
+      </c>
       <c r="BF9" s="16"/>
       <c r="BG9" s="17"/>
       <c r="BH9" s="16"/>
@@ -2561,12 +2599,14 @@
       <c r="BA10" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="BB10" s="66" t="s">
+      <c r="BB10" s="46" t="s">
         <v>163</v>
       </c>
       <c r="BC10" s="19"/>
-      <c r="BD10" s="68"/>
-      <c r="BE10" s="68"/>
+      <c r="BD10" s="48"/>
+      <c r="BE10" s="74" t="s">
+        <v>197</v>
+      </c>
       <c r="BF10" s="16"/>
       <c r="BG10" s="17"/>
       <c r="BH10" s="16"/>
@@ -2683,14 +2723,14 @@
       <c r="BA11" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="BB11" s="66" t="s">
+      <c r="BB11" s="46" t="s">
         <v>167</v>
       </c>
       <c r="BC11" s="19"/>
-      <c r="BD11" s="67">
+      <c r="BD11" s="47">
         <v>46310</v>
       </c>
-      <c r="BE11" s="68" t="s">
+      <c r="BE11" s="48" t="s">
         <v>179</v>
       </c>
       <c r="BF11" s="16"/>
@@ -2815,12 +2855,12 @@
       <c r="BA12" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="BB12" s="66"/>
+      <c r="BB12" s="46"/>
       <c r="BC12" s="19"/>
-      <c r="BD12" s="67">
+      <c r="BD12" s="47">
         <v>46315</v>
       </c>
-      <c r="BE12" s="69" t="s">
+      <c r="BE12" s="49" t="s">
         <v>181</v>
       </c>
       <c r="BF12" s="16"/>
@@ -2943,12 +2983,12 @@
       <c r="BA13" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="BB13" s="66"/>
+      <c r="BB13" s="46"/>
       <c r="BC13" s="17"/>
-      <c r="BD13" s="67">
+      <c r="BD13" s="47">
         <v>46315</v>
       </c>
-      <c r="BE13" s="68" t="s">
+      <c r="BE13" s="48" t="s">
         <v>183</v>
       </c>
       <c r="BF13" s="16"/>
@@ -3069,16 +3109,16 @@
       <c r="BA14" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="BB14" s="66"/>
+      <c r="BB14" s="46"/>
       <c r="BC14" s="16"/>
-      <c r="BD14" s="67">
+      <c r="BD14" s="47">
         <v>46310</v>
       </c>
-      <c r="BE14" s="68" t="s">
+      <c r="BE14" s="48" t="s">
         <v>179</v>
       </c>
       <c r="BF14" s="16"/>
-      <c r="BG14" s="16"/>
+      <c r="BG14" s="17"/>
       <c r="BH14" s="16"/>
       <c r="BI14" s="16"/>
       <c r="BJ14" s="16"/>
@@ -3193,14 +3233,14 @@
       <c r="BA15" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="BB15" s="66" t="s">
+      <c r="BB15" s="46" t="s">
         <v>167</v>
       </c>
       <c r="BC15" s="17"/>
-      <c r="BD15" s="67">
+      <c r="BD15" s="47">
         <v>46310</v>
       </c>
-      <c r="BE15" s="68" t="s">
+      <c r="BE15" s="48" t="s">
         <v>179</v>
       </c>
       <c r="BF15" s="16"/>
@@ -3323,12 +3363,14 @@
       <c r="BA16" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="BB16" s="66" t="s">
+      <c r="BB16" s="46" t="s">
         <v>33</v>
       </c>
       <c r="BC16" s="17"/>
-      <c r="BD16" s="68"/>
-      <c r="BE16" s="70"/>
+      <c r="BD16" s="48"/>
+      <c r="BE16" s="74" t="s">
+        <v>193</v>
+      </c>
       <c r="BF16" s="16"/>
       <c r="BG16" s="17"/>
       <c r="BH16" s="16"/>
@@ -3449,10 +3491,12 @@
       <c r="BA17" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="BB17" s="66"/>
+      <c r="BB17" s="46"/>
       <c r="BC17" s="17"/>
-      <c r="BD17" s="68"/>
-      <c r="BE17" s="68"/>
+      <c r="BD17" s="48"/>
+      <c r="BE17" s="74" t="s">
+        <v>198</v>
+      </c>
       <c r="BF17" s="16"/>
       <c r="BG17" s="17"/>
       <c r="BH17" s="16"/>
@@ -3575,10 +3619,12 @@
       <c r="BA18" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="BB18" s="66"/>
+      <c r="BB18" s="46"/>
       <c r="BC18" s="17"/>
-      <c r="BD18" s="68"/>
-      <c r="BE18" s="68"/>
+      <c r="BD18" s="48"/>
+      <c r="BE18" s="74" t="s">
+        <v>199</v>
+      </c>
       <c r="BF18" s="16"/>
       <c r="BG18" s="17"/>
       <c r="BH18" s="16"/>
@@ -3699,12 +3745,12 @@
       <c r="BA19" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="BB19" s="66"/>
-      <c r="BC19" s="74"/>
-      <c r="BD19" s="67">
+      <c r="BB19" s="46"/>
+      <c r="BC19" s="53"/>
+      <c r="BD19" s="47">
         <v>46315</v>
       </c>
-      <c r="BE19" s="69" t="s">
+      <c r="BE19" s="49" t="s">
         <v>181</v>
       </c>
       <c r="BF19" s="16"/>
@@ -3820,15 +3866,17 @@
         <v>137</v>
       </c>
       <c r="AZ20" s="17"/>
-      <c r="BA20" s="71" t="s">
+      <c r="BA20" s="50" t="s">
         <v>190</v>
       </c>
-      <c r="BB20" s="66" t="s">
+      <c r="BB20" s="46" t="s">
         <v>162</v>
       </c>
       <c r="BC20" s="16"/>
-      <c r="BD20" s="68"/>
-      <c r="BE20" s="68"/>
+      <c r="BD20" s="48"/>
+      <c r="BE20" s="74" t="s">
+        <v>196</v>
+      </c>
       <c r="BF20" s="16"/>
       <c r="BG20" s="17"/>
       <c r="BH20" s="16"/>
@@ -3940,15 +3988,17 @@
         <v>155</v>
       </c>
       <c r="AZ21" s="20"/>
-      <c r="BA21" s="71" t="s">
+      <c r="BA21" s="50" t="s">
         <v>189</v>
       </c>
-      <c r="BB21" s="66" t="s">
+      <c r="BB21" s="46" t="s">
         <v>161</v>
       </c>
       <c r="BC21" s="17"/>
-      <c r="BD21" s="68"/>
-      <c r="BE21" s="68"/>
+      <c r="BD21" s="48"/>
+      <c r="BE21" s="74" t="s">
+        <v>195</v>
+      </c>
       <c r="BF21" s="16"/>
       <c r="BG21" s="17"/>
       <c r="BH21" s="16"/>
@@ -4063,12 +4113,12 @@
       <c r="BA22" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="BB22" s="66"/>
+      <c r="BB22" s="46"/>
       <c r="BC22" s="17"/>
-      <c r="BD22" s="67">
+      <c r="BD22" s="47">
         <v>46315</v>
       </c>
-      <c r="BE22" s="68" t="s">
+      <c r="BE22" s="48" t="s">
         <v>184</v>
       </c>
       <c r="BF22" s="16"/>
@@ -4183,12 +4233,12 @@
       <c r="BA23" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="BB23" s="66"/>
+      <c r="BB23" s="46"/>
       <c r="BC23" s="16"/>
-      <c r="BD23" s="67">
+      <c r="BD23" s="47">
         <v>46315</v>
       </c>
-      <c r="BE23" s="68" t="s">
+      <c r="BE23" s="48" t="s">
         <v>183</v>
       </c>
       <c r="BF23" s="16"/>
@@ -4309,14 +4359,14 @@
       <c r="BA24" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="BB24" s="66" t="s">
+      <c r="BB24" s="46" t="s">
         <v>37</v>
       </c>
       <c r="BC24" s="16"/>
-      <c r="BD24" s="67">
+      <c r="BD24" s="47">
         <v>46303</v>
       </c>
-      <c r="BE24" s="68" t="s">
+      <c r="BE24" s="48" t="s">
         <v>173</v>
       </c>
       <c r="BF24" s="16"/>
@@ -4433,12 +4483,12 @@
       <c r="BA25" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="BB25" s="66"/>
+      <c r="BB25" s="46"/>
       <c r="BC25" s="17"/>
-      <c r="BD25" s="67">
+      <c r="BD25" s="47">
         <v>46315</v>
       </c>
-      <c r="BE25" s="68" t="s">
+      <c r="BE25" s="48" t="s">
         <v>183</v>
       </c>
       <c r="BF25" s="16"/>
@@ -4561,12 +4611,12 @@
       <c r="BA26" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="BB26" s="66"/>
+      <c r="BB26" s="46"/>
       <c r="BC26" s="17"/>
-      <c r="BD26" s="67">
+      <c r="BD26" s="47">
         <v>46315</v>
       </c>
-      <c r="BE26" s="68" t="s">
+      <c r="BE26" s="48" t="s">
         <v>183</v>
       </c>
       <c r="BF26" s="16"/>
@@ -4690,12 +4740,14 @@
       <c r="BA27" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="BB27" s="66" t="s">
+      <c r="BB27" s="46" t="s">
         <v>77</v>
       </c>
       <c r="BC27" s="16"/>
-      <c r="BD27" s="68"/>
-      <c r="BE27" s="68"/>
+      <c r="BD27" s="48"/>
+      <c r="BE27" s="74" t="s">
+        <v>200</v>
+      </c>
       <c r="BF27" s="16"/>
       <c r="BG27" s="17"/>
       <c r="BH27" s="16"/>
@@ -4812,10 +4864,12 @@
       <c r="BA28" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="BB28" s="66"/>
+      <c r="BB28" s="46"/>
       <c r="BC28" s="16"/>
-      <c r="BD28" s="68"/>
-      <c r="BE28" s="68"/>
+      <c r="BD28" s="48"/>
+      <c r="BE28" s="74" t="s">
+        <v>201</v>
+      </c>
       <c r="BF28" s="16"/>
       <c r="BG28" s="17"/>
       <c r="BH28" s="16"/>
@@ -4928,12 +4982,14 @@
       <c r="BA29" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="BB29" s="66" t="s">
+      <c r="BB29" s="46" t="s">
         <v>37</v>
       </c>
       <c r="BC29" s="16"/>
-      <c r="BD29" s="68"/>
-      <c r="BE29" s="68"/>
+      <c r="BD29" s="48"/>
+      <c r="BE29" s="74" t="s">
+        <v>192</v>
+      </c>
       <c r="BF29" s="16"/>
       <c r="BG29" s="17"/>
       <c r="BH29" s="16"/>
@@ -5048,10 +5104,12 @@
       <c r="BA30" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="BB30" s="66"/>
+      <c r="BB30" s="46"/>
       <c r="BC30" s="16"/>
-      <c r="BD30" s="68"/>
-      <c r="BE30" s="68"/>
+      <c r="BD30" s="48"/>
+      <c r="BE30" s="74" t="s">
+        <v>199</v>
+      </c>
       <c r="BF30" s="16"/>
       <c r="BG30" s="17"/>
       <c r="BH30" s="16"/>
@@ -5159,17 +5217,17 @@
         <v>132</v>
       </c>
       <c r="AZ31" s="17"/>
-      <c r="BA31" s="71" t="s">
+      <c r="BA31" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="BB31" s="66" t="s">
+      <c r="BB31" s="46" t="s">
         <v>160</v>
       </c>
       <c r="BC31" s="16"/>
-      <c r="BD31" s="67">
+      <c r="BD31" s="47">
         <v>46310</v>
       </c>
-      <c r="BE31" s="69" t="s">
+      <c r="BE31" s="49" t="s">
         <v>181</v>
       </c>
       <c r="BF31" s="16"/>
@@ -5286,12 +5344,14 @@
       <c r="BA32" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="BB32" s="66" t="s">
+      <c r="BB32" s="46" t="s">
         <v>44</v>
       </c>
       <c r="BC32" s="16"/>
-      <c r="BD32" s="68"/>
-      <c r="BE32" s="68"/>
+      <c r="BD32" s="48"/>
+      <c r="BE32" s="74" t="s">
+        <v>194</v>
+      </c>
       <c r="BF32" s="16"/>
       <c r="BG32" s="17"/>
       <c r="BH32" s="16"/>
@@ -5398,10 +5458,12 @@
       <c r="BA33" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="BB33" s="66"/>
+      <c r="BB33" s="46"/>
       <c r="BC33" s="16"/>
-      <c r="BD33" s="68"/>
-      <c r="BE33" s="68"/>
+      <c r="BD33" s="48"/>
+      <c r="BE33" s="74" t="s">
+        <v>202</v>
+      </c>
       <c r="BF33" s="16"/>
       <c r="BG33" s="17"/>
       <c r="BH33" s="16"/>
@@ -5516,10 +5578,12 @@
       <c r="BA34" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="BB34" s="66"/>
+      <c r="BB34" s="46"/>
       <c r="BC34" s="16"/>
-      <c r="BD34" s="68"/>
-      <c r="BE34" s="68"/>
+      <c r="BD34" s="48"/>
+      <c r="BE34" s="74" t="s">
+        <v>203</v>
+      </c>
       <c r="BF34" s="16"/>
       <c r="BG34" s="17"/>
       <c r="BH34" s="16"/>
@@ -5632,12 +5696,12 @@
       <c r="BA35" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="BB35" s="66"/>
+      <c r="BB35" s="46"/>
       <c r="BC35" s="16"/>
-      <c r="BD35" s="67">
+      <c r="BD35" s="47">
         <v>46310</v>
       </c>
-      <c r="BE35" s="68" t="s">
+      <c r="BE35" s="48" t="s">
         <v>182</v>
       </c>
       <c r="BF35" s="16"/>
@@ -5746,12 +5810,12 @@
       <c r="BA36" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="BB36" s="66"/>
+      <c r="BB36" s="46"/>
       <c r="BC36" s="16"/>
-      <c r="BD36" s="67">
+      <c r="BD36" s="47">
         <v>46315</v>
       </c>
-      <c r="BE36" s="68" t="s">
+      <c r="BE36" s="48" t="s">
         <v>183</v>
       </c>
       <c r="BF36" s="26"/>
@@ -5865,7 +5929,9 @@
       <c r="BB37" s="16"/>
       <c r="BC37" s="16"/>
       <c r="BD37" s="16"/>
-      <c r="BE37" s="26"/>
+      <c r="BE37" s="74" t="s">
+        <v>204</v>
+      </c>
       <c r="BF37" s="26"/>
       <c r="BG37" s="26"/>
       <c r="BH37" s="16"/>
@@ -5877,57 +5943,57 @@
       <c r="BN37" s="26"/>
     </row>
     <row r="38" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A38" s="46" t="s">
+      <c r="A38" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="B38" s="47"/>
-      <c r="C38" s="47"/>
-      <c r="D38" s="47"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="47"/>
-      <c r="G38" s="47"/>
-      <c r="H38" s="47"/>
-      <c r="I38" s="47"/>
-      <c r="J38" s="47"/>
-      <c r="K38" s="47"/>
-      <c r="L38" s="47"/>
-      <c r="M38" s="47"/>
-      <c r="N38" s="47"/>
-      <c r="O38" s="47"/>
-      <c r="P38" s="47"/>
-      <c r="Q38" s="47"/>
-      <c r="R38" s="47"/>
-      <c r="S38" s="47"/>
-      <c r="T38" s="47"/>
-      <c r="U38" s="47"/>
-      <c r="V38" s="47"/>
-      <c r="W38" s="47"/>
-      <c r="X38" s="47"/>
-      <c r="Y38" s="47"/>
-      <c r="Z38" s="47"/>
-      <c r="AA38" s="47"/>
-      <c r="AB38" s="47"/>
-      <c r="AC38" s="47"/>
-      <c r="AD38" s="47"/>
-      <c r="AE38" s="47"/>
-      <c r="AF38" s="47"/>
-      <c r="AG38" s="47"/>
-      <c r="AH38" s="47"/>
-      <c r="AI38" s="47"/>
-      <c r="AJ38" s="47"/>
-      <c r="AK38" s="47"/>
-      <c r="AL38" s="47"/>
-      <c r="AM38" s="47"/>
-      <c r="AN38" s="47"/>
-      <c r="AO38" s="47"/>
-      <c r="AP38" s="47"/>
-      <c r="AQ38" s="47"/>
-      <c r="AR38" s="47"/>
-      <c r="AS38" s="47"/>
-      <c r="AT38" s="47"/>
-      <c r="AU38" s="47"/>
-      <c r="AV38" s="47"/>
-      <c r="AW38" s="48"/>
+      <c r="B38" s="68"/>
+      <c r="C38" s="68"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="68"/>
+      <c r="H38" s="68"/>
+      <c r="I38" s="68"/>
+      <c r="J38" s="68"/>
+      <c r="K38" s="68"/>
+      <c r="L38" s="68"/>
+      <c r="M38" s="68"/>
+      <c r="N38" s="68"/>
+      <c r="O38" s="68"/>
+      <c r="P38" s="68"/>
+      <c r="Q38" s="68"/>
+      <c r="R38" s="68"/>
+      <c r="S38" s="68"/>
+      <c r="T38" s="68"/>
+      <c r="U38" s="68"/>
+      <c r="V38" s="68"/>
+      <c r="W38" s="68"/>
+      <c r="X38" s="68"/>
+      <c r="Y38" s="68"/>
+      <c r="Z38" s="68"/>
+      <c r="AA38" s="68"/>
+      <c r="AB38" s="68"/>
+      <c r="AC38" s="68"/>
+      <c r="AD38" s="68"/>
+      <c r="AE38" s="68"/>
+      <c r="AF38" s="68"/>
+      <c r="AG38" s="68"/>
+      <c r="AH38" s="68"/>
+      <c r="AI38" s="68"/>
+      <c r="AJ38" s="68"/>
+      <c r="AK38" s="68"/>
+      <c r="AL38" s="68"/>
+      <c r="AM38" s="68"/>
+      <c r="AN38" s="68"/>
+      <c r="AO38" s="68"/>
+      <c r="AP38" s="68"/>
+      <c r="AQ38" s="68"/>
+      <c r="AR38" s="68"/>
+      <c r="AS38" s="68"/>
+      <c r="AT38" s="68"/>
+      <c r="AU38" s="68"/>
+      <c r="AV38" s="68"/>
+      <c r="AW38" s="69"/>
       <c r="AX38" s="2"/>
       <c r="AY38" s="2"/>
       <c r="AZ38" s="2"/>
@@ -5953,57 +6019,57 @@
       </c>
     </row>
     <row r="39" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A39" s="49" t="s">
+      <c r="A39" s="70" t="s">
         <v>82</v>
       </c>
-      <c r="B39" s="50"/>
-      <c r="C39" s="50"/>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="50"/>
-      <c r="I39" s="50"/>
-      <c r="J39" s="50"/>
-      <c r="K39" s="50"/>
-      <c r="L39" s="50"/>
-      <c r="M39" s="50"/>
-      <c r="N39" s="50"/>
-      <c r="O39" s="50"/>
-      <c r="P39" s="50"/>
-      <c r="Q39" s="50"/>
-      <c r="R39" s="50"/>
-      <c r="S39" s="50"/>
-      <c r="T39" s="50"/>
-      <c r="U39" s="50"/>
-      <c r="V39" s="50"/>
-      <c r="W39" s="50"/>
-      <c r="X39" s="50"/>
-      <c r="Y39" s="50"/>
-      <c r="Z39" s="50"/>
-      <c r="AA39" s="50"/>
-      <c r="AB39" s="50"/>
-      <c r="AC39" s="50"/>
-      <c r="AD39" s="50"/>
-      <c r="AE39" s="50"/>
-      <c r="AF39" s="50"/>
-      <c r="AG39" s="50"/>
-      <c r="AH39" s="50"/>
-      <c r="AI39" s="50"/>
-      <c r="AJ39" s="50"/>
-      <c r="AK39" s="50"/>
-      <c r="AL39" s="50"/>
-      <c r="AM39" s="50"/>
-      <c r="AN39" s="50"/>
-      <c r="AO39" s="50"/>
-      <c r="AP39" s="50"/>
-      <c r="AQ39" s="50"/>
-      <c r="AR39" s="50"/>
-      <c r="AS39" s="50"/>
-      <c r="AT39" s="50"/>
-      <c r="AU39" s="50"/>
-      <c r="AV39" s="50"/>
-      <c r="AW39" s="51"/>
+      <c r="B39" s="71"/>
+      <c r="C39" s="71"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="71"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="71"/>
+      <c r="K39" s="71"/>
+      <c r="L39" s="71"/>
+      <c r="M39" s="71"/>
+      <c r="N39" s="71"/>
+      <c r="O39" s="71"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="71"/>
+      <c r="S39" s="71"/>
+      <c r="T39" s="71"/>
+      <c r="U39" s="71"/>
+      <c r="V39" s="71"/>
+      <c r="W39" s="71"/>
+      <c r="X39" s="71"/>
+      <c r="Y39" s="71"/>
+      <c r="Z39" s="71"/>
+      <c r="AA39" s="71"/>
+      <c r="AB39" s="71"/>
+      <c r="AC39" s="71"/>
+      <c r="AD39" s="71"/>
+      <c r="AE39" s="71"/>
+      <c r="AF39" s="71"/>
+      <c r="AG39" s="71"/>
+      <c r="AH39" s="71"/>
+      <c r="AI39" s="71"/>
+      <c r="AJ39" s="71"/>
+      <c r="AK39" s="71"/>
+      <c r="AL39" s="71"/>
+      <c r="AM39" s="71"/>
+      <c r="AN39" s="71"/>
+      <c r="AO39" s="71"/>
+      <c r="AP39" s="71"/>
+      <c r="AQ39" s="71"/>
+      <c r="AR39" s="71"/>
+      <c r="AS39" s="71"/>
+      <c r="AT39" s="71"/>
+      <c r="AU39" s="71"/>
+      <c r="AV39" s="71"/>
+      <c r="AW39" s="72"/>
       <c r="AX39" s="2"/>
       <c r="AY39" s="2"/>
       <c r="AZ39" s="2"/>
@@ -6601,12 +6667,38 @@
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="A38:AW38"/>
+    <mergeCell ref="A39:AW39"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="AS2:AS3"/>
+    <mergeCell ref="AT2:AT3"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="AQ2:AQ3"/>
+    <mergeCell ref="AR2:AR3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="BD2:BG3"/>
+    <mergeCell ref="BH2:BK3"/>
+    <mergeCell ref="BL2:BN3"/>
+    <mergeCell ref="A1:AW1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="AU2:AW3"/>
     <mergeCell ref="AX2:AZ3"/>
     <mergeCell ref="BA2:BC3"/>
     <mergeCell ref="AC2:AC3"/>
@@ -6623,38 +6715,12 @@
     <mergeCell ref="AO2:AO3"/>
     <mergeCell ref="AE2:AE3"/>
     <mergeCell ref="AJ2:AJ3"/>
-    <mergeCell ref="BD2:BG3"/>
-    <mergeCell ref="BH2:BK3"/>
-    <mergeCell ref="BL2:BN3"/>
-    <mergeCell ref="A1:AW1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="AU2:AW3"/>
-    <mergeCell ref="A38:AW38"/>
-    <mergeCell ref="A39:AW39"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="AS2:AS3"/>
-    <mergeCell ref="AT2:AT3"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="AQ2:AQ3"/>
-    <mergeCell ref="AR2:AR3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="AA2:AA3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="BQ6" r:id="rId1" display="Прикладная дискретная математика. Приложение. 2016. № 9. С. 68-70." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -6670,15 +6736,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Документ" ma:contentTypeID="0x0101004F6380A0290AF84484F859C9FFD97568" ma:contentTypeVersion="12" ma:contentTypeDescription="Создание документа." ma:contentTypeScope="" ma:versionID="1ee9877c88efff51dfb0d3a4b3e8ad1b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bffb7b91-0466-4de0-9379-f5c53c3acedf" xmlns:ns3="b78dbef7-f85b-47b5-8738-6377d50f4027" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="532d4df54980d57387e1b5dc96a6a32c" ns2:_="" ns3:_="">
     <xsd:import namespace="bffb7b91-0466-4de0-9379-f5c53c3acedf"/>
@@ -6879,6 +6936,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -6891,14 +6957,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00280879-8A9A-4335-93BC-405126DC8F0C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B6A6DF3-AE59-43BA-A5FF-CF9B7C54D4B8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6917,6 +6975,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00280879-8A9A-4335-93BC-405126DC8F0C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12ECB55F-B88E-4FE2-9AD5-5CA5D433F306}">
   <ds:schemaRefs>

--- a/Ведомость ТКИ-441 2026-2027.xlsx
+++ b/Ведомость ТКИ-441 2026-2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sidorenko\GIT_Reverse_Engineering\StegMethods\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3037D3F7-6097-4F22-BB59-82C18B9E02E1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F615848-C6AD-4260-9C9B-3BDCF37C877C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="207">
   <si>
     <t>Ведомость посещаемости занятий студентами группы ТКИ РУТ МИИТ</t>
   </si>
@@ -505,9 +505,6 @@
     <t xml:space="preserve">2 задание Конахович. Скрытие в изображениях и звуковых файлах. </t>
   </si>
   <si>
-    <t>3 задание. Форензика. Скрытие в текстовых файлах</t>
-  </si>
-  <si>
     <t>Chromatic Aberration (CA)</t>
   </si>
   <si>
@@ -526,9 +523,6 @@
     <t>9.6</t>
   </si>
   <si>
-    <t>9.8</t>
-  </si>
-  <si>
     <t>Clustering</t>
   </si>
   <si>
@@ -625,9 +619,6 @@
     <t>Бабочка ОПВ4</t>
   </si>
   <si>
-    <t>Бабочка ОПЧ4</t>
-  </si>
-  <si>
     <t>ППОВ4</t>
   </si>
   <si>
@@ -641,6 +632,21 @@
   </si>
   <si>
     <t>Выражения для ПЧ4</t>
+  </si>
+  <si>
+    <t>=</t>
+  </si>
+  <si>
+    <t>соревнования</t>
+  </si>
+  <si>
+    <t>3 задание. Форензика. Скрытие в текстовых файлах и др.</t>
+  </si>
+  <si>
+    <t>Метод стеганографического скрытия с использованием дискретного вейвлет-преобразования в графических контейнерах</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кубический нелинейный конгруэнтный генератор </t>
   </si>
 </sst>
 </file>
@@ -939,7 +945,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1038,6 +1044,8 @@
     <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1084,7 +1092,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1447,227 +1454,227 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="64"/>
-      <c r="O1" s="64"/>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="64"/>
-      <c r="R1" s="64"/>
-      <c r="S1" s="64"/>
-      <c r="T1" s="64"/>
-      <c r="U1" s="64"/>
-      <c r="V1" s="64"/>
-      <c r="W1" s="64"/>
-      <c r="X1" s="64"/>
-      <c r="Y1" s="64"/>
-      <c r="Z1" s="64"/>
-      <c r="AA1" s="64"/>
-      <c r="AB1" s="64"/>
-      <c r="AC1" s="64"/>
-      <c r="AD1" s="64"/>
-      <c r="AE1" s="64"/>
-      <c r="AF1" s="64"/>
-      <c r="AG1" s="64"/>
-      <c r="AH1" s="64"/>
-      <c r="AI1" s="64"/>
-      <c r="AJ1" s="64"/>
-      <c r="AK1" s="64"/>
-      <c r="AL1" s="64"/>
-      <c r="AM1" s="64"/>
-      <c r="AN1" s="64"/>
-      <c r="AO1" s="64"/>
-      <c r="AP1" s="64"/>
-      <c r="AQ1" s="64"/>
-      <c r="AR1" s="64"/>
-      <c r="AS1" s="64"/>
-      <c r="AT1" s="64"/>
-      <c r="AU1" s="64"/>
-      <c r="AV1" s="64"/>
-      <c r="AW1" s="64"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="66"/>
+      <c r="T1" s="66"/>
+      <c r="U1" s="66"/>
+      <c r="V1" s="66"/>
+      <c r="W1" s="66"/>
+      <c r="X1" s="66"/>
+      <c r="Y1" s="66"/>
+      <c r="Z1" s="66"/>
+      <c r="AA1" s="66"/>
+      <c r="AB1" s="66"/>
+      <c r="AC1" s="66"/>
+      <c r="AD1" s="66"/>
+      <c r="AE1" s="66"/>
+      <c r="AF1" s="66"/>
+      <c r="AG1" s="66"/>
+      <c r="AH1" s="66"/>
+      <c r="AI1" s="66"/>
+      <c r="AJ1" s="66"/>
+      <c r="AK1" s="66"/>
+      <c r="AL1" s="66"/>
+      <c r="AM1" s="66"/>
+      <c r="AN1" s="66"/>
+      <c r="AO1" s="66"/>
+      <c r="AP1" s="66"/>
+      <c r="AQ1" s="66"/>
+      <c r="AR1" s="66"/>
+      <c r="AS1" s="66"/>
+      <c r="AT1" s="66"/>
+      <c r="AU1" s="66"/>
+      <c r="AV1" s="66"/>
+      <c r="AW1" s="66"/>
     </row>
     <row r="2" spans="1:71" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="73" t="s">
+      <c r="B2" s="67"/>
+      <c r="C2" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="54">
+      <c r="D2" s="56">
         <v>46268</v>
       </c>
-      <c r="E2" s="54">
+      <c r="E2" s="56">
         <v>46272</v>
       </c>
-      <c r="F2" s="54">
+      <c r="F2" s="56">
         <v>46273</v>
       </c>
-      <c r="G2" s="54">
+      <c r="G2" s="56">
         <v>46275</v>
       </c>
-      <c r="H2" s="54">
+      <c r="H2" s="56">
         <v>46279</v>
       </c>
-      <c r="I2" s="62">
+      <c r="I2" s="64">
         <v>46282</v>
       </c>
-      <c r="J2" s="54">
+      <c r="J2" s="56">
         <v>46286</v>
       </c>
-      <c r="K2" s="54">
+      <c r="K2" s="56">
         <v>46287</v>
       </c>
-      <c r="L2" s="62">
+      <c r="L2" s="64">
         <v>46289</v>
       </c>
-      <c r="M2" s="54">
+      <c r="M2" s="56">
         <v>46293</v>
       </c>
-      <c r="N2" s="62">
+      <c r="N2" s="64">
         <v>46296</v>
       </c>
-      <c r="O2" s="54">
+      <c r="O2" s="56">
         <v>46300</v>
       </c>
-      <c r="P2" s="54">
+      <c r="P2" s="56">
         <v>46301</v>
       </c>
-      <c r="Q2" s="62">
+      <c r="Q2" s="64">
         <v>46303</v>
       </c>
-      <c r="R2" s="54">
+      <c r="R2" s="56">
         <v>46307</v>
       </c>
-      <c r="S2" s="62">
+      <c r="S2" s="64">
         <v>46310</v>
       </c>
-      <c r="T2" s="54">
+      <c r="T2" s="56">
         <v>46314</v>
       </c>
-      <c r="U2" s="54">
+      <c r="U2" s="56">
         <v>46315</v>
       </c>
-      <c r="V2" s="62">
+      <c r="V2" s="64">
         <v>46317</v>
       </c>
-      <c r="W2" s="54">
+      <c r="W2" s="56">
         <v>46321</v>
       </c>
-      <c r="X2" s="54">
+      <c r="X2" s="56">
         <v>46324</v>
       </c>
-      <c r="Y2" s="54">
+      <c r="Y2" s="56">
         <v>46328</v>
       </c>
-      <c r="Z2" s="54">
+      <c r="Z2" s="56">
         <v>46329</v>
       </c>
-      <c r="AA2" s="54">
+      <c r="AA2" s="56">
         <v>46331</v>
       </c>
-      <c r="AB2" s="54">
+      <c r="AB2" s="56">
         <v>46335</v>
       </c>
-      <c r="AC2" s="54">
+      <c r="AC2" s="56">
         <v>46338</v>
       </c>
-      <c r="AD2" s="54">
+      <c r="AD2" s="56">
         <v>46342</v>
       </c>
-      <c r="AE2" s="54">
+      <c r="AE2" s="56">
         <v>46343</v>
       </c>
-      <c r="AF2" s="54">
+      <c r="AF2" s="56">
         <v>46345</v>
       </c>
-      <c r="AG2" s="54">
+      <c r="AG2" s="56">
         <v>46349</v>
       </c>
-      <c r="AH2" s="54">
+      <c r="AH2" s="56">
         <v>46352</v>
       </c>
-      <c r="AI2" s="54">
+      <c r="AI2" s="56">
         <v>46356</v>
       </c>
-      <c r="AJ2" s="62">
+      <c r="AJ2" s="64">
         <v>46357</v>
       </c>
-      <c r="AK2" s="62">
+      <c r="AK2" s="64">
         <v>46359</v>
       </c>
-      <c r="AL2" s="62">
+      <c r="AL2" s="64">
         <v>46363</v>
       </c>
-      <c r="AM2" s="62">
+      <c r="AM2" s="64">
         <v>46366</v>
       </c>
-      <c r="AN2" s="62">
+      <c r="AN2" s="64">
         <v>46370</v>
       </c>
-      <c r="AO2" s="62">
+      <c r="AO2" s="64">
         <v>46371</v>
       </c>
-      <c r="AP2" s="62">
+      <c r="AP2" s="64">
         <v>46373</v>
       </c>
-      <c r="AQ2" s="62">
+      <c r="AQ2" s="64">
         <v>46377</v>
       </c>
-      <c r="AR2" s="62">
+      <c r="AR2" s="64">
         <v>46380</v>
       </c>
-      <c r="AS2" s="65" t="s">
+      <c r="AS2" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="AT2" s="65"/>
-      <c r="AU2" s="56" t="s">
+      <c r="AT2" s="67"/>
+      <c r="AU2" s="58" t="s">
         <v>117</v>
       </c>
-      <c r="AV2" s="57"/>
-      <c r="AW2" s="58"/>
-      <c r="AX2" s="56" t="s">
+      <c r="AV2" s="59"/>
+      <c r="AW2" s="60"/>
+      <c r="AX2" s="58" t="s">
         <v>158</v>
       </c>
-      <c r="AY2" s="57"/>
-      <c r="AZ2" s="58"/>
-      <c r="BA2" s="56" t="s">
-        <v>159</v>
-      </c>
-      <c r="BB2" s="57"/>
-      <c r="BC2" s="58"/>
-      <c r="BD2" s="56" t="s">
+      <c r="AY2" s="59"/>
+      <c r="AZ2" s="60"/>
+      <c r="BA2" s="58" t="s">
+        <v>204</v>
+      </c>
+      <c r="BB2" s="59"/>
+      <c r="BC2" s="60"/>
+      <c r="BD2" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="BE2" s="57"/>
-      <c r="BF2" s="57"/>
-      <c r="BG2" s="58"/>
-      <c r="BH2" s="56" t="s">
+      <c r="BE2" s="59"/>
+      <c r="BF2" s="59"/>
+      <c r="BG2" s="60"/>
+      <c r="BH2" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="BI2" s="57"/>
-      <c r="BJ2" s="57"/>
-      <c r="BK2" s="58" t="s">
+      <c r="BI2" s="59"/>
+      <c r="BJ2" s="59"/>
+      <c r="BK2" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="BL2" s="56" t="s">
+      <c r="BL2" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="BM2" s="57"/>
-      <c r="BN2" s="58"/>
+      <c r="BM2" s="59"/>
+      <c r="BN2" s="60"/>
     </row>
     <row r="3" spans="1:71" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1676,70 +1683,70 @@
       <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="65"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="55"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="55"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="55"/>
-      <c r="P3" s="55"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="55"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="55"/>
-      <c r="U3" s="55"/>
-      <c r="V3" s="63"/>
-      <c r="W3" s="55"/>
-      <c r="X3" s="55"/>
-      <c r="Y3" s="55"/>
-      <c r="Z3" s="55"/>
-      <c r="AA3" s="55"/>
-      <c r="AB3" s="55"/>
-      <c r="AC3" s="55"/>
-      <c r="AD3" s="55"/>
-      <c r="AE3" s="55"/>
-      <c r="AF3" s="55"/>
-      <c r="AG3" s="55"/>
-      <c r="AH3" s="55"/>
-      <c r="AI3" s="55"/>
-      <c r="AJ3" s="63"/>
-      <c r="AK3" s="63"/>
-      <c r="AL3" s="63"/>
-      <c r="AM3" s="63"/>
-      <c r="AN3" s="63"/>
-      <c r="AO3" s="63"/>
-      <c r="AP3" s="63"/>
-      <c r="AQ3" s="63"/>
-      <c r="AR3" s="63"/>
-      <c r="AS3" s="65"/>
-      <c r="AT3" s="65"/>
-      <c r="AU3" s="59"/>
-      <c r="AV3" s="66"/>
-      <c r="AW3" s="61"/>
-      <c r="AX3" s="59"/>
-      <c r="AY3" s="60"/>
-      <c r="AZ3" s="61"/>
-      <c r="BA3" s="59"/>
-      <c r="BB3" s="60"/>
-      <c r="BC3" s="61"/>
-      <c r="BD3" s="59"/>
-      <c r="BE3" s="60"/>
-      <c r="BF3" s="60"/>
-      <c r="BG3" s="61"/>
-      <c r="BH3" s="59"/>
-      <c r="BI3" s="60"/>
-      <c r="BJ3" s="60"/>
-      <c r="BK3" s="61"/>
-      <c r="BL3" s="59"/>
-      <c r="BM3" s="60"/>
-      <c r="BN3" s="61"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="57"/>
+      <c r="X3" s="57"/>
+      <c r="Y3" s="57"/>
+      <c r="Z3" s="57"/>
+      <c r="AA3" s="57"/>
+      <c r="AB3" s="57"/>
+      <c r="AC3" s="57"/>
+      <c r="AD3" s="57"/>
+      <c r="AE3" s="57"/>
+      <c r="AF3" s="57"/>
+      <c r="AG3" s="57"/>
+      <c r="AH3" s="57"/>
+      <c r="AI3" s="57"/>
+      <c r="AJ3" s="65"/>
+      <c r="AK3" s="65"/>
+      <c r="AL3" s="65"/>
+      <c r="AM3" s="65"/>
+      <c r="AN3" s="65"/>
+      <c r="AO3" s="65"/>
+      <c r="AP3" s="65"/>
+      <c r="AQ3" s="65"/>
+      <c r="AR3" s="65"/>
+      <c r="AS3" s="67"/>
+      <c r="AT3" s="67"/>
+      <c r="AU3" s="61"/>
+      <c r="AV3" s="68"/>
+      <c r="AW3" s="63"/>
+      <c r="AX3" s="61"/>
+      <c r="AY3" s="62"/>
+      <c r="AZ3" s="63"/>
+      <c r="BA3" s="61"/>
+      <c r="BB3" s="62"/>
+      <c r="BC3" s="63"/>
+      <c r="BD3" s="61"/>
+      <c r="BE3" s="62"/>
+      <c r="BF3" s="62"/>
+      <c r="BG3" s="63"/>
+      <c r="BH3" s="61"/>
+      <c r="BI3" s="62"/>
+      <c r="BJ3" s="62"/>
+      <c r="BK3" s="63"/>
+      <c r="BL3" s="61"/>
+      <c r="BM3" s="62"/>
+      <c r="BN3" s="63"/>
     </row>
     <row r="4" spans="1:71" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
@@ -1799,11 +1806,15 @@
       <c r="U4" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="V4" s="16"/>
+      <c r="V4" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W4" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="X4" s="16"/>
+      <c r="X4" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="Y4" s="16"/>
       <c r="Z4" s="16"/>
       <c r="AA4" s="16"/>
@@ -1827,10 +1838,10 @@
       <c r="AS4" s="17"/>
       <c r="AT4" s="16"/>
       <c r="AU4" s="18" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AV4" s="37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AW4" s="41">
         <v>46315</v>
@@ -1850,8 +1861,8 @@
       </c>
       <c r="BC4" s="52"/>
       <c r="BD4" s="16"/>
-      <c r="BE4" s="74" t="s">
-        <v>193</v>
+      <c r="BE4" s="54" t="s">
+        <v>191</v>
       </c>
       <c r="BF4" s="16"/>
       <c r="BG4" s="17"/>
@@ -1921,11 +1932,15 @@
       <c r="U5" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="V5" s="16"/>
+      <c r="V5" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W5" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="X5" s="16"/>
+      <c r="X5" s="16" t="s">
+        <v>116</v>
+      </c>
       <c r="Y5" s="16"/>
       <c r="Z5" s="16"/>
       <c r="AA5" s="16"/>
@@ -1949,10 +1964,10 @@
       <c r="AS5" s="17"/>
       <c r="AT5" s="16"/>
       <c r="AU5" s="39" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AV5" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AW5" s="41">
         <v>46307</v>
@@ -1975,7 +1990,7 @@
         <v>46310</v>
       </c>
       <c r="BE5" s="48" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="BF5" s="16"/>
       <c r="BG5" s="17"/>
@@ -2060,11 +2075,15 @@
       <c r="U6" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="V6" s="16"/>
+      <c r="V6" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W6" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="X6" s="16"/>
+      <c r="X6" s="16" t="s">
+        <v>203</v>
+      </c>
       <c r="Y6" s="16"/>
       <c r="Z6" s="16"/>
       <c r="AA6" s="16"/>
@@ -2088,10 +2107,10 @@
       <c r="AS6" s="17"/>
       <c r="AT6" s="16"/>
       <c r="AU6" s="39" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AV6" s="38" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AW6" s="41">
         <v>46315</v>
@@ -2111,8 +2130,8 @@
       </c>
       <c r="BC6" s="17"/>
       <c r="BD6" s="48"/>
-      <c r="BE6" s="74" t="s">
-        <v>194</v>
+      <c r="BE6" s="54" t="s">
+        <v>192</v>
       </c>
       <c r="BF6" s="16"/>
       <c r="BG6" s="17"/>
@@ -2188,11 +2207,15 @@
       <c r="U7" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="V7" s="16"/>
+      <c r="V7" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W7" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="X7" s="16"/>
+      <c r="X7" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="Y7" s="16"/>
       <c r="Z7" s="16"/>
       <c r="AA7" s="16"/>
@@ -2215,11 +2238,15 @@
       <c r="AR7" s="16"/>
       <c r="AS7" s="16"/>
       <c r="AT7" s="16"/>
-      <c r="AU7" s="18"/>
+      <c r="AU7" s="39" t="s">
+        <v>206</v>
+      </c>
       <c r="AV7" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="AW7" s="22"/>
+        <v>169</v>
+      </c>
+      <c r="AW7" s="41">
+        <v>46324</v>
+      </c>
       <c r="AX7" s="19" t="s">
         <v>133</v>
       </c>
@@ -2228,17 +2255,17 @@
       </c>
       <c r="AZ7" s="16"/>
       <c r="BA7" s="50" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="BB7" s="46" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="BC7" s="16"/>
       <c r="BD7" s="47">
         <v>46310</v>
       </c>
       <c r="BE7" s="49" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="BF7" s="16"/>
       <c r="BG7" s="48"/>
@@ -2314,11 +2341,15 @@
       <c r="U8" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="V8" s="16"/>
+      <c r="V8" s="16" t="s">
+        <v>202</v>
+      </c>
       <c r="W8" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="X8" s="16"/>
+      <c r="X8" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="Y8" s="16"/>
       <c r="Z8" s="16"/>
       <c r="AA8" s="16"/>
@@ -2352,15 +2383,15 @@
       </c>
       <c r="AZ8" s="16"/>
       <c r="BA8" s="50" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="BB8" s="46" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="BC8" s="16"/>
       <c r="BD8" s="48"/>
-      <c r="BE8" s="74" t="s">
-        <v>195</v>
+      <c r="BE8" s="54" t="s">
+        <v>193</v>
       </c>
       <c r="BF8" s="16"/>
       <c r="BH8" s="16"/>
@@ -2435,11 +2466,15 @@
       <c r="U9" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="V9" s="16"/>
+      <c r="V9" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W9" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="X9" s="16"/>
+      <c r="X9" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="Y9" s="16"/>
       <c r="Z9" s="16"/>
       <c r="AA9" s="16"/>
@@ -2464,7 +2499,7 @@
       <c r="AT9" s="16"/>
       <c r="AU9" s="18"/>
       <c r="AV9" s="37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AW9" s="20"/>
       <c r="AX9" s="24" t="s">
@@ -2475,15 +2510,15 @@
       </c>
       <c r="AZ9" s="20"/>
       <c r="BA9" s="50" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="BB9" s="46" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="BC9" s="17"/>
       <c r="BD9" s="48"/>
-      <c r="BE9" s="74" t="s">
-        <v>196</v>
+      <c r="BE9" s="54" t="s">
+        <v>194</v>
       </c>
       <c r="BF9" s="16"/>
       <c r="BG9" s="17"/>
@@ -2559,11 +2594,15 @@
       <c r="U10" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="V10" s="16"/>
+      <c r="V10" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W10" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="X10" s="16"/>
+      <c r="X10" s="16" t="s">
+        <v>116</v>
+      </c>
       <c r="Y10" s="16"/>
       <c r="Z10" s="16"/>
       <c r="AA10" s="16"/>
@@ -2597,15 +2636,15 @@
       </c>
       <c r="AZ10" s="17"/>
       <c r="BA10" s="18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="BB10" s="46" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="BC10" s="19"/>
       <c r="BD10" s="48"/>
-      <c r="BE10" s="74" t="s">
-        <v>197</v>
+      <c r="BE10" s="54" t="s">
+        <v>195</v>
       </c>
       <c r="BF10" s="16"/>
       <c r="BG10" s="17"/>
@@ -2681,16 +2720,22 @@
       <c r="U11" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="V11" s="16"/>
+      <c r="V11" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W11" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="X11" s="16"/>
+      <c r="X11" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="Y11" s="16"/>
       <c r="Z11" s="16"/>
       <c r="AA11" s="16"/>
       <c r="AB11" s="16"/>
-      <c r="AC11" s="16"/>
+      <c r="AC11" s="16">
+        <v>5</v>
+      </c>
       <c r="AD11" s="16"/>
       <c r="AE11" s="16"/>
       <c r="AF11" s="16"/>
@@ -2710,7 +2755,7 @@
       <c r="AT11" s="16"/>
       <c r="AU11" s="18"/>
       <c r="AV11" s="37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AW11" s="20"/>
       <c r="AX11" s="29" t="s">
@@ -2721,17 +2766,17 @@
       </c>
       <c r="AZ11" s="17"/>
       <c r="BA11" s="18" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="BB11" s="46" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="BC11" s="19"/>
       <c r="BD11" s="47">
         <v>46310</v>
       </c>
       <c r="BE11" s="48" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="BF11" s="16"/>
       <c r="BG11" s="17"/>
@@ -2809,11 +2854,15 @@
       <c r="U12" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="V12" s="16"/>
+      <c r="V12" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W12" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="X12" s="16"/>
+      <c r="X12" s="16" t="s">
+        <v>203</v>
+      </c>
       <c r="Y12" s="16"/>
       <c r="Z12" s="16"/>
       <c r="AA12" s="16"/>
@@ -2837,10 +2886,10 @@
       <c r="AS12" s="17"/>
       <c r="AT12" s="16"/>
       <c r="AU12" s="18" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AV12" s="37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AW12" s="41">
         <v>46307</v>
@@ -2853,7 +2902,7 @@
       </c>
       <c r="AZ12" s="20"/>
       <c r="BA12" s="18" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="BB12" s="46"/>
       <c r="BC12" s="19"/>
@@ -2861,7 +2910,7 @@
         <v>46315</v>
       </c>
       <c r="BE12" s="49" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="BF12" s="16"/>
       <c r="BG12" s="17"/>
@@ -2937,11 +2986,15 @@
       <c r="U13" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="V13" s="16"/>
+      <c r="V13" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W13" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="X13" s="16"/>
+      <c r="X13" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="Y13" s="16"/>
       <c r="Z13" s="16"/>
       <c r="AA13" s="16"/>
@@ -2965,10 +3018,10 @@
       <c r="AS13" s="17"/>
       <c r="AT13" s="16"/>
       <c r="AU13" s="18" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AV13" s="37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AW13" s="20">
         <v>46314</v>
@@ -2980,16 +3033,18 @@
         <v>147</v>
       </c>
       <c r="AZ13" s="17"/>
-      <c r="BA13" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="BB13" s="46"/>
+      <c r="BA13" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="BB13" s="55" t="s">
+        <v>26</v>
+      </c>
       <c r="BC13" s="17"/>
       <c r="BD13" s="47">
         <v>46315</v>
       </c>
       <c r="BE13" s="48" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="BF13" s="16"/>
       <c r="BG13" s="17"/>
@@ -3065,11 +3120,15 @@
       <c r="U14" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="V14" s="16"/>
+      <c r="V14" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W14" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="X14" s="16"/>
+      <c r="X14" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="Y14" s="16"/>
       <c r="Z14" s="16"/>
       <c r="AA14" s="16"/>
@@ -3094,7 +3153,7 @@
       <c r="AT14" s="16"/>
       <c r="AU14" s="18"/>
       <c r="AV14" s="37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AW14" s="22"/>
       <c r="AX14" s="32" t="s">
@@ -3107,7 +3166,7 @@
         <v>46315</v>
       </c>
       <c r="BA14" s="18" t="s">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="BB14" s="46"/>
       <c r="BC14" s="16"/>
@@ -3115,7 +3174,7 @@
         <v>46310</v>
       </c>
       <c r="BE14" s="48" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="BF14" s="16"/>
       <c r="BG14" s="17"/>
@@ -3191,16 +3250,22 @@
       <c r="U15" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="V15" s="16"/>
+      <c r="V15" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W15" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="X15" s="16"/>
+      <c r="X15" s="16" t="s">
+        <v>203</v>
+      </c>
       <c r="Y15" s="16"/>
       <c r="Z15" s="16"/>
       <c r="AA15" s="16"/>
       <c r="AB15" s="16"/>
-      <c r="AC15" s="16"/>
+      <c r="AC15" s="16">
+        <v>5</v>
+      </c>
       <c r="AD15" s="16"/>
       <c r="AE15" s="16"/>
       <c r="AF15" s="16"/>
@@ -3220,7 +3285,7 @@
       <c r="AT15" s="16"/>
       <c r="AU15" s="18"/>
       <c r="AV15" s="37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AW15" s="17"/>
       <c r="AX15" s="29" t="s">
@@ -3231,17 +3296,17 @@
       </c>
       <c r="AZ15" s="20"/>
       <c r="BA15" s="18" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="BB15" s="46" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="BC15" s="17"/>
       <c r="BD15" s="47">
         <v>46310</v>
       </c>
       <c r="BE15" s="48" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="BF15" s="16"/>
       <c r="BG15" s="17"/>
@@ -3317,11 +3382,15 @@
       <c r="U16" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="V16" s="16"/>
+      <c r="V16" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W16" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="X16" s="16"/>
+      <c r="X16" s="16" t="s">
+        <v>116</v>
+      </c>
       <c r="Y16" s="16"/>
       <c r="Z16" s="16"/>
       <c r="AA16" s="16"/>
@@ -3345,10 +3414,10 @@
       <c r="AS16" s="17"/>
       <c r="AT16" s="16"/>
       <c r="AU16" s="18" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AV16" s="37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AW16" s="41">
         <v>46315</v>
@@ -3368,8 +3437,8 @@
       </c>
       <c r="BC16" s="17"/>
       <c r="BD16" s="48"/>
-      <c r="BE16" s="74" t="s">
-        <v>193</v>
+      <c r="BE16" s="54" t="s">
+        <v>191</v>
       </c>
       <c r="BF16" s="16"/>
       <c r="BG16" s="17"/>
@@ -3445,16 +3514,22 @@
       <c r="U17" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="V17" s="16"/>
+      <c r="V17" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W17" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="X17" s="16"/>
+      <c r="X17" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="Y17" s="16"/>
       <c r="Z17" s="16"/>
       <c r="AA17" s="16"/>
       <c r="AB17" s="16"/>
-      <c r="AC17" s="16"/>
+      <c r="AC17" s="16">
+        <v>3</v>
+      </c>
       <c r="AD17" s="16"/>
       <c r="AE17" s="16"/>
       <c r="AF17" s="16"/>
@@ -3473,10 +3548,10 @@
       <c r="AS17" s="17"/>
       <c r="AT17" s="16"/>
       <c r="AU17" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="AV17" s="38" t="s">
-        <v>171</v>
+        <v>185</v>
+      </c>
+      <c r="AV17" s="37" t="s">
+        <v>169</v>
       </c>
       <c r="AW17" s="41">
         <v>46315</v>
@@ -3494,8 +3569,8 @@
       <c r="BB17" s="46"/>
       <c r="BC17" s="17"/>
       <c r="BD17" s="48"/>
-      <c r="BE17" s="74" t="s">
-        <v>198</v>
+      <c r="BE17" s="54" t="s">
+        <v>196</v>
       </c>
       <c r="BF17" s="16"/>
       <c r="BG17" s="17"/>
@@ -3573,11 +3648,15 @@
       <c r="U18" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="V18" s="16"/>
+      <c r="V18" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W18" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="X18" s="16"/>
+      <c r="X18" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="Y18" s="16"/>
       <c r="Z18" s="16"/>
       <c r="AA18" s="16"/>
@@ -3601,10 +3680,10 @@
       <c r="AS18" s="17"/>
       <c r="AT18" s="16"/>
       <c r="AU18" s="39" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AV18" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AW18" s="41">
         <v>46307</v>
@@ -3622,8 +3701,8 @@
       <c r="BB18" s="46"/>
       <c r="BC18" s="17"/>
       <c r="BD18" s="48"/>
-      <c r="BE18" s="74" t="s">
-        <v>199</v>
+      <c r="BE18" s="48" t="s">
+        <v>181</v>
       </c>
       <c r="BF18" s="16"/>
       <c r="BG18" s="17"/>
@@ -3699,16 +3778,22 @@
       <c r="U19" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="V19" s="16"/>
+      <c r="V19" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W19" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="X19" s="16"/>
+      <c r="X19" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="Y19" s="16"/>
       <c r="Z19" s="16"/>
       <c r="AA19" s="16"/>
       <c r="AB19" s="16"/>
-      <c r="AC19" s="16"/>
+      <c r="AC19" s="16">
+        <v>3</v>
+      </c>
       <c r="AD19" s="16"/>
       <c r="AE19" s="16"/>
       <c r="AF19" s="16"/>
@@ -3727,10 +3812,10 @@
       <c r="AS19" s="17"/>
       <c r="AT19" s="16"/>
       <c r="AU19" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="AV19" s="38" t="s">
-        <v>171</v>
+        <v>185</v>
+      </c>
+      <c r="AV19" s="37" t="s">
+        <v>169</v>
       </c>
       <c r="AW19" s="41">
         <v>46315</v>
@@ -3751,7 +3836,7 @@
         <v>46315</v>
       </c>
       <c r="BE19" s="49" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="BF19" s="16"/>
       <c r="BG19" s="17"/>
@@ -3827,11 +3912,15 @@
       <c r="U20" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="V20" s="16"/>
+      <c r="V20" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W20" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="X20" s="16"/>
+      <c r="X20" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="Y20" s="16"/>
       <c r="Z20" s="16"/>
       <c r="AA20" s="16"/>
@@ -3856,7 +3945,7 @@
       <c r="AT20" s="16"/>
       <c r="AU20" s="18"/>
       <c r="AV20" s="37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AW20" s="20"/>
       <c r="AX20" s="24" t="s">
@@ -3867,15 +3956,15 @@
       </c>
       <c r="AZ20" s="17"/>
       <c r="BA20" s="50" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="BB20" s="46" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="BC20" s="16"/>
       <c r="BD20" s="48"/>
-      <c r="BE20" s="74" t="s">
-        <v>196</v>
+      <c r="BE20" s="54" t="s">
+        <v>194</v>
       </c>
       <c r="BF20" s="16"/>
       <c r="BG20" s="17"/>
@@ -3951,11 +4040,15 @@
       <c r="U21" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="V21" s="16"/>
+      <c r="V21" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W21" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="X21" s="16"/>
+      <c r="X21" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="Y21" s="16"/>
       <c r="Z21" s="16"/>
       <c r="AA21" s="16"/>
@@ -3989,15 +4082,15 @@
       </c>
       <c r="AZ21" s="20"/>
       <c r="BA21" s="50" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="BB21" s="46" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="BC21" s="17"/>
       <c r="BD21" s="48"/>
-      <c r="BE21" s="74" t="s">
-        <v>195</v>
+      <c r="BE21" s="54" t="s">
+        <v>193</v>
       </c>
       <c r="BF21" s="16"/>
       <c r="BG21" s="17"/>
@@ -4073,11 +4166,15 @@
       <c r="U22" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="V22" s="16"/>
+      <c r="V22" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W22" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="X22" s="16"/>
+      <c r="X22" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="Y22" s="16"/>
       <c r="Z22" s="16"/>
       <c r="AA22" s="16"/>
@@ -4119,7 +4216,7 @@
         <v>46315</v>
       </c>
       <c r="BE22" s="48" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="BF22" s="16"/>
       <c r="BG22" s="17"/>
@@ -4195,11 +4292,15 @@
       <c r="U23" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="V23" s="16"/>
+      <c r="V23" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W23" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="X23" s="16"/>
+      <c r="X23" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="Y23" s="16"/>
       <c r="Z23" s="16"/>
       <c r="AA23" s="16"/>
@@ -4239,7 +4340,7 @@
         <v>46315</v>
       </c>
       <c r="BE23" s="48" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="BF23" s="16"/>
       <c r="BG23" s="17"/>
@@ -4315,16 +4416,22 @@
       <c r="U24" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="V24" s="16"/>
+      <c r="V24" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W24" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="X24" s="16"/>
+      <c r="X24" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="Y24" s="16"/>
       <c r="Z24" s="16"/>
       <c r="AA24" s="16"/>
       <c r="AB24" s="16"/>
-      <c r="AC24" s="16"/>
+      <c r="AC24" s="16">
+        <v>5</v>
+      </c>
       <c r="AD24" s="16"/>
       <c r="AE24" s="16"/>
       <c r="AF24" s="16"/>
@@ -4343,10 +4450,10 @@
       <c r="AS24" s="16"/>
       <c r="AT24" s="16"/>
       <c r="AU24" s="39" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AV24" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AW24" s="41">
         <v>46307</v>
@@ -4355,7 +4462,9 @@
         <v>157</v>
       </c>
       <c r="AY24" s="16"/>
-      <c r="AZ24" s="16"/>
+      <c r="AZ24" s="41">
+        <v>46324</v>
+      </c>
       <c r="BA24" s="18" t="s">
         <v>56</v>
       </c>
@@ -4367,7 +4476,7 @@
         <v>46303</v>
       </c>
       <c r="BE24" s="48" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="BF24" s="16"/>
       <c r="BG24" s="16"/>
@@ -4445,11 +4554,15 @@
       <c r="U25" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="V25" s="16"/>
+      <c r="V25" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W25" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="X25" s="16"/>
+      <c r="X25" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="Y25" s="16"/>
       <c r="Z25" s="16"/>
       <c r="AA25" s="16"/>
@@ -4489,7 +4602,7 @@
         <v>46315</v>
       </c>
       <c r="BE25" s="48" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="BF25" s="16"/>
       <c r="BG25" s="17"/>
@@ -4565,11 +4678,15 @@
       <c r="U26" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="V26" s="25"/>
+      <c r="V26" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W26" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="X26" s="25"/>
+      <c r="X26" s="25" t="s">
+        <v>115</v>
+      </c>
       <c r="Y26" s="25"/>
       <c r="Z26" s="25"/>
       <c r="AA26" s="25"/>
@@ -4593,10 +4710,10 @@
       <c r="AS26" s="17"/>
       <c r="AT26" s="25"/>
       <c r="AU26" s="18" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AV26" s="37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AW26" s="20">
         <v>46314</v>
@@ -4608,16 +4725,18 @@
         <v>147</v>
       </c>
       <c r="AZ26" s="17"/>
-      <c r="BA26" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="BB26" s="46"/>
+      <c r="BA26" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="BB26" s="55" t="s">
+        <v>26</v>
+      </c>
       <c r="BC26" s="17"/>
       <c r="BD26" s="47">
         <v>46315</v>
       </c>
       <c r="BE26" s="48" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="BF26" s="16"/>
       <c r="BG26" s="17"/>
@@ -4696,9 +4815,13 @@
       <c r="U27" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="V27" s="25"/>
+      <c r="V27" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W27" s="25"/>
-      <c r="X27" s="26"/>
+      <c r="X27" s="26" t="s">
+        <v>115</v>
+      </c>
       <c r="Y27" s="26"/>
       <c r="Z27" s="26"/>
       <c r="AA27" s="26"/>
@@ -4722,10 +4845,10 @@
       <c r="AS27" s="17"/>
       <c r="AT27" s="26"/>
       <c r="AU27" s="39" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AV27" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AW27" s="41">
         <v>46307</v>
@@ -4745,8 +4868,8 @@
       </c>
       <c r="BC27" s="16"/>
       <c r="BD27" s="48"/>
-      <c r="BE27" s="74" t="s">
-        <v>200</v>
+      <c r="BE27" s="54" t="s">
+        <v>197</v>
       </c>
       <c r="BF27" s="16"/>
       <c r="BG27" s="17"/>
@@ -4824,11 +4947,15 @@
       <c r="U28" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="V28" s="25"/>
+      <c r="V28" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W28" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="X28" s="26"/>
+      <c r="X28" s="26" t="s">
+        <v>115</v>
+      </c>
       <c r="Y28" s="26"/>
       <c r="Z28" s="26"/>
       <c r="AA28" s="26"/>
@@ -4867,8 +4994,8 @@
       <c r="BB28" s="46"/>
       <c r="BC28" s="16"/>
       <c r="BD28" s="48"/>
-      <c r="BE28" s="74" t="s">
-        <v>201</v>
+      <c r="BE28" s="54" t="s">
+        <v>198</v>
       </c>
       <c r="BF28" s="16"/>
       <c r="BG28" s="17"/>
@@ -4938,16 +5065,22 @@
       <c r="U29" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="V29" s="25"/>
+      <c r="V29" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W29" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="X29" s="26"/>
+      <c r="X29" s="26" t="s">
+        <v>115</v>
+      </c>
       <c r="Y29" s="26"/>
       <c r="Z29" s="26"/>
       <c r="AA29" s="26"/>
       <c r="AB29" s="26"/>
-      <c r="AC29" s="26"/>
+      <c r="AC29" s="26">
+        <v>5</v>
+      </c>
       <c r="AD29" s="26"/>
       <c r="AE29" s="26"/>
       <c r="AF29" s="26"/>
@@ -4966,10 +5099,10 @@
       <c r="AS29" s="17"/>
       <c r="AT29" s="26"/>
       <c r="AU29" s="39" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AV29" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AW29" s="41">
         <v>46307</v>
@@ -4978,7 +5111,9 @@
         <v>157</v>
       </c>
       <c r="AY29" s="18"/>
-      <c r="AZ29" s="17"/>
+      <c r="AZ29" s="41">
+        <v>46324</v>
+      </c>
       <c r="BA29" s="18" t="s">
         <v>56</v>
       </c>
@@ -4986,9 +5121,11 @@
         <v>37</v>
       </c>
       <c r="BC29" s="16"/>
-      <c r="BD29" s="48"/>
-      <c r="BE29" s="74" t="s">
-        <v>192</v>
+      <c r="BD29" s="47">
+        <v>46324</v>
+      </c>
+      <c r="BE29" s="54" t="s">
+        <v>190</v>
       </c>
       <c r="BF29" s="16"/>
       <c r="BG29" s="17"/>
@@ -5058,11 +5195,15 @@
       <c r="U30" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="V30" s="25"/>
+      <c r="V30" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W30" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="X30" s="26"/>
+      <c r="X30" s="26" t="s">
+        <v>115</v>
+      </c>
       <c r="Y30" s="26"/>
       <c r="Z30" s="26"/>
       <c r="AA30" s="26"/>
@@ -5086,10 +5227,10 @@
       <c r="AS30" s="17"/>
       <c r="AT30" s="26"/>
       <c r="AU30" s="39" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AV30" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AW30" s="41">
         <v>46307</v>
@@ -5106,9 +5247,11 @@
       </c>
       <c r="BB30" s="46"/>
       <c r="BC30" s="16"/>
-      <c r="BD30" s="48"/>
-      <c r="BE30" s="74" t="s">
-        <v>199</v>
+      <c r="BD30" s="47">
+        <v>46315</v>
+      </c>
+      <c r="BE30" s="48" t="s">
+        <v>181</v>
       </c>
       <c r="BF30" s="16"/>
       <c r="BG30" s="17"/>
@@ -5178,11 +5321,15 @@
       <c r="U31" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="V31" s="25"/>
+      <c r="V31" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W31" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="X31" s="26"/>
+      <c r="X31" s="26" t="s">
+        <v>115</v>
+      </c>
       <c r="Y31" s="26"/>
       <c r="Z31" s="26"/>
       <c r="AA31" s="26"/>
@@ -5205,11 +5352,15 @@
       <c r="AR31" s="26"/>
       <c r="AS31" s="17"/>
       <c r="AT31" s="26"/>
-      <c r="AU31" s="18"/>
+      <c r="AU31" s="39" t="s">
+        <v>206</v>
+      </c>
       <c r="AV31" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="AW31" s="28"/>
+        <v>169</v>
+      </c>
+      <c r="AW31" s="41">
+        <v>46324</v>
+      </c>
       <c r="AX31" s="19" t="s">
         <v>133</v>
       </c>
@@ -5218,17 +5369,17 @@
       </c>
       <c r="AZ31" s="17"/>
       <c r="BA31" s="50" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="BB31" s="46" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="BC31" s="16"/>
       <c r="BD31" s="47">
         <v>46310</v>
       </c>
       <c r="BE31" s="49" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="BF31" s="16"/>
       <c r="BG31" s="17"/>
@@ -5298,11 +5449,15 @@
       <c r="U32" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="V32" s="25"/>
+      <c r="V32" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W32" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="X32" s="26"/>
+      <c r="X32" s="26" t="s">
+        <v>115</v>
+      </c>
       <c r="Y32" s="26"/>
       <c r="Z32" s="26"/>
       <c r="AA32" s="26"/>
@@ -5326,10 +5481,10 @@
       <c r="AS32" s="17"/>
       <c r="AT32" s="26"/>
       <c r="AU32" s="39" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AV32" s="38" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AW32" s="41">
         <v>46315</v>
@@ -5349,8 +5504,8 @@
       </c>
       <c r="BC32" s="16"/>
       <c r="BD32" s="48"/>
-      <c r="BE32" s="74" t="s">
-        <v>194</v>
+      <c r="BE32" s="54" t="s">
+        <v>192</v>
       </c>
       <c r="BF32" s="16"/>
       <c r="BG32" s="17"/>
@@ -5420,11 +5575,15 @@
       <c r="U33" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="V33" s="25"/>
+      <c r="V33" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W33" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="X33" s="26"/>
+      <c r="X33" s="26" t="s">
+        <v>115</v>
+      </c>
       <c r="Y33" s="26"/>
       <c r="Z33" s="26"/>
       <c r="AA33" s="26"/>
@@ -5461,8 +5620,8 @@
       <c r="BB33" s="46"/>
       <c r="BC33" s="16"/>
       <c r="BD33" s="48"/>
-      <c r="BE33" s="74" t="s">
-        <v>202</v>
+      <c r="BE33" s="54" t="s">
+        <v>199</v>
       </c>
       <c r="BF33" s="16"/>
       <c r="BG33" s="17"/>
@@ -5532,11 +5691,15 @@
       <c r="U34" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="V34" s="25"/>
+      <c r="V34" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W34" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="X34" s="26"/>
+      <c r="X34" s="26" t="s">
+        <v>115</v>
+      </c>
       <c r="Y34" s="26"/>
       <c r="Z34" s="26"/>
       <c r="AA34" s="26"/>
@@ -5560,10 +5723,10 @@
       <c r="AS34" s="17"/>
       <c r="AT34" s="26"/>
       <c r="AU34" s="18" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AV34" s="37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AW34" s="41">
         <v>46307</v>
@@ -5576,13 +5739,13 @@
       </c>
       <c r="AZ34" s="17"/>
       <c r="BA34" s="18" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="BB34" s="46"/>
       <c r="BC34" s="16"/>
       <c r="BD34" s="48"/>
-      <c r="BE34" s="74" t="s">
-        <v>203</v>
+      <c r="BE34" s="54" t="s">
+        <v>200</v>
       </c>
       <c r="BF34" s="16"/>
       <c r="BG34" s="17"/>
@@ -5652,11 +5815,15 @@
       <c r="U35" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="V35" s="25"/>
+      <c r="V35" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W35" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="X35" s="26"/>
+      <c r="X35" s="26" t="s">
+        <v>115</v>
+      </c>
       <c r="Y35" s="26"/>
       <c r="Z35" s="26"/>
       <c r="AA35" s="26"/>
@@ -5681,7 +5848,7 @@
       <c r="AT35" s="26"/>
       <c r="AU35" s="18"/>
       <c r="AV35" s="37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AW35" s="28"/>
       <c r="AX35" s="32" t="s">
@@ -5694,7 +5861,7 @@
         <v>46315</v>
       </c>
       <c r="BA35" s="18" t="s">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="BB35" s="46"/>
       <c r="BC35" s="16"/>
@@ -5702,7 +5869,7 @@
         <v>46310</v>
       </c>
       <c r="BE35" s="48" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="BF35" s="16"/>
       <c r="BG35" s="17"/>
@@ -5772,11 +5939,15 @@
       <c r="U36" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="V36" s="25"/>
+      <c r="V36" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W36" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="X36" s="26"/>
+      <c r="X36" s="26" t="s">
+        <v>115</v>
+      </c>
       <c r="Y36" s="26"/>
       <c r="Z36" s="26"/>
       <c r="AA36" s="26"/>
@@ -5816,7 +5987,7 @@
         <v>46315</v>
       </c>
       <c r="BE36" s="48" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="BF36" s="26"/>
       <c r="BG36" s="26"/>
@@ -5888,11 +6059,15 @@
       <c r="U37" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="V37" s="25"/>
+      <c r="V37" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="W37" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="X37" s="26"/>
+      <c r="X37" s="26" t="s">
+        <v>116</v>
+      </c>
       <c r="Y37" s="26"/>
       <c r="Z37" s="26"/>
       <c r="AA37" s="26"/>
@@ -5929,8 +6104,8 @@
       <c r="BB37" s="16"/>
       <c r="BC37" s="16"/>
       <c r="BD37" s="16"/>
-      <c r="BE37" s="74" t="s">
-        <v>204</v>
+      <c r="BE37" s="54" t="s">
+        <v>201</v>
       </c>
       <c r="BF37" s="26"/>
       <c r="BG37" s="26"/>
@@ -5943,57 +6118,57 @@
       <c r="BN37" s="26"/>
     </row>
     <row r="38" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A38" s="67" t="s">
+      <c r="A38" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="B38" s="68"/>
-      <c r="C38" s="68"/>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="68"/>
-      <c r="G38" s="68"/>
-      <c r="H38" s="68"/>
-      <c r="I38" s="68"/>
-      <c r="J38" s="68"/>
-      <c r="K38" s="68"/>
-      <c r="L38" s="68"/>
-      <c r="M38" s="68"/>
-      <c r="N38" s="68"/>
-      <c r="O38" s="68"/>
-      <c r="P38" s="68"/>
-      <c r="Q38" s="68"/>
-      <c r="R38" s="68"/>
-      <c r="S38" s="68"/>
-      <c r="T38" s="68"/>
-      <c r="U38" s="68"/>
-      <c r="V38" s="68"/>
-      <c r="W38" s="68"/>
-      <c r="X38" s="68"/>
-      <c r="Y38" s="68"/>
-      <c r="Z38" s="68"/>
-      <c r="AA38" s="68"/>
-      <c r="AB38" s="68"/>
-      <c r="AC38" s="68"/>
-      <c r="AD38" s="68"/>
-      <c r="AE38" s="68"/>
-      <c r="AF38" s="68"/>
-      <c r="AG38" s="68"/>
-      <c r="AH38" s="68"/>
-      <c r="AI38" s="68"/>
-      <c r="AJ38" s="68"/>
-      <c r="AK38" s="68"/>
-      <c r="AL38" s="68"/>
-      <c r="AM38" s="68"/>
-      <c r="AN38" s="68"/>
-      <c r="AO38" s="68"/>
-      <c r="AP38" s="68"/>
-      <c r="AQ38" s="68"/>
-      <c r="AR38" s="68"/>
-      <c r="AS38" s="68"/>
-      <c r="AT38" s="68"/>
-      <c r="AU38" s="68"/>
-      <c r="AV38" s="68"/>
-      <c r="AW38" s="69"/>
+      <c r="B38" s="70"/>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="70"/>
+      <c r="M38" s="70"/>
+      <c r="N38" s="70"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="70"/>
+      <c r="Q38" s="70"/>
+      <c r="R38" s="70"/>
+      <c r="S38" s="70"/>
+      <c r="T38" s="70"/>
+      <c r="U38" s="70"/>
+      <c r="V38" s="70"/>
+      <c r="W38" s="70"/>
+      <c r="X38" s="70"/>
+      <c r="Y38" s="70"/>
+      <c r="Z38" s="70"/>
+      <c r="AA38" s="70"/>
+      <c r="AB38" s="70"/>
+      <c r="AC38" s="70"/>
+      <c r="AD38" s="70"/>
+      <c r="AE38" s="70"/>
+      <c r="AF38" s="70"/>
+      <c r="AG38" s="70"/>
+      <c r="AH38" s="70"/>
+      <c r="AI38" s="70"/>
+      <c r="AJ38" s="70"/>
+      <c r="AK38" s="70"/>
+      <c r="AL38" s="70"/>
+      <c r="AM38" s="70"/>
+      <c r="AN38" s="70"/>
+      <c r="AO38" s="70"/>
+      <c r="AP38" s="70"/>
+      <c r="AQ38" s="70"/>
+      <c r="AR38" s="70"/>
+      <c r="AS38" s="70"/>
+      <c r="AT38" s="70"/>
+      <c r="AU38" s="70"/>
+      <c r="AV38" s="70"/>
+      <c r="AW38" s="71"/>
       <c r="AX38" s="2"/>
       <c r="AY38" s="2"/>
       <c r="AZ38" s="2"/>
@@ -6019,57 +6194,57 @@
       </c>
     </row>
     <row r="39" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A39" s="70" t="s">
+      <c r="A39" s="72" t="s">
         <v>82</v>
       </c>
-      <c r="B39" s="71"/>
-      <c r="C39" s="71"/>
-      <c r="D39" s="71"/>
-      <c r="E39" s="71"/>
-      <c r="F39" s="71"/>
-      <c r="G39" s="71"/>
-      <c r="H39" s="71"/>
-      <c r="I39" s="71"/>
-      <c r="J39" s="71"/>
-      <c r="K39" s="71"/>
-      <c r="L39" s="71"/>
-      <c r="M39" s="71"/>
-      <c r="N39" s="71"/>
-      <c r="O39" s="71"/>
-      <c r="P39" s="71"/>
-      <c r="Q39" s="71"/>
-      <c r="R39" s="71"/>
-      <c r="S39" s="71"/>
-      <c r="T39" s="71"/>
-      <c r="U39" s="71"/>
-      <c r="V39" s="71"/>
-      <c r="W39" s="71"/>
-      <c r="X39" s="71"/>
-      <c r="Y39" s="71"/>
-      <c r="Z39" s="71"/>
-      <c r="AA39" s="71"/>
-      <c r="AB39" s="71"/>
-      <c r="AC39" s="71"/>
-      <c r="AD39" s="71"/>
-      <c r="AE39" s="71"/>
-      <c r="AF39" s="71"/>
-      <c r="AG39" s="71"/>
-      <c r="AH39" s="71"/>
-      <c r="AI39" s="71"/>
-      <c r="AJ39" s="71"/>
-      <c r="AK39" s="71"/>
-      <c r="AL39" s="71"/>
-      <c r="AM39" s="71"/>
-      <c r="AN39" s="71"/>
-      <c r="AO39" s="71"/>
-      <c r="AP39" s="71"/>
-      <c r="AQ39" s="71"/>
-      <c r="AR39" s="71"/>
-      <c r="AS39" s="71"/>
-      <c r="AT39" s="71"/>
-      <c r="AU39" s="71"/>
-      <c r="AV39" s="71"/>
-      <c r="AW39" s="72"/>
+      <c r="B39" s="73"/>
+      <c r="C39" s="73"/>
+      <c r="D39" s="73"/>
+      <c r="E39" s="73"/>
+      <c r="F39" s="73"/>
+      <c r="G39" s="73"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="73"/>
+      <c r="J39" s="73"/>
+      <c r="K39" s="73"/>
+      <c r="L39" s="73"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="73"/>
+      <c r="O39" s="73"/>
+      <c r="P39" s="73"/>
+      <c r="Q39" s="73"/>
+      <c r="R39" s="73"/>
+      <c r="S39" s="73"/>
+      <c r="T39" s="73"/>
+      <c r="U39" s="73"/>
+      <c r="V39" s="73"/>
+      <c r="W39" s="73"/>
+      <c r="X39" s="73"/>
+      <c r="Y39" s="73"/>
+      <c r="Z39" s="73"/>
+      <c r="AA39" s="73"/>
+      <c r="AB39" s="73"/>
+      <c r="AC39" s="73"/>
+      <c r="AD39" s="73"/>
+      <c r="AE39" s="73"/>
+      <c r="AF39" s="73"/>
+      <c r="AG39" s="73"/>
+      <c r="AH39" s="73"/>
+      <c r="AI39" s="73"/>
+      <c r="AJ39" s="73"/>
+      <c r="AK39" s="73"/>
+      <c r="AL39" s="73"/>
+      <c r="AM39" s="73"/>
+      <c r="AN39" s="73"/>
+      <c r="AO39" s="73"/>
+      <c r="AP39" s="73"/>
+      <c r="AQ39" s="73"/>
+      <c r="AR39" s="73"/>
+      <c r="AS39" s="73"/>
+      <c r="AT39" s="73"/>
+      <c r="AU39" s="73"/>
+      <c r="AV39" s="73"/>
+      <c r="AW39" s="74"/>
       <c r="AX39" s="2"/>
       <c r="AY39" s="2"/>
       <c r="AZ39" s="2"/>
@@ -6364,13 +6539,13 @@
         <v>141</v>
       </c>
       <c r="K42" t="s">
+        <v>168</v>
+      </c>
+      <c r="L42" t="s">
+        <v>167</v>
+      </c>
+      <c r="N42" t="s">
         <v>170</v>
-      </c>
-      <c r="L42" t="s">
-        <v>169</v>
-      </c>
-      <c r="N42" t="s">
-        <v>172</v>
       </c>
       <c r="P42" t="s">
         <v>67</v>
@@ -6379,13 +6554,13 @@
         <v>67</v>
       </c>
       <c r="R42" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="S42" t="s">
         <v>67</v>
       </c>
       <c r="T42" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="U42" t="s">
         <v>67</v>
